--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEE9131-A45A-104C-8B53-7961E0A95E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF2276E-8D1D-D444-8408-2584C794EC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="493">
   <si>
     <t>id</t>
   </si>
@@ -1271,6 +1271,234 @@
   </si>
   <si>
     <t>maristas;GVX;violetas</t>
+  </si>
+  <si>
+    <t>DIS-0048</t>
+  </si>
+  <si>
+    <t>DIS-0049</t>
+  </si>
+  <si>
+    <t>DIS-0050</t>
+  </si>
+  <si>
+    <t>DIS-0051</t>
+  </si>
+  <si>
+    <t>DIS-0052</t>
+  </si>
+  <si>
+    <t>DIS-0053</t>
+  </si>
+  <si>
+    <t>Bordado Etapas GVX</t>
+  </si>
+  <si>
+    <t>Logo GVX local</t>
+  </si>
+  <si>
+    <t>textil;sticker</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2024</t>
+  </si>
+  <si>
+    <t>Camiseta Elegir Vivir Ir (espalda)</t>
+  </si>
+  <si>
+    <t>GVX Verano 2017</t>
+  </si>
+  <si>
+    <t>Volver al origen para empezar de nuevo</t>
+  </si>
+  <si>
+    <t>C_Towers_ProvMediterranea</t>
+  </si>
+  <si>
+    <t>GVX Verano 2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DA VIDA </t>
+  </si>
+  <si>
+    <t>Arturo_MP_Texeira_ProvMediterranea</t>
+  </si>
+  <si>
+    <t>GVX;champagnat;violetas</t>
+  </si>
+  <si>
+    <t>Semana Vocacional</t>
+  </si>
+  <si>
+    <t>Para semana Vocacional Sevilla</t>
+  </si>
+  <si>
+    <t>maristas;educacion;vocacional</t>
+  </si>
+  <si>
+    <t>Posibles camisetas #escuchaaunniño</t>
+  </si>
+  <si>
+    <t>ILU-0057</t>
+  </si>
+  <si>
+    <t>ILU-0058</t>
+  </si>
+  <si>
+    <t>ILU-0059</t>
+  </si>
+  <si>
+    <t>ILU-0060</t>
+  </si>
+  <si>
+    <t>ILU-0061</t>
+  </si>
+  <si>
+    <t>ILU-0062</t>
+  </si>
+  <si>
+    <t>ILU-0063</t>
+  </si>
+  <si>
+    <t>ILU-0064</t>
+  </si>
+  <si>
+    <t>ILU-0065</t>
+  </si>
+  <si>
+    <t>ILU-0066</t>
+  </si>
+  <si>
+    <t>ILU-0067</t>
+  </si>
+  <si>
+    <t>ILU-0068</t>
+  </si>
+  <si>
+    <t>ILU-0069</t>
+  </si>
+  <si>
+    <t>ILU-0070</t>
+  </si>
+  <si>
+    <t>ILU-0071</t>
+  </si>
+  <si>
+    <t>JUMP</t>
+  </si>
+  <si>
+    <t>Jump Walk Dream</t>
+  </si>
+  <si>
+    <t>ProvMediterranea</t>
+  </si>
+  <si>
+    <t>Champagnat 2000+</t>
+  </si>
+  <si>
+    <t>Llamadas</t>
+  </si>
+  <si>
+    <t>maristas;champagnat;vocacional</t>
+  </si>
+  <si>
+    <t>Silueta Champagnat acuarela</t>
+  </si>
+  <si>
+    <t>San Marcelino Champagnat</t>
+  </si>
+  <si>
+    <t>J_Ramos</t>
+  </si>
+  <si>
+    <t>maristas;champagnat;violetas</t>
+  </si>
+  <si>
+    <t>BuenaJente</t>
+  </si>
+  <si>
+    <t>Jesús, el BuenaJente</t>
+  </si>
+  <si>
+    <t>mural;cartel;textil</t>
+  </si>
+  <si>
+    <t>Atardece</t>
+  </si>
+  <si>
+    <t>Quédate con nosotros (de GVX Pascua 2026)</t>
+  </si>
+  <si>
+    <t>Qué te han contado los niños? (ita)</t>
+  </si>
+  <si>
+    <t>Da Vida</t>
+  </si>
+  <si>
+    <t>De GVX Verano 22</t>
+  </si>
+  <si>
+    <t>Futuro</t>
+  </si>
+  <si>
+    <t>Para Semana Vocacional</t>
+  </si>
+  <si>
+    <t>Arturo_MP_J_Ramos</t>
+  </si>
+  <si>
+    <t>maristas;educacion;vocacional;violetas</t>
+  </si>
+  <si>
+    <t>Gente normal (esp)</t>
+  </si>
+  <si>
+    <t>Sencillez</t>
+  </si>
+  <si>
+    <t>Violetas Marist II</t>
+  </si>
+  <si>
+    <t>Los pequeños grandes detalles</t>
+  </si>
+  <si>
+    <t>Voluntariado marista</t>
+  </si>
+  <si>
+    <t>Para formación RRHH Mediterránea</t>
+  </si>
+  <si>
+    <t>Protección de la Infancia</t>
+  </si>
+  <si>
+    <t>Para formación Mediterránea</t>
+  </si>
+  <si>
+    <t>sticker;postal</t>
+  </si>
+  <si>
+    <t>Inspira</t>
+  </si>
+  <si>
+    <t>Ilustrar Interioridad</t>
+  </si>
+  <si>
+    <t>Como Dios</t>
+  </si>
+  <si>
+    <t>Para vivir como Dios,ama, perdona y…</t>
+  </si>
+  <si>
+    <t>ChicaCora</t>
+  </si>
+  <si>
+    <t>Ama (os, te, les)</t>
+  </si>
+  <si>
+    <t>#Soy la 100 II</t>
+  </si>
+  <si>
+    <t>Y salió a buscarla</t>
   </si>
 </sst>
 </file>
@@ -1627,7 +1855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="31.1640625" customWidth="1"/>
@@ -6109,6 +6337,897 @@
         <v>16</v>
       </c>
     </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B105" t="s">
+        <v>423</v>
+      </c>
+      <c r="C105" t="s">
+        <v>424</v>
+      </c>
+      <c r="D105" t="s">
+        <v>90</v>
+      </c>
+      <c r="E105" t="s">
+        <v>33</v>
+      </c>
+      <c r="F105" t="s">
+        <v>32</v>
+      </c>
+      <c r="G105" t="s">
+        <v>270</v>
+      </c>
+      <c r="H105" t="s">
+        <v>415</v>
+      </c>
+      <c r="I105" t="s">
+        <v>167</v>
+      </c>
+      <c r="J105" t="s">
+        <v>425</v>
+      </c>
+      <c r="K105" t="s">
+        <v>55</v>
+      </c>
+      <c r="L105" t="s">
+        <v>14</v>
+      </c>
+      <c r="M105" t="s">
+        <v>15</v>
+      </c>
+      <c r="N105" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B106" t="s">
+        <v>426</v>
+      </c>
+      <c r="C106" t="s">
+        <v>427</v>
+      </c>
+      <c r="D106" t="s">
+        <v>90</v>
+      </c>
+      <c r="E106" t="s">
+        <v>58</v>
+      </c>
+      <c r="F106" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" t="s">
+        <v>332</v>
+      </c>
+      <c r="H106" t="s">
+        <v>327</v>
+      </c>
+      <c r="J106" t="s">
+        <v>233</v>
+      </c>
+      <c r="K106" t="s">
+        <v>55</v>
+      </c>
+      <c r="L106" t="s">
+        <v>14</v>
+      </c>
+      <c r="M106" t="s">
+        <v>15</v>
+      </c>
+      <c r="N106" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B107" t="s">
+        <v>428</v>
+      </c>
+      <c r="C107" t="s">
+        <v>429</v>
+      </c>
+      <c r="D107" t="s">
+        <v>90</v>
+      </c>
+      <c r="E107" t="s">
+        <v>58</v>
+      </c>
+      <c r="F107" t="s">
+        <v>32</v>
+      </c>
+      <c r="G107" t="s">
+        <v>430</v>
+      </c>
+      <c r="H107" t="s">
+        <v>415</v>
+      </c>
+      <c r="I107" t="s">
+        <v>87</v>
+      </c>
+      <c r="J107" t="s">
+        <v>233</v>
+      </c>
+      <c r="K107" t="s">
+        <v>55</v>
+      </c>
+      <c r="L107" t="s">
+        <v>14</v>
+      </c>
+      <c r="M107" t="s">
+        <v>15</v>
+      </c>
+      <c r="N107" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B108" t="s">
+        <v>431</v>
+      </c>
+      <c r="C108" t="s">
+        <v>432</v>
+      </c>
+      <c r="D108" t="s">
+        <v>90</v>
+      </c>
+      <c r="E108" t="s">
+        <v>33</v>
+      </c>
+      <c r="F108" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" t="s">
+        <v>433</v>
+      </c>
+      <c r="H108" t="s">
+        <v>434</v>
+      </c>
+      <c r="J108" t="s">
+        <v>233</v>
+      </c>
+      <c r="K108" t="s">
+        <v>55</v>
+      </c>
+      <c r="L108" t="s">
+        <v>14</v>
+      </c>
+      <c r="M108" t="s">
+        <v>15</v>
+      </c>
+      <c r="N108" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B109" t="s">
+        <v>435</v>
+      </c>
+      <c r="C109" t="s">
+        <v>436</v>
+      </c>
+      <c r="D109" t="s">
+        <v>90</v>
+      </c>
+      <c r="E109" t="s">
+        <v>58</v>
+      </c>
+      <c r="F109" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" t="s">
+        <v>178</v>
+      </c>
+      <c r="H109" t="s">
+        <v>437</v>
+      </c>
+      <c r="J109" t="s">
+        <v>183</v>
+      </c>
+      <c r="K109" t="s">
+        <v>55</v>
+      </c>
+      <c r="L109" t="s">
+        <v>14</v>
+      </c>
+      <c r="M109" t="s">
+        <v>15</v>
+      </c>
+      <c r="N109" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B110" t="s">
+        <v>469</v>
+      </c>
+      <c r="C110" t="s">
+        <v>438</v>
+      </c>
+      <c r="D110" t="s">
+        <v>90</v>
+      </c>
+      <c r="E110" t="s">
+        <v>58</v>
+      </c>
+      <c r="F110" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" t="s">
+        <v>178</v>
+      </c>
+      <c r="H110" t="s">
+        <v>248</v>
+      </c>
+      <c r="I110" t="s">
+        <v>87</v>
+      </c>
+      <c r="J110" t="s">
+        <v>233</v>
+      </c>
+      <c r="K110" t="s">
+        <v>55</v>
+      </c>
+      <c r="L110" t="s">
+        <v>14</v>
+      </c>
+      <c r="M110" t="s">
+        <v>15</v>
+      </c>
+      <c r="N110" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B111" t="s">
+        <v>454</v>
+      </c>
+      <c r="C111" t="s">
+        <v>455</v>
+      </c>
+      <c r="D111" t="s">
+        <v>54</v>
+      </c>
+      <c r="E111" t="s">
+        <v>58</v>
+      </c>
+      <c r="F111" t="s">
+        <v>32</v>
+      </c>
+      <c r="G111" t="s">
+        <v>456</v>
+      </c>
+      <c r="H111" t="s">
+        <v>437</v>
+      </c>
+      <c r="I111" t="s">
+        <v>252</v>
+      </c>
+      <c r="J111" t="s">
+        <v>242</v>
+      </c>
+      <c r="K111" t="s">
+        <v>55</v>
+      </c>
+      <c r="L111" t="s">
+        <v>14</v>
+      </c>
+      <c r="M111" t="s">
+        <v>15</v>
+      </c>
+      <c r="N111" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B112" t="s">
+        <v>457</v>
+      </c>
+      <c r="C112" t="s">
+        <v>458</v>
+      </c>
+      <c r="D112" t="s">
+        <v>54</v>
+      </c>
+      <c r="E112" t="s">
+        <v>33</v>
+      </c>
+      <c r="F112" t="s">
+        <v>32</v>
+      </c>
+      <c r="G112" t="s">
+        <v>182</v>
+      </c>
+      <c r="H112" t="s">
+        <v>459</v>
+      </c>
+      <c r="J112" t="s">
+        <v>109</v>
+      </c>
+      <c r="K112" t="s">
+        <v>57</v>
+      </c>
+      <c r="L112" t="s">
+        <v>14</v>
+      </c>
+      <c r="M112" t="s">
+        <v>15</v>
+      </c>
+      <c r="N112" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B113" t="s">
+        <v>461</v>
+      </c>
+      <c r="C113" t="s">
+        <v>460</v>
+      </c>
+      <c r="D113" t="s">
+        <v>54</v>
+      </c>
+      <c r="E113" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" t="s">
+        <v>32</v>
+      </c>
+      <c r="G113" t="s">
+        <v>462</v>
+      </c>
+      <c r="H113" t="s">
+        <v>463</v>
+      </c>
+      <c r="I113" t="s">
+        <v>61</v>
+      </c>
+      <c r="J113" t="s">
+        <v>183</v>
+      </c>
+      <c r="K113" t="s">
+        <v>55</v>
+      </c>
+      <c r="L113" t="s">
+        <v>14</v>
+      </c>
+      <c r="M113" t="s">
+        <v>15</v>
+      </c>
+      <c r="N113" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B114" t="s">
+        <v>464</v>
+      </c>
+      <c r="C114" t="s">
+        <v>465</v>
+      </c>
+      <c r="D114" t="s">
+        <v>54</v>
+      </c>
+      <c r="E114" t="s">
+        <v>140</v>
+      </c>
+      <c r="F114" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" t="s">
+        <v>332</v>
+      </c>
+      <c r="H114" t="s">
+        <v>327</v>
+      </c>
+      <c r="J114" t="s">
+        <v>466</v>
+      </c>
+      <c r="K114" t="s">
+        <v>55</v>
+      </c>
+      <c r="L114" t="s">
+        <v>14</v>
+      </c>
+      <c r="M114" t="s">
+        <v>15</v>
+      </c>
+      <c r="N114" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B115" t="s">
+        <v>467</v>
+      </c>
+      <c r="C115" t="s">
+        <v>468</v>
+      </c>
+      <c r="D115" t="s">
+        <v>54</v>
+      </c>
+      <c r="E115" t="s">
+        <v>33</v>
+      </c>
+      <c r="F115" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" t="s">
+        <v>332</v>
+      </c>
+      <c r="H115" t="s">
+        <v>327</v>
+      </c>
+      <c r="I115" t="s">
+        <v>87</v>
+      </c>
+      <c r="J115" t="s">
+        <v>242</v>
+      </c>
+      <c r="K115" t="s">
+        <v>55</v>
+      </c>
+      <c r="L115" t="s">
+        <v>14</v>
+      </c>
+      <c r="M115" t="s">
+        <v>15</v>
+      </c>
+      <c r="N115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B116" t="s">
+        <v>470</v>
+      </c>
+      <c r="C116" t="s">
+        <v>471</v>
+      </c>
+      <c r="D116" t="s">
+        <v>54</v>
+      </c>
+      <c r="E116" t="s">
+        <v>58</v>
+      </c>
+      <c r="F116" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" t="s">
+        <v>334</v>
+      </c>
+      <c r="H116" t="s">
+        <v>415</v>
+      </c>
+      <c r="I116" t="s">
+        <v>177</v>
+      </c>
+      <c r="J116" t="s">
+        <v>348</v>
+      </c>
+      <c r="K116" t="s">
+        <v>55</v>
+      </c>
+      <c r="L116" t="s">
+        <v>14</v>
+      </c>
+      <c r="M116" t="s">
+        <v>15</v>
+      </c>
+      <c r="N116" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B117" t="s">
+        <v>472</v>
+      </c>
+      <c r="C117" t="s">
+        <v>473</v>
+      </c>
+      <c r="D117" t="s">
+        <v>54</v>
+      </c>
+      <c r="E117" t="s">
+        <v>33</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" t="s">
+        <v>474</v>
+      </c>
+      <c r="H117" t="s">
+        <v>475</v>
+      </c>
+      <c r="J117" t="s">
+        <v>183</v>
+      </c>
+      <c r="K117" t="s">
+        <v>55</v>
+      </c>
+      <c r="L117" t="s">
+        <v>14</v>
+      </c>
+      <c r="M117" t="s">
+        <v>15</v>
+      </c>
+      <c r="N117" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B118" t="s">
+        <v>476</v>
+      </c>
+      <c r="C118" t="s">
+        <v>477</v>
+      </c>
+      <c r="D118" t="s">
+        <v>54</v>
+      </c>
+      <c r="E118" t="s">
+        <v>58</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" t="s">
+        <v>178</v>
+      </c>
+      <c r="H118" t="s">
+        <v>232</v>
+      </c>
+      <c r="J118" t="s">
+        <v>222</v>
+      </c>
+      <c r="K118" t="s">
+        <v>55</v>
+      </c>
+      <c r="L118" t="s">
+        <v>14</v>
+      </c>
+      <c r="M118" t="s">
+        <v>15</v>
+      </c>
+      <c r="N118" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B119" t="s">
+        <v>478</v>
+      </c>
+      <c r="C119" t="s">
+        <v>479</v>
+      </c>
+      <c r="D119" t="s">
+        <v>54</v>
+      </c>
+      <c r="E119" t="s">
+        <v>33</v>
+      </c>
+      <c r="F119" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" t="s">
+        <v>270</v>
+      </c>
+      <c r="H119" t="s">
+        <v>232</v>
+      </c>
+      <c r="I119" t="s">
+        <v>62</v>
+      </c>
+      <c r="J119" t="s">
+        <v>222</v>
+      </c>
+      <c r="K119" t="s">
+        <v>55</v>
+      </c>
+      <c r="L119" t="s">
+        <v>14</v>
+      </c>
+      <c r="M119" t="s">
+        <v>15</v>
+      </c>
+      <c r="N119" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B120" t="s">
+        <v>480</v>
+      </c>
+      <c r="C120" t="s">
+        <v>481</v>
+      </c>
+      <c r="D120" t="s">
+        <v>54</v>
+      </c>
+      <c r="E120" t="s">
+        <v>58</v>
+      </c>
+      <c r="F120" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" t="s">
+        <v>332</v>
+      </c>
+      <c r="H120" t="s">
+        <v>248</v>
+      </c>
+      <c r="J120" t="s">
+        <v>484</v>
+      </c>
+      <c r="K120" t="s">
+        <v>55</v>
+      </c>
+      <c r="L120" t="s">
+        <v>14</v>
+      </c>
+      <c r="M120" t="s">
+        <v>15</v>
+      </c>
+      <c r="N120" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B121" t="s">
+        <v>482</v>
+      </c>
+      <c r="C121" t="s">
+        <v>483</v>
+      </c>
+      <c r="D121" t="s">
+        <v>54</v>
+      </c>
+      <c r="E121" t="s">
+        <v>58</v>
+      </c>
+      <c r="F121" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121" t="s">
+        <v>178</v>
+      </c>
+      <c r="H121" t="s">
+        <v>127</v>
+      </c>
+      <c r="J121" t="s">
+        <v>484</v>
+      </c>
+      <c r="K121" t="s">
+        <v>55</v>
+      </c>
+      <c r="L121" t="s">
+        <v>14</v>
+      </c>
+      <c r="M121" t="s">
+        <v>15</v>
+      </c>
+      <c r="N121" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B122" t="s">
+        <v>485</v>
+      </c>
+      <c r="C122" t="s">
+        <v>486</v>
+      </c>
+      <c r="D122" t="s">
+        <v>54</v>
+      </c>
+      <c r="E122" t="s">
+        <v>140</v>
+      </c>
+      <c r="F122" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" t="s">
+        <v>178</v>
+      </c>
+      <c r="H122" t="s">
+        <v>248</v>
+      </c>
+      <c r="I122" t="s">
+        <v>62</v>
+      </c>
+      <c r="J122" t="s">
+        <v>222</v>
+      </c>
+      <c r="K122" t="s">
+        <v>55</v>
+      </c>
+      <c r="L122" t="s">
+        <v>14</v>
+      </c>
+      <c r="M122" t="s">
+        <v>15</v>
+      </c>
+      <c r="N122" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B123" t="s">
+        <v>487</v>
+      </c>
+      <c r="C123" t="s">
+        <v>488</v>
+      </c>
+      <c r="D123" t="s">
+        <v>54</v>
+      </c>
+      <c r="E123" t="s">
+        <v>58</v>
+      </c>
+      <c r="F123" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" t="s">
+        <v>272</v>
+      </c>
+      <c r="H123" t="s">
+        <v>342</v>
+      </c>
+      <c r="J123" t="s">
+        <v>221</v>
+      </c>
+      <c r="K123" t="s">
+        <v>55</v>
+      </c>
+      <c r="L123" t="s">
+        <v>14</v>
+      </c>
+      <c r="M123" t="s">
+        <v>15</v>
+      </c>
+      <c r="N123" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B124" t="s">
+        <v>489</v>
+      </c>
+      <c r="C124" t="s">
+        <v>490</v>
+      </c>
+      <c r="D124" t="s">
+        <v>54</v>
+      </c>
+      <c r="E124" t="s">
+        <v>140</v>
+      </c>
+      <c r="F124" t="s">
+        <v>32</v>
+      </c>
+      <c r="G124" t="s">
+        <v>269</v>
+      </c>
+      <c r="H124" t="s">
+        <v>253</v>
+      </c>
+      <c r="I124" t="s">
+        <v>62</v>
+      </c>
+      <c r="J124" t="s">
+        <v>222</v>
+      </c>
+      <c r="K124" t="s">
+        <v>55</v>
+      </c>
+      <c r="L124" t="s">
+        <v>14</v>
+      </c>
+      <c r="M124" t="s">
+        <v>15</v>
+      </c>
+      <c r="N124" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B125" t="s">
+        <v>492</v>
+      </c>
+      <c r="C125" t="s">
+        <v>491</v>
+      </c>
+      <c r="D125" t="s">
+        <v>54</v>
+      </c>
+      <c r="E125" t="s">
+        <v>33</v>
+      </c>
+      <c r="F125" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" t="s">
+        <v>272</v>
+      </c>
+      <c r="H125" t="s">
+        <v>342</v>
+      </c>
+      <c r="J125" t="s">
+        <v>242</v>
+      </c>
+      <c r="K125" t="s">
+        <v>55</v>
+      </c>
+      <c r="L125" t="s">
+        <v>14</v>
+      </c>
+      <c r="M125" t="s">
+        <v>15</v>
+      </c>
+      <c r="N125" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF2276E-8D1D-D444-8408-2584C794EC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5833C9D-90F9-F848-B85A-D3DEC99093A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="517">
   <si>
     <t>id</t>
   </si>
@@ -445,18 +445,12 @@
     <t>figura</t>
   </si>
   <si>
-    <t>maria;maristas;violetas</t>
-  </si>
-  <si>
     <t>María II</t>
   </si>
   <si>
     <t>Maria Niña (I love Jesus)</t>
   </si>
   <si>
-    <t>maria;maristas;paz</t>
-  </si>
-  <si>
     <t>María, Buena Madre I</t>
   </si>
   <si>
@@ -805,15 +799,9 @@
     <t>3 Violetas II</t>
   </si>
   <si>
-    <t>Las tres violetas</t>
-  </si>
-  <si>
     <t>3 Violetas III BN</t>
   </si>
   <si>
-    <t xml:space="preserve">Las 3 violetas </t>
-  </si>
-  <si>
     <t>3 Violetas III color</t>
   </si>
   <si>
@@ -934,18 +922,12 @@
     <t>Un mismo agua</t>
   </si>
   <si>
-    <t>Para convivencia GVX</t>
-  </si>
-  <si>
     <t>ILU-0046</t>
   </si>
   <si>
     <t>Vayamos al Fondo</t>
   </si>
   <si>
-    <t>Para convivencia GVX II</t>
-  </si>
-  <si>
     <t>ILU-0047</t>
   </si>
   <si>
@@ -1009,9 +991,6 @@
     <t>sticker;taza;rrss</t>
   </si>
   <si>
-    <t>Change &gt; Chance</t>
-  </si>
-  <si>
     <t>Para Asamblea Mediterránea</t>
   </si>
   <si>
@@ -1150,9 +1129,6 @@
     <t>VI Jornadas Educadores Maristas</t>
   </si>
   <si>
-    <t>Cartel 2025 Jornadas Mediterránea</t>
-  </si>
-  <si>
     <t>Eucaristía</t>
   </si>
   <si>
@@ -1165,9 +1141,6 @@
     <t>IV Jornadas Educadores Maristas</t>
   </si>
   <si>
-    <t>Cartel 2022 Jornadas Mediterránea</t>
-  </si>
-  <si>
     <t>El mundo, la mejor cocina</t>
   </si>
   <si>
@@ -1499,6 +1472,105 @@
   </si>
   <si>
     <t>Y salió a buscarla</t>
+  </si>
+  <si>
+    <t>ILU-0072</t>
+  </si>
+  <si>
+    <t>ILU-0073</t>
+  </si>
+  <si>
+    <t>ILU-0074</t>
+  </si>
+  <si>
+    <t>ILU-0075</t>
+  </si>
+  <si>
+    <t>ILU-0076</t>
+  </si>
+  <si>
+    <t>Atardece II</t>
+  </si>
+  <si>
+    <t>#accesoeducativo Todos con cole</t>
+  </si>
+  <si>
+    <t>Buena Madre II</t>
+  </si>
+  <si>
+    <t>Silueta María, Buena Madre</t>
+  </si>
+  <si>
+    <t>Anagrama María</t>
+  </si>
+  <si>
+    <t>Basado en antiguo anagrama edificio</t>
+  </si>
+  <si>
+    <t>Quien no ama…</t>
+  </si>
+  <si>
+    <t>Para educar es preciso amar</t>
+  </si>
+  <si>
+    <t>maristas;champagnat;educacion</t>
+  </si>
+  <si>
+    <t>Escuchas?</t>
+  </si>
+  <si>
+    <t>Hasta en la brisa</t>
+  </si>
+  <si>
+    <t>evangelio;vocacional</t>
+  </si>
+  <si>
+    <t>DIS-0054</t>
+  </si>
+  <si>
+    <t>DIS-0055</t>
+  </si>
+  <si>
+    <t>Ceda el paso y sígalos</t>
+  </si>
+  <si>
+    <t>Para Viaje a Belén Maristas Jaén</t>
+  </si>
+  <si>
+    <t>maristas;evangelio;educacion</t>
+  </si>
+  <si>
+    <t>Para convivencia Marcha GVX</t>
+  </si>
+  <si>
+    <t>Para convivencia Marcha GVX II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuestras 3 violetas </t>
+  </si>
+  <si>
+    <t>Change &lt; &gt; Chance</t>
+  </si>
+  <si>
+    <t>Cartel 2025 Mediterránea</t>
+  </si>
+  <si>
+    <t>Cartel 2022 Mediterránea</t>
+  </si>
+  <si>
+    <t>Recordando al Hno Boni FQ</t>
+  </si>
+  <si>
+    <t>Excusas yo?</t>
+  </si>
+  <si>
+    <t>maria;violetas</t>
+  </si>
+  <si>
+    <t>maria;paz</t>
+  </si>
+  <si>
+    <t>sin_fondo;minimalista</t>
   </si>
 </sst>
 </file>
@@ -1855,7 +1927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N125"/>
+  <dimension ref="A1:N132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="31.1640625" customWidth="1"/>
@@ -1918,10 +1990,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D2" t="s">
         <v>54</v>
@@ -1933,13 +2005,13 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H2" t="s">
         <v>84</v>
       </c>
       <c r="I2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -1962,7 +2034,7 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D3" t="s">
         <v>54</v>
@@ -1974,7 +2046,7 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H3" t="s">
         <v>28</v>
@@ -2015,7 +2087,7 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H4" t="s">
         <v>28</v>
@@ -2103,7 +2175,7 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H6" t="s">
         <v>28</v>
@@ -2144,7 +2216,7 @@
         <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H7" t="s">
         <v>59</v>
@@ -2173,7 +2245,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -2229,7 +2301,7 @@
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H9" t="s">
         <v>28</v>
@@ -2273,7 +2345,7 @@
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H10" t="s">
         <v>28</v>
@@ -2317,7 +2389,7 @@
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H11" t="s">
         <v>28</v>
@@ -2361,7 +2433,7 @@
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H12" t="s">
         <v>28</v>
@@ -2405,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H13" t="s">
         <v>28</v>
@@ -2414,7 +2486,7 @@
         <v>61</v>
       </c>
       <c r="J13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
@@ -2449,7 +2521,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H14" t="s">
         <v>28</v>
@@ -2493,7 +2565,7 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H15" t="s">
         <v>81</v>
@@ -2537,7 +2609,7 @@
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H16" t="s">
         <v>28</v>
@@ -2590,7 +2662,7 @@
         <v>62</v>
       </c>
       <c r="J17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K17" t="s">
         <v>55</v>
@@ -2631,7 +2703,7 @@
         <v>85</v>
       </c>
       <c r="J18" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K18" t="s">
         <v>55</v>
@@ -2792,7 +2864,7 @@
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H22" t="s">
         <v>28</v>
@@ -2801,7 +2873,7 @@
         <v>62</v>
       </c>
       <c r="J22" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K22" t="s">
         <v>55</v>
@@ -2836,7 +2908,7 @@
         <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H23" t="s">
         <v>59</v>
@@ -2845,7 +2917,7 @@
         <v>62</v>
       </c>
       <c r="J23" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K23" t="s">
         <v>55</v>
@@ -2921,10 +2993,10 @@
         <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H25" t="s">
-        <v>141</v>
+        <v>514</v>
       </c>
       <c r="J25" t="s">
         <v>88</v>
@@ -2947,10 +3019,10 @@
         <v>132</v>
       </c>
       <c r="B26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" t="s">
         <v>142</v>
-      </c>
-      <c r="C26" t="s">
-        <v>143</v>
       </c>
       <c r="D26" t="s">
         <v>54</v>
@@ -2962,10 +3034,10 @@
         <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H26" t="s">
-        <v>144</v>
+        <v>515</v>
       </c>
       <c r="J26" t="s">
         <v>109</v>
@@ -2988,10 +3060,10 @@
         <v>133</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D27" t="s">
         <v>54</v>
@@ -3003,10 +3075,10 @@
         <v>32</v>
       </c>
       <c r="G27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J27" t="s">
         <v>88</v>
@@ -3029,10 +3101,10 @@
         <v>134</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
         <v>54</v>
@@ -3044,16 +3116,16 @@
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H28" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I28" t="s">
         <v>62</v>
       </c>
       <c r="J28" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K28" t="s">
         <v>56</v>
@@ -3073,10 +3145,10 @@
         <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
         <v>54</v>
@@ -3091,7 +3163,7 @@
         <v>102</v>
       </c>
       <c r="H29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J29" t="s">
         <v>88</v>
@@ -3114,10 +3186,10 @@
         <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C30" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D30" t="s">
         <v>54</v>
@@ -3129,10 +3201,10 @@
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J30" t="s">
         <v>109</v>
@@ -3155,10 +3227,10 @@
         <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D31" t="s">
         <v>54</v>
@@ -3170,10 +3242,10 @@
         <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H31" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J31" t="s">
         <v>109</v>
@@ -3193,13 +3265,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" t="s">
         <v>168</v>
       </c>
-      <c r="B32" t="s">
-        <v>170</v>
-      </c>
       <c r="C32" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D32" t="s">
         <v>54</v>
@@ -3211,10 +3283,10 @@
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H32" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J32" t="s">
         <v>109</v>
@@ -3234,13 +3306,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D33" t="s">
         <v>54</v>
@@ -3252,10 +3324,10 @@
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H33" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="J33" t="s">
         <v>109</v>
@@ -3275,13 +3347,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" t="s">
         <v>174</v>
-      </c>
-      <c r="B34" t="s">
-        <v>175</v>
-      </c>
-      <c r="C34" t="s">
-        <v>176</v>
       </c>
       <c r="D34" t="s">
         <v>54</v>
@@ -3296,13 +3368,13 @@
         <v>102</v>
       </c>
       <c r="H34" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J34" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K34" t="s">
         <v>55</v>
@@ -3319,7 +3391,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s">
         <v>29</v>
@@ -3337,7 +3409,7 @@
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H35" t="s">
         <v>84</v>
@@ -3363,7 +3435,7 @@
         <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C36" t="s">
         <v>71</v>
@@ -3378,7 +3450,7 @@
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H36" t="s">
         <v>35</v>
@@ -3387,7 +3459,7 @@
         <v>110</v>
       </c>
       <c r="J36" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K36" t="s">
         <v>55</v>
@@ -3422,7 +3494,7 @@
         <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H37" t="s">
         <v>28</v>
@@ -3451,7 +3523,7 @@
         <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C38" t="s">
         <v>74</v>
@@ -3466,7 +3538,7 @@
         <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H38" t="s">
         <v>35</v>
@@ -3475,7 +3547,7 @@
         <v>107</v>
       </c>
       <c r="J38" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K38" t="s">
         <v>55</v>
@@ -3498,7 +3570,7 @@
         <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D39" t="s">
         <v>90</v>
@@ -3510,7 +3582,7 @@
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H39" t="s">
         <v>82</v>
@@ -3583,7 +3655,7 @@
         <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D41" t="s">
         <v>90</v>
@@ -3595,13 +3667,13 @@
         <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H41" t="s">
         <v>28</v>
       </c>
       <c r="J41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K41" t="s">
         <v>55</v>
@@ -3636,7 +3708,7 @@
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H42" t="s">
         <v>83</v>
@@ -3645,7 +3717,7 @@
         <v>87</v>
       </c>
       <c r="J42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K42" t="s">
         <v>55</v>
@@ -3680,7 +3752,7 @@
         <v>32</v>
       </c>
       <c r="G43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H43" t="s">
         <v>28</v>
@@ -3689,7 +3761,7 @@
         <v>107</v>
       </c>
       <c r="J43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K43" t="s">
         <v>55</v>
@@ -3706,13 +3778,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
         <v>90</v>
@@ -3724,16 +3796,16 @@
         <v>32</v>
       </c>
       <c r="G44" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H44" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I44" t="s">
         <v>87</v>
       </c>
       <c r="J44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K44" t="s">
         <v>55</v>
@@ -3750,13 +3822,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B45" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
         <v>90</v>
@@ -3768,10 +3840,10 @@
         <v>32</v>
       </c>
       <c r="G45" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H45" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I45" t="s">
         <v>87</v>
@@ -3794,13 +3866,13 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B46" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D46" t="s">
         <v>90</v>
@@ -3812,16 +3884,16 @@
         <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H46" t="s">
         <v>127</v>
       </c>
       <c r="I46" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K46" t="s">
         <v>55</v>
@@ -3838,13 +3910,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B47" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C47" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D47" t="s">
         <v>90</v>
@@ -3856,13 +3928,13 @@
         <v>13</v>
       </c>
       <c r="G47" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H47" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J47" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K47" t="s">
         <v>55</v>
@@ -3879,13 +3951,13 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C48" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D48" t="s">
         <v>90</v>
@@ -3897,16 +3969,16 @@
         <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H48" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I48" t="s">
         <v>87</v>
       </c>
       <c r="J48" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K48" t="s">
         <v>55</v>
@@ -3923,13 +3995,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B49" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C49" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D49" t="s">
         <v>90</v>
@@ -3941,13 +4013,13 @@
         <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H49" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J49" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K49" t="s">
         <v>55</v>
@@ -3964,13 +4036,13 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D50" t="s">
         <v>90</v>
@@ -3982,16 +4054,16 @@
         <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H50" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I50" t="s">
         <v>87</v>
       </c>
       <c r="J50" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K50" t="s">
         <v>55</v>
@@ -4008,13 +4080,13 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C51" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D51" t="s">
         <v>90</v>
@@ -4026,16 +4098,16 @@
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H51" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I51" t="s">
         <v>87</v>
       </c>
       <c r="J51" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K51" t="s">
         <v>55</v>
@@ -4052,13 +4124,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B52" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C52" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D52" t="s">
         <v>90</v>
@@ -4070,13 +4142,13 @@
         <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H52" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="J52" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K52" t="s">
         <v>55</v>
@@ -4093,13 +4165,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B53" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C53" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D53" t="s">
         <v>90</v>
@@ -4111,13 +4183,13 @@
         <v>13</v>
       </c>
       <c r="G53" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H53" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J53" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K53" t="s">
         <v>55</v>
@@ -4134,13 +4206,13 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B54" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C54" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D54" t="s">
         <v>90</v>
@@ -4152,16 +4224,16 @@
         <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H54" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I54" t="s">
         <v>87</v>
       </c>
       <c r="J54" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K54" t="s">
         <v>55</v>
@@ -4178,13 +4250,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C55" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D55" t="s">
         <v>90</v>
@@ -4196,16 +4268,16 @@
         <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H55" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I55" t="s">
         <v>87</v>
       </c>
       <c r="J55" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -4222,13 +4294,13 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B56" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C56" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D56" t="s">
         <v>90</v>
@@ -4240,16 +4312,16 @@
         <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H56" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I56" t="s">
         <v>87</v>
       </c>
       <c r="J56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K56" t="s">
         <v>55</v>
@@ -4266,13 +4338,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B57" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C57" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D57" t="s">
         <v>90</v>
@@ -4284,16 +4356,16 @@
         <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H57" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I57" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J57" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K57" t="s">
         <v>55</v>
@@ -4310,13 +4382,13 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B58" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C58" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D58" t="s">
         <v>90</v>
@@ -4328,16 +4400,16 @@
         <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H58" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I58" t="s">
         <v>87</v>
       </c>
       <c r="J58" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K58" t="s">
         <v>55</v>
@@ -4354,13 +4426,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B59" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C59" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D59" t="s">
         <v>54</v>
@@ -4372,16 +4444,16 @@
         <v>13</v>
       </c>
       <c r="G59" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H59" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I59" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J59" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K59" t="s">
         <v>55</v>
@@ -4398,13 +4470,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B60" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C60" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D60" t="s">
         <v>54</v>
@@ -4416,16 +4488,16 @@
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H60" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I60" t="s">
         <v>87</v>
       </c>
       <c r="J60" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K60" t="s">
         <v>55</v>
@@ -4442,13 +4514,13 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B61" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C61" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D61" t="s">
         <v>54</v>
@@ -4460,16 +4532,16 @@
         <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H61" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I61" t="s">
         <v>61</v>
       </c>
       <c r="J61" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -4486,13 +4558,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B62" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C62" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D62" t="s">
         <v>54</v>
@@ -4504,16 +4576,16 @@
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H62" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I62" t="s">
         <v>61</v>
       </c>
       <c r="J62" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K62" t="s">
         <v>55</v>
@@ -4530,13 +4602,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B63" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C63" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D63" t="s">
         <v>54</v>
@@ -4548,16 +4620,16 @@
         <v>32</v>
       </c>
       <c r="G63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H63" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I63" t="s">
         <v>62</v>
       </c>
       <c r="J63" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K63" t="s">
         <v>55</v>
@@ -4574,13 +4646,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B64" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C64" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D64" t="s">
         <v>54</v>
@@ -4592,16 +4664,16 @@
         <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H64" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I64" t="s">
         <v>61</v>
       </c>
       <c r="J64" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K64" t="s">
         <v>55</v>
@@ -4618,13 +4690,13 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B65" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C65" t="s">
-        <v>261</v>
+        <v>174</v>
       </c>
       <c r="D65" t="s">
         <v>54</v>
@@ -4636,16 +4708,16 @@
         <v>13</v>
       </c>
       <c r="G65" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H65" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I65" t="s">
         <v>62</v>
       </c>
       <c r="J65" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K65" t="s">
         <v>55</v>
@@ -4662,13 +4734,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B66" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>508</v>
       </c>
       <c r="D66" t="s">
         <v>54</v>
@@ -4680,16 +4752,16 @@
         <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H66" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I66" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J66" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K66" t="s">
         <v>57</v>
@@ -4706,13 +4778,13 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B67" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C67" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>54</v>
@@ -4724,16 +4796,16 @@
         <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H67" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I67" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J67" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K67" t="s">
         <v>55</v>
@@ -4750,13 +4822,13 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B68" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D68" t="s">
         <v>54</v>
@@ -4768,16 +4840,16 @@
         <v>13</v>
       </c>
       <c r="G68" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H68" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I68" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J68" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K68" t="s">
         <v>55</v>
@@ -4794,13 +4866,13 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C69" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D69" t="s">
         <v>90</v>
@@ -4812,16 +4884,16 @@
         <v>13</v>
       </c>
       <c r="G69" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H69" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I69" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J69" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K69" t="s">
         <v>55</v>
@@ -4838,13 +4910,13 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B70" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C70" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D70" t="s">
         <v>90</v>
@@ -4856,13 +4928,13 @@
         <v>13</v>
       </c>
       <c r="G70" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H70" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J70" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K70" t="s">
         <v>55</v>
@@ -4879,13 +4951,13 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C71" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D71" t="s">
         <v>90</v>
@@ -4897,16 +4969,16 @@
         <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="H71" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I71" t="s">
         <v>87</v>
       </c>
       <c r="J71" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K71" t="s">
         <v>55</v>
@@ -4923,13 +4995,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B72" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C72" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D72" t="s">
         <v>90</v>
@@ -4941,16 +5013,16 @@
         <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H72" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I72" t="s">
         <v>87</v>
       </c>
       <c r="J72" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K72" t="s">
         <v>55</v>
@@ -4967,13 +5039,13 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B73" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C73" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D73" t="s">
         <v>90</v>
@@ -4985,13 +5057,13 @@
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H73" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J73" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K73" t="s">
         <v>55</v>
@@ -5008,13 +5080,13 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B74" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C74" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D74" t="s">
         <v>90</v>
@@ -5026,13 +5098,13 @@
         <v>13</v>
       </c>
       <c r="G74" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H74" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J74" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K74" t="s">
         <v>55</v>
@@ -5049,13 +5121,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B75" t="s">
+        <v>290</v>
+      </c>
+      <c r="C75" t="s">
         <v>293</v>
-      </c>
-      <c r="B75" t="s">
-        <v>294</v>
-      </c>
-      <c r="C75" t="s">
-        <v>297</v>
       </c>
       <c r="D75" t="s">
         <v>90</v>
@@ -5067,16 +5139,16 @@
         <v>13</v>
       </c>
       <c r="G75" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H75" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I75" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J75" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K75" t="s">
         <v>55</v>
@@ -5093,13 +5165,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B76" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C76" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D76" t="s">
         <v>90</v>
@@ -5111,13 +5183,13 @@
         <v>13</v>
       </c>
       <c r="G76" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H76" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J76" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K76" t="s">
         <v>55</v>
@@ -5134,13 +5206,13 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B77" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C77" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D77" t="s">
         <v>90</v>
@@ -5152,13 +5224,13 @@
         <v>13</v>
       </c>
       <c r="G77" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H77" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="J77" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K77" t="s">
         <v>55</v>
@@ -5175,13 +5247,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B78" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C78" t="s">
-        <v>304</v>
+        <v>506</v>
       </c>
       <c r="D78" t="s">
         <v>54</v>
@@ -5193,16 +5265,16 @@
         <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H78" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="I78" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J78" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K78" t="s">
         <v>55</v>
@@ -5219,13 +5291,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B79" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C79" t="s">
-        <v>307</v>
+        <v>507</v>
       </c>
       <c r="D79" t="s">
         <v>54</v>
@@ -5237,16 +5309,16 @@
         <v>13</v>
       </c>
       <c r="G79" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H79" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="I79" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J79" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K79" t="s">
         <v>55</v>
@@ -5263,13 +5335,13 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B80" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C80" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D80" t="s">
         <v>54</v>
@@ -5281,16 +5353,16 @@
         <v>13</v>
       </c>
       <c r="G80" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H80" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I80" t="s">
         <v>61</v>
       </c>
       <c r="J80" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="K80" t="s">
         <v>55</v>
@@ -5307,13 +5379,13 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B81" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C81" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D81" t="s">
         <v>54</v>
@@ -5325,16 +5397,16 @@
         <v>13</v>
       </c>
       <c r="G81" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H81" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="I81" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J81" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K81" t="s">
         <v>55</v>
@@ -5351,13 +5423,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B82" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C82" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D82" t="s">
         <v>54</v>
@@ -5369,13 +5441,13 @@
         <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H82" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="I82" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J82" t="s">
         <v>109</v>
@@ -5395,13 +5467,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B83" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C83" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D83" t="s">
         <v>54</v>
@@ -5413,13 +5485,13 @@
         <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H83" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="I83" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J83" t="s">
         <v>109</v>
@@ -5439,13 +5511,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B84" t="s">
-        <v>329</v>
+        <v>509</v>
       </c>
       <c r="C84" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D84" t="s">
         <v>54</v>
@@ -5457,16 +5529,16 @@
         <v>13</v>
       </c>
       <c r="G84" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="H84" t="s">
         <v>127</v>
       </c>
       <c r="I84" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J84" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="K84" t="s">
         <v>55</v>
@@ -5483,13 +5555,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B85" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C85" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D85" t="s">
         <v>54</v>
@@ -5501,10 +5573,10 @@
         <v>13</v>
       </c>
       <c r="G85" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H85" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="I85" t="s">
         <v>62</v>
@@ -5527,13 +5599,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B86" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C86" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D86" t="s">
         <v>54</v>
@@ -5545,10 +5617,10 @@
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H86" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="J86" t="s">
         <v>109</v>
@@ -5568,13 +5640,13 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B87" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C87" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D87" t="s">
         <v>54</v>
@@ -5586,16 +5658,16 @@
         <v>13</v>
       </c>
       <c r="G87" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H87" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="I87" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J87" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="K87" t="s">
         <v>55</v>
@@ -5612,13 +5684,13 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B88" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C88" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="D88" t="s">
         <v>54</v>
@@ -5630,16 +5702,16 @@
         <v>13</v>
       </c>
       <c r="G88" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H88" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="I88" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="J88" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="K88" t="s">
         <v>55</v>
@@ -5656,13 +5728,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B89" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C89" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D89" t="s">
         <v>54</v>
@@ -5674,7 +5746,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H89" t="s">
         <v>127</v>
@@ -5697,13 +5769,13 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B90" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C90" t="s">
-        <v>376</v>
+        <v>510</v>
       </c>
       <c r="D90" t="s">
         <v>90</v>
@@ -5715,10 +5787,10 @@
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H90" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J90" t="s">
         <v>111</v>
@@ -5738,13 +5810,13 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B91" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C91" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D91" t="s">
         <v>90</v>
@@ -5756,13 +5828,13 @@
         <v>32</v>
       </c>
       <c r="G91" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H91" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="J91" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K91" t="s">
         <v>55</v>
@@ -5779,13 +5851,13 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B92" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C92" t="s">
-        <v>381</v>
+        <v>511</v>
       </c>
       <c r="D92" t="s">
         <v>90</v>
@@ -5797,10 +5869,10 @@
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H92" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J92" t="s">
         <v>111</v>
@@ -5820,13 +5892,13 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B93" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C93" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D93" t="s">
         <v>90</v>
@@ -5838,16 +5910,16 @@
         <v>13</v>
       </c>
       <c r="G93" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H93" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="I93" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J93" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K93" t="s">
         <v>55</v>
@@ -5864,13 +5936,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B94" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C94" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="D94" t="s">
         <v>90</v>
@@ -5882,16 +5954,16 @@
         <v>13</v>
       </c>
       <c r="G94" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H94" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="J94" t="s">
         <v>109</v>
       </c>
       <c r="K94" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L94" t="s">
         <v>14</v>
@@ -5905,13 +5977,13 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B95" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C95" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D95" t="s">
         <v>90</v>
@@ -5923,16 +5995,16 @@
         <v>13</v>
       </c>
       <c r="G95" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H95" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="I95" t="s">
         <v>87</v>
       </c>
       <c r="J95" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K95" t="s">
         <v>55</v>
@@ -5949,13 +6021,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B96" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C96" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D96" t="s">
         <v>90</v>
@@ -5967,16 +6039,16 @@
         <v>13</v>
       </c>
       <c r="G96" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="H96" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="I96" t="s">
         <v>87</v>
       </c>
       <c r="J96" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K96" t="s">
         <v>55</v>
@@ -5993,13 +6065,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B97" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C97" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="D97" t="s">
         <v>90</v>
@@ -6011,7 +6083,7 @@
         <v>32</v>
       </c>
       <c r="G97" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H97" t="s">
         <v>83</v>
@@ -6034,13 +6106,13 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B98" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C98" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="D98" t="s">
         <v>90</v>
@@ -6052,7 +6124,7 @@
         <v>13</v>
       </c>
       <c r="G98" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H98" t="s">
         <v>127</v>
@@ -6075,13 +6147,13 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B99" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C99" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D99" t="s">
         <v>90</v>
@@ -6093,16 +6165,16 @@
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H99" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="I99" t="s">
         <v>87</v>
       </c>
       <c r="J99" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K99" t="s">
         <v>55</v>
@@ -6119,13 +6191,13 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B100" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C100" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="D100" t="s">
         <v>90</v>
@@ -6137,16 +6209,16 @@
         <v>32</v>
       </c>
       <c r="G100" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="H100" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="I100" t="s">
         <v>87</v>
       </c>
       <c r="J100" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K100" t="s">
         <v>55</v>
@@ -6163,13 +6235,13 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B101" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="C101" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D101" t="s">
         <v>90</v>
@@ -6181,16 +6253,16 @@
         <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="H101" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="I101" t="s">
         <v>87</v>
       </c>
       <c r="J101" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K101" t="s">
         <v>55</v>
@@ -6207,13 +6279,13 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B102" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C102" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D102" t="s">
         <v>90</v>
@@ -6225,16 +6297,16 @@
         <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H102" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="I102" t="s">
         <v>87</v>
       </c>
       <c r="J102" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K102" t="s">
         <v>55</v>
@@ -6251,13 +6323,13 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B103" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C103" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="D103" t="s">
         <v>90</v>
@@ -6269,16 +6341,16 @@
         <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H103" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="I103" t="s">
         <v>87</v>
       </c>
       <c r="J103" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K103" t="s">
         <v>55</v>
@@ -6295,13 +6367,13 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B104" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C104" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="D104" t="s">
         <v>90</v>
@@ -6313,16 +6385,16 @@
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H104" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="I104" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J104" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="K104" t="s">
         <v>55</v>
@@ -6339,13 +6411,13 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B105" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="C105" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="D105" t="s">
         <v>90</v>
@@ -6357,16 +6429,16 @@
         <v>32</v>
       </c>
       <c r="G105" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H105" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="I105" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J105" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="K105" t="s">
         <v>55</v>
@@ -6383,13 +6455,13 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B106" t="s">
+        <v>417</v>
+      </c>
+      <c r="C106" t="s">
         <v>418</v>
-      </c>
-      <c r="B106" t="s">
-        <v>426</v>
-      </c>
-      <c r="C106" t="s">
-        <v>427</v>
       </c>
       <c r="D106" t="s">
         <v>90</v>
@@ -6401,13 +6473,13 @@
         <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H106" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="J106" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K106" t="s">
         <v>55</v>
@@ -6424,13 +6496,13 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B107" t="s">
         <v>419</v>
       </c>
-      <c r="B107" t="s">
-        <v>428</v>
-      </c>
       <c r="C107" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="D107" t="s">
         <v>90</v>
@@ -6442,16 +6514,16 @@
         <v>32</v>
       </c>
       <c r="G107" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="H107" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="I107" t="s">
         <v>87</v>
       </c>
       <c r="J107" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K107" t="s">
         <v>55</v>
@@ -6468,13 +6540,13 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B108" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C108" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="D108" t="s">
         <v>90</v>
@@ -6486,13 +6558,13 @@
         <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="H108" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="J108" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K108" t="s">
         <v>55</v>
@@ -6509,13 +6581,13 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B109" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="C109" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="D109" t="s">
         <v>90</v>
@@ -6527,13 +6599,13 @@
         <v>13</v>
       </c>
       <c r="G109" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H109" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="J109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K109" t="s">
         <v>55</v>
@@ -6550,13 +6622,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B110" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="C110" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="D110" t="s">
         <v>90</v>
@@ -6568,16 +6640,16 @@
         <v>13</v>
       </c>
       <c r="G110" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H110" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I110" t="s">
         <v>87</v>
       </c>
       <c r="J110" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K110" t="s">
         <v>55</v>
@@ -6594,13 +6666,13 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B111" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="C111" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D111" t="s">
         <v>54</v>
@@ -6612,16 +6684,16 @@
         <v>32</v>
       </c>
       <c r="G111" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="H111" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="I111" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J111" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K111" t="s">
         <v>55</v>
@@ -6638,13 +6710,13 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="B112" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C112" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="D112" t="s">
         <v>54</v>
@@ -6656,10 +6728,10 @@
         <v>32</v>
       </c>
       <c r="G112" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H112" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="J112" t="s">
         <v>109</v>
@@ -6679,13 +6751,13 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="B113" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C113" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D113" t="s">
         <v>54</v>
@@ -6697,16 +6769,16 @@
         <v>32</v>
       </c>
       <c r="G113" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="H113" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="I113" t="s">
         <v>61</v>
       </c>
       <c r="J113" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K113" t="s">
         <v>55</v>
@@ -6723,13 +6795,13 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B114" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C114" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="D114" t="s">
         <v>54</v>
@@ -6741,13 +6813,13 @@
         <v>13</v>
       </c>
       <c r="G114" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H114" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="J114" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="K114" t="s">
         <v>55</v>
@@ -6764,13 +6836,13 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B115" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C115" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D115" t="s">
         <v>54</v>
@@ -6782,16 +6854,16 @@
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H115" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="I115" t="s">
         <v>87</v>
       </c>
       <c r="J115" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K115" t="s">
         <v>55</v>
@@ -6808,13 +6880,13 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B116" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="C116" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D116" t="s">
         <v>54</v>
@@ -6826,16 +6898,16 @@
         <v>13</v>
       </c>
       <c r="G116" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H116" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="I116" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J116" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="K116" t="s">
         <v>55</v>
@@ -6852,13 +6924,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B117" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="C117" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="D117" t="s">
         <v>54</v>
@@ -6870,13 +6942,13 @@
         <v>13</v>
       </c>
       <c r="G117" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="H117" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="J117" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K117" t="s">
         <v>55</v>
@@ -6893,13 +6965,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B118" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C118" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="D118" t="s">
         <v>54</v>
@@ -6911,13 +6983,13 @@
         <v>13</v>
       </c>
       <c r="G118" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H118" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J118" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K118" t="s">
         <v>55</v>
@@ -6934,13 +7006,13 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="B119" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C119" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="D119" t="s">
         <v>54</v>
@@ -6952,16 +7024,16 @@
         <v>13</v>
       </c>
       <c r="G119" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H119" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I119" t="s">
         <v>62</v>
       </c>
       <c r="J119" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K119" t="s">
         <v>55</v>
@@ -6978,13 +7050,13 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="B120" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="C120" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="D120" t="s">
         <v>54</v>
@@ -6996,13 +7068,13 @@
         <v>13</v>
       </c>
       <c r="G120" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H120" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J120" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="K120" t="s">
         <v>55</v>
@@ -7019,13 +7091,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B121" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="C121" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D121" t="s">
         <v>54</v>
@@ -7037,13 +7109,13 @@
         <v>13</v>
       </c>
       <c r="G121" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H121" t="s">
         <v>127</v>
       </c>
       <c r="J121" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="K121" t="s">
         <v>55</v>
@@ -7060,13 +7132,13 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="B122" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C122" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="D122" t="s">
         <v>54</v>
@@ -7078,16 +7150,16 @@
         <v>13</v>
       </c>
       <c r="G122" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H122" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I122" t="s">
         <v>62</v>
       </c>
       <c r="J122" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K122" t="s">
         <v>55</v>
@@ -7104,13 +7176,13 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B123" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C123" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="D123" t="s">
         <v>54</v>
@@ -7122,13 +7194,13 @@
         <v>13</v>
       </c>
       <c r="G123" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H123" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="J123" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K123" t="s">
         <v>55</v>
@@ -7145,13 +7217,13 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B124" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C124" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="D124" t="s">
         <v>54</v>
@@ -7163,16 +7235,16 @@
         <v>32</v>
       </c>
       <c r="G124" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H124" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I124" t="s">
         <v>62</v>
       </c>
       <c r="J124" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K124" t="s">
         <v>55</v>
@@ -7189,13 +7261,13 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B125" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="C125" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="D125" t="s">
         <v>54</v>
@@ -7207,13 +7279,13 @@
         <v>13</v>
       </c>
       <c r="G125" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H125" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="J125" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K125" t="s">
         <v>55</v>
@@ -7225,6 +7297,308 @@
         <v>15</v>
       </c>
       <c r="N125" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B126" t="s">
+        <v>489</v>
+      </c>
+      <c r="C126" t="s">
+        <v>490</v>
+      </c>
+      <c r="D126" t="s">
+        <v>54</v>
+      </c>
+      <c r="E126" t="s">
+        <v>33</v>
+      </c>
+      <c r="F126" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" t="s">
+        <v>176</v>
+      </c>
+      <c r="H126" t="s">
+        <v>247</v>
+      </c>
+      <c r="J126" t="s">
+        <v>220</v>
+      </c>
+      <c r="K126" t="s">
+        <v>55</v>
+      </c>
+      <c r="L126" t="s">
+        <v>14</v>
+      </c>
+      <c r="M126" t="s">
+        <v>15</v>
+      </c>
+      <c r="N126" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B127" t="s">
+        <v>491</v>
+      </c>
+      <c r="C127" t="s">
+        <v>492</v>
+      </c>
+      <c r="D127" t="s">
+        <v>54</v>
+      </c>
+      <c r="E127" t="s">
+        <v>140</v>
+      </c>
+      <c r="F127" t="s">
+        <v>32</v>
+      </c>
+      <c r="G127" t="s">
+        <v>176</v>
+      </c>
+      <c r="H127" t="s">
+        <v>145</v>
+      </c>
+      <c r="I127" t="s">
+        <v>516</v>
+      </c>
+      <c r="J127" t="s">
+        <v>220</v>
+      </c>
+      <c r="K127" t="s">
+        <v>55</v>
+      </c>
+      <c r="L127" t="s">
+        <v>14</v>
+      </c>
+      <c r="M127" t="s">
+        <v>15</v>
+      </c>
+      <c r="N127" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B128" t="s">
+        <v>493</v>
+      </c>
+      <c r="C128" t="s">
+        <v>494</v>
+      </c>
+      <c r="D128" t="s">
+        <v>54</v>
+      </c>
+      <c r="E128" t="s">
+        <v>58</v>
+      </c>
+      <c r="F128" t="s">
+        <v>32</v>
+      </c>
+      <c r="G128" t="s">
+        <v>176</v>
+      </c>
+      <c r="H128" t="s">
+        <v>162</v>
+      </c>
+      <c r="I128" t="s">
+        <v>175</v>
+      </c>
+      <c r="J128" t="s">
+        <v>220</v>
+      </c>
+      <c r="K128" t="s">
+        <v>55</v>
+      </c>
+      <c r="L128" t="s">
+        <v>14</v>
+      </c>
+      <c r="M128" t="s">
+        <v>15</v>
+      </c>
+      <c r="N128" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B129" t="s">
+        <v>495</v>
+      </c>
+      <c r="C129" t="s">
+        <v>496</v>
+      </c>
+      <c r="D129" t="s">
+        <v>54</v>
+      </c>
+      <c r="E129" t="s">
+        <v>58</v>
+      </c>
+      <c r="F129" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" t="s">
+        <v>268</v>
+      </c>
+      <c r="H129" t="s">
+        <v>497</v>
+      </c>
+      <c r="I129" t="s">
+        <v>62</v>
+      </c>
+      <c r="J129" t="s">
+        <v>240</v>
+      </c>
+      <c r="K129" t="s">
+        <v>55</v>
+      </c>
+      <c r="L129" t="s">
+        <v>14</v>
+      </c>
+      <c r="M129" t="s">
+        <v>15</v>
+      </c>
+      <c r="N129" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B130" t="s">
+        <v>498</v>
+      </c>
+      <c r="C130" t="s">
+        <v>499</v>
+      </c>
+      <c r="D130" t="s">
+        <v>54</v>
+      </c>
+      <c r="E130" t="s">
+        <v>140</v>
+      </c>
+      <c r="F130" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" t="s">
+        <v>176</v>
+      </c>
+      <c r="H130" t="s">
+        <v>500</v>
+      </c>
+      <c r="I130" t="s">
+        <v>62</v>
+      </c>
+      <c r="J130" t="s">
+        <v>220</v>
+      </c>
+      <c r="K130" t="s">
+        <v>56</v>
+      </c>
+      <c r="L130" t="s">
+        <v>14</v>
+      </c>
+      <c r="M130" t="s">
+        <v>15</v>
+      </c>
+      <c r="N130" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B131" t="s">
+        <v>513</v>
+      </c>
+      <c r="C131" t="s">
+        <v>512</v>
+      </c>
+      <c r="D131" t="s">
+        <v>90</v>
+      </c>
+      <c r="E131" t="s">
+        <v>58</v>
+      </c>
+      <c r="F131" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" t="s">
+        <v>176</v>
+      </c>
+      <c r="H131" t="s">
+        <v>218</v>
+      </c>
+      <c r="I131" t="s">
+        <v>87</v>
+      </c>
+      <c r="J131" t="s">
+        <v>109</v>
+      </c>
+      <c r="K131" t="s">
+        <v>55</v>
+      </c>
+      <c r="L131" t="s">
+        <v>14</v>
+      </c>
+      <c r="M131" t="s">
+        <v>15</v>
+      </c>
+      <c r="N131" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B132" t="s">
+        <v>503</v>
+      </c>
+      <c r="C132" t="s">
+        <v>504</v>
+      </c>
+      <c r="D132" t="s">
+        <v>90</v>
+      </c>
+      <c r="E132" t="s">
+        <v>33</v>
+      </c>
+      <c r="F132" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" t="s">
+        <v>176</v>
+      </c>
+      <c r="H132" t="s">
+        <v>505</v>
+      </c>
+      <c r="J132" t="s">
+        <v>224</v>
+      </c>
+      <c r="K132" t="s">
+        <v>55</v>
+      </c>
+      <c r="L132" t="s">
+        <v>14</v>
+      </c>
+      <c r="M132" t="s">
+        <v>15</v>
+      </c>
+      <c r="N132" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5833C9D-90F9-F848-B85A-D3DEC99093A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BC29DC-9186-B648-B813-CA7540DD570E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="588">
   <si>
     <t>id</t>
   </si>
@@ -1571,6 +1571,219 @@
   </si>
   <si>
     <t>sin_fondo;minimalista</t>
+  </si>
+  <si>
+    <t>ILU-0077</t>
+  </si>
+  <si>
+    <t>ILU-0078</t>
+  </si>
+  <si>
+    <t>ILU-0079</t>
+  </si>
+  <si>
+    <t>ILU-0080</t>
+  </si>
+  <si>
+    <t>Tras sus pasos</t>
+  </si>
+  <si>
+    <t>Seguimiento</t>
+  </si>
+  <si>
+    <t>Mi primera Eucaristía</t>
+  </si>
+  <si>
+    <t>evangelio;paz;violetas</t>
+  </si>
+  <si>
+    <t>Recordatorio</t>
+  </si>
+  <si>
+    <t>R-Evolution</t>
+  </si>
+  <si>
+    <t>La revolución de la Sencillez</t>
+  </si>
+  <si>
+    <t>Orienta 2</t>
+  </si>
+  <si>
+    <t>Orientación profesional y vocacional</t>
+  </si>
+  <si>
+    <t>educacion;vocacional</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Jose_MR_C_Towers</t>
+  </si>
+  <si>
+    <t>ILU-0081</t>
+  </si>
+  <si>
+    <t>ILU-0082</t>
+  </si>
+  <si>
+    <t>ILU-0083</t>
+  </si>
+  <si>
+    <t>ILU-0084</t>
+  </si>
+  <si>
+    <t>ILU-0085</t>
+  </si>
+  <si>
+    <t>ILU-0086</t>
+  </si>
+  <si>
+    <t>ILU-0087</t>
+  </si>
+  <si>
+    <t>ILU-0088</t>
+  </si>
+  <si>
+    <t>ILU-0089</t>
+  </si>
+  <si>
+    <t>Barco de papel</t>
+  </si>
+  <si>
+    <t>educacion;maria</t>
+  </si>
+  <si>
+    <t>Estrella de papel</t>
+  </si>
+  <si>
+    <t>Parte cartel 'Cambia' (MRE)</t>
+  </si>
+  <si>
+    <t>L´Hermitage</t>
+  </si>
+  <si>
+    <t>Silueta edificio actual NS L´Hermitage</t>
+  </si>
+  <si>
+    <t>maristas;champagnat;hermitage</t>
+  </si>
+  <si>
+    <t>Para orientación profesional y vocacional</t>
+  </si>
+  <si>
+    <t>Arturo_MP_RRSS</t>
+  </si>
+  <si>
+    <t>Elegir y compartir</t>
+  </si>
+  <si>
+    <t>Diálogo</t>
+  </si>
+  <si>
+    <t>No-Violencia</t>
+  </si>
+  <si>
+    <t>paz;educacion</t>
+  </si>
+  <si>
+    <t>Como María</t>
+  </si>
+  <si>
+    <t>Anagrama humano</t>
+  </si>
+  <si>
+    <t>maria;evangelio</t>
+  </si>
+  <si>
+    <t>Piratilla</t>
+  </si>
+  <si>
+    <t>Para actividad complementaria</t>
+  </si>
+  <si>
+    <t>Paz</t>
+  </si>
+  <si>
+    <t>Paloma y rama de olivo</t>
+  </si>
+  <si>
+    <t>educacion;paz</t>
+  </si>
+  <si>
+    <t>Pajarita de papel</t>
+  </si>
+  <si>
+    <t>DIS-0056</t>
+  </si>
+  <si>
+    <t>DIS-0057</t>
+  </si>
+  <si>
+    <t>DIS-0058</t>
+  </si>
+  <si>
+    <t>DIS-0059</t>
+  </si>
+  <si>
+    <t>DIS-0060</t>
+  </si>
+  <si>
+    <t>DIS-0061</t>
+  </si>
+  <si>
+    <t>DIS-0062</t>
+  </si>
+  <si>
+    <t>Posible logo</t>
+  </si>
+  <si>
+    <t>MarCha Maristas Toledo</t>
+  </si>
+  <si>
+    <t>Hey Bro (por)</t>
+  </si>
+  <si>
+    <t>Para bemaristbrother.com</t>
+  </si>
+  <si>
+    <t>Camina, Reza, Ama</t>
+  </si>
+  <si>
+    <t>Para formación Comunidad GVX</t>
+  </si>
+  <si>
+    <t>maristas;evangelio;GVX</t>
+  </si>
+  <si>
+    <t>postal;sticker</t>
+  </si>
+  <si>
+    <t>Hey Bro (esp)</t>
+  </si>
+  <si>
+    <t>Feliz Navidad I</t>
+  </si>
+  <si>
+    <t>Felicitación</t>
+  </si>
+  <si>
+    <t>GVX Verano 1988</t>
+  </si>
+  <si>
+    <t>Camiseta Tensar los vientos (frontal)</t>
+  </si>
+  <si>
+    <t>Arturo_MP_A_Arroyo</t>
+  </si>
+  <si>
+    <t>Diversos y Complementarios</t>
+  </si>
+  <si>
+    <t>Soy marista</t>
+  </si>
+  <si>
+    <t>Marcelino Champagnat</t>
+  </si>
+  <si>
+    <t>M Champagnat</t>
   </si>
 </sst>
 </file>
@@ -1927,7 +2140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N132"/>
+  <dimension ref="A1:N152"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="31.1640625" customWidth="1"/>
@@ -2072,7 +2285,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>587</v>
       </c>
       <c r="C4" t="s">
         <v>91</v>
@@ -2330,7 +2543,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>586</v>
       </c>
       <c r="C10" t="s">
         <v>95</v>
@@ -2374,7 +2587,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>587</v>
       </c>
       <c r="C11" t="s">
         <v>96</v>
@@ -2418,7 +2631,7 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>587</v>
       </c>
       <c r="C12" t="s">
         <v>97</v>
@@ -2462,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>587</v>
       </c>
       <c r="C13" t="s">
         <v>98</v>
@@ -2506,7 +2719,7 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>587</v>
       </c>
       <c r="C14" t="s">
         <v>99</v>
@@ -7599,6 +7812,877 @@
         <v>15</v>
       </c>
       <c r="N132" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B133" t="s">
+        <v>521</v>
+      </c>
+      <c r="C133" t="s">
+        <v>522</v>
+      </c>
+      <c r="D133" t="s">
+        <v>54</v>
+      </c>
+      <c r="E133" t="s">
+        <v>33</v>
+      </c>
+      <c r="F133" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" t="s">
+        <v>176</v>
+      </c>
+      <c r="H133" t="s">
+        <v>500</v>
+      </c>
+      <c r="I133" t="s">
+        <v>62</v>
+      </c>
+      <c r="J133" t="s">
+        <v>220</v>
+      </c>
+      <c r="K133" t="s">
+        <v>55</v>
+      </c>
+      <c r="L133" t="s">
+        <v>14</v>
+      </c>
+      <c r="M133" t="s">
+        <v>15</v>
+      </c>
+      <c r="N133" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B134" t="s">
+        <v>523</v>
+      </c>
+      <c r="C134" t="s">
+        <v>525</v>
+      </c>
+      <c r="D134" t="s">
+        <v>54</v>
+      </c>
+      <c r="E134" t="s">
+        <v>33</v>
+      </c>
+      <c r="F134" t="s">
+        <v>32</v>
+      </c>
+      <c r="G134" t="s">
+        <v>531</v>
+      </c>
+      <c r="H134" t="s">
+        <v>524</v>
+      </c>
+      <c r="I134" t="s">
+        <v>62</v>
+      </c>
+      <c r="J134" t="s">
+        <v>475</v>
+      </c>
+      <c r="K134" t="s">
+        <v>55</v>
+      </c>
+      <c r="L134" t="s">
+        <v>14</v>
+      </c>
+      <c r="M134" t="s">
+        <v>15</v>
+      </c>
+      <c r="N134" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B135" t="s">
+        <v>526</v>
+      </c>
+      <c r="C135" t="s">
+        <v>527</v>
+      </c>
+      <c r="D135" t="s">
+        <v>54</v>
+      </c>
+      <c r="E135" t="s">
+        <v>58</v>
+      </c>
+      <c r="F135" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" t="s">
+        <v>176</v>
+      </c>
+      <c r="H135" t="s">
+        <v>230</v>
+      </c>
+      <c r="I135" t="s">
+        <v>62</v>
+      </c>
+      <c r="J135" t="s">
+        <v>220</v>
+      </c>
+      <c r="K135" t="s">
+        <v>55</v>
+      </c>
+      <c r="L135" t="s">
+        <v>14</v>
+      </c>
+      <c r="M135" t="s">
+        <v>15</v>
+      </c>
+      <c r="N135" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B136" t="s">
+        <v>528</v>
+      </c>
+      <c r="C136" t="s">
+        <v>529</v>
+      </c>
+      <c r="D136" t="s">
+        <v>54</v>
+      </c>
+      <c r="E136" t="s">
+        <v>33</v>
+      </c>
+      <c r="F136" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" t="s">
+        <v>176</v>
+      </c>
+      <c r="H136" t="s">
+        <v>530</v>
+      </c>
+      <c r="I136" t="s">
+        <v>62</v>
+      </c>
+      <c r="J136" t="s">
+        <v>240</v>
+      </c>
+      <c r="K136" t="s">
+        <v>55</v>
+      </c>
+      <c r="L136" t="s">
+        <v>14</v>
+      </c>
+      <c r="M136" t="s">
+        <v>15</v>
+      </c>
+      <c r="N136" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B137" t="s">
+        <v>541</v>
+      </c>
+      <c r="C137" t="s">
+        <v>544</v>
+      </c>
+      <c r="D137" t="s">
+        <v>54</v>
+      </c>
+      <c r="E137" t="s">
+        <v>33</v>
+      </c>
+      <c r="F137" t="s">
+        <v>13</v>
+      </c>
+      <c r="G137" t="s">
+        <v>176</v>
+      </c>
+      <c r="H137" t="s">
+        <v>542</v>
+      </c>
+      <c r="I137" t="s">
+        <v>62</v>
+      </c>
+      <c r="J137" t="s">
+        <v>220</v>
+      </c>
+      <c r="K137" t="s">
+        <v>55</v>
+      </c>
+      <c r="L137" t="s">
+        <v>14</v>
+      </c>
+      <c r="M137" t="s">
+        <v>15</v>
+      </c>
+      <c r="N137" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B138" t="s">
+        <v>543</v>
+      </c>
+      <c r="C138" t="s">
+        <v>544</v>
+      </c>
+      <c r="D138" t="s">
+        <v>54</v>
+      </c>
+      <c r="E138" t="s">
+        <v>33</v>
+      </c>
+      <c r="F138" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" t="s">
+        <v>268</v>
+      </c>
+      <c r="H138" t="s">
+        <v>247</v>
+      </c>
+      <c r="I138" t="s">
+        <v>62</v>
+      </c>
+      <c r="J138" t="s">
+        <v>220</v>
+      </c>
+      <c r="K138" t="s">
+        <v>55</v>
+      </c>
+      <c r="L138" t="s">
+        <v>14</v>
+      </c>
+      <c r="M138" t="s">
+        <v>15</v>
+      </c>
+      <c r="N138" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B139" t="s">
+        <v>545</v>
+      </c>
+      <c r="C139" t="s">
+        <v>546</v>
+      </c>
+      <c r="D139" t="s">
+        <v>54</v>
+      </c>
+      <c r="E139" t="s">
+        <v>33</v>
+      </c>
+      <c r="F139" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" t="s">
+        <v>176</v>
+      </c>
+      <c r="H139" t="s">
+        <v>547</v>
+      </c>
+      <c r="I139" t="s">
+        <v>62</v>
+      </c>
+      <c r="J139" t="s">
+        <v>220</v>
+      </c>
+      <c r="K139" t="s">
+        <v>55</v>
+      </c>
+      <c r="L139" t="s">
+        <v>14</v>
+      </c>
+      <c r="M139" t="s">
+        <v>15</v>
+      </c>
+      <c r="N139" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B140" t="s">
+        <v>550</v>
+      </c>
+      <c r="C140" t="s">
+        <v>548</v>
+      </c>
+      <c r="D140" t="s">
+        <v>54</v>
+      </c>
+      <c r="E140" t="s">
+        <v>140</v>
+      </c>
+      <c r="F140" t="s">
+        <v>32</v>
+      </c>
+      <c r="G140" t="s">
+        <v>549</v>
+      </c>
+      <c r="H140" t="s">
+        <v>530</v>
+      </c>
+      <c r="I140" t="s">
+        <v>62</v>
+      </c>
+      <c r="J140" t="s">
+        <v>240</v>
+      </c>
+      <c r="K140" t="s">
+        <v>55</v>
+      </c>
+      <c r="L140" t="s">
+        <v>14</v>
+      </c>
+      <c r="M140" t="s">
+        <v>15</v>
+      </c>
+      <c r="N140" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B141" t="s">
+        <v>551</v>
+      </c>
+      <c r="C141" t="s">
+        <v>552</v>
+      </c>
+      <c r="D141" t="s">
+        <v>54</v>
+      </c>
+      <c r="E141" t="s">
+        <v>58</v>
+      </c>
+      <c r="F141" t="s">
+        <v>32</v>
+      </c>
+      <c r="G141" t="s">
+        <v>549</v>
+      </c>
+      <c r="H141" t="s">
+        <v>553</v>
+      </c>
+      <c r="I141" t="s">
+        <v>62</v>
+      </c>
+      <c r="J141" t="s">
+        <v>220</v>
+      </c>
+      <c r="K141" t="s">
+        <v>56</v>
+      </c>
+      <c r="L141" t="s">
+        <v>14</v>
+      </c>
+      <c r="M141" t="s">
+        <v>15</v>
+      </c>
+      <c r="N141" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B142" t="s">
+        <v>554</v>
+      </c>
+      <c r="C142" t="s">
+        <v>555</v>
+      </c>
+      <c r="D142" t="s">
+        <v>54</v>
+      </c>
+      <c r="E142" t="s">
+        <v>140</v>
+      </c>
+      <c r="F142" t="s">
+        <v>13</v>
+      </c>
+      <c r="G142" t="s">
+        <v>176</v>
+      </c>
+      <c r="H142" t="s">
+        <v>556</v>
+      </c>
+      <c r="I142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J142" t="s">
+        <v>220</v>
+      </c>
+      <c r="K142" t="s">
+        <v>57</v>
+      </c>
+      <c r="L142" t="s">
+        <v>14</v>
+      </c>
+      <c r="M142" t="s">
+        <v>15</v>
+      </c>
+      <c r="N142" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B143" t="s">
+        <v>557</v>
+      </c>
+      <c r="C143" t="s">
+        <v>558</v>
+      </c>
+      <c r="D143" t="s">
+        <v>54</v>
+      </c>
+      <c r="E143" t="s">
+        <v>140</v>
+      </c>
+      <c r="F143" t="s">
+        <v>32</v>
+      </c>
+      <c r="G143" t="s">
+        <v>178</v>
+      </c>
+      <c r="H143" t="s">
+        <v>247</v>
+      </c>
+      <c r="I143" t="s">
+        <v>62</v>
+      </c>
+      <c r="J143" t="s">
+        <v>220</v>
+      </c>
+      <c r="K143" t="s">
+        <v>55</v>
+      </c>
+      <c r="L143" t="s">
+        <v>14</v>
+      </c>
+      <c r="M143" t="s">
+        <v>15</v>
+      </c>
+      <c r="N143" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B144" t="s">
+        <v>559</v>
+      </c>
+      <c r="C144" t="s">
+        <v>560</v>
+      </c>
+      <c r="D144" t="s">
+        <v>54</v>
+      </c>
+      <c r="E144" t="s">
+        <v>33</v>
+      </c>
+      <c r="F144" t="s">
+        <v>32</v>
+      </c>
+      <c r="G144" t="s">
+        <v>178</v>
+      </c>
+      <c r="H144" t="s">
+        <v>561</v>
+      </c>
+      <c r="I144" t="s">
+        <v>62</v>
+      </c>
+      <c r="J144" t="s">
+        <v>220</v>
+      </c>
+      <c r="K144" t="s">
+        <v>55</v>
+      </c>
+      <c r="L144" t="s">
+        <v>14</v>
+      </c>
+      <c r="M144" t="s">
+        <v>15</v>
+      </c>
+      <c r="N144" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B145" t="s">
+        <v>562</v>
+      </c>
+      <c r="C145" t="s">
+        <v>544</v>
+      </c>
+      <c r="D145" t="s">
+        <v>54</v>
+      </c>
+      <c r="E145" t="s">
+        <v>33</v>
+      </c>
+      <c r="F145" t="s">
+        <v>13</v>
+      </c>
+      <c r="G145" t="s">
+        <v>176</v>
+      </c>
+      <c r="H145" t="s">
+        <v>247</v>
+      </c>
+      <c r="I145" t="s">
+        <v>62</v>
+      </c>
+      <c r="J145" t="s">
+        <v>220</v>
+      </c>
+      <c r="K145" t="s">
+        <v>57</v>
+      </c>
+      <c r="L145" t="s">
+        <v>14</v>
+      </c>
+      <c r="M145" t="s">
+        <v>15</v>
+      </c>
+      <c r="N145" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B146" t="s">
+        <v>570</v>
+      </c>
+      <c r="C146" t="s">
+        <v>571</v>
+      </c>
+      <c r="D146" t="s">
+        <v>90</v>
+      </c>
+      <c r="E146" t="s">
+        <v>58</v>
+      </c>
+      <c r="F146" t="s">
+        <v>13</v>
+      </c>
+      <c r="G146" t="s">
+        <v>176</v>
+      </c>
+      <c r="H146" t="s">
+        <v>194</v>
+      </c>
+      <c r="I146" t="s">
+        <v>165</v>
+      </c>
+      <c r="J146" t="s">
+        <v>219</v>
+      </c>
+      <c r="K146" t="s">
+        <v>55</v>
+      </c>
+      <c r="L146" t="s">
+        <v>14</v>
+      </c>
+      <c r="M146" t="s">
+        <v>15</v>
+      </c>
+      <c r="N146" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B147" t="s">
+        <v>572</v>
+      </c>
+      <c r="C147" t="s">
+        <v>573</v>
+      </c>
+      <c r="D147" t="s">
+        <v>90</v>
+      </c>
+      <c r="E147" t="s">
+        <v>58</v>
+      </c>
+      <c r="F147" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147" t="s">
+        <v>176</v>
+      </c>
+      <c r="H147" t="s">
+        <v>218</v>
+      </c>
+      <c r="I147" t="s">
+        <v>87</v>
+      </c>
+      <c r="J147" t="s">
+        <v>240</v>
+      </c>
+      <c r="K147" t="s">
+        <v>55</v>
+      </c>
+      <c r="L147" t="s">
+        <v>14</v>
+      </c>
+      <c r="M147" t="s">
+        <v>15</v>
+      </c>
+      <c r="N147" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B148" t="s">
+        <v>574</v>
+      </c>
+      <c r="C148" t="s">
+        <v>575</v>
+      </c>
+      <c r="D148" t="s">
+        <v>90</v>
+      </c>
+      <c r="E148" t="s">
+        <v>58</v>
+      </c>
+      <c r="F148" t="s">
+        <v>13</v>
+      </c>
+      <c r="G148" t="s">
+        <v>325</v>
+      </c>
+      <c r="H148" t="s">
+        <v>576</v>
+      </c>
+      <c r="I148" t="s">
+        <v>87</v>
+      </c>
+      <c r="J148" t="s">
+        <v>577</v>
+      </c>
+      <c r="K148" t="s">
+        <v>55</v>
+      </c>
+      <c r="L148" t="s">
+        <v>14</v>
+      </c>
+      <c r="M148" t="s">
+        <v>15</v>
+      </c>
+      <c r="N148" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B149" t="s">
+        <v>578</v>
+      </c>
+      <c r="C149" t="s">
+        <v>573</v>
+      </c>
+      <c r="D149" t="s">
+        <v>90</v>
+      </c>
+      <c r="E149" t="s">
+        <v>58</v>
+      </c>
+      <c r="F149" t="s">
+        <v>13</v>
+      </c>
+      <c r="G149" t="s">
+        <v>176</v>
+      </c>
+      <c r="H149" t="s">
+        <v>218</v>
+      </c>
+      <c r="I149" t="s">
+        <v>87</v>
+      </c>
+      <c r="J149" t="s">
+        <v>240</v>
+      </c>
+      <c r="K149" t="s">
+        <v>55</v>
+      </c>
+      <c r="L149" t="s">
+        <v>14</v>
+      </c>
+      <c r="M149" t="s">
+        <v>15</v>
+      </c>
+      <c r="N149" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B150" t="s">
+        <v>579</v>
+      </c>
+      <c r="C150" t="s">
+        <v>580</v>
+      </c>
+      <c r="D150" t="s">
+        <v>90</v>
+      </c>
+      <c r="E150" t="s">
+        <v>33</v>
+      </c>
+      <c r="F150" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" t="s">
+        <v>176</v>
+      </c>
+      <c r="H150" t="s">
+        <v>335</v>
+      </c>
+      <c r="J150" t="s">
+        <v>577</v>
+      </c>
+      <c r="K150" t="s">
+        <v>55</v>
+      </c>
+      <c r="L150" t="s">
+        <v>14</v>
+      </c>
+      <c r="M150" t="s">
+        <v>15</v>
+      </c>
+      <c r="N150" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B151" t="s">
+        <v>581</v>
+      </c>
+      <c r="C151" t="s">
+        <v>582</v>
+      </c>
+      <c r="D151" t="s">
+        <v>90</v>
+      </c>
+      <c r="E151" t="s">
+        <v>33</v>
+      </c>
+      <c r="F151" t="s">
+        <v>32</v>
+      </c>
+      <c r="G151" t="s">
+        <v>583</v>
+      </c>
+      <c r="H151" t="s">
+        <v>406</v>
+      </c>
+      <c r="J151" t="s">
+        <v>231</v>
+      </c>
+      <c r="K151" t="s">
+        <v>56</v>
+      </c>
+      <c r="L151" t="s">
+        <v>14</v>
+      </c>
+      <c r="M151" t="s">
+        <v>15</v>
+      </c>
+      <c r="N151" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B152" t="s">
+        <v>584</v>
+      </c>
+      <c r="C152" t="s">
+        <v>585</v>
+      </c>
+      <c r="D152" t="s">
+        <v>90</v>
+      </c>
+      <c r="E152" t="s">
+        <v>58</v>
+      </c>
+      <c r="F152" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152" t="s">
+        <v>176</v>
+      </c>
+      <c r="H152" t="s">
+        <v>127</v>
+      </c>
+      <c r="J152" t="s">
+        <v>475</v>
+      </c>
+      <c r="K152" t="s">
+        <v>55</v>
+      </c>
+      <c r="L152" t="s">
+        <v>14</v>
+      </c>
+      <c r="M152" t="s">
+        <v>15</v>
+      </c>
+      <c r="N152" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BC29DC-9186-B648-B813-CA7540DD570E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2339E9E8-9815-9E4A-BCC7-BDF741F12516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="614">
   <si>
     <t>id</t>
   </si>
@@ -202,9 +202,6 @@
     <t>champagnat;maristas;infantil</t>
   </si>
   <si>
-    <t>firma;sin_fondo</t>
-  </si>
-  <si>
     <t>minimalista</t>
   </si>
   <si>
@@ -265,24 +262,12 @@
     <t>Camiseta viaje a L´Hermitage</t>
   </si>
   <si>
-    <t>champagnat;maristas;vocacional;hermitage</t>
-  </si>
-  <si>
-    <t>champagnat;maristas;infantil;hermitage</t>
-  </si>
-  <si>
-    <t>champagnat;maristas;hermitage</t>
-  </si>
-  <si>
     <t>champagnat;maristas;violetas</t>
   </si>
   <si>
     <t>champagnat;maristas;infantil;violetas</t>
   </si>
   <si>
-    <t>champagnat;maristas;GVX;infantil;violetas</t>
-  </si>
-  <si>
     <t>frase</t>
   </si>
   <si>
@@ -346,9 +331,6 @@
     <t>firma</t>
   </si>
   <si>
-    <t>triptico</t>
-  </si>
-  <si>
     <t>postal</t>
   </si>
   <si>
@@ -457,9 +439,6 @@
     <t>Buena Madre B/N</t>
   </si>
   <si>
-    <t>maria;maristas</t>
-  </si>
-  <si>
     <t>Nuestra Buena Madre</t>
   </si>
   <si>
@@ -472,9 +451,6 @@
     <t>A Jesús por María</t>
   </si>
   <si>
-    <t>champagnat;maristas;maria</t>
-  </si>
-  <si>
     <t>María, Buena Madre II</t>
   </si>
   <si>
@@ -604,9 +580,6 @@
     <t>DIS-0020</t>
   </si>
   <si>
-    <t>maristas;GVX</t>
-  </si>
-  <si>
     <t>GVX Verano 2014</t>
   </si>
   <si>
@@ -691,9 +664,6 @@
     <t>Estoy a la puerta y llamo</t>
   </si>
   <si>
-    <t>maristas;GVX;vocacional</t>
-  </si>
-  <si>
     <t>cartel;rrss</t>
   </si>
   <si>
@@ -886,9 +856,6 @@
     <t>Camiseta HERE WE ARE 2021 (frontal)</t>
   </si>
   <si>
-    <t>maristas;GVX;evangelio</t>
-  </si>
-  <si>
     <t>DIS-0030</t>
   </si>
   <si>
@@ -1042,9 +1009,6 @@
     <t>Marist Runners</t>
   </si>
   <si>
-    <t>frase;logo</t>
-  </si>
-  <si>
     <t>sticker;textil</t>
   </si>
   <si>
@@ -1057,9 +1021,6 @@
     <t>Preparación Capítulo General</t>
   </si>
   <si>
-    <t>maristas;maria;deporte</t>
-  </si>
-  <si>
     <t>Ilustraciones maristas</t>
   </si>
   <si>
@@ -1144,9 +1105,6 @@
     <t>El mundo, la mejor cocina</t>
   </si>
   <si>
-    <t>maristas;GVX;educacion</t>
-  </si>
-  <si>
     <t>Para encuentro Delegados de Pastoral (delantal)</t>
   </si>
   <si>
@@ -1237,15 +1195,9 @@
     <t>taza</t>
   </si>
   <si>
-    <t>maria;maristas;violetas;paz</t>
-  </si>
-  <si>
     <t>GVX</t>
   </si>
   <si>
-    <t>maristas;GVX;violetas</t>
-  </si>
-  <si>
     <t>DIS-0048</t>
   </si>
   <si>
@@ -1306,9 +1258,6 @@
     <t>Para semana Vocacional Sevilla</t>
   </si>
   <si>
-    <t>maristas;educacion;vocacional</t>
-  </si>
-  <si>
     <t>Posibles camisetas #escuchaaunniño</t>
   </si>
   <si>
@@ -1372,9 +1321,6 @@
     <t>Llamadas</t>
   </si>
   <si>
-    <t>maristas;champagnat;vocacional</t>
-  </si>
-  <si>
     <t>Silueta Champagnat acuarela</t>
   </si>
   <si>
@@ -1420,9 +1366,6 @@
     <t>Arturo_MP_J_Ramos</t>
   </si>
   <si>
-    <t>maristas;educacion;vocacional;violetas</t>
-  </si>
-  <si>
     <t>Gente normal (esp)</t>
   </si>
   <si>
@@ -1513,9 +1456,6 @@
     <t>Para educar es preciso amar</t>
   </si>
   <si>
-    <t>maristas;champagnat;educacion</t>
-  </si>
-  <si>
     <t>Escuchas?</t>
   </si>
   <si>
@@ -1537,9 +1477,6 @@
     <t>Para Viaje a Belén Maristas Jaén</t>
   </si>
   <si>
-    <t>maristas;evangelio;educacion</t>
-  </si>
-  <si>
     <t>Para convivencia Marcha GVX</t>
   </si>
   <si>
@@ -1663,9 +1600,6 @@
     <t>Silueta edificio actual NS L´Hermitage</t>
   </si>
   <si>
-    <t>maristas;champagnat;hermitage</t>
-  </si>
-  <si>
     <t>Para orientación profesional y vocacional</t>
   </si>
   <si>
@@ -1750,12 +1684,6 @@
     <t>Para formación Comunidad GVX</t>
   </si>
   <si>
-    <t>maristas;evangelio;GVX</t>
-  </si>
-  <si>
-    <t>postal;sticker</t>
-  </si>
-  <si>
     <t>Hey Bro (esp)</t>
   </si>
   <si>
@@ -1784,6 +1712,156 @@
   </si>
   <si>
     <t>M Champagnat</t>
+  </si>
+  <si>
+    <t>champagnat;vocacional;hermitage</t>
+  </si>
+  <si>
+    <t>champagnat;infantil;violetas</t>
+  </si>
+  <si>
+    <t>champagnat</t>
+  </si>
+  <si>
+    <t>maria;violetas;paz</t>
+  </si>
+  <si>
+    <t>champagnat;vocacional</t>
+  </si>
+  <si>
+    <t>champagnat;infantil;hermitage</t>
+  </si>
+  <si>
+    <t>champagnat;hermitage</t>
+  </si>
+  <si>
+    <t>GVX;violetas</t>
+  </si>
+  <si>
+    <t>GVX;vocacional</t>
+  </si>
+  <si>
+    <t>violetas</t>
+  </si>
+  <si>
+    <t>deporte</t>
+  </si>
+  <si>
+    <t>maristas;hermitage</t>
+  </si>
+  <si>
+    <t>educacion;vocacional;violetas</t>
+  </si>
+  <si>
+    <t>social;educacion</t>
+  </si>
+  <si>
+    <t>maristas;educacion;infantil</t>
+  </si>
+  <si>
+    <t>champagnat;educacion</t>
+  </si>
+  <si>
+    <t>evangelio;educacion</t>
+  </si>
+  <si>
+    <t>hermitage</t>
+  </si>
+  <si>
+    <t>sin_fondo;firma</t>
+  </si>
+  <si>
+    <t>sticker;triptico</t>
+  </si>
+  <si>
+    <t>postal;rrss</t>
+  </si>
+  <si>
+    <t>ILU-0090</t>
+  </si>
+  <si>
+    <t>ILU-0091</t>
+  </si>
+  <si>
+    <t>ILU-0092</t>
+  </si>
+  <si>
+    <t>ILU-0093</t>
+  </si>
+  <si>
+    <t>ILU-0094</t>
+  </si>
+  <si>
+    <t>Sois la luz del mundo</t>
+  </si>
+  <si>
+    <t>Comedor de Fuenteheridos I</t>
+  </si>
+  <si>
+    <t>cartel;mural;textil</t>
+  </si>
+  <si>
+    <t>La Chispa</t>
+  </si>
+  <si>
+    <t>Comedor de Fuenteheridos II</t>
+  </si>
+  <si>
+    <t>Eucaristía II</t>
+  </si>
+  <si>
+    <t>Trigo y pan</t>
+  </si>
+  <si>
+    <t>Chispa</t>
+  </si>
+  <si>
+    <t>Para frontal camiseta GVX 2023</t>
+  </si>
+  <si>
+    <t>En el pesebre</t>
+  </si>
+  <si>
+    <t>Navidad</t>
+  </si>
+  <si>
+    <t>DIS-0063</t>
+  </si>
+  <si>
+    <t>DIS-0064</t>
+  </si>
+  <si>
+    <t>DIS-0065</t>
+  </si>
+  <si>
+    <t>DIS-0066</t>
+  </si>
+  <si>
+    <t>GVX Verano 2019 (GA-Marcha)</t>
+  </si>
+  <si>
+    <t>Camiseta GVX 2019 (ita)</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2017</t>
+  </si>
+  <si>
+    <t>Camiseta Pascua 2017 (frontal)</t>
+  </si>
+  <si>
+    <t>Dónde Vives?</t>
+  </si>
+  <si>
+    <t>Para convivencia Vocacional Marcha GVX</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Luis_G</t>
+  </si>
+  <si>
+    <t>GVX 25 aniversario 2007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiseta GVX 2007 </t>
   </si>
 </sst>
 </file>
@@ -2140,16 +2218,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:N161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="31.1640625" customWidth="1"/>
-    <col min="3" max="3" width="45.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="42.1640625" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" customWidth="1"/>
     <col min="6" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="19.5" customWidth="1"/>
-    <col min="8" max="8" width="38.1640625" customWidth="1"/>
+    <col min="8" max="8" width="30.1640625" customWidth="1"/>
     <col min="9" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.5" customWidth="1"/>
   </cols>
@@ -2183,10 +2261,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
@@ -2203,10 +2281,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D2" t="s">
         <v>54</v>
@@ -2218,13 +2296,16 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="I2" t="s">
-        <v>175</v>
+        <v>167</v>
+      </c>
+      <c r="J2" t="s">
+        <v>211</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -2247,7 +2328,7 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D3" t="s">
         <v>54</v>
@@ -2259,13 +2340,16 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H3" t="s">
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>582</v>
+      </c>
+      <c r="J3" t="s">
+        <v>211</v>
       </c>
       <c r="K3" t="s">
         <v>56</v>
@@ -2285,10 +2369,10 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
         <v>54</v>
@@ -2300,16 +2384,16 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H4" t="s">
         <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K4" t="s">
         <v>55</v>
@@ -2329,10 +2413,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
         <v>54</v>
@@ -2344,16 +2428,16 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H5" t="s">
         <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K5" t="s">
         <v>55</v>
@@ -2373,10 +2457,10 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
         <v>54</v>
@@ -2388,13 +2472,13 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H6" t="s">
         <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K6" t="s">
         <v>57</v>
@@ -2429,13 +2513,13 @@
         <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H7" t="s">
         <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="K7" t="s">
         <v>56</v>
@@ -2458,7 +2542,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -2470,16 +2554,16 @@
         <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H8" t="s">
         <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>108</v>
+        <v>583</v>
       </c>
       <c r="K8" t="s">
         <v>55</v>
@@ -2499,10 +2583,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
         <v>54</v>
@@ -2514,16 +2598,16 @@
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H9" t="s">
         <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K9" t="s">
         <v>57</v>
@@ -2543,10 +2627,10 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
         <v>54</v>
@@ -2558,16 +2642,16 @@
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H10" t="s">
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K10" t="s">
         <v>55</v>
@@ -2587,10 +2671,10 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -2602,16 +2686,16 @@
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H11" t="s">
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K11" t="s">
         <v>55</v>
@@ -2631,10 +2715,10 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
         <v>54</v>
@@ -2646,16 +2730,16 @@
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H12" t="s">
         <v>28</v>
       </c>
       <c r="I12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K12" t="s">
         <v>55</v>
@@ -2675,10 +2759,10 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2690,16 +2774,16 @@
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H13" t="s">
         <v>28</v>
       </c>
       <c r="I13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
@@ -2719,10 +2803,10 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
         <v>54</v>
@@ -2734,16 +2818,16 @@
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H14" t="s">
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="J14" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="K14" t="s">
         <v>56</v>
@@ -2778,16 +2862,16 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="H15" t="s">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="I15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="J15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K15" t="s">
         <v>55</v>
@@ -2810,7 +2894,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>54</v>
@@ -2822,16 +2906,16 @@
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H16" t="s">
         <v>28</v>
       </c>
       <c r="I16" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="J16" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K16" t="s">
         <v>55</v>
@@ -2854,28 +2938,28 @@
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
         <v>54</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F17" t="s">
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
         <v>59</v>
       </c>
       <c r="I17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J17" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K17" t="s">
         <v>55</v>
@@ -2910,13 +2994,13 @@
         <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>565</v>
       </c>
       <c r="J18" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K18" t="s">
         <v>55</v>
@@ -2945,22 +3029,22 @@
         <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F19" t="s">
         <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H19" t="s">
         <v>28</v>
       </c>
       <c r="I19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="J19" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="K19" t="s">
         <v>55</v>
@@ -2983,7 +3067,7 @@
         <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -2995,13 +3079,13 @@
         <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J20" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K20" t="s">
         <v>55</v>
@@ -3018,13 +3102,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
         <v>54</v>
@@ -3036,13 +3120,13 @@
         <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s">
         <v>56</v>
@@ -3059,34 +3143,34 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
         <v>54</v>
       </c>
       <c r="E22" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
+        <v>566</v>
       </c>
       <c r="I22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J22" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K22" t="s">
         <v>55</v>
@@ -3103,13 +3187,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -3121,16 +3205,16 @@
         <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="H23" t="s">
         <v>59</v>
       </c>
       <c r="I23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K23" t="s">
         <v>55</v>
@@ -3147,31 +3231,31 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s">
         <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
       </c>
       <c r="E24" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F24" t="s">
         <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H24" t="s">
         <v>28</v>
       </c>
       <c r="J24" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="K24" t="s">
         <v>55</v>
@@ -3188,31 +3272,31 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
         <v>54</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F25" t="s">
         <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H25" t="s">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="J25" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s">
         <v>56</v>
@@ -3229,31 +3313,31 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
         <v>54</v>
       </c>
       <c r="E26" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F26" t="s">
         <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H26" t="s">
-        <v>515</v>
+        <v>494</v>
       </c>
       <c r="J26" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K26" t="s">
         <v>55</v>
@@ -3270,31 +3354,31 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
         <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F27" t="s">
         <v>32</v>
       </c>
       <c r="G27" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H27" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J27" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="K27" t="s">
         <v>56</v>
@@ -3311,34 +3395,34 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" t="s">
         <v>134</v>
       </c>
-      <c r="B28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" t="s">
-        <v>147</v>
-      </c>
-      <c r="D28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" t="s">
-        <v>140</v>
-      </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H28" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>220</v>
+        <v>456</v>
       </c>
       <c r="K28" t="s">
         <v>56</v>
@@ -3355,13 +3439,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D29" t="s">
         <v>54</v>
@@ -3373,13 +3457,13 @@
         <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H29" t="s">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="J29" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="K29" t="s">
         <v>56</v>
@@ -3396,31 +3480,31 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D30" t="s">
         <v>54</v>
       </c>
       <c r="E30" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="H30" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J30" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K30" t="s">
         <v>55</v>
@@ -3437,31 +3521,31 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B31" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
         <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s">
         <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H31" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J31" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K31" t="s">
         <v>55</v>
@@ -3478,13 +3562,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D32" t="s">
         <v>54</v>
@@ -3496,13 +3580,13 @@
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H32" t="s">
-        <v>162</v>
+        <v>534</v>
       </c>
       <c r="J32" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K32" t="s">
         <v>55</v>
@@ -3519,31 +3603,31 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B33" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D33" t="s">
         <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H33" t="s">
-        <v>405</v>
+        <v>567</v>
       </c>
       <c r="J33" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K33" t="s">
         <v>55</v>
@@ -3560,13 +3644,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D34" t="s">
         <v>54</v>
@@ -3578,16 +3662,16 @@
         <v>32</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H34" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="I34" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J34" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K34" t="s">
         <v>55</v>
@@ -3604,7 +3688,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
         <v>29</v>
@@ -3622,13 +3706,13 @@
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J35" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K35" t="s">
         <v>55</v>
@@ -3645,16 +3729,16 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E36" t="s">
         <v>58</v>
@@ -3663,16 +3747,16 @@
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H36" t="s">
-        <v>35</v>
+        <v>568</v>
       </c>
       <c r="I36" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="J36" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K36" t="s">
         <v>55</v>
@@ -3689,16 +3773,16 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" t="s">
         <v>72</v>
       </c>
-      <c r="C37" t="s">
-        <v>73</v>
-      </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E37" t="s">
         <v>58</v>
@@ -3707,16 +3791,16 @@
         <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H37" t="s">
-        <v>28</v>
+        <v>566</v>
       </c>
       <c r="I37" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J37" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K37" t="s">
         <v>55</v>
@@ -3733,16 +3817,16 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
@@ -3751,16 +3835,16 @@
         <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H38" t="s">
         <v>35</v>
       </c>
       <c r="I38" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="J38" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="K38" t="s">
         <v>55</v>
@@ -3777,16 +3861,16 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E39" t="s">
         <v>33</v>
@@ -3795,13 +3879,13 @@
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H39" t="s">
-        <v>82</v>
+        <v>569</v>
       </c>
       <c r="J39" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K39" t="s">
         <v>57</v>
@@ -3818,16 +3902,16 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" t="s">
         <v>76</v>
       </c>
-      <c r="C40" t="s">
-        <v>77</v>
-      </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E40" t="s">
         <v>58</v>
@@ -3836,16 +3920,16 @@
         <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H40" t="s">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="I40" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J40" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K40" t="s">
         <v>55</v>
@@ -3862,16 +3946,16 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E41" t="s">
         <v>58</v>
@@ -3880,13 +3964,13 @@
         <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H41" t="s">
-        <v>28</v>
+        <v>566</v>
       </c>
       <c r="J41" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K41" t="s">
         <v>55</v>
@@ -3903,16 +3987,16 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" t="s">
         <v>79</v>
       </c>
-      <c r="C42" t="s">
-        <v>80</v>
-      </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E42" t="s">
         <v>58</v>
@@ -3921,16 +4005,16 @@
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="H42" t="s">
-        <v>83</v>
+        <v>570</v>
       </c>
       <c r="I42" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K42" t="s">
         <v>55</v>
@@ -3947,16 +4031,16 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E43" t="s">
         <v>31</v>
@@ -3965,16 +4049,16 @@
         <v>32</v>
       </c>
       <c r="G43" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="H43" t="s">
         <v>28</v>
       </c>
       <c r="I43" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="J43" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K43" t="s">
         <v>55</v>
@@ -3991,16 +4075,16 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C44" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E44" t="s">
         <v>58</v>
@@ -4009,16 +4093,16 @@
         <v>32</v>
       </c>
       <c r="G44" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H44" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I44" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J44" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="K44" t="s">
         <v>55</v>
@@ -4035,16 +4119,16 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E45" t="s">
         <v>58</v>
@@ -4053,16 +4137,16 @@
         <v>32</v>
       </c>
       <c r="G45" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H45" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I45" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s">
         <v>56</v>
@@ -4079,16 +4163,16 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C46" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E46" t="s">
         <v>58</v>
@@ -4097,16 +4181,16 @@
         <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H46" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I46" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J46" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K46" t="s">
         <v>55</v>
@@ -4123,16 +4207,16 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C47" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E47" t="s">
         <v>58</v>
@@ -4141,13 +4225,13 @@
         <v>13</v>
       </c>
       <c r="G47" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H47" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="J47" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K47" t="s">
         <v>55</v>
@@ -4164,16 +4248,16 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B48" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C48" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E48" t="s">
         <v>58</v>
@@ -4182,16 +4266,16 @@
         <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H48" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="I48" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K48" t="s">
         <v>55</v>
@@ -4208,16 +4292,16 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B49" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C49" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D49" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E49" t="s">
         <v>58</v>
@@ -4226,13 +4310,13 @@
         <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H49" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="J49" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K49" t="s">
         <v>55</v>
@@ -4249,16 +4333,16 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B50" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D50" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E50" t="s">
         <v>58</v>
@@ -4267,16 +4351,16 @@
         <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H50" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="I50" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J50" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K50" t="s">
         <v>55</v>
@@ -4293,16 +4377,16 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B51" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C51" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E51" t="s">
         <v>58</v>
@@ -4311,16 +4395,16 @@
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="H51" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="I51" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J51" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K51" t="s">
         <v>55</v>
@@ -4337,16 +4421,16 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C52" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D52" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
@@ -4355,13 +4439,13 @@
         <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H52" t="s">
-        <v>407</v>
+        <v>571</v>
       </c>
       <c r="J52" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K52" t="s">
         <v>55</v>
@@ -4378,16 +4462,16 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B53" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C53" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D53" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -4396,13 +4480,13 @@
         <v>13</v>
       </c>
       <c r="G53" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H53" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="J53" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K53" t="s">
         <v>55</v>
@@ -4419,16 +4503,16 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C54" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D54" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E54" t="s">
         <v>58</v>
@@ -4437,16 +4521,16 @@
         <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H54" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="I54" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K54" t="s">
         <v>55</v>
@@ -4463,16 +4547,16 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B55" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C55" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D55" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E55" t="s">
         <v>33</v>
@@ -4481,16 +4565,16 @@
         <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H55" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="I55" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J55" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -4507,16 +4591,16 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B56" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C56" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D56" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E56" t="s">
         <v>58</v>
@@ -4525,16 +4609,16 @@
         <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H56" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="I56" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J56" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="K56" t="s">
         <v>55</v>
@@ -4551,16 +4635,16 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B57" t="s">
         <v>213</v>
       </c>
-      <c r="B57" t="s">
-        <v>222</v>
-      </c>
       <c r="C57" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D57" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E57" t="s">
         <v>58</v>
@@ -4569,16 +4653,16 @@
         <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H57" t="s">
-        <v>223</v>
+        <v>572</v>
       </c>
       <c r="I57" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J57" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K57" t="s">
         <v>55</v>
@@ -4595,16 +4679,16 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B58" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C58" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D58" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E58" t="s">
         <v>33</v>
@@ -4613,16 +4697,16 @@
         <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H58" t="s">
-        <v>223</v>
+        <v>572</v>
       </c>
       <c r="I58" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J58" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K58" t="s">
         <v>55</v>
@@ -4639,13 +4723,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B59" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C59" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D59" t="s">
         <v>54</v>
@@ -4657,16 +4741,16 @@
         <v>13</v>
       </c>
       <c r="G59" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H59" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="I59" t="s">
-        <v>250</v>
+        <v>167</v>
       </c>
       <c r="J59" t="s">
-        <v>231</v>
+        <v>400</v>
       </c>
       <c r="K59" t="s">
         <v>55</v>
@@ -4683,13 +4767,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B60" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C60" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D60" t="s">
         <v>54</v>
@@ -4701,16 +4785,16 @@
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H60" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="I60" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K60" t="s">
         <v>55</v>
@@ -4727,13 +4811,13 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B61" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C61" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="D61" t="s">
         <v>54</v>
@@ -4745,16 +4829,16 @@
         <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H61" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="I61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J61" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -4771,13 +4855,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" t="s">
         <v>234</v>
       </c>
-      <c r="B62" t="s">
-        <v>244</v>
-      </c>
       <c r="C62" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D62" t="s">
         <v>54</v>
@@ -4789,16 +4873,16 @@
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H62" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="I62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J62" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K62" t="s">
         <v>55</v>
@@ -4815,13 +4899,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B63" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C63" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D63" t="s">
         <v>54</v>
@@ -4833,16 +4917,16 @@
         <v>32</v>
       </c>
       <c r="G63" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H63" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="I63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J63" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K63" t="s">
         <v>55</v>
@@ -4859,13 +4943,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B64" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D64" t="s">
         <v>54</v>
@@ -4877,16 +4961,16 @@
         <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H64" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="I64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J64" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="K64" t="s">
         <v>55</v>
@@ -4903,13 +4987,13 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B65" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C65" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D65" t="s">
         <v>54</v>
@@ -4921,16 +5005,16 @@
         <v>13</v>
       </c>
       <c r="G65" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H65" t="s">
-        <v>230</v>
+        <v>573</v>
       </c>
       <c r="I65" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J65" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K65" t="s">
         <v>55</v>
@@ -4947,13 +5031,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B66" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C66" t="s">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="D66" t="s">
         <v>54</v>
@@ -4965,16 +5049,16 @@
         <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H66" t="s">
-        <v>230</v>
+        <v>573</v>
       </c>
       <c r="I66" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J66" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K66" t="s">
         <v>57</v>
@@ -4991,13 +5075,13 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B67" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C67" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D67" t="s">
         <v>54</v>
@@ -5009,16 +5093,16 @@
         <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H67" t="s">
-        <v>230</v>
+        <v>573</v>
       </c>
       <c r="I67" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J67" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K67" t="s">
         <v>55</v>
@@ -5035,13 +5119,13 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="B68" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C68" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D68" t="s">
         <v>54</v>
@@ -5053,16 +5137,16 @@
         <v>13</v>
       </c>
       <c r="G68" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H68" t="s">
-        <v>230</v>
+        <v>573</v>
       </c>
       <c r="I68" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J68" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K68" t="s">
         <v>55</v>
@@ -5079,16 +5163,16 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B69" t="s">
+        <v>268</v>
+      </c>
+      <c r="C69" t="s">
         <v>269</v>
       </c>
-      <c r="B69" t="s">
-        <v>278</v>
-      </c>
-      <c r="C69" t="s">
-        <v>279</v>
-      </c>
       <c r="D69" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E69" t="s">
         <v>58</v>
@@ -5097,16 +5181,16 @@
         <v>13</v>
       </c>
       <c r="G69" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H69" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="I69" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="J69" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K69" t="s">
         <v>55</v>
@@ -5123,16 +5207,16 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B70" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C70" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D70" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E70" t="s">
         <v>33</v>
@@ -5141,13 +5225,13 @@
         <v>13</v>
       </c>
       <c r="G70" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H70" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="J70" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K70" t="s">
         <v>55</v>
@@ -5164,16 +5248,16 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B71" t="s">
         <v>271</v>
       </c>
-      <c r="B71" t="s">
-        <v>281</v>
-      </c>
       <c r="C71" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D71" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E71" t="s">
         <v>58</v>
@@ -5182,16 +5266,16 @@
         <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="H71" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="I71" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J71" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K71" t="s">
         <v>55</v>
@@ -5208,16 +5292,16 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="B72" t="s">
+        <v>267</v>
+      </c>
+      <c r="C72" t="s">
         <v>277</v>
       </c>
-      <c r="C72" t="s">
-        <v>287</v>
-      </c>
       <c r="D72" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E72" t="s">
         <v>58</v>
@@ -5226,16 +5310,16 @@
         <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H72" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="I72" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J72" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K72" t="s">
         <v>55</v>
@@ -5252,16 +5336,16 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B73" t="s">
         <v>273</v>
       </c>
-      <c r="B73" t="s">
-        <v>283</v>
-      </c>
       <c r="C73" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -5270,13 +5354,13 @@
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H73" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="J73" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="K73" t="s">
         <v>55</v>
@@ -5293,16 +5377,16 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="B74" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C74" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D74" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E74" t="s">
         <v>33</v>
@@ -5311,13 +5395,13 @@
         <v>13</v>
       </c>
       <c r="G74" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="H74" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="J74" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K74" t="s">
         <v>55</v>
@@ -5334,16 +5418,16 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B75" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C75" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D75" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E75" t="s">
         <v>33</v>
@@ -5352,16 +5436,16 @@
         <v>13</v>
       </c>
       <c r="G75" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H75" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="I75" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J75" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K75" t="s">
         <v>55</v>
@@ -5378,16 +5462,16 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B76" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C76" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="D76" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E76" t="s">
         <v>58</v>
@@ -5396,13 +5480,13 @@
         <v>13</v>
       </c>
       <c r="G76" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="H76" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="J76" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K76" t="s">
         <v>55</v>
@@ -5419,16 +5503,16 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B77" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C77" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D77" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E77" t="s">
         <v>33</v>
@@ -5437,13 +5521,13 @@
         <v>13</v>
       </c>
       <c r="G77" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H77" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="J77" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K77" t="s">
         <v>55</v>
@@ -5460,13 +5544,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B78" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="C78" t="s">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="D78" t="s">
         <v>54</v>
@@ -5478,16 +5562,16 @@
         <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H78" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="I78" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J78" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K78" t="s">
         <v>55</v>
@@ -5504,13 +5588,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B79" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="C79" t="s">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="D79" t="s">
         <v>54</v>
@@ -5522,16 +5606,16 @@
         <v>13</v>
       </c>
       <c r="G79" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H79" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="I79" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J79" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K79" t="s">
         <v>55</v>
@@ -5548,13 +5632,13 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B80" t="s">
+        <v>301</v>
+      </c>
+      <c r="C80" t="s">
         <v>302</v>
-      </c>
-      <c r="B80" t="s">
-        <v>312</v>
-      </c>
-      <c r="C80" t="s">
-        <v>313</v>
       </c>
       <c r="D80" t="s">
         <v>54</v>
@@ -5566,16 +5650,16 @@
         <v>13</v>
       </c>
       <c r="G80" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H80" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="I80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J80" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="K80" t="s">
         <v>55</v>
@@ -5592,13 +5676,13 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B81" t="s">
         <v>303</v>
       </c>
-      <c r="B81" t="s">
-        <v>314</v>
-      </c>
       <c r="C81" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D81" t="s">
         <v>54</v>
@@ -5610,16 +5694,16 @@
         <v>13</v>
       </c>
       <c r="G81" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H81" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="I81" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J81" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K81" t="s">
         <v>55</v>
@@ -5636,13 +5720,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B82" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C82" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="D82" t="s">
         <v>54</v>
@@ -5654,16 +5738,16 @@
         <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H82" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="I82" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J82" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K82" t="s">
         <v>55</v>
@@ -5680,13 +5764,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B83" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C83" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D83" t="s">
         <v>54</v>
@@ -5698,16 +5782,16 @@
         <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H83" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="I83" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J83" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K83" t="s">
         <v>55</v>
@@ -5724,13 +5808,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B84" t="s">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="C84" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="D84" t="s">
         <v>54</v>
@@ -5742,16 +5826,16 @@
         <v>13</v>
       </c>
       <c r="G84" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="H84" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I84" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J84" t="s">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="K84" t="s">
         <v>55</v>
@@ -5768,13 +5852,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="B85" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="C85" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="D85" t="s">
         <v>54</v>
@@ -5786,16 +5870,16 @@
         <v>13</v>
       </c>
       <c r="G85" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H85" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="I85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J85" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K85" t="s">
         <v>55</v>
@@ -5812,13 +5896,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="B86" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="C86" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D86" t="s">
         <v>54</v>
@@ -5830,13 +5914,13 @@
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H86" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="J86" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K86" t="s">
         <v>55</v>
@@ -5853,13 +5937,13 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="B87" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C87" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="D87" t="s">
         <v>54</v>
@@ -5871,16 +5955,16 @@
         <v>13</v>
       </c>
       <c r="G87" t="s">
+        <v>314</v>
+      </c>
+      <c r="H87" t="s">
         <v>325</v>
       </c>
-      <c r="H87" t="s">
-        <v>336</v>
-      </c>
       <c r="I87" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J87" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="K87" t="s">
         <v>55</v>
@@ -5897,13 +5981,13 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="B88" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="C88" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D88" t="s">
         <v>54</v>
@@ -5915,16 +5999,16 @@
         <v>13</v>
       </c>
       <c r="G88" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H88" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="I88" t="s">
-        <v>340</v>
+        <v>167</v>
       </c>
       <c r="J88" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="K88" t="s">
         <v>55</v>
@@ -5941,13 +6025,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="B89" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="C89" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="D89" t="s">
         <v>54</v>
@@ -5959,13 +6043,13 @@
         <v>13</v>
       </c>
       <c r="G89" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H89" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J89" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K89" t="s">
         <v>55</v>
@@ -5982,16 +6066,16 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="B90" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="C90" t="s">
-        <v>510</v>
+        <v>489</v>
       </c>
       <c r="D90" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E90" t="s">
         <v>58</v>
@@ -6000,13 +6084,13 @@
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H90" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="J90" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K90" t="s">
         <v>55</v>
@@ -6023,16 +6107,16 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B91" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="C91" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="D91" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
@@ -6041,13 +6125,13 @@
         <v>32</v>
       </c>
       <c r="G91" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H91" t="s">
-        <v>371</v>
+        <v>324</v>
       </c>
       <c r="J91" t="s">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="K91" t="s">
         <v>55</v>
@@ -6064,16 +6148,16 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="B92" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="C92" t="s">
-        <v>511</v>
+        <v>490</v>
       </c>
       <c r="D92" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E92" t="s">
         <v>58</v>
@@ -6082,13 +6166,13 @@
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H92" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="J92" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K92" t="s">
         <v>55</v>
@@ -6105,16 +6189,16 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="B93" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="C93" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="D93" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E93" t="s">
         <v>58</v>
@@ -6123,16 +6207,16 @@
         <v>13</v>
       </c>
       <c r="G93" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H93" t="s">
-        <v>374</v>
+        <v>237</v>
       </c>
       <c r="I93" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J93" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K93" t="s">
         <v>55</v>
@@ -6149,16 +6233,16 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="B94" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C94" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D94" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -6167,13 +6251,13 @@
         <v>13</v>
       </c>
       <c r="G94" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H94" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="J94" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K94" t="s">
         <v>56</v>
@@ -6190,16 +6274,16 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="B95" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="C95" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="D95" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E95" t="s">
         <v>58</v>
@@ -6208,16 +6292,16 @@
         <v>13</v>
       </c>
       <c r="G95" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H95" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="I95" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J95" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K95" t="s">
         <v>55</v>
@@ -6234,16 +6318,16 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="B96" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="C96" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="D96" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E96" t="s">
         <v>58</v>
@@ -6252,16 +6336,16 @@
         <v>13</v>
       </c>
       <c r="G96" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="H96" t="s">
-        <v>384</v>
+        <v>574</v>
       </c>
       <c r="I96" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J96" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K96" t="s">
         <v>55</v>
@@ -6278,16 +6362,16 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="B97" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="C97" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="D97" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
@@ -6296,13 +6380,13 @@
         <v>32</v>
       </c>
       <c r="G97" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H97" t="s">
-        <v>83</v>
+        <v>575</v>
       </c>
       <c r="J97" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K97" t="s">
         <v>55</v>
@@ -6319,16 +6403,16 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B98" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="C98" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="D98" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E98" t="s">
         <v>58</v>
@@ -6337,13 +6421,13 @@
         <v>13</v>
       </c>
       <c r="G98" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H98" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J98" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K98" t="s">
         <v>55</v>
@@ -6360,16 +6444,16 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="B99" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="C99" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="D99" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E99" t="s">
         <v>58</v>
@@ -6378,16 +6462,16 @@
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H99" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="I99" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J99" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K99" t="s">
         <v>55</v>
@@ -6404,16 +6488,16 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="C100" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="D100" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E100" t="s">
         <v>58</v>
@@ -6422,16 +6506,16 @@
         <v>32</v>
       </c>
       <c r="G100" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="H100" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="I100" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J100" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K100" t="s">
         <v>55</v>
@@ -6448,16 +6532,16 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="B101" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="C101" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="D101" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E101" t="s">
         <v>58</v>
@@ -6466,16 +6550,16 @@
         <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="H101" t="s">
-        <v>379</v>
+        <v>241</v>
       </c>
       <c r="I101" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J101" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K101" t="s">
         <v>55</v>
@@ -6492,16 +6576,16 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="B102" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="C102" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="D102" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E102" t="s">
         <v>58</v>
@@ -6510,16 +6594,16 @@
         <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H102" t="s">
-        <v>379</v>
+        <v>241</v>
       </c>
       <c r="I102" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J102" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K102" t="s">
         <v>55</v>
@@ -6536,16 +6620,16 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="B103" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="C103" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="D103" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E103" t="s">
         <v>58</v>
@@ -6554,16 +6638,16 @@
         <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H103" t="s">
-        <v>379</v>
+        <v>241</v>
       </c>
       <c r="I103" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J103" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K103" t="s">
         <v>55</v>
@@ -6580,16 +6664,16 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="B104" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="C104" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="D104" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E104" t="s">
         <v>33</v>
@@ -6598,16 +6682,16 @@
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H104" t="s">
-        <v>384</v>
+        <v>574</v>
       </c>
       <c r="I104" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J104" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="K104" t="s">
         <v>55</v>
@@ -6624,16 +6708,16 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="B105" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C105" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="D105" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E105" t="s">
         <v>33</v>
@@ -6642,16 +6726,16 @@
         <v>32</v>
       </c>
       <c r="G105" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="H105" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="I105" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J105" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="K105" t="s">
         <v>55</v>
@@ -6668,16 +6752,16 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="B106" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="C106" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="D106" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E106" t="s">
         <v>58</v>
@@ -6686,13 +6770,13 @@
         <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H106" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="J106" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K106" t="s">
         <v>55</v>
@@ -6709,16 +6793,16 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="B107" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="C107" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="D107" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E107" t="s">
         <v>58</v>
@@ -6727,16 +6811,16 @@
         <v>32</v>
       </c>
       <c r="G107" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="H107" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="I107" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J107" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K107" t="s">
         <v>55</v>
@@ -6753,16 +6837,16 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="B108" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C108" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="D108" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E108" t="s">
         <v>33</v>
@@ -6771,13 +6855,13 @@
         <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="H108" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="J108" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K108" t="s">
         <v>55</v>
@@ -6794,16 +6878,16 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="B109" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="C109" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="D109" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E109" t="s">
         <v>58</v>
@@ -6812,13 +6896,13 @@
         <v>13</v>
       </c>
       <c r="G109" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H109" t="s">
-        <v>428</v>
+        <v>509</v>
       </c>
       <c r="J109" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K109" t="s">
         <v>55</v>
@@ -6835,16 +6919,16 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="B110" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="C110" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="D110" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E110" t="s">
         <v>58</v>
@@ -6853,16 +6937,16 @@
         <v>13</v>
       </c>
       <c r="G110" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H110" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="I110" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J110" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K110" t="s">
         <v>55</v>
@@ -6879,13 +6963,13 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="B111" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="C111" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="D111" t="s">
         <v>54</v>
@@ -6897,16 +6981,16 @@
         <v>32</v>
       </c>
       <c r="G111" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="H111" t="s">
-        <v>428</v>
+        <v>509</v>
       </c>
       <c r="I111" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="J111" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K111" t="s">
         <v>55</v>
@@ -6923,13 +7007,13 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B112" t="s">
         <v>431</v>
       </c>
-      <c r="B112" t="s">
-        <v>448</v>
-      </c>
       <c r="C112" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="D112" t="s">
         <v>54</v>
@@ -6941,13 +7025,13 @@
         <v>32</v>
       </c>
       <c r="G112" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="H112" t="s">
-        <v>450</v>
+        <v>568</v>
       </c>
       <c r="J112" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K112" t="s">
         <v>57</v>
@@ -6964,13 +7048,13 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="B113" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="C113" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="D113" t="s">
         <v>54</v>
@@ -6982,16 +7066,16 @@
         <v>32</v>
       </c>
       <c r="G113" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="H113" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="I113" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J113" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K113" t="s">
         <v>55</v>
@@ -7008,31 +7092,31 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="B114" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="C114" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="D114" t="s">
         <v>54</v>
       </c>
       <c r="E114" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F114" t="s">
         <v>13</v>
       </c>
       <c r="G114" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H114" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="J114" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="K114" t="s">
         <v>55</v>
@@ -7049,13 +7133,13 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="B115" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="C115" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="D115" t="s">
         <v>54</v>
@@ -7067,16 +7151,16 @@
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H115" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="I115" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J115" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K115" t="s">
         <v>55</v>
@@ -7093,13 +7177,13 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="B116" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="C116" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="D116" t="s">
         <v>54</v>
@@ -7111,16 +7195,16 @@
         <v>13</v>
       </c>
       <c r="G116" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="H116" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="I116" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J116" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="K116" t="s">
         <v>55</v>
@@ -7137,13 +7221,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="B117" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="C117" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="D117" t="s">
         <v>54</v>
@@ -7155,13 +7239,13 @@
         <v>13</v>
       </c>
       <c r="G117" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="H117" t="s">
-        <v>466</v>
+        <v>576</v>
       </c>
       <c r="J117" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K117" t="s">
         <v>55</v>
@@ -7178,13 +7262,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="B118" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="C118" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="D118" t="s">
         <v>54</v>
@@ -7196,13 +7280,13 @@
         <v>13</v>
       </c>
       <c r="G118" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H118" t="s">
-        <v>230</v>
+        <v>121</v>
       </c>
       <c r="J118" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K118" t="s">
         <v>55</v>
@@ -7219,13 +7303,13 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="B119" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="C119" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="D119" t="s">
         <v>54</v>
@@ -7237,16 +7321,16 @@
         <v>13</v>
       </c>
       <c r="G119" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="H119" t="s">
-        <v>230</v>
+        <v>573</v>
       </c>
       <c r="I119" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J119" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K119" t="s">
         <v>55</v>
@@ -7263,13 +7347,13 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="B120" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="C120" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="D120" t="s">
         <v>54</v>
@@ -7281,13 +7365,13 @@
         <v>13</v>
       </c>
       <c r="G120" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H120" t="s">
-        <v>246</v>
+        <v>577</v>
       </c>
       <c r="J120" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="K120" t="s">
         <v>55</v>
@@ -7304,13 +7388,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="B121" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="C121" t="s">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="D121" t="s">
         <v>54</v>
@@ -7322,13 +7406,13 @@
         <v>13</v>
       </c>
       <c r="G121" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H121" t="s">
-        <v>127</v>
+        <v>578</v>
       </c>
       <c r="J121" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="K121" t="s">
         <v>55</v>
@@ -7345,34 +7429,34 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="B122" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="C122" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="D122" t="s">
         <v>54</v>
       </c>
       <c r="E122" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F122" t="s">
         <v>13</v>
       </c>
       <c r="G122" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H122" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="I122" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J122" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K122" t="s">
         <v>55</v>
@@ -7389,13 +7473,13 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="B123" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="C123" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="D123" t="s">
         <v>54</v>
@@ -7407,13 +7491,13 @@
         <v>13</v>
       </c>
       <c r="G123" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H123" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="J123" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="K123" t="s">
         <v>55</v>
@@ -7430,34 +7514,34 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="B124" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="C124" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="D124" t="s">
         <v>54</v>
       </c>
       <c r="E124" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F124" t="s">
         <v>32</v>
       </c>
       <c r="G124" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H124" t="s">
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="I124" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J124" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K124" t="s">
         <v>55</v>
@@ -7474,13 +7558,13 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="B125" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="C125" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="D125" t="s">
         <v>54</v>
@@ -7492,13 +7576,13 @@
         <v>13</v>
       </c>
       <c r="G125" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H125" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="J125" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K125" t="s">
         <v>55</v>
@@ -7515,13 +7599,13 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="B126" t="s">
-        <v>489</v>
+        <v>470</v>
       </c>
       <c r="C126" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="D126" t="s">
         <v>54</v>
@@ -7533,13 +7617,13 @@
         <v>13</v>
       </c>
       <c r="G126" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H126" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="J126" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K126" t="s">
         <v>55</v>
@@ -7556,34 +7640,34 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="B127" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="C127" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="D127" t="s">
         <v>54</v>
       </c>
       <c r="E127" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F127" t="s">
         <v>32</v>
       </c>
       <c r="G127" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H127" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I127" t="s">
-        <v>516</v>
+        <v>495</v>
       </c>
       <c r="J127" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K127" t="s">
         <v>55</v>
@@ -7600,13 +7684,13 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="B128" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="C128" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="D128" t="s">
         <v>54</v>
@@ -7618,16 +7702,16 @@
         <v>32</v>
       </c>
       <c r="G128" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H128" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I128" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J128" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K128" t="s">
         <v>55</v>
@@ -7644,13 +7728,13 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="B129" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="C129" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="D129" t="s">
         <v>54</v>
@@ -7662,16 +7746,16 @@
         <v>13</v>
       </c>
       <c r="G129" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H129" t="s">
-        <v>497</v>
+        <v>579</v>
       </c>
       <c r="I129" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J129" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K129" t="s">
         <v>55</v>
@@ -7688,34 +7772,34 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="B130" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="C130" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="D130" t="s">
         <v>54</v>
       </c>
       <c r="E130" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F130" t="s">
         <v>13</v>
       </c>
       <c r="G130" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H130" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="I130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J130" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K130" t="s">
         <v>56</v>
@@ -7732,16 +7816,16 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="B131" t="s">
-        <v>513</v>
+        <v>492</v>
       </c>
       <c r="C131" t="s">
-        <v>512</v>
+        <v>491</v>
       </c>
       <c r="D131" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E131" t="s">
         <v>58</v>
@@ -7750,16 +7834,16 @@
         <v>13</v>
       </c>
       <c r="G131" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H131" t="s">
-        <v>218</v>
+        <v>305</v>
       </c>
       <c r="I131" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J131" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K131" t="s">
         <v>55</v>
@@ -7776,16 +7860,16 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="B132" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="C132" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
       <c r="D132" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E132" t="s">
         <v>33</v>
@@ -7794,13 +7878,13 @@
         <v>13</v>
       </c>
       <c r="G132" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H132" t="s">
-        <v>505</v>
+        <v>580</v>
       </c>
       <c r="J132" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K132" t="s">
         <v>55</v>
@@ -7817,13 +7901,13 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="B133" t="s">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="C133" t="s">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="D133" t="s">
         <v>54</v>
@@ -7835,16 +7919,16 @@
         <v>13</v>
       </c>
       <c r="G133" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H133" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="I133" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J133" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K133" t="s">
         <v>55</v>
@@ -7861,13 +7945,13 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
       <c r="B134" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="C134" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="D134" t="s">
         <v>54</v>
@@ -7879,16 +7963,16 @@
         <v>32</v>
       </c>
       <c r="G134" t="s">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="H134" t="s">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="I134" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J134" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="K134" t="s">
         <v>55</v>
@@ -7905,13 +7989,13 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="B135" t="s">
-        <v>526</v>
+        <v>505</v>
       </c>
       <c r="C135" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="D135" t="s">
         <v>54</v>
@@ -7923,16 +8007,16 @@
         <v>13</v>
       </c>
       <c r="G135" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H135" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="I135" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J135" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K135" t="s">
         <v>55</v>
@@ -7949,13 +8033,13 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="B136" t="s">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="C136" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="D136" t="s">
         <v>54</v>
@@ -7967,16 +8051,16 @@
         <v>13</v>
       </c>
       <c r="G136" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H136" t="s">
-        <v>530</v>
+        <v>509</v>
       </c>
       <c r="I136" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J136" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K136" t="s">
         <v>55</v>
@@ -7993,13 +8077,13 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="B137" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="C137" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="D137" t="s">
         <v>54</v>
@@ -8011,16 +8095,16 @@
         <v>13</v>
       </c>
       <c r="G137" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H137" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="I137" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J137" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K137" t="s">
         <v>55</v>
@@ -8037,13 +8121,13 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="B138" t="s">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="C138" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="D138" t="s">
         <v>54</v>
@@ -8055,16 +8139,16 @@
         <v>13</v>
       </c>
       <c r="G138" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H138" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="I138" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J138" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K138" t="s">
         <v>55</v>
@@ -8081,13 +8165,13 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="B139" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="C139" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="D139" t="s">
         <v>54</v>
@@ -8099,16 +8183,16 @@
         <v>13</v>
       </c>
       <c r="G139" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H139" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
       <c r="I139" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J139" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K139" t="s">
         <v>55</v>
@@ -8125,34 +8209,34 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="B140" t="s">
-        <v>550</v>
+        <v>528</v>
       </c>
       <c r="C140" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="D140" t="s">
         <v>54</v>
       </c>
       <c r="E140" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F140" t="s">
         <v>32</v>
       </c>
       <c r="G140" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
       <c r="H140" t="s">
-        <v>530</v>
+        <v>509</v>
       </c>
       <c r="I140" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J140" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K140" t="s">
         <v>55</v>
@@ -8169,13 +8253,13 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="B141" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
       <c r="C141" t="s">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="D141" t="s">
         <v>54</v>
@@ -8187,16 +8271,16 @@
         <v>32</v>
       </c>
       <c r="G141" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
       <c r="H141" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="I141" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J141" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K141" t="s">
         <v>56</v>
@@ -8213,34 +8297,34 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="B142" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="C142" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D142" t="s">
         <v>54</v>
       </c>
       <c r="E142" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F142" t="s">
         <v>13</v>
       </c>
       <c r="G142" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H142" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="I142" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J142" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K142" t="s">
         <v>57</v>
@@ -8257,34 +8341,34 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="B143" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="C143" t="s">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="D143" t="s">
         <v>54</v>
       </c>
       <c r="E143" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F143" t="s">
         <v>32</v>
       </c>
       <c r="G143" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H143" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="I143" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J143" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K143" t="s">
         <v>55</v>
@@ -8301,13 +8385,13 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="B144" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="C144" t="s">
-        <v>560</v>
+        <v>538</v>
       </c>
       <c r="D144" t="s">
         <v>54</v>
@@ -8319,16 +8403,16 @@
         <v>32</v>
       </c>
       <c r="G144" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H144" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
       <c r="I144" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J144" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K144" t="s">
         <v>55</v>
@@ -8345,13 +8429,13 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B145" t="s">
         <v>540</v>
       </c>
-      <c r="B145" t="s">
-        <v>562</v>
-      </c>
       <c r="C145" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="D145" t="s">
         <v>54</v>
@@ -8363,16 +8447,16 @@
         <v>13</v>
       </c>
       <c r="G145" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H145" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="I145" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J145" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K145" t="s">
         <v>57</v>
@@ -8389,16 +8473,16 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="B146" t="s">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="C146" t="s">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="D146" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E146" t="s">
         <v>58</v>
@@ -8407,16 +8491,16 @@
         <v>13</v>
       </c>
       <c r="G146" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H146" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
       <c r="I146" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J146" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="K146" t="s">
         <v>55</v>
@@ -8433,16 +8517,16 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="B147" t="s">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="C147" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="D147" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E147" t="s">
         <v>58</v>
@@ -8451,16 +8535,16 @@
         <v>13</v>
       </c>
       <c r="G147" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H147" t="s">
-        <v>218</v>
+        <v>305</v>
       </c>
       <c r="I147" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J147" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K147" t="s">
         <v>55</v>
@@ -8477,16 +8561,16 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="B148" t="s">
-        <v>574</v>
+        <v>552</v>
       </c>
       <c r="C148" t="s">
-        <v>575</v>
+        <v>553</v>
       </c>
       <c r="D148" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E148" t="s">
         <v>58</v>
@@ -8495,16 +8579,16 @@
         <v>13</v>
       </c>
       <c r="G148" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H148" t="s">
-        <v>576</v>
+        <v>358</v>
       </c>
       <c r="I148" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J148" t="s">
-        <v>577</v>
+        <v>103</v>
       </c>
       <c r="K148" t="s">
         <v>55</v>
@@ -8521,16 +8605,16 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
       <c r="B149" t="s">
-        <v>578</v>
+        <v>554</v>
       </c>
       <c r="C149" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="D149" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E149" t="s">
         <v>58</v>
@@ -8539,16 +8623,16 @@
         <v>13</v>
       </c>
       <c r="G149" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H149" t="s">
-        <v>218</v>
+        <v>305</v>
       </c>
       <c r="I149" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J149" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K149" t="s">
         <v>55</v>
@@ -8565,16 +8649,16 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="B150" t="s">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="C150" t="s">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="D150" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E150" t="s">
         <v>33</v>
@@ -8583,13 +8667,13 @@
         <v>13</v>
       </c>
       <c r="G150" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H150" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="J150" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="K150" t="s">
         <v>55</v>
@@ -8606,16 +8690,16 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="B151" t="s">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="C151" t="s">
-        <v>582</v>
+        <v>558</v>
       </c>
       <c r="D151" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E151" t="s">
         <v>33</v>
@@ -8624,13 +8708,13 @@
         <v>32</v>
       </c>
       <c r="G151" t="s">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="H151" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="J151" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K151" t="s">
         <v>56</v>
@@ -8647,16 +8731,16 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="B152" t="s">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="C152" t="s">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="D152" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E152" t="s">
         <v>58</v>
@@ -8665,13 +8749,13 @@
         <v>13</v>
       </c>
       <c r="G152" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H152" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J152" t="s">
-        <v>475</v>
+        <v>211</v>
       </c>
       <c r="K152" t="s">
         <v>55</v>
@@ -8683,6 +8767,393 @@
         <v>15</v>
       </c>
       <c r="N152" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B153" t="s">
+        <v>590</v>
+      </c>
+      <c r="C153" t="s">
+        <v>591</v>
+      </c>
+      <c r="D153" t="s">
+        <v>54</v>
+      </c>
+      <c r="E153" t="s">
+        <v>33</v>
+      </c>
+      <c r="F153" t="s">
+        <v>13</v>
+      </c>
+      <c r="G153" t="s">
+        <v>256</v>
+      </c>
+      <c r="H153" t="s">
+        <v>310</v>
+      </c>
+      <c r="I153" t="s">
+        <v>82</v>
+      </c>
+      <c r="J153" t="s">
+        <v>592</v>
+      </c>
+      <c r="K153" t="s">
+        <v>55</v>
+      </c>
+      <c r="L153" t="s">
+        <v>14</v>
+      </c>
+      <c r="M153" t="s">
+        <v>15</v>
+      </c>
+      <c r="N153" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B154" t="s">
+        <v>593</v>
+      </c>
+      <c r="C154" t="s">
+        <v>594</v>
+      </c>
+      <c r="D154" t="s">
+        <v>54</v>
+      </c>
+      <c r="E154" t="s">
+        <v>33</v>
+      </c>
+      <c r="F154" t="s">
+        <v>13</v>
+      </c>
+      <c r="G154" t="s">
+        <v>256</v>
+      </c>
+      <c r="H154" t="s">
+        <v>391</v>
+      </c>
+      <c r="J154" t="s">
+        <v>84</v>
+      </c>
+      <c r="K154" t="s">
+        <v>55</v>
+      </c>
+      <c r="L154" t="s">
+        <v>14</v>
+      </c>
+      <c r="M154" t="s">
+        <v>15</v>
+      </c>
+      <c r="N154" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B155" t="s">
+        <v>595</v>
+      </c>
+      <c r="C155" t="s">
+        <v>596</v>
+      </c>
+      <c r="D155" t="s">
+        <v>54</v>
+      </c>
+      <c r="E155" t="s">
+        <v>33</v>
+      </c>
+      <c r="F155" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" t="s">
+        <v>256</v>
+      </c>
+      <c r="H155" t="s">
+        <v>324</v>
+      </c>
+      <c r="I155" t="s">
+        <v>61</v>
+      </c>
+      <c r="J155" t="s">
+        <v>211</v>
+      </c>
+      <c r="K155" t="s">
+        <v>55</v>
+      </c>
+      <c r="L155" t="s">
+        <v>14</v>
+      </c>
+      <c r="M155" t="s">
+        <v>15</v>
+      </c>
+      <c r="N155" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B156" t="s">
+        <v>597</v>
+      </c>
+      <c r="C156" t="s">
+        <v>598</v>
+      </c>
+      <c r="D156" t="s">
+        <v>54</v>
+      </c>
+      <c r="E156" t="s">
+        <v>33</v>
+      </c>
+      <c r="F156" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" t="s">
+        <v>168</v>
+      </c>
+      <c r="H156" t="s">
+        <v>391</v>
+      </c>
+      <c r="I156" t="s">
+        <v>61</v>
+      </c>
+      <c r="J156" t="s">
+        <v>329</v>
+      </c>
+      <c r="K156" t="s">
+        <v>55</v>
+      </c>
+      <c r="L156" t="s">
+        <v>14</v>
+      </c>
+      <c r="M156" t="s">
+        <v>15</v>
+      </c>
+      <c r="N156" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B157" t="s">
+        <v>599</v>
+      </c>
+      <c r="C157" t="s">
+        <v>600</v>
+      </c>
+      <c r="D157" t="s">
+        <v>54</v>
+      </c>
+      <c r="E157" t="s">
+        <v>33</v>
+      </c>
+      <c r="F157" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" t="s">
+        <v>256</v>
+      </c>
+      <c r="H157" t="s">
+        <v>324</v>
+      </c>
+      <c r="I157" t="s">
+        <v>61</v>
+      </c>
+      <c r="J157" t="s">
+        <v>211</v>
+      </c>
+      <c r="K157" t="s">
+        <v>55</v>
+      </c>
+      <c r="L157" t="s">
+        <v>14</v>
+      </c>
+      <c r="M157" t="s">
+        <v>15</v>
+      </c>
+      <c r="N157" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B158" t="s">
+        <v>605</v>
+      </c>
+      <c r="C158" t="s">
+        <v>606</v>
+      </c>
+      <c r="D158" t="s">
+        <v>85</v>
+      </c>
+      <c r="E158" t="s">
+        <v>58</v>
+      </c>
+      <c r="F158" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" t="s">
+        <v>168</v>
+      </c>
+      <c r="H158" t="s">
+        <v>391</v>
+      </c>
+      <c r="I158" t="s">
+        <v>82</v>
+      </c>
+      <c r="J158" t="s">
+        <v>221</v>
+      </c>
+      <c r="K158" t="s">
+        <v>55</v>
+      </c>
+      <c r="L158" t="s">
+        <v>14</v>
+      </c>
+      <c r="M158" t="s">
+        <v>15</v>
+      </c>
+      <c r="N158" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B159" t="s">
+        <v>607</v>
+      </c>
+      <c r="C159" t="s">
+        <v>608</v>
+      </c>
+      <c r="D159" t="s">
+        <v>85</v>
+      </c>
+      <c r="E159" t="s">
+        <v>33</v>
+      </c>
+      <c r="F159" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" t="s">
+        <v>168</v>
+      </c>
+      <c r="H159" t="s">
+        <v>391</v>
+      </c>
+      <c r="J159" t="s">
+        <v>221</v>
+      </c>
+      <c r="K159" t="s">
+        <v>55</v>
+      </c>
+      <c r="L159" t="s">
+        <v>14</v>
+      </c>
+      <c r="M159" t="s">
+        <v>15</v>
+      </c>
+      <c r="N159" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B160" t="s">
+        <v>609</v>
+      </c>
+      <c r="C160" t="s">
+        <v>610</v>
+      </c>
+      <c r="D160" t="s">
+        <v>85</v>
+      </c>
+      <c r="E160" t="s">
+        <v>33</v>
+      </c>
+      <c r="F160" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" t="s">
+        <v>611</v>
+      </c>
+      <c r="H160" t="s">
+        <v>572</v>
+      </c>
+      <c r="I160" t="s">
+        <v>82</v>
+      </c>
+      <c r="J160" t="s">
+        <v>105</v>
+      </c>
+      <c r="K160" t="s">
+        <v>55</v>
+      </c>
+      <c r="L160" t="s">
+        <v>14</v>
+      </c>
+      <c r="M160" t="s">
+        <v>15</v>
+      </c>
+      <c r="N160" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B161" t="s">
+        <v>612</v>
+      </c>
+      <c r="C161" t="s">
+        <v>613</v>
+      </c>
+      <c r="D161" t="s">
+        <v>85</v>
+      </c>
+      <c r="E161" t="s">
+        <v>58</v>
+      </c>
+      <c r="F161" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" t="s">
+        <v>168</v>
+      </c>
+      <c r="H161" t="s">
+        <v>391</v>
+      </c>
+      <c r="J161" t="s">
+        <v>221</v>
+      </c>
+      <c r="K161" t="s">
+        <v>55</v>
+      </c>
+      <c r="L161" t="s">
+        <v>14</v>
+      </c>
+      <c r="M161" t="s">
+        <v>15</v>
+      </c>
+      <c r="N161" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2339E9E8-9815-9E4A-BCC7-BDF741F12516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78E4303-7D33-3D43-93B3-F9DA4F5B7163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="639">
   <si>
     <t>id</t>
   </si>
@@ -607,9 +607,6 @@
     <t>GVX Verano 2016</t>
   </si>
   <si>
-    <t>GVX Comunidad Verano 2018</t>
-  </si>
-  <si>
     <t>Camiseta Da Vida 2018</t>
   </si>
   <si>
@@ -838,9 +835,6 @@
     <t>GVX Pascua 2023</t>
   </si>
   <si>
-    <t>Camiseta Tanto va… 2023</t>
-  </si>
-  <si>
     <t>GVX Sticker Pascua 2025</t>
   </si>
   <si>
@@ -1243,9 +1237,6 @@
     <t>GVX Verano 2018</t>
   </si>
   <si>
-    <t xml:space="preserve">DA VIDA </t>
-  </si>
-  <si>
     <t>Arturo_MP_Texeira_ProvMediterranea</t>
   </si>
   <si>
@@ -1615,9 +1606,6 @@
     <t>No-Violencia</t>
   </si>
   <si>
-    <t>paz;educacion</t>
-  </si>
-  <si>
     <t>Como María</t>
   </si>
   <si>
@@ -1639,9 +1627,6 @@
     <t>Paloma y rama de olivo</t>
   </si>
   <si>
-    <t>educacion;paz</t>
-  </si>
-  <si>
     <t>Pajarita de papel</t>
   </si>
   <si>
@@ -1666,12 +1651,6 @@
     <t>DIS-0062</t>
   </si>
   <si>
-    <t>Posible logo</t>
-  </si>
-  <si>
-    <t>MarCha Maristas Toledo</t>
-  </si>
-  <si>
     <t>Hey Bro (por)</t>
   </si>
   <si>
@@ -1756,9 +1735,6 @@
     <t>social;educacion</t>
   </si>
   <si>
-    <t>maristas;educacion;infantil</t>
-  </si>
-  <si>
     <t>champagnat;educacion</t>
   </si>
   <si>
@@ -1862,6 +1838,105 @@
   </si>
   <si>
     <t xml:space="preserve">Camiseta GVX 2007 </t>
+  </si>
+  <si>
+    <t>Camiseta Tanto va… 2023 (frontal)</t>
+  </si>
+  <si>
+    <t>GVX Verano 2018 Comunidad</t>
+  </si>
+  <si>
+    <t>maristas;educacion;social</t>
+  </si>
+  <si>
+    <t>educacion;social</t>
+  </si>
+  <si>
+    <t>maristas;social</t>
+  </si>
+  <si>
+    <t>paz;educacion;social</t>
+  </si>
+  <si>
+    <t>maria;evangelio;social</t>
+  </si>
+  <si>
+    <t>educacion;paz;social</t>
+  </si>
+  <si>
+    <t>GVX;evangelio;social</t>
+  </si>
+  <si>
+    <t>champagnat;vocacional;social</t>
+  </si>
+  <si>
+    <t>champagnat;social</t>
+  </si>
+  <si>
+    <t>champagnat;maristas;vocacional;social</t>
+  </si>
+  <si>
+    <t>vocacional;social</t>
+  </si>
+  <si>
+    <t>DIS-0067</t>
+  </si>
+  <si>
+    <t>DIS-0068</t>
+  </si>
+  <si>
+    <t>DIS-0069</t>
+  </si>
+  <si>
+    <t>GVX Verano 2023 (Bordado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polo GVX 2023 </t>
+  </si>
+  <si>
+    <t>Camiseta GMG-JMJ Lisboa (espalda)</t>
+  </si>
+  <si>
+    <t>GVX;maristas</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2024 (ita)</t>
+  </si>
+  <si>
+    <t>Maristas en la JMJ 2023 (esp-ita)</t>
+  </si>
+  <si>
+    <t>Scegliere. Vivere. Andare</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiseta GA. DA VIDA </t>
+  </si>
+  <si>
+    <t>ILU-0095</t>
+  </si>
+  <si>
+    <t>ILU-0096</t>
+  </si>
+  <si>
+    <t>La Chispa II</t>
+  </si>
+  <si>
+    <t>Luz. Presencia.</t>
+  </si>
+  <si>
+    <t>Be Light</t>
+  </si>
+  <si>
+    <t>Diseño para GVX</t>
+  </si>
+  <si>
+    <t>Marcha Toledo</t>
+  </si>
+  <si>
+    <t>Posible Logo</t>
   </si>
 </sst>
 </file>
@@ -2218,7 +2293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N161"/>
+  <dimension ref="A1:N166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
@@ -2284,7 +2359,7 @@
         <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D2" t="s">
         <v>54</v>
@@ -2299,13 +2374,13 @@
         <v>168</v>
       </c>
       <c r="H2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I2" t="s">
         <v>167</v>
       </c>
       <c r="J2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -2328,7 +2403,7 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D3" t="s">
         <v>54</v>
@@ -2346,10 +2421,10 @@
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="J3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K3" t="s">
         <v>56</v>
@@ -2369,7 +2444,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C4" t="s">
         <v>86</v>
@@ -2542,7 +2617,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -2563,7 +2638,7 @@
         <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="K8" t="s">
         <v>55</v>
@@ -2627,7 +2702,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C10" t="s">
         <v>90</v>
@@ -2671,7 +2746,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
@@ -2715,7 +2790,7 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C12" t="s">
         <v>92</v>
@@ -2759,7 +2834,7 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C13" t="s">
         <v>93</v>
@@ -2783,7 +2858,7 @@
         <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
@@ -2803,7 +2878,7 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C14" t="s">
         <v>94</v>
@@ -2862,10 +2937,10 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H15" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="I15" t="s">
         <v>102</v>
@@ -2959,7 +3034,7 @@
         <v>61</v>
       </c>
       <c r="J17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K17" t="s">
         <v>55</v>
@@ -2997,10 +3072,10 @@
         <v>119</v>
       </c>
       <c r="H18" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="J18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K18" t="s">
         <v>55</v>
@@ -3164,13 +3239,13 @@
         <v>168</v>
       </c>
       <c r="H22" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="I22" t="s">
         <v>61</v>
       </c>
       <c r="J22" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K22" t="s">
         <v>55</v>
@@ -3214,7 +3289,7 @@
         <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K23" t="s">
         <v>55</v>
@@ -3290,10 +3365,10 @@
         <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H25" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J25" t="s">
         <v>83</v>
@@ -3331,10 +3406,10 @@
         <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H26" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J26" t="s">
         <v>103</v>
@@ -3422,7 +3497,7 @@
         <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="K28" t="s">
         <v>56</v>
@@ -3460,7 +3535,7 @@
         <v>97</v>
       </c>
       <c r="H29" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J29" t="s">
         <v>83</v>
@@ -3498,7 +3573,7 @@
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H30" t="s">
         <v>154</v>
@@ -3539,7 +3614,7 @@
         <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H31" t="s">
         <v>154</v>
@@ -3583,7 +3658,7 @@
         <v>168</v>
       </c>
       <c r="H32" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="J32" t="s">
         <v>103</v>
@@ -3624,7 +3699,7 @@
         <v>168</v>
       </c>
       <c r="H33" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="J33" t="s">
         <v>103</v>
@@ -3665,13 +3740,13 @@
         <v>97</v>
       </c>
       <c r="H34" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I34" t="s">
         <v>167</v>
       </c>
       <c r="J34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K34" t="s">
         <v>55</v>
@@ -3729,16 +3804,16 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="B36" t="s">
-        <v>336</v>
+        <v>217</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>218</v>
       </c>
       <c r="D36" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
         <v>58</v>
@@ -3750,13 +3825,13 @@
         <v>168</v>
       </c>
       <c r="H36" t="s">
-        <v>568</v>
+        <v>219</v>
       </c>
       <c r="I36" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="J36" t="s">
-        <v>211</v>
+        <v>398</v>
       </c>
       <c r="K36" t="s">
         <v>55</v>
@@ -3773,16 +3848,16 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>64</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>226</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>227</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
         <v>58</v>
@@ -3791,16 +3866,16 @@
         <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>168</v>
+        <v>257</v>
       </c>
       <c r="H37" t="s">
-        <v>566</v>
+        <v>228</v>
       </c>
       <c r="I37" t="s">
         <v>82</v>
       </c>
       <c r="J37" t="s">
-        <v>103</v>
+        <v>229</v>
       </c>
       <c r="K37" t="s">
         <v>55</v>
@@ -3817,19 +3892,19 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>65</v>
+        <v>222</v>
       </c>
       <c r="B38" t="s">
-        <v>337</v>
+        <v>230</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>231</v>
       </c>
       <c r="D38" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E38" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
         <v>13</v>
@@ -3838,13 +3913,13 @@
         <v>168</v>
       </c>
       <c r="H38" t="s">
-        <v>35</v>
+        <v>236</v>
       </c>
       <c r="I38" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="J38" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="K38" t="s">
         <v>55</v>
@@ -3861,16 +3936,16 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>233</v>
       </c>
       <c r="C39" t="s">
-        <v>338</v>
+        <v>234</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E39" t="s">
         <v>33</v>
@@ -3882,13 +3957,16 @@
         <v>168</v>
       </c>
       <c r="H39" t="s">
-        <v>569</v>
+        <v>235</v>
+      </c>
+      <c r="I39" t="s">
+        <v>60</v>
       </c>
       <c r="J39" t="s">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="K39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L39" t="s">
         <v>14</v>
@@ -3902,34 +3980,34 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="D40" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E40" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G40" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="H40" t="s">
-        <v>564</v>
+        <v>240</v>
       </c>
       <c r="I40" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="J40" t="s">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="K40" t="s">
         <v>55</v>
@@ -3946,19 +4024,19 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>68</v>
+        <v>225</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>241</v>
       </c>
       <c r="C41" t="s">
-        <v>339</v>
+        <v>242</v>
       </c>
       <c r="D41" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E41" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
         <v>13</v>
@@ -3967,10 +4045,13 @@
         <v>168</v>
       </c>
       <c r="H41" t="s">
-        <v>566</v>
+        <v>235</v>
+      </c>
+      <c r="I41" t="s">
+        <v>60</v>
       </c>
       <c r="J41" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K41" t="s">
         <v>55</v>
@@ -3987,34 +4068,34 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>69</v>
+        <v>243</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="D42" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E42" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>257</v>
+        <v>168</v>
       </c>
       <c r="H42" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I42" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="J42" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K42" t="s">
         <v>55</v>
@@ -4031,37 +4112,37 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>108</v>
+        <v>244</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="C43" t="s">
-        <v>110</v>
+        <v>484</v>
       </c>
       <c r="D43" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F43" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H43" t="s">
-        <v>28</v>
+        <v>566</v>
       </c>
       <c r="I43" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="J43" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="K43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L43" t="s">
         <v>14</v>
@@ -4075,34 +4156,34 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>147</v>
+        <v>245</v>
       </c>
       <c r="B44" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="D44" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F44" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G44" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
       <c r="H44" t="s">
-        <v>154</v>
+        <v>566</v>
       </c>
       <c r="I44" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="J44" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="K44" t="s">
         <v>55</v>
@@ -4119,37 +4200,37 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>148</v>
+        <v>246</v>
       </c>
       <c r="B45" t="s">
-        <v>153</v>
+        <v>251</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E45" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G45" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H45" t="s">
-        <v>154</v>
+        <v>566</v>
       </c>
       <c r="I45" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="J45" t="s">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="K45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L45" t="s">
         <v>14</v>
@@ -4163,19 +4244,19 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>149</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s">
-        <v>155</v>
+        <v>286</v>
       </c>
       <c r="C46" t="s">
-        <v>156</v>
+        <v>482</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E46" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
         <v>13</v>
@@ -4184,13 +4265,13 @@
         <v>168</v>
       </c>
       <c r="H46" t="s">
-        <v>121</v>
+        <v>389</v>
       </c>
       <c r="I46" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="J46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K46" t="s">
         <v>55</v>
@@ -4207,31 +4288,34 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>177</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s">
-        <v>186</v>
+        <v>288</v>
       </c>
       <c r="C47" t="s">
-        <v>187</v>
+        <v>483</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E47" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F47" t="s">
         <v>13</v>
       </c>
       <c r="G47" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H47" t="s">
-        <v>391</v>
+        <v>389</v>
+      </c>
+      <c r="I47" t="s">
+        <v>167</v>
       </c>
       <c r="J47" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K47" t="s">
         <v>55</v>
@@ -4248,34 +4332,34 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>178</v>
+        <v>289</v>
       </c>
       <c r="B48" t="s">
-        <v>188</v>
+        <v>299</v>
       </c>
       <c r="C48" t="s">
-        <v>189</v>
+        <v>300</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E48" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F48" t="s">
         <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
-        <v>391</v>
+        <v>240</v>
       </c>
       <c r="I48" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="J48" t="s">
-        <v>221</v>
+        <v>309</v>
       </c>
       <c r="K48" t="s">
         <v>55</v>
@@ -4292,16 +4376,16 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>179</v>
+        <v>290</v>
       </c>
       <c r="B49" t="s">
-        <v>190</v>
+        <v>301</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>302</v>
       </c>
       <c r="D49" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E49" t="s">
         <v>58</v>
@@ -4310,13 +4394,16 @@
         <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H49" t="s">
-        <v>391</v>
+        <v>303</v>
+      </c>
+      <c r="I49" t="s">
+        <v>157</v>
       </c>
       <c r="J49" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K49" t="s">
         <v>55</v>
@@ -4333,34 +4420,34 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>180</v>
+        <v>291</v>
       </c>
       <c r="B50" t="s">
-        <v>192</v>
+        <v>304</v>
       </c>
       <c r="C50" t="s">
-        <v>193</v>
+        <v>306</v>
       </c>
       <c r="D50" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F50" t="s">
         <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="H50" t="s">
-        <v>391</v>
+        <v>322</v>
       </c>
       <c r="I50" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="J50" t="s">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="K50" t="s">
         <v>55</v>
@@ -4377,34 +4464,34 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>181</v>
+        <v>292</v>
       </c>
       <c r="B51" t="s">
-        <v>194</v>
+        <v>305</v>
       </c>
       <c r="C51" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="D51" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E51" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F51" t="s">
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>318</v>
+        <v>257</v>
       </c>
       <c r="H51" t="s">
-        <v>391</v>
+        <v>322</v>
       </c>
       <c r="I51" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="J51" t="s">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="K51" t="s">
         <v>55</v>
@@ -4421,31 +4508,34 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>182</v>
+        <v>293</v>
       </c>
       <c r="B52" t="s">
-        <v>195</v>
+        <v>485</v>
       </c>
       <c r="C52" t="s">
-        <v>196</v>
+        <v>310</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F52" t="s">
         <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H52" t="s">
-        <v>571</v>
+        <v>121</v>
+      </c>
+      <c r="I52" t="s">
+        <v>167</v>
       </c>
       <c r="J52" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="K52" t="s">
         <v>55</v>
@@ -4462,16 +4552,16 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>183</v>
+        <v>294</v>
       </c>
       <c r="B53" t="s">
-        <v>197</v>
+        <v>317</v>
       </c>
       <c r="C53" t="s">
-        <v>198</v>
+        <v>318</v>
       </c>
       <c r="D53" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -4480,13 +4570,16 @@
         <v>13</v>
       </c>
       <c r="G53" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H53" t="s">
-        <v>391</v>
+        <v>319</v>
+      </c>
+      <c r="I53" t="s">
+        <v>61</v>
       </c>
       <c r="J53" t="s">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="K53" t="s">
         <v>55</v>
@@ -4503,34 +4596,31 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="B54" t="s">
-        <v>199</v>
+        <v>320</v>
       </c>
       <c r="C54" t="s">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="D54" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E54" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="H54" t="s">
-        <v>391</v>
-      </c>
-      <c r="I54" t="s">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="J54" t="s">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="K54" t="s">
         <v>55</v>
@@ -4547,16 +4637,16 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>185</v>
+        <v>296</v>
       </c>
       <c r="B55" t="s">
-        <v>201</v>
+        <v>325</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
       <c r="D55" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E55" t="s">
         <v>33</v>
@@ -4565,16 +4655,16 @@
         <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H55" t="s">
-        <v>391</v>
+        <v>323</v>
       </c>
       <c r="I55" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="J55" t="s">
-        <v>221</v>
+        <v>324</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -4591,16 +4681,16 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="B56" t="s">
-        <v>207</v>
+        <v>326</v>
       </c>
       <c r="C56" t="s">
-        <v>208</v>
+        <v>328</v>
       </c>
       <c r="D56" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E56" t="s">
         <v>58</v>
@@ -4612,13 +4702,13 @@
         <v>168</v>
       </c>
       <c r="H56" t="s">
-        <v>209</v>
+        <v>368</v>
       </c>
       <c r="I56" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="J56" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
       <c r="K56" t="s">
         <v>55</v>
@@ -4635,34 +4725,31 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="B57" t="s">
-        <v>213</v>
+        <v>329</v>
       </c>
       <c r="C57" t="s">
-        <v>215</v>
+        <v>330</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E57" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F57" t="s">
         <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H57" t="s">
-        <v>572</v>
-      </c>
-      <c r="I57" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="J57" t="s">
-        <v>214</v>
+        <v>103</v>
       </c>
       <c r="K57" t="s">
         <v>55</v>
@@ -4679,34 +4766,34 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>205</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s">
-        <v>216</v>
+        <v>425</v>
       </c>
       <c r="C58" t="s">
-        <v>217</v>
+        <v>426</v>
       </c>
       <c r="D58" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G58" t="s">
-        <v>168</v>
+        <v>427</v>
       </c>
       <c r="H58" t="s">
-        <v>572</v>
+        <v>506</v>
       </c>
       <c r="I58" t="s">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="J58" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="K58" t="s">
         <v>55</v>
@@ -4723,37 +4810,34 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>206</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s">
-        <v>218</v>
+        <v>428</v>
       </c>
       <c r="C59" t="s">
-        <v>219</v>
+        <v>429</v>
       </c>
       <c r="D59" t="s">
         <v>54</v>
       </c>
       <c r="E59" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G59" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H59" t="s">
-        <v>220</v>
-      </c>
-      <c r="I59" t="s">
-        <v>167</v>
+        <v>561</v>
       </c>
       <c r="J59" t="s">
-        <v>400</v>
+        <v>103</v>
       </c>
       <c r="K59" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L59" t="s">
         <v>14</v>
@@ -4767,34 +4851,34 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>222</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s">
-        <v>227</v>
+        <v>431</v>
       </c>
       <c r="C60" t="s">
-        <v>228</v>
+        <v>430</v>
       </c>
       <c r="D60" t="s">
         <v>54</v>
       </c>
       <c r="E60" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G60" t="s">
-        <v>258</v>
+        <v>432</v>
       </c>
       <c r="H60" t="s">
-        <v>229</v>
+        <v>433</v>
       </c>
       <c r="I60" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="J60" t="s">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="K60" t="s">
         <v>55</v>
@@ -4811,34 +4895,31 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>223</v>
+        <v>413</v>
       </c>
       <c r="B61" t="s">
-        <v>231</v>
+        <v>434</v>
       </c>
       <c r="C61" t="s">
-        <v>232</v>
+        <v>435</v>
       </c>
       <c r="D61" t="s">
         <v>54</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H61" t="s">
-        <v>237</v>
-      </c>
-      <c r="I61" t="s">
-        <v>60</v>
+        <v>308</v>
       </c>
       <c r="J61" t="s">
-        <v>233</v>
+        <v>436</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -4855,13 +4936,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>224</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s">
-        <v>234</v>
+        <v>437</v>
       </c>
       <c r="C62" t="s">
-        <v>235</v>
+        <v>438</v>
       </c>
       <c r="D62" t="s">
         <v>54</v>
@@ -4873,16 +4954,16 @@
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H62" t="s">
-        <v>236</v>
+        <v>308</v>
       </c>
       <c r="I62" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="J62" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="K62" t="s">
         <v>55</v>
@@ -4899,34 +4980,34 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>225</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s">
-        <v>238</v>
+        <v>440</v>
       </c>
       <c r="C63" t="s">
-        <v>239</v>
+        <v>441</v>
       </c>
       <c r="D63" t="s">
         <v>54</v>
       </c>
       <c r="E63" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>170</v>
+        <v>314</v>
       </c>
       <c r="H63" t="s">
-        <v>241</v>
+        <v>389</v>
       </c>
       <c r="I63" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="J63" t="s">
-        <v>211</v>
+        <v>327</v>
       </c>
       <c r="K63" t="s">
         <v>55</v>
@@ -4943,13 +5024,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>226</v>
+        <v>416</v>
       </c>
       <c r="B64" t="s">
-        <v>242</v>
+        <v>442</v>
       </c>
       <c r="C64" t="s">
-        <v>243</v>
+        <v>443</v>
       </c>
       <c r="D64" t="s">
         <v>54</v>
@@ -4961,16 +5042,13 @@
         <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>168</v>
+        <v>444</v>
       </c>
       <c r="H64" t="s">
-        <v>236</v>
-      </c>
-      <c r="I64" t="s">
-        <v>60</v>
+        <v>569</v>
       </c>
       <c r="J64" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="K64" t="s">
         <v>55</v>
@@ -4987,19 +5065,19 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>244</v>
+        <v>417</v>
       </c>
       <c r="B65" t="s">
-        <v>248</v>
+        <v>445</v>
       </c>
       <c r="C65" t="s">
-        <v>166</v>
+        <v>446</v>
       </c>
       <c r="D65" t="s">
         <v>54</v>
       </c>
       <c r="E65" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -5008,13 +5086,10 @@
         <v>168</v>
       </c>
       <c r="H65" t="s">
-        <v>573</v>
-      </c>
-      <c r="I65" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="J65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K65" t="s">
         <v>55</v>
@@ -5031,13 +5106,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>245</v>
+        <v>418</v>
       </c>
       <c r="B66" t="s">
-        <v>249</v>
+        <v>447</v>
       </c>
       <c r="C66" t="s">
-        <v>487</v>
+        <v>448</v>
       </c>
       <c r="D66" t="s">
         <v>54</v>
@@ -5049,19 +5124,19 @@
         <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="H66" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="I66" t="s">
         <v>61</v>
       </c>
       <c r="J66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K66" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L66" t="s">
         <v>14</v>
@@ -5075,34 +5150,31 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>246</v>
+        <v>419</v>
       </c>
       <c r="B67" t="s">
-        <v>250</v>
+        <v>449</v>
       </c>
       <c r="C67" t="s">
-        <v>251</v>
+        <v>450</v>
       </c>
       <c r="D67" t="s">
         <v>54</v>
       </c>
       <c r="E67" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F67" t="s">
         <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H67" t="s">
-        <v>573</v>
-      </c>
-      <c r="I67" t="s">
-        <v>61</v>
+        <v>570</v>
       </c>
       <c r="J67" t="s">
-        <v>211</v>
+        <v>453</v>
       </c>
       <c r="K67" t="s">
         <v>55</v>
@@ -5119,19 +5191,19 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>247</v>
+        <v>420</v>
       </c>
       <c r="B68" t="s">
-        <v>252</v>
+        <v>451</v>
       </c>
       <c r="C68" t="s">
-        <v>253</v>
+        <v>452</v>
       </c>
       <c r="D68" t="s">
         <v>54</v>
       </c>
       <c r="E68" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F68" t="s">
         <v>13</v>
@@ -5140,13 +5212,10 @@
         <v>168</v>
       </c>
       <c r="H68" t="s">
-        <v>573</v>
-      </c>
-      <c r="I68" t="s">
-        <v>157</v>
+        <v>608</v>
       </c>
       <c r="J68" t="s">
-        <v>221</v>
+        <v>453</v>
       </c>
       <c r="K68" t="s">
         <v>55</v>
@@ -5163,34 +5232,34 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>259</v>
+        <v>421</v>
       </c>
       <c r="B69" t="s">
-        <v>268</v>
+        <v>454</v>
       </c>
       <c r="C69" t="s">
-        <v>269</v>
+        <v>455</v>
       </c>
       <c r="D69" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E69" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
       </c>
       <c r="G69" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H69" t="s">
-        <v>310</v>
+        <v>235</v>
       </c>
       <c r="I69" t="s">
-        <v>270</v>
+        <v>61</v>
       </c>
       <c r="J69" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K69" t="s">
         <v>55</v>
@@ -5207,31 +5276,31 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>260</v>
+        <v>422</v>
       </c>
       <c r="B70" t="s">
-        <v>265</v>
+        <v>456</v>
       </c>
       <c r="C70" t="s">
-        <v>266</v>
+        <v>457</v>
       </c>
       <c r="D70" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E70" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F70" t="s">
         <v>13</v>
       </c>
       <c r="G70" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="H70" t="s">
-        <v>391</v>
+        <v>322</v>
       </c>
       <c r="J70" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="K70" t="s">
         <v>55</v>
@@ -5248,34 +5317,34 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>261</v>
+        <v>423</v>
       </c>
       <c r="B71" t="s">
-        <v>271</v>
+        <v>458</v>
       </c>
       <c r="C71" t="s">
-        <v>272</v>
+        <v>459</v>
       </c>
       <c r="D71" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E71" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F71" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G71" t="s">
-        <v>317</v>
+        <v>254</v>
       </c>
       <c r="H71" t="s">
-        <v>391</v>
+        <v>322</v>
       </c>
       <c r="I71" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="J71" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K71" t="s">
         <v>55</v>
@@ -5292,34 +5361,31 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>262</v>
+        <v>424</v>
       </c>
       <c r="B72" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C72" t="s">
-        <v>277</v>
+        <v>460</v>
       </c>
       <c r="D72" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E72" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="H72" t="s">
-        <v>310</v>
-      </c>
-      <c r="I72" t="s">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="J72" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="K72" t="s">
         <v>55</v>
@@ -5336,16 +5402,16 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>263</v>
+        <v>462</v>
       </c>
       <c r="B73" t="s">
-        <v>273</v>
+        <v>467</v>
       </c>
       <c r="C73" t="s">
-        <v>274</v>
+        <v>468</v>
       </c>
       <c r="D73" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -5354,13 +5420,13 @@
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H73" t="s">
-        <v>391</v>
+        <v>609</v>
       </c>
       <c r="J73" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K73" t="s">
         <v>55</v>
@@ -5377,31 +5443,34 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>264</v>
+        <v>463</v>
       </c>
       <c r="B74" t="s">
-        <v>275</v>
+        <v>469</v>
       </c>
       <c r="C74" t="s">
-        <v>276</v>
+        <v>470</v>
       </c>
       <c r="D74" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E74" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G74" t="s">
-        <v>316</v>
+        <v>168</v>
       </c>
       <c r="H74" t="s">
-        <v>391</v>
+        <v>154</v>
+      </c>
+      <c r="I74" t="s">
+        <v>492</v>
       </c>
       <c r="J74" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K74" t="s">
         <v>55</v>
@@ -5418,34 +5487,34 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>278</v>
+        <v>464</v>
       </c>
       <c r="B75" t="s">
-        <v>279</v>
+        <v>471</v>
       </c>
       <c r="C75" t="s">
-        <v>282</v>
+        <v>472</v>
       </c>
       <c r="D75" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E75" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G75" t="s">
         <v>168</v>
       </c>
       <c r="H75" t="s">
-        <v>391</v>
+        <v>154</v>
       </c>
       <c r="I75" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="J75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K75" t="s">
         <v>55</v>
@@ -5462,16 +5531,16 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>280</v>
+        <v>465</v>
       </c>
       <c r="B76" t="s">
-        <v>199</v>
+        <v>473</v>
       </c>
       <c r="C76" t="s">
-        <v>281</v>
+        <v>474</v>
       </c>
       <c r="D76" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E76" t="s">
         <v>58</v>
@@ -5480,13 +5549,16 @@
         <v>13</v>
       </c>
       <c r="G76" t="s">
-        <v>315</v>
+        <v>257</v>
       </c>
       <c r="H76" t="s">
-        <v>391</v>
+        <v>571</v>
+      </c>
+      <c r="I76" t="s">
+        <v>61</v>
       </c>
       <c r="J76" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="K76" t="s">
         <v>55</v>
@@ -5503,34 +5575,37 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>284</v>
+        <v>466</v>
       </c>
       <c r="B77" t="s">
-        <v>286</v>
+        <v>475</v>
       </c>
       <c r="C77" t="s">
-        <v>285</v>
+        <v>476</v>
       </c>
       <c r="D77" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E77" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="F77" t="s">
         <v>13</v>
       </c>
       <c r="G77" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H77" t="s">
-        <v>310</v>
+        <v>477</v>
+      </c>
+      <c r="I77" t="s">
+        <v>61</v>
       </c>
       <c r="J77" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K77" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L77" t="s">
         <v>14</v>
@@ -5544,13 +5619,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>287</v>
+        <v>493</v>
       </c>
       <c r="B78" t="s">
-        <v>288</v>
+        <v>497</v>
       </c>
       <c r="C78" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="D78" t="s">
         <v>54</v>
@@ -5565,13 +5640,13 @@
         <v>168</v>
       </c>
       <c r="H78" t="s">
-        <v>391</v>
+        <v>477</v>
       </c>
       <c r="I78" t="s">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="J78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K78" t="s">
         <v>55</v>
@@ -5588,13 +5663,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>289</v>
+        <v>494</v>
       </c>
       <c r="B79" t="s">
-        <v>290</v>
+        <v>499</v>
       </c>
       <c r="C79" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="D79" t="s">
         <v>54</v>
@@ -5603,19 +5678,19 @@
         <v>33</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G79" t="s">
-        <v>168</v>
+        <v>507</v>
       </c>
       <c r="H79" t="s">
-        <v>391</v>
+        <v>500</v>
       </c>
       <c r="I79" t="s">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="J79" t="s">
-        <v>211</v>
+        <v>453</v>
       </c>
       <c r="K79" t="s">
         <v>55</v>
@@ -5632,19 +5707,19 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>291</v>
+        <v>495</v>
       </c>
       <c r="B80" t="s">
-        <v>301</v>
+        <v>502</v>
       </c>
       <c r="C80" t="s">
-        <v>302</v>
+        <v>503</v>
       </c>
       <c r="D80" t="s">
         <v>54</v>
       </c>
       <c r="E80" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F80" t="s">
         <v>13</v>
@@ -5653,13 +5728,13 @@
         <v>168</v>
       </c>
       <c r="H80" t="s">
-        <v>241</v>
+        <v>610</v>
       </c>
       <c r="I80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J80" t="s">
-        <v>311</v>
+        <v>210</v>
       </c>
       <c r="K80" t="s">
         <v>55</v>
@@ -5676,19 +5751,19 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>292</v>
+        <v>496</v>
       </c>
       <c r="B81" t="s">
-        <v>303</v>
+        <v>504</v>
       </c>
       <c r="C81" t="s">
-        <v>304</v>
+        <v>505</v>
       </c>
       <c r="D81" t="s">
         <v>54</v>
       </c>
       <c r="E81" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F81" t="s">
         <v>13</v>
@@ -5697,13 +5772,13 @@
         <v>168</v>
       </c>
       <c r="H81" t="s">
-        <v>305</v>
+        <v>506</v>
       </c>
       <c r="I81" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="J81" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="K81" t="s">
         <v>55</v>
@@ -5720,13 +5795,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>293</v>
+        <v>508</v>
       </c>
       <c r="B82" t="s">
-        <v>306</v>
+        <v>517</v>
       </c>
       <c r="C82" t="s">
-        <v>308</v>
+        <v>520</v>
       </c>
       <c r="D82" t="s">
         <v>54</v>
@@ -5738,16 +5813,16 @@
         <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>258</v>
+        <v>168</v>
       </c>
       <c r="H82" t="s">
-        <v>310</v>
+        <v>518</v>
       </c>
       <c r="I82" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="J82" t="s">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="K82" t="s">
         <v>55</v>
@@ -5764,13 +5839,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>294</v>
+        <v>509</v>
       </c>
       <c r="B83" t="s">
-        <v>307</v>
+        <v>519</v>
       </c>
       <c r="C83" t="s">
-        <v>309</v>
+        <v>520</v>
       </c>
       <c r="D83" t="s">
         <v>54</v>
@@ -5782,16 +5857,16 @@
         <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H83" t="s">
-        <v>310</v>
+        <v>236</v>
       </c>
       <c r="I83" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="J83" t="s">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="K83" t="s">
         <v>55</v>
@@ -5808,34 +5883,34 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>295</v>
+        <v>510</v>
       </c>
       <c r="B84" t="s">
-        <v>488</v>
+        <v>521</v>
       </c>
       <c r="C84" t="s">
-        <v>312</v>
+        <v>522</v>
       </c>
       <c r="D84" t="s">
         <v>54</v>
       </c>
       <c r="E84" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F84" t="s">
         <v>13</v>
       </c>
       <c r="G84" t="s">
-        <v>313</v>
+        <v>168</v>
       </c>
       <c r="H84" t="s">
-        <v>121</v>
+        <v>573</v>
       </c>
       <c r="I84" t="s">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="J84" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K84" t="s">
         <v>55</v>
@@ -5852,34 +5927,34 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>296</v>
+        <v>511</v>
       </c>
       <c r="B85" t="s">
-        <v>319</v>
+        <v>525</v>
       </c>
       <c r="C85" t="s">
-        <v>320</v>
+        <v>523</v>
       </c>
       <c r="D85" t="s">
         <v>54</v>
       </c>
       <c r="E85" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G85" t="s">
-        <v>168</v>
+        <v>524</v>
       </c>
       <c r="H85" t="s">
-        <v>321</v>
+        <v>506</v>
       </c>
       <c r="I85" t="s">
         <v>61</v>
       </c>
       <c r="J85" t="s">
-        <v>103</v>
+        <v>229</v>
       </c>
       <c r="K85" t="s">
         <v>55</v>
@@ -5896,34 +5971,37 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>297</v>
+        <v>512</v>
       </c>
       <c r="B86" t="s">
-        <v>322</v>
+        <v>526</v>
       </c>
       <c r="C86" t="s">
-        <v>323</v>
+        <v>527</v>
       </c>
       <c r="D86" t="s">
         <v>54</v>
       </c>
       <c r="E86" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G86" t="s">
-        <v>258</v>
+        <v>524</v>
       </c>
       <c r="H86" t="s">
-        <v>324</v>
+        <v>611</v>
+      </c>
+      <c r="I86" t="s">
+        <v>61</v>
       </c>
       <c r="J86" t="s">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="K86" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L86" t="s">
         <v>14</v>
@@ -5937,37 +6015,37 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>298</v>
+        <v>513</v>
       </c>
       <c r="B87" t="s">
-        <v>327</v>
+        <v>528</v>
       </c>
       <c r="C87" t="s">
-        <v>312</v>
+        <v>529</v>
       </c>
       <c r="D87" t="s">
         <v>54</v>
       </c>
       <c r="E87" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="F87" t="s">
         <v>13</v>
       </c>
       <c r="G87" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H87" t="s">
-        <v>325</v>
+        <v>612</v>
       </c>
       <c r="I87" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="J87" t="s">
-        <v>326</v>
+        <v>210</v>
       </c>
       <c r="K87" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L87" t="s">
         <v>14</v>
@@ -5981,34 +6059,34 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>299</v>
+        <v>514</v>
       </c>
       <c r="B88" t="s">
-        <v>328</v>
+        <v>531</v>
       </c>
       <c r="C88" t="s">
-        <v>330</v>
+        <v>532</v>
       </c>
       <c r="D88" t="s">
         <v>54</v>
       </c>
       <c r="E88" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G88" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H88" t="s">
-        <v>370</v>
+        <v>236</v>
       </c>
       <c r="I88" t="s">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="J88" t="s">
-        <v>329</v>
+        <v>210</v>
       </c>
       <c r="K88" t="s">
         <v>55</v>
@@ -6025,13 +6103,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>300</v>
+        <v>515</v>
       </c>
       <c r="B89" t="s">
-        <v>331</v>
+        <v>533</v>
       </c>
       <c r="C89" t="s">
-        <v>332</v>
+        <v>534</v>
       </c>
       <c r="D89" t="s">
         <v>54</v>
@@ -6040,16 +6118,19 @@
         <v>33</v>
       </c>
       <c r="F89" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G89" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H89" t="s">
-        <v>121</v>
+        <v>613</v>
+      </c>
+      <c r="I89" t="s">
+        <v>61</v>
       </c>
       <c r="J89" t="s">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="K89" t="s">
         <v>55</v>
@@ -6066,34 +6147,37 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>340</v>
+        <v>516</v>
       </c>
       <c r="B90" t="s">
-        <v>355</v>
+        <v>535</v>
       </c>
       <c r="C90" t="s">
-        <v>489</v>
+        <v>520</v>
       </c>
       <c r="D90" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E90" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H90" t="s">
         <v>236</v>
       </c>
+      <c r="I90" t="s">
+        <v>61</v>
+      </c>
       <c r="J90" t="s">
-        <v>105</v>
+        <v>210</v>
       </c>
       <c r="K90" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L90" t="s">
         <v>14</v>
@@ -6107,31 +6191,34 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>341</v>
+        <v>577</v>
       </c>
       <c r="B91" t="s">
-        <v>356</v>
+        <v>582</v>
       </c>
       <c r="C91" t="s">
-        <v>357</v>
+        <v>583</v>
       </c>
       <c r="D91" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E91" t="s">
         <v>33</v>
       </c>
       <c r="F91" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G91" t="s">
         <v>255</v>
       </c>
       <c r="H91" t="s">
-        <v>324</v>
+        <v>614</v>
+      </c>
+      <c r="I91" t="s">
+        <v>82</v>
       </c>
       <c r="J91" t="s">
-        <v>105</v>
+        <v>584</v>
       </c>
       <c r="K91" t="s">
         <v>55</v>
@@ -6148,31 +6235,31 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>342</v>
+        <v>578</v>
       </c>
       <c r="B92" t="s">
-        <v>359</v>
+        <v>585</v>
       </c>
       <c r="C92" t="s">
-        <v>490</v>
+        <v>586</v>
       </c>
       <c r="D92" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E92" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F92" t="s">
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="H92" t="s">
-        <v>236</v>
+        <v>389</v>
       </c>
       <c r="J92" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="K92" t="s">
         <v>55</v>
@@ -6189,34 +6276,34 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>343</v>
+        <v>579</v>
       </c>
       <c r="B93" t="s">
-        <v>360</v>
+        <v>587</v>
       </c>
       <c r="C93" t="s">
-        <v>361</v>
+        <v>588</v>
       </c>
       <c r="D93" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E93" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F93" t="s">
         <v>13</v>
       </c>
       <c r="G93" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="H93" t="s">
-        <v>237</v>
+        <v>322</v>
       </c>
       <c r="I93" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="J93" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K93" t="s">
         <v>55</v>
@@ -6233,16 +6320,16 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>344</v>
+        <v>580</v>
       </c>
       <c r="B94" t="s">
-        <v>362</v>
+        <v>589</v>
       </c>
       <c r="C94" t="s">
-        <v>363</v>
+        <v>590</v>
       </c>
       <c r="D94" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -6254,13 +6341,16 @@
         <v>168</v>
       </c>
       <c r="H94" t="s">
-        <v>324</v>
+        <v>389</v>
+      </c>
+      <c r="I94" t="s">
+        <v>61</v>
       </c>
       <c r="J94" t="s">
-        <v>103</v>
+        <v>327</v>
       </c>
       <c r="K94" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L94" t="s">
         <v>14</v>
@@ -6274,34 +6364,34 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>345</v>
+        <v>581</v>
       </c>
       <c r="B95" t="s">
-        <v>364</v>
+        <v>591</v>
       </c>
       <c r="C95" t="s">
-        <v>366</v>
+        <v>592</v>
       </c>
       <c r="D95" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E95" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F95" t="s">
         <v>13</v>
       </c>
       <c r="G95" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="H95" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="I95" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="J95" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K95" t="s">
         <v>55</v>
@@ -6318,34 +6408,34 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>346</v>
+        <v>631</v>
       </c>
       <c r="B96" t="s">
-        <v>367</v>
+        <v>633</v>
       </c>
       <c r="C96" t="s">
-        <v>368</v>
+        <v>634</v>
       </c>
       <c r="D96" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E96" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F96" t="s">
         <v>13</v>
       </c>
       <c r="G96" t="s">
-        <v>369</v>
+        <v>168</v>
       </c>
       <c r="H96" t="s">
-        <v>574</v>
+        <v>308</v>
       </c>
       <c r="I96" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="J96" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K96" t="s">
         <v>55</v>
@@ -6362,31 +6452,34 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>347</v>
+        <v>632</v>
       </c>
       <c r="B97" t="s">
-        <v>371</v>
+        <v>635</v>
       </c>
       <c r="C97" t="s">
-        <v>372</v>
+        <v>636</v>
       </c>
       <c r="D97" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="E97" t="s">
         <v>33</v>
       </c>
       <c r="F97" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G97" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H97" t="s">
-        <v>575</v>
+        <v>308</v>
+      </c>
+      <c r="I97" t="s">
+        <v>82</v>
       </c>
       <c r="J97" t="s">
-        <v>103</v>
+        <v>453</v>
       </c>
       <c r="K97" t="s">
         <v>55</v>
@@ -6403,13 +6496,13 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>348</v>
+        <v>63</v>
       </c>
       <c r="B98" t="s">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c r="C98" t="s">
-        <v>374</v>
+        <v>70</v>
       </c>
       <c r="D98" t="s">
         <v>85</v>
@@ -6421,13 +6514,16 @@
         <v>13</v>
       </c>
       <c r="G98" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H98" t="s">
-        <v>121</v>
+        <v>615</v>
+      </c>
+      <c r="I98" t="s">
+        <v>104</v>
       </c>
       <c r="J98" t="s">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="K98" t="s">
         <v>55</v>
@@ -6444,13 +6540,13 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>349</v>
+        <v>64</v>
       </c>
       <c r="B99" t="s">
-        <v>375</v>
+        <v>71</v>
       </c>
       <c r="C99" t="s">
-        <v>376</v>
+        <v>72</v>
       </c>
       <c r="D99" t="s">
         <v>85</v>
@@ -6462,16 +6558,16 @@
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H99" t="s">
-        <v>365</v>
+        <v>616</v>
       </c>
       <c r="I99" t="s">
         <v>82</v>
       </c>
       <c r="J99" t="s">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="K99" t="s">
         <v>55</v>
@@ -6488,13 +6584,13 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>350</v>
+        <v>65</v>
       </c>
       <c r="B100" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="C100" t="s">
-        <v>378</v>
+        <v>73</v>
       </c>
       <c r="D100" t="s">
         <v>85</v>
@@ -6503,19 +6599,19 @@
         <v>58</v>
       </c>
       <c r="F100" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G100" t="s">
-        <v>379</v>
+        <v>168</v>
       </c>
       <c r="H100" t="s">
-        <v>380</v>
+        <v>617</v>
       </c>
       <c r="I100" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="J100" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="K100" t="s">
         <v>55</v>
@@ -6532,37 +6628,34 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>351</v>
+        <v>66</v>
       </c>
       <c r="B101" t="s">
-        <v>381</v>
+        <v>74</v>
       </c>
       <c r="C101" t="s">
-        <v>382</v>
+        <v>336</v>
       </c>
       <c r="D101" t="s">
         <v>85</v>
       </c>
       <c r="E101" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F101" t="s">
         <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>383</v>
+        <v>168</v>
       </c>
       <c r="H101" t="s">
-        <v>241</v>
-      </c>
-      <c r="I101" t="s">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="J101" t="s">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="K101" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L101" t="s">
         <v>14</v>
@@ -6576,13 +6669,13 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>352</v>
+        <v>67</v>
       </c>
       <c r="B102" t="s">
-        <v>384</v>
+        <v>75</v>
       </c>
       <c r="C102" t="s">
-        <v>385</v>
+        <v>76</v>
       </c>
       <c r="D102" t="s">
         <v>85</v>
@@ -6594,16 +6687,16 @@
         <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="H102" t="s">
-        <v>241</v>
+        <v>557</v>
       </c>
       <c r="I102" t="s">
         <v>82</v>
       </c>
       <c r="J102" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="K102" t="s">
         <v>55</v>
@@ -6620,13 +6713,13 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>353</v>
+        <v>68</v>
       </c>
       <c r="B103" t="s">
-        <v>386</v>
+        <v>77</v>
       </c>
       <c r="C103" t="s">
-        <v>387</v>
+        <v>337</v>
       </c>
       <c r="D103" t="s">
         <v>85</v>
@@ -6638,16 +6731,13 @@
         <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="H103" t="s">
-        <v>241</v>
-      </c>
-      <c r="I103" t="s">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="J103" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="K103" t="s">
         <v>55</v>
@@ -6664,34 +6754,34 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>354</v>
+        <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="C104" t="s">
-        <v>389</v>
+        <v>79</v>
       </c>
       <c r="D104" t="s">
         <v>85</v>
       </c>
       <c r="E104" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F104" t="s">
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>168</v>
+        <v>256</v>
       </c>
       <c r="H104" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="I104" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="J104" t="s">
-        <v>390</v>
+        <v>220</v>
       </c>
       <c r="K104" t="s">
         <v>55</v>
@@ -6708,34 +6798,34 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>392</v>
+        <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>398</v>
+        <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>399</v>
+        <v>110</v>
       </c>
       <c r="D105" t="s">
         <v>85</v>
       </c>
       <c r="E105" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F105" t="s">
         <v>32</v>
       </c>
       <c r="G105" t="s">
-        <v>256</v>
+        <v>172</v>
       </c>
       <c r="H105" t="s">
-        <v>391</v>
+        <v>28</v>
       </c>
       <c r="I105" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="J105" t="s">
-        <v>400</v>
+        <v>173</v>
       </c>
       <c r="K105" t="s">
         <v>55</v>
@@ -6752,13 +6842,13 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>393</v>
+        <v>147</v>
       </c>
       <c r="B106" t="s">
-        <v>401</v>
+        <v>150</v>
       </c>
       <c r="C106" t="s">
-        <v>402</v>
+        <v>151</v>
       </c>
       <c r="D106" t="s">
         <v>85</v>
@@ -6767,16 +6857,19 @@
         <v>58</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G106" t="s">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="H106" t="s">
-        <v>310</v>
+        <v>154</v>
+      </c>
+      <c r="I106" t="s">
+        <v>82</v>
       </c>
       <c r="J106" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="K106" t="s">
         <v>55</v>
@@ -6793,13 +6886,13 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>394</v>
+        <v>148</v>
       </c>
       <c r="B107" t="s">
-        <v>403</v>
+        <v>153</v>
       </c>
       <c r="C107" t="s">
-        <v>404</v>
+        <v>152</v>
       </c>
       <c r="D107" t="s">
         <v>85</v>
@@ -6811,19 +6904,19 @@
         <v>32</v>
       </c>
       <c r="G107" t="s">
-        <v>405</v>
+        <v>170</v>
       </c>
       <c r="H107" t="s">
-        <v>391</v>
+        <v>154</v>
       </c>
       <c r="I107" t="s">
         <v>82</v>
       </c>
       <c r="J107" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="K107" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L107" t="s">
         <v>14</v>
@@ -6837,31 +6930,34 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>395</v>
+        <v>149</v>
       </c>
       <c r="B108" t="s">
-        <v>406</v>
+        <v>155</v>
       </c>
       <c r="C108" t="s">
-        <v>407</v>
+        <v>156</v>
       </c>
       <c r="D108" t="s">
         <v>85</v>
       </c>
       <c r="E108" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F108" t="s">
         <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>408</v>
+        <v>168</v>
       </c>
       <c r="H108" t="s">
-        <v>409</v>
+        <v>121</v>
+      </c>
+      <c r="I108" t="s">
+        <v>157</v>
       </c>
       <c r="J108" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K108" t="s">
         <v>55</v>
@@ -6878,34 +6974,34 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>396</v>
+        <v>541</v>
       </c>
       <c r="B109" t="s">
-        <v>410</v>
+        <v>550</v>
       </c>
       <c r="C109" t="s">
-        <v>411</v>
+        <v>551</v>
       </c>
       <c r="D109" t="s">
         <v>85</v>
       </c>
       <c r="E109" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F109" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G109" t="s">
-        <v>168</v>
+        <v>552</v>
       </c>
       <c r="H109" t="s">
-        <v>509</v>
+        <v>389</v>
       </c>
       <c r="J109" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="K109" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L109" t="s">
         <v>14</v>
@@ -6919,13 +7015,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>397</v>
+        <v>596</v>
       </c>
       <c r="B110" t="s">
-        <v>442</v>
+        <v>604</v>
       </c>
       <c r="C110" t="s">
-        <v>412</v>
+        <v>605</v>
       </c>
       <c r="D110" t="s">
         <v>85</v>
@@ -6940,13 +7036,10 @@
         <v>168</v>
       </c>
       <c r="H110" t="s">
-        <v>237</v>
-      </c>
-      <c r="I110" t="s">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="J110" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K110" t="s">
         <v>55</v>
@@ -6963,34 +7056,31 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>413</v>
+        <v>177</v>
       </c>
       <c r="B111" t="s">
-        <v>428</v>
+        <v>186</v>
       </c>
       <c r="C111" t="s">
-        <v>429</v>
+        <v>187</v>
       </c>
       <c r="D111" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E111" t="s">
         <v>58</v>
       </c>
       <c r="F111" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G111" t="s">
-        <v>430</v>
+        <v>312</v>
       </c>
       <c r="H111" t="s">
-        <v>509</v>
-      </c>
-      <c r="I111" t="s">
-        <v>240</v>
+        <v>389</v>
       </c>
       <c r="J111" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K111" t="s">
         <v>55</v>
@@ -7007,34 +7097,37 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>414</v>
+        <v>178</v>
       </c>
       <c r="B112" t="s">
-        <v>431</v>
+        <v>188</v>
       </c>
       <c r="C112" t="s">
-        <v>432</v>
+        <v>189</v>
       </c>
       <c r="D112" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E112" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F112" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G112" t="s">
-        <v>172</v>
+        <v>312</v>
       </c>
       <c r="H112" t="s">
-        <v>568</v>
+        <v>389</v>
+      </c>
+      <c r="I112" t="s">
+        <v>82</v>
       </c>
       <c r="J112" t="s">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="K112" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L112" t="s">
         <v>14</v>
@@ -7048,34 +7141,31 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>415</v>
+        <v>179</v>
       </c>
       <c r="B113" t="s">
-        <v>434</v>
+        <v>190</v>
       </c>
       <c r="C113" t="s">
-        <v>433</v>
+        <v>191</v>
       </c>
       <c r="D113" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E113" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F113" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G113" t="s">
-        <v>435</v>
+        <v>312</v>
       </c>
       <c r="H113" t="s">
-        <v>436</v>
-      </c>
-      <c r="I113" t="s">
-        <v>60</v>
+        <v>389</v>
       </c>
       <c r="J113" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="K113" t="s">
         <v>55</v>
@@ -7092,31 +7182,34 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>416</v>
+        <v>180</v>
       </c>
       <c r="B114" t="s">
-        <v>437</v>
+        <v>192</v>
       </c>
       <c r="C114" t="s">
-        <v>438</v>
+        <v>193</v>
       </c>
       <c r="D114" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E114" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="F114" t="s">
         <v>13</v>
       </c>
       <c r="G114" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H114" t="s">
-        <v>310</v>
+        <v>389</v>
+      </c>
+      <c r="I114" t="s">
+        <v>82</v>
       </c>
       <c r="J114" t="s">
-        <v>439</v>
+        <v>220</v>
       </c>
       <c r="K114" t="s">
         <v>55</v>
@@ -7133,34 +7226,34 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>417</v>
+        <v>181</v>
       </c>
       <c r="B115" t="s">
-        <v>440</v>
+        <v>194</v>
       </c>
       <c r="C115" t="s">
-        <v>441</v>
+        <v>281</v>
       </c>
       <c r="D115" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E115" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F115" t="s">
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H115" t="s">
-        <v>310</v>
+        <v>389</v>
       </c>
       <c r="I115" t="s">
         <v>82</v>
       </c>
       <c r="J115" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K115" t="s">
         <v>55</v>
@@ -7177,34 +7270,31 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>418</v>
+        <v>594</v>
       </c>
       <c r="B116" t="s">
-        <v>443</v>
+        <v>599</v>
       </c>
       <c r="C116" t="s">
-        <v>444</v>
+        <v>600</v>
       </c>
       <c r="D116" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E116" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F116" t="s">
         <v>13</v>
       </c>
       <c r="G116" t="s">
-        <v>316</v>
+        <v>168</v>
       </c>
       <c r="H116" t="s">
-        <v>391</v>
-      </c>
-      <c r="I116" t="s">
-        <v>167</v>
+        <v>389</v>
       </c>
       <c r="J116" t="s">
-        <v>329</v>
+        <v>220</v>
       </c>
       <c r="K116" t="s">
         <v>55</v>
@@ -7221,31 +7311,34 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="B117" t="s">
-        <v>445</v>
+        <v>401</v>
       </c>
       <c r="C117" t="s">
-        <v>446</v>
+        <v>402</v>
       </c>
       <c r="D117" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E117" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F117" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G117" t="s">
-        <v>447</v>
+        <v>403</v>
       </c>
       <c r="H117" t="s">
-        <v>576</v>
+        <v>389</v>
+      </c>
+      <c r="I117" t="s">
+        <v>82</v>
       </c>
       <c r="J117" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="K117" t="s">
         <v>55</v>
@@ -7262,31 +7355,31 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="B118" t="s">
-        <v>448</v>
+        <v>404</v>
       </c>
       <c r="C118" t="s">
-        <v>449</v>
+        <v>630</v>
       </c>
       <c r="D118" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E118" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F118" t="s">
         <v>13</v>
       </c>
       <c r="G118" t="s">
-        <v>168</v>
+        <v>405</v>
       </c>
       <c r="H118" t="s">
-        <v>121</v>
+        <v>406</v>
       </c>
       <c r="J118" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K118" t="s">
         <v>55</v>
@@ -7303,16 +7396,16 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>421</v>
+        <v>182</v>
       </c>
       <c r="B119" t="s">
-        <v>450</v>
+        <v>607</v>
       </c>
       <c r="C119" t="s">
-        <v>451</v>
+        <v>195</v>
       </c>
       <c r="D119" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E119" t="s">
         <v>33</v>
@@ -7321,16 +7414,13 @@
         <v>13</v>
       </c>
       <c r="G119" t="s">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="H119" t="s">
-        <v>573</v>
-      </c>
-      <c r="I119" t="s">
-        <v>61</v>
+        <v>564</v>
       </c>
       <c r="J119" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K119" t="s">
         <v>55</v>
@@ -7347,31 +7437,31 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>422</v>
+        <v>183</v>
       </c>
       <c r="B120" t="s">
-        <v>452</v>
+        <v>196</v>
       </c>
       <c r="C120" t="s">
-        <v>453</v>
+        <v>197</v>
       </c>
       <c r="D120" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E120" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F120" t="s">
         <v>13</v>
       </c>
       <c r="G120" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H120" t="s">
-        <v>577</v>
+        <v>389</v>
       </c>
       <c r="J120" t="s">
-        <v>456</v>
+        <v>220</v>
       </c>
       <c r="K120" t="s">
         <v>55</v>
@@ -7388,16 +7478,16 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>423</v>
+        <v>593</v>
       </c>
       <c r="B121" t="s">
-        <v>454</v>
+        <v>597</v>
       </c>
       <c r="C121" t="s">
-        <v>455</v>
+        <v>598</v>
       </c>
       <c r="D121" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E121" t="s">
         <v>58</v>
@@ -7409,10 +7499,13 @@
         <v>168</v>
       </c>
       <c r="H121" t="s">
-        <v>578</v>
+        <v>389</v>
+      </c>
+      <c r="I121" t="s">
+        <v>82</v>
       </c>
       <c r="J121" t="s">
-        <v>456</v>
+        <v>220</v>
       </c>
       <c r="K121" t="s">
         <v>55</v>
@@ -7429,34 +7522,31 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>424</v>
+        <v>259</v>
       </c>
       <c r="B122" t="s">
-        <v>457</v>
+        <v>264</v>
       </c>
       <c r="C122" t="s">
-        <v>458</v>
+        <v>265</v>
       </c>
       <c r="D122" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E122" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="F122" t="s">
         <v>13</v>
       </c>
       <c r="G122" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H122" t="s">
-        <v>236</v>
-      </c>
-      <c r="I122" t="s">
-        <v>61</v>
+        <v>389</v>
       </c>
       <c r="J122" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K122" t="s">
         <v>55</v>
@@ -7473,16 +7563,16 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>425</v>
+        <v>261</v>
       </c>
       <c r="B123" t="s">
-        <v>459</v>
+        <v>266</v>
       </c>
       <c r="C123" t="s">
-        <v>460</v>
+        <v>275</v>
       </c>
       <c r="D123" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E123" t="s">
         <v>58</v>
@@ -7491,13 +7581,16 @@
         <v>13</v>
       </c>
       <c r="G123" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="H123" t="s">
-        <v>324</v>
+        <v>308</v>
+      </c>
+      <c r="I123" t="s">
+        <v>82</v>
       </c>
       <c r="J123" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="K123" t="s">
         <v>55</v>
@@ -7514,34 +7607,34 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>426</v>
+        <v>258</v>
       </c>
       <c r="B124" t="s">
-        <v>461</v>
+        <v>267</v>
       </c>
       <c r="C124" t="s">
-        <v>462</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E124" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="F124" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G124" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="H124" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="I124" t="s">
-        <v>61</v>
+        <v>269</v>
       </c>
       <c r="J124" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K124" t="s">
         <v>55</v>
@@ -7558,16 +7651,16 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>427</v>
+        <v>263</v>
       </c>
       <c r="B125" t="s">
-        <v>464</v>
+        <v>273</v>
       </c>
       <c r="C125" t="s">
-        <v>463</v>
+        <v>274</v>
       </c>
       <c r="D125" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E125" t="s">
         <v>33</v>
@@ -7576,13 +7669,13 @@
         <v>13</v>
       </c>
       <c r="G125" t="s">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="H125" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="J125" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K125" t="s">
         <v>55</v>
@@ -7599,31 +7692,34 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>465</v>
+        <v>260</v>
       </c>
       <c r="B126" t="s">
-        <v>470</v>
+        <v>270</v>
       </c>
       <c r="C126" t="s">
-        <v>471</v>
+        <v>606</v>
       </c>
       <c r="D126" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E126" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F126" t="s">
         <v>13</v>
       </c>
       <c r="G126" t="s">
-        <v>168</v>
+        <v>315</v>
       </c>
       <c r="H126" t="s">
-        <v>237</v>
+        <v>389</v>
+      </c>
+      <c r="I126" t="s">
+        <v>82</v>
       </c>
       <c r="J126" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K126" t="s">
         <v>55</v>
@@ -7640,34 +7736,34 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>466</v>
+        <v>185</v>
       </c>
       <c r="B127" t="s">
-        <v>472</v>
+        <v>200</v>
       </c>
       <c r="C127" t="s">
-        <v>473</v>
+        <v>201</v>
       </c>
       <c r="D127" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E127" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="F127" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G127" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H127" t="s">
-        <v>154</v>
+        <v>389</v>
       </c>
       <c r="I127" t="s">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="J127" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K127" t="s">
         <v>55</v>
@@ -7684,34 +7780,34 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>467</v>
+        <v>619</v>
       </c>
       <c r="B128" t="s">
-        <v>474</v>
+        <v>622</v>
       </c>
       <c r="C128" t="s">
-        <v>475</v>
+        <v>623</v>
       </c>
       <c r="D128" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E128" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F128" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G128" t="s">
         <v>168</v>
       </c>
       <c r="H128" t="s">
-        <v>154</v>
+        <v>564</v>
       </c>
       <c r="I128" t="s">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="J128" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K128" t="s">
         <v>55</v>
@@ -7728,16 +7824,16 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>468</v>
+        <v>391</v>
       </c>
       <c r="B129" t="s">
-        <v>476</v>
+        <v>399</v>
       </c>
       <c r="C129" t="s">
-        <v>477</v>
+        <v>400</v>
       </c>
       <c r="D129" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E129" t="s">
         <v>58</v>
@@ -7746,16 +7842,13 @@
         <v>13</v>
       </c>
       <c r="G129" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="H129" t="s">
-        <v>579</v>
-      </c>
-      <c r="I129" t="s">
-        <v>61</v>
+        <v>308</v>
       </c>
       <c r="J129" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K129" t="s">
         <v>55</v>
@@ -7772,37 +7865,37 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>469</v>
+        <v>184</v>
       </c>
       <c r="B130" t="s">
-        <v>478</v>
+        <v>629</v>
       </c>
       <c r="C130" t="s">
-        <v>479</v>
+        <v>199</v>
       </c>
       <c r="D130" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E130" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="F130" t="s">
         <v>13</v>
       </c>
       <c r="G130" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H130" t="s">
-        <v>480</v>
+        <v>389</v>
       </c>
       <c r="I130" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="J130" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K130" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L130" t="s">
         <v>14</v>
@@ -7816,34 +7909,31 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>481</v>
+        <v>262</v>
       </c>
       <c r="B131" t="s">
-        <v>492</v>
+        <v>271</v>
       </c>
       <c r="C131" t="s">
-        <v>491</v>
+        <v>272</v>
       </c>
       <c r="D131" t="s">
         <v>85</v>
       </c>
       <c r="E131" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F131" t="s">
         <v>13</v>
       </c>
       <c r="G131" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H131" t="s">
-        <v>305</v>
-      </c>
-      <c r="I131" t="s">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="J131" t="s">
-        <v>103</v>
+        <v>211</v>
       </c>
       <c r="K131" t="s">
         <v>55</v>
@@ -7860,31 +7950,31 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>482</v>
+        <v>278</v>
       </c>
       <c r="B132" t="s">
-        <v>483</v>
+        <v>198</v>
       </c>
       <c r="C132" t="s">
-        <v>484</v>
+        <v>279</v>
       </c>
       <c r="D132" t="s">
         <v>85</v>
       </c>
       <c r="E132" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
       </c>
       <c r="G132" t="s">
-        <v>168</v>
+        <v>313</v>
       </c>
       <c r="H132" t="s">
-        <v>580</v>
+        <v>389</v>
       </c>
       <c r="J132" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="K132" t="s">
         <v>55</v>
@@ -7901,19 +7991,19 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>496</v>
+        <v>202</v>
       </c>
       <c r="B133" t="s">
-        <v>500</v>
+        <v>206</v>
       </c>
       <c r="C133" t="s">
-        <v>501</v>
+        <v>207</v>
       </c>
       <c r="D133" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E133" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F133" t="s">
         <v>13</v>
@@ -7922,13 +8012,13 @@
         <v>168</v>
       </c>
       <c r="H133" t="s">
-        <v>480</v>
+        <v>208</v>
       </c>
       <c r="I133" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="J133" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K133" t="s">
         <v>55</v>
@@ -7945,34 +8035,34 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>497</v>
+        <v>203</v>
       </c>
       <c r="B134" t="s">
-        <v>502</v>
+        <v>212</v>
       </c>
       <c r="C134" t="s">
-        <v>504</v>
+        <v>214</v>
       </c>
       <c r="D134" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E134" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F134" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G134" t="s">
-        <v>510</v>
+        <v>312</v>
       </c>
       <c r="H134" t="s">
-        <v>503</v>
+        <v>565</v>
       </c>
       <c r="I134" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="J134" t="s">
-        <v>456</v>
+        <v>213</v>
       </c>
       <c r="K134" t="s">
         <v>55</v>
@@ -7989,19 +8079,19 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>498</v>
+        <v>204</v>
       </c>
       <c r="B135" t="s">
-        <v>505</v>
+        <v>215</v>
       </c>
       <c r="C135" t="s">
-        <v>506</v>
+        <v>216</v>
       </c>
       <c r="D135" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E135" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F135" t="s">
         <v>13</v>
@@ -8010,13 +8100,13 @@
         <v>168</v>
       </c>
       <c r="H135" t="s">
-        <v>220</v>
+        <v>565</v>
       </c>
       <c r="I135" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="J135" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K135" t="s">
         <v>55</v>
@@ -8033,16 +8123,16 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>499</v>
+        <v>276</v>
       </c>
       <c r="B136" t="s">
-        <v>507</v>
+        <v>277</v>
       </c>
       <c r="C136" t="s">
-        <v>508</v>
+        <v>280</v>
       </c>
       <c r="D136" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E136" t="s">
         <v>33</v>
@@ -8054,13 +8144,13 @@
         <v>168</v>
       </c>
       <c r="H136" t="s">
-        <v>509</v>
+        <v>389</v>
       </c>
       <c r="I136" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="J136" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="K136" t="s">
         <v>55</v>
@@ -8077,16 +8167,16 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>511</v>
+        <v>282</v>
       </c>
       <c r="B137" t="s">
-        <v>520</v>
+        <v>284</v>
       </c>
       <c r="C137" t="s">
-        <v>523</v>
+        <v>283</v>
       </c>
       <c r="D137" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E137" t="s">
         <v>33</v>
@@ -8095,16 +8185,13 @@
         <v>13</v>
       </c>
       <c r="G137" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H137" t="s">
-        <v>521</v>
-      </c>
-      <c r="I137" t="s">
-        <v>61</v>
+        <v>308</v>
       </c>
       <c r="J137" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K137" t="s">
         <v>55</v>
@@ -8121,34 +8208,31 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>512</v>
+        <v>338</v>
       </c>
       <c r="B138" t="s">
-        <v>522</v>
+        <v>353</v>
       </c>
       <c r="C138" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="D138" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E138" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F138" t="s">
         <v>13</v>
       </c>
       <c r="G138" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="H138" t="s">
-        <v>237</v>
-      </c>
-      <c r="I138" t="s">
-        <v>61</v>
+        <v>235</v>
       </c>
       <c r="J138" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="K138" t="s">
         <v>55</v>
@@ -8165,34 +8249,31 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>513</v>
+        <v>339</v>
       </c>
       <c r="B139" t="s">
-        <v>524</v>
+        <v>354</v>
       </c>
       <c r="C139" t="s">
-        <v>525</v>
+        <v>355</v>
       </c>
       <c r="D139" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
       </c>
       <c r="F139" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G139" t="s">
-        <v>168</v>
+        <v>254</v>
       </c>
       <c r="H139" t="s">
-        <v>581</v>
-      </c>
-      <c r="I139" t="s">
-        <v>61</v>
+        <v>322</v>
       </c>
       <c r="J139" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="K139" t="s">
         <v>55</v>
@@ -8209,34 +8290,31 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>514</v>
+        <v>340</v>
       </c>
       <c r="B140" t="s">
-        <v>528</v>
+        <v>357</v>
       </c>
       <c r="C140" t="s">
-        <v>526</v>
+        <v>487</v>
       </c>
       <c r="D140" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E140" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="F140" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G140" t="s">
-        <v>527</v>
+        <v>312</v>
       </c>
       <c r="H140" t="s">
-        <v>509</v>
-      </c>
-      <c r="I140" t="s">
-        <v>61</v>
+        <v>235</v>
       </c>
       <c r="J140" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="K140" t="s">
         <v>55</v>
@@ -8253,37 +8331,37 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>515</v>
+        <v>341</v>
       </c>
       <c r="B141" t="s">
-        <v>529</v>
+        <v>358</v>
       </c>
       <c r="C141" t="s">
-        <v>530</v>
+        <v>359</v>
       </c>
       <c r="D141" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E141" t="s">
         <v>58</v>
       </c>
       <c r="F141" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G141" t="s">
-        <v>527</v>
+        <v>312</v>
       </c>
       <c r="H141" t="s">
-        <v>531</v>
+        <v>609</v>
       </c>
       <c r="I141" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="J141" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K141" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L141" t="s">
         <v>14</v>
@@ -8297,19 +8375,19 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>516</v>
+        <v>342</v>
       </c>
       <c r="B142" t="s">
-        <v>532</v>
+        <v>360</v>
       </c>
       <c r="C142" t="s">
-        <v>533</v>
+        <v>361</v>
       </c>
       <c r="D142" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E142" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="F142" t="s">
         <v>13</v>
@@ -8318,16 +8396,13 @@
         <v>168</v>
       </c>
       <c r="H142" t="s">
-        <v>534</v>
-      </c>
-      <c r="I142" t="s">
-        <v>61</v>
+        <v>322</v>
       </c>
       <c r="J142" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="K142" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L142" t="s">
         <v>14</v>
@@ -8341,34 +8416,34 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>517</v>
+        <v>343</v>
       </c>
       <c r="B143" t="s">
-        <v>535</v>
+        <v>362</v>
       </c>
       <c r="C143" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="D143" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E143" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="F143" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G143" t="s">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="H143" t="s">
-        <v>237</v>
+        <v>363</v>
       </c>
       <c r="I143" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="J143" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K143" t="s">
         <v>55</v>
@@ -8385,34 +8460,34 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>518</v>
+        <v>344</v>
       </c>
       <c r="B144" t="s">
-        <v>537</v>
+        <v>365</v>
       </c>
       <c r="C144" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="D144" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E144" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F144" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G144" t="s">
-        <v>170</v>
+        <v>367</v>
       </c>
       <c r="H144" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="I144" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="J144" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K144" t="s">
         <v>55</v>
@@ -8429,37 +8504,34 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>519</v>
+        <v>345</v>
       </c>
       <c r="B145" t="s">
-        <v>540</v>
+        <v>369</v>
       </c>
       <c r="C145" t="s">
-        <v>523</v>
+        <v>370</v>
       </c>
       <c r="D145" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E145" t="s">
         <v>33</v>
       </c>
       <c r="F145" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G145" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H145" t="s">
-        <v>237</v>
-      </c>
-      <c r="I145" t="s">
-        <v>61</v>
+        <v>568</v>
       </c>
       <c r="J145" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="K145" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L145" t="s">
         <v>14</v>
@@ -8473,13 +8545,13 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>541</v>
+        <v>346</v>
       </c>
       <c r="B146" t="s">
-        <v>548</v>
+        <v>371</v>
       </c>
       <c r="C146" t="s">
-        <v>549</v>
+        <v>372</v>
       </c>
       <c r="D146" t="s">
         <v>85</v>
@@ -8491,16 +8563,13 @@
         <v>13</v>
       </c>
       <c r="G146" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H146" t="s">
         <v>121</v>
       </c>
-      <c r="I146" t="s">
-        <v>157</v>
-      </c>
       <c r="J146" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="K146" t="s">
         <v>55</v>
@@ -8517,13 +8586,13 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>542</v>
+        <v>347</v>
       </c>
       <c r="B147" t="s">
-        <v>550</v>
+        <v>373</v>
       </c>
       <c r="C147" t="s">
-        <v>551</v>
+        <v>374</v>
       </c>
       <c r="D147" t="s">
         <v>85</v>
@@ -8535,16 +8604,16 @@
         <v>13</v>
       </c>
       <c r="G147" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H147" t="s">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="I147" t="s">
         <v>82</v>
       </c>
       <c r="J147" t="s">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="K147" t="s">
         <v>55</v>
@@ -8561,13 +8630,13 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>543</v>
+        <v>348</v>
       </c>
       <c r="B148" t="s">
-        <v>552</v>
+        <v>375</v>
       </c>
       <c r="C148" t="s">
-        <v>553</v>
+        <v>376</v>
       </c>
       <c r="D148" t="s">
         <v>85</v>
@@ -8576,19 +8645,19 @@
         <v>58</v>
       </c>
       <c r="F148" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G148" t="s">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="H148" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="I148" t="s">
         <v>82</v>
       </c>
       <c r="J148" t="s">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="K148" t="s">
         <v>55</v>
@@ -8605,13 +8674,13 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>544</v>
+        <v>349</v>
       </c>
       <c r="B149" t="s">
-        <v>554</v>
+        <v>379</v>
       </c>
       <c r="C149" t="s">
-        <v>551</v>
+        <v>380</v>
       </c>
       <c r="D149" t="s">
         <v>85</v>
@@ -8623,16 +8692,16 @@
         <v>13</v>
       </c>
       <c r="G149" t="s">
-        <v>168</v>
+        <v>381</v>
       </c>
       <c r="H149" t="s">
-        <v>305</v>
+        <v>240</v>
       </c>
       <c r="I149" t="s">
         <v>82</v>
       </c>
       <c r="J149" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="K149" t="s">
         <v>55</v>
@@ -8649,31 +8718,34 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>545</v>
+        <v>350</v>
       </c>
       <c r="B150" t="s">
-        <v>555</v>
+        <v>382</v>
       </c>
       <c r="C150" t="s">
-        <v>556</v>
+        <v>383</v>
       </c>
       <c r="D150" t="s">
         <v>85</v>
       </c>
       <c r="E150" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F150" t="s">
         <v>13</v>
       </c>
       <c r="G150" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="H150" t="s">
-        <v>324</v>
+        <v>240</v>
+      </c>
+      <c r="I150" t="s">
+        <v>82</v>
       </c>
       <c r="J150" t="s">
-        <v>584</v>
+        <v>173</v>
       </c>
       <c r="K150" t="s">
         <v>55</v>
@@ -8690,34 +8762,37 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>546</v>
+        <v>351</v>
       </c>
       <c r="B151" t="s">
-        <v>557</v>
+        <v>384</v>
       </c>
       <c r="C151" t="s">
-        <v>558</v>
+        <v>385</v>
       </c>
       <c r="D151" t="s">
         <v>85</v>
       </c>
       <c r="E151" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F151" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G151" t="s">
-        <v>559</v>
+        <v>312</v>
       </c>
       <c r="H151" t="s">
-        <v>391</v>
+        <v>240</v>
+      </c>
+      <c r="I151" t="s">
+        <v>82</v>
       </c>
       <c r="J151" t="s">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="K151" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L151" t="s">
         <v>14</v>
@@ -8731,19 +8806,19 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>547</v>
+        <v>352</v>
       </c>
       <c r="B152" t="s">
-        <v>560</v>
+        <v>386</v>
       </c>
       <c r="C152" t="s">
-        <v>561</v>
+        <v>387</v>
       </c>
       <c r="D152" t="s">
         <v>85</v>
       </c>
       <c r="E152" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F152" t="s">
         <v>13</v>
@@ -8752,10 +8827,13 @@
         <v>168</v>
       </c>
       <c r="H152" t="s">
-        <v>121</v>
+        <v>567</v>
+      </c>
+      <c r="I152" t="s">
+        <v>157</v>
       </c>
       <c r="J152" t="s">
-        <v>211</v>
+        <v>388</v>
       </c>
       <c r="K152" t="s">
         <v>55</v>
@@ -8772,34 +8850,34 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>585</v>
+        <v>390</v>
       </c>
       <c r="B153" t="s">
-        <v>590</v>
+        <v>396</v>
       </c>
       <c r="C153" t="s">
-        <v>591</v>
+        <v>397</v>
       </c>
       <c r="D153" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E153" t="s">
         <v>33</v>
       </c>
       <c r="F153" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G153" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H153" t="s">
-        <v>310</v>
+        <v>389</v>
       </c>
       <c r="I153" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="J153" t="s">
-        <v>592</v>
+        <v>398</v>
       </c>
       <c r="K153" t="s">
         <v>55</v>
@@ -8816,31 +8894,31 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>586</v>
+        <v>394</v>
       </c>
       <c r="B154" t="s">
-        <v>593</v>
+        <v>407</v>
       </c>
       <c r="C154" t="s">
-        <v>594</v>
+        <v>408</v>
       </c>
       <c r="D154" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E154" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F154" t="s">
         <v>13</v>
       </c>
       <c r="G154" t="s">
-        <v>256</v>
+        <v>168</v>
       </c>
       <c r="H154" t="s">
-        <v>391</v>
+        <v>506</v>
       </c>
       <c r="J154" t="s">
-        <v>84</v>
+        <v>173</v>
       </c>
       <c r="K154" t="s">
         <v>55</v>
@@ -8857,34 +8935,34 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>587</v>
+        <v>395</v>
       </c>
       <c r="B155" t="s">
-        <v>595</v>
+        <v>439</v>
       </c>
       <c r="C155" t="s">
-        <v>596</v>
+        <v>409</v>
       </c>
       <c r="D155" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E155" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F155" t="s">
         <v>13</v>
       </c>
       <c r="G155" t="s">
-        <v>256</v>
+        <v>168</v>
       </c>
       <c r="H155" t="s">
-        <v>324</v>
+        <v>609</v>
       </c>
       <c r="I155" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="J155" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K155" t="s">
         <v>55</v>
@@ -8901,19 +8979,19 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>588</v>
+        <v>478</v>
       </c>
       <c r="B156" t="s">
-        <v>597</v>
+        <v>489</v>
       </c>
       <c r="C156" t="s">
-        <v>598</v>
+        <v>488</v>
       </c>
       <c r="D156" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E156" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F156" t="s">
         <v>13</v>
@@ -8922,13 +9000,13 @@
         <v>168</v>
       </c>
       <c r="H156" t="s">
-        <v>391</v>
+        <v>618</v>
       </c>
       <c r="I156" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="J156" t="s">
-        <v>329</v>
+        <v>103</v>
       </c>
       <c r="K156" t="s">
         <v>55</v>
@@ -8945,16 +9023,16 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>589</v>
+        <v>479</v>
       </c>
       <c r="B157" t="s">
-        <v>599</v>
+        <v>480</v>
       </c>
       <c r="C157" t="s">
-        <v>600</v>
+        <v>481</v>
       </c>
       <c r="D157" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E157" t="s">
         <v>33</v>
@@ -8963,16 +9041,13 @@
         <v>13</v>
       </c>
       <c r="G157" t="s">
-        <v>256</v>
+        <v>168</v>
       </c>
       <c r="H157" t="s">
-        <v>324</v>
-      </c>
-      <c r="I157" t="s">
-        <v>61</v>
+        <v>572</v>
       </c>
       <c r="J157" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K157" t="s">
         <v>55</v>
@@ -8989,13 +9064,13 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>601</v>
+        <v>536</v>
       </c>
       <c r="B158" t="s">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="C158" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="D158" t="s">
         <v>85</v>
@@ -9010,13 +9085,13 @@
         <v>168</v>
       </c>
       <c r="H158" t="s">
-        <v>391</v>
+        <v>121</v>
       </c>
       <c r="I158" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="J158" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K158" t="s">
         <v>55</v>
@@ -9033,19 +9108,19 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>602</v>
+        <v>537</v>
       </c>
       <c r="B159" t="s">
-        <v>607</v>
+        <v>543</v>
       </c>
       <c r="C159" t="s">
-        <v>608</v>
+        <v>544</v>
       </c>
       <c r="D159" t="s">
         <v>85</v>
       </c>
       <c r="E159" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F159" t="s">
         <v>13</v>
@@ -9054,10 +9129,13 @@
         <v>168</v>
       </c>
       <c r="H159" t="s">
-        <v>391</v>
+        <v>303</v>
+      </c>
+      <c r="I159" t="s">
+        <v>82</v>
       </c>
       <c r="J159" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="K159" t="s">
         <v>55</v>
@@ -9074,34 +9152,34 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>603</v>
+        <v>538</v>
       </c>
       <c r="B160" t="s">
-        <v>609</v>
+        <v>545</v>
       </c>
       <c r="C160" t="s">
-        <v>610</v>
+        <v>546</v>
       </c>
       <c r="D160" t="s">
         <v>85</v>
       </c>
       <c r="E160" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F160" t="s">
         <v>13</v>
       </c>
       <c r="G160" t="s">
-        <v>611</v>
+        <v>312</v>
       </c>
       <c r="H160" t="s">
-        <v>572</v>
+        <v>356</v>
       </c>
       <c r="I160" t="s">
         <v>82</v>
       </c>
       <c r="J160" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K160" t="s">
         <v>55</v>
@@ -9118,13 +9196,13 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>604</v>
+        <v>539</v>
       </c>
       <c r="B161" t="s">
-        <v>612</v>
+        <v>547</v>
       </c>
       <c r="C161" t="s">
-        <v>613</v>
+        <v>544</v>
       </c>
       <c r="D161" t="s">
         <v>85</v>
@@ -9139,10 +9217,13 @@
         <v>168</v>
       </c>
       <c r="H161" t="s">
-        <v>391</v>
+        <v>303</v>
+      </c>
+      <c r="I161" t="s">
+        <v>82</v>
       </c>
       <c r="J161" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="K161" t="s">
         <v>55</v>
@@ -9154,6 +9235,217 @@
         <v>15</v>
       </c>
       <c r="N161" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B162" t="s">
+        <v>548</v>
+      </c>
+      <c r="C162" t="s">
+        <v>549</v>
+      </c>
+      <c r="D162" t="s">
+        <v>85</v>
+      </c>
+      <c r="E162" t="s">
+        <v>33</v>
+      </c>
+      <c r="F162" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" t="s">
+        <v>168</v>
+      </c>
+      <c r="H162" t="s">
+        <v>322</v>
+      </c>
+      <c r="J162" t="s">
+        <v>576</v>
+      </c>
+      <c r="K162" t="s">
+        <v>55</v>
+      </c>
+      <c r="L162" t="s">
+        <v>14</v>
+      </c>
+      <c r="M162" t="s">
+        <v>15</v>
+      </c>
+      <c r="N162" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B163" t="s">
+        <v>553</v>
+      </c>
+      <c r="C163" t="s">
+        <v>554</v>
+      </c>
+      <c r="D163" t="s">
+        <v>85</v>
+      </c>
+      <c r="E163" t="s">
+        <v>58</v>
+      </c>
+      <c r="F163" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" t="s">
+        <v>168</v>
+      </c>
+      <c r="H163" t="s">
+        <v>121</v>
+      </c>
+      <c r="J163" t="s">
+        <v>210</v>
+      </c>
+      <c r="K163" t="s">
+        <v>55</v>
+      </c>
+      <c r="L163" t="s">
+        <v>14</v>
+      </c>
+      <c r="M163" t="s">
+        <v>15</v>
+      </c>
+      <c r="N163" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B164" t="s">
+        <v>601</v>
+      </c>
+      <c r="C164" t="s">
+        <v>602</v>
+      </c>
+      <c r="D164" t="s">
+        <v>85</v>
+      </c>
+      <c r="E164" t="s">
+        <v>33</v>
+      </c>
+      <c r="F164" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" t="s">
+        <v>603</v>
+      </c>
+      <c r="H164" t="s">
+        <v>565</v>
+      </c>
+      <c r="I164" t="s">
+        <v>82</v>
+      </c>
+      <c r="J164" t="s">
+        <v>105</v>
+      </c>
+      <c r="K164" t="s">
+        <v>55</v>
+      </c>
+      <c r="L164" t="s">
+        <v>14</v>
+      </c>
+      <c r="M164" t="s">
+        <v>15</v>
+      </c>
+      <c r="N164" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B165" t="s">
+        <v>627</v>
+      </c>
+      <c r="C165" t="s">
+        <v>624</v>
+      </c>
+      <c r="D165" t="s">
+        <v>85</v>
+      </c>
+      <c r="E165" t="s">
+        <v>58</v>
+      </c>
+      <c r="F165" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" t="s">
+        <v>168</v>
+      </c>
+      <c r="H165" t="s">
+        <v>625</v>
+      </c>
+      <c r="I165" t="s">
+        <v>157</v>
+      </c>
+      <c r="J165" t="s">
+        <v>220</v>
+      </c>
+      <c r="K165" t="s">
+        <v>55</v>
+      </c>
+      <c r="L165" t="s">
+        <v>14</v>
+      </c>
+      <c r="M165" t="s">
+        <v>15</v>
+      </c>
+      <c r="N165" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B166" t="s">
+        <v>626</v>
+      </c>
+      <c r="C166" t="s">
+        <v>628</v>
+      </c>
+      <c r="D166" t="s">
+        <v>85</v>
+      </c>
+      <c r="E166" t="s">
+        <v>58</v>
+      </c>
+      <c r="F166" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" t="s">
+        <v>168</v>
+      </c>
+      <c r="H166" t="s">
+        <v>389</v>
+      </c>
+      <c r="J166" t="s">
+        <v>220</v>
+      </c>
+      <c r="K166" t="s">
+        <v>55</v>
+      </c>
+      <c r="L166" t="s">
+        <v>14</v>
+      </c>
+      <c r="M166" t="s">
+        <v>15</v>
+      </c>
+      <c r="N166" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78E4303-7D33-3D43-93B3-F9DA4F5B7163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5222171-3787-B641-8A2E-D1D0BF30D9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="667">
   <si>
     <t>id</t>
   </si>
@@ -316,1627 +316,1711 @@
     <t>maristas_esp</t>
   </si>
   <si>
+    <t>maristas_huelva</t>
+  </si>
+  <si>
+    <t>rrss</t>
+  </si>
+  <si>
+    <t>usos</t>
+  </si>
+  <si>
+    <t>firma</t>
+  </si>
+  <si>
+    <t>postal</t>
+  </si>
+  <si>
+    <t>firma;minimalista</t>
+  </si>
+  <si>
+    <t>cartel</t>
+  </si>
+  <si>
+    <t>ILU-0020</t>
+  </si>
+  <si>
+    <t>Champagnat - GVX BN</t>
+  </si>
+  <si>
+    <t>DIS-0008</t>
+  </si>
+  <si>
+    <t>Centenario</t>
+  </si>
+  <si>
+    <t>Parte cartel 100 años ESP vectorizado</t>
+  </si>
+  <si>
+    <t>ILU-0021</t>
+  </si>
+  <si>
+    <t>ILU-0022</t>
+  </si>
+  <si>
+    <t>ILU-0023</t>
+  </si>
+  <si>
+    <t>Click Champagnat</t>
+  </si>
+  <si>
+    <t>San Marcelino playmobil</t>
+  </si>
+  <si>
+    <t>San Marcelino XXII</t>
+  </si>
+  <si>
+    <t>De imagen San Marcelino II - Brasil</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>RRSS</t>
+  </si>
+  <si>
+    <t>jarts</t>
+  </si>
+  <si>
+    <t>maristas</t>
+  </si>
+  <si>
+    <t>M. Champagnat</t>
+  </si>
+  <si>
+    <t>San Marcelino Champagnat BN</t>
+  </si>
+  <si>
+    <t>Champagnat Beatif.</t>
+  </si>
+  <si>
+    <t>ILU-0024</t>
+  </si>
+  <si>
+    <t>ILU-0025</t>
+  </si>
+  <si>
+    <t>ILU-0026</t>
+  </si>
+  <si>
+    <t>ILU-0027</t>
+  </si>
+  <si>
+    <t>ILU-0028</t>
+  </si>
+  <si>
+    <t>ILU-0029</t>
+  </si>
+  <si>
+    <t>ILU-0030</t>
+  </si>
+  <si>
+    <t>Nº Sª de Fourviere</t>
+  </si>
+  <si>
+    <t>Nuestra Señora de Fourviere</t>
+  </si>
+  <si>
+    <t>figura</t>
+  </si>
+  <si>
+    <t>María II</t>
+  </si>
+  <si>
+    <t>Maria Niña (I love Jesus)</t>
+  </si>
+  <si>
+    <t>María, Buena Madre I</t>
+  </si>
+  <si>
+    <t>Buena Madre B/N</t>
+  </si>
+  <si>
+    <t>Nuestra Buena Madre</t>
+  </si>
+  <si>
+    <t>Buena Madre FR</t>
+  </si>
+  <si>
+    <t>María III</t>
+  </si>
+  <si>
+    <t>A Jesús por María</t>
+  </si>
+  <si>
+    <t>María, Buena Madre II</t>
+  </si>
+  <si>
+    <t>Mi Buena Madre</t>
+  </si>
+  <si>
+    <t>María, Buena Madre III</t>
+  </si>
+  <si>
+    <t>María, Buena Madre</t>
+  </si>
+  <si>
+    <t>DIS-0009</t>
+  </si>
+  <si>
+    <t>DIS-0010</t>
+  </si>
+  <si>
+    <t>DIS-0011</t>
+  </si>
+  <si>
+    <t>La casa de María</t>
+  </si>
+  <si>
+    <t>Vector de mural (Badajoz)</t>
+  </si>
+  <si>
+    <t>Vector de mural B/N (Badajoz)</t>
+  </si>
+  <si>
+    <t>La casa de María B/N</t>
+  </si>
+  <si>
+    <t>maria</t>
+  </si>
+  <si>
+    <t>Moteros Maristas</t>
+  </si>
+  <si>
+    <t>Logo moteros maristas</t>
+  </si>
+  <si>
+    <t>logo</t>
+  </si>
+  <si>
+    <t>ILU-0031</t>
+  </si>
+  <si>
+    <t>ILU-0032</t>
+  </si>
+  <si>
+    <t>Magnificat</t>
+  </si>
+  <si>
+    <t>María e Isabel</t>
+  </si>
+  <si>
+    <t>María, Buena Madre IV</t>
+  </si>
+  <si>
+    <t>María, Madre</t>
+  </si>
+  <si>
+    <t>ILU-0033</t>
+  </si>
+  <si>
+    <t>3 Violetas</t>
+  </si>
+  <si>
+    <t>Humildad, Sencillez y Modestia</t>
+  </si>
+  <si>
+    <t>sin_fondo;logo</t>
+  </si>
+  <si>
+    <t>Arturo_MP</t>
+  </si>
+  <si>
+    <t>FMS</t>
+  </si>
+  <si>
+    <t>C_Towers</t>
+  </si>
+  <si>
+    <t>A_Gil</t>
+  </si>
+  <si>
+    <t>Goyo_D</t>
+  </si>
+  <si>
+    <t>cartel;postal</t>
+  </si>
+  <si>
+    <t>mural;rrss</t>
+  </si>
+  <si>
+    <t>ILU-0034</t>
+  </si>
+  <si>
+    <t>Marist-Art</t>
+  </si>
+  <si>
+    <t>DIS-0012</t>
+  </si>
+  <si>
+    <t>DIS-0013</t>
+  </si>
+  <si>
+    <t>DIS-0014</t>
+  </si>
+  <si>
+    <t>DIS-0015</t>
+  </si>
+  <si>
+    <t>DIS-0016</t>
+  </si>
+  <si>
+    <t>DIS-0017</t>
+  </si>
+  <si>
+    <t>DIS-0018</t>
+  </si>
+  <si>
+    <t>DIS-0019</t>
+  </si>
+  <si>
+    <t>DIS-0020</t>
+  </si>
+  <si>
+    <t>GVX Verano 2014</t>
+  </si>
+  <si>
+    <t>Camiseta Da Vida 2014</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2015</t>
+  </si>
+  <si>
+    <t>Camiseta Pascua 2015</t>
+  </si>
+  <si>
+    <t>GVX Verano 2015</t>
+  </si>
+  <si>
+    <t>Camiseta de grupos 2015</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2016</t>
+  </si>
+  <si>
+    <t>Camiseta Pascua 2016</t>
+  </si>
+  <si>
+    <t>GVX Verano 2016</t>
+  </si>
+  <si>
+    <t>Camiseta Da Vida 2018</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2018</t>
+  </si>
+  <si>
+    <t>Camiseta Pascua 2018</t>
+  </si>
+  <si>
+    <t>GVX Verano 2025</t>
+  </si>
+  <si>
+    <t>Camisetas Ojos que ven… 2025 (espalda)</t>
+  </si>
+  <si>
+    <t>GVX Verano 2023</t>
+  </si>
+  <si>
+    <t>Camiseta Ser la Chispa… 2023 (espalda + logo delantero)</t>
+  </si>
+  <si>
+    <t>DIS-0021</t>
+  </si>
+  <si>
+    <t>DIS-0022</t>
+  </si>
+  <si>
+    <t>DIS-0023</t>
+  </si>
+  <si>
+    <t>ILU-0035</t>
+  </si>
+  <si>
+    <t>BRO mode</t>
+  </si>
+  <si>
+    <t>maristas;vocacional</t>
+  </si>
+  <si>
+    <t>postal;rrss;sticker</t>
+  </si>
+  <si>
+    <t>sticker</t>
+  </si>
+  <si>
+    <t>sticker;taza</t>
+  </si>
+  <si>
+    <t>Estoy a la puerta y llamo</t>
+  </si>
+  <si>
+    <t>cartel;rrss</t>
+  </si>
+  <si>
+    <t>Convivencia vocacional GVX 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cree en ti </t>
+  </si>
+  <si>
+    <t>Convivencia vocacional GVX 2024</t>
+  </si>
+  <si>
+    <t>Maristas</t>
+  </si>
+  <si>
+    <t>Desde 1817</t>
+  </si>
+  <si>
+    <t>maristas;violetas</t>
+  </si>
+  <si>
+    <t>textil</t>
+  </si>
+  <si>
+    <t>ILU-0036</t>
+  </si>
+  <si>
+    <t>ILU-0037</t>
+  </si>
+  <si>
+    <t>ILU-0038</t>
+  </si>
+  <si>
+    <t>ILU-0039</t>
+  </si>
+  <si>
+    <t>ILU-0040</t>
+  </si>
+  <si>
+    <t>La Oveja Encontrada</t>
+  </si>
+  <si>
+    <t>#Soy la 100</t>
+  </si>
+  <si>
+    <t>evangelio;violetas</t>
+  </si>
+  <si>
+    <t>sticker;rrss</t>
+  </si>
+  <si>
+    <t>Titulada</t>
+  </si>
+  <si>
+    <t>Graduación</t>
+  </si>
+  <si>
+    <t>sticker;cartel</t>
+  </si>
+  <si>
+    <t>Atienden</t>
+  </si>
+  <si>
+    <t>En clase</t>
+  </si>
+  <si>
+    <t>maristas;educacion</t>
+  </si>
+  <si>
+    <t>educacion</t>
+  </si>
+  <si>
+    <t>Con corazón</t>
+  </si>
+  <si>
+    <t>Saltando</t>
+  </si>
+  <si>
+    <t>logo;sin_fondo</t>
+  </si>
+  <si>
+    <t>educacion;evangelio</t>
+  </si>
+  <si>
+    <t>Estudiando</t>
+  </si>
+  <si>
+    <t>En clase II</t>
+  </si>
+  <si>
+    <t>ILU-0041</t>
+  </si>
+  <si>
+    <t>ILU-0042</t>
+  </si>
+  <si>
+    <t>ILU-0043</t>
+  </si>
+  <si>
+    <t>ILU-0044</t>
+  </si>
+  <si>
+    <t>3 Violetas II</t>
+  </si>
+  <si>
+    <t>3 Violetas III BN</t>
+  </si>
+  <si>
+    <t>3 Violetas III color</t>
+  </si>
+  <si>
+    <t>Nuestras 3 violetas</t>
+  </si>
+  <si>
+    <t>Violetas Marist</t>
+  </si>
+  <si>
+    <t>Dos combinaciones bordado</t>
+  </si>
+  <si>
+    <t>PxM_maristas_chile</t>
+  </si>
+  <si>
+    <t>C_Towers_jarts</t>
+  </si>
+  <si>
+    <t>Arturo_MP_C_Towers</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Goyo_D</t>
+  </si>
+  <si>
+    <t>DIS-0024</t>
+  </si>
+  <si>
+    <t>DIS-0025</t>
+  </si>
+  <si>
+    <t>DIS-0026</t>
+  </si>
+  <si>
+    <t>DIS-0027</t>
+  </si>
+  <si>
+    <t>DIS-0028</t>
+  </si>
+  <si>
+    <t>DIS-0029</t>
+  </si>
+  <si>
+    <t>GVX Verano 2019</t>
+  </si>
+  <si>
+    <t>Camiseta Comunidad 2019 (espalda)</t>
+  </si>
+  <si>
+    <t>GVX Verano 2021</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2022</t>
+  </si>
+  <si>
+    <t>frase;logo;sin_fondo</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2023</t>
+  </si>
+  <si>
+    <t>GVX Sticker Pascua 2025</t>
+  </si>
+  <si>
+    <t>Portavela Pascua 2025</t>
+  </si>
+  <si>
+    <t>GVX Verano 2022</t>
+  </si>
+  <si>
+    <t>Camiseta Chispa Da Vida 2022</t>
+  </si>
+  <si>
+    <t>Camiseta HERE WE ARE 2021 (frontal)</t>
+  </si>
+  <si>
+    <t>DIS-0030</t>
+  </si>
+  <si>
+    <t>GVX Sticker 2024</t>
+  </si>
+  <si>
+    <t>DIS-0031</t>
+  </si>
+  <si>
+    <t>Camiseta Da Vida 2025 (espalda)</t>
+  </si>
+  <si>
+    <t>Sticker G de Grupos</t>
+  </si>
+  <si>
+    <t>Camiseta a better World 2016</t>
+  </si>
+  <si>
+    <t>DIS-0032</t>
+  </si>
+  <si>
+    <t>Camiseta GVX Sal</t>
+  </si>
+  <si>
+    <t>GVX Sevilla 2007</t>
+  </si>
+  <si>
+    <t>ILU-0045</t>
+  </si>
+  <si>
+    <t>Un mismo agua</t>
+  </si>
+  <si>
+    <t>ILU-0046</t>
+  </si>
+  <si>
+    <t>Vayamos al Fondo</t>
+  </si>
+  <si>
+    <t>ILU-0047</t>
+  </si>
+  <si>
+    <t>ILU-0048</t>
+  </si>
+  <si>
+    <t>ILU-0049</t>
+  </si>
+  <si>
+    <t>ILU-0050</t>
+  </si>
+  <si>
+    <t>ILU-0051</t>
+  </si>
+  <si>
+    <t>ILU-0052</t>
+  </si>
+  <si>
+    <t>ILU-0053</t>
+  </si>
+  <si>
+    <t>ILU-0054</t>
+  </si>
+  <si>
+    <t>ILU-0055</t>
+  </si>
+  <si>
+    <t>ILU-0056</t>
+  </si>
+  <si>
+    <t>Busco estrella</t>
+  </si>
+  <si>
+    <t>Viaje a Belén Navidad</t>
+  </si>
+  <si>
+    <t>Vocacción</t>
+  </si>
+  <si>
+    <t>No haremos 3 tiendas</t>
+  </si>
+  <si>
+    <t>vocacional</t>
+  </si>
+  <si>
+    <t>Cruz Espíritu I</t>
+  </si>
+  <si>
+    <t>Cruz Espíritu II</t>
+  </si>
+  <si>
+    <t>Confirmación Sevilla</t>
+  </si>
+  <si>
+    <t>Confirmación Sevilla II</t>
+  </si>
+  <si>
+    <t>GVX;evangelio</t>
+  </si>
+  <si>
+    <t>sticker;taza;rrss</t>
+  </si>
+  <si>
+    <t>Para Asamblea Mediterránea</t>
+  </si>
+  <si>
+    <t>Arturo_MP_ ProvMediterranea</t>
+  </si>
+  <si>
+    <t>Arturo_MP_ProvMediterranea</t>
+  </si>
+  <si>
+    <t>Arturo_MP_ Jorge_MR_ProvMediterranea</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Jorge_MR_ProvMediterranea</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Fer_OR_ProvMediterranea</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Arturo_MR_ProvMediterranea</t>
+  </si>
+  <si>
+    <t>Cada Navidad</t>
+  </si>
+  <si>
+    <t>Para felicitación Colegio Sevilla</t>
+  </si>
+  <si>
+    <t>maristas;evangelio;violetas</t>
+  </si>
+  <si>
+    <t>Panes y peces</t>
+  </si>
+  <si>
+    <t>Ilustración documentos</t>
+  </si>
+  <si>
+    <t>evangelio</t>
+  </si>
+  <si>
+    <t>maristas;evangelio</t>
+  </si>
+  <si>
+    <t>sticker;cartel;postal</t>
+  </si>
+  <si>
+    <t>Sal y Luz I - Evangelío</t>
+  </si>
+  <si>
+    <t>Marist Runners</t>
+  </si>
+  <si>
+    <t>sticker;textil</t>
+  </si>
+  <si>
+    <t>Camiseta carrera solidaria</t>
+  </si>
+  <si>
+    <t>Un corazón, una misión</t>
+  </si>
+  <si>
+    <t>Preparación Capítulo General</t>
+  </si>
+  <si>
+    <t>Ilustraciones maristas</t>
+  </si>
+  <si>
+    <t>Firma de Champagnat</t>
+  </si>
+  <si>
+    <t>En Tríptico Vocacional</t>
+  </si>
+  <si>
+    <t>Join the Revolution I</t>
+  </si>
+  <si>
+    <t>Join the Revolution II</t>
+  </si>
+  <si>
+    <t>Si hiciéramos uno…</t>
+  </si>
+  <si>
+    <t>Para Escuela de Tiempo Libre</t>
+  </si>
+  <si>
+    <t>DIS-0033</t>
+  </si>
+  <si>
+    <t>DIS-0034</t>
+  </si>
+  <si>
+    <t>DIS-0035</t>
+  </si>
+  <si>
+    <t>DIS-0036</t>
+  </si>
+  <si>
+    <t>DIS-0037</t>
+  </si>
+  <si>
+    <t>DIS-0038</t>
+  </si>
+  <si>
+    <t>DIS-0039</t>
+  </si>
+  <si>
+    <t>DIS-0040</t>
+  </si>
+  <si>
+    <t>DIS-0041</t>
+  </si>
+  <si>
+    <t>DIS-0042</t>
+  </si>
+  <si>
+    <t>DIS-0043</t>
+  </si>
+  <si>
+    <t>DIS-0044</t>
+  </si>
+  <si>
+    <t>DIS-0045</t>
+  </si>
+  <si>
+    <t>DIS-0046</t>
+  </si>
+  <si>
+    <t>DIS-0047</t>
+  </si>
+  <si>
+    <t>VI Jornadas Educadores Maristas</t>
+  </si>
+  <si>
+    <t>Eucaristía</t>
+  </si>
+  <si>
+    <t>Para Primera Eucaristía Sevilla 2017</t>
+  </si>
+  <si>
+    <t>evangelio;GVX</t>
+  </si>
+  <si>
+    <t>IV Jornadas Educadores Maristas</t>
+  </si>
+  <si>
+    <t>El mundo, la mejor cocina</t>
+  </si>
+  <si>
+    <t>Para encuentro Delegados de Pastoral (delantal)</t>
+  </si>
+  <si>
+    <t>¿Qué tal tu amor?</t>
+  </si>
+  <si>
+    <t>Viñeta</t>
+  </si>
+  <si>
+    <t>Hagamos de la casa hogar</t>
+  </si>
+  <si>
+    <t>maristas;educacion;evangelio</t>
+  </si>
+  <si>
+    <t>Para tiempo Cuaresma I Mediterránea (esp)</t>
+  </si>
+  <si>
+    <t>Constancia</t>
+  </si>
+  <si>
+    <t>Para CB Maristas Sevilla</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Arturo_MR</t>
+  </si>
+  <si>
+    <t>maristas;deporte</t>
+  </si>
+  <si>
+    <t>La Valla</t>
+  </si>
+  <si>
+    <t>Cuadro mesa de La Valla</t>
+  </si>
+  <si>
+    <t>Faros de Esperanza</t>
+  </si>
+  <si>
+    <t>Para Capítulo Prov Mediterránea</t>
+  </si>
+  <si>
+    <t>…una casa acogliente</t>
+  </si>
+  <si>
+    <t>Para tiempo Cuaresma I Mediterránea (ita)</t>
+  </si>
+  <si>
+    <t>The Home of Mary</t>
+  </si>
+  <si>
+    <t>Camiseta campaña Sevilla 2015</t>
+  </si>
+  <si>
+    <t>Arturo_MP_maristas_USA</t>
+  </si>
+  <si>
+    <t>maristas;maria</t>
+  </si>
+  <si>
+    <t>Se escucha un latido</t>
+  </si>
+  <si>
+    <t>Para tiempo Adviento I Mediterránea (esp)</t>
+  </si>
+  <si>
+    <t>Arturo_MP_ProvMediterranea_Fer_OR</t>
+  </si>
+  <si>
+    <t>Somos las manos de Dios</t>
+  </si>
+  <si>
+    <t>Para tiempo Cuaresma II Mediterránea (esp)</t>
+  </si>
+  <si>
+    <t>Siamo le mani di Dio</t>
+  </si>
+  <si>
+    <t>Para tiempo Cuaresma II Mediterránea (ita)</t>
+  </si>
+  <si>
+    <t>CB Maristas (anterior logo)</t>
+  </si>
+  <si>
+    <t>Para taza CB Maristas Sevilla</t>
+  </si>
+  <si>
+    <t>taza</t>
+  </si>
+  <si>
+    <t>GVX</t>
+  </si>
+  <si>
+    <t>DIS-0048</t>
+  </si>
+  <si>
+    <t>DIS-0049</t>
+  </si>
+  <si>
+    <t>DIS-0050</t>
+  </si>
+  <si>
+    <t>DIS-0051</t>
+  </si>
+  <si>
+    <t>DIS-0052</t>
+  </si>
+  <si>
+    <t>DIS-0053</t>
+  </si>
+  <si>
+    <t>Bordado Etapas GVX</t>
+  </si>
+  <si>
+    <t>Logo GVX local</t>
+  </si>
+  <si>
+    <t>textil;sticker</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2024</t>
+  </si>
+  <si>
+    <t>Camiseta Elegir Vivir Ir (espalda)</t>
+  </si>
+  <si>
+    <t>GVX Verano 2017</t>
+  </si>
+  <si>
+    <t>Volver al origen para empezar de nuevo</t>
+  </si>
+  <si>
+    <t>C_Towers_ProvMediterranea</t>
+  </si>
+  <si>
+    <t>GVX Verano 2018</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Texeira_ProvMediterranea</t>
+  </si>
+  <si>
+    <t>GVX;champagnat;violetas</t>
+  </si>
+  <si>
+    <t>Semana Vocacional</t>
+  </si>
+  <si>
+    <t>Para semana Vocacional Sevilla</t>
+  </si>
+  <si>
+    <t>Posibles camisetas #escuchaaunniño</t>
+  </si>
+  <si>
+    <t>ILU-0057</t>
+  </si>
+  <si>
+    <t>ILU-0058</t>
+  </si>
+  <si>
+    <t>ILU-0059</t>
+  </si>
+  <si>
+    <t>ILU-0060</t>
+  </si>
+  <si>
+    <t>ILU-0061</t>
+  </si>
+  <si>
+    <t>ILU-0062</t>
+  </si>
+  <si>
+    <t>ILU-0063</t>
+  </si>
+  <si>
+    <t>ILU-0064</t>
+  </si>
+  <si>
+    <t>ILU-0065</t>
+  </si>
+  <si>
+    <t>ILU-0066</t>
+  </si>
+  <si>
+    <t>ILU-0067</t>
+  </si>
+  <si>
+    <t>ILU-0068</t>
+  </si>
+  <si>
+    <t>ILU-0069</t>
+  </si>
+  <si>
+    <t>ILU-0070</t>
+  </si>
+  <si>
+    <t>ILU-0071</t>
+  </si>
+  <si>
+    <t>JUMP</t>
+  </si>
+  <si>
+    <t>Jump Walk Dream</t>
+  </si>
+  <si>
+    <t>ProvMediterranea</t>
+  </si>
+  <si>
+    <t>Champagnat 2000+</t>
+  </si>
+  <si>
+    <t>Llamadas</t>
+  </si>
+  <si>
+    <t>Silueta Champagnat acuarela</t>
+  </si>
+  <si>
+    <t>San Marcelino Champagnat</t>
+  </si>
+  <si>
+    <t>J_Ramos</t>
+  </si>
+  <si>
+    <t>maristas;champagnat;violetas</t>
+  </si>
+  <si>
+    <t>BuenaJente</t>
+  </si>
+  <si>
+    <t>Jesús, el BuenaJente</t>
+  </si>
+  <si>
+    <t>mural;cartel;textil</t>
+  </si>
+  <si>
+    <t>Atardece</t>
+  </si>
+  <si>
+    <t>Quédate con nosotros (de GVX Pascua 2026)</t>
+  </si>
+  <si>
+    <t>Qué te han contado los niños? (ita)</t>
+  </si>
+  <si>
+    <t>Da Vida</t>
+  </si>
+  <si>
+    <t>De GVX Verano 22</t>
+  </si>
+  <si>
+    <t>Futuro</t>
+  </si>
+  <si>
+    <t>Para Semana Vocacional</t>
+  </si>
+  <si>
+    <t>Arturo_MP_J_Ramos</t>
+  </si>
+  <si>
+    <t>Gente normal (esp)</t>
+  </si>
+  <si>
+    <t>Sencillez</t>
+  </si>
+  <si>
+    <t>Violetas Marist II</t>
+  </si>
+  <si>
+    <t>Los pequeños grandes detalles</t>
+  </si>
+  <si>
+    <t>Voluntariado marista</t>
+  </si>
+  <si>
+    <t>Para formación RRHH Mediterránea</t>
+  </si>
+  <si>
+    <t>Protección de la Infancia</t>
+  </si>
+  <si>
+    <t>Para formación Mediterránea</t>
+  </si>
+  <si>
+    <t>sticker;postal</t>
+  </si>
+  <si>
+    <t>Inspira</t>
+  </si>
+  <si>
+    <t>Ilustrar Interioridad</t>
+  </si>
+  <si>
+    <t>Como Dios</t>
+  </si>
+  <si>
+    <t>Para vivir como Dios,ama, perdona y…</t>
+  </si>
+  <si>
+    <t>ChicaCora</t>
+  </si>
+  <si>
+    <t>Ama (os, te, les)</t>
+  </si>
+  <si>
+    <t>#Soy la 100 II</t>
+  </si>
+  <si>
+    <t>Y salió a buscarla</t>
+  </si>
+  <si>
+    <t>ILU-0072</t>
+  </si>
+  <si>
+    <t>ILU-0073</t>
+  </si>
+  <si>
+    <t>ILU-0074</t>
+  </si>
+  <si>
+    <t>ILU-0075</t>
+  </si>
+  <si>
+    <t>ILU-0076</t>
+  </si>
+  <si>
+    <t>Atardece II</t>
+  </si>
+  <si>
+    <t>#accesoeducativo Todos con cole</t>
+  </si>
+  <si>
+    <t>Buena Madre II</t>
+  </si>
+  <si>
+    <t>Silueta María, Buena Madre</t>
+  </si>
+  <si>
+    <t>Anagrama María</t>
+  </si>
+  <si>
+    <t>Basado en antiguo anagrama edificio</t>
+  </si>
+  <si>
+    <t>Quien no ama…</t>
+  </si>
+  <si>
+    <t>Para educar es preciso amar</t>
+  </si>
+  <si>
+    <t>Escuchas?</t>
+  </si>
+  <si>
+    <t>Hasta en la brisa</t>
+  </si>
+  <si>
+    <t>evangelio;vocacional</t>
+  </si>
+  <si>
+    <t>DIS-0054</t>
+  </si>
+  <si>
+    <t>DIS-0055</t>
+  </si>
+  <si>
+    <t>Ceda el paso y sígalos</t>
+  </si>
+  <si>
+    <t>Para Viaje a Belén Maristas Jaén</t>
+  </si>
+  <si>
+    <t>Para convivencia Marcha GVX</t>
+  </si>
+  <si>
+    <t>Para convivencia Marcha GVX II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuestras 3 violetas </t>
+  </si>
+  <si>
+    <t>Change &lt; &gt; Chance</t>
+  </si>
+  <si>
+    <t>Cartel 2025 Mediterránea</t>
+  </si>
+  <si>
+    <t>Cartel 2022 Mediterránea</t>
+  </si>
+  <si>
+    <t>Recordando al Hno Boni FQ</t>
+  </si>
+  <si>
+    <t>Excusas yo?</t>
+  </si>
+  <si>
+    <t>maria;violetas</t>
+  </si>
+  <si>
+    <t>maria;paz</t>
+  </si>
+  <si>
+    <t>sin_fondo;minimalista</t>
+  </si>
+  <si>
+    <t>ILU-0077</t>
+  </si>
+  <si>
+    <t>ILU-0078</t>
+  </si>
+  <si>
+    <t>ILU-0079</t>
+  </si>
+  <si>
+    <t>ILU-0080</t>
+  </si>
+  <si>
+    <t>Tras sus pasos</t>
+  </si>
+  <si>
+    <t>Seguimiento</t>
+  </si>
+  <si>
+    <t>Mi primera Eucaristía</t>
+  </si>
+  <si>
+    <t>evangelio;paz;violetas</t>
+  </si>
+  <si>
+    <t>Recordatorio</t>
+  </si>
+  <si>
+    <t>R-Evolution</t>
+  </si>
+  <si>
+    <t>La revolución de la Sencillez</t>
+  </si>
+  <si>
+    <t>Orienta 2</t>
+  </si>
+  <si>
+    <t>Orientación profesional y vocacional</t>
+  </si>
+  <si>
+    <t>educacion;vocacional</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Jose_MR_C_Towers</t>
+  </si>
+  <si>
+    <t>ILU-0081</t>
+  </si>
+  <si>
+    <t>ILU-0082</t>
+  </si>
+  <si>
+    <t>ILU-0083</t>
+  </si>
+  <si>
+    <t>ILU-0084</t>
+  </si>
+  <si>
+    <t>ILU-0085</t>
+  </si>
+  <si>
+    <t>ILU-0086</t>
+  </si>
+  <si>
+    <t>ILU-0087</t>
+  </si>
+  <si>
+    <t>ILU-0088</t>
+  </si>
+  <si>
+    <t>ILU-0089</t>
+  </si>
+  <si>
+    <t>Barco de papel</t>
+  </si>
+  <si>
+    <t>educacion;maria</t>
+  </si>
+  <si>
+    <t>Estrella de papel</t>
+  </si>
+  <si>
+    <t>Parte cartel 'Cambia' (MRE)</t>
+  </si>
+  <si>
+    <t>L´Hermitage</t>
+  </si>
+  <si>
+    <t>Silueta edificio actual NS L´Hermitage</t>
+  </si>
+  <si>
+    <t>Para orientación profesional y vocacional</t>
+  </si>
+  <si>
+    <t>Arturo_MP_RRSS</t>
+  </si>
+  <si>
+    <t>Elegir y compartir</t>
+  </si>
+  <si>
+    <t>Diálogo</t>
+  </si>
+  <si>
+    <t>No-Violencia</t>
+  </si>
+  <si>
+    <t>Como María</t>
+  </si>
+  <si>
+    <t>Anagrama humano</t>
+  </si>
+  <si>
+    <t>maria;evangelio</t>
+  </si>
+  <si>
+    <t>Piratilla</t>
+  </si>
+  <si>
+    <t>Para actividad complementaria</t>
+  </si>
+  <si>
+    <t>Paz</t>
+  </si>
+  <si>
+    <t>Paloma y rama de olivo</t>
+  </si>
+  <si>
+    <t>Pajarita de papel</t>
+  </si>
+  <si>
+    <t>DIS-0056</t>
+  </si>
+  <si>
+    <t>DIS-0057</t>
+  </si>
+  <si>
+    <t>DIS-0058</t>
+  </si>
+  <si>
+    <t>DIS-0059</t>
+  </si>
+  <si>
+    <t>DIS-0060</t>
+  </si>
+  <si>
+    <t>DIS-0061</t>
+  </si>
+  <si>
+    <t>DIS-0062</t>
+  </si>
+  <si>
+    <t>Hey Bro (por)</t>
+  </si>
+  <si>
+    <t>Para bemaristbrother.com</t>
+  </si>
+  <si>
+    <t>Camina, Reza, Ama</t>
+  </si>
+  <si>
+    <t>Para formación Comunidad GVX</t>
+  </si>
+  <si>
+    <t>Hey Bro (esp)</t>
+  </si>
+  <si>
+    <t>Feliz Navidad I</t>
+  </si>
+  <si>
+    <t>Felicitación</t>
+  </si>
+  <si>
+    <t>GVX Verano 1988</t>
+  </si>
+  <si>
+    <t>Camiseta Tensar los vientos (frontal)</t>
+  </si>
+  <si>
+    <t>Diversos y Complementarios</t>
+  </si>
+  <si>
+    <t>Soy marista</t>
+  </si>
+  <si>
+    <t>Marcelino Champagnat</t>
+  </si>
+  <si>
+    <t>M Champagnat</t>
+  </si>
+  <si>
+    <t>champagnat;vocacional;hermitage</t>
+  </si>
+  <si>
+    <t>champagnat;infantil;violetas</t>
+  </si>
+  <si>
+    <t>champagnat</t>
+  </si>
+  <si>
+    <t>maria;violetas;paz</t>
+  </si>
+  <si>
+    <t>champagnat;vocacional</t>
+  </si>
+  <si>
+    <t>champagnat;infantil;hermitage</t>
+  </si>
+  <si>
+    <t>champagnat;hermitage</t>
+  </si>
+  <si>
+    <t>GVX;violetas</t>
+  </si>
+  <si>
+    <t>GVX;vocacional</t>
+  </si>
+  <si>
+    <t>violetas</t>
+  </si>
+  <si>
+    <t>deporte</t>
+  </si>
+  <si>
+    <t>maristas;hermitage</t>
+  </si>
+  <si>
+    <t>educacion;vocacional;violetas</t>
+  </si>
+  <si>
+    <t>social;educacion</t>
+  </si>
+  <si>
+    <t>champagnat;educacion</t>
+  </si>
+  <si>
+    <t>evangelio;educacion</t>
+  </si>
+  <si>
+    <t>hermitage</t>
+  </si>
+  <si>
+    <t>sin_fondo;firma</t>
+  </si>
+  <si>
+    <t>sticker;triptico</t>
+  </si>
+  <si>
+    <t>postal;rrss</t>
+  </si>
+  <si>
+    <t>ILU-0090</t>
+  </si>
+  <si>
+    <t>ILU-0091</t>
+  </si>
+  <si>
+    <t>ILU-0092</t>
+  </si>
+  <si>
+    <t>ILU-0093</t>
+  </si>
+  <si>
+    <t>ILU-0094</t>
+  </si>
+  <si>
+    <t>Sois la luz del mundo</t>
+  </si>
+  <si>
+    <t>Comedor de Fuenteheridos I</t>
+  </si>
+  <si>
+    <t>cartel;mural;textil</t>
+  </si>
+  <si>
+    <t>La Chispa</t>
+  </si>
+  <si>
+    <t>Comedor de Fuenteheridos II</t>
+  </si>
+  <si>
+    <t>Eucaristía II</t>
+  </si>
+  <si>
+    <t>Trigo y pan</t>
+  </si>
+  <si>
+    <t>Chispa</t>
+  </si>
+  <si>
+    <t>En el pesebre</t>
+  </si>
+  <si>
+    <t>Navidad</t>
+  </si>
+  <si>
+    <t>DIS-0063</t>
+  </si>
+  <si>
+    <t>DIS-0064</t>
+  </si>
+  <si>
+    <t>DIS-0065</t>
+  </si>
+  <si>
+    <t>DIS-0066</t>
+  </si>
+  <si>
+    <t>GVX Verano 2019 (GA-Marcha)</t>
+  </si>
+  <si>
+    <t>Camiseta GVX 2019 (ita)</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2017</t>
+  </si>
+  <si>
+    <t>Camiseta Pascua 2017 (frontal)</t>
+  </si>
+  <si>
+    <t>Dónde Vives?</t>
+  </si>
+  <si>
+    <t>Para convivencia Vocacional Marcha GVX</t>
+  </si>
+  <si>
+    <t>Arturo_MP_Luis_G</t>
+  </si>
+  <si>
+    <t>GVX 25 aniversario 2007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiseta GVX 2007 </t>
+  </si>
+  <si>
+    <t>GVX Verano 2018 Comunidad</t>
+  </si>
+  <si>
+    <t>maristas;educacion;social</t>
+  </si>
+  <si>
+    <t>educacion;social</t>
+  </si>
+  <si>
+    <t>maristas;social</t>
+  </si>
+  <si>
+    <t>paz;educacion;social</t>
+  </si>
+  <si>
+    <t>maria;evangelio;social</t>
+  </si>
+  <si>
+    <t>educacion;paz;social</t>
+  </si>
+  <si>
+    <t>GVX;evangelio;social</t>
+  </si>
+  <si>
+    <t>champagnat;vocacional;social</t>
+  </si>
+  <si>
+    <t>champagnat;social</t>
+  </si>
+  <si>
+    <t>champagnat;maristas;vocacional;social</t>
+  </si>
+  <si>
+    <t>vocacional;social</t>
+  </si>
+  <si>
+    <t>DIS-0067</t>
+  </si>
+  <si>
+    <t>DIS-0068</t>
+  </si>
+  <si>
+    <t>DIS-0069</t>
+  </si>
+  <si>
+    <t>GVX Verano 2023 (Bordado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polo GVX 2023 </t>
+  </si>
+  <si>
+    <t>Camiseta GMG-JMJ Lisboa (espalda)</t>
+  </si>
+  <si>
+    <t>GVX;maristas</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2024 (ita)</t>
+  </si>
+  <si>
+    <t>Maristas en la JMJ 2023 (esp-ita)</t>
+  </si>
+  <si>
+    <t>Scegliere. Vivere. Andare</t>
+  </si>
+  <si>
+    <t>GVX Pascua 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiseta GA. DA VIDA </t>
+  </si>
+  <si>
+    <t>ILU-0095</t>
+  </si>
+  <si>
+    <t>ILU-0096</t>
+  </si>
+  <si>
+    <t>La Chispa II</t>
+  </si>
+  <si>
+    <t>Luz. Presencia.</t>
+  </si>
+  <si>
+    <t>Be Light</t>
+  </si>
+  <si>
+    <t>Diseño para GVX</t>
+  </si>
+  <si>
+    <t>Marcha Toledo</t>
+  </si>
+  <si>
+    <t>Posible Logo</t>
+  </si>
+  <si>
+    <t>Camiseta Tanto va… 2023 (espalda)</t>
+  </si>
+  <si>
+    <t>Camiseta Sal a ser sal 2022 (logo frontal)</t>
+  </si>
+  <si>
+    <t>Logo frontal camiseta GVX 2023</t>
+  </si>
+  <si>
+    <t>sticker;colorear</t>
+  </si>
+  <si>
+    <t>RRSSmaristas</t>
+  </si>
+  <si>
     <t>maristas_brasil</t>
   </si>
   <si>
-    <t>maristas_huelva</t>
-  </si>
-  <si>
-    <t>rrss</t>
-  </si>
-  <si>
-    <t>usos</t>
-  </si>
-  <si>
-    <t>firma</t>
-  </si>
-  <si>
-    <t>postal</t>
-  </si>
-  <si>
-    <t>firma;minimalista</t>
-  </si>
-  <si>
-    <t>cartel</t>
-  </si>
-  <si>
-    <t>ILU-0020</t>
-  </si>
-  <si>
-    <t>Champagnat - GVX BN</t>
-  </si>
-  <si>
-    <t>DIS-0008</t>
-  </si>
-  <si>
-    <t>Centenario</t>
-  </si>
-  <si>
-    <t>Parte cartel 100 años ESP vectorizado</t>
-  </si>
-  <si>
-    <t>ILU-0021</t>
-  </si>
-  <si>
-    <t>ILU-0022</t>
-  </si>
-  <si>
-    <t>ILU-0023</t>
-  </si>
-  <si>
-    <t>Click Champagnat</t>
-  </si>
-  <si>
-    <t>San Marcelino playmobil</t>
-  </si>
-  <si>
-    <t>San Marcelino XXII</t>
-  </si>
-  <si>
-    <t>De imagen San Marcelino II - Brasil</t>
-  </si>
-  <si>
-    <t>color</t>
-  </si>
-  <si>
-    <t>RRSS</t>
-  </si>
-  <si>
-    <t>jarts</t>
-  </si>
-  <si>
-    <t>maristas</t>
-  </si>
-  <si>
-    <t>M. Champagnat</t>
-  </si>
-  <si>
-    <t>San Marcelino Champagnat BN</t>
-  </si>
-  <si>
-    <t>Champagnat Beatif.</t>
-  </si>
-  <si>
-    <t>ILU-0024</t>
-  </si>
-  <si>
-    <t>ILU-0025</t>
-  </si>
-  <si>
-    <t>ILU-0026</t>
-  </si>
-  <si>
-    <t>ILU-0027</t>
-  </si>
-  <si>
-    <t>ILU-0028</t>
-  </si>
-  <si>
-    <t>ILU-0029</t>
-  </si>
-  <si>
-    <t>ILU-0030</t>
-  </si>
-  <si>
-    <t>Nº Sª de Fourviere</t>
-  </si>
-  <si>
-    <t>Nuestra Señora de Fourviere</t>
-  </si>
-  <si>
-    <t>figura</t>
-  </si>
-  <si>
-    <t>María II</t>
-  </si>
-  <si>
-    <t>Maria Niña (I love Jesus)</t>
-  </si>
-  <si>
-    <t>María, Buena Madre I</t>
-  </si>
-  <si>
-    <t>Buena Madre B/N</t>
-  </si>
-  <si>
-    <t>Nuestra Buena Madre</t>
-  </si>
-  <si>
-    <t>Buena Madre FR</t>
-  </si>
-  <si>
-    <t>María III</t>
-  </si>
-  <si>
-    <t>A Jesús por María</t>
-  </si>
-  <si>
-    <t>María, Buena Madre II</t>
-  </si>
-  <si>
-    <t>Mi Buena Madre</t>
-  </si>
-  <si>
-    <t>María, Buena Madre III</t>
-  </si>
-  <si>
-    <t>María, Buena Madre</t>
-  </si>
-  <si>
-    <t>DIS-0009</t>
-  </si>
-  <si>
-    <t>DIS-0010</t>
-  </si>
-  <si>
-    <t>DIS-0011</t>
-  </si>
-  <si>
-    <t>La casa de María</t>
-  </si>
-  <si>
-    <t>Vector de mural (Badajoz)</t>
-  </si>
-  <si>
-    <t>Vector de mural B/N (Badajoz)</t>
-  </si>
-  <si>
-    <t>La casa de María B/N</t>
-  </si>
-  <si>
-    <t>maria</t>
-  </si>
-  <si>
-    <t>Moteros Maristas</t>
-  </si>
-  <si>
-    <t>Logo moteros maristas</t>
-  </si>
-  <si>
-    <t>logo</t>
-  </si>
-  <si>
-    <t>ILU-0031</t>
-  </si>
-  <si>
-    <t>ILU-0032</t>
-  </si>
-  <si>
-    <t>Magnificat</t>
-  </si>
-  <si>
-    <t>María e Isabel</t>
-  </si>
-  <si>
-    <t>María, Buena Madre IV</t>
-  </si>
-  <si>
-    <t>María, Madre</t>
-  </si>
-  <si>
-    <t>ILU-0033</t>
-  </si>
-  <si>
-    <t>3 Violetas</t>
-  </si>
-  <si>
-    <t>Humildad, Sencillez y Modestia</t>
-  </si>
-  <si>
-    <t>sin_fondo;logo</t>
-  </si>
-  <si>
-    <t>Arturo_MP</t>
-  </si>
-  <si>
-    <t>FMS</t>
-  </si>
-  <si>
-    <t>C_Towers</t>
-  </si>
-  <si>
-    <t>A_Gil</t>
-  </si>
-  <si>
-    <t>Goyo_D</t>
-  </si>
-  <si>
-    <t>cartel;postal</t>
-  </si>
-  <si>
-    <t>mural;rrss</t>
-  </si>
-  <si>
-    <t>ILU-0034</t>
-  </si>
-  <si>
-    <t>Marist-Art</t>
-  </si>
-  <si>
-    <t>DIS-0012</t>
-  </si>
-  <si>
-    <t>DIS-0013</t>
-  </si>
-  <si>
-    <t>DIS-0014</t>
-  </si>
-  <si>
-    <t>DIS-0015</t>
-  </si>
-  <si>
-    <t>DIS-0016</t>
-  </si>
-  <si>
-    <t>DIS-0017</t>
-  </si>
-  <si>
-    <t>DIS-0018</t>
-  </si>
-  <si>
-    <t>DIS-0019</t>
-  </si>
-  <si>
-    <t>DIS-0020</t>
-  </si>
-  <si>
-    <t>GVX Verano 2014</t>
-  </si>
-  <si>
-    <t>Camiseta Da Vida 2014</t>
-  </si>
-  <si>
-    <t>GVX Pascua 2015</t>
-  </si>
-  <si>
-    <t>Camiseta Pascua 2015</t>
-  </si>
-  <si>
-    <t>GVX Verano 2015</t>
-  </si>
-  <si>
-    <t>Camiseta de grupos 2015</t>
-  </si>
-  <si>
-    <t>GVX Pascua 2016</t>
-  </si>
-  <si>
-    <t>Camiseta Pascua 2016</t>
-  </si>
-  <si>
-    <t>GVX Verano 2016</t>
-  </si>
-  <si>
-    <t>Camiseta Da Vida 2018</t>
-  </si>
-  <si>
-    <t>GVX Pascua 2018</t>
-  </si>
-  <si>
-    <t>Camiseta Pascua 2018</t>
-  </si>
-  <si>
-    <t>GVX Verano 2025</t>
-  </si>
-  <si>
-    <t>Camisetas Ojos que ven… 2025 (espalda)</t>
-  </si>
-  <si>
-    <t>GVX Verano 2023</t>
-  </si>
-  <si>
-    <t>Camiseta Ser la Chispa… 2023 (espalda + logo delantero)</t>
-  </si>
-  <si>
-    <t>DIS-0021</t>
-  </si>
-  <si>
-    <t>DIS-0022</t>
-  </si>
-  <si>
-    <t>DIS-0023</t>
-  </si>
-  <si>
-    <t>ILU-0035</t>
-  </si>
-  <si>
-    <t>BRO mode</t>
-  </si>
-  <si>
-    <t>Marist Brother</t>
-  </si>
-  <si>
-    <t>maristas;vocacional</t>
-  </si>
-  <si>
-    <t>postal;rrss;sticker</t>
-  </si>
-  <si>
-    <t>sticker</t>
-  </si>
-  <si>
-    <t>sticker;taza</t>
-  </si>
-  <si>
-    <t>Estoy a la puerta y llamo</t>
-  </si>
-  <si>
-    <t>cartel;rrss</t>
-  </si>
-  <si>
-    <t>Convivencia vocacional GVX 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cree en ti </t>
-  </si>
-  <si>
-    <t>Convivencia vocacional GVX 2024</t>
-  </si>
-  <si>
-    <t>Maristas</t>
-  </si>
-  <si>
-    <t>Desde 1817</t>
-  </si>
-  <si>
-    <t>maristas;violetas</t>
-  </si>
-  <si>
-    <t>textil</t>
-  </si>
-  <si>
-    <t>ILU-0036</t>
-  </si>
-  <si>
-    <t>ILU-0037</t>
-  </si>
-  <si>
-    <t>ILU-0038</t>
-  </si>
-  <si>
-    <t>ILU-0039</t>
-  </si>
-  <si>
-    <t>ILU-0040</t>
-  </si>
-  <si>
-    <t>La Oveja Encontrada</t>
-  </si>
-  <si>
-    <t>#Soy la 100</t>
-  </si>
-  <si>
-    <t>evangelio;violetas</t>
-  </si>
-  <si>
-    <t>sticker;rrss</t>
-  </si>
-  <si>
-    <t>Titulada</t>
-  </si>
-  <si>
-    <t>Graduación</t>
-  </si>
-  <si>
-    <t>sticker;cartel</t>
-  </si>
-  <si>
-    <t>Atienden</t>
-  </si>
-  <si>
-    <t>En clase</t>
-  </si>
-  <si>
-    <t>maristas;educacion</t>
-  </si>
-  <si>
-    <t>educacion</t>
-  </si>
-  <si>
-    <t>Con corazón</t>
-  </si>
-  <si>
-    <t>Saltando</t>
-  </si>
-  <si>
-    <t>logo;sin_fondo</t>
-  </si>
-  <si>
-    <t>educacion;evangelio</t>
-  </si>
-  <si>
-    <t>Estudiando</t>
-  </si>
-  <si>
-    <t>En clase II</t>
-  </si>
-  <si>
-    <t>ILU-0041</t>
-  </si>
-  <si>
-    <t>ILU-0042</t>
-  </si>
-  <si>
-    <t>ILU-0043</t>
-  </si>
-  <si>
-    <t>ILU-0044</t>
-  </si>
-  <si>
-    <t>3 Violetas II</t>
-  </si>
-  <si>
-    <t>3 Violetas III BN</t>
-  </si>
-  <si>
-    <t>3 Violetas III color</t>
-  </si>
-  <si>
-    <t>Nuestras 3 violetas</t>
-  </si>
-  <si>
-    <t>Violetas Marist</t>
-  </si>
-  <si>
-    <t>Dos combinaciones bordado</t>
-  </si>
-  <si>
-    <t>PxM_maristas_chile</t>
-  </si>
-  <si>
-    <t>C_Towers_jarts</t>
-  </si>
-  <si>
-    <t>Arturo_MP_C_Towers</t>
-  </si>
-  <si>
-    <t>Arturo_MP_Goyo_D</t>
-  </si>
-  <si>
-    <t>Arturo_MP_jarts</t>
-  </si>
-  <si>
-    <t>DIS-0024</t>
-  </si>
-  <si>
-    <t>DIS-0025</t>
-  </si>
-  <si>
-    <t>DIS-0026</t>
-  </si>
-  <si>
-    <t>DIS-0027</t>
-  </si>
-  <si>
-    <t>DIS-0028</t>
-  </si>
-  <si>
-    <t>DIS-0029</t>
-  </si>
-  <si>
-    <t>GVX Verano 2019</t>
-  </si>
-  <si>
-    <t>Camiseta Comunidad 2019 (espalda)</t>
-  </si>
-  <si>
-    <t>GVX Verano 2021</t>
-  </si>
-  <si>
-    <t>GVX Pascua 2022</t>
-  </si>
-  <si>
-    <t>Camiseta Sal a ser sal 2022 (frontal)</t>
-  </si>
-  <si>
-    <t>frase;logo;sin_fondo</t>
-  </si>
-  <si>
-    <t>GVX Pascua 2023</t>
-  </si>
-  <si>
-    <t>GVX Sticker Pascua 2025</t>
-  </si>
-  <si>
-    <t>Portavela Pascua 2025</t>
-  </si>
-  <si>
-    <t>GVX Verano 2022</t>
-  </si>
-  <si>
-    <t>Camiseta Chispa Da Vida 2022</t>
-  </si>
-  <si>
-    <t>Camiseta HERE WE ARE 2021 (frontal)</t>
-  </si>
-  <si>
-    <t>DIS-0030</t>
-  </si>
-  <si>
-    <t>GVX Sticker 2024</t>
-  </si>
-  <si>
-    <t>DIS-0031</t>
-  </si>
-  <si>
-    <t>Camiseta Da Vida 2025 (espalda)</t>
-  </si>
-  <si>
-    <t>Sticker G de Grupos</t>
-  </si>
-  <si>
-    <t>Camiseta a better World 2016</t>
-  </si>
-  <si>
-    <t>DIS-0032</t>
-  </si>
-  <si>
-    <t>Camiseta GVX Sal</t>
-  </si>
-  <si>
-    <t>GVX Sevilla 2007</t>
-  </si>
-  <si>
-    <t>ILU-0045</t>
-  </si>
-  <si>
-    <t>Un mismo agua</t>
-  </si>
-  <si>
-    <t>ILU-0046</t>
-  </si>
-  <si>
-    <t>Vayamos al Fondo</t>
-  </si>
-  <si>
-    <t>ILU-0047</t>
-  </si>
-  <si>
-    <t>ILU-0048</t>
-  </si>
-  <si>
-    <t>ILU-0049</t>
-  </si>
-  <si>
-    <t>ILU-0050</t>
-  </si>
-  <si>
-    <t>ILU-0051</t>
-  </si>
-  <si>
-    <t>ILU-0052</t>
-  </si>
-  <si>
-    <t>ILU-0053</t>
-  </si>
-  <si>
-    <t>ILU-0054</t>
-  </si>
-  <si>
-    <t>ILU-0055</t>
-  </si>
-  <si>
-    <t>ILU-0056</t>
-  </si>
-  <si>
-    <t>Busco estrella</t>
-  </si>
-  <si>
-    <t>Viaje a Belén Navidad</t>
-  </si>
-  <si>
-    <t>Vocacción</t>
-  </si>
-  <si>
-    <t>No haremos 3 tiendas</t>
-  </si>
-  <si>
-    <t>vocacional</t>
-  </si>
-  <si>
-    <t>Cruz Espíritu I</t>
-  </si>
-  <si>
-    <t>Cruz Espíritu II</t>
-  </si>
-  <si>
-    <t>Confirmación Sevilla</t>
-  </si>
-  <si>
-    <t>Confirmación Sevilla II</t>
-  </si>
-  <si>
-    <t>GVX;evangelio</t>
-  </si>
-  <si>
-    <t>sticker;taza;rrss</t>
-  </si>
-  <si>
-    <t>Para Asamblea Mediterránea</t>
-  </si>
-  <si>
-    <t>Arturo_MP_ ProvMediterranea</t>
-  </si>
-  <si>
-    <t>Arturo_MP_ProvMediterranea</t>
-  </si>
-  <si>
-    <t>Arturo_MP_ Jorge_MR_ProvMediterranea</t>
-  </si>
-  <si>
-    <t>Arturo_MP_Jorge_MR_ProvMediterranea</t>
-  </si>
-  <si>
-    <t>Arturo_MP_Fer_OR_ProvMediterranea</t>
-  </si>
-  <si>
-    <t>Arturo_MP_Arturo_MR_ProvMediterranea</t>
-  </si>
-  <si>
-    <t>Cada Navidad</t>
-  </si>
-  <si>
-    <t>Para felicitación Colegio Sevilla</t>
-  </si>
-  <si>
-    <t>maristas;evangelio;violetas</t>
-  </si>
-  <si>
-    <t>Panes y peces</t>
-  </si>
-  <si>
-    <t>Ilustración documentos</t>
-  </si>
-  <si>
-    <t>evangelio</t>
-  </si>
-  <si>
-    <t>maristas;evangelio</t>
-  </si>
-  <si>
-    <t>sticker;cartel;postal</t>
-  </si>
-  <si>
-    <t>Sal y Luz I - Evangelío</t>
-  </si>
-  <si>
-    <t>Marist Runners</t>
-  </si>
-  <si>
-    <t>sticker;textil</t>
-  </si>
-  <si>
-    <t>Camiseta carrera solidaria</t>
-  </si>
-  <si>
-    <t>Un corazón, una misión</t>
-  </si>
-  <si>
-    <t>Preparación Capítulo General</t>
-  </si>
-  <si>
-    <t>Ilustraciones maristas</t>
-  </si>
-  <si>
-    <t>Firma de Champagnat</t>
-  </si>
-  <si>
-    <t>En Tríptico Vocacional</t>
-  </si>
-  <si>
-    <t>Join the Revolution I</t>
-  </si>
-  <si>
-    <t>Join the Revolution II</t>
-  </si>
-  <si>
-    <t>Si hiciéramos uno…</t>
-  </si>
-  <si>
-    <t>Para Escuela de Tiempo Libre</t>
-  </si>
-  <si>
-    <t>DIS-0033</t>
-  </si>
-  <si>
-    <t>DIS-0034</t>
-  </si>
-  <si>
-    <t>DIS-0035</t>
-  </si>
-  <si>
-    <t>DIS-0036</t>
-  </si>
-  <si>
-    <t>DIS-0037</t>
-  </si>
-  <si>
-    <t>DIS-0038</t>
-  </si>
-  <si>
-    <t>DIS-0039</t>
-  </si>
-  <si>
-    <t>DIS-0040</t>
-  </si>
-  <si>
-    <t>DIS-0041</t>
-  </si>
-  <si>
-    <t>DIS-0042</t>
-  </si>
-  <si>
-    <t>DIS-0043</t>
-  </si>
-  <si>
-    <t>DIS-0044</t>
-  </si>
-  <si>
-    <t>DIS-0045</t>
-  </si>
-  <si>
-    <t>DIS-0046</t>
-  </si>
-  <si>
-    <t>DIS-0047</t>
-  </si>
-  <si>
-    <t>VI Jornadas Educadores Maristas</t>
-  </si>
-  <si>
-    <t>Eucaristía</t>
-  </si>
-  <si>
-    <t>Para Primera Eucaristía Sevilla 2017</t>
-  </si>
-  <si>
-    <t>evangelio;GVX</t>
-  </si>
-  <si>
-    <t>IV Jornadas Educadores Maristas</t>
-  </si>
-  <si>
-    <t>El mundo, la mejor cocina</t>
-  </si>
-  <si>
-    <t>Para encuentro Delegados de Pastoral (delantal)</t>
-  </si>
-  <si>
-    <t>¿Qué tal tu amor?</t>
-  </si>
-  <si>
-    <t>Viñeta</t>
-  </si>
-  <si>
-    <t>Hagamos de la casa hogar</t>
-  </si>
-  <si>
-    <t>maristas;educacion;evangelio</t>
-  </si>
-  <si>
-    <t>Para tiempo Cuaresma I Mediterránea (esp)</t>
-  </si>
-  <si>
-    <t>Constancia</t>
-  </si>
-  <si>
-    <t>Para CB Maristas Sevilla</t>
-  </si>
-  <si>
-    <t>Arturo_MP_Arturo_MR</t>
-  </si>
-  <si>
-    <t>maristas;deporte</t>
-  </si>
-  <si>
-    <t>La Valla</t>
-  </si>
-  <si>
-    <t>Cuadro mesa de La Valla</t>
-  </si>
-  <si>
-    <t>Faros de Esperanza</t>
-  </si>
-  <si>
-    <t>Para Capítulo Prov Mediterránea</t>
-  </si>
-  <si>
-    <t>…una casa acogliente</t>
-  </si>
-  <si>
-    <t>Para tiempo Cuaresma I Mediterránea (ita)</t>
-  </si>
-  <si>
-    <t>The Home of Mary</t>
-  </si>
-  <si>
-    <t>Camiseta campaña Sevilla 2015</t>
-  </si>
-  <si>
-    <t>Arturo_MP_maristas_USA</t>
-  </si>
-  <si>
-    <t>maristas;maria</t>
-  </si>
-  <si>
-    <t>Se escucha un latido</t>
-  </si>
-  <si>
-    <t>Para tiempo Adviento I Mediterránea (esp)</t>
-  </si>
-  <si>
-    <t>Arturo_MP_ProvMediterranea_Fer_OR</t>
-  </si>
-  <si>
-    <t>Somos las manos de Dios</t>
-  </si>
-  <si>
-    <t>Para tiempo Cuaresma II Mediterránea (esp)</t>
-  </si>
-  <si>
-    <t>Siamo le mani di Dio</t>
-  </si>
-  <si>
-    <t>Para tiempo Cuaresma II Mediterránea (ita)</t>
-  </si>
-  <si>
-    <t>CB Maristas (anterior logo)</t>
-  </si>
-  <si>
-    <t>Para taza CB Maristas Sevilla</t>
-  </si>
-  <si>
-    <t>taza</t>
-  </si>
-  <si>
-    <t>GVX</t>
-  </si>
-  <si>
-    <t>DIS-0048</t>
-  </si>
-  <si>
-    <t>DIS-0049</t>
-  </si>
-  <si>
-    <t>DIS-0050</t>
-  </si>
-  <si>
-    <t>DIS-0051</t>
-  </si>
-  <si>
-    <t>DIS-0052</t>
-  </si>
-  <si>
-    <t>DIS-0053</t>
-  </si>
-  <si>
-    <t>Bordado Etapas GVX</t>
-  </si>
-  <si>
-    <t>Logo GVX local</t>
-  </si>
-  <si>
-    <t>textil;sticker</t>
-  </si>
-  <si>
-    <t>GVX Pascua 2024</t>
-  </si>
-  <si>
-    <t>Camiseta Elegir Vivir Ir (espalda)</t>
-  </si>
-  <si>
-    <t>GVX Verano 2017</t>
-  </si>
-  <si>
-    <t>Volver al origen para empezar de nuevo</t>
-  </si>
-  <si>
-    <t>C_Towers_ProvMediterranea</t>
-  </si>
-  <si>
-    <t>GVX Verano 2018</t>
-  </si>
-  <si>
-    <t>Arturo_MP_Texeira_ProvMediterranea</t>
-  </si>
-  <si>
-    <t>GVX;champagnat;violetas</t>
-  </si>
-  <si>
-    <t>Semana Vocacional</t>
-  </si>
-  <si>
-    <t>Para semana Vocacional Sevilla</t>
-  </si>
-  <si>
-    <t>Posibles camisetas #escuchaaunniño</t>
-  </si>
-  <si>
-    <t>ILU-0057</t>
-  </si>
-  <si>
-    <t>ILU-0058</t>
-  </si>
-  <si>
-    <t>ILU-0059</t>
-  </si>
-  <si>
-    <t>ILU-0060</t>
-  </si>
-  <si>
-    <t>ILU-0061</t>
-  </si>
-  <si>
-    <t>ILU-0062</t>
-  </si>
-  <si>
-    <t>ILU-0063</t>
-  </si>
-  <si>
-    <t>ILU-0064</t>
-  </si>
-  <si>
-    <t>ILU-0065</t>
-  </si>
-  <si>
-    <t>ILU-0066</t>
-  </si>
-  <si>
-    <t>ILU-0067</t>
-  </si>
-  <si>
-    <t>ILU-0068</t>
-  </si>
-  <si>
-    <t>ILU-0069</t>
-  </si>
-  <si>
-    <t>ILU-0070</t>
-  </si>
-  <si>
-    <t>ILU-0071</t>
-  </si>
-  <si>
-    <t>JUMP</t>
-  </si>
-  <si>
-    <t>Jump Walk Dream</t>
-  </si>
-  <si>
-    <t>ProvMediterranea</t>
-  </si>
-  <si>
-    <t>Champagnat 2000+</t>
-  </si>
-  <si>
-    <t>Llamadas</t>
-  </si>
-  <si>
-    <t>Silueta Champagnat acuarela</t>
-  </si>
-  <si>
-    <t>San Marcelino Champagnat</t>
-  </si>
-  <si>
-    <t>J_Ramos</t>
-  </si>
-  <si>
-    <t>maristas;champagnat;violetas</t>
-  </si>
-  <si>
-    <t>BuenaJente</t>
-  </si>
-  <si>
-    <t>Jesús, el BuenaJente</t>
-  </si>
-  <si>
-    <t>mural;cartel;textil</t>
-  </si>
-  <si>
-    <t>Atardece</t>
-  </si>
-  <si>
-    <t>Quédate con nosotros (de GVX Pascua 2026)</t>
-  </si>
-  <si>
-    <t>Qué te han contado los niños? (ita)</t>
-  </si>
-  <si>
-    <t>Da Vida</t>
-  </si>
-  <si>
-    <t>De GVX Verano 22</t>
-  </si>
-  <si>
-    <t>Futuro</t>
-  </si>
-  <si>
-    <t>Para Semana Vocacional</t>
-  </si>
-  <si>
-    <t>Arturo_MP_J_Ramos</t>
-  </si>
-  <si>
-    <t>Gente normal (esp)</t>
-  </si>
-  <si>
-    <t>Sencillez</t>
-  </si>
-  <si>
-    <t>Violetas Marist II</t>
-  </si>
-  <si>
-    <t>Los pequeños grandes detalles</t>
-  </si>
-  <si>
-    <t>Voluntariado marista</t>
-  </si>
-  <si>
-    <t>Para formación RRHH Mediterránea</t>
-  </si>
-  <si>
-    <t>Protección de la Infancia</t>
-  </si>
-  <si>
-    <t>Para formación Mediterránea</t>
-  </si>
-  <si>
-    <t>sticker;postal</t>
-  </si>
-  <si>
-    <t>Inspira</t>
-  </si>
-  <si>
-    <t>Ilustrar Interioridad</t>
-  </si>
-  <si>
-    <t>Como Dios</t>
-  </si>
-  <si>
-    <t>Para vivir como Dios,ama, perdona y…</t>
-  </si>
-  <si>
-    <t>ChicaCora</t>
-  </si>
-  <si>
-    <t>Ama (os, te, les)</t>
-  </si>
-  <si>
-    <t>#Soy la 100 II</t>
-  </si>
-  <si>
-    <t>Y salió a buscarla</t>
-  </si>
-  <si>
-    <t>ILU-0072</t>
-  </si>
-  <si>
-    <t>ILU-0073</t>
-  </si>
-  <si>
-    <t>ILU-0074</t>
-  </si>
-  <si>
-    <t>ILU-0075</t>
-  </si>
-  <si>
-    <t>ILU-0076</t>
-  </si>
-  <si>
-    <t>Atardece II</t>
-  </si>
-  <si>
-    <t>#accesoeducativo Todos con cole</t>
-  </si>
-  <si>
-    <t>Buena Madre II</t>
-  </si>
-  <si>
-    <t>Silueta María, Buena Madre</t>
-  </si>
-  <si>
-    <t>Anagrama María</t>
-  </si>
-  <si>
-    <t>Basado en antiguo anagrama edificio</t>
-  </si>
-  <si>
-    <t>Quien no ama…</t>
-  </si>
-  <si>
-    <t>Para educar es preciso amar</t>
-  </si>
-  <si>
-    <t>Escuchas?</t>
-  </si>
-  <si>
-    <t>Hasta en la brisa</t>
-  </si>
-  <si>
-    <t>evangelio;vocacional</t>
-  </si>
-  <si>
-    <t>DIS-0054</t>
-  </si>
-  <si>
-    <t>DIS-0055</t>
-  </si>
-  <si>
-    <t>Ceda el paso y sígalos</t>
-  </si>
-  <si>
-    <t>Para Viaje a Belén Maristas Jaén</t>
-  </si>
-  <si>
-    <t>Para convivencia Marcha GVX</t>
-  </si>
-  <si>
-    <t>Para convivencia Marcha GVX II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuestras 3 violetas </t>
-  </si>
-  <si>
-    <t>Change &lt; &gt; Chance</t>
-  </si>
-  <si>
-    <t>Cartel 2025 Mediterránea</t>
-  </si>
-  <si>
-    <t>Cartel 2022 Mediterránea</t>
-  </si>
-  <si>
-    <t>Recordando al Hno Boni FQ</t>
-  </si>
-  <si>
-    <t>Excusas yo?</t>
-  </si>
-  <si>
-    <t>maria;violetas</t>
-  </si>
-  <si>
-    <t>maria;paz</t>
-  </si>
-  <si>
-    <t>sin_fondo;minimalista</t>
-  </si>
-  <si>
-    <t>ILU-0077</t>
-  </si>
-  <si>
-    <t>ILU-0078</t>
-  </si>
-  <si>
-    <t>ILU-0079</t>
-  </si>
-  <si>
-    <t>ILU-0080</t>
-  </si>
-  <si>
-    <t>Tras sus pasos</t>
-  </si>
-  <si>
-    <t>Seguimiento</t>
-  </si>
-  <si>
-    <t>Mi primera Eucaristía</t>
-  </si>
-  <si>
-    <t>evangelio;paz;violetas</t>
-  </si>
-  <si>
-    <t>Recordatorio</t>
-  </si>
-  <si>
-    <t>R-Evolution</t>
-  </si>
-  <si>
-    <t>La revolución de la Sencillez</t>
-  </si>
-  <si>
-    <t>Orienta 2</t>
-  </si>
-  <si>
-    <t>Orientación profesional y vocacional</t>
-  </si>
-  <si>
-    <t>educacion;vocacional</t>
-  </si>
-  <si>
-    <t>Arturo_MP_Jose_MR_C_Towers</t>
-  </si>
-  <si>
-    <t>ILU-0081</t>
-  </si>
-  <si>
-    <t>ILU-0082</t>
-  </si>
-  <si>
-    <t>ILU-0083</t>
-  </si>
-  <si>
-    <t>ILU-0084</t>
-  </si>
-  <si>
-    <t>ILU-0085</t>
-  </si>
-  <si>
-    <t>ILU-0086</t>
-  </si>
-  <si>
-    <t>ILU-0087</t>
-  </si>
-  <si>
-    <t>ILU-0088</t>
-  </si>
-  <si>
-    <t>ILU-0089</t>
-  </si>
-  <si>
-    <t>Barco de papel</t>
-  </si>
-  <si>
-    <t>educacion;maria</t>
-  </si>
-  <si>
-    <t>Estrella de papel</t>
-  </si>
-  <si>
-    <t>Parte cartel 'Cambia' (MRE)</t>
-  </si>
-  <si>
-    <t>L´Hermitage</t>
-  </si>
-  <si>
-    <t>Silueta edificio actual NS L´Hermitage</t>
-  </si>
-  <si>
-    <t>Para orientación profesional y vocacional</t>
-  </si>
-  <si>
-    <t>Arturo_MP_RRSS</t>
-  </si>
-  <si>
-    <t>Elegir y compartir</t>
-  </si>
-  <si>
-    <t>Diálogo</t>
-  </si>
-  <si>
-    <t>No-Violencia</t>
-  </si>
-  <si>
-    <t>Como María</t>
-  </si>
-  <si>
-    <t>Anagrama humano</t>
-  </si>
-  <si>
-    <t>maria;evangelio</t>
-  </si>
-  <si>
-    <t>Piratilla</t>
-  </si>
-  <si>
-    <t>Para actividad complementaria</t>
-  </si>
-  <si>
-    <t>Paz</t>
-  </si>
-  <si>
-    <t>Paloma y rama de olivo</t>
-  </si>
-  <si>
-    <t>Pajarita de papel</t>
-  </si>
-  <si>
-    <t>DIS-0056</t>
-  </si>
-  <si>
-    <t>DIS-0057</t>
-  </si>
-  <si>
-    <t>DIS-0058</t>
-  </si>
-  <si>
-    <t>DIS-0059</t>
-  </si>
-  <si>
-    <t>DIS-0060</t>
-  </si>
-  <si>
-    <t>DIS-0061</t>
-  </si>
-  <si>
-    <t>DIS-0062</t>
-  </si>
-  <si>
-    <t>Hey Bro (por)</t>
-  </si>
-  <si>
-    <t>Para bemaristbrother.com</t>
-  </si>
-  <si>
-    <t>Camina, Reza, Ama</t>
-  </si>
-  <si>
-    <t>Para formación Comunidad GVX</t>
-  </si>
-  <si>
-    <t>Hey Bro (esp)</t>
-  </si>
-  <si>
-    <t>Feliz Navidad I</t>
-  </si>
-  <si>
-    <t>Felicitación</t>
-  </si>
-  <si>
-    <t>GVX Verano 1988</t>
-  </si>
-  <si>
-    <t>Camiseta Tensar los vientos (frontal)</t>
-  </si>
-  <si>
-    <t>Arturo_MP_A_Arroyo</t>
-  </si>
-  <si>
-    <t>Diversos y Complementarios</t>
-  </si>
-  <si>
-    <t>Soy marista</t>
-  </si>
-  <si>
-    <t>Marcelino Champagnat</t>
-  </si>
-  <si>
-    <t>M Champagnat</t>
-  </si>
-  <si>
-    <t>champagnat;vocacional;hermitage</t>
-  </si>
-  <si>
-    <t>champagnat;infantil;violetas</t>
-  </si>
-  <si>
-    <t>champagnat</t>
-  </si>
-  <si>
-    <t>maria;violetas;paz</t>
-  </si>
-  <si>
-    <t>champagnat;vocacional</t>
-  </si>
-  <si>
-    <t>champagnat;infantil;hermitage</t>
-  </si>
-  <si>
-    <t>champagnat;hermitage</t>
-  </si>
-  <si>
-    <t>GVX;violetas</t>
-  </si>
-  <si>
-    <t>GVX;vocacional</t>
-  </si>
-  <si>
-    <t>violetas</t>
-  </si>
-  <si>
-    <t>deporte</t>
-  </si>
-  <si>
-    <t>maristas;hermitage</t>
-  </si>
-  <si>
-    <t>educacion;vocacional;violetas</t>
-  </si>
-  <si>
-    <t>social;educacion</t>
-  </si>
-  <si>
-    <t>champagnat;educacion</t>
-  </si>
-  <si>
-    <t>evangelio;educacion</t>
-  </si>
-  <si>
-    <t>hermitage</t>
-  </si>
-  <si>
-    <t>sin_fondo;firma</t>
-  </si>
-  <si>
-    <t>sticker;triptico</t>
-  </si>
-  <si>
-    <t>postal;rrss</t>
-  </si>
-  <si>
-    <t>ILU-0090</t>
-  </si>
-  <si>
-    <t>ILU-0091</t>
-  </si>
-  <si>
-    <t>ILU-0092</t>
-  </si>
-  <si>
-    <t>ILU-0093</t>
-  </si>
-  <si>
-    <t>ILU-0094</t>
-  </si>
-  <si>
-    <t>Sois la luz del mundo</t>
-  </si>
-  <si>
-    <t>Comedor de Fuenteheridos I</t>
-  </si>
-  <si>
-    <t>cartel;mural;textil</t>
-  </si>
-  <si>
-    <t>La Chispa</t>
-  </si>
-  <si>
-    <t>Comedor de Fuenteheridos II</t>
-  </si>
-  <si>
-    <t>Eucaristía II</t>
-  </si>
-  <si>
-    <t>Trigo y pan</t>
-  </si>
-  <si>
-    <t>Chispa</t>
-  </si>
-  <si>
-    <t>Para frontal camiseta GVX 2023</t>
-  </si>
-  <si>
-    <t>En el pesebre</t>
-  </si>
-  <si>
-    <t>Navidad</t>
-  </si>
-  <si>
-    <t>DIS-0063</t>
-  </si>
-  <si>
-    <t>DIS-0064</t>
-  </si>
-  <si>
-    <t>DIS-0065</t>
-  </si>
-  <si>
-    <t>DIS-0066</t>
-  </si>
-  <si>
-    <t>GVX Verano 2019 (GA-Marcha)</t>
-  </si>
-  <si>
-    <t>Camiseta GVX 2019 (ita)</t>
-  </si>
-  <si>
-    <t>GVX Pascua 2017</t>
-  </si>
-  <si>
-    <t>Camiseta Pascua 2017 (frontal)</t>
-  </si>
-  <si>
-    <t>Dónde Vives?</t>
-  </si>
-  <si>
-    <t>Para convivencia Vocacional Marcha GVX</t>
-  </si>
-  <si>
-    <t>Arturo_MP_Luis_G</t>
-  </si>
-  <si>
-    <t>GVX 25 aniversario 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camiseta GVX 2007 </t>
-  </si>
-  <si>
-    <t>Camiseta Tanto va… 2023 (frontal)</t>
-  </si>
-  <si>
-    <t>GVX Verano 2018 Comunidad</t>
-  </si>
-  <si>
-    <t>maristas;educacion;social</t>
-  </si>
-  <si>
-    <t>educacion;social</t>
-  </si>
-  <si>
-    <t>maristas;social</t>
-  </si>
-  <si>
-    <t>paz;educacion;social</t>
-  </si>
-  <si>
-    <t>maria;evangelio;social</t>
-  </si>
-  <si>
-    <t>educacion;paz;social</t>
-  </si>
-  <si>
-    <t>GVX;evangelio;social</t>
-  </si>
-  <si>
-    <t>champagnat;vocacional;social</t>
-  </si>
-  <si>
-    <t>champagnat;social</t>
-  </si>
-  <si>
-    <t>champagnat;maristas;vocacional;social</t>
-  </si>
-  <si>
-    <t>vocacional;social</t>
-  </si>
-  <si>
-    <t>DIS-0067</t>
-  </si>
-  <si>
-    <t>DIS-0068</t>
-  </si>
-  <si>
-    <t>DIS-0069</t>
-  </si>
-  <si>
-    <t>GVX Verano 2023 (Bordado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polo GVX 2023 </t>
-  </si>
-  <si>
-    <t>Camiseta GMG-JMJ Lisboa (espalda)</t>
-  </si>
-  <si>
-    <t>GVX;maristas</t>
-  </si>
-  <si>
-    <t>GVX Pascua 2024 (ita)</t>
-  </si>
-  <si>
-    <t>Maristas en la JMJ 2023 (esp-ita)</t>
-  </si>
-  <si>
-    <t>Scegliere. Vivere. Andare</t>
-  </si>
-  <si>
-    <t>GVX Pascua 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camiseta GA. DA VIDA </t>
-  </si>
-  <si>
-    <t>ILU-0095</t>
-  </si>
-  <si>
-    <t>ILU-0096</t>
-  </si>
-  <si>
-    <t>La Chispa II</t>
-  </si>
-  <si>
-    <t>Luz. Presencia.</t>
-  </si>
-  <si>
-    <t>Be Light</t>
-  </si>
-  <si>
-    <t>Diseño para GVX</t>
-  </si>
-  <si>
-    <t>Marcha Toledo</t>
-  </si>
-  <si>
-    <t>Posible Logo</t>
+    <t>A_Arroyo</t>
+  </si>
+  <si>
+    <t>Be Marist Brother punto com</t>
+  </si>
+  <si>
+    <t>DIS-0070</t>
+  </si>
+  <si>
+    <t>DIS-0071</t>
+  </si>
+  <si>
+    <t>DIS-0072</t>
+  </si>
+  <si>
+    <t>DIS-0073</t>
+  </si>
+  <si>
+    <t>Choose Marist Brothers</t>
+  </si>
+  <si>
+    <t>Para sudadera Prov_Mediterranea</t>
+  </si>
+  <si>
+    <t>Hoy puede ser…</t>
+  </si>
+  <si>
+    <t>Wonderfulismo realista</t>
+  </si>
+  <si>
+    <t>Runners Maristas</t>
+  </si>
+  <si>
+    <t>Para camiseta deportiva Sevilla</t>
+  </si>
+  <si>
+    <t>Fundación Marcelino Champagnat Huelva</t>
+  </si>
+  <si>
+    <t>20 años de Nuevo Horizonte, 1994</t>
+  </si>
+  <si>
+    <t>textil;postal</t>
+  </si>
+  <si>
+    <t>ILU-0100</t>
+  </si>
+  <si>
+    <t>ILU-0097</t>
+  </si>
+  <si>
+    <t>ILU-0098</t>
+  </si>
+  <si>
+    <t>ILU-0099</t>
+  </si>
+  <si>
+    <t>ILU-0101</t>
+  </si>
+  <si>
+    <t>De dibujos Goyo D</t>
+  </si>
+  <si>
+    <t>Nuevos educadores</t>
+  </si>
+  <si>
+    <t>Aprendizaje y Servicio</t>
+  </si>
+  <si>
+    <t>GoOD People</t>
+  </si>
+  <si>
+    <t>sticker;postal;taza</t>
+  </si>
+  <si>
+    <t>textil;sticker;taza</t>
+  </si>
+  <si>
+    <t>Nueva versión de camiseta GVX Sevilla 1993</t>
+  </si>
+  <si>
+    <t>Mi Buena Madre (esp)</t>
+  </si>
+  <si>
+    <t>Nuestro recurso ordinario</t>
   </si>
 </sst>
 </file>
@@ -2293,11 +2377,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N166"/>
+  <dimension ref="A1:N175"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="42.1640625" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" customWidth="1"/>
     <col min="5" max="5" width="7.83203125" customWidth="1"/>
     <col min="6" max="6" width="9.5" customWidth="1"/>
@@ -2336,10 +2420,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
@@ -2356,10 +2440,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D2" t="s">
         <v>54</v>
@@ -2371,16 +2455,16 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -2403,7 +2487,7 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D3" t="s">
         <v>54</v>
@@ -2415,16 +2499,16 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H3" t="s">
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="J3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K3" t="s">
         <v>56</v>
@@ -2444,7 +2528,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C4" t="s">
         <v>86</v>
@@ -2459,7 +2543,7 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H4" t="s">
         <v>28</v>
@@ -2468,7 +2552,7 @@
         <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K4" t="s">
         <v>55</v>
@@ -2488,7 +2572,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
         <v>87</v>
@@ -2503,16 +2587,13 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H5" t="s">
         <v>28</v>
       </c>
-      <c r="I5" t="s">
-        <v>60</v>
-      </c>
       <c r="J5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K5" t="s">
         <v>55</v>
@@ -2532,7 +2613,7 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
         <v>88</v>
@@ -2547,13 +2628,13 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H6" t="s">
         <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s">
         <v>57</v>
@@ -2588,7 +2669,7 @@
         <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H7" t="s">
         <v>59</v>
@@ -2617,7 +2698,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -2638,7 +2719,7 @@
         <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="K8" t="s">
         <v>55</v>
@@ -2658,7 +2739,7 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
         <v>89</v>
@@ -2673,7 +2754,7 @@
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H9" t="s">
         <v>28</v>
@@ -2682,7 +2763,7 @@
         <v>60</v>
       </c>
       <c r="J9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K9" t="s">
         <v>57</v>
@@ -2702,7 +2783,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C10" t="s">
         <v>90</v>
@@ -2717,7 +2798,7 @@
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H10" t="s">
         <v>28</v>
@@ -2726,7 +2807,7 @@
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K10" t="s">
         <v>55</v>
@@ -2746,7 +2827,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
@@ -2761,16 +2842,16 @@
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H11" t="s">
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K11" t="s">
         <v>55</v>
@@ -2790,7 +2871,7 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C12" t="s">
         <v>92</v>
@@ -2805,7 +2886,7 @@
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H12" t="s">
         <v>28</v>
@@ -2814,7 +2895,7 @@
         <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K12" t="s">
         <v>55</v>
@@ -2834,7 +2915,7 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C13" t="s">
         <v>93</v>
@@ -2849,7 +2930,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H13" t="s">
         <v>28</v>
@@ -2858,7 +2939,7 @@
         <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
@@ -2878,7 +2959,7 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C14" t="s">
         <v>94</v>
@@ -2893,13 +2974,13 @@
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H14" t="s">
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J14" t="s">
         <v>83</v>
@@ -2937,16 +3018,16 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H15" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="I15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K15" t="s">
         <v>55</v>
@@ -2981,16 +3062,16 @@
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>168</v>
+        <v>520</v>
       </c>
       <c r="H16" t="s">
         <v>28</v>
       </c>
       <c r="I16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s">
         <v>55</v>
@@ -3019,13 +3100,13 @@
         <v>54</v>
       </c>
       <c r="E17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F17" t="s">
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>119</v>
+        <v>636</v>
       </c>
       <c r="H17" t="s">
         <v>59</v>
@@ -3034,7 +3115,7 @@
         <v>61</v>
       </c>
       <c r="J17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K17" t="s">
         <v>55</v>
@@ -3069,13 +3150,13 @@
         <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>119</v>
+        <v>636</v>
       </c>
       <c r="H18" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="J18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K18" t="s">
         <v>55</v>
@@ -3104,19 +3185,19 @@
         <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F19" t="s">
         <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>637</v>
       </c>
       <c r="H19" t="s">
         <v>28</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J19" t="s">
         <v>84</v>
@@ -3154,13 +3235,13 @@
         <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H20" t="s">
         <v>81</v>
       </c>
       <c r="J20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K20" t="s">
         <v>55</v>
@@ -3177,10 +3258,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
         <v>106</v>
-      </c>
-      <c r="B21" t="s">
-        <v>107</v>
       </c>
       <c r="C21" t="s">
         <v>62</v>
@@ -3195,7 +3276,7 @@
         <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H21" t="s">
         <v>81</v>
@@ -3218,34 +3299,34 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" t="s">
         <v>114</v>
       </c>
-      <c r="C22" t="s">
-        <v>115</v>
-      </c>
       <c r="D22" t="s">
         <v>54</v>
       </c>
       <c r="E22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H22" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="I22" t="s">
         <v>61</v>
       </c>
       <c r="J22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K22" t="s">
         <v>55</v>
@@ -3262,13 +3343,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -3280,7 +3361,7 @@
         <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H23" t="s">
         <v>59</v>
@@ -3289,7 +3370,7 @@
         <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K23" t="s">
         <v>55</v>
@@ -3306,25 +3387,25 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
         <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
       </c>
       <c r="E24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F24" t="s">
         <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
+        <v>637</v>
       </c>
       <c r="H24" t="s">
         <v>28</v>
@@ -3347,28 +3428,28 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" t="s">
         <v>132</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" t="s">
         <v>133</v>
-      </c>
-      <c r="D25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" t="s">
-        <v>134</v>
       </c>
       <c r="F25" t="s">
         <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>254</v>
+        <v>169</v>
       </c>
       <c r="H25" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="J25" t="s">
         <v>83</v>
@@ -3388,31 +3469,31 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
         <v>135</v>
       </c>
-      <c r="C26" t="s">
-        <v>136</v>
-      </c>
       <c r="D26" t="s">
         <v>54</v>
       </c>
       <c r="E26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F26" t="s">
         <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>254</v>
+        <v>169</v>
       </c>
       <c r="H26" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="J26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K26" t="s">
         <v>55</v>
@@ -3429,28 +3510,28 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" t="s">
         <v>137</v>
       </c>
-      <c r="C27" t="s">
-        <v>138</v>
-      </c>
       <c r="D27" t="s">
         <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
         <v>32</v>
       </c>
       <c r="G27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J27" t="s">
         <v>83</v>
@@ -3470,34 +3551,34 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s">
         <v>139</v>
       </c>
-      <c r="C28" t="s">
-        <v>140</v>
-      </c>
       <c r="D28" t="s">
         <v>54</v>
       </c>
       <c r="E28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I28" t="s">
         <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>453</v>
+        <v>635</v>
       </c>
       <c r="K28" t="s">
         <v>56</v>
@@ -3514,13 +3595,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
         <v>141</v>
-      </c>
-      <c r="C29" t="s">
-        <v>142</v>
       </c>
       <c r="D29" t="s">
         <v>54</v>
@@ -3535,7 +3616,10 @@
         <v>97</v>
       </c>
       <c r="H29" t="s">
-        <v>378</v>
+        <v>374</v>
+      </c>
+      <c r="I29" t="s">
+        <v>82</v>
       </c>
       <c r="J29" t="s">
         <v>83</v>
@@ -3555,31 +3639,31 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" t="s">
         <v>143</v>
       </c>
-      <c r="C30" t="s">
-        <v>144</v>
-      </c>
       <c r="D30" t="s">
         <v>54</v>
       </c>
       <c r="E30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K30" t="s">
         <v>55</v>
@@ -3596,31 +3680,31 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s">
         <v>145</v>
       </c>
-      <c r="C31" t="s">
-        <v>146</v>
-      </c>
       <c r="D31" t="s">
         <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F31" t="s">
         <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>254</v>
+        <v>169</v>
       </c>
       <c r="H31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K31" t="s">
         <v>55</v>
@@ -3637,13 +3721,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" t="s">
         <v>160</v>
-      </c>
-      <c r="C32" t="s">
-        <v>161</v>
       </c>
       <c r="D32" t="s">
         <v>54</v>
@@ -3655,13 +3739,13 @@
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H32" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="J32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K32" t="s">
         <v>55</v>
@@ -3678,31 +3762,31 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
+        <v>161</v>
+      </c>
+      <c r="C33" t="s">
         <v>162</v>
       </c>
-      <c r="C33" t="s">
-        <v>163</v>
-      </c>
       <c r="D33" t="s">
         <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H33" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="J33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K33" t="s">
         <v>55</v>
@@ -3719,13 +3803,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" t="s">
         <v>164</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>165</v>
-      </c>
-      <c r="C34" t="s">
-        <v>166</v>
       </c>
       <c r="D34" t="s">
         <v>54</v>
@@ -3740,13 +3824,13 @@
         <v>97</v>
       </c>
       <c r="H34" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J34" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K34" t="s">
         <v>55</v>
@@ -3763,7 +3847,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s">
         <v>29</v>
@@ -3781,13 +3865,13 @@
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H35" t="s">
         <v>80</v>
       </c>
       <c r="J35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K35" t="s">
         <v>55</v>
@@ -3804,13 +3888,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C36" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D36" t="s">
         <v>54</v>
@@ -3822,16 +3906,16 @@
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H36" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J36" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="K36" t="s">
         <v>55</v>
@@ -3848,13 +3932,13 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D37" t="s">
         <v>54</v>
@@ -3866,16 +3950,16 @@
         <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>257</v>
+        <v>167</v>
       </c>
       <c r="H37" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I37" t="s">
         <v>82</v>
       </c>
       <c r="J37" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K37" t="s">
         <v>55</v>
@@ -3892,13 +3976,13 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D38" t="s">
         <v>54</v>
@@ -3907,19 +3991,19 @@
         <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G38" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="H38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I38" t="s">
         <v>60</v>
       </c>
       <c r="J38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K38" t="s">
         <v>55</v>
@@ -3936,13 +4020,13 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D39" t="s">
         <v>54</v>
@@ -3954,16 +4038,16 @@
         <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I39" t="s">
         <v>60</v>
       </c>
       <c r="J39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K39" t="s">
         <v>55</v>
@@ -3980,13 +4064,13 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B40" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C40" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D40" t="s">
         <v>54</v>
@@ -3998,16 +4082,16 @@
         <v>32</v>
       </c>
       <c r="G40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H40" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I40" t="s">
         <v>61</v>
       </c>
       <c r="J40" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K40" t="s">
         <v>55</v>
@@ -4024,13 +4108,13 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B41" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C41" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D41" t="s">
         <v>54</v>
@@ -4042,16 +4126,16 @@
         <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H41" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I41" t="s">
         <v>60</v>
       </c>
       <c r="J41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K41" t="s">
         <v>55</v>
@@ -4068,13 +4152,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B42" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D42" t="s">
         <v>54</v>
@@ -4086,16 +4170,16 @@
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H42" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="I42" t="s">
         <v>61</v>
       </c>
       <c r="J42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K42" t="s">
         <v>55</v>
@@ -4112,13 +4196,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B43" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C43" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="D43" t="s">
         <v>54</v>
@@ -4130,16 +4214,16 @@
         <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H43" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="I43" t="s">
         <v>61</v>
       </c>
       <c r="J43" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K43" t="s">
         <v>57</v>
@@ -4156,13 +4240,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D44" t="s">
         <v>54</v>
@@ -4174,16 +4258,16 @@
         <v>13</v>
       </c>
       <c r="G44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H44" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="I44" t="s">
         <v>61</v>
       </c>
       <c r="J44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K44" t="s">
         <v>55</v>
@@ -4200,13 +4284,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B45" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C45" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D45" t="s">
         <v>54</v>
@@ -4218,16 +4302,16 @@
         <v>13</v>
       </c>
       <c r="G45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H45" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="I45" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J45" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K45" t="s">
         <v>55</v>
@@ -4244,13 +4328,13 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B46" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C46" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D46" t="s">
         <v>54</v>
@@ -4262,16 +4346,16 @@
         <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H46" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J46" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K46" t="s">
         <v>55</v>
@@ -4288,13 +4372,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B47" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C47" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D47" t="s">
         <v>54</v>
@@ -4306,16 +4390,16 @@
         <v>13</v>
       </c>
       <c r="G47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H47" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I47" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J47" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K47" t="s">
         <v>55</v>
@@ -4332,13 +4416,13 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B48" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C48" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D48" t="s">
         <v>54</v>
@@ -4350,16 +4434,16 @@
         <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H48" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I48" t="s">
         <v>60</v>
       </c>
       <c r="J48" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K48" t="s">
         <v>55</v>
@@ -4376,13 +4460,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B49" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C49" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D49" t="s">
         <v>54</v>
@@ -4394,16 +4478,16 @@
         <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H49" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J49" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K49" t="s">
         <v>55</v>
@@ -4420,13 +4504,13 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B50" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C50" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D50" t="s">
         <v>54</v>
@@ -4438,16 +4522,16 @@
         <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="H50" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I50" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K50" t="s">
         <v>55</v>
@@ -4464,13 +4548,13 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B51" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C51" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D51" t="s">
         <v>54</v>
@@ -4482,16 +4566,16 @@
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="H51" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K51" t="s">
         <v>55</v>
@@ -4508,13 +4592,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B52" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C52" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D52" t="s">
         <v>54</v>
@@ -4526,16 +4610,16 @@
         <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H52" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J52" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K52" t="s">
         <v>55</v>
@@ -4552,13 +4636,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B53" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C53" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D53" t="s">
         <v>54</v>
@@ -4570,16 +4654,16 @@
         <v>13</v>
       </c>
       <c r="G53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H53" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I53" t="s">
         <v>61</v>
       </c>
       <c r="J53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K53" t="s">
         <v>55</v>
@@ -4596,13 +4680,13 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B54" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C54" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D54" t="s">
         <v>54</v>
@@ -4614,13 +4698,13 @@
         <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>257</v>
+        <v>167</v>
       </c>
       <c r="H54" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K54" t="s">
         <v>55</v>
@@ -4637,13 +4721,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B55" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C55" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D55" t="s">
         <v>54</v>
@@ -4655,16 +4739,16 @@
         <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H55" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J55" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -4681,13 +4765,13 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B56" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C56" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D56" t="s">
         <v>54</v>
@@ -4699,16 +4783,16 @@
         <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H56" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="I56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J56" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="K56" t="s">
         <v>55</v>
@@ -4725,13 +4809,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B57" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C57" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D57" t="s">
         <v>54</v>
@@ -4743,13 +4827,13 @@
         <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H57" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K57" t="s">
         <v>55</v>
@@ -4766,13 +4850,13 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B58" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C58" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D58" t="s">
         <v>54</v>
@@ -4784,16 +4868,16 @@
         <v>32</v>
       </c>
       <c r="G58" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H58" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="I58" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J58" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K58" t="s">
         <v>55</v>
@@ -4810,13 +4894,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B59" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C59" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D59" t="s">
         <v>54</v>
@@ -4828,13 +4912,13 @@
         <v>32</v>
       </c>
       <c r="G59" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H59" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="J59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K59" t="s">
         <v>57</v>
@@ -4851,13 +4935,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B60" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C60" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D60" t="s">
         <v>54</v>
@@ -4869,16 +4953,16 @@
         <v>32</v>
       </c>
       <c r="G60" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="H60" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="I60" t="s">
         <v>60</v>
       </c>
       <c r="J60" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K60" t="s">
         <v>55</v>
@@ -4895,31 +4979,31 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C61" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D61" t="s">
         <v>54</v>
       </c>
       <c r="E61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H61" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J61" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -4936,13 +5020,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B62" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C62" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D62" t="s">
         <v>54</v>
@@ -4954,16 +5038,16 @@
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H62" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I62" t="s">
         <v>82</v>
       </c>
       <c r="J62" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K62" t="s">
         <v>55</v>
@@ -4980,13 +5064,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C63" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D63" t="s">
         <v>54</v>
@@ -4998,16 +5082,16 @@
         <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H63" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I63" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="K63" t="s">
         <v>55</v>
@@ -5024,13 +5108,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C64" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D64" t="s">
         <v>54</v>
@@ -5042,13 +5126,13 @@
         <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H64" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="J64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K64" t="s">
         <v>55</v>
@@ -5065,13 +5149,13 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B65" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C65" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D65" t="s">
         <v>54</v>
@@ -5083,13 +5167,13 @@
         <v>13</v>
       </c>
       <c r="G65" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H65" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J65" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K65" t="s">
         <v>55</v>
@@ -5106,13 +5190,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B66" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C66" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D66" t="s">
         <v>54</v>
@@ -5124,16 +5208,16 @@
         <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H66" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="I66" t="s">
         <v>61</v>
       </c>
       <c r="J66" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K66" t="s">
         <v>55</v>
@@ -5150,13 +5234,13 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B67" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C67" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D67" t="s">
         <v>54</v>
@@ -5168,13 +5252,13 @@
         <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H67" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="J67" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K67" t="s">
         <v>55</v>
@@ -5191,13 +5275,13 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B68" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C68" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D68" t="s">
         <v>54</v>
@@ -5209,13 +5293,13 @@
         <v>13</v>
       </c>
       <c r="G68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H68" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="J68" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K68" t="s">
         <v>55</v>
@@ -5232,34 +5316,34 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B69" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C69" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D69" t="s">
         <v>54</v>
       </c>
       <c r="E69" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
       </c>
       <c r="G69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H69" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I69" t="s">
         <v>61</v>
       </c>
       <c r="J69" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K69" t="s">
         <v>55</v>
@@ -5276,13 +5360,13 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B70" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C70" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D70" t="s">
         <v>54</v>
@@ -5294,13 +5378,13 @@
         <v>13</v>
       </c>
       <c r="G70" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="H70" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J70" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K70" t="s">
         <v>55</v>
@@ -5317,34 +5401,34 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B71" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C71" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D71" t="s">
         <v>54</v>
       </c>
       <c r="E71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F71" t="s">
         <v>32</v>
       </c>
       <c r="G71" t="s">
-        <v>254</v>
+        <v>169</v>
       </c>
       <c r="H71" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I71" t="s">
         <v>61</v>
       </c>
       <c r="J71" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K71" t="s">
         <v>55</v>
@@ -5361,13 +5445,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B72" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C72" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D72" t="s">
         <v>54</v>
@@ -5379,13 +5463,13 @@
         <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>257</v>
+        <v>167</v>
       </c>
       <c r="H72" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K72" t="s">
         <v>55</v>
@@ -5402,13 +5486,13 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B73" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C73" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D73" t="s">
         <v>54</v>
@@ -5420,13 +5504,13 @@
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H73" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="J73" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K73" t="s">
         <v>55</v>
@@ -5443,34 +5527,34 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B74" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C74" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D74" t="s">
         <v>54</v>
       </c>
       <c r="E74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F74" t="s">
         <v>32</v>
       </c>
       <c r="G74" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H74" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I74" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="J74" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K74" t="s">
         <v>55</v>
@@ -5487,13 +5571,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B75" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C75" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D75" t="s">
         <v>54</v>
@@ -5505,16 +5589,16 @@
         <v>32</v>
       </c>
       <c r="G75" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="H75" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I75" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J75" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K75" t="s">
         <v>55</v>
@@ -5531,13 +5615,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B76" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C76" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D76" t="s">
         <v>54</v>
@@ -5549,16 +5633,16 @@
         <v>13</v>
       </c>
       <c r="G76" t="s">
-        <v>257</v>
+        <v>167</v>
       </c>
       <c r="H76" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="I76" t="s">
         <v>61</v>
       </c>
       <c r="J76" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K76" t="s">
         <v>55</v>
@@ -5575,34 +5659,34 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B77" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C77" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D77" t="s">
         <v>54</v>
       </c>
       <c r="E77" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F77" t="s">
         <v>13</v>
       </c>
       <c r="G77" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H77" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="I77" t="s">
         <v>61</v>
       </c>
       <c r="J77" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K77" t="s">
         <v>56</v>
@@ -5619,13 +5703,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B78" t="s">
         <v>493</v>
       </c>
-      <c r="B78" t="s">
-        <v>497</v>
-      </c>
       <c r="C78" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D78" t="s">
         <v>54</v>
@@ -5637,16 +5721,16 @@
         <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H78" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="I78" t="s">
         <v>61</v>
       </c>
       <c r="J78" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K78" t="s">
         <v>55</v>
@@ -5663,13 +5747,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B79" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C79" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D79" t="s">
         <v>54</v>
@@ -5681,16 +5765,16 @@
         <v>32</v>
       </c>
       <c r="G79" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="H79" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="I79" t="s">
         <v>61</v>
       </c>
       <c r="J79" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K79" t="s">
         <v>55</v>
@@ -5707,13 +5791,13 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B80" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C80" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="D80" t="s">
         <v>54</v>
@@ -5725,16 +5809,16 @@
         <v>13</v>
       </c>
       <c r="G80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H80" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="I80" t="s">
         <v>61</v>
       </c>
       <c r="J80" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K80" t="s">
         <v>55</v>
@@ -5751,13 +5835,13 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B81" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C81" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="D81" t="s">
         <v>54</v>
@@ -5769,16 +5853,16 @@
         <v>13</v>
       </c>
       <c r="G81" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H81" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="I81" t="s">
         <v>61</v>
       </c>
       <c r="J81" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K81" t="s">
         <v>55</v>
@@ -5795,13 +5879,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B82" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C82" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D82" t="s">
         <v>54</v>
@@ -5813,16 +5897,16 @@
         <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="H82" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="I82" t="s">
         <v>61</v>
       </c>
       <c r="J82" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K82" t="s">
         <v>55</v>
@@ -5839,13 +5923,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B83" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C83" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D83" t="s">
         <v>54</v>
@@ -5857,16 +5941,16 @@
         <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="H83" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I83" t="s">
         <v>61</v>
       </c>
       <c r="J83" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K83" t="s">
         <v>55</v>
@@ -5883,13 +5967,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B84" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C84" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D84" t="s">
         <v>54</v>
@@ -5901,16 +5985,16 @@
         <v>13</v>
       </c>
       <c r="G84" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H84" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I84" t="s">
         <v>61</v>
       </c>
       <c r="J84" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K84" t="s">
         <v>55</v>
@@ -5927,34 +6011,34 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B85" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C85" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D85" t="s">
         <v>54</v>
       </c>
       <c r="E85" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F85" t="s">
         <v>32</v>
       </c>
       <c r="G85" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="H85" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="I85" t="s">
         <v>61</v>
       </c>
       <c r="J85" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K85" t="s">
         <v>55</v>
@@ -5971,13 +6055,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B86" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C86" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D86" t="s">
         <v>54</v>
@@ -5989,16 +6073,16 @@
         <v>32</v>
       </c>
       <c r="G86" t="s">
-        <v>524</v>
+        <v>118</v>
       </c>
       <c r="H86" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="I86" t="s">
         <v>61</v>
       </c>
       <c r="J86" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K86" t="s">
         <v>56</v>
@@ -6015,34 +6099,34 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B87" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C87" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D87" t="s">
         <v>54</v>
       </c>
       <c r="E87" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F87" t="s">
         <v>13</v>
       </c>
       <c r="G87" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H87" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="I87" t="s">
         <v>61</v>
       </c>
       <c r="J87" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K87" t="s">
         <v>57</v>
@@ -6059,34 +6143,34 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B88" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C88" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D88" t="s">
         <v>54</v>
       </c>
       <c r="E88" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F88" t="s">
         <v>32</v>
       </c>
       <c r="G88" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H88" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I88" t="s">
         <v>61</v>
       </c>
       <c r="J88" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K88" t="s">
         <v>55</v>
@@ -6103,13 +6187,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B89" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C89" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D89" t="s">
         <v>54</v>
@@ -6121,16 +6205,16 @@
         <v>32</v>
       </c>
       <c r="G89" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H89" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="I89" t="s">
         <v>61</v>
       </c>
       <c r="J89" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K89" t="s">
         <v>55</v>
@@ -6147,13 +6231,13 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B90" t="s">
+        <v>531</v>
+      </c>
+      <c r="C90" t="s">
         <v>516</v>
-      </c>
-      <c r="B90" t="s">
-        <v>535</v>
-      </c>
-      <c r="C90" t="s">
-        <v>520</v>
       </c>
       <c r="D90" t="s">
         <v>54</v>
@@ -6165,16 +6249,16 @@
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="H90" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I90" t="s">
         <v>61</v>
       </c>
       <c r="J90" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K90" t="s">
         <v>57</v>
@@ -6191,13 +6275,13 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B91" t="s">
         <v>577</v>
       </c>
-      <c r="B91" t="s">
-        <v>582</v>
-      </c>
       <c r="C91" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D91" t="s">
         <v>54</v>
@@ -6209,16 +6293,16 @@
         <v>13</v>
       </c>
       <c r="G91" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H91" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="I91" t="s">
         <v>82</v>
       </c>
       <c r="J91" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="K91" t="s">
         <v>55</v>
@@ -6235,13 +6319,13 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B92" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C92" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="D92" t="s">
         <v>54</v>
@@ -6253,10 +6337,10 @@
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H92" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J92" t="s">
         <v>84</v>
@@ -6276,13 +6360,13 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B93" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C93" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D93" t="s">
         <v>54</v>
@@ -6294,16 +6378,16 @@
         <v>13</v>
       </c>
       <c r="G93" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H93" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I93" t="s">
         <v>61</v>
       </c>
       <c r="J93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K93" t="s">
         <v>55</v>
@@ -6320,13 +6404,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B94" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C94" t="s">
-        <v>590</v>
+        <v>634</v>
       </c>
       <c r="D94" t="s">
         <v>54</v>
@@ -6338,16 +6422,16 @@
         <v>13</v>
       </c>
       <c r="G94" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H94" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I94" t="s">
         <v>61</v>
       </c>
       <c r="J94" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="K94" t="s">
         <v>55</v>
@@ -6364,13 +6448,13 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B95" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C95" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D95" t="s">
         <v>54</v>
@@ -6379,19 +6463,19 @@
         <v>33</v>
       </c>
       <c r="F95" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G95" t="s">
-        <v>255</v>
+        <v>169</v>
       </c>
       <c r="H95" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I95" t="s">
         <v>61</v>
       </c>
       <c r="J95" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K95" t="s">
         <v>55</v>
@@ -6408,13 +6492,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="B96" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="C96" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="D96" t="s">
         <v>54</v>
@@ -6426,16 +6510,16 @@
         <v>13</v>
       </c>
       <c r="G96" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H96" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I96" t="s">
         <v>61</v>
       </c>
       <c r="J96" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K96" t="s">
         <v>55</v>
@@ -6452,13 +6536,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="B97" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="C97" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="D97" t="s">
         <v>54</v>
@@ -6470,16 +6554,16 @@
         <v>13</v>
       </c>
       <c r="G97" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H97" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I97" t="s">
         <v>82</v>
       </c>
       <c r="J97" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K97" t="s">
         <v>55</v>
@@ -6499,7 +6583,7 @@
         <v>63</v>
       </c>
       <c r="B98" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C98" t="s">
         <v>70</v>
@@ -6514,16 +6598,16 @@
         <v>13</v>
       </c>
       <c r="G98" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H98" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="I98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J98" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K98" t="s">
         <v>55</v>
@@ -6558,16 +6642,16 @@
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H99" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="I99" t="s">
         <v>82</v>
       </c>
       <c r="J99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K99" t="s">
         <v>55</v>
@@ -6587,7 +6671,7 @@
         <v>65</v>
       </c>
       <c r="B100" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C100" t="s">
         <v>73</v>
@@ -6602,16 +6686,16 @@
         <v>13</v>
       </c>
       <c r="G100" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H100" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="I100" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J100" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K100" t="s">
         <v>55</v>
@@ -6634,7 +6718,7 @@
         <v>74</v>
       </c>
       <c r="C101" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D101" t="s">
         <v>85</v>
@@ -6646,13 +6730,13 @@
         <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H101" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="J101" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K101" t="s">
         <v>57</v>
@@ -6687,16 +6771,16 @@
         <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H102" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="I102" t="s">
         <v>82</v>
       </c>
       <c r="J102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K102" t="s">
         <v>55</v>
@@ -6719,7 +6803,7 @@
         <v>77</v>
       </c>
       <c r="C103" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D103" t="s">
         <v>85</v>
@@ -6731,13 +6815,13 @@
         <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H103" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="J103" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K103" t="s">
         <v>55</v>
@@ -6772,16 +6856,16 @@
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H104" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="I104" t="s">
         <v>82</v>
       </c>
       <c r="J104" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K104" t="s">
         <v>55</v>
@@ -6798,13 +6882,13 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B105" t="s">
         <v>108</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>109</v>
-      </c>
-      <c r="C105" t="s">
-        <v>110</v>
       </c>
       <c r="D105" t="s">
         <v>85</v>
@@ -6816,16 +6900,16 @@
         <v>32</v>
       </c>
       <c r="G105" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H105" t="s">
         <v>28</v>
       </c>
       <c r="I105" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J105" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K105" t="s">
         <v>55</v>
@@ -6842,13 +6926,13 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B106" t="s">
+        <v>149</v>
+      </c>
+      <c r="C106" t="s">
         <v>150</v>
-      </c>
-      <c r="C106" t="s">
-        <v>151</v>
       </c>
       <c r="D106" t="s">
         <v>85</v>
@@ -6860,16 +6944,16 @@
         <v>32</v>
       </c>
       <c r="G106" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H106" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I106" t="s">
         <v>82</v>
       </c>
       <c r="J106" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K106" t="s">
         <v>55</v>
@@ -6886,13 +6970,13 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B107" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C107" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D107" t="s">
         <v>85</v>
@@ -6904,10 +6988,10 @@
         <v>32</v>
       </c>
       <c r="G107" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="H107" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I107" t="s">
         <v>82</v>
@@ -6930,13 +7014,13 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B108" t="s">
+        <v>154</v>
+      </c>
+      <c r="C108" t="s">
         <v>155</v>
-      </c>
-      <c r="C108" t="s">
-        <v>156</v>
       </c>
       <c r="D108" t="s">
         <v>85</v>
@@ -6948,16 +7032,16 @@
         <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H108" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I108" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K108" t="s">
         <v>55</v>
@@ -6974,13 +7058,13 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B109" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C109" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D109" t="s">
         <v>85</v>
@@ -6992,13 +7076,13 @@
         <v>32</v>
       </c>
       <c r="G109" t="s">
-        <v>552</v>
+        <v>638</v>
       </c>
       <c r="H109" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J109" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K109" t="s">
         <v>56</v>
@@ -7015,13 +7099,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="B110" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C110" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="D110" t="s">
         <v>85</v>
@@ -7033,13 +7117,13 @@
         <v>13</v>
       </c>
       <c r="G110" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H110" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J110" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K110" t="s">
         <v>55</v>
@@ -7056,13 +7140,13 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B111" t="s">
+        <v>185</v>
+      </c>
+      <c r="C111" t="s">
         <v>186</v>
-      </c>
-      <c r="C111" t="s">
-        <v>187</v>
       </c>
       <c r="D111" t="s">
         <v>85</v>
@@ -7074,13 +7158,13 @@
         <v>13</v>
       </c>
       <c r="G111" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H111" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J111" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K111" t="s">
         <v>55</v>
@@ -7097,13 +7181,13 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B112" t="s">
+        <v>187</v>
+      </c>
+      <c r="C112" t="s">
         <v>188</v>
-      </c>
-      <c r="C112" t="s">
-        <v>189</v>
       </c>
       <c r="D112" t="s">
         <v>85</v>
@@ -7115,16 +7199,16 @@
         <v>13</v>
       </c>
       <c r="G112" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H112" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I112" t="s">
         <v>82</v>
       </c>
       <c r="J112" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K112" t="s">
         <v>55</v>
@@ -7141,13 +7225,13 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B113" t="s">
+        <v>189</v>
+      </c>
+      <c r="C113" t="s">
         <v>190</v>
-      </c>
-      <c r="C113" t="s">
-        <v>191</v>
       </c>
       <c r="D113" t="s">
         <v>85</v>
@@ -7159,13 +7243,13 @@
         <v>13</v>
       </c>
       <c r="G113" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H113" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J113" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K113" t="s">
         <v>55</v>
@@ -7182,13 +7266,13 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B114" t="s">
+        <v>191</v>
+      </c>
+      <c r="C114" t="s">
         <v>192</v>
-      </c>
-      <c r="C114" t="s">
-        <v>193</v>
       </c>
       <c r="D114" t="s">
         <v>85</v>
@@ -7200,16 +7284,16 @@
         <v>13</v>
       </c>
       <c r="G114" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H114" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I114" t="s">
         <v>82</v>
       </c>
       <c r="J114" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K114" t="s">
         <v>55</v>
@@ -7226,13 +7310,13 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B115" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C115" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D115" t="s">
         <v>85</v>
@@ -7244,16 +7328,16 @@
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H115" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I115" t="s">
         <v>82</v>
       </c>
       <c r="J115" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K115" t="s">
         <v>55</v>
@@ -7270,13 +7354,13 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B116" t="s">
+        <v>593</v>
+      </c>
+      <c r="C116" t="s">
         <v>594</v>
-      </c>
-      <c r="B116" t="s">
-        <v>599</v>
-      </c>
-      <c r="C116" t="s">
-        <v>600</v>
       </c>
       <c r="D116" t="s">
         <v>85</v>
@@ -7288,13 +7372,13 @@
         <v>13</v>
       </c>
       <c r="G116" t="s">
-        <v>168</v>
+        <v>308</v>
       </c>
       <c r="H116" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J116" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K116" t="s">
         <v>55</v>
@@ -7311,13 +7395,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B117" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C117" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D117" t="s">
         <v>85</v>
@@ -7329,16 +7413,16 @@
         <v>32</v>
       </c>
       <c r="G117" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H117" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I117" t="s">
         <v>82</v>
       </c>
       <c r="J117" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K117" t="s">
         <v>55</v>
@@ -7355,13 +7439,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B118" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C118" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="D118" t="s">
         <v>85</v>
@@ -7373,13 +7457,13 @@
         <v>13</v>
       </c>
       <c r="G118" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H118" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="J118" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K118" t="s">
         <v>55</v>
@@ -7396,13 +7480,13 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B119" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="C119" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D119" t="s">
         <v>85</v>
@@ -7414,13 +7498,13 @@
         <v>13</v>
       </c>
       <c r="G119" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H119" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="J119" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K119" t="s">
         <v>55</v>
@@ -7437,13 +7521,13 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B120" t="s">
+        <v>195</v>
+      </c>
+      <c r="C120" t="s">
         <v>196</v>
-      </c>
-      <c r="C120" t="s">
-        <v>197</v>
       </c>
       <c r="D120" t="s">
         <v>85</v>
@@ -7455,13 +7539,13 @@
         <v>13</v>
       </c>
       <c r="G120" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H120" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J120" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K120" t="s">
         <v>55</v>
@@ -7478,13 +7562,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B121" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="C121" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="D121" t="s">
         <v>85</v>
@@ -7496,16 +7580,16 @@
         <v>13</v>
       </c>
       <c r="G121" t="s">
-        <v>168</v>
+        <v>308</v>
       </c>
       <c r="H121" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I121" t="s">
         <v>82</v>
       </c>
       <c r="J121" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K121" t="s">
         <v>55</v>
@@ -7522,13 +7606,13 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B122" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C122" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>85</v>
@@ -7540,13 +7624,13 @@
         <v>13</v>
       </c>
       <c r="G122" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H122" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J122" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K122" t="s">
         <v>55</v>
@@ -7563,13 +7647,13 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B123" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C123" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D123" t="s">
         <v>85</v>
@@ -7581,16 +7665,16 @@
         <v>13</v>
       </c>
       <c r="G123" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H123" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I123" t="s">
         <v>82</v>
       </c>
       <c r="J123" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K123" t="s">
         <v>55</v>
@@ -7607,13 +7691,13 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B124" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C124" t="s">
-        <v>268</v>
+        <v>633</v>
       </c>
       <c r="D124" t="s">
         <v>85</v>
@@ -7625,16 +7709,16 @@
         <v>13</v>
       </c>
       <c r="G124" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H124" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I124" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J124" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K124" t="s">
         <v>55</v>
@@ -7651,13 +7735,13 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B125" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C125" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D125" t="s">
         <v>85</v>
@@ -7669,13 +7753,13 @@
         <v>13</v>
       </c>
       <c r="G125" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H125" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J125" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K125" t="s">
         <v>55</v>
@@ -7692,13 +7776,13 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B126" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C126" t="s">
-        <v>606</v>
+        <v>632</v>
       </c>
       <c r="D126" t="s">
         <v>85</v>
@@ -7710,16 +7794,16 @@
         <v>13</v>
       </c>
       <c r="G126" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H126" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I126" t="s">
         <v>82</v>
       </c>
       <c r="J126" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K126" t="s">
         <v>55</v>
@@ -7736,13 +7820,13 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B127" t="s">
+        <v>199</v>
+      </c>
+      <c r="C127" t="s">
         <v>200</v>
-      </c>
-      <c r="C127" t="s">
-        <v>201</v>
       </c>
       <c r="D127" t="s">
         <v>85</v>
@@ -7754,16 +7838,16 @@
         <v>13</v>
       </c>
       <c r="G127" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H127" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I127" t="s">
         <v>82</v>
       </c>
       <c r="J127" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K127" t="s">
         <v>55</v>
@@ -7780,13 +7864,13 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="B128" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="C128" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="D128" t="s">
         <v>85</v>
@@ -7798,16 +7882,16 @@
         <v>13</v>
       </c>
       <c r="G128" t="s">
-        <v>168</v>
+        <v>308</v>
       </c>
       <c r="H128" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="I128" t="s">
         <v>61</v>
       </c>
       <c r="J128" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K128" t="s">
         <v>55</v>
@@ -7824,13 +7908,13 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B129" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C129" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D129" t="s">
         <v>85</v>
@@ -7842,13 +7926,13 @@
         <v>13</v>
       </c>
       <c r="G129" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H129" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J129" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K129" t="s">
         <v>55</v>
@@ -7865,13 +7949,13 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B130" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="C130" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D130" t="s">
         <v>85</v>
@@ -7883,16 +7967,16 @@
         <v>13</v>
       </c>
       <c r="G130" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H130" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I130" t="s">
         <v>82</v>
       </c>
       <c r="J130" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K130" t="s">
         <v>55</v>
@@ -7909,13 +7993,13 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B131" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C131" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D131" t="s">
         <v>85</v>
@@ -7927,13 +8011,13 @@
         <v>13</v>
       </c>
       <c r="G131" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H131" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J131" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K131" t="s">
         <v>55</v>
@@ -7950,13 +8034,13 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B132" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C132" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D132" t="s">
         <v>85</v>
@@ -7968,13 +8052,13 @@
         <v>13</v>
       </c>
       <c r="G132" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="H132" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J132" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K132" t="s">
         <v>55</v>
@@ -7991,13 +8075,13 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B133" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C133" t="s">
-        <v>207</v>
+        <v>639</v>
       </c>
       <c r="D133" t="s">
         <v>85</v>
@@ -8009,16 +8093,16 @@
         <v>13</v>
       </c>
       <c r="G133" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H133" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I133" t="s">
         <v>82</v>
       </c>
       <c r="J133" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K133" t="s">
         <v>55</v>
@@ -8035,13 +8119,13 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B134" t="s">
+        <v>210</v>
+      </c>
+      <c r="C134" t="s">
         <v>212</v>
-      </c>
-      <c r="C134" t="s">
-        <v>214</v>
       </c>
       <c r="D134" t="s">
         <v>85</v>
@@ -8053,16 +8137,16 @@
         <v>13</v>
       </c>
       <c r="G134" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H134" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I134" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J134" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K134" t="s">
         <v>55</v>
@@ -8079,13 +8163,13 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B135" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C135" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D135" t="s">
         <v>85</v>
@@ -8097,16 +8181,16 @@
         <v>13</v>
       </c>
       <c r="G135" t="s">
-        <v>168</v>
+        <v>308</v>
       </c>
       <c r="H135" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I135" t="s">
         <v>82</v>
       </c>
       <c r="J135" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K135" t="s">
         <v>55</v>
@@ -8123,13 +8207,13 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B136" t="s">
+        <v>273</v>
+      </c>
+      <c r="C136" t="s">
         <v>276</v>
-      </c>
-      <c r="B136" t="s">
-        <v>277</v>
-      </c>
-      <c r="C136" t="s">
-        <v>280</v>
       </c>
       <c r="D136" t="s">
         <v>85</v>
@@ -8141,16 +8225,16 @@
         <v>13</v>
       </c>
       <c r="G136" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H136" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I136" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J136" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K136" t="s">
         <v>55</v>
@@ -8167,13 +8251,13 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B137" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C137" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D137" t="s">
         <v>85</v>
@@ -8185,13 +8269,13 @@
         <v>13</v>
       </c>
       <c r="G137" t="s">
-        <v>312</v>
+        <v>167</v>
       </c>
       <c r="H137" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J137" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K137" t="s">
         <v>55</v>
@@ -8208,13 +8292,13 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B138" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C138" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D138" t="s">
         <v>85</v>
@@ -8226,13 +8310,13 @@
         <v>13</v>
       </c>
       <c r="G138" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H138" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K138" t="s">
         <v>55</v>
@@ -8249,13 +8333,13 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B139" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C139" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D139" t="s">
         <v>85</v>
@@ -8267,13 +8351,13 @@
         <v>32</v>
       </c>
       <c r="G139" t="s">
-        <v>254</v>
+        <v>169</v>
       </c>
       <c r="H139" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J139" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K139" t="s">
         <v>55</v>
@@ -8290,13 +8374,13 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B140" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C140" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D140" t="s">
         <v>85</v>
@@ -8308,13 +8392,13 @@
         <v>13</v>
       </c>
       <c r="G140" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H140" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J140" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K140" t="s">
         <v>55</v>
@@ -8331,13 +8415,13 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B141" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C141" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D141" t="s">
         <v>85</v>
@@ -8349,16 +8433,16 @@
         <v>13</v>
       </c>
       <c r="G141" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H141" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="I141" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J141" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K141" t="s">
         <v>55</v>
@@ -8375,13 +8459,13 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B142" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C142" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D142" t="s">
         <v>85</v>
@@ -8393,13 +8477,13 @@
         <v>13</v>
       </c>
       <c r="G142" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H142" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J142" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K142" t="s">
         <v>56</v>
@@ -8416,13 +8500,13 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B143" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C143" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D143" t="s">
         <v>85</v>
@@ -8434,16 +8518,16 @@
         <v>13</v>
       </c>
       <c r="G143" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H143" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="I143" t="s">
         <v>82</v>
       </c>
       <c r="J143" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K143" t="s">
         <v>55</v>
@@ -8460,13 +8544,13 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B144" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C144" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D144" t="s">
         <v>85</v>
@@ -8478,16 +8562,16 @@
         <v>13</v>
       </c>
       <c r="G144" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="H144" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="I144" t="s">
         <v>82</v>
       </c>
       <c r="J144" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K144" t="s">
         <v>55</v>
@@ -8504,13 +8588,13 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B145" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C145" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D145" t="s">
         <v>85</v>
@@ -8522,13 +8606,13 @@
         <v>32</v>
       </c>
       <c r="G145" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H145" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="J145" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K145" t="s">
         <v>55</v>
@@ -8545,13 +8629,13 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B146" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C146" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D146" t="s">
         <v>85</v>
@@ -8563,13 +8647,13 @@
         <v>13</v>
       </c>
       <c r="G146" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H146" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J146" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K146" t="s">
         <v>55</v>
@@ -8586,13 +8670,13 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B147" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C147" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D147" t="s">
         <v>85</v>
@@ -8604,16 +8688,16 @@
         <v>13</v>
       </c>
       <c r="G147" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H147" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="I147" t="s">
         <v>82</v>
       </c>
       <c r="J147" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K147" t="s">
         <v>55</v>
@@ -8630,13 +8714,13 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B148" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C148" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D148" t="s">
         <v>85</v>
@@ -8648,16 +8732,16 @@
         <v>32</v>
       </c>
       <c r="G148" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H148" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="I148" t="s">
         <v>82</v>
       </c>
       <c r="J148" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K148" t="s">
         <v>55</v>
@@ -8674,13 +8758,13 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B149" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C149" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D149" t="s">
         <v>85</v>
@@ -8692,16 +8776,16 @@
         <v>13</v>
       </c>
       <c r="G149" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="H149" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I149" t="s">
         <v>82</v>
       </c>
       <c r="J149" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K149" t="s">
         <v>55</v>
@@ -8718,13 +8802,13 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B150" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C150" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D150" t="s">
         <v>85</v>
@@ -8736,16 +8820,16 @@
         <v>13</v>
       </c>
       <c r="G150" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H150" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I150" t="s">
         <v>82</v>
       </c>
       <c r="J150" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K150" t="s">
         <v>55</v>
@@ -8762,13 +8846,13 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B151" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C151" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D151" t="s">
         <v>85</v>
@@ -8780,16 +8864,16 @@
         <v>13</v>
       </c>
       <c r="G151" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H151" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I151" t="s">
         <v>82</v>
       </c>
       <c r="J151" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K151" t="s">
         <v>55</v>
@@ -8806,13 +8890,13 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B152" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C152" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D152" t="s">
         <v>85</v>
@@ -8824,16 +8908,16 @@
         <v>13</v>
       </c>
       <c r="G152" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H152" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="I152" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J152" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K152" t="s">
         <v>55</v>
@@ -8850,13 +8934,13 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B153" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C153" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D153" t="s">
         <v>85</v>
@@ -8868,16 +8952,16 @@
         <v>32</v>
       </c>
       <c r="G153" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H153" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I153" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J153" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="K153" t="s">
         <v>55</v>
@@ -8894,13 +8978,13 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B154" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C154" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D154" t="s">
         <v>85</v>
@@ -8912,13 +8996,13 @@
         <v>13</v>
       </c>
       <c r="G154" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H154" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J154" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K154" t="s">
         <v>55</v>
@@ -8935,13 +9019,13 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B155" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C155" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D155" t="s">
         <v>85</v>
@@ -8953,16 +9037,16 @@
         <v>13</v>
       </c>
       <c r="G155" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="H155" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="I155" t="s">
         <v>82</v>
       </c>
       <c r="J155" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K155" t="s">
         <v>55</v>
@@ -8979,13 +9063,13 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B156" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C156" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D156" t="s">
         <v>85</v>
@@ -8997,16 +9081,16 @@
         <v>13</v>
       </c>
       <c r="G156" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H156" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="I156" t="s">
         <v>82</v>
       </c>
       <c r="J156" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K156" t="s">
         <v>55</v>
@@ -9023,13 +9107,13 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B157" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C157" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="D157" t="s">
         <v>85</v>
@@ -9041,13 +9125,13 @@
         <v>13</v>
       </c>
       <c r="G157" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H157" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J157" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K157" t="s">
         <v>55</v>
@@ -9064,13 +9148,13 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B158" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="C158" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="D158" t="s">
         <v>85</v>
@@ -9082,16 +9166,16 @@
         <v>13</v>
       </c>
       <c r="G158" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H158" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I158" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J158" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K158" t="s">
         <v>55</v>
@@ -9108,13 +9192,13 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B159" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C159" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D159" t="s">
         <v>85</v>
@@ -9126,16 +9210,16 @@
         <v>13</v>
       </c>
       <c r="G159" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H159" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I159" t="s">
         <v>82</v>
       </c>
       <c r="J159" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K159" t="s">
         <v>55</v>
@@ -9152,13 +9236,13 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B160" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C160" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D160" t="s">
         <v>85</v>
@@ -9170,16 +9254,16 @@
         <v>13</v>
       </c>
       <c r="G160" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H160" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I160" t="s">
         <v>82</v>
       </c>
       <c r="J160" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K160" t="s">
         <v>55</v>
@@ -9196,13 +9280,13 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B161" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C161" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D161" t="s">
         <v>85</v>
@@ -9214,16 +9298,16 @@
         <v>13</v>
       </c>
       <c r="G161" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H161" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I161" t="s">
         <v>82</v>
       </c>
       <c r="J161" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K161" t="s">
         <v>55</v>
@@ -9240,13 +9324,13 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B162" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C162" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D162" t="s">
         <v>85</v>
@@ -9258,13 +9342,13 @@
         <v>13</v>
       </c>
       <c r="G162" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H162" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J162" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="K162" t="s">
         <v>55</v>
@@ -9281,13 +9365,13 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B163" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C163" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="D163" t="s">
         <v>85</v>
@@ -9299,13 +9383,13 @@
         <v>13</v>
       </c>
       <c r="G163" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H163" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J163" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K163" t="s">
         <v>55</v>
@@ -9322,13 +9406,13 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B164" t="s">
         <v>595</v>
       </c>
-      <c r="B164" t="s">
-        <v>601</v>
-      </c>
       <c r="C164" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D164" t="s">
         <v>85</v>
@@ -9337,19 +9421,19 @@
         <v>33</v>
       </c>
       <c r="F164" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G164" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="H164" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I164" t="s">
         <v>82</v>
       </c>
       <c r="J164" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K164" t="s">
         <v>55</v>
@@ -9366,13 +9450,13 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B165" t="s">
         <v>620</v>
       </c>
-      <c r="B165" t="s">
-        <v>627</v>
-      </c>
       <c r="C165" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="D165" t="s">
         <v>85</v>
@@ -9384,16 +9468,16 @@
         <v>13</v>
       </c>
       <c r="G165" t="s">
-        <v>168</v>
+        <v>308</v>
       </c>
       <c r="H165" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="I165" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J165" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K165" t="s">
         <v>55</v>
@@ -9410,13 +9494,13 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B166" t="s">
+        <v>619</v>
+      </c>
+      <c r="C166" t="s">
         <v>621</v>
-      </c>
-      <c r="B166" t="s">
-        <v>626</v>
-      </c>
-      <c r="C166" t="s">
-        <v>628</v>
       </c>
       <c r="D166" t="s">
         <v>85</v>
@@ -9428,13 +9512,13 @@
         <v>13</v>
       </c>
       <c r="G166" t="s">
-        <v>168</v>
+        <v>308</v>
       </c>
       <c r="H166" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J166" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K166" t="s">
         <v>55</v>
@@ -9446,6 +9530,387 @@
         <v>15</v>
       </c>
       <c r="N166" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A167" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B167" t="s">
+        <v>644</v>
+      </c>
+      <c r="C167" t="s">
+        <v>645</v>
+      </c>
+      <c r="D167" t="s">
+        <v>85</v>
+      </c>
+      <c r="E167" t="s">
+        <v>58</v>
+      </c>
+      <c r="F167" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" t="s">
+        <v>167</v>
+      </c>
+      <c r="H167" t="s">
+        <v>564</v>
+      </c>
+      <c r="I167" t="s">
+        <v>82</v>
+      </c>
+      <c r="J167" t="s">
+        <v>218</v>
+      </c>
+      <c r="K167" t="s">
+        <v>55</v>
+      </c>
+      <c r="L167" t="s">
+        <v>14</v>
+      </c>
+      <c r="M167" t="s">
+        <v>15</v>
+      </c>
+      <c r="N167" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A168" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B168" t="s">
+        <v>646</v>
+      </c>
+      <c r="C168" t="s">
+        <v>647</v>
+      </c>
+      <c r="D168" t="s">
+        <v>85</v>
+      </c>
+      <c r="E168" t="s">
+        <v>58</v>
+      </c>
+      <c r="F168" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" t="s">
+        <v>119</v>
+      </c>
+      <c r="I168" t="s">
+        <v>82</v>
+      </c>
+      <c r="J168" t="s">
+        <v>227</v>
+      </c>
+      <c r="K168" t="s">
+        <v>55</v>
+      </c>
+      <c r="L168" t="s">
+        <v>14</v>
+      </c>
+      <c r="M168" t="s">
+        <v>15</v>
+      </c>
+      <c r="N168" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B169" t="s">
+        <v>648</v>
+      </c>
+      <c r="C169" t="s">
+        <v>649</v>
+      </c>
+      <c r="D169" t="s">
+        <v>85</v>
+      </c>
+      <c r="E169" t="s">
+        <v>58</v>
+      </c>
+      <c r="F169" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" t="s">
+        <v>167</v>
+      </c>
+      <c r="H169" t="s">
+        <v>562</v>
+      </c>
+      <c r="I169" t="s">
+        <v>61</v>
+      </c>
+      <c r="J169" t="s">
+        <v>663</v>
+      </c>
+      <c r="K169" t="s">
+        <v>55</v>
+      </c>
+      <c r="L169" t="s">
+        <v>14</v>
+      </c>
+      <c r="M169" t="s">
+        <v>15</v>
+      </c>
+      <c r="N169" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B170" t="s">
+        <v>651</v>
+      </c>
+      <c r="C170" t="s">
+        <v>650</v>
+      </c>
+      <c r="D170" t="s">
+        <v>85</v>
+      </c>
+      <c r="E170" t="s">
+        <v>58</v>
+      </c>
+      <c r="F170" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" t="s">
+        <v>167</v>
+      </c>
+      <c r="H170" t="s">
+        <v>565</v>
+      </c>
+      <c r="I170" t="s">
+        <v>82</v>
+      </c>
+      <c r="J170" t="s">
+        <v>652</v>
+      </c>
+      <c r="K170" t="s">
+        <v>55</v>
+      </c>
+      <c r="L170" t="s">
+        <v>14</v>
+      </c>
+      <c r="M170" t="s">
+        <v>15</v>
+      </c>
+      <c r="N170" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A171" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B171" t="s">
+        <v>550</v>
+      </c>
+      <c r="C171" t="s">
+        <v>658</v>
+      </c>
+      <c r="D171" t="s">
+        <v>54</v>
+      </c>
+      <c r="E171" t="s">
+        <v>133</v>
+      </c>
+      <c r="F171" t="s">
+        <v>32</v>
+      </c>
+      <c r="G171" t="s">
+        <v>171</v>
+      </c>
+      <c r="H171" t="s">
+        <v>28</v>
+      </c>
+      <c r="J171" t="s">
+        <v>102</v>
+      </c>
+      <c r="K171" t="s">
+        <v>56</v>
+      </c>
+      <c r="L171" t="s">
+        <v>14</v>
+      </c>
+      <c r="M171" t="s">
+        <v>15</v>
+      </c>
+      <c r="N171" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A172" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B172" t="s">
+        <v>659</v>
+      </c>
+      <c r="C172" t="s">
+        <v>446</v>
+      </c>
+      <c r="D172" t="s">
+        <v>54</v>
+      </c>
+      <c r="E172" t="s">
+        <v>33</v>
+      </c>
+      <c r="F172" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" t="s">
+        <v>308</v>
+      </c>
+      <c r="H172" t="s">
+        <v>234</v>
+      </c>
+      <c r="J172" t="s">
+        <v>449</v>
+      </c>
+      <c r="K172" t="s">
+        <v>55</v>
+      </c>
+      <c r="L172" t="s">
+        <v>14</v>
+      </c>
+      <c r="M172" t="s">
+        <v>15</v>
+      </c>
+      <c r="N172" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A173" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B173" t="s">
+        <v>660</v>
+      </c>
+      <c r="C173" t="s">
+        <v>446</v>
+      </c>
+      <c r="D173" t="s">
+        <v>54</v>
+      </c>
+      <c r="E173" t="s">
+        <v>33</v>
+      </c>
+      <c r="F173" t="s">
+        <v>13</v>
+      </c>
+      <c r="G173" t="s">
+        <v>308</v>
+      </c>
+      <c r="H173" t="s">
+        <v>602</v>
+      </c>
+      <c r="J173" t="s">
+        <v>662</v>
+      </c>
+      <c r="K173" t="s">
+        <v>55</v>
+      </c>
+      <c r="L173" t="s">
+        <v>14</v>
+      </c>
+      <c r="M173" t="s">
+        <v>15</v>
+      </c>
+      <c r="N173" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A174" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B174" t="s">
+        <v>661</v>
+      </c>
+      <c r="C174" t="s">
+        <v>664</v>
+      </c>
+      <c r="D174" t="s">
+        <v>54</v>
+      </c>
+      <c r="E174" t="s">
+        <v>58</v>
+      </c>
+      <c r="F174" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174" t="s">
+        <v>167</v>
+      </c>
+      <c r="H174" t="s">
+        <v>304</v>
+      </c>
+      <c r="I174" t="s">
+        <v>82</v>
+      </c>
+      <c r="J174" t="s">
+        <v>652</v>
+      </c>
+      <c r="K174" t="s">
+        <v>55</v>
+      </c>
+      <c r="L174" t="s">
+        <v>14</v>
+      </c>
+      <c r="M174" t="s">
+        <v>15</v>
+      </c>
+      <c r="N174" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A175" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B175" t="s">
+        <v>665</v>
+      </c>
+      <c r="C175" t="s">
+        <v>666</v>
+      </c>
+      <c r="D175" t="s">
+        <v>54</v>
+      </c>
+      <c r="E175" t="s">
+        <v>133</v>
+      </c>
+      <c r="F175" t="s">
+        <v>13</v>
+      </c>
+      <c r="G175" t="s">
+        <v>119</v>
+      </c>
+      <c r="H175" t="s">
+        <v>153</v>
+      </c>
+      <c r="J175" t="s">
+        <v>449</v>
+      </c>
+      <c r="K175" t="s">
+        <v>55</v>
+      </c>
+      <c r="L175" t="s">
+        <v>14</v>
+      </c>
+      <c r="M175" t="s">
+        <v>15</v>
+      </c>
+      <c r="N175" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5222171-3787-B641-8A2E-D1D0BF30D9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBE69E1-ABD8-444C-AEF1-7C319B14E731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="693">
   <si>
     <t>id</t>
   </si>
@@ -1963,9 +1963,6 @@
     <t>Hoy puede ser…</t>
   </si>
   <si>
-    <t>Wonderfulismo realista</t>
-  </si>
-  <si>
     <t>Runners Maristas</t>
   </si>
   <si>
@@ -1975,9 +1972,6 @@
     <t>Fundación Marcelino Champagnat Huelva</t>
   </si>
   <si>
-    <t>20 años de Nuevo Horizonte, 1994</t>
-  </si>
-  <si>
     <t>textil;postal</t>
   </si>
   <si>
@@ -2021,6 +2015,90 @@
   </si>
   <si>
     <t>Nuestro recurso ordinario</t>
+  </si>
+  <si>
+    <t>ILU-0102</t>
+  </si>
+  <si>
+    <t>ILU-0103</t>
+  </si>
+  <si>
+    <t>ILU-0104</t>
+  </si>
+  <si>
+    <t>ILU-0105</t>
+  </si>
+  <si>
+    <t>Cine Marista</t>
+  </si>
+  <si>
+    <t>Para equipo comunicación Mediterránea</t>
+  </si>
+  <si>
+    <t>Dando color, Dando Calor (Badajoz)</t>
+  </si>
+  <si>
+    <t>social</t>
+  </si>
+  <si>
+    <t>Haced vosotros lo mismo</t>
+  </si>
+  <si>
+    <t>Claretianos</t>
+  </si>
+  <si>
+    <t>Brindamos</t>
+  </si>
+  <si>
+    <t>El vino nuevo</t>
+  </si>
+  <si>
+    <t>20 años de Nuevo Horizonte, (1994)</t>
+  </si>
+  <si>
+    <t>DIS-0074</t>
+  </si>
+  <si>
+    <t>DIS-0076</t>
+  </si>
+  <si>
+    <t>DIS-0075</t>
+  </si>
+  <si>
+    <t>DIS-0077</t>
+  </si>
+  <si>
+    <t>Parte cuadro lavatorio Jueves Santo</t>
+  </si>
+  <si>
+    <t>Wonderfulismo realista en lunes</t>
+  </si>
+  <si>
+    <t>Navidad en el Mediterráneo</t>
+  </si>
+  <si>
+    <t>Felicitación EPP Mediterránea</t>
+  </si>
+  <si>
+    <t>social;educacion;evangelio</t>
+  </si>
+  <si>
+    <t>No hay Amor más grande</t>
+  </si>
+  <si>
+    <t>Para tiempo Cuaresma III Mediterránea (esp)</t>
+  </si>
+  <si>
+    <t>Por favor, Paz</t>
+  </si>
+  <si>
+    <t>Camiseta (1993) con necesidad actual</t>
+  </si>
+  <si>
+    <t>En lo secreto</t>
+  </si>
+  <si>
+    <t>Viñeta 'Al fin, luz'</t>
   </si>
 </sst>
 </file>
@@ -2377,7 +2455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N175"/>
+  <dimension ref="A1:N183"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
@@ -9585,7 +9663,7 @@
         <v>646</v>
       </c>
       <c r="C168" t="s">
-        <v>647</v>
+        <v>683</v>
       </c>
       <c r="D168" t="s">
         <v>85</v>
@@ -9623,10 +9701,10 @@
         <v>642</v>
       </c>
       <c r="B169" t="s">
+        <v>647</v>
+      </c>
+      <c r="C169" t="s">
         <v>648</v>
-      </c>
-      <c r="C169" t="s">
-        <v>649</v>
       </c>
       <c r="D169" t="s">
         <v>85</v>
@@ -9647,7 +9725,7 @@
         <v>61</v>
       </c>
       <c r="J169" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="K169" t="s">
         <v>55</v>
@@ -9667,10 +9745,10 @@
         <v>643</v>
       </c>
       <c r="B170" t="s">
-        <v>651</v>
+        <v>677</v>
       </c>
       <c r="C170" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D170" t="s">
         <v>85</v>
@@ -9691,7 +9769,7 @@
         <v>82</v>
       </c>
       <c r="J170" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="K170" t="s">
         <v>55</v>
@@ -9708,13 +9786,13 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B171" t="s">
         <v>550</v>
       </c>
       <c r="C171" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D171" t="s">
         <v>54</v>
@@ -9749,10 +9827,10 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B172" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C172" t="s">
         <v>446</v>
@@ -9790,10 +9868,10 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B173" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C173" t="s">
         <v>446</v>
@@ -9814,7 +9892,7 @@
         <v>602</v>
       </c>
       <c r="J173" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K173" t="s">
         <v>55</v>
@@ -9831,13 +9909,13 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B174" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C174" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D174" t="s">
         <v>54</v>
@@ -9858,7 +9936,7 @@
         <v>82</v>
       </c>
       <c r="J174" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="K174" t="s">
         <v>55</v>
@@ -9875,13 +9953,13 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B175" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C175" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D175" t="s">
         <v>54</v>
@@ -9911,6 +9989,358 @@
         <v>15</v>
       </c>
       <c r="N175" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B176" t="s">
+        <v>669</v>
+      </c>
+      <c r="C176" t="s">
+        <v>670</v>
+      </c>
+      <c r="D176" t="s">
+        <v>54</v>
+      </c>
+      <c r="E176" t="s">
+        <v>33</v>
+      </c>
+      <c r="F176" t="s">
+        <v>13</v>
+      </c>
+      <c r="G176" t="s">
+        <v>167</v>
+      </c>
+      <c r="H176" t="s">
+        <v>565</v>
+      </c>
+      <c r="I176" t="s">
+        <v>166</v>
+      </c>
+      <c r="J176" t="s">
+        <v>208</v>
+      </c>
+      <c r="K176" t="s">
+        <v>55</v>
+      </c>
+      <c r="L176" t="s">
+        <v>14</v>
+      </c>
+      <c r="M176" t="s">
+        <v>15</v>
+      </c>
+      <c r="N176" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A177" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B177" t="s">
+        <v>671</v>
+      </c>
+      <c r="C177" t="s">
+        <v>631</v>
+      </c>
+      <c r="D177" t="s">
+        <v>54</v>
+      </c>
+      <c r="E177" t="s">
+        <v>58</v>
+      </c>
+      <c r="F177" t="s">
+        <v>13</v>
+      </c>
+      <c r="G177" t="s">
+        <v>167</v>
+      </c>
+      <c r="H177" t="s">
+        <v>672</v>
+      </c>
+      <c r="I177" t="s">
+        <v>156</v>
+      </c>
+      <c r="J177" t="s">
+        <v>208</v>
+      </c>
+      <c r="K177" t="s">
+        <v>55</v>
+      </c>
+      <c r="L177" t="s">
+        <v>14</v>
+      </c>
+      <c r="M177" t="s">
+        <v>15</v>
+      </c>
+      <c r="N177" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A178" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B178" t="s">
+        <v>673</v>
+      </c>
+      <c r="C178" t="s">
+        <v>682</v>
+      </c>
+      <c r="D178" t="s">
+        <v>54</v>
+      </c>
+      <c r="E178" t="s">
+        <v>33</v>
+      </c>
+      <c r="F178" t="s">
+        <v>32</v>
+      </c>
+      <c r="G178" t="s">
+        <v>674</v>
+      </c>
+      <c r="H178" t="s">
+        <v>318</v>
+      </c>
+      <c r="I178" t="s">
+        <v>82</v>
+      </c>
+      <c r="J178" t="s">
+        <v>650</v>
+      </c>
+      <c r="K178" t="s">
+        <v>55</v>
+      </c>
+      <c r="L178" t="s">
+        <v>14</v>
+      </c>
+      <c r="M178" t="s">
+        <v>15</v>
+      </c>
+      <c r="N178" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A179" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B179" t="s">
+        <v>675</v>
+      </c>
+      <c r="C179" t="s">
+        <v>676</v>
+      </c>
+      <c r="D179" t="s">
+        <v>54</v>
+      </c>
+      <c r="E179" t="s">
+        <v>33</v>
+      </c>
+      <c r="F179" t="s">
+        <v>13</v>
+      </c>
+      <c r="G179" t="s">
+        <v>167</v>
+      </c>
+      <c r="H179" t="s">
+        <v>561</v>
+      </c>
+      <c r="I179" t="s">
+        <v>61</v>
+      </c>
+      <c r="J179" t="s">
+        <v>209</v>
+      </c>
+      <c r="K179" t="s">
+        <v>55</v>
+      </c>
+      <c r="L179" t="s">
+        <v>14</v>
+      </c>
+      <c r="M179" t="s">
+        <v>15</v>
+      </c>
+      <c r="N179" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A180" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B180" t="s">
+        <v>684</v>
+      </c>
+      <c r="C180" t="s">
+        <v>685</v>
+      </c>
+      <c r="D180" t="s">
+        <v>85</v>
+      </c>
+      <c r="E180" t="s">
+        <v>33</v>
+      </c>
+      <c r="F180" t="s">
+        <v>13</v>
+      </c>
+      <c r="G180" t="s">
+        <v>308</v>
+      </c>
+      <c r="H180" t="s">
+        <v>686</v>
+      </c>
+      <c r="I180" t="s">
+        <v>60</v>
+      </c>
+      <c r="J180" t="s">
+        <v>571</v>
+      </c>
+      <c r="K180" t="s">
+        <v>55</v>
+      </c>
+      <c r="L180" t="s">
+        <v>14</v>
+      </c>
+      <c r="M180" t="s">
+        <v>15</v>
+      </c>
+      <c r="N180" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A181" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B181" t="s">
+        <v>687</v>
+      </c>
+      <c r="C181" t="s">
+        <v>688</v>
+      </c>
+      <c r="D181" t="s">
+        <v>85</v>
+      </c>
+      <c r="E181" t="s">
+        <v>58</v>
+      </c>
+      <c r="F181" t="s">
+        <v>13</v>
+      </c>
+      <c r="G181" t="s">
+        <v>308</v>
+      </c>
+      <c r="H181" t="s">
+        <v>567</v>
+      </c>
+      <c r="I181" t="s">
+        <v>82</v>
+      </c>
+      <c r="J181" t="s">
+        <v>172</v>
+      </c>
+      <c r="K181" t="s">
+        <v>55</v>
+      </c>
+      <c r="L181" t="s">
+        <v>14</v>
+      </c>
+      <c r="M181" t="s">
+        <v>15</v>
+      </c>
+      <c r="N181" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A182" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B182" t="s">
+        <v>689</v>
+      </c>
+      <c r="C182" t="s">
+        <v>690</v>
+      </c>
+      <c r="D182" t="s">
+        <v>85</v>
+      </c>
+      <c r="E182" t="s">
+        <v>58</v>
+      </c>
+      <c r="F182" t="s">
+        <v>13</v>
+      </c>
+      <c r="G182" t="s">
+        <v>167</v>
+      </c>
+      <c r="H182" t="s">
+        <v>565</v>
+      </c>
+      <c r="I182" t="s">
+        <v>82</v>
+      </c>
+      <c r="J182" t="s">
+        <v>218</v>
+      </c>
+      <c r="K182" t="s">
+        <v>55</v>
+      </c>
+      <c r="L182" t="s">
+        <v>14</v>
+      </c>
+      <c r="M182" t="s">
+        <v>15</v>
+      </c>
+      <c r="N182" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A183" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B183" t="s">
+        <v>691</v>
+      </c>
+      <c r="C183" t="s">
+        <v>692</v>
+      </c>
+      <c r="D183" t="s">
+        <v>85</v>
+      </c>
+      <c r="E183" t="s">
+        <v>58</v>
+      </c>
+      <c r="F183" t="s">
+        <v>13</v>
+      </c>
+      <c r="G183" t="s">
+        <v>167</v>
+      </c>
+      <c r="H183" t="s">
+        <v>318</v>
+      </c>
+      <c r="I183" t="s">
+        <v>82</v>
+      </c>
+      <c r="J183" t="s">
+        <v>102</v>
+      </c>
+      <c r="K183" t="s">
+        <v>56</v>
+      </c>
+      <c r="L183" t="s">
+        <v>14</v>
+      </c>
+      <c r="M183" t="s">
+        <v>15</v>
+      </c>
+      <c r="N183" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBE69E1-ABD8-444C-AEF1-7C319B14E731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFB46FF-D57C-3B4B-8683-52A9C2FFB76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="751">
   <si>
     <t>id</t>
   </si>
@@ -850,9 +850,6 @@
     <t>Camiseta Da Vida 2025 (espalda)</t>
   </si>
   <si>
-    <t>Sticker G de Grupos</t>
-  </si>
-  <si>
     <t>Camiseta a better World 2016</t>
   </si>
   <si>
@@ -1075,9 +1072,6 @@
     <t>Eucaristía</t>
   </si>
   <si>
-    <t>Para Primera Eucaristía Sevilla 2017</t>
-  </si>
-  <si>
     <t>evangelio;GVX</t>
   </si>
   <si>
@@ -1126,9 +1120,6 @@
     <t>Faros de Esperanza</t>
   </si>
   <si>
-    <t>Para Capítulo Prov Mediterránea</t>
-  </si>
-  <si>
     <t>…una casa acogliente</t>
   </si>
   <si>
@@ -1468,12 +1459,6 @@
     <t>Change &lt; &gt; Chance</t>
   </si>
   <si>
-    <t>Cartel 2025 Mediterránea</t>
-  </si>
-  <si>
-    <t>Cartel 2022 Mediterránea</t>
-  </si>
-  <si>
     <t>Recordando al Hno Boni FQ</t>
   </si>
   <si>
@@ -1939,9 +1924,6 @@
     <t>A_Arroyo</t>
   </si>
   <si>
-    <t>Be Marist Brother punto com</t>
-  </si>
-  <si>
     <t>DIS-0070</t>
   </si>
   <si>
@@ -2008,9 +1990,6 @@
     <t>textil;sticker;taza</t>
   </si>
   <si>
-    <t>Nueva versión de camiseta GVX Sevilla 1993</t>
-  </si>
-  <si>
     <t>Mi Buena Madre (esp)</t>
   </si>
   <si>
@@ -2099,6 +2078,201 @@
   </si>
   <si>
     <t>Viñeta 'Al fin, luz'</t>
+  </si>
+  <si>
+    <t>Para Asamblea Mediterránea 2018</t>
+  </si>
+  <si>
+    <t>Para Capítulo Prov Mediterránea 2021</t>
+  </si>
+  <si>
+    <t>Nueva versión de camiseta GVX Sevilla (1993)</t>
+  </si>
+  <si>
+    <t>ILU-0106</t>
+  </si>
+  <si>
+    <t>ILU-0107</t>
+  </si>
+  <si>
+    <t>ILU-0108</t>
+  </si>
+  <si>
+    <t>ILU-0109</t>
+  </si>
+  <si>
+    <t>ILU-0110</t>
+  </si>
+  <si>
+    <t>ILU-0111</t>
+  </si>
+  <si>
+    <t>ILU-0112</t>
+  </si>
+  <si>
+    <t>ILU-0113</t>
+  </si>
+  <si>
+    <t>ILU-0114</t>
+  </si>
+  <si>
+    <t>ILU-0115</t>
+  </si>
+  <si>
+    <t>ILU-0116</t>
+  </si>
+  <si>
+    <t>DIS-0078</t>
+  </si>
+  <si>
+    <t>DIS-0079</t>
+  </si>
+  <si>
+    <t>DIS-0080</t>
+  </si>
+  <si>
+    <t>DIS-0081</t>
+  </si>
+  <si>
+    <t>DIS-0082</t>
+  </si>
+  <si>
+    <t>DIS-0083</t>
+  </si>
+  <si>
+    <t>DIS-0084</t>
+  </si>
+  <si>
+    <t>DIS-0085</t>
+  </si>
+  <si>
+    <t>DIS-0086</t>
+  </si>
+  <si>
+    <t>Cartel Asamblea Mediterránea 2018</t>
+  </si>
+  <si>
+    <t>Maristas Champions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiseta Voluntarios </t>
+  </si>
+  <si>
+    <t>II Jornadas Educadores Maristas</t>
+  </si>
+  <si>
+    <t>Cartel Jornadas 2017 Mediterránea</t>
+  </si>
+  <si>
+    <t>III Jornadas Educadores Maristas (fra)</t>
+  </si>
+  <si>
+    <t>Cartel Jornadas 2019 Mediterránea</t>
+  </si>
+  <si>
+    <t>Cartel Jornadas 2022 Mediterránea</t>
+  </si>
+  <si>
+    <t>Cartel Jornadas 2025 Mediterránea</t>
+  </si>
+  <si>
+    <t>Para GIX Sevilla 2017</t>
+  </si>
+  <si>
+    <t>Be Marist Brother (punto) com</t>
+  </si>
+  <si>
+    <t>G de Grupos</t>
+  </si>
+  <si>
+    <t>Maristas Innova 2017</t>
+  </si>
+  <si>
+    <t>Para Jornadas 2017 Mediterránea</t>
+  </si>
+  <si>
+    <t>Agenda Escolar Sevilla 2012-2013</t>
+  </si>
+  <si>
+    <t>Portada y contraportada</t>
+  </si>
+  <si>
+    <t>Agenda Escolar Sevilla 2011-2012</t>
+  </si>
+  <si>
+    <t>Portada y contraportada (con escudos maristas)</t>
+  </si>
+  <si>
+    <t>Occupiamo il futuro</t>
+  </si>
+  <si>
+    <t>Para asamblea zona Italia</t>
+  </si>
+  <si>
+    <t>Buen Camino</t>
+  </si>
+  <si>
+    <t>Camiseta Camino Pastoral Sevilla 2018</t>
+  </si>
+  <si>
+    <t>Mascota asamblea</t>
+  </si>
+  <si>
+    <t>Probando ideas</t>
+  </si>
+  <si>
+    <t>Real wi-fi</t>
+  </si>
+  <si>
+    <t>También parte del cartel 'Sonríe de corazón' MRE</t>
+  </si>
+  <si>
+    <t>Avión de papel</t>
+  </si>
+  <si>
+    <t>Maori Marist Pillars I</t>
+  </si>
+  <si>
+    <t>Maori Marist Pillars II</t>
+  </si>
+  <si>
+    <t>Maori Marist Pillars III</t>
+  </si>
+  <si>
+    <t>Maori Marist Pillars IV</t>
+  </si>
+  <si>
+    <t>Maori Marist Pillars V</t>
+  </si>
+  <si>
+    <t>Marist_NewZealand</t>
+  </si>
+  <si>
+    <t>Amor al trabajo (eng, mao)</t>
+  </si>
+  <si>
+    <t>Sencillez (eng, mao)</t>
+  </si>
+  <si>
+    <t>Al estilo de María (eng, mao)</t>
+  </si>
+  <si>
+    <t>Presencia (eng, mao)</t>
+  </si>
+  <si>
+    <t>Espíritu de familia (eng, mao)</t>
+  </si>
+  <si>
+    <t>La chasca</t>
+  </si>
+  <si>
+    <t>María, Buena Madre V</t>
+  </si>
+  <si>
+    <t>Para capilla colegio S Pio XII Roma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasión </t>
   </si>
 </sst>
 </file>
@@ -2455,15 +2629,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N183"/>
+  <dimension ref="A1:N203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="36.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" customWidth="1"/>
     <col min="5" max="5" width="7.83203125" customWidth="1"/>
     <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="19.5" customWidth="1"/>
+    <col min="7" max="7" width="26.1640625" customWidth="1"/>
     <col min="8" max="8" width="30.1640625" customWidth="1"/>
     <col min="9" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.5" customWidth="1"/>
@@ -2521,7 +2695,7 @@
         <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D2" t="s">
         <v>54</v>
@@ -2565,7 +2739,7 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D3" t="s">
         <v>54</v>
@@ -2583,7 +2757,7 @@
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="J3" t="s">
         <v>208</v>
@@ -2606,7 +2780,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C4" t="s">
         <v>86</v>
@@ -2776,7 +2950,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -2797,7 +2971,7 @@
         <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="K8" t="s">
         <v>55</v>
@@ -2861,7 +3035,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C10" t="s">
         <v>90</v>
@@ -2905,7 +3079,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
@@ -2949,7 +3123,7 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C12" t="s">
         <v>92</v>
@@ -2993,7 +3167,7 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C13" t="s">
         <v>93</v>
@@ -3037,7 +3211,7 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C14" t="s">
         <v>94</v>
@@ -3099,7 +3273,7 @@
         <v>251</v>
       </c>
       <c r="H15" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="I15" t="s">
         <v>101</v>
@@ -3140,7 +3314,7 @@
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="H16" t="s">
         <v>28</v>
@@ -3184,7 +3358,7 @@
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="H17" t="s">
         <v>59</v>
@@ -3228,10 +3402,10 @@
         <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="H18" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="J18" t="s">
         <v>208</v>
@@ -3269,7 +3443,7 @@
         <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H19" t="s">
         <v>28</v>
@@ -3398,7 +3572,7 @@
         <v>167</v>
       </c>
       <c r="H22" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="I22" t="s">
         <v>61</v>
@@ -3483,7 +3657,7 @@
         <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H24" t="s">
         <v>28</v>
@@ -3527,7 +3701,7 @@
         <v>169</v>
       </c>
       <c r="H25" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="J25" t="s">
         <v>83</v>
@@ -3568,7 +3742,7 @@
         <v>169</v>
       </c>
       <c r="H26" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="J26" t="s">
         <v>102</v>
@@ -3656,7 +3830,7 @@
         <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="K28" t="s">
         <v>56</v>
@@ -3694,7 +3868,7 @@
         <v>97</v>
       </c>
       <c r="H29" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I29" t="s">
         <v>82</v>
@@ -3820,7 +3994,7 @@
         <v>167</v>
       </c>
       <c r="H32" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="J32" t="s">
         <v>102</v>
@@ -3861,7 +4035,7 @@
         <v>167</v>
       </c>
       <c r="H33" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="J33" t="s">
         <v>102</v>
@@ -3993,7 +4167,7 @@
         <v>166</v>
       </c>
       <c r="J36" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="K36" t="s">
         <v>55</v>
@@ -4251,7 +4425,7 @@
         <v>167</v>
       </c>
       <c r="H42" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="I42" t="s">
         <v>61</v>
@@ -4280,7 +4454,7 @@
         <v>246</v>
       </c>
       <c r="C43" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D43" t="s">
         <v>54</v>
@@ -4295,7 +4469,7 @@
         <v>167</v>
       </c>
       <c r="H43" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="I43" t="s">
         <v>61</v>
@@ -4339,7 +4513,7 @@
         <v>167</v>
       </c>
       <c r="H44" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="I44" t="s">
         <v>61</v>
@@ -4383,7 +4557,7 @@
         <v>167</v>
       </c>
       <c r="H45" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="I45" t="s">
         <v>156</v>
@@ -4406,13 +4580,13 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B46" t="s">
         <v>281</v>
       </c>
-      <c r="B46" t="s">
-        <v>282</v>
-      </c>
       <c r="C46" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D46" t="s">
         <v>54</v>
@@ -4427,7 +4601,7 @@
         <v>167</v>
       </c>
       <c r="H46" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I46" t="s">
         <v>166</v>
@@ -4450,13 +4624,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B47" t="s">
         <v>283</v>
       </c>
-      <c r="B47" t="s">
-        <v>284</v>
-      </c>
       <c r="C47" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D47" t="s">
         <v>54</v>
@@ -4471,7 +4645,7 @@
         <v>167</v>
       </c>
       <c r="H47" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I47" t="s">
         <v>166</v>
@@ -4494,13 +4668,13 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B48" t="s">
+        <v>294</v>
+      </c>
+      <c r="C48" t="s">
         <v>295</v>
-      </c>
-      <c r="C48" t="s">
-        <v>296</v>
       </c>
       <c r="D48" t="s">
         <v>54</v>
@@ -4521,7 +4695,7 @@
         <v>60</v>
       </c>
       <c r="J48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K48" t="s">
         <v>55</v>
@@ -4538,13 +4712,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B49" t="s">
+        <v>296</v>
+      </c>
+      <c r="C49" t="s">
         <v>297</v>
-      </c>
-      <c r="C49" t="s">
-        <v>298</v>
       </c>
       <c r="D49" t="s">
         <v>54</v>
@@ -4559,7 +4733,7 @@
         <v>167</v>
       </c>
       <c r="H49" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I49" t="s">
         <v>156</v>
@@ -4582,13 +4756,13 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D50" t="s">
         <v>54</v>
@@ -4603,7 +4777,7 @@
         <v>119</v>
       </c>
       <c r="H50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I50" t="s">
         <v>156</v>
@@ -4626,13 +4800,13 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B51" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C51" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D51" t="s">
         <v>54</v>
@@ -4647,7 +4821,7 @@
         <v>119</v>
       </c>
       <c r="H51" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I51" t="s">
         <v>156</v>
@@ -4670,13 +4844,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B52" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C52" t="s">
-        <v>306</v>
+        <v>686</v>
       </c>
       <c r="D52" t="s">
         <v>54</v>
@@ -4688,7 +4862,7 @@
         <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H52" t="s">
         <v>120</v>
@@ -4714,13 +4888,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B53" t="s">
+        <v>312</v>
+      </c>
+      <c r="C53" t="s">
         <v>313</v>
-      </c>
-      <c r="C53" t="s">
-        <v>314</v>
       </c>
       <c r="D53" t="s">
         <v>54</v>
@@ -4735,7 +4909,7 @@
         <v>167</v>
       </c>
       <c r="H53" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I53" t="s">
         <v>61</v>
@@ -4758,13 +4932,13 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B54" t="s">
+        <v>315</v>
+      </c>
+      <c r="C54" t="s">
         <v>316</v>
-      </c>
-      <c r="C54" t="s">
-        <v>317</v>
       </c>
       <c r="D54" t="s">
         <v>54</v>
@@ -4779,7 +4953,7 @@
         <v>167</v>
       </c>
       <c r="H54" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J54" t="s">
         <v>102</v>
@@ -4799,13 +4973,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B55" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C55" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D55" t="s">
         <v>54</v>
@@ -4817,16 +4991,16 @@
         <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H55" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I55" t="s">
         <v>156</v>
       </c>
       <c r="J55" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -4843,13 +5017,13 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B56" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D56" t="s">
         <v>54</v>
@@ -4864,13 +5038,13 @@
         <v>167</v>
       </c>
       <c r="H56" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I56" t="s">
         <v>166</v>
       </c>
       <c r="J56" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K56" t="s">
         <v>55</v>
@@ -4887,13 +5061,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B57" t="s">
+        <v>324</v>
+      </c>
+      <c r="C57" t="s">
         <v>325</v>
-      </c>
-      <c r="C57" t="s">
-        <v>326</v>
       </c>
       <c r="D57" t="s">
         <v>54</v>
@@ -4928,13 +5102,13 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C58" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D58" t="s">
         <v>54</v>
@@ -4946,10 +5120,10 @@
         <v>32</v>
       </c>
       <c r="G58" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H58" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="I58" t="s">
         <v>237</v>
@@ -4972,13 +5146,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C59" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D59" t="s">
         <v>54</v>
@@ -4993,7 +5167,7 @@
         <v>171</v>
       </c>
       <c r="H59" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="J59" t="s">
         <v>102</v>
@@ -5013,13 +5187,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B60" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C60" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D60" t="s">
         <v>54</v>
@@ -5031,10 +5205,10 @@
         <v>32</v>
       </c>
       <c r="G60" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H60" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="I60" t="s">
         <v>60</v>
@@ -5057,13 +5231,13 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C61" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D61" t="s">
         <v>54</v>
@@ -5075,13 +5249,13 @@
         <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H61" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J61" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -5098,13 +5272,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C62" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D62" t="s">
         <v>54</v>
@@ -5116,10 +5290,10 @@
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H62" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I62" t="s">
         <v>82</v>
@@ -5142,13 +5316,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C63" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D63" t="s">
         <v>54</v>
@@ -5160,16 +5334,16 @@
         <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H63" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I63" t="s">
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K63" t="s">
         <v>55</v>
@@ -5186,13 +5360,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B64" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C64" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D64" t="s">
         <v>54</v>
@@ -5204,10 +5378,10 @@
         <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H64" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="J64" t="s">
         <v>172</v>
@@ -5227,13 +5401,13 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B65" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C65" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D65" t="s">
         <v>54</v>
@@ -5268,13 +5442,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B66" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C66" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D66" t="s">
         <v>54</v>
@@ -5289,7 +5463,7 @@
         <v>253</v>
       </c>
       <c r="H66" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="I66" t="s">
         <v>61</v>
@@ -5312,13 +5486,13 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B67" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C67" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D67" t="s">
         <v>54</v>
@@ -5330,13 +5504,13 @@
         <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H67" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="J67" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K67" t="s">
         <v>55</v>
@@ -5353,13 +5527,13 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B68" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C68" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D68" t="s">
         <v>54</v>
@@ -5374,10 +5548,10 @@
         <v>167</v>
       </c>
       <c r="H68" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="J68" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K68" t="s">
         <v>55</v>
@@ -5394,13 +5568,13 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B69" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C69" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D69" t="s">
         <v>54</v>
@@ -5438,13 +5612,13 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B70" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C70" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D70" t="s">
         <v>54</v>
@@ -5459,7 +5633,7 @@
         <v>119</v>
       </c>
       <c r="H70" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J70" t="s">
         <v>207</v>
@@ -5479,13 +5653,13 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C71" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D71" t="s">
         <v>54</v>
@@ -5500,7 +5674,7 @@
         <v>169</v>
       </c>
       <c r="H71" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I71" t="s">
         <v>61</v>
@@ -5523,13 +5697,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C72" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D72" t="s">
         <v>54</v>
@@ -5544,7 +5718,7 @@
         <v>167</v>
       </c>
       <c r="H72" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J72" t="s">
         <v>227</v>
@@ -5564,13 +5738,13 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B73" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C73" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D73" t="s">
         <v>54</v>
@@ -5585,7 +5759,7 @@
         <v>167</v>
       </c>
       <c r="H73" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="J73" t="s">
         <v>208</v>
@@ -5605,13 +5779,13 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B74" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C74" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D74" t="s">
         <v>54</v>
@@ -5629,7 +5803,7 @@
         <v>153</v>
       </c>
       <c r="I74" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="J74" t="s">
         <v>208</v>
@@ -5649,13 +5823,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B75" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C75" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D75" t="s">
         <v>54</v>
@@ -5693,13 +5867,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B76" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C76" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D76" t="s">
         <v>54</v>
@@ -5714,7 +5888,7 @@
         <v>167</v>
       </c>
       <c r="H76" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="I76" t="s">
         <v>61</v>
@@ -5737,13 +5911,13 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B77" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C77" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D77" t="s">
         <v>54</v>
@@ -5758,7 +5932,7 @@
         <v>167</v>
       </c>
       <c r="H77" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I77" t="s">
         <v>61</v>
@@ -5781,13 +5955,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B78" t="s">
+        <v>488</v>
+      </c>
+      <c r="C78" t="s">
         <v>489</v>
-      </c>
-      <c r="B78" t="s">
-        <v>493</v>
-      </c>
-      <c r="C78" t="s">
-        <v>494</v>
       </c>
       <c r="D78" t="s">
         <v>54</v>
@@ -5802,7 +5976,7 @@
         <v>167</v>
       </c>
       <c r="H78" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I78" t="s">
         <v>61</v>
@@ -5825,13 +5999,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B79" t="s">
         <v>490</v>
       </c>
-      <c r="B79" t="s">
-        <v>495</v>
-      </c>
       <c r="C79" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D79" t="s">
         <v>54</v>
@@ -5843,16 +6017,16 @@
         <v>32</v>
       </c>
       <c r="G79" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="H79" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="I79" t="s">
         <v>61</v>
       </c>
       <c r="J79" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K79" t="s">
         <v>55</v>
@@ -5869,13 +6043,13 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B80" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C80" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="D80" t="s">
         <v>54</v>
@@ -5890,7 +6064,7 @@
         <v>167</v>
       </c>
       <c r="H80" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="I80" t="s">
         <v>61</v>
@@ -5913,13 +6087,13 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B81" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C81" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D81" t="s">
         <v>54</v>
@@ -5934,7 +6108,7 @@
         <v>167</v>
       </c>
       <c r="H81" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="I81" t="s">
         <v>61</v>
@@ -5957,13 +6131,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B82" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C82" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D82" t="s">
         <v>54</v>
@@ -5978,7 +6152,7 @@
         <v>119</v>
       </c>
       <c r="H82" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="I82" t="s">
         <v>61</v>
@@ -6001,13 +6175,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B83" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C83" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D83" t="s">
         <v>54</v>
@@ -6045,13 +6219,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B84" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C84" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D84" t="s">
         <v>54</v>
@@ -6066,7 +6240,7 @@
         <v>167</v>
       </c>
       <c r="H84" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="I84" t="s">
         <v>61</v>
@@ -6089,13 +6263,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B85" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C85" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="D85" t="s">
         <v>54</v>
@@ -6107,10 +6281,10 @@
         <v>32</v>
       </c>
       <c r="G85" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="H85" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="I85" t="s">
         <v>61</v>
@@ -6133,13 +6307,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B86" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C86" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="D86" t="s">
         <v>54</v>
@@ -6154,7 +6328,7 @@
         <v>118</v>
       </c>
       <c r="H86" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="I86" t="s">
         <v>61</v>
@@ -6177,13 +6351,13 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B87" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C87" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="D87" t="s">
         <v>54</v>
@@ -6198,7 +6372,7 @@
         <v>167</v>
       </c>
       <c r="H87" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="I87" t="s">
         <v>61</v>
@@ -6221,13 +6395,13 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B88" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C88" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="D88" t="s">
         <v>54</v>
@@ -6265,13 +6439,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B89" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C89" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D89" t="s">
         <v>54</v>
@@ -6286,7 +6460,7 @@
         <v>169</v>
       </c>
       <c r="H89" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="I89" t="s">
         <v>61</v>
@@ -6309,13 +6483,13 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B90" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C90" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D90" t="s">
         <v>54</v>
@@ -6353,13 +6527,13 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B91" t="s">
         <v>572</v>
       </c>
-      <c r="B91" t="s">
-        <v>577</v>
-      </c>
       <c r="C91" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="D91" t="s">
         <v>54</v>
@@ -6374,13 +6548,13 @@
         <v>253</v>
       </c>
       <c r="H91" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="I91" t="s">
         <v>82</v>
       </c>
       <c r="J91" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="K91" t="s">
         <v>55</v>
@@ -6397,13 +6571,13 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B92" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C92" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="D92" t="s">
         <v>54</v>
@@ -6418,7 +6592,7 @@
         <v>253</v>
       </c>
       <c r="H92" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J92" t="s">
         <v>84</v>
@@ -6438,13 +6612,13 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B93" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C93" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D93" t="s">
         <v>54</v>
@@ -6459,7 +6633,7 @@
         <v>253</v>
       </c>
       <c r="H93" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I93" t="s">
         <v>61</v>
@@ -6482,13 +6656,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B94" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C94" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="D94" t="s">
         <v>54</v>
@@ -6503,13 +6677,13 @@
         <v>167</v>
       </c>
       <c r="H94" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I94" t="s">
         <v>61</v>
       </c>
       <c r="J94" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K94" t="s">
         <v>55</v>
@@ -6526,13 +6700,13 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B95" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C95" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="D95" t="s">
         <v>54</v>
@@ -6547,7 +6721,7 @@
         <v>169</v>
       </c>
       <c r="H95" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I95" t="s">
         <v>61</v>
@@ -6570,13 +6744,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B96" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C96" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="D96" t="s">
         <v>54</v>
@@ -6591,7 +6765,7 @@
         <v>167</v>
       </c>
       <c r="H96" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I96" t="s">
         <v>61</v>
@@ -6614,13 +6788,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B97" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C97" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D97" t="s">
         <v>54</v>
@@ -6635,13 +6809,13 @@
         <v>167</v>
       </c>
       <c r="H97" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I97" t="s">
         <v>82</v>
       </c>
       <c r="J97" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K97" t="s">
         <v>55</v>
@@ -6661,7 +6835,7 @@
         <v>63</v>
       </c>
       <c r="B98" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C98" t="s">
         <v>70</v>
@@ -6679,7 +6853,7 @@
         <v>167</v>
       </c>
       <c r="H98" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="I98" t="s">
         <v>103</v>
@@ -6723,7 +6897,7 @@
         <v>167</v>
       </c>
       <c r="H99" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="I99" t="s">
         <v>82</v>
@@ -6749,7 +6923,7 @@
         <v>65</v>
       </c>
       <c r="B100" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C100" t="s">
         <v>73</v>
@@ -6767,7 +6941,7 @@
         <v>167</v>
       </c>
       <c r="H100" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="I100" t="s">
         <v>101</v>
@@ -6796,7 +6970,7 @@
         <v>74</v>
       </c>
       <c r="C101" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D101" t="s">
         <v>85</v>
@@ -6811,7 +6985,7 @@
         <v>167</v>
       </c>
       <c r="H101" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="J101" t="s">
         <v>99</v>
@@ -6852,7 +7026,7 @@
         <v>119</v>
       </c>
       <c r="H102" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="I102" t="s">
         <v>82</v>
@@ -6881,7 +7055,7 @@
         <v>77</v>
       </c>
       <c r="C103" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D103" t="s">
         <v>85</v>
@@ -6896,7 +7070,7 @@
         <v>167</v>
       </c>
       <c r="H103" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="J103" t="s">
         <v>208</v>
@@ -6937,7 +7111,7 @@
         <v>254</v>
       </c>
       <c r="H104" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="I104" t="s">
         <v>82</v>
@@ -7136,13 +7310,13 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B109" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C109" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="D109" t="s">
         <v>85</v>
@@ -7154,10 +7328,10 @@
         <v>32</v>
       </c>
       <c r="G109" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="H109" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J109" t="s">
         <v>218</v>
@@ -7177,13 +7351,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B110" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C110" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="D110" t="s">
         <v>85</v>
@@ -7198,7 +7372,7 @@
         <v>167</v>
       </c>
       <c r="H110" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J110" t="s">
         <v>218</v>
@@ -7236,10 +7410,10 @@
         <v>13</v>
       </c>
       <c r="G111" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H111" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J111" t="s">
         <v>218</v>
@@ -7277,10 +7451,10 @@
         <v>13</v>
       </c>
       <c r="G112" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H112" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I112" t="s">
         <v>82</v>
@@ -7321,10 +7495,10 @@
         <v>13</v>
       </c>
       <c r="G113" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H113" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J113" t="s">
         <v>218</v>
@@ -7362,10 +7536,10 @@
         <v>13</v>
       </c>
       <c r="G114" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H114" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I114" t="s">
         <v>82</v>
@@ -7394,7 +7568,7 @@
         <v>193</v>
       </c>
       <c r="C115" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D115" t="s">
         <v>85</v>
@@ -7406,10 +7580,10 @@
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H115" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I115" t="s">
         <v>82</v>
@@ -7432,13 +7606,13 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B116" t="s">
         <v>588</v>
       </c>
-      <c r="B116" t="s">
-        <v>593</v>
-      </c>
       <c r="C116" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D116" t="s">
         <v>85</v>
@@ -7450,10 +7624,10 @@
         <v>13</v>
       </c>
       <c r="G116" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H116" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J116" t="s">
         <v>218</v>
@@ -7473,13 +7647,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B117" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C117" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D117" t="s">
         <v>85</v>
@@ -7491,10 +7665,10 @@
         <v>32</v>
       </c>
       <c r="G117" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H117" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I117" t="s">
         <v>82</v>
@@ -7517,13 +7691,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B118" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C118" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="D118" t="s">
         <v>85</v>
@@ -7535,10 +7709,10 @@
         <v>13</v>
       </c>
       <c r="G118" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H118" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J118" t="s">
         <v>218</v>
@@ -7561,7 +7735,7 @@
         <v>181</v>
       </c>
       <c r="B119" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C119" t="s">
         <v>194</v>
@@ -7576,10 +7750,10 @@
         <v>13</v>
       </c>
       <c r="G119" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H119" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="J119" t="s">
         <v>218</v>
@@ -7617,10 +7791,10 @@
         <v>13</v>
       </c>
       <c r="G120" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H120" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J120" t="s">
         <v>218</v>
@@ -7640,13 +7814,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B121" t="s">
+        <v>586</v>
+      </c>
+      <c r="C121" t="s">
         <v>587</v>
-      </c>
-      <c r="B121" t="s">
-        <v>591</v>
-      </c>
-      <c r="C121" t="s">
-        <v>592</v>
       </c>
       <c r="D121" t="s">
         <v>85</v>
@@ -7658,10 +7832,10 @@
         <v>13</v>
       </c>
       <c r="G121" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H121" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I121" t="s">
         <v>82</v>
@@ -7702,10 +7876,10 @@
         <v>13</v>
       </c>
       <c r="G122" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H122" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J122" t="s">
         <v>218</v>
@@ -7743,10 +7917,10 @@
         <v>13</v>
       </c>
       <c r="G123" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H123" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I123" t="s">
         <v>82</v>
@@ -7775,7 +7949,7 @@
         <v>264</v>
       </c>
       <c r="C124" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="D124" t="s">
         <v>85</v>
@@ -7787,10 +7961,10 @@
         <v>13</v>
       </c>
       <c r="G124" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H124" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I124" t="s">
         <v>265</v>
@@ -7831,10 +8005,10 @@
         <v>13</v>
       </c>
       <c r="G125" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H125" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J125" t="s">
         <v>218</v>
@@ -7860,7 +8034,7 @@
         <v>266</v>
       </c>
       <c r="C126" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D126" t="s">
         <v>85</v>
@@ -7872,10 +8046,10 @@
         <v>13</v>
       </c>
       <c r="G126" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H126" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I126" t="s">
         <v>82</v>
@@ -7916,10 +8090,10 @@
         <v>13</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H127" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I127" t="s">
         <v>82</v>
@@ -7942,13 +8116,13 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="B128" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="C128" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="D128" t="s">
         <v>85</v>
@@ -7960,10 +8134,10 @@
         <v>13</v>
       </c>
       <c r="G128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H128" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="I128" t="s">
         <v>61</v>
@@ -7986,13 +8160,13 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B129" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C129" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D129" t="s">
         <v>85</v>
@@ -8004,10 +8178,10 @@
         <v>13</v>
       </c>
       <c r="G129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H129" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J129" t="s">
         <v>218</v>
@@ -8030,7 +8204,7 @@
         <v>183</v>
       </c>
       <c r="B130" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C130" t="s">
         <v>198</v>
@@ -8045,10 +8219,10 @@
         <v>13</v>
       </c>
       <c r="G130" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H130" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I130" t="s">
         <v>82</v>
@@ -8089,10 +8263,10 @@
         <v>13</v>
       </c>
       <c r="G131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H131" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J131" t="s">
         <v>209</v>
@@ -8130,10 +8304,10 @@
         <v>13</v>
       </c>
       <c r="G132" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H132" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J132" t="s">
         <v>218</v>
@@ -8159,7 +8333,7 @@
         <v>205</v>
       </c>
       <c r="C133" t="s">
-        <v>639</v>
+        <v>719</v>
       </c>
       <c r="D133" t="s">
         <v>85</v>
@@ -8215,10 +8389,10 @@
         <v>13</v>
       </c>
       <c r="G134" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H134" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I134" t="s">
         <v>156</v>
@@ -8259,10 +8433,10 @@
         <v>13</v>
       </c>
       <c r="G135" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H135" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I135" t="s">
         <v>82</v>
@@ -8291,7 +8465,7 @@
         <v>273</v>
       </c>
       <c r="C136" t="s">
-        <v>276</v>
+        <v>720</v>
       </c>
       <c r="D136" t="s">
         <v>85</v>
@@ -8306,7 +8480,7 @@
         <v>167</v>
       </c>
       <c r="H136" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I136" t="s">
         <v>156</v>
@@ -8329,13 +8503,13 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B137" t="s">
+        <v>279</v>
+      </c>
+      <c r="C137" t="s">
         <v>278</v>
-      </c>
-      <c r="B137" t="s">
-        <v>280</v>
-      </c>
-      <c r="C137" t="s">
-        <v>279</v>
       </c>
       <c r="D137" t="s">
         <v>85</v>
@@ -8350,7 +8524,7 @@
         <v>167</v>
       </c>
       <c r="H137" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J137" t="s">
         <v>218</v>
@@ -8370,13 +8544,13 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B138" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C138" t="s">
-        <v>482</v>
+        <v>717</v>
       </c>
       <c r="D138" t="s">
         <v>85</v>
@@ -8388,7 +8562,7 @@
         <v>13</v>
       </c>
       <c r="G138" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H138" t="s">
         <v>233</v>
@@ -8411,13 +8585,13 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B139" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C139" t="s">
-        <v>351</v>
+        <v>718</v>
       </c>
       <c r="D139" t="s">
         <v>85</v>
@@ -8432,7 +8606,7 @@
         <v>169</v>
       </c>
       <c r="H139" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J139" t="s">
         <v>104</v>
@@ -8452,13 +8626,13 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B140" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C140" t="s">
-        <v>483</v>
+        <v>716</v>
       </c>
       <c r="D140" t="s">
         <v>85</v>
@@ -8470,7 +8644,7 @@
         <v>13</v>
       </c>
       <c r="G140" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H140" t="s">
         <v>233</v>
@@ -8493,13 +8667,13 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B141" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C141" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D141" t="s">
         <v>85</v>
@@ -8511,10 +8685,10 @@
         <v>13</v>
       </c>
       <c r="G141" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H141" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="I141" t="s">
         <v>156</v>
@@ -8537,13 +8711,13 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B142" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C142" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D142" t="s">
         <v>85</v>
@@ -8558,7 +8732,7 @@
         <v>167</v>
       </c>
       <c r="H142" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J142" t="s">
         <v>102</v>
@@ -8578,13 +8752,13 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B143" t="s">
+        <v>356</v>
+      </c>
+      <c r="C143" t="s">
         <v>358</v>
-      </c>
-      <c r="C143" t="s">
-        <v>360</v>
       </c>
       <c r="D143" t="s">
         <v>85</v>
@@ -8596,10 +8770,10 @@
         <v>13</v>
       </c>
       <c r="G143" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H143" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I143" t="s">
         <v>82</v>
@@ -8622,13 +8796,13 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B144" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C144" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D144" t="s">
         <v>85</v>
@@ -8640,10 +8814,10 @@
         <v>13</v>
       </c>
       <c r="G144" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H144" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="I144" t="s">
         <v>82</v>
@@ -8666,13 +8840,13 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B145" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C145" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D145" t="s">
         <v>85</v>
@@ -8687,7 +8861,7 @@
         <v>169</v>
       </c>
       <c r="H145" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="J145" t="s">
         <v>102</v>
@@ -8707,13 +8881,13 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B146" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C146" t="s">
-        <v>368</v>
+        <v>687</v>
       </c>
       <c r="D146" t="s">
         <v>85</v>
@@ -8725,7 +8899,7 @@
         <v>13</v>
       </c>
       <c r="G146" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H146" t="s">
         <v>120</v>
@@ -8748,13 +8922,13 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B147" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C147" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D147" t="s">
         <v>85</v>
@@ -8766,16 +8940,16 @@
         <v>13</v>
       </c>
       <c r="G147" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H147" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I147" t="s">
         <v>82</v>
       </c>
       <c r="J147" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="K147" t="s">
         <v>55</v>
@@ -8792,13 +8966,13 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B148" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C148" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D148" t="s">
         <v>85</v>
@@ -8810,10 +8984,10 @@
         <v>32</v>
       </c>
       <c r="G148" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H148" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I148" t="s">
         <v>82</v>
@@ -8836,13 +9010,13 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B149" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C149" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D149" t="s">
         <v>85</v>
@@ -8854,7 +9028,7 @@
         <v>13</v>
       </c>
       <c r="G149" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H149" t="s">
         <v>238</v>
@@ -8863,7 +9037,7 @@
         <v>82</v>
       </c>
       <c r="J149" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="K149" t="s">
         <v>55</v>
@@ -8880,13 +9054,13 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B150" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C150" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D150" t="s">
         <v>85</v>
@@ -8898,7 +9072,7 @@
         <v>13</v>
       </c>
       <c r="G150" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H150" t="s">
         <v>238</v>
@@ -8907,7 +9081,7 @@
         <v>82</v>
       </c>
       <c r="J150" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="K150" t="s">
         <v>55</v>
@@ -8924,13 +9098,13 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B151" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C151" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D151" t="s">
         <v>85</v>
@@ -8942,7 +9116,7 @@
         <v>13</v>
       </c>
       <c r="G151" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H151" t="s">
         <v>238</v>
@@ -8951,7 +9125,7 @@
         <v>82</v>
       </c>
       <c r="J151" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="K151" t="s">
         <v>55</v>
@@ -8968,13 +9142,13 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B152" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C152" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D152" t="s">
         <v>85</v>
@@ -8989,13 +9163,13 @@
         <v>167</v>
       </c>
       <c r="H152" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="I152" t="s">
         <v>156</v>
       </c>
       <c r="J152" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="K152" t="s">
         <v>55</v>
@@ -9012,13 +9186,13 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B153" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C153" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D153" t="s">
         <v>85</v>
@@ -9033,13 +9207,13 @@
         <v>253</v>
       </c>
       <c r="H153" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I153" t="s">
         <v>156</v>
       </c>
       <c r="J153" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="K153" t="s">
         <v>55</v>
@@ -9056,13 +9230,13 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B154" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C154" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D154" t="s">
         <v>85</v>
@@ -9077,7 +9251,7 @@
         <v>167</v>
       </c>
       <c r="H154" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="J154" t="s">
         <v>172</v>
@@ -9097,13 +9271,13 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B155" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C155" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D155" t="s">
         <v>85</v>
@@ -9118,7 +9292,7 @@
         <v>119</v>
       </c>
       <c r="H155" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="I155" t="s">
         <v>82</v>
@@ -9141,13 +9315,13 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B156" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C156" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="D156" t="s">
         <v>85</v>
@@ -9162,7 +9336,7 @@
         <v>167</v>
       </c>
       <c r="H156" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="I156" t="s">
         <v>82</v>
@@ -9185,13 +9359,13 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B157" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C157" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D157" t="s">
         <v>85</v>
@@ -9206,7 +9380,7 @@
         <v>167</v>
       </c>
       <c r="H157" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="J157" t="s">
         <v>211</v>
@@ -9226,13 +9400,13 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B158" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="C158" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="D158" t="s">
         <v>85</v>
@@ -9270,13 +9444,13 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B159" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C159" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D159" t="s">
         <v>85</v>
@@ -9291,7 +9465,7 @@
         <v>167</v>
       </c>
       <c r="H159" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I159" t="s">
         <v>82</v>
@@ -9314,13 +9488,13 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B160" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C160" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="D160" t="s">
         <v>85</v>
@@ -9332,10 +9506,10 @@
         <v>13</v>
       </c>
       <c r="G160" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H160" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="I160" t="s">
         <v>82</v>
@@ -9358,13 +9532,13 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B161" t="s">
+        <v>538</v>
+      </c>
+      <c r="C161" t="s">
         <v>535</v>
-      </c>
-      <c r="B161" t="s">
-        <v>543</v>
-      </c>
-      <c r="C161" t="s">
-        <v>540</v>
       </c>
       <c r="D161" t="s">
         <v>85</v>
@@ -9379,7 +9553,7 @@
         <v>167</v>
       </c>
       <c r="H161" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I161" t="s">
         <v>82</v>
@@ -9402,13 +9576,13 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B162" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C162" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="D162" t="s">
         <v>85</v>
@@ -9423,10 +9597,10 @@
         <v>167</v>
       </c>
       <c r="H162" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J162" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="K162" t="s">
         <v>55</v>
@@ -9443,13 +9617,13 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B163" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C163" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="D163" t="s">
         <v>85</v>
@@ -9484,13 +9658,13 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B164" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C164" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="D164" t="s">
         <v>85</v>
@@ -9502,10 +9676,10 @@
         <v>32</v>
       </c>
       <c r="G164" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="H164" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I164" t="s">
         <v>82</v>
@@ -9528,13 +9702,13 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B165" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C165" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="D165" t="s">
         <v>85</v>
@@ -9546,10 +9720,10 @@
         <v>13</v>
       </c>
       <c r="G165" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H165" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="I165" t="s">
         <v>156</v>
@@ -9572,13 +9746,13 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B166" t="s">
         <v>614</v>
       </c>
-      <c r="B166" t="s">
-        <v>619</v>
-      </c>
       <c r="C166" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="D166" t="s">
         <v>85</v>
@@ -9590,10 +9764,10 @@
         <v>13</v>
       </c>
       <c r="G166" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H166" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J166" t="s">
         <v>218</v>
@@ -9613,13 +9787,13 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B167" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C167" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D167" t="s">
         <v>85</v>
@@ -9634,7 +9808,7 @@
         <v>167</v>
       </c>
       <c r="H167" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="I167" t="s">
         <v>82</v>
@@ -9657,13 +9831,13 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B168" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C168" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="D168" t="s">
         <v>85</v>
@@ -9698,13 +9872,13 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B169" t="s">
+        <v>641</v>
+      </c>
+      <c r="C169" t="s">
         <v>642</v>
-      </c>
-      <c r="B169" t="s">
-        <v>647</v>
-      </c>
-      <c r="C169" t="s">
-        <v>648</v>
       </c>
       <c r="D169" t="s">
         <v>85</v>
@@ -9719,13 +9893,13 @@
         <v>167</v>
       </c>
       <c r="H169" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="I169" t="s">
         <v>61</v>
       </c>
       <c r="J169" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="K169" t="s">
         <v>55</v>
@@ -9742,13 +9916,13 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B170" t="s">
+        <v>670</v>
+      </c>
+      <c r="C170" t="s">
         <v>643</v>
-      </c>
-      <c r="B170" t="s">
-        <v>677</v>
-      </c>
-      <c r="C170" t="s">
-        <v>649</v>
       </c>
       <c r="D170" t="s">
         <v>85</v>
@@ -9763,13 +9937,13 @@
         <v>167</v>
       </c>
       <c r="H170" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I170" t="s">
         <v>82</v>
       </c>
       <c r="J170" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="K170" t="s">
         <v>55</v>
@@ -9786,13 +9960,13 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B171" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C171" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="D171" t="s">
         <v>54</v>
@@ -9827,13 +10001,13 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B172" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="C172" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D172" t="s">
         <v>54</v>
@@ -9845,13 +10019,13 @@
         <v>13</v>
       </c>
       <c r="G172" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H172" t="s">
         <v>234</v>
       </c>
       <c r="J172" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K172" t="s">
         <v>55</v>
@@ -9868,13 +10042,13 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B173" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C173" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D173" t="s">
         <v>54</v>
@@ -9886,13 +10060,13 @@
         <v>13</v>
       </c>
       <c r="G173" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H173" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="J173" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="K173" t="s">
         <v>55</v>
@@ -9909,13 +10083,13 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B174" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C174" t="s">
-        <v>662</v>
+        <v>688</v>
       </c>
       <c r="D174" t="s">
         <v>54</v>
@@ -9930,13 +10104,13 @@
         <v>167</v>
       </c>
       <c r="H174" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I174" t="s">
         <v>82</v>
       </c>
       <c r="J174" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="K174" t="s">
         <v>55</v>
@@ -9953,13 +10127,13 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="B175" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="C175" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="D175" t="s">
         <v>54</v>
@@ -9977,7 +10151,7 @@
         <v>153</v>
       </c>
       <c r="J175" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K175" t="s">
         <v>55</v>
@@ -9994,13 +10168,13 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="B176" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C176" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="D176" t="s">
         <v>54</v>
@@ -10015,7 +10189,7 @@
         <v>167</v>
       </c>
       <c r="H176" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I176" t="s">
         <v>166</v>
@@ -10038,13 +10212,13 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B177" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="C177" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="D177" t="s">
         <v>54</v>
@@ -10059,7 +10233,7 @@
         <v>167</v>
       </c>
       <c r="H177" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="I177" t="s">
         <v>156</v>
@@ -10082,13 +10256,13 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B178" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="C178" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="D178" t="s">
         <v>54</v>
@@ -10100,16 +10274,16 @@
         <v>32</v>
       </c>
       <c r="G178" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H178" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I178" t="s">
         <v>82</v>
       </c>
       <c r="J178" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="K178" t="s">
         <v>55</v>
@@ -10126,13 +10300,13 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B179" t="s">
         <v>668</v>
       </c>
-      <c r="B179" t="s">
-        <v>675</v>
-      </c>
       <c r="C179" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="D179" t="s">
         <v>54</v>
@@ -10147,7 +10321,7 @@
         <v>167</v>
       </c>
       <c r="H179" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="I179" t="s">
         <v>61</v>
@@ -10170,13 +10344,13 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B180" t="s">
+        <v>677</v>
+      </c>
+      <c r="C180" t="s">
         <v>678</v>
-      </c>
-      <c r="B180" t="s">
-        <v>684</v>
-      </c>
-      <c r="C180" t="s">
-        <v>685</v>
       </c>
       <c r="D180" t="s">
         <v>85</v>
@@ -10188,16 +10362,16 @@
         <v>13</v>
       </c>
       <c r="G180" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H180" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I180" t="s">
         <v>60</v>
       </c>
       <c r="J180" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="K180" t="s">
         <v>55</v>
@@ -10214,13 +10388,13 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B181" t="s">
         <v>680</v>
       </c>
-      <c r="B181" t="s">
-        <v>687</v>
-      </c>
       <c r="C181" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="D181" t="s">
         <v>85</v>
@@ -10232,16 +10406,16 @@
         <v>13</v>
       </c>
       <c r="G181" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H181" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="I181" t="s">
         <v>82</v>
       </c>
       <c r="J181" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="K181" t="s">
         <v>55</v>
@@ -10258,13 +10432,13 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="B182" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C182" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="D182" t="s">
         <v>85</v>
@@ -10279,7 +10453,7 @@
         <v>167</v>
       </c>
       <c r="H182" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I182" t="s">
         <v>82</v>
@@ -10302,13 +10476,13 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B183" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="C183" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="D183" t="s">
         <v>85</v>
@@ -10323,7 +10497,7 @@
         <v>167</v>
       </c>
       <c r="H183" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I183" t="s">
         <v>82</v>
@@ -10341,6 +10515,829 @@
         <v>15</v>
       </c>
       <c r="N183" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A184" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B184" t="s">
+        <v>478</v>
+      </c>
+      <c r="C184" t="s">
+        <v>709</v>
+      </c>
+      <c r="D184" t="s">
+        <v>85</v>
+      </c>
+      <c r="E184" t="s">
+        <v>58</v>
+      </c>
+      <c r="F184" t="s">
+        <v>13</v>
+      </c>
+      <c r="G184" t="s">
+        <v>307</v>
+      </c>
+      <c r="H184" t="s">
+        <v>233</v>
+      </c>
+      <c r="J184" t="s">
+        <v>104</v>
+      </c>
+      <c r="K184" t="s">
+        <v>55</v>
+      </c>
+      <c r="L184" t="s">
+        <v>14</v>
+      </c>
+      <c r="M184" t="s">
+        <v>15</v>
+      </c>
+      <c r="N184" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A185" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B185" t="s">
+        <v>710</v>
+      </c>
+      <c r="C185" t="s">
+        <v>711</v>
+      </c>
+      <c r="D185" t="s">
+        <v>85</v>
+      </c>
+      <c r="E185" t="s">
+        <v>58</v>
+      </c>
+      <c r="F185" t="s">
+        <v>13</v>
+      </c>
+      <c r="G185" t="s">
+        <v>167</v>
+      </c>
+      <c r="H185" t="s">
+        <v>597</v>
+      </c>
+      <c r="J185" t="s">
+        <v>218</v>
+      </c>
+      <c r="K185" t="s">
+        <v>56</v>
+      </c>
+      <c r="L185" t="s">
+        <v>14</v>
+      </c>
+      <c r="M185" t="s">
+        <v>15</v>
+      </c>
+      <c r="N185" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A186" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B186" t="s">
+        <v>712</v>
+      </c>
+      <c r="C186" t="s">
+        <v>713</v>
+      </c>
+      <c r="D186" t="s">
+        <v>85</v>
+      </c>
+      <c r="E186" t="s">
+        <v>58</v>
+      </c>
+      <c r="F186" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" t="s">
+        <v>307</v>
+      </c>
+      <c r="H186" t="s">
+        <v>233</v>
+      </c>
+      <c r="J186" t="s">
+        <v>104</v>
+      </c>
+      <c r="K186" t="s">
+        <v>55</v>
+      </c>
+      <c r="L186" t="s">
+        <v>14</v>
+      </c>
+      <c r="M186" t="s">
+        <v>15</v>
+      </c>
+      <c r="N186" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A187" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B187" t="s">
+        <v>714</v>
+      </c>
+      <c r="C187" t="s">
+        <v>715</v>
+      </c>
+      <c r="D187" t="s">
+        <v>85</v>
+      </c>
+      <c r="E187" t="s">
+        <v>58</v>
+      </c>
+      <c r="F187" t="s">
+        <v>13</v>
+      </c>
+      <c r="G187" t="s">
+        <v>307</v>
+      </c>
+      <c r="H187" t="s">
+        <v>233</v>
+      </c>
+      <c r="J187" t="s">
+        <v>104</v>
+      </c>
+      <c r="K187" t="s">
+        <v>55</v>
+      </c>
+      <c r="L187" t="s">
+        <v>14</v>
+      </c>
+      <c r="M187" t="s">
+        <v>15</v>
+      </c>
+      <c r="N187" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A188" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B188" t="s">
+        <v>721</v>
+      </c>
+      <c r="C188" t="s">
+        <v>722</v>
+      </c>
+      <c r="D188" t="s">
+        <v>85</v>
+      </c>
+      <c r="E188" t="s">
+        <v>33</v>
+      </c>
+      <c r="F188" t="s">
+        <v>13</v>
+      </c>
+      <c r="G188" t="s">
+        <v>167</v>
+      </c>
+      <c r="H188" t="s">
+        <v>233</v>
+      </c>
+      <c r="I188" t="s">
+        <v>156</v>
+      </c>
+      <c r="J188" t="s">
+        <v>381</v>
+      </c>
+      <c r="K188" t="s">
+        <v>55</v>
+      </c>
+      <c r="L188" t="s">
+        <v>14</v>
+      </c>
+      <c r="M188" t="s">
+        <v>15</v>
+      </c>
+      <c r="N188" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A189" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B189" t="s">
+        <v>723</v>
+      </c>
+      <c r="C189" t="s">
+        <v>724</v>
+      </c>
+      <c r="D189" t="s">
+        <v>85</v>
+      </c>
+      <c r="E189" t="s">
+        <v>58</v>
+      </c>
+      <c r="F189" t="s">
+        <v>32</v>
+      </c>
+      <c r="G189" t="s">
+        <v>254</v>
+      </c>
+      <c r="H189" t="s">
+        <v>234</v>
+      </c>
+      <c r="J189" t="s">
+        <v>102</v>
+      </c>
+      <c r="K189" t="s">
+        <v>55</v>
+      </c>
+      <c r="L189" t="s">
+        <v>14</v>
+      </c>
+      <c r="M189" t="s">
+        <v>15</v>
+      </c>
+      <c r="N189" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A190" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B190" t="s">
+        <v>725</v>
+      </c>
+      <c r="C190" t="s">
+        <v>726</v>
+      </c>
+      <c r="D190" t="s">
+        <v>85</v>
+      </c>
+      <c r="E190" t="s">
+        <v>58</v>
+      </c>
+      <c r="F190" t="s">
+        <v>32</v>
+      </c>
+      <c r="G190" t="s">
+        <v>515</v>
+      </c>
+      <c r="H190" t="s">
+        <v>234</v>
+      </c>
+      <c r="J190" t="s">
+        <v>102</v>
+      </c>
+      <c r="K190" t="s">
+        <v>55</v>
+      </c>
+      <c r="L190" t="s">
+        <v>14</v>
+      </c>
+      <c r="M190" t="s">
+        <v>15</v>
+      </c>
+      <c r="N190" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A191" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B191" t="s">
+        <v>727</v>
+      </c>
+      <c r="C191" t="s">
+        <v>728</v>
+      </c>
+      <c r="D191" t="s">
+        <v>85</v>
+      </c>
+      <c r="E191" t="s">
+        <v>33</v>
+      </c>
+      <c r="F191" t="s">
+        <v>13</v>
+      </c>
+      <c r="G191" t="s">
+        <v>167</v>
+      </c>
+      <c r="H191" t="s">
+        <v>233</v>
+      </c>
+      <c r="I191" t="s">
+        <v>156</v>
+      </c>
+      <c r="J191" t="s">
+        <v>391</v>
+      </c>
+      <c r="K191" t="s">
+        <v>55</v>
+      </c>
+      <c r="L191" t="s">
+        <v>14</v>
+      </c>
+      <c r="M191" t="s">
+        <v>15</v>
+      </c>
+      <c r="N191" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A192" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B192" t="s">
+        <v>729</v>
+      </c>
+      <c r="C192" t="s">
+        <v>730</v>
+      </c>
+      <c r="D192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E192" t="s">
+        <v>33</v>
+      </c>
+      <c r="F192" t="s">
+        <v>32</v>
+      </c>
+      <c r="G192" t="s">
+        <v>515</v>
+      </c>
+      <c r="H192" t="s">
+        <v>317</v>
+      </c>
+      <c r="J192" t="s">
+        <v>218</v>
+      </c>
+      <c r="K192" t="s">
+        <v>55</v>
+      </c>
+      <c r="L192" t="s">
+        <v>14</v>
+      </c>
+      <c r="M192" t="s">
+        <v>15</v>
+      </c>
+      <c r="N192" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A193" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B193" t="s">
+        <v>731</v>
+      </c>
+      <c r="C193" t="s">
+        <v>732</v>
+      </c>
+      <c r="D193" t="s">
+        <v>54</v>
+      </c>
+      <c r="E193" t="s">
+        <v>33</v>
+      </c>
+      <c r="F193" t="s">
+        <v>13</v>
+      </c>
+      <c r="G193" t="s">
+        <v>167</v>
+      </c>
+      <c r="J193" t="s">
+        <v>208</v>
+      </c>
+      <c r="K193" t="s">
+        <v>55</v>
+      </c>
+      <c r="L193" t="s">
+        <v>14</v>
+      </c>
+      <c r="M193" t="s">
+        <v>15</v>
+      </c>
+      <c r="N193" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A194" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B194" t="s">
+        <v>733</v>
+      </c>
+      <c r="C194" t="s">
+        <v>734</v>
+      </c>
+      <c r="D194" t="s">
+        <v>54</v>
+      </c>
+      <c r="E194" t="s">
+        <v>33</v>
+      </c>
+      <c r="F194" t="s">
+        <v>13</v>
+      </c>
+      <c r="G194" t="s">
+        <v>167</v>
+      </c>
+      <c r="I194" t="s">
+        <v>61</v>
+      </c>
+      <c r="J194" t="s">
+        <v>208</v>
+      </c>
+      <c r="K194" t="s">
+        <v>55</v>
+      </c>
+      <c r="L194" t="s">
+        <v>14</v>
+      </c>
+      <c r="M194" t="s">
+        <v>15</v>
+      </c>
+      <c r="N194" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A195" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B195" t="s">
+        <v>735</v>
+      </c>
+      <c r="C195" t="s">
+        <v>511</v>
+      </c>
+      <c r="D195" t="s">
+        <v>54</v>
+      </c>
+      <c r="E195" t="s">
+        <v>33</v>
+      </c>
+      <c r="F195" t="s">
+        <v>13</v>
+      </c>
+      <c r="G195" t="s">
+        <v>119</v>
+      </c>
+      <c r="I195" t="s">
+        <v>61</v>
+      </c>
+      <c r="J195" t="s">
+        <v>209</v>
+      </c>
+      <c r="K195" t="s">
+        <v>55</v>
+      </c>
+      <c r="L195" t="s">
+        <v>14</v>
+      </c>
+      <c r="M195" t="s">
+        <v>15</v>
+      </c>
+      <c r="N195" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A196" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B196" t="s">
+        <v>736</v>
+      </c>
+      <c r="C196" t="s">
+        <v>742</v>
+      </c>
+      <c r="D196" t="s">
+        <v>54</v>
+      </c>
+      <c r="E196" t="s">
+        <v>33</v>
+      </c>
+      <c r="F196" t="s">
+        <v>32</v>
+      </c>
+      <c r="G196" t="s">
+        <v>741</v>
+      </c>
+      <c r="H196" t="s">
+        <v>120</v>
+      </c>
+      <c r="J196" t="s">
+        <v>446</v>
+      </c>
+      <c r="K196" t="s">
+        <v>55</v>
+      </c>
+      <c r="L196" t="s">
+        <v>14</v>
+      </c>
+      <c r="M196" t="s">
+        <v>15</v>
+      </c>
+      <c r="N196" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A197" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B197" t="s">
+        <v>747</v>
+      </c>
+      <c r="D197" t="s">
+        <v>54</v>
+      </c>
+      <c r="E197" t="s">
+        <v>33</v>
+      </c>
+      <c r="F197" t="s">
+        <v>13</v>
+      </c>
+      <c r="G197" t="s">
+        <v>167</v>
+      </c>
+      <c r="H197" t="s">
+        <v>233</v>
+      </c>
+      <c r="I197" t="s">
+        <v>61</v>
+      </c>
+      <c r="J197" t="s">
+        <v>208</v>
+      </c>
+      <c r="K197" t="s">
+        <v>55</v>
+      </c>
+      <c r="L197" t="s">
+        <v>14</v>
+      </c>
+      <c r="M197" t="s">
+        <v>15</v>
+      </c>
+      <c r="N197" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A198" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B198" t="s">
+        <v>737</v>
+      </c>
+      <c r="C198" t="s">
+        <v>743</v>
+      </c>
+      <c r="D198" t="s">
+        <v>54</v>
+      </c>
+      <c r="E198" t="s">
+        <v>33</v>
+      </c>
+      <c r="F198" t="s">
+        <v>32</v>
+      </c>
+      <c r="G198" t="s">
+        <v>741</v>
+      </c>
+      <c r="H198" t="s">
+        <v>120</v>
+      </c>
+      <c r="J198" t="s">
+        <v>446</v>
+      </c>
+      <c r="K198" t="s">
+        <v>55</v>
+      </c>
+      <c r="L198" t="s">
+        <v>14</v>
+      </c>
+      <c r="M198" t="s">
+        <v>15</v>
+      </c>
+      <c r="N198" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A199" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B199" t="s">
+        <v>738</v>
+      </c>
+      <c r="C199" t="s">
+        <v>744</v>
+      </c>
+      <c r="D199" t="s">
+        <v>54</v>
+      </c>
+      <c r="E199" t="s">
+        <v>33</v>
+      </c>
+      <c r="F199" t="s">
+        <v>32</v>
+      </c>
+      <c r="G199" t="s">
+        <v>741</v>
+      </c>
+      <c r="H199" t="s">
+        <v>371</v>
+      </c>
+      <c r="J199" t="s">
+        <v>446</v>
+      </c>
+      <c r="K199" t="s">
+        <v>55</v>
+      </c>
+      <c r="L199" t="s">
+        <v>14</v>
+      </c>
+      <c r="M199" t="s">
+        <v>15</v>
+      </c>
+      <c r="N199" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A200" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B200" t="s">
+        <v>748</v>
+      </c>
+      <c r="C200" t="s">
+        <v>749</v>
+      </c>
+      <c r="D200" t="s">
+        <v>54</v>
+      </c>
+      <c r="E200" t="s">
+        <v>133</v>
+      </c>
+      <c r="F200" t="s">
+        <v>32</v>
+      </c>
+      <c r="G200" t="s">
+        <v>167</v>
+      </c>
+      <c r="H200" t="s">
+        <v>153</v>
+      </c>
+      <c r="I200" t="s">
+        <v>483</v>
+      </c>
+      <c r="J200" t="s">
+        <v>84</v>
+      </c>
+      <c r="K200" t="s">
+        <v>55</v>
+      </c>
+      <c r="L200" t="s">
+        <v>14</v>
+      </c>
+      <c r="M200" t="s">
+        <v>15</v>
+      </c>
+      <c r="N200" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A201" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B201" t="s">
+        <v>739</v>
+      </c>
+      <c r="C201" t="s">
+        <v>745</v>
+      </c>
+      <c r="D201" t="s">
+        <v>54</v>
+      </c>
+      <c r="E201" t="s">
+        <v>33</v>
+      </c>
+      <c r="F201" t="s">
+        <v>32</v>
+      </c>
+      <c r="G201" t="s">
+        <v>741</v>
+      </c>
+      <c r="H201" t="s">
+        <v>120</v>
+      </c>
+      <c r="J201" t="s">
+        <v>446</v>
+      </c>
+      <c r="K201" t="s">
+        <v>55</v>
+      </c>
+      <c r="L201" t="s">
+        <v>14</v>
+      </c>
+      <c r="M201" t="s">
+        <v>15</v>
+      </c>
+      <c r="N201" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A202" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B202" t="s">
+        <v>750</v>
+      </c>
+      <c r="D202" t="s">
+        <v>54</v>
+      </c>
+      <c r="E202" t="s">
+        <v>133</v>
+      </c>
+      <c r="F202" t="s">
+        <v>32</v>
+      </c>
+      <c r="G202" t="s">
+        <v>169</v>
+      </c>
+      <c r="H202" t="s">
+        <v>317</v>
+      </c>
+      <c r="J202" t="s">
+        <v>208</v>
+      </c>
+      <c r="K202" t="s">
+        <v>55</v>
+      </c>
+      <c r="L202" t="s">
+        <v>14</v>
+      </c>
+      <c r="M202" t="s">
+        <v>15</v>
+      </c>
+      <c r="N202" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A203" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B203" t="s">
+        <v>740</v>
+      </c>
+      <c r="C203" t="s">
+        <v>746</v>
+      </c>
+      <c r="D203" t="s">
+        <v>54</v>
+      </c>
+      <c r="E203" t="s">
+        <v>33</v>
+      </c>
+      <c r="F203" t="s">
+        <v>32</v>
+      </c>
+      <c r="G203" t="s">
+        <v>741</v>
+      </c>
+      <c r="H203" t="s">
+        <v>120</v>
+      </c>
+      <c r="J203" t="s">
+        <v>446</v>
+      </c>
+      <c r="K203" t="s">
+        <v>55</v>
+      </c>
+      <c r="L203" t="s">
+        <v>14</v>
+      </c>
+      <c r="M203" t="s">
+        <v>15</v>
+      </c>
+      <c r="N203" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFB46FF-D57C-3B4B-8683-52A9C2FFB76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA29D15-D775-4441-BBAD-5ACA74E87D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="793">
   <si>
     <t>id</t>
   </si>
@@ -2273,6 +2273,132 @@
   </si>
   <si>
     <t xml:space="preserve">Pasión </t>
+  </si>
+  <si>
+    <t>ILU-0117</t>
+  </si>
+  <si>
+    <t>ILU-0118</t>
+  </si>
+  <si>
+    <t>ILU-0119</t>
+  </si>
+  <si>
+    <t>ILU-0120</t>
+  </si>
+  <si>
+    <t>ILU-0121</t>
+  </si>
+  <si>
+    <t>ILU-0122</t>
+  </si>
+  <si>
+    <t>ILU-0123</t>
+  </si>
+  <si>
+    <t>ILU-0124</t>
+  </si>
+  <si>
+    <t>ILU-0125</t>
+  </si>
+  <si>
+    <t>ILU-0126</t>
+  </si>
+  <si>
+    <t>ILU-0127</t>
+  </si>
+  <si>
+    <t>ILU-0128</t>
+  </si>
+  <si>
+    <t>ILU-0129</t>
+  </si>
+  <si>
+    <t>ILU-0130</t>
+  </si>
+  <si>
+    <t>DIS-0087</t>
+  </si>
+  <si>
+    <t>DIS-0088</t>
+  </si>
+  <si>
+    <t>Marcelino con niños (Color)</t>
+  </si>
+  <si>
+    <t>Marist Coin</t>
+  </si>
+  <si>
+    <t>Para encuentro EJEM</t>
+  </si>
+  <si>
+    <t>Actualización ERE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para profes de Religión </t>
+  </si>
+  <si>
+    <t>Sal fuera y brilla</t>
+  </si>
+  <si>
+    <t>No se enciende una lámpara para…</t>
+  </si>
+  <si>
+    <t>Dar Vida</t>
+  </si>
+  <si>
+    <t>Pascua</t>
+  </si>
+  <si>
+    <t>Coffee Break (Badajoz)</t>
+  </si>
+  <si>
+    <t>Logo actividad con familias</t>
+  </si>
+  <si>
+    <t>Adviento</t>
+  </si>
+  <si>
+    <t>Te espero</t>
+  </si>
+  <si>
+    <t>Reinz: Marist Moustard</t>
+  </si>
+  <si>
+    <t>Bienvenido a la familia</t>
+  </si>
+  <si>
+    <t>sticker;postal;textil</t>
+  </si>
+  <si>
+    <t>Coffee Break (Badajoz) sin fondo</t>
+  </si>
+  <si>
+    <t>En Belén</t>
+  </si>
+  <si>
+    <t>Navidad en el portal</t>
+  </si>
+  <si>
+    <t>El taburete</t>
+  </si>
+  <si>
+    <t>La Chispa III</t>
+  </si>
+  <si>
+    <t>Comedor de Fuenteheridos III</t>
+  </si>
+  <si>
+    <t>Partido a partido</t>
+  </si>
+  <si>
+    <t>Camiseta para jornadas SED Sevilla</t>
+  </si>
+  <si>
+    <t>deporte;social</t>
+  </si>
+  <si>
+    <t>Diploma Escolar Dibujo</t>
   </si>
 </sst>
 </file>
@@ -2629,7 +2755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N203"/>
+  <dimension ref="A1:N219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="32.33203125" customWidth="1"/>
@@ -11326,18 +11452,692 @@
         <v>120</v>
       </c>
       <c r="J203" t="s">
+        <v>208</v>
+      </c>
+      <c r="K203" t="s">
+        <v>55</v>
+      </c>
+      <c r="L203" t="s">
+        <v>14</v>
+      </c>
+      <c r="M203" t="s">
+        <v>15</v>
+      </c>
+      <c r="N203" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A204" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B204" t="s">
+        <v>424</v>
+      </c>
+      <c r="C204" t="s">
+        <v>767</v>
+      </c>
+      <c r="D204" t="s">
+        <v>54</v>
+      </c>
+      <c r="E204" t="s">
+        <v>133</v>
+      </c>
+      <c r="F204" t="s">
+        <v>32</v>
+      </c>
+      <c r="G204" t="s">
+        <v>169</v>
+      </c>
+      <c r="H204" t="s">
+        <v>553</v>
+      </c>
+      <c r="J204" t="s">
+        <v>208</v>
+      </c>
+      <c r="K204" t="s">
+        <v>55</v>
+      </c>
+      <c r="L204" t="s">
+        <v>14</v>
+      </c>
+      <c r="M204" t="s">
+        <v>15</v>
+      </c>
+      <c r="N204" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A205" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B205" t="s">
+        <v>768</v>
+      </c>
+      <c r="C205" t="s">
+        <v>769</v>
+      </c>
+      <c r="D205" t="s">
+        <v>54</v>
+      </c>
+      <c r="E205" t="s">
+        <v>33</v>
+      </c>
+      <c r="F205" t="s">
+        <v>13</v>
+      </c>
+      <c r="G205" t="s">
+        <v>167</v>
+      </c>
+      <c r="H205" t="s">
+        <v>549</v>
+      </c>
+      <c r="I205" t="s">
+        <v>483</v>
+      </c>
+      <c r="J205" t="s">
+        <v>208</v>
+      </c>
+      <c r="K205" t="s">
+        <v>55</v>
+      </c>
+      <c r="L205" t="s">
+        <v>14</v>
+      </c>
+      <c r="M205" t="s">
+        <v>15</v>
+      </c>
+      <c r="N205" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A206" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B206" t="s">
+        <v>29</v>
+      </c>
+      <c r="D206" t="s">
+        <v>54</v>
+      </c>
+      <c r="E206" t="s">
+        <v>133</v>
+      </c>
+      <c r="F206" t="s">
+        <v>32</v>
+      </c>
+      <c r="G206" t="s">
+        <v>171</v>
+      </c>
+      <c r="H206" t="s">
+        <v>549</v>
+      </c>
+      <c r="I206" t="s">
+        <v>61</v>
+      </c>
+      <c r="J206" t="s">
+        <v>208</v>
+      </c>
+      <c r="K206" t="s">
+        <v>55</v>
+      </c>
+      <c r="L206" t="s">
+        <v>14</v>
+      </c>
+      <c r="M206" t="s">
+        <v>15</v>
+      </c>
+      <c r="N206" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A207" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B207" t="s">
+        <v>770</v>
+      </c>
+      <c r="C207" t="s">
+        <v>771</v>
+      </c>
+      <c r="D207" t="s">
+        <v>54</v>
+      </c>
+      <c r="E207" t="s">
+        <v>58</v>
+      </c>
+      <c r="F207" t="s">
+        <v>13</v>
+      </c>
+      <c r="G207" t="s">
+        <v>167</v>
+      </c>
+      <c r="H207" t="s">
+        <v>234</v>
+      </c>
+      <c r="I207" t="s">
+        <v>156</v>
+      </c>
+      <c r="J207" t="s">
+        <v>208</v>
+      </c>
+      <c r="K207" t="s">
+        <v>55</v>
+      </c>
+      <c r="L207" t="s">
+        <v>14</v>
+      </c>
+      <c r="M207" t="s">
+        <v>15</v>
+      </c>
+      <c r="N207" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A208" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B208" t="s">
+        <v>772</v>
+      </c>
+      <c r="C208" t="s">
+        <v>773</v>
+      </c>
+      <c r="D208" t="s">
+        <v>54</v>
+      </c>
+      <c r="E208" t="s">
+        <v>58</v>
+      </c>
+      <c r="F208" t="s">
+        <v>13</v>
+      </c>
+      <c r="G208" t="s">
+        <v>119</v>
+      </c>
+      <c r="H208" t="s">
+        <v>317</v>
+      </c>
+      <c r="I208" t="s">
+        <v>82</v>
+      </c>
+      <c r="J208" t="s">
+        <v>208</v>
+      </c>
+      <c r="K208" t="s">
+        <v>55</v>
+      </c>
+      <c r="L208" t="s">
+        <v>14</v>
+      </c>
+      <c r="M208" t="s">
+        <v>15</v>
+      </c>
+      <c r="N208" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A209" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B209" t="s">
+        <v>774</v>
+      </c>
+      <c r="C209" t="s">
+        <v>775</v>
+      </c>
+      <c r="D209" t="s">
+        <v>54</v>
+      </c>
+      <c r="E209" t="s">
+        <v>33</v>
+      </c>
+      <c r="F209" t="s">
+        <v>13</v>
+      </c>
+      <c r="G209" t="s">
+        <v>167</v>
+      </c>
+      <c r="H209" t="s">
+        <v>317</v>
+      </c>
+      <c r="J209" t="s">
+        <v>391</v>
+      </c>
+      <c r="K209" t="s">
+        <v>55</v>
+      </c>
+      <c r="L209" t="s">
+        <v>14</v>
+      </c>
+      <c r="M209" t="s">
+        <v>15</v>
+      </c>
+      <c r="N209" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A210" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B210" t="s">
+        <v>776</v>
+      </c>
+      <c r="C210" t="s">
+        <v>777</v>
+      </c>
+      <c r="D210" t="s">
+        <v>54</v>
+      </c>
+      <c r="E210" t="s">
+        <v>33</v>
+      </c>
+      <c r="F210" t="s">
+        <v>13</v>
+      </c>
+      <c r="G210" t="s">
+        <v>515</v>
+      </c>
+      <c r="H210" t="s">
+        <v>234</v>
+      </c>
+      <c r="I210" t="s">
+        <v>156</v>
+      </c>
+      <c r="J210" t="s">
         <v>446</v>
       </c>
-      <c r="K203" t="s">
-        <v>55</v>
-      </c>
-      <c r="L203" t="s">
-        <v>14</v>
-      </c>
-      <c r="M203" t="s">
-        <v>15</v>
-      </c>
-      <c r="N203" t="s">
+      <c r="K210" t="s">
+        <v>55</v>
+      </c>
+      <c r="L210" t="s">
+        <v>14</v>
+      </c>
+      <c r="M210" t="s">
+        <v>15</v>
+      </c>
+      <c r="N210" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A211" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B211" t="s">
+        <v>778</v>
+      </c>
+      <c r="C211" t="s">
+        <v>779</v>
+      </c>
+      <c r="D211" t="s">
+        <v>54</v>
+      </c>
+      <c r="E211" t="s">
+        <v>58</v>
+      </c>
+      <c r="F211" t="s">
+        <v>13</v>
+      </c>
+      <c r="G211" t="s">
+        <v>119</v>
+      </c>
+      <c r="H211" t="s">
+        <v>317</v>
+      </c>
+      <c r="I211" t="s">
+        <v>82</v>
+      </c>
+      <c r="J211" t="s">
+        <v>208</v>
+      </c>
+      <c r="K211" t="s">
+        <v>55</v>
+      </c>
+      <c r="L211" t="s">
+        <v>14</v>
+      </c>
+      <c r="M211" t="s">
+        <v>15</v>
+      </c>
+      <c r="N211" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A212" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B212" t="s">
+        <v>780</v>
+      </c>
+      <c r="D212" t="s">
+        <v>54</v>
+      </c>
+      <c r="E212" t="s">
+        <v>33</v>
+      </c>
+      <c r="F212" t="s">
+        <v>13</v>
+      </c>
+      <c r="G212" t="s">
+        <v>167</v>
+      </c>
+      <c r="H212" t="s">
+        <v>317</v>
+      </c>
+      <c r="J212" t="s">
+        <v>208</v>
+      </c>
+      <c r="K212" t="s">
+        <v>55</v>
+      </c>
+      <c r="L212" t="s">
+        <v>14</v>
+      </c>
+      <c r="M212" t="s">
+        <v>15</v>
+      </c>
+      <c r="N212" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A213" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B213" t="s">
+        <v>781</v>
+      </c>
+      <c r="D213" t="s">
+        <v>54</v>
+      </c>
+      <c r="E213" t="s">
+        <v>33</v>
+      </c>
+      <c r="F213" t="s">
+        <v>13</v>
+      </c>
+      <c r="G213" t="s">
+        <v>167</v>
+      </c>
+      <c r="H213" t="s">
+        <v>217</v>
+      </c>
+      <c r="I213" t="s">
+        <v>82</v>
+      </c>
+      <c r="J213" t="s">
+        <v>782</v>
+      </c>
+      <c r="K213" t="s">
+        <v>55</v>
+      </c>
+      <c r="L213" t="s">
+        <v>14</v>
+      </c>
+      <c r="M213" t="s">
+        <v>15</v>
+      </c>
+      <c r="N213" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A214" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B214" t="s">
+        <v>783</v>
+      </c>
+      <c r="C214" t="s">
+        <v>777</v>
+      </c>
+      <c r="D214" t="s">
+        <v>54</v>
+      </c>
+      <c r="E214" t="s">
+        <v>33</v>
+      </c>
+      <c r="F214" t="s">
+        <v>13</v>
+      </c>
+      <c r="G214" t="s">
+        <v>515</v>
+      </c>
+      <c r="H214" t="s">
+        <v>234</v>
+      </c>
+      <c r="I214" t="s">
+        <v>237</v>
+      </c>
+      <c r="J214" t="s">
+        <v>654</v>
+      </c>
+      <c r="K214" t="s">
+        <v>55</v>
+      </c>
+      <c r="L214" t="s">
+        <v>14</v>
+      </c>
+      <c r="M214" t="s">
+        <v>15</v>
+      </c>
+      <c r="N214" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A215" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B215" t="s">
+        <v>784</v>
+      </c>
+      <c r="C215" t="s">
+        <v>785</v>
+      </c>
+      <c r="D215" t="s">
+        <v>54</v>
+      </c>
+      <c r="E215" t="s">
+        <v>33</v>
+      </c>
+      <c r="F215" t="s">
+        <v>32</v>
+      </c>
+      <c r="G215" t="s">
+        <v>118</v>
+      </c>
+      <c r="H215" t="s">
+        <v>317</v>
+      </c>
+      <c r="I215" t="s">
+        <v>483</v>
+      </c>
+      <c r="J215" t="s">
+        <v>208</v>
+      </c>
+      <c r="K215" t="s">
+        <v>55</v>
+      </c>
+      <c r="L215" t="s">
+        <v>14</v>
+      </c>
+      <c r="M215" t="s">
+        <v>15</v>
+      </c>
+      <c r="N215" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A216" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B216" t="s">
+        <v>786</v>
+      </c>
+      <c r="C216" t="s">
+        <v>382</v>
+      </c>
+      <c r="D216" t="s">
+        <v>54</v>
+      </c>
+      <c r="E216" t="s">
+        <v>33</v>
+      </c>
+      <c r="F216" t="s">
+        <v>13</v>
+      </c>
+      <c r="G216" t="s">
+        <v>167</v>
+      </c>
+      <c r="H216" t="s">
+        <v>382</v>
+      </c>
+      <c r="J216" t="s">
+        <v>208</v>
+      </c>
+      <c r="K216" t="s">
+        <v>56</v>
+      </c>
+      <c r="L216" t="s">
+        <v>14</v>
+      </c>
+      <c r="M216" t="s">
+        <v>15</v>
+      </c>
+      <c r="N216" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A217" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B217" t="s">
+        <v>787</v>
+      </c>
+      <c r="C217" t="s">
+        <v>788</v>
+      </c>
+      <c r="D217" t="s">
+        <v>54</v>
+      </c>
+      <c r="E217" t="s">
+        <v>33</v>
+      </c>
+      <c r="F217" t="s">
+        <v>32</v>
+      </c>
+      <c r="G217" t="s">
+        <v>169</v>
+      </c>
+      <c r="H217" t="s">
+        <v>382</v>
+      </c>
+      <c r="J217" t="s">
+        <v>84</v>
+      </c>
+      <c r="K217" t="s">
+        <v>55</v>
+      </c>
+      <c r="L217" t="s">
+        <v>14</v>
+      </c>
+      <c r="M217" t="s">
+        <v>15</v>
+      </c>
+      <c r="N217" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A218" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B218" t="s">
+        <v>789</v>
+      </c>
+      <c r="C218" t="s">
+        <v>790</v>
+      </c>
+      <c r="D218" t="s">
+        <v>85</v>
+      </c>
+      <c r="E218" t="s">
+        <v>58</v>
+      </c>
+      <c r="F218" t="s">
+        <v>13</v>
+      </c>
+      <c r="G218" t="s">
+        <v>167</v>
+      </c>
+      <c r="H218" t="s">
+        <v>791</v>
+      </c>
+      <c r="J218" t="s">
+        <v>218</v>
+      </c>
+      <c r="K218" t="s">
+        <v>55</v>
+      </c>
+      <c r="L218" t="s">
+        <v>14</v>
+      </c>
+      <c r="M218" t="s">
+        <v>15</v>
+      </c>
+      <c r="N218" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A219" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B219" t="s">
+        <v>792</v>
+      </c>
+      <c r="D219" t="s">
+        <v>85</v>
+      </c>
+      <c r="E219" t="s">
+        <v>58</v>
+      </c>
+      <c r="F219" t="s">
+        <v>32</v>
+      </c>
+      <c r="G219" t="s">
+        <v>169</v>
+      </c>
+      <c r="H219" t="s">
+        <v>234</v>
+      </c>
+      <c r="I219" t="s">
+        <v>82</v>
+      </c>
+      <c r="J219" t="s">
+        <v>102</v>
+      </c>
+      <c r="K219" t="s">
+        <v>55</v>
+      </c>
+      <c r="L219" t="s">
+        <v>14</v>
+      </c>
+      <c r="M219" t="s">
+        <v>15</v>
+      </c>
+      <c r="N219" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA29D15-D775-4441-BBAD-5ACA74E87D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1940DC-E0BB-7942-8EBE-B5475791D945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="791">
   <si>
     <t>id</t>
   </si>
@@ -712,9 +712,6 @@
     <t>Graduación</t>
   </si>
   <si>
-    <t>sticker;cartel</t>
-  </si>
-  <si>
     <t>Atienden</t>
   </si>
   <si>
@@ -979,9 +976,6 @@
     <t>maristas;evangelio</t>
   </si>
   <si>
-    <t>sticker;cartel;postal</t>
-  </si>
-  <si>
     <t>Sal y Luz I - Evangelío</t>
   </si>
   <si>
@@ -1309,9 +1303,6 @@
     <t>Jesús, el BuenaJente</t>
   </si>
   <si>
-    <t>mural;cartel;textil</t>
-  </si>
-  <si>
     <t>Atardece</t>
   </si>
   <si>
@@ -2399,6 +2390,9 @@
   </si>
   <si>
     <t>Diploma Escolar Dibujo</t>
+  </si>
+  <si>
+    <t>mural;postal;textil</t>
   </si>
 </sst>
 </file>
@@ -2821,7 +2815,7 @@
         <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D2" t="s">
         <v>54</v>
@@ -2865,7 +2859,7 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D3" t="s">
         <v>54</v>
@@ -2883,7 +2877,7 @@
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="J3" t="s">
         <v>208</v>
@@ -2906,7 +2900,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C4" t="s">
         <v>86</v>
@@ -3076,7 +3070,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -3097,7 +3091,7 @@
         <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="K8" t="s">
         <v>55</v>
@@ -3161,7 +3155,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C10" t="s">
         <v>90</v>
@@ -3205,7 +3199,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
@@ -3249,7 +3243,7 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C12" t="s">
         <v>92</v>
@@ -3293,7 +3287,7 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C13" t="s">
         <v>93</v>
@@ -3337,7 +3331,7 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C14" t="s">
         <v>94</v>
@@ -3396,10 +3390,10 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H15" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I15" t="s">
         <v>101</v>
@@ -3440,7 +3434,7 @@
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H16" t="s">
         <v>28</v>
@@ -3484,7 +3478,7 @@
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H17" t="s">
         <v>59</v>
@@ -3528,10 +3522,10 @@
         <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H18" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="J18" t="s">
         <v>208</v>
@@ -3569,7 +3563,7 @@
         <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="H19" t="s">
         <v>28</v>
@@ -3698,7 +3692,7 @@
         <v>167</v>
       </c>
       <c r="H22" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I22" t="s">
         <v>61</v>
@@ -3783,7 +3777,7 @@
         <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="H24" t="s">
         <v>28</v>
@@ -3827,7 +3821,7 @@
         <v>169</v>
       </c>
       <c r="H25" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J25" t="s">
         <v>83</v>
@@ -3868,7 +3862,7 @@
         <v>169</v>
       </c>
       <c r="H26" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="J26" t="s">
         <v>102</v>
@@ -3956,7 +3950,7 @@
         <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K28" t="s">
         <v>56</v>
@@ -3994,7 +3988,7 @@
         <v>97</v>
       </c>
       <c r="H29" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I29" t="s">
         <v>82</v>
@@ -4035,7 +4029,7 @@
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H30" t="s">
         <v>153</v>
@@ -4120,7 +4114,7 @@
         <v>167</v>
       </c>
       <c r="H32" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="J32" t="s">
         <v>102</v>
@@ -4161,7 +4155,7 @@
         <v>167</v>
       </c>
       <c r="H33" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="J33" t="s">
         <v>102</v>
@@ -4293,7 +4287,7 @@
         <v>166</v>
       </c>
       <c r="J36" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K36" t="s">
         <v>55</v>
@@ -4375,13 +4369,13 @@
         <v>118</v>
       </c>
       <c r="H38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I38" t="s">
         <v>60</v>
       </c>
       <c r="J38" t="s">
-        <v>230</v>
+        <v>443</v>
       </c>
       <c r="K38" t="s">
         <v>55</v>
@@ -4401,10 +4395,10 @@
         <v>221</v>
       </c>
       <c r="B39" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" t="s">
         <v>231</v>
-      </c>
-      <c r="C39" t="s">
-        <v>232</v>
       </c>
       <c r="D39" t="s">
         <v>54</v>
@@ -4419,7 +4413,7 @@
         <v>167</v>
       </c>
       <c r="H39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I39" t="s">
         <v>60</v>
@@ -4445,10 +4439,10 @@
         <v>222</v>
       </c>
       <c r="B40" t="s">
+        <v>234</v>
+      </c>
+      <c r="C40" t="s">
         <v>235</v>
-      </c>
-      <c r="C40" t="s">
-        <v>236</v>
       </c>
       <c r="D40" t="s">
         <v>54</v>
@@ -4463,7 +4457,7 @@
         <v>169</v>
       </c>
       <c r="H40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I40" t="s">
         <v>61</v>
@@ -4489,10 +4483,10 @@
         <v>223</v>
       </c>
       <c r="B41" t="s">
+        <v>238</v>
+      </c>
+      <c r="C41" t="s">
         <v>239</v>
-      </c>
-      <c r="C41" t="s">
-        <v>240</v>
       </c>
       <c r="D41" t="s">
         <v>54</v>
@@ -4507,7 +4501,7 @@
         <v>167</v>
       </c>
       <c r="H41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I41" t="s">
         <v>60</v>
@@ -4530,10 +4524,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B42" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C42" t="s">
         <v>165</v>
@@ -4551,7 +4545,7 @@
         <v>167</v>
       </c>
       <c r="H42" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I42" t="s">
         <v>61</v>
@@ -4574,13 +4568,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B43" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C43" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D43" t="s">
         <v>54</v>
@@ -4595,7 +4589,7 @@
         <v>167</v>
       </c>
       <c r="H43" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I43" t="s">
         <v>61</v>
@@ -4618,13 +4612,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B44" t="s">
+        <v>246</v>
+      </c>
+      <c r="C44" t="s">
         <v>247</v>
-      </c>
-      <c r="C44" t="s">
-        <v>248</v>
       </c>
       <c r="D44" t="s">
         <v>54</v>
@@ -4639,7 +4633,7 @@
         <v>167</v>
       </c>
       <c r="H44" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I44" t="s">
         <v>61</v>
@@ -4662,13 +4656,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B45" t="s">
+        <v>248</v>
+      </c>
+      <c r="C45" t="s">
         <v>249</v>
-      </c>
-      <c r="C45" t="s">
-        <v>250</v>
       </c>
       <c r="D45" t="s">
         <v>54</v>
@@ -4683,7 +4677,7 @@
         <v>167</v>
       </c>
       <c r="H45" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I45" t="s">
         <v>156</v>
@@ -4706,13 +4700,13 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B46" t="s">
         <v>280</v>
       </c>
-      <c r="B46" t="s">
-        <v>281</v>
-      </c>
       <c r="C46" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D46" t="s">
         <v>54</v>
@@ -4727,7 +4721,7 @@
         <v>167</v>
       </c>
       <c r="H46" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I46" t="s">
         <v>166</v>
@@ -4750,13 +4744,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B47" t="s">
         <v>282</v>
       </c>
-      <c r="B47" t="s">
-        <v>283</v>
-      </c>
       <c r="C47" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D47" t="s">
         <v>54</v>
@@ -4771,7 +4765,7 @@
         <v>167</v>
       </c>
       <c r="H47" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I47" t="s">
         <v>166</v>
@@ -4794,13 +4788,13 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B48" t="s">
+        <v>293</v>
+      </c>
+      <c r="C48" t="s">
         <v>294</v>
-      </c>
-      <c r="C48" t="s">
-        <v>295</v>
       </c>
       <c r="D48" t="s">
         <v>54</v>
@@ -4815,13 +4809,13 @@
         <v>167</v>
       </c>
       <c r="H48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I48" t="s">
         <v>60</v>
       </c>
       <c r="J48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K48" t="s">
         <v>55</v>
@@ -4838,13 +4832,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B49" t="s">
+        <v>295</v>
+      </c>
+      <c r="C49" t="s">
         <v>296</v>
-      </c>
-      <c r="C49" t="s">
-        <v>297</v>
       </c>
       <c r="D49" t="s">
         <v>54</v>
@@ -4859,7 +4853,7 @@
         <v>167</v>
       </c>
       <c r="H49" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I49" t="s">
         <v>156</v>
@@ -4882,13 +4876,13 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B50" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D50" t="s">
         <v>54</v>
@@ -4903,7 +4897,7 @@
         <v>119</v>
       </c>
       <c r="H50" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I50" t="s">
         <v>156</v>
@@ -4926,13 +4920,13 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B51" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C51" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D51" t="s">
         <v>54</v>
@@ -4947,7 +4941,7 @@
         <v>119</v>
       </c>
       <c r="H51" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I51" t="s">
         <v>156</v>
@@ -4970,13 +4964,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B52" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C52" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D52" t="s">
         <v>54</v>
@@ -4988,7 +4982,7 @@
         <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H52" t="s">
         <v>120</v>
@@ -5014,13 +5008,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B53" t="s">
+        <v>311</v>
+      </c>
+      <c r="C53" t="s">
         <v>312</v>
-      </c>
-      <c r="C53" t="s">
-        <v>313</v>
       </c>
       <c r="D53" t="s">
         <v>54</v>
@@ -5035,7 +5029,7 @@
         <v>167</v>
       </c>
       <c r="H53" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I53" t="s">
         <v>61</v>
@@ -5058,13 +5052,13 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B54" t="s">
+        <v>314</v>
+      </c>
+      <c r="C54" t="s">
         <v>315</v>
-      </c>
-      <c r="C54" t="s">
-        <v>316</v>
       </c>
       <c r="D54" t="s">
         <v>54</v>
@@ -5079,7 +5073,7 @@
         <v>167</v>
       </c>
       <c r="H54" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J54" t="s">
         <v>102</v>
@@ -5099,13 +5093,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B55" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C55" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D55" t="s">
         <v>54</v>
@@ -5117,16 +5111,16 @@
         <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H55" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I55" t="s">
         <v>156</v>
       </c>
       <c r="J55" t="s">
-        <v>319</v>
+        <v>443</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -5143,13 +5137,13 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B56" t="s">
+        <v>319</v>
+      </c>
+      <c r="C56" t="s">
         <v>321</v>
-      </c>
-      <c r="C56" t="s">
-        <v>323</v>
       </c>
       <c r="D56" t="s">
         <v>54</v>
@@ -5164,13 +5158,13 @@
         <v>167</v>
       </c>
       <c r="H56" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I56" t="s">
         <v>166</v>
       </c>
       <c r="J56" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K56" t="s">
         <v>55</v>
@@ -5187,13 +5181,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B57" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C57" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D57" t="s">
         <v>54</v>
@@ -5228,13 +5222,13 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C58" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D58" t="s">
         <v>54</v>
@@ -5246,13 +5240,13 @@
         <v>32</v>
       </c>
       <c r="G58" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H58" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I58" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J58" t="s">
         <v>227</v>
@@ -5272,13 +5266,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B59" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C59" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D59" t="s">
         <v>54</v>
@@ -5293,7 +5287,7 @@
         <v>171</v>
       </c>
       <c r="H59" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="J59" t="s">
         <v>102</v>
@@ -5313,13 +5307,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C60" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D60" t="s">
         <v>54</v>
@@ -5331,10 +5325,10 @@
         <v>32</v>
       </c>
       <c r="G60" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H60" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I60" t="s">
         <v>60</v>
@@ -5357,13 +5351,13 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B61" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C61" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D61" t="s">
         <v>54</v>
@@ -5375,13 +5369,13 @@
         <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H61" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J61" t="s">
-        <v>429</v>
+        <v>790</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -5398,13 +5392,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C62" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D62" t="s">
         <v>54</v>
@@ -5416,10 +5410,10 @@
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H62" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I62" t="s">
         <v>82</v>
@@ -5442,13 +5436,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B63" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C63" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D63" t="s">
         <v>54</v>
@@ -5460,16 +5454,16 @@
         <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H63" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I63" t="s">
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K63" t="s">
         <v>55</v>
@@ -5486,13 +5480,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C64" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D64" t="s">
         <v>54</v>
@@ -5504,10 +5498,10 @@
         <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H64" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="J64" t="s">
         <v>172</v>
@@ -5527,13 +5521,13 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B65" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C65" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D65" t="s">
         <v>54</v>
@@ -5568,13 +5562,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B66" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C66" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D66" t="s">
         <v>54</v>
@@ -5586,10 +5580,10 @@
         <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H66" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I66" t="s">
         <v>61</v>
@@ -5612,13 +5606,13 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B67" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C67" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D67" t="s">
         <v>54</v>
@@ -5630,13 +5624,13 @@
         <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H67" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="J67" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K67" t="s">
         <v>55</v>
@@ -5653,13 +5647,13 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B68" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C68" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D68" t="s">
         <v>54</v>
@@ -5674,10 +5668,10 @@
         <v>167</v>
       </c>
       <c r="H68" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="J68" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K68" t="s">
         <v>55</v>
@@ -5694,13 +5688,13 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B69" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C69" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D69" t="s">
         <v>54</v>
@@ -5715,7 +5709,7 @@
         <v>167</v>
       </c>
       <c r="H69" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I69" t="s">
         <v>61</v>
@@ -5738,13 +5732,13 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B70" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C70" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D70" t="s">
         <v>54</v>
@@ -5759,7 +5753,7 @@
         <v>119</v>
       </c>
       <c r="H70" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J70" t="s">
         <v>207</v>
@@ -5779,13 +5773,13 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B71" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C71" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D71" t="s">
         <v>54</v>
@@ -5800,7 +5794,7 @@
         <v>169</v>
       </c>
       <c r="H71" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I71" t="s">
         <v>61</v>
@@ -5823,13 +5817,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B72" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C72" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D72" t="s">
         <v>54</v>
@@ -5844,7 +5838,7 @@
         <v>167</v>
       </c>
       <c r="H72" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J72" t="s">
         <v>227</v>
@@ -5864,13 +5858,13 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B73" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C73" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D73" t="s">
         <v>54</v>
@@ -5885,7 +5879,7 @@
         <v>167</v>
       </c>
       <c r="H73" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J73" t="s">
         <v>208</v>
@@ -5905,13 +5899,13 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B74" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C74" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D74" t="s">
         <v>54</v>
@@ -5929,7 +5923,7 @@
         <v>153</v>
       </c>
       <c r="I74" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J74" t="s">
         <v>208</v>
@@ -5949,13 +5943,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B75" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C75" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D75" t="s">
         <v>54</v>
@@ -5993,13 +5987,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B76" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C76" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D76" t="s">
         <v>54</v>
@@ -6014,7 +6008,7 @@
         <v>167</v>
       </c>
       <c r="H76" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I76" t="s">
         <v>61</v>
@@ -6037,13 +6031,13 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B77" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C77" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D77" t="s">
         <v>54</v>
@@ -6058,7 +6052,7 @@
         <v>167</v>
       </c>
       <c r="H77" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I77" t="s">
         <v>61</v>
@@ -6081,13 +6075,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C78" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D78" t="s">
         <v>54</v>
@@ -6102,7 +6096,7 @@
         <v>167</v>
       </c>
       <c r="H78" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I78" t="s">
         <v>61</v>
@@ -6125,13 +6119,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B79" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C79" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D79" t="s">
         <v>54</v>
@@ -6143,16 +6137,16 @@
         <v>32</v>
       </c>
       <c r="G79" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H79" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="I79" t="s">
         <v>61</v>
       </c>
       <c r="J79" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K79" t="s">
         <v>55</v>
@@ -6169,13 +6163,13 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B80" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C80" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D80" t="s">
         <v>54</v>
@@ -6190,7 +6184,7 @@
         <v>167</v>
       </c>
       <c r="H80" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="I80" t="s">
         <v>61</v>
@@ -6213,13 +6207,13 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B81" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C81" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D81" t="s">
         <v>54</v>
@@ -6234,7 +6228,7 @@
         <v>167</v>
       </c>
       <c r="H81" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I81" t="s">
         <v>61</v>
@@ -6257,13 +6251,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B82" t="s">
+        <v>505</v>
+      </c>
+      <c r="C82" t="s">
         <v>508</v>
-      </c>
-      <c r="C82" t="s">
-        <v>511</v>
       </c>
       <c r="D82" t="s">
         <v>54</v>
@@ -6278,7 +6272,7 @@
         <v>119</v>
       </c>
       <c r="H82" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="I82" t="s">
         <v>61</v>
@@ -6301,13 +6295,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B83" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C83" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D83" t="s">
         <v>54</v>
@@ -6322,7 +6316,7 @@
         <v>119</v>
       </c>
       <c r="H83" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I83" t="s">
         <v>61</v>
@@ -6345,13 +6339,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B84" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C84" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D84" t="s">
         <v>54</v>
@@ -6366,7 +6360,7 @@
         <v>167</v>
       </c>
       <c r="H84" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I84" t="s">
         <v>61</v>
@@ -6389,13 +6383,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B85" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C85" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D85" t="s">
         <v>54</v>
@@ -6407,10 +6401,10 @@
         <v>32</v>
       </c>
       <c r="G85" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H85" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I85" t="s">
         <v>61</v>
@@ -6433,13 +6427,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B86" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C86" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D86" t="s">
         <v>54</v>
@@ -6454,7 +6448,7 @@
         <v>118</v>
       </c>
       <c r="H86" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="I86" t="s">
         <v>61</v>
@@ -6477,13 +6471,13 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B87" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C87" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D87" t="s">
         <v>54</v>
@@ -6498,7 +6492,7 @@
         <v>167</v>
       </c>
       <c r="H87" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="I87" t="s">
         <v>61</v>
@@ -6521,13 +6515,13 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B88" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C88" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D88" t="s">
         <v>54</v>
@@ -6542,7 +6536,7 @@
         <v>169</v>
       </c>
       <c r="H88" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I88" t="s">
         <v>61</v>
@@ -6565,13 +6559,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B89" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C89" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D89" t="s">
         <v>54</v>
@@ -6586,7 +6580,7 @@
         <v>169</v>
       </c>
       <c r="H89" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="I89" t="s">
         <v>61</v>
@@ -6609,13 +6603,13 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C90" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D90" t="s">
         <v>54</v>
@@ -6630,7 +6624,7 @@
         <v>119</v>
       </c>
       <c r="H90" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I90" t="s">
         <v>61</v>
@@ -6653,13 +6647,13 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B91" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C91" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D91" t="s">
         <v>54</v>
@@ -6671,16 +6665,16 @@
         <v>13</v>
       </c>
       <c r="G91" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H91" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="I91" t="s">
         <v>82</v>
       </c>
       <c r="J91" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="K91" t="s">
         <v>55</v>
@@ -6697,13 +6691,13 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B92" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C92" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D92" t="s">
         <v>54</v>
@@ -6715,10 +6709,10 @@
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H92" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J92" t="s">
         <v>84</v>
@@ -6738,13 +6732,13 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B93" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C93" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D93" t="s">
         <v>54</v>
@@ -6756,10 +6750,10 @@
         <v>13</v>
       </c>
       <c r="G93" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H93" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I93" t="s">
         <v>61</v>
@@ -6782,13 +6776,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B94" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C94" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D94" t="s">
         <v>54</v>
@@ -6803,13 +6797,13 @@
         <v>167</v>
       </c>
       <c r="H94" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I94" t="s">
         <v>61</v>
       </c>
       <c r="J94" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K94" t="s">
         <v>55</v>
@@ -6826,13 +6820,13 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B95" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C95" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D95" t="s">
         <v>54</v>
@@ -6847,7 +6841,7 @@
         <v>169</v>
       </c>
       <c r="H95" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I95" t="s">
         <v>61</v>
@@ -6870,13 +6864,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B96" t="s">
+        <v>618</v>
+      </c>
+      <c r="C96" t="s">
         <v>619</v>
-      </c>
-      <c r="B96" t="s">
-        <v>621</v>
-      </c>
-      <c r="C96" t="s">
-        <v>622</v>
       </c>
       <c r="D96" t="s">
         <v>54</v>
@@ -6891,7 +6885,7 @@
         <v>167</v>
       </c>
       <c r="H96" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I96" t="s">
         <v>61</v>
@@ -6914,13 +6908,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B97" t="s">
         <v>620</v>
       </c>
-      <c r="B97" t="s">
-        <v>623</v>
-      </c>
       <c r="C97" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D97" t="s">
         <v>54</v>
@@ -6935,13 +6929,13 @@
         <v>167</v>
       </c>
       <c r="H97" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I97" t="s">
         <v>82</v>
       </c>
       <c r="J97" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K97" t="s">
         <v>55</v>
@@ -6961,7 +6955,7 @@
         <v>63</v>
       </c>
       <c r="B98" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C98" t="s">
         <v>70</v>
@@ -6979,7 +6973,7 @@
         <v>167</v>
       </c>
       <c r="H98" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="I98" t="s">
         <v>103</v>
@@ -7023,7 +7017,7 @@
         <v>167</v>
       </c>
       <c r="H99" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="I99" t="s">
         <v>82</v>
@@ -7049,7 +7043,7 @@
         <v>65</v>
       </c>
       <c r="B100" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C100" t="s">
         <v>73</v>
@@ -7067,7 +7061,7 @@
         <v>167</v>
       </c>
       <c r="H100" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="I100" t="s">
         <v>101</v>
@@ -7096,7 +7090,7 @@
         <v>74</v>
       </c>
       <c r="C101" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D101" t="s">
         <v>85</v>
@@ -7111,7 +7105,7 @@
         <v>167</v>
       </c>
       <c r="H101" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J101" t="s">
         <v>99</v>
@@ -7152,7 +7146,7 @@
         <v>119</v>
       </c>
       <c r="H102" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I102" t="s">
         <v>82</v>
@@ -7181,7 +7175,7 @@
         <v>77</v>
       </c>
       <c r="C103" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D103" t="s">
         <v>85</v>
@@ -7196,7 +7190,7 @@
         <v>167</v>
       </c>
       <c r="H103" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J103" t="s">
         <v>208</v>
@@ -7234,10 +7228,10 @@
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H104" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="I104" t="s">
         <v>82</v>
@@ -7322,7 +7316,7 @@
         <v>32</v>
       </c>
       <c r="G106" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H106" t="s">
         <v>153</v>
@@ -7366,7 +7360,7 @@
         <v>32</v>
       </c>
       <c r="G107" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H107" t="s">
         <v>153</v>
@@ -7436,13 +7430,13 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B109" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C109" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D109" t="s">
         <v>85</v>
@@ -7454,10 +7448,10 @@
         <v>32</v>
       </c>
       <c r="G109" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H109" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J109" t="s">
         <v>218</v>
@@ -7477,13 +7471,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B110" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C110" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D110" t="s">
         <v>85</v>
@@ -7498,7 +7492,7 @@
         <v>167</v>
       </c>
       <c r="H110" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J110" t="s">
         <v>218</v>
@@ -7536,10 +7530,10 @@
         <v>13</v>
       </c>
       <c r="G111" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H111" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J111" t="s">
         <v>218</v>
@@ -7577,10 +7571,10 @@
         <v>13</v>
       </c>
       <c r="G112" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H112" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I112" t="s">
         <v>82</v>
@@ -7621,10 +7615,10 @@
         <v>13</v>
       </c>
       <c r="G113" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H113" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J113" t="s">
         <v>218</v>
@@ -7662,10 +7656,10 @@
         <v>13</v>
       </c>
       <c r="G114" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H114" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I114" t="s">
         <v>82</v>
@@ -7694,7 +7688,7 @@
         <v>193</v>
       </c>
       <c r="C115" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D115" t="s">
         <v>85</v>
@@ -7706,10 +7700,10 @@
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H115" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I115" t="s">
         <v>82</v>
@@ -7732,13 +7726,13 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B116" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C116" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D116" t="s">
         <v>85</v>
@@ -7750,10 +7744,10 @@
         <v>13</v>
       </c>
       <c r="G116" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H116" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J116" t="s">
         <v>218</v>
@@ -7773,13 +7767,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B117" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C117" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D117" t="s">
         <v>85</v>
@@ -7791,10 +7785,10 @@
         <v>32</v>
       </c>
       <c r="G117" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H117" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I117" t="s">
         <v>82</v>
@@ -7817,13 +7811,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B118" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C118" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D118" t="s">
         <v>85</v>
@@ -7835,10 +7829,10 @@
         <v>13</v>
       </c>
       <c r="G118" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H118" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J118" t="s">
         <v>218</v>
@@ -7861,7 +7855,7 @@
         <v>181</v>
       </c>
       <c r="B119" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C119" t="s">
         <v>194</v>
@@ -7876,10 +7870,10 @@
         <v>13</v>
       </c>
       <c r="G119" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H119" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="J119" t="s">
         <v>218</v>
@@ -7917,10 +7911,10 @@
         <v>13</v>
       </c>
       <c r="G120" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H120" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J120" t="s">
         <v>218</v>
@@ -7940,13 +7934,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B121" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C121" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D121" t="s">
         <v>85</v>
@@ -7958,10 +7952,10 @@
         <v>13</v>
       </c>
       <c r="G121" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H121" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I121" t="s">
         <v>82</v>
@@ -7984,13 +7978,13 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B122" t="s">
+        <v>260</v>
+      </c>
+      <c r="C122" t="s">
         <v>261</v>
-      </c>
-      <c r="C122" t="s">
-        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>85</v>
@@ -8002,10 +7996,10 @@
         <v>13</v>
       </c>
       <c r="G122" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H122" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J122" t="s">
         <v>218</v>
@@ -8025,13 +8019,13 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B123" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D123" t="s">
         <v>85</v>
@@ -8043,10 +8037,10 @@
         <v>13</v>
       </c>
       <c r="G123" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H123" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I123" t="s">
         <v>82</v>
@@ -8069,13 +8063,13 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B124" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D124" t="s">
         <v>85</v>
@@ -8087,13 +8081,13 @@
         <v>13</v>
       </c>
       <c r="G124" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H124" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I124" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J124" t="s">
         <v>218</v>
@@ -8113,13 +8107,13 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B125" t="s">
+        <v>268</v>
+      </c>
+      <c r="C125" t="s">
         <v>269</v>
-      </c>
-      <c r="C125" t="s">
-        <v>270</v>
       </c>
       <c r="D125" t="s">
         <v>85</v>
@@ -8131,10 +8125,10 @@
         <v>13</v>
       </c>
       <c r="G125" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H125" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J125" t="s">
         <v>218</v>
@@ -8154,13 +8148,13 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B126" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C126" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D126" t="s">
         <v>85</v>
@@ -8172,10 +8166,10 @@
         <v>13</v>
       </c>
       <c r="G126" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H126" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I126" t="s">
         <v>82</v>
@@ -8216,10 +8210,10 @@
         <v>13</v>
       </c>
       <c r="G127" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H127" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I127" t="s">
         <v>82</v>
@@ -8242,13 +8236,13 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B128" t="s">
         <v>607</v>
       </c>
-      <c r="B128" t="s">
-        <v>610</v>
-      </c>
       <c r="C128" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D128" t="s">
         <v>85</v>
@@ -8260,10 +8254,10 @@
         <v>13</v>
       </c>
       <c r="G128" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H128" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="I128" t="s">
         <v>61</v>
@@ -8286,13 +8280,13 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B129" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C129" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D129" t="s">
         <v>85</v>
@@ -8304,10 +8298,10 @@
         <v>13</v>
       </c>
       <c r="G129" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H129" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J129" t="s">
         <v>218</v>
@@ -8330,7 +8324,7 @@
         <v>183</v>
       </c>
       <c r="B130" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C130" t="s">
         <v>198</v>
@@ -8345,10 +8339,10 @@
         <v>13</v>
       </c>
       <c r="G130" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H130" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I130" t="s">
         <v>82</v>
@@ -8371,13 +8365,13 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B131" t="s">
+        <v>266</v>
+      </c>
+      <c r="C131" t="s">
         <v>267</v>
-      </c>
-      <c r="C131" t="s">
-        <v>268</v>
       </c>
       <c r="D131" t="s">
         <v>85</v>
@@ -8389,10 +8383,10 @@
         <v>13</v>
       </c>
       <c r="G131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H131" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J131" t="s">
         <v>209</v>
@@ -8412,13 +8406,13 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B132" t="s">
         <v>197</v>
       </c>
       <c r="C132" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D132" t="s">
         <v>85</v>
@@ -8430,10 +8424,10 @@
         <v>13</v>
       </c>
       <c r="G132" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H132" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J132" t="s">
         <v>218</v>
@@ -8459,7 +8453,7 @@
         <v>205</v>
       </c>
       <c r="C133" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D133" t="s">
         <v>85</v>
@@ -8515,16 +8509,16 @@
         <v>13</v>
       </c>
       <c r="G134" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H134" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="I134" t="s">
         <v>156</v>
       </c>
       <c r="J134" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="K134" t="s">
         <v>55</v>
@@ -8559,16 +8553,16 @@
         <v>13</v>
       </c>
       <c r="G135" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H135" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="I135" t="s">
         <v>82</v>
       </c>
       <c r="J135" t="s">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="K135" t="s">
         <v>55</v>
@@ -8585,13 +8579,13 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B136" t="s">
         <v>272</v>
       </c>
-      <c r="B136" t="s">
-        <v>273</v>
-      </c>
       <c r="C136" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D136" t="s">
         <v>85</v>
@@ -8606,7 +8600,7 @@
         <v>167</v>
       </c>
       <c r="H136" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I136" t="s">
         <v>156</v>
@@ -8629,13 +8623,13 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B137" t="s">
+        <v>278</v>
+      </c>
+      <c r="C137" t="s">
         <v>277</v>
-      </c>
-      <c r="B137" t="s">
-        <v>279</v>
-      </c>
-      <c r="C137" t="s">
-        <v>278</v>
       </c>
       <c r="D137" t="s">
         <v>85</v>
@@ -8650,7 +8644,7 @@
         <v>167</v>
       </c>
       <c r="H137" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J137" t="s">
         <v>218</v>
@@ -8670,13 +8664,13 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B138" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C138" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D138" t="s">
         <v>85</v>
@@ -8688,10 +8682,10 @@
         <v>13</v>
       </c>
       <c r="G138" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H138" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J138" t="s">
         <v>104</v>
@@ -8711,13 +8705,13 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B139" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C139" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D139" t="s">
         <v>85</v>
@@ -8732,7 +8726,7 @@
         <v>169</v>
       </c>
       <c r="H139" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J139" t="s">
         <v>104</v>
@@ -8752,13 +8746,13 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B140" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C140" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D140" t="s">
         <v>85</v>
@@ -8770,10 +8764,10 @@
         <v>13</v>
       </c>
       <c r="G140" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H140" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J140" t="s">
         <v>104</v>
@@ -8793,13 +8787,13 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B141" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C141" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D141" t="s">
         <v>85</v>
@@ -8811,10 +8805,10 @@
         <v>13</v>
       </c>
       <c r="G141" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H141" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="I141" t="s">
         <v>156</v>
@@ -8837,13 +8831,13 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B142" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C142" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D142" t="s">
         <v>85</v>
@@ -8858,7 +8852,7 @@
         <v>167</v>
       </c>
       <c r="H142" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J142" t="s">
         <v>102</v>
@@ -8878,13 +8872,13 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B143" t="s">
+        <v>354</v>
+      </c>
+      <c r="C143" t="s">
         <v>356</v>
-      </c>
-      <c r="C143" t="s">
-        <v>358</v>
       </c>
       <c r="D143" t="s">
         <v>85</v>
@@ -8896,10 +8890,10 @@
         <v>13</v>
       </c>
       <c r="G143" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H143" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I143" t="s">
         <v>82</v>
@@ -8922,13 +8916,13 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B144" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C144" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D144" t="s">
         <v>85</v>
@@ -8940,10 +8934,10 @@
         <v>13</v>
       </c>
       <c r="G144" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H144" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="I144" t="s">
         <v>82</v>
@@ -8966,13 +8960,13 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B145" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C145" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D145" t="s">
         <v>85</v>
@@ -8987,7 +8981,7 @@
         <v>169</v>
       </c>
       <c r="H145" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J145" t="s">
         <v>102</v>
@@ -9007,13 +9001,13 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B146" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C146" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D146" t="s">
         <v>85</v>
@@ -9025,7 +9019,7 @@
         <v>13</v>
       </c>
       <c r="G146" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H146" t="s">
         <v>120</v>
@@ -9048,13 +9042,13 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B147" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C147" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D147" t="s">
         <v>85</v>
@@ -9066,10 +9060,10 @@
         <v>13</v>
       </c>
       <c r="G147" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H147" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I147" t="s">
         <v>82</v>
@@ -9092,13 +9086,13 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B148" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C148" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D148" t="s">
         <v>85</v>
@@ -9110,10 +9104,10 @@
         <v>32</v>
       </c>
       <c r="G148" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H148" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I148" t="s">
         <v>82</v>
@@ -9136,13 +9130,13 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B149" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C149" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D149" t="s">
         <v>85</v>
@@ -9154,10 +9148,10 @@
         <v>13</v>
       </c>
       <c r="G149" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H149" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I149" t="s">
         <v>82</v>
@@ -9180,13 +9174,13 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B150" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C150" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D150" t="s">
         <v>85</v>
@@ -9198,10 +9192,10 @@
         <v>13</v>
       </c>
       <c r="G150" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H150" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I150" t="s">
         <v>82</v>
@@ -9224,13 +9218,13 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B151" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C151" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D151" t="s">
         <v>85</v>
@@ -9242,10 +9236,10 @@
         <v>13</v>
       </c>
       <c r="G151" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H151" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I151" t="s">
         <v>82</v>
@@ -9268,13 +9262,13 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B152" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C152" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D152" t="s">
         <v>85</v>
@@ -9289,13 +9283,13 @@
         <v>167</v>
       </c>
       <c r="H152" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="I152" t="s">
         <v>156</v>
       </c>
       <c r="J152" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K152" t="s">
         <v>55</v>
@@ -9312,13 +9306,13 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B153" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C153" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D153" t="s">
         <v>85</v>
@@ -9330,16 +9324,16 @@
         <v>32</v>
       </c>
       <c r="G153" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H153" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I153" t="s">
         <v>156</v>
       </c>
       <c r="J153" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K153" t="s">
         <v>55</v>
@@ -9356,13 +9350,13 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B154" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C154" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D154" t="s">
         <v>85</v>
@@ -9377,10 +9371,10 @@
         <v>167</v>
       </c>
       <c r="H154" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J154" t="s">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="K154" t="s">
         <v>55</v>
@@ -9397,13 +9391,13 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B155" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C155" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D155" t="s">
         <v>85</v>
@@ -9418,7 +9412,7 @@
         <v>119</v>
       </c>
       <c r="H155" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="I155" t="s">
         <v>82</v>
@@ -9441,13 +9435,13 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B156" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C156" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D156" t="s">
         <v>85</v>
@@ -9462,7 +9456,7 @@
         <v>167</v>
       </c>
       <c r="H156" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="I156" t="s">
         <v>82</v>
@@ -9485,13 +9479,13 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B157" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C157" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D157" t="s">
         <v>85</v>
@@ -9506,7 +9500,7 @@
         <v>167</v>
       </c>
       <c r="H157" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J157" t="s">
         <v>211</v>
@@ -9526,13 +9520,13 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B158" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C158" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D158" t="s">
         <v>85</v>
@@ -9570,13 +9564,13 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B159" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C159" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D159" t="s">
         <v>85</v>
@@ -9591,7 +9585,7 @@
         <v>167</v>
       </c>
       <c r="H159" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I159" t="s">
         <v>82</v>
@@ -9614,13 +9608,13 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B160" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C160" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D160" t="s">
         <v>85</v>
@@ -9632,10 +9626,10 @@
         <v>13</v>
       </c>
       <c r="G160" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H160" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I160" t="s">
         <v>82</v>
@@ -9658,13 +9652,13 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B161" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C161" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D161" t="s">
         <v>85</v>
@@ -9679,7 +9673,7 @@
         <v>167</v>
       </c>
       <c r="H161" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I161" t="s">
         <v>82</v>
@@ -9702,13 +9696,13 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B162" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C162" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D162" t="s">
         <v>85</v>
@@ -9723,10 +9717,10 @@
         <v>167</v>
       </c>
       <c r="H162" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J162" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="K162" t="s">
         <v>55</v>
@@ -9743,13 +9737,13 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B163" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C163" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D163" t="s">
         <v>85</v>
@@ -9784,13 +9778,13 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B164" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C164" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D164" t="s">
         <v>85</v>
@@ -9802,16 +9796,16 @@
         <v>32</v>
       </c>
       <c r="G164" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="H164" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="I164" t="s">
         <v>82</v>
       </c>
       <c r="J164" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="K164" t="s">
         <v>55</v>
@@ -9828,13 +9822,13 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B165" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C165" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D165" t="s">
         <v>85</v>
@@ -9846,10 +9840,10 @@
         <v>13</v>
       </c>
       <c r="G165" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H165" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="I165" t="s">
         <v>156</v>
@@ -9872,13 +9866,13 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B166" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C166" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D166" t="s">
         <v>85</v>
@@ -9890,10 +9884,10 @@
         <v>13</v>
       </c>
       <c r="G166" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H166" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J166" t="s">
         <v>218</v>
@@ -9913,13 +9907,13 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B167" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C167" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="D167" t="s">
         <v>85</v>
@@ -9934,7 +9928,7 @@
         <v>167</v>
       </c>
       <c r="H167" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I167" t="s">
         <v>82</v>
@@ -9957,13 +9951,13 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B168" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C168" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D168" t="s">
         <v>85</v>
@@ -9998,13 +9992,13 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B169" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C169" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D169" t="s">
         <v>85</v>
@@ -10019,13 +10013,13 @@
         <v>167</v>
       </c>
       <c r="H169" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="I169" t="s">
         <v>61</v>
       </c>
       <c r="J169" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="K169" t="s">
         <v>55</v>
@@ -10042,13 +10036,13 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B170" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C170" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D170" t="s">
         <v>85</v>
@@ -10063,13 +10057,13 @@
         <v>167</v>
       </c>
       <c r="H170" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I170" t="s">
         <v>82</v>
       </c>
       <c r="J170" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="K170" t="s">
         <v>55</v>
@@ -10086,13 +10080,13 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B171" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C171" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D171" t="s">
         <v>54</v>
@@ -10110,7 +10104,7 @@
         <v>28</v>
       </c>
       <c r="J171" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="K171" t="s">
         <v>56</v>
@@ -10127,13 +10121,13 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B172" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C172" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D172" t="s">
         <v>54</v>
@@ -10145,13 +10139,13 @@
         <v>13</v>
       </c>
       <c r="G172" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H172" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J172" t="s">
-        <v>446</v>
+        <v>208</v>
       </c>
       <c r="K172" t="s">
         <v>55</v>
@@ -10168,13 +10162,13 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B173" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C173" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D173" t="s">
         <v>54</v>
@@ -10186,13 +10180,13 @@
         <v>13</v>
       </c>
       <c r="G173" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H173" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J173" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="K173" t="s">
         <v>55</v>
@@ -10209,13 +10203,13 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B174" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C174" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D174" t="s">
         <v>54</v>
@@ -10230,13 +10224,13 @@
         <v>167</v>
       </c>
       <c r="H174" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I174" t="s">
         <v>82</v>
       </c>
       <c r="J174" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="K174" t="s">
         <v>55</v>
@@ -10253,13 +10247,13 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B175" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C175" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D175" t="s">
         <v>54</v>
@@ -10277,7 +10271,7 @@
         <v>153</v>
       </c>
       <c r="J175" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K175" t="s">
         <v>55</v>
@@ -10294,13 +10288,13 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B176" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C176" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D176" t="s">
         <v>54</v>
@@ -10315,7 +10309,7 @@
         <v>167</v>
       </c>
       <c r="H176" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I176" t="s">
         <v>166</v>
@@ -10338,13 +10332,13 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B177" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C177" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D177" t="s">
         <v>54</v>
@@ -10359,7 +10353,7 @@
         <v>167</v>
       </c>
       <c r="H177" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="I177" t="s">
         <v>156</v>
@@ -10382,13 +10376,13 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B178" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C178" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D178" t="s">
         <v>54</v>
@@ -10400,16 +10394,16 @@
         <v>32</v>
       </c>
       <c r="G178" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H178" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I178" t="s">
         <v>82</v>
       </c>
       <c r="J178" t="s">
-        <v>644</v>
+        <v>208</v>
       </c>
       <c r="K178" t="s">
         <v>55</v>
@@ -10426,13 +10420,13 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B179" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C179" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D179" t="s">
         <v>54</v>
@@ -10447,7 +10441,7 @@
         <v>167</v>
       </c>
       <c r="H179" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I179" t="s">
         <v>61</v>
@@ -10470,13 +10464,13 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B180" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C180" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D180" t="s">
         <v>85</v>
@@ -10488,16 +10482,16 @@
         <v>13</v>
       </c>
       <c r="G180" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H180" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="I180" t="s">
         <v>60</v>
       </c>
       <c r="J180" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="K180" t="s">
         <v>55</v>
@@ -10514,13 +10508,13 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B181" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C181" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D181" t="s">
         <v>85</v>
@@ -10532,10 +10526,10 @@
         <v>13</v>
       </c>
       <c r="G181" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H181" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="I181" t="s">
         <v>82</v>
@@ -10558,13 +10552,13 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B182" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C182" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D182" t="s">
         <v>85</v>
@@ -10579,7 +10573,7 @@
         <v>167</v>
       </c>
       <c r="H182" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I182" t="s">
         <v>82</v>
@@ -10602,13 +10596,13 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B183" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C183" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D183" t="s">
         <v>85</v>
@@ -10623,7 +10617,7 @@
         <v>167</v>
       </c>
       <c r="H183" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I183" t="s">
         <v>82</v>
@@ -10646,13 +10640,13 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B184" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C184" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D184" t="s">
         <v>85</v>
@@ -10664,10 +10658,10 @@
         <v>13</v>
       </c>
       <c r="G184" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H184" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J184" t="s">
         <v>104</v>
@@ -10687,13 +10681,13 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B185" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C185" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D185" t="s">
         <v>85</v>
@@ -10708,7 +10702,7 @@
         <v>167</v>
       </c>
       <c r="H185" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J185" t="s">
         <v>218</v>
@@ -10728,13 +10722,13 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B186" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C186" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D186" t="s">
         <v>85</v>
@@ -10746,10 +10740,10 @@
         <v>13</v>
       </c>
       <c r="G186" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H186" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J186" t="s">
         <v>104</v>
@@ -10769,13 +10763,13 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B187" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C187" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D187" t="s">
         <v>85</v>
@@ -10787,10 +10781,10 @@
         <v>13</v>
       </c>
       <c r="G187" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H187" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J187" t="s">
         <v>104</v>
@@ -10810,13 +10804,13 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B188" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C188" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D188" t="s">
         <v>85</v>
@@ -10831,13 +10825,13 @@
         <v>167</v>
       </c>
       <c r="H188" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I188" t="s">
         <v>156</v>
       </c>
       <c r="J188" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K188" t="s">
         <v>55</v>
@@ -10854,13 +10848,13 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B189" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C189" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D189" t="s">
         <v>85</v>
@@ -10872,10 +10866,10 @@
         <v>32</v>
       </c>
       <c r="G189" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H189" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J189" t="s">
         <v>102</v>
@@ -10895,13 +10889,13 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B190" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C190" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D190" t="s">
         <v>85</v>
@@ -10913,10 +10907,10 @@
         <v>32</v>
       </c>
       <c r="G190" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H190" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J190" t="s">
         <v>102</v>
@@ -10936,13 +10930,13 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B191" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C191" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D191" t="s">
         <v>85</v>
@@ -10957,13 +10951,13 @@
         <v>167</v>
       </c>
       <c r="H191" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I191" t="s">
         <v>156</v>
       </c>
       <c r="J191" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K191" t="s">
         <v>55</v>
@@ -10980,13 +10974,13 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B192" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C192" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D192" t="s">
         <v>85</v>
@@ -10998,10 +10992,10 @@
         <v>32</v>
       </c>
       <c r="G192" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H192" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J192" t="s">
         <v>218</v>
@@ -11021,13 +11015,13 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B193" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C193" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D193" t="s">
         <v>54</v>
@@ -11059,13 +11053,13 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B194" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C194" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D194" t="s">
         <v>54</v>
@@ -11100,13 +11094,13 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B195" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C195" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D195" t="s">
         <v>54</v>
@@ -11141,13 +11135,13 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B196" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C196" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D196" t="s">
         <v>54</v>
@@ -11159,13 +11153,13 @@
         <v>32</v>
       </c>
       <c r="G196" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="H196" t="s">
         <v>120</v>
       </c>
       <c r="J196" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K196" t="s">
         <v>55</v>
@@ -11182,10 +11176,10 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B197" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D197" t="s">
         <v>54</v>
@@ -11200,7 +11194,7 @@
         <v>167</v>
       </c>
       <c r="H197" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I197" t="s">
         <v>61</v>
@@ -11223,13 +11217,13 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B198" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C198" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D198" t="s">
         <v>54</v>
@@ -11241,13 +11235,13 @@
         <v>32</v>
       </c>
       <c r="G198" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="H198" t="s">
         <v>120</v>
       </c>
       <c r="J198" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K198" t="s">
         <v>55</v>
@@ -11264,13 +11258,13 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B199" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C199" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D199" t="s">
         <v>54</v>
@@ -11282,13 +11276,13 @@
         <v>32</v>
       </c>
       <c r="G199" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="H199" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J199" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K199" t="s">
         <v>55</v>
@@ -11305,13 +11299,13 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B200" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C200" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D200" t="s">
         <v>54</v>
@@ -11329,7 +11323,7 @@
         <v>153</v>
       </c>
       <c r="I200" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J200" t="s">
         <v>84</v>
@@ -11349,13 +11343,13 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B201" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C201" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D201" t="s">
         <v>54</v>
@@ -11367,13 +11361,13 @@
         <v>32</v>
       </c>
       <c r="G201" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="H201" t="s">
         <v>120</v>
       </c>
       <c r="J201" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K201" t="s">
         <v>55</v>
@@ -11390,10 +11384,10 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B202" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D202" t="s">
         <v>54</v>
@@ -11408,7 +11402,7 @@
         <v>169</v>
       </c>
       <c r="H202" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J202" t="s">
         <v>208</v>
@@ -11428,13 +11422,13 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B203" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C203" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D203" t="s">
         <v>54</v>
@@ -11446,7 +11440,7 @@
         <v>32</v>
       </c>
       <c r="G203" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="H203" t="s">
         <v>120</v>
@@ -11469,13 +11463,13 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B204" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C204" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D204" t="s">
         <v>54</v>
@@ -11490,7 +11484,7 @@
         <v>169</v>
       </c>
       <c r="H204" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="J204" t="s">
         <v>208</v>
@@ -11510,13 +11504,13 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B205" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C205" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D205" t="s">
         <v>54</v>
@@ -11531,10 +11525,10 @@
         <v>167</v>
       </c>
       <c r="H205" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I205" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J205" t="s">
         <v>208</v>
@@ -11554,7 +11548,7 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B206" t="s">
         <v>29</v>
@@ -11572,7 +11566,7 @@
         <v>171</v>
       </c>
       <c r="H206" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I206" t="s">
         <v>61</v>
@@ -11595,13 +11589,13 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B207" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C207" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D207" t="s">
         <v>54</v>
@@ -11616,7 +11610,7 @@
         <v>167</v>
       </c>
       <c r="H207" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I207" t="s">
         <v>156</v>
@@ -11639,13 +11633,13 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B208" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C208" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D208" t="s">
         <v>54</v>
@@ -11660,7 +11654,7 @@
         <v>119</v>
       </c>
       <c r="H208" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I208" t="s">
         <v>82</v>
@@ -11683,13 +11677,13 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B209" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C209" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D209" t="s">
         <v>54</v>
@@ -11704,10 +11698,10 @@
         <v>167</v>
       </c>
       <c r="H209" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J209" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K209" t="s">
         <v>55</v>
@@ -11724,13 +11718,13 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B210" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C210" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D210" t="s">
         <v>54</v>
@@ -11742,16 +11736,16 @@
         <v>13</v>
       </c>
       <c r="G210" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H210" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I210" t="s">
         <v>156</v>
       </c>
       <c r="J210" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K210" t="s">
         <v>55</v>
@@ -11768,13 +11762,13 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B211" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C211" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D211" t="s">
         <v>54</v>
@@ -11789,7 +11783,7 @@
         <v>119</v>
       </c>
       <c r="H211" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I211" t="s">
         <v>82</v>
@@ -11812,10 +11806,10 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B212" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D212" t="s">
         <v>54</v>
@@ -11830,7 +11824,7 @@
         <v>167</v>
       </c>
       <c r="H212" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J212" t="s">
         <v>208</v>
@@ -11850,10 +11844,10 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B213" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D213" t="s">
         <v>54</v>
@@ -11874,7 +11868,7 @@
         <v>82</v>
       </c>
       <c r="J213" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="K213" t="s">
         <v>55</v>
@@ -11891,13 +11885,13 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B214" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C214" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D214" t="s">
         <v>54</v>
@@ -11909,16 +11903,16 @@
         <v>13</v>
       </c>
       <c r="G214" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H214" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I214" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J214" t="s">
-        <v>654</v>
+        <v>209</v>
       </c>
       <c r="K214" t="s">
         <v>55</v>
@@ -11935,13 +11929,13 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B215" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C215" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D215" t="s">
         <v>54</v>
@@ -11956,10 +11950,10 @@
         <v>118</v>
       </c>
       <c r="H215" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I215" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J215" t="s">
         <v>208</v>
@@ -11979,13 +11973,13 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B216" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C216" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D216" t="s">
         <v>54</v>
@@ -12000,7 +11994,7 @@
         <v>167</v>
       </c>
       <c r="H216" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J216" t="s">
         <v>208</v>
@@ -12020,13 +12014,13 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B217" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C217" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D217" t="s">
         <v>54</v>
@@ -12041,7 +12035,7 @@
         <v>169</v>
       </c>
       <c r="H217" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J217" t="s">
         <v>84</v>
@@ -12061,13 +12055,13 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B218" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C218" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D218" t="s">
         <v>85</v>
@@ -12082,7 +12076,7 @@
         <v>167</v>
       </c>
       <c r="H218" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="J218" t="s">
         <v>218</v>
@@ -12102,10 +12096,10 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B219" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D219" t="s">
         <v>85</v>
@@ -12120,7 +12114,7 @@
         <v>169</v>
       </c>
       <c r="H219" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I219" t="s">
         <v>82</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1940DC-E0BB-7942-8EBE-B5475791D945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF708F7-193E-064B-9AC7-F0A981A5ECE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="793">
   <si>
     <t>id</t>
   </si>
@@ -2383,9 +2383,6 @@
     <t>Partido a partido</t>
   </si>
   <si>
-    <t>Camiseta para jornadas SED Sevilla</t>
-  </si>
-  <si>
     <t>deporte;social</t>
   </si>
   <si>
@@ -2393,6 +2390,15 @@
   </si>
   <si>
     <t>mural;postal;textil</t>
+  </si>
+  <si>
+    <t>Camiseta para jornadas SED Sevilla (2013)</t>
+  </si>
+  <si>
+    <t>Para felicitación Infantil-Primaria</t>
+  </si>
+  <si>
+    <t>Como grano de mostaza</t>
   </si>
 </sst>
 </file>
@@ -5375,7 +5381,7 @@
         <v>302</v>
       </c>
       <c r="J61" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -11811,6 +11817,9 @@
       <c r="B212" t="s">
         <v>777</v>
       </c>
+      <c r="C212" t="s">
+        <v>792</v>
+      </c>
       <c r="D212" t="s">
         <v>54</v>
       </c>
@@ -12061,7 +12070,7 @@
         <v>786</v>
       </c>
       <c r="C218" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D218" t="s">
         <v>85</v>
@@ -12076,7 +12085,7 @@
         <v>167</v>
       </c>
       <c r="H218" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="J218" t="s">
         <v>218</v>
@@ -12099,7 +12108,10 @@
         <v>763</v>
       </c>
       <c r="B219" t="s">
-        <v>789</v>
+        <v>788</v>
+      </c>
+      <c r="C219" t="s">
+        <v>791</v>
       </c>
       <c r="D219" t="s">
         <v>85</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF708F7-193E-064B-9AC7-F0A981A5ECE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DEF1BB-7C3E-A646-835C-63D8C6A14FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3243" uniqueCount="844">
   <si>
     <t>id</t>
   </si>
@@ -2353,9 +2353,6 @@
     <t>Te espero</t>
   </si>
   <si>
-    <t>Reinz: Marist Moustard</t>
-  </si>
-  <si>
     <t>Bienvenido a la familia</t>
   </si>
   <si>
@@ -2398,7 +2395,163 @@
     <t>Para felicitación Infantil-Primaria</t>
   </si>
   <si>
-    <t>Como grano de mostaza</t>
+    <t>DIS-0089</t>
+  </si>
+  <si>
+    <t>DIS-0090</t>
+  </si>
+  <si>
+    <t>DIS-0091</t>
+  </si>
+  <si>
+    <t>DIS-0092</t>
+  </si>
+  <si>
+    <t>Piensa y Actúa</t>
+  </si>
+  <si>
+    <t>Campamento Urbano Huelva 2016</t>
+  </si>
+  <si>
+    <t>Camiseta SED</t>
+  </si>
+  <si>
+    <t>Camiseta Nuevo Horizonte 2026 (FMCH)</t>
+  </si>
+  <si>
+    <t>Conectados por María</t>
+  </si>
+  <si>
+    <t>Reinz: Marist Mustard</t>
+  </si>
+  <si>
+    <t>Como granos de mostaza</t>
+  </si>
+  <si>
+    <t>Un gran día para Dar Vida</t>
+  </si>
+  <si>
+    <t>Para taza GVX Sevilla</t>
+  </si>
+  <si>
+    <t>ILU-0131</t>
+  </si>
+  <si>
+    <t>ILU-0132</t>
+  </si>
+  <si>
+    <t>ILU-0133</t>
+  </si>
+  <si>
+    <t>ILU-0134</t>
+  </si>
+  <si>
+    <t>ILU-0135</t>
+  </si>
+  <si>
+    <t>ILU-0136</t>
+  </si>
+  <si>
+    <t>ILU-0137</t>
+  </si>
+  <si>
+    <t>ILU-0138</t>
+  </si>
+  <si>
+    <t>ILU-0139</t>
+  </si>
+  <si>
+    <t>ILU-0140</t>
+  </si>
+  <si>
+    <t>ILU-0141</t>
+  </si>
+  <si>
+    <t>ILU-0142</t>
+  </si>
+  <si>
+    <t>ILU-0143</t>
+  </si>
+  <si>
+    <t>ILU-0144</t>
+  </si>
+  <si>
+    <t>ILU-0145</t>
+  </si>
+  <si>
+    <t>ILU-0146</t>
+  </si>
+  <si>
+    <t>Caridad</t>
+  </si>
+  <si>
+    <t>Muévete (Jaén)</t>
+  </si>
+  <si>
+    <t>La Chispa IV</t>
+  </si>
+  <si>
+    <t>María Niña</t>
+  </si>
+  <si>
+    <t>Nº Sª de Fourvière II</t>
+  </si>
+  <si>
+    <t>Con un solo corazón</t>
+  </si>
+  <si>
+    <t>Literal</t>
+  </si>
+  <si>
+    <t>Para Marcha Toledo</t>
+  </si>
+  <si>
+    <t>Consumo Justo</t>
+  </si>
+  <si>
+    <t>Conversión</t>
+  </si>
+  <si>
+    <t>Limosna</t>
+  </si>
+  <si>
+    <t>Oración</t>
+  </si>
+  <si>
+    <t>Ayuno</t>
+  </si>
+  <si>
+    <t>Fuertes de Corazón</t>
+  </si>
+  <si>
+    <t>Ceda</t>
+  </si>
+  <si>
+    <t>Hojas de Olivo</t>
+  </si>
+  <si>
+    <t>Hojas de Olivo II</t>
+  </si>
+  <si>
+    <t>Dando paso a la Navidad</t>
+  </si>
+  <si>
+    <t>Para lema Cuaresma Mediterránea</t>
+  </si>
+  <si>
+    <t>Cuaresma</t>
+  </si>
+  <si>
+    <t>Para campaña SED local</t>
+  </si>
+  <si>
+    <t>Logo Asociación</t>
+  </si>
+  <si>
+    <t>maria;champagnat</t>
+  </si>
+  <si>
+    <t>Acoger</t>
   </si>
 </sst>
 </file>
@@ -2755,17 +2908,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N219"/>
+  <dimension ref="A1:N239"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="32.33203125" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" customWidth="1"/>
+    <col min="3" max="3" width="31.1640625" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" customWidth="1"/>
     <col min="5" max="5" width="7.83203125" customWidth="1"/>
     <col min="6" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="26.1640625" customWidth="1"/>
     <col min="8" max="8" width="30.1640625" customWidth="1"/>
-    <col min="9" max="10" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" customWidth="1"/>
     <col min="11" max="11" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5381,7 +5535,7 @@
         <v>302</v>
       </c>
       <c r="J61" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -11815,10 +11969,10 @@
         <v>756</v>
       </c>
       <c r="B212" t="s">
-        <v>777</v>
+        <v>800</v>
       </c>
       <c r="C212" t="s">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="D212" t="s">
         <v>54</v>
@@ -11856,7 +12010,7 @@
         <v>757</v>
       </c>
       <c r="B213" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D213" t="s">
         <v>54</v>
@@ -11877,7 +12031,7 @@
         <v>82</v>
       </c>
       <c r="J213" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K213" t="s">
         <v>55</v>
@@ -11897,7 +12051,7 @@
         <v>758</v>
       </c>
       <c r="B214" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C214" t="s">
         <v>774</v>
@@ -11941,10 +12095,10 @@
         <v>759</v>
       </c>
       <c r="B215" t="s">
+        <v>780</v>
+      </c>
+      <c r="C215" t="s">
         <v>781</v>
-      </c>
-      <c r="C215" t="s">
-        <v>782</v>
       </c>
       <c r="D215" t="s">
         <v>54</v>
@@ -11985,7 +12139,7 @@
         <v>760</v>
       </c>
       <c r="B216" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C216" t="s">
         <v>380</v>
@@ -12026,10 +12180,10 @@
         <v>761</v>
       </c>
       <c r="B217" t="s">
+        <v>783</v>
+      </c>
+      <c r="C217" t="s">
         <v>784</v>
-      </c>
-      <c r="C217" t="s">
-        <v>785</v>
       </c>
       <c r="D217" t="s">
         <v>54</v>
@@ -12067,10 +12221,10 @@
         <v>762</v>
       </c>
       <c r="B218" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C218" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D218" t="s">
         <v>85</v>
@@ -12085,7 +12239,7 @@
         <v>167</v>
       </c>
       <c r="H218" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J218" t="s">
         <v>218</v>
@@ -12108,10 +12262,10 @@
         <v>763</v>
       </c>
       <c r="B219" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C219" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D219" t="s">
         <v>85</v>
@@ -12144,6 +12298,835 @@
         <v>15</v>
       </c>
       <c r="N219" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A220" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B220" t="s">
+        <v>795</v>
+      </c>
+      <c r="C220" t="s">
+        <v>797</v>
+      </c>
+      <c r="D220" t="s">
+        <v>85</v>
+      </c>
+      <c r="E220" t="s">
+        <v>33</v>
+      </c>
+      <c r="F220" t="s">
+        <v>13</v>
+      </c>
+      <c r="G220" t="s">
+        <v>167</v>
+      </c>
+      <c r="H220" t="s">
+        <v>594</v>
+      </c>
+      <c r="J220" t="s">
+        <v>389</v>
+      </c>
+      <c r="K220" t="s">
+        <v>56</v>
+      </c>
+      <c r="L220" t="s">
+        <v>14</v>
+      </c>
+      <c r="M220" t="s">
+        <v>15</v>
+      </c>
+      <c r="N220" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A221" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B221" t="s">
+        <v>796</v>
+      </c>
+      <c r="C221" t="s">
+        <v>798</v>
+      </c>
+      <c r="D221" t="s">
+        <v>85</v>
+      </c>
+      <c r="E221" t="s">
+        <v>33</v>
+      </c>
+      <c r="F221" t="s">
+        <v>13</v>
+      </c>
+      <c r="G221" t="s">
+        <v>167</v>
+      </c>
+      <c r="H221" t="s">
+        <v>662</v>
+      </c>
+      <c r="J221" t="s">
+        <v>218</v>
+      </c>
+      <c r="K221" t="s">
+        <v>56</v>
+      </c>
+      <c r="L221" t="s">
+        <v>14</v>
+      </c>
+      <c r="M221" t="s">
+        <v>15</v>
+      </c>
+      <c r="N221" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A222" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B222" t="s">
+        <v>799</v>
+      </c>
+      <c r="D222" t="s">
+        <v>85</v>
+      </c>
+      <c r="E222" t="s">
+        <v>58</v>
+      </c>
+      <c r="F222" t="s">
+        <v>13</v>
+      </c>
+      <c r="G222" t="s">
+        <v>119</v>
+      </c>
+      <c r="H222" t="s">
+        <v>369</v>
+      </c>
+      <c r="I222" t="s">
+        <v>82</v>
+      </c>
+      <c r="J222" t="s">
+        <v>102</v>
+      </c>
+      <c r="K222" t="s">
+        <v>55</v>
+      </c>
+      <c r="L222" t="s">
+        <v>14</v>
+      </c>
+      <c r="M222" t="s">
+        <v>15</v>
+      </c>
+      <c r="N222" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A223" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B223" t="s">
+        <v>802</v>
+      </c>
+      <c r="C223" t="s">
+        <v>803</v>
+      </c>
+      <c r="D223" t="s">
+        <v>85</v>
+      </c>
+      <c r="E223" t="s">
+        <v>58</v>
+      </c>
+      <c r="F223" t="s">
+        <v>13</v>
+      </c>
+      <c r="G223" t="s">
+        <v>167</v>
+      </c>
+      <c r="H223" t="s">
+        <v>380</v>
+      </c>
+      <c r="I223" t="s">
+        <v>82</v>
+      </c>
+      <c r="J223" t="s">
+        <v>379</v>
+      </c>
+      <c r="K223" t="s">
+        <v>55</v>
+      </c>
+      <c r="L223" t="s">
+        <v>14</v>
+      </c>
+      <c r="M223" t="s">
+        <v>15</v>
+      </c>
+      <c r="N223" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A224" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B224" t="s">
+        <v>835</v>
+      </c>
+      <c r="D224" t="s">
+        <v>54</v>
+      </c>
+      <c r="E224" t="s">
+        <v>33</v>
+      </c>
+      <c r="F224" t="s">
+        <v>13</v>
+      </c>
+      <c r="G224" t="s">
+        <v>167</v>
+      </c>
+      <c r="J224" t="s">
+        <v>208</v>
+      </c>
+      <c r="K224" t="s">
+        <v>55</v>
+      </c>
+      <c r="L224" t="s">
+        <v>14</v>
+      </c>
+      <c r="M224" t="s">
+        <v>15</v>
+      </c>
+      <c r="N224" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A225" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="B225" t="s">
+        <v>836</v>
+      </c>
+      <c r="D225" t="s">
+        <v>54</v>
+      </c>
+      <c r="E225" t="s">
+        <v>33</v>
+      </c>
+      <c r="F225" t="s">
+        <v>13</v>
+      </c>
+      <c r="G225" t="s">
+        <v>167</v>
+      </c>
+      <c r="J225" t="s">
+        <v>208</v>
+      </c>
+      <c r="K225" t="s">
+        <v>55</v>
+      </c>
+      <c r="L225" t="s">
+        <v>14</v>
+      </c>
+      <c r="M225" t="s">
+        <v>15</v>
+      </c>
+      <c r="N225" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A226" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B226" t="s">
+        <v>834</v>
+      </c>
+      <c r="C226" t="s">
+        <v>837</v>
+      </c>
+      <c r="D226" t="s">
+        <v>54</v>
+      </c>
+      <c r="E226" t="s">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>32</v>
+      </c>
+      <c r="G226" t="s">
+        <v>252</v>
+      </c>
+      <c r="J226" t="s">
+        <v>208</v>
+      </c>
+      <c r="K226" t="s">
+        <v>55</v>
+      </c>
+      <c r="L226" t="s">
+        <v>14</v>
+      </c>
+      <c r="M226" t="s">
+        <v>15</v>
+      </c>
+      <c r="N226" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A227" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B227" t="s">
+        <v>833</v>
+      </c>
+      <c r="C227" t="s">
+        <v>838</v>
+      </c>
+      <c r="D227" t="s">
+        <v>54</v>
+      </c>
+      <c r="E227" t="s">
+        <v>58</v>
+      </c>
+      <c r="F227" t="s">
+        <v>13</v>
+      </c>
+      <c r="G227" t="s">
+        <v>306</v>
+      </c>
+      <c r="H227" t="s">
+        <v>237</v>
+      </c>
+      <c r="I227" t="s">
+        <v>236</v>
+      </c>
+      <c r="J227" t="s">
+        <v>208</v>
+      </c>
+      <c r="K227" t="s">
+        <v>55</v>
+      </c>
+      <c r="L227" t="s">
+        <v>14</v>
+      </c>
+      <c r="M227" t="s">
+        <v>15</v>
+      </c>
+      <c r="N227" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A228" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B228" t="s">
+        <v>832</v>
+      </c>
+      <c r="C228" t="s">
+        <v>839</v>
+      </c>
+      <c r="D228" t="s">
+        <v>54</v>
+      </c>
+      <c r="E228" t="s">
+        <v>33</v>
+      </c>
+      <c r="F228" t="s">
+        <v>13</v>
+      </c>
+      <c r="G228" t="s">
+        <v>306</v>
+      </c>
+      <c r="H228" t="s">
+        <v>316</v>
+      </c>
+      <c r="I228" t="s">
+        <v>61</v>
+      </c>
+      <c r="J228" t="s">
+        <v>208</v>
+      </c>
+      <c r="K228" t="s">
+        <v>55</v>
+      </c>
+      <c r="L228" t="s">
+        <v>14</v>
+      </c>
+      <c r="M228" t="s">
+        <v>15</v>
+      </c>
+      <c r="N228" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A229" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B229" t="s">
+        <v>831</v>
+      </c>
+      <c r="C229" t="s">
+        <v>839</v>
+      </c>
+      <c r="D229" t="s">
+        <v>54</v>
+      </c>
+      <c r="E229" t="s">
+        <v>33</v>
+      </c>
+      <c r="F229" t="s">
+        <v>13</v>
+      </c>
+      <c r="G229" t="s">
+        <v>306</v>
+      </c>
+      <c r="H229" t="s">
+        <v>316</v>
+      </c>
+      <c r="I229" t="s">
+        <v>61</v>
+      </c>
+      <c r="J229" t="s">
+        <v>208</v>
+      </c>
+      <c r="K229" t="s">
+        <v>55</v>
+      </c>
+      <c r="L229" t="s">
+        <v>14</v>
+      </c>
+      <c r="M229" t="s">
+        <v>15</v>
+      </c>
+      <c r="N229" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A230" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B230" t="s">
+        <v>830</v>
+      </c>
+      <c r="C230" t="s">
+        <v>839</v>
+      </c>
+      <c r="D230" t="s">
+        <v>54</v>
+      </c>
+      <c r="E230" t="s">
+        <v>33</v>
+      </c>
+      <c r="F230" t="s">
+        <v>13</v>
+      </c>
+      <c r="G230" t="s">
+        <v>306</v>
+      </c>
+      <c r="H230" t="s">
+        <v>316</v>
+      </c>
+      <c r="I230" t="s">
+        <v>61</v>
+      </c>
+      <c r="J230" t="s">
+        <v>208</v>
+      </c>
+      <c r="K230" t="s">
+        <v>55</v>
+      </c>
+      <c r="L230" t="s">
+        <v>14</v>
+      </c>
+      <c r="M230" t="s">
+        <v>15</v>
+      </c>
+      <c r="N230" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A231" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B231" t="s">
+        <v>829</v>
+      </c>
+      <c r="C231" t="s">
+        <v>839</v>
+      </c>
+      <c r="D231" t="s">
+        <v>54</v>
+      </c>
+      <c r="E231" t="s">
+        <v>33</v>
+      </c>
+      <c r="F231" t="s">
+        <v>13</v>
+      </c>
+      <c r="G231" t="s">
+        <v>306</v>
+      </c>
+      <c r="H231" t="s">
+        <v>316</v>
+      </c>
+      <c r="I231" t="s">
+        <v>166</v>
+      </c>
+      <c r="J231" t="s">
+        <v>208</v>
+      </c>
+      <c r="K231" t="s">
+        <v>55</v>
+      </c>
+      <c r="L231" t="s">
+        <v>14</v>
+      </c>
+      <c r="M231" t="s">
+        <v>15</v>
+      </c>
+      <c r="N231" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A232" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="B232" t="s">
+        <v>828</v>
+      </c>
+      <c r="C232" t="s">
+        <v>840</v>
+      </c>
+      <c r="D232" t="s">
+        <v>54</v>
+      </c>
+      <c r="E232" t="s">
+        <v>58</v>
+      </c>
+      <c r="F232" t="s">
+        <v>13</v>
+      </c>
+      <c r="G232" t="s">
+        <v>167</v>
+      </c>
+      <c r="H232" t="s">
+        <v>557</v>
+      </c>
+      <c r="I232" t="s">
+        <v>82</v>
+      </c>
+      <c r="J232" t="s">
+        <v>227</v>
+      </c>
+      <c r="K232" t="s">
+        <v>55</v>
+      </c>
+      <c r="L232" t="s">
+        <v>14</v>
+      </c>
+      <c r="M232" t="s">
+        <v>15</v>
+      </c>
+      <c r="N232" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A233" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="B233" t="s">
+        <v>827</v>
+      </c>
+      <c r="C233" t="s">
+        <v>623</v>
+      </c>
+      <c r="D233" t="s">
+        <v>54</v>
+      </c>
+      <c r="E233" t="s">
+        <v>58</v>
+      </c>
+      <c r="F233" t="s">
+        <v>13</v>
+      </c>
+      <c r="G233" t="s">
+        <v>167</v>
+      </c>
+      <c r="J233" t="s">
+        <v>208</v>
+      </c>
+      <c r="K233" t="s">
+        <v>55</v>
+      </c>
+      <c r="L233" t="s">
+        <v>14</v>
+      </c>
+      <c r="M233" t="s">
+        <v>15</v>
+      </c>
+      <c r="N233" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A234" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B234" t="s">
+        <v>825</v>
+      </c>
+      <c r="C234" t="s">
+        <v>826</v>
+      </c>
+      <c r="D234" t="s">
+        <v>54</v>
+      </c>
+      <c r="E234" t="s">
+        <v>33</v>
+      </c>
+      <c r="F234" t="s">
+        <v>13</v>
+      </c>
+      <c r="G234" t="s">
+        <v>167</v>
+      </c>
+      <c r="H234" t="s">
+        <v>120</v>
+      </c>
+      <c r="J234" t="s">
+        <v>208</v>
+      </c>
+      <c r="K234" t="s">
+        <v>55</v>
+      </c>
+      <c r="L234" t="s">
+        <v>14</v>
+      </c>
+      <c r="M234" t="s">
+        <v>15</v>
+      </c>
+      <c r="N234" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A235" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="B235" t="s">
+        <v>824</v>
+      </c>
+      <c r="D235" t="s">
+        <v>54</v>
+      </c>
+      <c r="E235" t="s">
+        <v>133</v>
+      </c>
+      <c r="F235" t="s">
+        <v>32</v>
+      </c>
+      <c r="G235" t="s">
+        <v>169</v>
+      </c>
+      <c r="H235" t="s">
+        <v>842</v>
+      </c>
+      <c r="J235" t="s">
+        <v>443</v>
+      </c>
+      <c r="K235" t="s">
+        <v>55</v>
+      </c>
+      <c r="L235" t="s">
+        <v>14</v>
+      </c>
+      <c r="M235" t="s">
+        <v>15</v>
+      </c>
+      <c r="N235" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A236" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="B236" t="s">
+        <v>823</v>
+      </c>
+      <c r="C236" t="s">
+        <v>843</v>
+      </c>
+      <c r="D236" t="s">
+        <v>54</v>
+      </c>
+      <c r="E236" t="s">
+        <v>133</v>
+      </c>
+      <c r="F236" t="s">
+        <v>32</v>
+      </c>
+      <c r="G236" t="s">
+        <v>512</v>
+      </c>
+      <c r="H236" t="s">
+        <v>153</v>
+      </c>
+      <c r="I236" t="s">
+        <v>61</v>
+      </c>
+      <c r="J236" t="s">
+        <v>208</v>
+      </c>
+      <c r="K236" t="s">
+        <v>55</v>
+      </c>
+      <c r="L236" t="s">
+        <v>14</v>
+      </c>
+      <c r="M236" t="s">
+        <v>15</v>
+      </c>
+      <c r="N236" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A237" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="B237" t="s">
+        <v>822</v>
+      </c>
+      <c r="D237" t="s">
+        <v>54</v>
+      </c>
+      <c r="E237" t="s">
+        <v>33</v>
+      </c>
+      <c r="F237" t="s">
+        <v>13</v>
+      </c>
+      <c r="G237" t="s">
+        <v>167</v>
+      </c>
+      <c r="H237" t="s">
+        <v>380</v>
+      </c>
+      <c r="I237" t="s">
+        <v>61</v>
+      </c>
+      <c r="J237" t="s">
+        <v>443</v>
+      </c>
+      <c r="K237" t="s">
+        <v>55</v>
+      </c>
+      <c r="L237" t="s">
+        <v>14</v>
+      </c>
+      <c r="M237" t="s">
+        <v>15</v>
+      </c>
+      <c r="N237" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A238" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B238" t="s">
+        <v>821</v>
+      </c>
+      <c r="C238" t="s">
+        <v>841</v>
+      </c>
+      <c r="D238" t="s">
+        <v>54</v>
+      </c>
+      <c r="E238" t="s">
+        <v>58</v>
+      </c>
+      <c r="F238" t="s">
+        <v>32</v>
+      </c>
+      <c r="G238" t="s">
+        <v>169</v>
+      </c>
+      <c r="H238" t="s">
+        <v>594</v>
+      </c>
+      <c r="I238" t="s">
+        <v>166</v>
+      </c>
+      <c r="J238" t="s">
+        <v>208</v>
+      </c>
+      <c r="K238" t="s">
+        <v>55</v>
+      </c>
+      <c r="L238" t="s">
+        <v>14</v>
+      </c>
+      <c r="M238" t="s">
+        <v>15</v>
+      </c>
+      <c r="N238" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A239" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B239" t="s">
+        <v>820</v>
+      </c>
+      <c r="C239" t="s">
+        <v>839</v>
+      </c>
+      <c r="D239" t="s">
+        <v>54</v>
+      </c>
+      <c r="E239" t="s">
+        <v>33</v>
+      </c>
+      <c r="F239" t="s">
+        <v>13</v>
+      </c>
+      <c r="G239" t="s">
+        <v>306</v>
+      </c>
+      <c r="H239" t="s">
+        <v>316</v>
+      </c>
+      <c r="I239" t="s">
+        <v>61</v>
+      </c>
+      <c r="J239" t="s">
+        <v>208</v>
+      </c>
+      <c r="K239" t="s">
+        <v>55</v>
+      </c>
+      <c r="L239" t="s">
+        <v>14</v>
+      </c>
+      <c r="M239" t="s">
+        <v>15</v>
+      </c>
+      <c r="N239" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115B1396-B18D-3A4E-80F8-F8B3EAD53E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115B1396-B18D-3A4E-80F8-F8B3EAD53E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41983B5-D91D-E34D-9D7E-58D4A4C94AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13000,10 +13000,10 @@
         <v>32</v>
       </c>
       <c r="F237" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G237" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H237" t="s">
         <v>336</v>
@@ -13044,10 +13044,10 @@
         <v>52</v>
       </c>
       <c r="F238" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G238" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H238" t="s">
         <v>525</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41983B5-D91D-E34D-9D7E-58D4A4C94AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D7A226-15C3-A143-A31A-005A658C3023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3266" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="845">
   <si>
     <t>id</t>
   </si>
@@ -1675,9 +1675,6 @@
     <t>Be Light</t>
   </si>
   <si>
-    <t>Diseño para GVX</t>
-  </si>
-  <si>
     <t>Marcha Toledo</t>
   </si>
   <si>
@@ -2488,9 +2485,6 @@
     <t>Maori Marist Pillars - III</t>
   </si>
   <si>
-    <t>María, Buena Madre - V</t>
-  </si>
-  <si>
     <t>Maori Marist Pillars - IV</t>
   </si>
   <si>
@@ -2543,6 +2537,24 @@
   </si>
   <si>
     <t>monocolor</t>
+  </si>
+  <si>
+    <t>ILU-0147</t>
+  </si>
+  <si>
+    <t>ILU-0148</t>
+  </si>
+  <si>
+    <t>Cruz Espíritu - III</t>
+  </si>
+  <si>
+    <t>Confirmación, Pentecostés</t>
+  </si>
+  <si>
+    <t>Olivo</t>
+  </si>
+  <si>
+    <t>María, Buena Madre - VI</t>
   </si>
 </sst>
 </file>
@@ -2899,7 +2911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N241"/>
+  <dimension ref="A1:N243"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="23.6640625" customWidth="1"/>
@@ -2993,7 +3005,7 @@
         <v>182</v>
       </c>
       <c r="K2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="L2" t="s">
         <v>14</v>
@@ -3139,7 +3151,7 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C6" t="s">
         <v>82</v>
@@ -3183,7 +3195,7 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
@@ -3221,7 +3233,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C8" t="s">
         <v>289</v>
@@ -3265,7 +3277,7 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C9" t="s">
         <v>83</v>
@@ -3468,7 +3480,7 @@
         <v>190</v>
       </c>
       <c r="K13" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="L13" t="s">
         <v>14</v>
@@ -3632,7 +3644,7 @@
         <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H17" t="s">
         <v>53</v>
@@ -3661,10 +3673,10 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
+        <v>759</v>
+      </c>
+      <c r="C18" t="s">
         <v>760</v>
-      </c>
-      <c r="C18" t="s">
-        <v>761</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
@@ -3676,7 +3688,7 @@
         <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H18" t="s">
         <v>480</v>
@@ -3717,7 +3729,7 @@
         <v>31</v>
       </c>
       <c r="G19" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H19" t="s">
         <v>28</v>
@@ -3746,7 +3758,7 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C20" t="s">
         <v>56</v>
@@ -3787,7 +3799,7 @@
         <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C21" t="s">
         <v>56</v>
@@ -3831,7 +3843,7 @@
         <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
@@ -3872,10 +3884,10 @@
         <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C23" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
@@ -3931,7 +3943,7 @@
         <v>31</v>
       </c>
       <c r="G24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H24" t="s">
         <v>28</v>
@@ -3953,35 +3965,35 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>113</v>
+      <c r="A25" t="s">
+        <v>149</v>
       </c>
       <c r="B25" t="s">
-        <v>766</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>767</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H25" t="s">
-        <v>417</v>
+        <v>74</v>
       </c>
       <c r="J25" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="K25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L25" t="s">
         <v>14</v>
@@ -3995,34 +4007,34 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>114</v>
+        <v>357</v>
       </c>
       <c r="B26" t="s">
-        <v>768</v>
+        <v>373</v>
       </c>
       <c r="C26" t="s">
-        <v>769</v>
+        <v>374</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
         <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H26" t="s">
-        <v>418</v>
+        <v>483</v>
       </c>
       <c r="J26" t="s">
         <v>96</v>
       </c>
       <c r="K26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L26" t="s">
         <v>14</v>
@@ -4036,31 +4048,37 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>115</v>
+        <v>358</v>
       </c>
       <c r="B27" t="s">
-        <v>772</v>
+        <v>112</v>
+      </c>
+      <c r="C27" t="s">
+        <v>781</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>144</v>
+        <v>376</v>
       </c>
       <c r="H27" t="s">
-        <v>131</v>
+        <v>377</v>
+      </c>
+      <c r="I27" t="s">
+        <v>54</v>
       </c>
       <c r="J27" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="K27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L27" t="s">
         <v>14</v>
@@ -4074,16 +4092,19 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>770</v>
+        <v>68</v>
+      </c>
+      <c r="C28" t="s">
+        <v>292</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -4092,16 +4113,13 @@
         <v>142</v>
       </c>
       <c r="H28" t="s">
-        <v>131</v>
-      </c>
-      <c r="I28" t="s">
-        <v>55</v>
+        <v>484</v>
       </c>
       <c r="J28" t="s">
-        <v>557</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L28" t="s">
         <v>14</v>
@@ -4115,37 +4133,37 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>771</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
         <v>31</v>
       </c>
       <c r="G29" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="H29" t="s">
-        <v>328</v>
+        <v>28</v>
       </c>
       <c r="I29" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="J29" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="K29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L29" t="s">
         <v>14</v>
@@ -4159,13 +4177,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>118</v>
+        <v>571</v>
       </c>
       <c r="B30" t="s">
-        <v>773</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>575</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
@@ -4174,19 +4192,19 @@
         <v>120</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G30" t="s">
-        <v>221</v>
+        <v>146</v>
       </c>
       <c r="H30" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="J30" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K30" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L30" t="s">
         <v>14</v>
@@ -4200,13 +4218,13 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>119</v>
+        <v>664</v>
       </c>
       <c r="B31" t="s">
-        <v>774</v>
+        <v>375</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>680</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
@@ -4221,10 +4239,10 @@
         <v>144</v>
       </c>
       <c r="H31" t="s">
-        <v>131</v>
+        <v>485</v>
       </c>
       <c r="J31" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K31" t="s">
         <v>49</v>
@@ -4241,13 +4259,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>135</v>
+        <v>665</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>681</v>
       </c>
       <c r="C32" t="s">
-        <v>776</v>
+        <v>682</v>
       </c>
       <c r="D32" t="s">
         <v>48</v>
@@ -4262,10 +4280,13 @@
         <v>142</v>
       </c>
       <c r="H32" t="s">
-        <v>456</v>
+        <v>481</v>
+      </c>
+      <c r="I32" t="s">
+        <v>419</v>
       </c>
       <c r="J32" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K32" t="s">
         <v>49</v>
@@ -4282,13 +4303,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>136</v>
+        <v>666</v>
       </c>
       <c r="B33" t="s">
-        <v>775</v>
+        <v>112</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>824</v>
       </c>
       <c r="D33" t="s">
         <v>48</v>
@@ -4297,16 +4318,19 @@
         <v>120</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G33" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H33" t="s">
-        <v>482</v>
+        <v>481</v>
+      </c>
+      <c r="I33" t="s">
+        <v>55</v>
       </c>
       <c r="J33" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K33" t="s">
         <v>49</v>
@@ -4323,37 +4347,34 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>766</v>
       </c>
       <c r="D34" t="s">
         <v>48</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F34" t="s">
         <v>31</v>
       </c>
       <c r="G34" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="H34" t="s">
-        <v>189</v>
-      </c>
-      <c r="I34" t="s">
-        <v>141</v>
+        <v>417</v>
       </c>
       <c r="J34" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="K34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L34" t="s">
         <v>14</v>
@@ -4366,32 +4387,29 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>149</v>
+      <c r="A35" s="1" t="s">
+        <v>729</v>
       </c>
       <c r="B35" t="s">
-        <v>112</v>
-      </c>
-      <c r="C35" t="s">
-        <v>29</v>
+        <v>827</v>
       </c>
       <c r="D35" t="s">
         <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G35" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>753</v>
       </c>
       <c r="J35" t="s">
-        <v>96</v>
+        <v>390</v>
       </c>
       <c r="K35" t="s">
         <v>49</v>
@@ -4408,34 +4426,31 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="B36" t="s">
-        <v>187</v>
+        <v>767</v>
       </c>
       <c r="C36" t="s">
-        <v>188</v>
+        <v>768</v>
       </c>
       <c r="D36" t="s">
         <v>48</v>
       </c>
       <c r="E36" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G36" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H36" t="s">
-        <v>189</v>
-      </c>
-      <c r="I36" t="s">
-        <v>141</v>
+        <v>418</v>
       </c>
       <c r="J36" t="s">
-        <v>345</v>
+        <v>96</v>
       </c>
       <c r="K36" t="s">
         <v>49</v>
@@ -4452,37 +4467,31 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>196</v>
-      </c>
-      <c r="C37" t="s">
-        <v>197</v>
+        <v>771</v>
       </c>
       <c r="D37" t="s">
         <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G37" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H37" t="s">
-        <v>198</v>
-      </c>
-      <c r="I37" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="J37" t="s">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="K37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L37" t="s">
         <v>14</v>
@@ -4496,37 +4505,34 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
-      </c>
-      <c r="C38" t="s">
-        <v>201</v>
+        <v>769</v>
       </c>
       <c r="D38" t="s">
         <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="H38" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="I38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J38" t="s">
-        <v>390</v>
+        <v>556</v>
       </c>
       <c r="K38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L38" t="s">
         <v>14</v>
@@ -4540,13 +4546,13 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>193</v>
+        <v>117</v>
       </c>
       <c r="B39" t="s">
-        <v>202</v>
+        <v>770</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
         <v>48</v>
@@ -4555,22 +4561,22 @@
         <v>32</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G39" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s">
-        <v>204</v>
+        <v>328</v>
       </c>
       <c r="I39" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="J39" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L39" t="s">
         <v>14</v>
@@ -4584,34 +4590,31 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>194</v>
+        <v>118</v>
       </c>
       <c r="B40" t="s">
-        <v>206</v>
+        <v>772</v>
       </c>
       <c r="C40" t="s">
-        <v>207</v>
+        <v>122</v>
       </c>
       <c r="D40" t="s">
         <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>144</v>
+        <v>221</v>
       </c>
       <c r="H40" t="s">
-        <v>209</v>
-      </c>
-      <c r="I40" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="J40" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K40" t="s">
         <v>49</v>
@@ -4628,34 +4631,31 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>195</v>
+        <v>119</v>
       </c>
       <c r="B41" t="s">
-        <v>210</v>
+        <v>773</v>
       </c>
       <c r="C41" t="s">
-        <v>211</v>
+        <v>123</v>
       </c>
       <c r="D41" t="s">
         <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H41" t="s">
-        <v>204</v>
-      </c>
-      <c r="I41" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="J41" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="K41" t="s">
         <v>49</v>
@@ -4672,13 +4672,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="B42" t="s">
-        <v>788</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>775</v>
       </c>
       <c r="D42" t="s">
         <v>48</v>
@@ -4693,13 +4693,10 @@
         <v>142</v>
       </c>
       <c r="H42" t="s">
-        <v>488</v>
-      </c>
-      <c r="I42" t="s">
-        <v>55</v>
+        <v>456</v>
       </c>
       <c r="J42" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K42" t="s">
         <v>49</v>
@@ -4716,19 +4713,19 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>213</v>
+        <v>136</v>
       </c>
       <c r="B43" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="C43" t="s">
-        <v>414</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
         <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F43" t="s">
         <v>13</v>
@@ -4737,16 +4734,13 @@
         <v>142</v>
       </c>
       <c r="H43" t="s">
-        <v>488</v>
-      </c>
-      <c r="I43" t="s">
-        <v>55</v>
+        <v>482</v>
       </c>
       <c r="J43" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K43" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L43" t="s">
         <v>14</v>
@@ -4760,37 +4754,37 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>214</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C44" t="s">
-        <v>216</v>
+        <v>403</v>
       </c>
       <c r="D44" t="s">
         <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
         <v>142</v>
       </c>
       <c r="H44" t="s">
-        <v>488</v>
+        <v>131</v>
       </c>
       <c r="I44" t="s">
-        <v>55</v>
+        <v>419</v>
       </c>
       <c r="J44" t="s">
         <v>182</v>
       </c>
       <c r="K44" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L44" t="s">
         <v>14</v>
@@ -4804,34 +4798,34 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>215</v>
+        <v>618</v>
       </c>
       <c r="B45" t="s">
-        <v>217</v>
+        <v>844</v>
       </c>
       <c r="C45" t="s">
-        <v>218</v>
+        <v>662</v>
       </c>
       <c r="D45" t="s">
         <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G45" t="s">
         <v>142</v>
       </c>
       <c r="H45" t="s">
-        <v>488</v>
+        <v>131</v>
       </c>
       <c r="I45" t="s">
-        <v>134</v>
+        <v>419</v>
       </c>
       <c r="J45" t="s">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="K45" t="s">
         <v>49</v>
@@ -4848,34 +4842,31 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>247</v>
+        <v>574</v>
       </c>
       <c r="B46" t="s">
-        <v>248</v>
+        <v>581</v>
       </c>
       <c r="C46" t="s">
-        <v>412</v>
+        <v>582</v>
       </c>
       <c r="D46" t="s">
         <v>48</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F46" t="s">
         <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="H46" t="s">
-        <v>336</v>
-      </c>
-      <c r="I46" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="J46" t="s">
-        <v>182</v>
+        <v>390</v>
       </c>
       <c r="K46" t="s">
         <v>49</v>
@@ -4892,31 +4883,31 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>249</v>
+        <v>730</v>
       </c>
       <c r="B47" t="s">
-        <v>250</v>
+        <v>828</v>
       </c>
       <c r="C47" t="s">
-        <v>413</v>
+        <v>754</v>
       </c>
       <c r="D47" t="s">
         <v>48</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G47" t="s">
-        <v>142</v>
+        <v>450</v>
       </c>
       <c r="H47" t="s">
-        <v>336</v>
+        <v>131</v>
       </c>
       <c r="I47" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="J47" t="s">
         <v>182</v>
@@ -4936,37 +4927,37 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>251</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
-        <v>261</v>
+        <v>127</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E48" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="H48" t="s">
-        <v>209</v>
+        <v>131</v>
       </c>
       <c r="I48" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="J48" t="s">
-        <v>269</v>
+        <v>148</v>
       </c>
       <c r="K48" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L48" t="s">
         <v>14</v>
@@ -4980,37 +4971,37 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>252</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>263</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>264</v>
+        <v>129</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E49" t="s">
         <v>52</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G49" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="H49" t="s">
-        <v>265</v>
+        <v>131</v>
       </c>
       <c r="I49" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="J49" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L49" t="s">
         <v>14</v>
@@ -5024,37 +5015,37 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>253</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s">
-        <v>778</v>
+        <v>404</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>405</v>
       </c>
       <c r="D50" t="s">
         <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H50" t="s">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="I50" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J50" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K50" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="L50" t="s">
         <v>14</v>
@@ -5068,37 +5059,37 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>254</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s">
-        <v>779</v>
+        <v>454</v>
       </c>
       <c r="C51" t="s">
-        <v>267</v>
+        <v>455</v>
       </c>
       <c r="D51" t="s">
         <v>48</v>
       </c>
       <c r="E51" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F51" t="s">
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="H51" t="s">
-        <v>281</v>
+        <v>528</v>
       </c>
       <c r="I51" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="J51" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K51" t="s">
-        <v>840</v>
+        <v>51</v>
       </c>
       <c r="L51" t="s">
         <v>14</v>
@@ -5112,16 +5103,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>255</v>
+        <v>707</v>
       </c>
       <c r="B52" t="s">
-        <v>415</v>
-      </c>
-      <c r="C52" t="s">
-        <v>610</v>
+        <v>713</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E52" t="s">
         <v>52</v>
@@ -5130,19 +5118,19 @@
         <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>271</v>
+        <v>110</v>
       </c>
       <c r="H52" t="s">
-        <v>111</v>
+        <v>328</v>
       </c>
       <c r="I52" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="J52" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="K52" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L52" t="s">
         <v>14</v>
@@ -5156,19 +5144,19 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="B53" t="s">
-        <v>277</v>
+        <v>187</v>
       </c>
       <c r="C53" t="s">
-        <v>278</v>
+        <v>188</v>
       </c>
       <c r="D53" t="s">
         <v>48</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F53" t="s">
         <v>13</v>
@@ -5177,13 +5165,13 @@
         <v>142</v>
       </c>
       <c r="H53" t="s">
-        <v>279</v>
+        <v>189</v>
       </c>
       <c r="I53" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="J53" t="s">
-        <v>96</v>
+        <v>345</v>
       </c>
       <c r="K53" t="s">
         <v>49</v>
@@ -5200,16 +5188,19 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="B54" t="s">
-        <v>280</v>
+        <v>196</v>
+      </c>
+      <c r="C54" t="s">
+        <v>197</v>
       </c>
       <c r="D54" t="s">
         <v>48</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
@@ -5218,10 +5209,13 @@
         <v>142</v>
       </c>
       <c r="H54" t="s">
-        <v>281</v>
+        <v>198</v>
+      </c>
+      <c r="I54" t="s">
+        <v>76</v>
       </c>
       <c r="J54" t="s">
-        <v>96</v>
+        <v>199</v>
       </c>
       <c r="K54" t="s">
         <v>49</v>
@@ -5238,13 +5232,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s">
-        <v>780</v>
+        <v>200</v>
       </c>
       <c r="C55" t="s">
-        <v>270</v>
+        <v>201</v>
       </c>
       <c r="D55" t="s">
         <v>48</v>
@@ -5253,16 +5247,16 @@
         <v>32</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G55" t="s">
-        <v>272</v>
+        <v>109</v>
       </c>
       <c r="H55" t="s">
-        <v>282</v>
+        <v>205</v>
       </c>
       <c r="I55" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="J55" t="s">
         <v>390</v>
@@ -5282,19 +5276,19 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="B56" t="s">
-        <v>781</v>
+        <v>202</v>
       </c>
       <c r="C56" t="s">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="D56" t="s">
         <v>48</v>
       </c>
       <c r="E56" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F56" t="s">
         <v>13</v>
@@ -5303,16 +5297,16 @@
         <v>142</v>
       </c>
       <c r="H56" t="s">
-        <v>321</v>
+        <v>204</v>
       </c>
       <c r="I56" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="J56" t="s">
-        <v>283</v>
+        <v>182</v>
       </c>
       <c r="K56" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L56" t="s">
         <v>14</v>
@@ -5326,13 +5320,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
-        <v>285</v>
+        <v>206</v>
       </c>
       <c r="C57" t="s">
-        <v>286</v>
+        <v>207</v>
       </c>
       <c r="D57" t="s">
         <v>48</v>
@@ -5341,19 +5335,22 @@
         <v>32</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G57" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H57" t="s">
-        <v>111</v>
+        <v>209</v>
+      </c>
+      <c r="I57" t="s">
+        <v>55</v>
       </c>
       <c r="J57" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K57" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L57" t="s">
         <v>14</v>
@@ -5367,34 +5364,34 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>356</v>
+        <v>195</v>
       </c>
       <c r="B58" t="s">
-        <v>371</v>
+        <v>210</v>
       </c>
       <c r="C58" t="s">
-        <v>381</v>
+        <v>211</v>
       </c>
       <c r="D58" t="s">
         <v>48</v>
       </c>
       <c r="E58" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F58" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="H58" t="s">
-        <v>433</v>
+        <v>204</v>
       </c>
       <c r="I58" t="s">
-        <v>208</v>
+        <v>54</v>
       </c>
       <c r="J58" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="K58" t="s">
         <v>49</v>
@@ -5411,13 +5408,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="B59" t="s">
-        <v>373</v>
+        <v>776</v>
       </c>
       <c r="C59" t="s">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="D59" t="s">
         <v>48</v>
@@ -5429,16 +5426,19 @@
         <v>31</v>
       </c>
       <c r="G59" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s">
-        <v>483</v>
+        <v>189</v>
+      </c>
+      <c r="I59" t="s">
+        <v>141</v>
       </c>
       <c r="J59" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L59" t="s">
         <v>14</v>
@@ -5452,13 +5452,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>358</v>
+        <v>212</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>787</v>
       </c>
       <c r="C60" t="s">
-        <v>782</v>
+        <v>140</v>
       </c>
       <c r="D60" t="s">
         <v>48</v>
@@ -5467,19 +5467,19 @@
         <v>32</v>
       </c>
       <c r="F60" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>376</v>
+        <v>142</v>
       </c>
       <c r="H60" t="s">
-        <v>377</v>
+        <v>488</v>
       </c>
       <c r="I60" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J60" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="K60" t="s">
         <v>49</v>
@@ -5496,34 +5496,37 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>359</v>
+        <v>213</v>
       </c>
       <c r="B61" t="s">
-        <v>378</v>
+        <v>788</v>
       </c>
       <c r="C61" t="s">
-        <v>783</v>
+        <v>414</v>
       </c>
       <c r="D61" t="s">
         <v>48</v>
       </c>
       <c r="E61" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H61" t="s">
-        <v>268</v>
+        <v>488</v>
+      </c>
+      <c r="I61" t="s">
+        <v>55</v>
       </c>
       <c r="J61" t="s">
-        <v>703</v>
+        <v>182</v>
       </c>
       <c r="K61" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L61" t="s">
         <v>14</v>
@@ -5537,13 +5540,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>360</v>
+        <v>214</v>
       </c>
       <c r="B62" t="s">
-        <v>379</v>
+        <v>789</v>
       </c>
       <c r="C62" t="s">
-        <v>784</v>
+        <v>216</v>
       </c>
       <c r="D62" t="s">
         <v>48</v>
@@ -5555,16 +5558,16 @@
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H62" t="s">
-        <v>268</v>
+        <v>488</v>
       </c>
       <c r="I62" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J62" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="K62" t="s">
         <v>49</v>
@@ -5581,34 +5584,34 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>361</v>
+        <v>215</v>
       </c>
       <c r="B63" t="s">
-        <v>786</v>
+        <v>217</v>
       </c>
       <c r="C63" t="s">
-        <v>785</v>
+        <v>218</v>
       </c>
       <c r="D63" t="s">
         <v>48</v>
       </c>
       <c r="E63" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c r="H63" t="s">
-        <v>336</v>
+        <v>488</v>
       </c>
       <c r="I63" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="J63" t="s">
-        <v>283</v>
+        <v>190</v>
       </c>
       <c r="K63" t="s">
         <v>49</v>
@@ -5625,13 +5628,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B64" t="s">
-        <v>380</v>
+        <v>786</v>
       </c>
       <c r="C64" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D64" t="s">
         <v>48</v>
@@ -5643,13 +5646,16 @@
         <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>382</v>
+        <v>221</v>
       </c>
       <c r="H64" t="s">
-        <v>491</v>
+        <v>488</v>
+      </c>
+      <c r="I64" t="s">
+        <v>55</v>
       </c>
       <c r="J64" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="K64" t="s">
         <v>49</v>
@@ -5666,19 +5672,19 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>363</v>
+        <v>247</v>
       </c>
       <c r="B65" t="s">
-        <v>383</v>
+        <v>248</v>
       </c>
       <c r="C65" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="D65" t="s">
         <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -5687,7 +5693,10 @@
         <v>142</v>
       </c>
       <c r="H65" t="s">
-        <v>111</v>
+        <v>336</v>
+      </c>
+      <c r="I65" t="s">
+        <v>141</v>
       </c>
       <c r="J65" t="s">
         <v>182</v>
@@ -5707,13 +5716,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>364</v>
+        <v>249</v>
       </c>
       <c r="B66" t="s">
-        <v>787</v>
+        <v>250</v>
       </c>
       <c r="C66" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="D66" t="s">
         <v>48</v>
@@ -5725,13 +5734,13 @@
         <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="H66" t="s">
-        <v>488</v>
+        <v>336</v>
       </c>
       <c r="I66" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="J66" t="s">
         <v>182</v>
@@ -5751,34 +5760,37 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>365</v>
+        <v>251</v>
       </c>
       <c r="B67" t="s">
-        <v>386</v>
+        <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>387</v>
+        <v>262</v>
       </c>
       <c r="D67" t="s">
         <v>48</v>
       </c>
       <c r="E67" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F67" t="s">
         <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H67" t="s">
-        <v>492</v>
+        <v>209</v>
+      </c>
+      <c r="I67" t="s">
+        <v>54</v>
       </c>
       <c r="J67" t="s">
-        <v>390</v>
+        <v>269</v>
       </c>
       <c r="K67" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L67" t="s">
         <v>14</v>
@@ -5792,13 +5804,13 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>366</v>
+        <v>252</v>
       </c>
       <c r="B68" t="s">
-        <v>388</v>
+        <v>263</v>
       </c>
       <c r="C68" t="s">
-        <v>389</v>
+        <v>264</v>
       </c>
       <c r="D68" t="s">
         <v>48</v>
@@ -5813,13 +5825,16 @@
         <v>142</v>
       </c>
       <c r="H68" t="s">
-        <v>524</v>
+        <v>265</v>
+      </c>
+      <c r="I68" t="s">
+        <v>134</v>
       </c>
       <c r="J68" t="s">
-        <v>390</v>
+        <v>182</v>
       </c>
       <c r="K68" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L68" t="s">
         <v>14</v>
@@ -5833,37 +5848,37 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>367</v>
+        <v>253</v>
       </c>
       <c r="B69" t="s">
-        <v>391</v>
+        <v>777</v>
       </c>
       <c r="C69" t="s">
-        <v>392</v>
+        <v>266</v>
       </c>
       <c r="D69" t="s">
         <v>48</v>
       </c>
       <c r="E69" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
       </c>
       <c r="G69" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="H69" t="s">
-        <v>204</v>
+        <v>281</v>
       </c>
       <c r="I69" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="J69" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K69" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L69" t="s">
         <v>14</v>
@@ -5877,19 +5892,19 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>368</v>
+        <v>254</v>
       </c>
       <c r="B70" t="s">
-        <v>393</v>
+        <v>778</v>
       </c>
       <c r="C70" t="s">
-        <v>394</v>
+        <v>267</v>
       </c>
       <c r="D70" t="s">
         <v>48</v>
       </c>
       <c r="E70" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F70" t="s">
         <v>13</v>
@@ -5900,11 +5915,14 @@
       <c r="H70" t="s">
         <v>281</v>
       </c>
+      <c r="I70" t="s">
+        <v>134</v>
+      </c>
       <c r="J70" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="K70" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L70" t="s">
         <v>14</v>
@@ -5918,34 +5936,37 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>369</v>
+        <v>255</v>
       </c>
       <c r="B71" t="s">
-        <v>791</v>
+        <v>415</v>
+      </c>
+      <c r="C71" t="s">
+        <v>609</v>
       </c>
       <c r="D71" t="s">
         <v>48</v>
       </c>
       <c r="E71" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>144</v>
+        <v>271</v>
       </c>
       <c r="H71" t="s">
-        <v>281</v>
+        <v>111</v>
       </c>
       <c r="I71" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="J71" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K71" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L71" t="s">
         <v>14</v>
@@ -5959,13 +5980,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>370</v>
+        <v>256</v>
       </c>
       <c r="B72" t="s">
-        <v>396</v>
+        <v>277</v>
       </c>
       <c r="C72" t="s">
-        <v>395</v>
+        <v>278</v>
       </c>
       <c r="D72" t="s">
         <v>48</v>
@@ -5980,10 +6001,13 @@
         <v>142</v>
       </c>
       <c r="H72" t="s">
-        <v>281</v>
+        <v>279</v>
+      </c>
+      <c r="I72" t="s">
+        <v>55</v>
       </c>
       <c r="J72" t="s">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="K72" t="s">
         <v>49</v>
@@ -6000,13 +6024,10 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>397</v>
+        <v>257</v>
       </c>
       <c r="B73" t="s">
-        <v>792</v>
-      </c>
-      <c r="C73" t="s">
-        <v>402</v>
+        <v>280</v>
       </c>
       <c r="D73" t="s">
         <v>48</v>
@@ -6021,10 +6042,10 @@
         <v>142</v>
       </c>
       <c r="H73" t="s">
-        <v>525</v>
+        <v>281</v>
       </c>
       <c r="J73" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K73" t="s">
         <v>49</v>
@@ -6041,37 +6062,37 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>398</v>
+        <v>258</v>
       </c>
       <c r="B74" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="C74" t="s">
-        <v>403</v>
+        <v>270</v>
       </c>
       <c r="D74" t="s">
         <v>48</v>
       </c>
       <c r="E74" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F74" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G74" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H74" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="I74" t="s">
-        <v>419</v>
+        <v>134</v>
       </c>
       <c r="J74" t="s">
-        <v>182</v>
+        <v>390</v>
       </c>
       <c r="K74" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L74" t="s">
         <v>14</v>
@@ -6085,13 +6106,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>399</v>
+        <v>259</v>
       </c>
       <c r="B75" t="s">
-        <v>404</v>
+        <v>780</v>
       </c>
       <c r="C75" t="s">
-        <v>405</v>
+        <v>284</v>
       </c>
       <c r="D75" t="s">
         <v>48</v>
@@ -6100,22 +6121,22 @@
         <v>52</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G75" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="H75" t="s">
-        <v>131</v>
+        <v>321</v>
       </c>
       <c r="I75" t="s">
         <v>141</v>
       </c>
       <c r="J75" t="s">
-        <v>182</v>
+        <v>283</v>
       </c>
       <c r="K75" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="L75" t="s">
         <v>14</v>
@@ -6129,19 +6150,19 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="B76" t="s">
-        <v>406</v>
+        <v>285</v>
       </c>
       <c r="C76" t="s">
-        <v>407</v>
+        <v>286</v>
       </c>
       <c r="D76" t="s">
         <v>48</v>
       </c>
       <c r="E76" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F76" t="s">
         <v>13</v>
@@ -6150,16 +6171,13 @@
         <v>142</v>
       </c>
       <c r="H76" t="s">
-        <v>493</v>
-      </c>
-      <c r="I76" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="J76" t="s">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="K76" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L76" t="s">
         <v>14</v>
@@ -6173,37 +6191,37 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>401</v>
+        <v>356</v>
       </c>
       <c r="B77" t="s">
-        <v>794</v>
+        <v>371</v>
       </c>
       <c r="C77" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="D77" t="s">
         <v>48</v>
       </c>
       <c r="E77" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G77" t="s">
-        <v>142</v>
+        <v>372</v>
       </c>
       <c r="H77" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="I77" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
       <c r="J77" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="K77" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L77" t="s">
         <v>14</v>
@@ -6217,34 +6235,31 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>420</v>
+        <v>359</v>
       </c>
       <c r="B78" t="s">
-        <v>424</v>
+        <v>378</v>
       </c>
       <c r="C78" t="s">
-        <v>425</v>
+        <v>782</v>
       </c>
       <c r="D78" t="s">
         <v>48</v>
       </c>
       <c r="E78" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H78" t="s">
-        <v>409</v>
-      </c>
-      <c r="I78" t="s">
-        <v>55</v>
+        <v>268</v>
       </c>
       <c r="J78" t="s">
-        <v>182</v>
+        <v>702</v>
       </c>
       <c r="K78" t="s">
         <v>49</v>
@@ -6261,13 +6276,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>421</v>
+        <v>360</v>
       </c>
       <c r="B79" t="s">
-        <v>426</v>
+        <v>379</v>
       </c>
       <c r="C79" t="s">
-        <v>428</v>
+        <v>783</v>
       </c>
       <c r="D79" t="s">
         <v>48</v>
@@ -6276,19 +6291,19 @@
         <v>32</v>
       </c>
       <c r="F79" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G79" t="s">
-        <v>434</v>
+        <v>272</v>
       </c>
       <c r="H79" t="s">
-        <v>427</v>
+        <v>268</v>
       </c>
       <c r="I79" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="J79" t="s">
-        <v>390</v>
+        <v>199</v>
       </c>
       <c r="K79" t="s">
         <v>49</v>
@@ -6305,37 +6320,34 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="B80" t="s">
-        <v>429</v>
+        <v>380</v>
       </c>
       <c r="C80" t="s">
-        <v>430</v>
+        <v>381</v>
       </c>
       <c r="D80" t="s">
         <v>48</v>
       </c>
       <c r="E80" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F80" t="s">
         <v>13</v>
       </c>
       <c r="G80" t="s">
-        <v>142</v>
+        <v>382</v>
       </c>
       <c r="H80" t="s">
-        <v>526</v>
-      </c>
-      <c r="I80" t="s">
-        <v>55</v>
+        <v>491</v>
       </c>
       <c r="J80" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="K80" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L80" t="s">
         <v>14</v>
@@ -6349,19 +6361,19 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="B81" t="s">
-        <v>431</v>
+        <v>383</v>
       </c>
       <c r="C81" t="s">
-        <v>432</v>
+        <v>384</v>
       </c>
       <c r="D81" t="s">
         <v>48</v>
       </c>
       <c r="E81" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F81" t="s">
         <v>13</v>
@@ -6370,13 +6382,10 @@
         <v>142</v>
       </c>
       <c r="H81" t="s">
-        <v>433</v>
-      </c>
-      <c r="I81" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="J81" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="K81" t="s">
         <v>49</v>
@@ -6393,34 +6402,31 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>435</v>
+        <v>365</v>
       </c>
       <c r="B82" t="s">
-        <v>444</v>
+        <v>386</v>
       </c>
       <c r="C82" t="s">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="D82" t="s">
         <v>48</v>
       </c>
       <c r="E82" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F82" t="s">
         <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>110</v>
+        <v>272</v>
       </c>
       <c r="H82" t="s">
-        <v>445</v>
-      </c>
-      <c r="I82" t="s">
-        <v>55</v>
+        <v>492</v>
       </c>
       <c r="J82" t="s">
-        <v>182</v>
+        <v>390</v>
       </c>
       <c r="K82" t="s">
         <v>49</v>
@@ -6437,37 +6443,34 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>436</v>
+        <v>366</v>
       </c>
       <c r="B83" t="s">
-        <v>446</v>
+        <v>388</v>
       </c>
       <c r="C83" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="D83" t="s">
         <v>48</v>
       </c>
       <c r="E83" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F83" t="s">
         <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="H83" t="s">
-        <v>205</v>
-      </c>
-      <c r="I83" t="s">
-        <v>55</v>
+        <v>524</v>
       </c>
       <c r="J83" t="s">
-        <v>182</v>
+        <v>390</v>
       </c>
       <c r="K83" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L83" t="s">
         <v>14</v>
@@ -6481,19 +6484,19 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>437</v>
+        <v>367</v>
       </c>
       <c r="B84" t="s">
-        <v>448</v>
+        <v>391</v>
       </c>
       <c r="C84" t="s">
-        <v>795</v>
+        <v>392</v>
       </c>
       <c r="D84" t="s">
         <v>48</v>
       </c>
       <c r="E84" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F84" t="s">
         <v>13</v>
@@ -6502,7 +6505,7 @@
         <v>142</v>
       </c>
       <c r="H84" t="s">
-        <v>495</v>
+        <v>204</v>
       </c>
       <c r="I84" t="s">
         <v>55</v>
@@ -6511,7 +6514,7 @@
         <v>182</v>
       </c>
       <c r="K84" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L84" t="s">
         <v>14</v>
@@ -6525,37 +6528,34 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>438</v>
+        <v>368</v>
       </c>
       <c r="B85" t="s">
-        <v>451</v>
+        <v>393</v>
       </c>
       <c r="C85" t="s">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="D85" t="s">
         <v>48</v>
       </c>
       <c r="E85" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F85" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G85" t="s">
-        <v>450</v>
+        <v>110</v>
       </c>
       <c r="H85" t="s">
-        <v>433</v>
-      </c>
-      <c r="I85" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="J85" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="K85" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L85" t="s">
         <v>14</v>
@@ -6569,28 +6569,25 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>439</v>
+        <v>369</v>
       </c>
       <c r="B86" t="s">
-        <v>452</v>
-      </c>
-      <c r="C86" t="s">
-        <v>453</v>
+        <v>790</v>
       </c>
       <c r="D86" t="s">
         <v>48</v>
       </c>
       <c r="E86" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="F86" t="s">
         <v>31</v>
       </c>
       <c r="G86" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="H86" t="s">
-        <v>527</v>
+        <v>281</v>
       </c>
       <c r="I86" t="s">
         <v>55</v>
@@ -6599,7 +6596,7 @@
         <v>182</v>
       </c>
       <c r="K86" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L86" t="s">
         <v>14</v>
@@ -6613,19 +6610,19 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>440</v>
+        <v>370</v>
       </c>
       <c r="B87" t="s">
-        <v>454</v>
+        <v>396</v>
       </c>
       <c r="C87" t="s">
-        <v>455</v>
+        <v>395</v>
       </c>
       <c r="D87" t="s">
         <v>48</v>
       </c>
       <c r="E87" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F87" t="s">
         <v>13</v>
@@ -6634,16 +6631,13 @@
         <v>142</v>
       </c>
       <c r="H87" t="s">
-        <v>528</v>
-      </c>
-      <c r="I87" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="J87" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="K87" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L87" t="s">
         <v>14</v>
@@ -6657,31 +6651,28 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="B88" t="s">
-        <v>457</v>
+        <v>791</v>
       </c>
       <c r="C88" t="s">
-        <v>458</v>
+        <v>402</v>
       </c>
       <c r="D88" t="s">
         <v>48</v>
       </c>
       <c r="E88" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F88" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G88" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H88" t="s">
-        <v>205</v>
-      </c>
-      <c r="I88" t="s">
-        <v>55</v>
+        <v>525</v>
       </c>
       <c r="J88" t="s">
         <v>182</v>
@@ -6701,34 +6692,34 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>442</v>
+        <v>400</v>
       </c>
       <c r="B89" t="s">
-        <v>459</v>
+        <v>406</v>
       </c>
       <c r="C89" t="s">
-        <v>460</v>
+        <v>407</v>
       </c>
       <c r="D89" t="s">
         <v>48</v>
       </c>
       <c r="E89" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F89" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G89" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H89" t="s">
-        <v>529</v>
+        <v>493</v>
       </c>
       <c r="I89" t="s">
         <v>55</v>
       </c>
       <c r="J89" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="K89" t="s">
         <v>49</v>
@@ -6745,28 +6736,28 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>443</v>
+        <v>401</v>
       </c>
       <c r="B90" t="s">
-        <v>461</v>
+        <v>793</v>
       </c>
       <c r="C90" t="s">
-        <v>447</v>
+        <v>408</v>
       </c>
       <c r="D90" t="s">
         <v>48</v>
       </c>
       <c r="E90" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="H90" t="s">
-        <v>205</v>
+        <v>409</v>
       </c>
       <c r="I90" t="s">
         <v>55</v>
@@ -6775,7 +6766,7 @@
         <v>182</v>
       </c>
       <c r="K90" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L90" t="s">
         <v>14</v>
@@ -6789,13 +6780,13 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>499</v>
+        <v>420</v>
       </c>
       <c r="B91" t="s">
-        <v>504</v>
+        <v>424</v>
       </c>
       <c r="C91" t="s">
-        <v>505</v>
+        <v>425</v>
       </c>
       <c r="D91" t="s">
         <v>48</v>
@@ -6807,16 +6798,16 @@
         <v>13</v>
       </c>
       <c r="G91" t="s">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="H91" t="s">
-        <v>530</v>
+        <v>409</v>
       </c>
       <c r="I91" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J91" t="s">
-        <v>506</v>
+        <v>182</v>
       </c>
       <c r="K91" t="s">
         <v>49</v>
@@ -6833,13 +6824,13 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>500</v>
+        <v>421</v>
       </c>
       <c r="B92" t="s">
-        <v>798</v>
+        <v>426</v>
       </c>
       <c r="C92" t="s">
-        <v>507</v>
+        <v>428</v>
       </c>
       <c r="D92" t="s">
         <v>48</v>
@@ -6848,16 +6839,19 @@
         <v>32</v>
       </c>
       <c r="F92" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G92" t="s">
-        <v>221</v>
+        <v>434</v>
       </c>
       <c r="H92" t="s">
-        <v>336</v>
+        <v>427</v>
+      </c>
+      <c r="I92" t="s">
+        <v>55</v>
       </c>
       <c r="J92" t="s">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="K92" t="s">
         <v>49</v>
@@ -6874,28 +6868,28 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>501</v>
+        <v>422</v>
       </c>
       <c r="B93" t="s">
-        <v>801</v>
+        <v>429</v>
       </c>
       <c r="C93" t="s">
-        <v>508</v>
+        <v>430</v>
       </c>
       <c r="D93" t="s">
         <v>48</v>
       </c>
       <c r="E93" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F93" t="s">
         <v>13</v>
       </c>
       <c r="G93" t="s">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="H93" t="s">
-        <v>281</v>
+        <v>526</v>
       </c>
       <c r="I93" t="s">
         <v>55</v>
@@ -6904,7 +6898,7 @@
         <v>182</v>
       </c>
       <c r="K93" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L93" t="s">
         <v>14</v>
@@ -6918,13 +6912,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>502</v>
+        <v>423</v>
       </c>
       <c r="B94" t="s">
-        <v>797</v>
+        <v>431</v>
       </c>
       <c r="C94" t="s">
-        <v>556</v>
+        <v>432</v>
       </c>
       <c r="D94" t="s">
         <v>48</v>
@@ -6939,16 +6933,16 @@
         <v>142</v>
       </c>
       <c r="H94" t="s">
-        <v>336</v>
+        <v>433</v>
       </c>
       <c r="I94" t="s">
         <v>55</v>
       </c>
       <c r="J94" t="s">
-        <v>283</v>
+        <v>199</v>
       </c>
       <c r="K94" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L94" t="s">
         <v>14</v>
@@ -6962,13 +6956,13 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>503</v>
+        <v>435</v>
       </c>
       <c r="B95" t="s">
-        <v>509</v>
+        <v>444</v>
       </c>
       <c r="C95" t="s">
-        <v>510</v>
+        <v>447</v>
       </c>
       <c r="D95" t="s">
         <v>48</v>
@@ -6977,13 +6971,13 @@
         <v>32</v>
       </c>
       <c r="F95" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G95" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="H95" t="s">
-        <v>281</v>
+        <v>445</v>
       </c>
       <c r="I95" t="s">
         <v>55</v>
@@ -7006,13 +7000,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>547</v>
+        <v>436</v>
       </c>
       <c r="B96" t="s">
-        <v>796</v>
+        <v>446</v>
       </c>
       <c r="C96" t="s">
-        <v>549</v>
+        <v>447</v>
       </c>
       <c r="D96" t="s">
         <v>48</v>
@@ -7024,10 +7018,10 @@
         <v>13</v>
       </c>
       <c r="G96" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="H96" t="s">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="I96" t="s">
         <v>55</v>
@@ -7050,13 +7044,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>548</v>
+        <v>437</v>
       </c>
       <c r="B97" t="s">
-        <v>550</v>
+        <v>448</v>
       </c>
       <c r="C97" t="s">
-        <v>551</v>
+        <v>794</v>
       </c>
       <c r="D97" t="s">
         <v>48</v>
@@ -7071,16 +7065,16 @@
         <v>142</v>
       </c>
       <c r="H97" t="s">
-        <v>268</v>
+        <v>495</v>
       </c>
       <c r="I97" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J97" t="s">
-        <v>390</v>
+        <v>182</v>
       </c>
       <c r="K97" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="L97" t="s">
         <v>14</v>
@@ -7094,37 +7088,37 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>57</v>
+        <v>438</v>
       </c>
       <c r="B98" t="s">
-        <v>290</v>
+        <v>451</v>
       </c>
       <c r="C98" t="s">
-        <v>64</v>
+        <v>449</v>
       </c>
       <c r="D98" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E98" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G98" t="s">
-        <v>142</v>
+        <v>450</v>
       </c>
       <c r="H98" t="s">
-        <v>531</v>
+        <v>433</v>
       </c>
       <c r="I98" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="J98" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="K98" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L98" t="s">
         <v>14</v>
@@ -7138,37 +7132,37 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>58</v>
+        <v>439</v>
       </c>
       <c r="B99" t="s">
-        <v>65</v>
+        <v>452</v>
       </c>
       <c r="C99" t="s">
-        <v>66</v>
+        <v>453</v>
       </c>
       <c r="D99" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E99" t="s">
         <v>52</v>
       </c>
       <c r="F99" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G99" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="H99" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="I99" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J99" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K99" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L99" t="s">
         <v>14</v>
@@ -7182,34 +7176,34 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>59</v>
+        <v>441</v>
       </c>
       <c r="B100" t="s">
-        <v>291</v>
+        <v>457</v>
       </c>
       <c r="C100" t="s">
-        <v>67</v>
+        <v>458</v>
       </c>
       <c r="D100" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E100" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="F100" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G100" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H100" t="s">
-        <v>533</v>
+        <v>205</v>
       </c>
       <c r="I100" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="J100" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K100" t="s">
         <v>49</v>
@@ -7226,34 +7220,37 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>60</v>
+        <v>442</v>
       </c>
       <c r="B101" t="s">
-        <v>68</v>
+        <v>459</v>
       </c>
       <c r="C101" t="s">
-        <v>292</v>
+        <v>460</v>
       </c>
       <c r="D101" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E101" t="s">
         <v>32</v>
       </c>
       <c r="F101" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G101" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H101" t="s">
-        <v>484</v>
+        <v>529</v>
+      </c>
+      <c r="I101" t="s">
+        <v>55</v>
       </c>
       <c r="J101" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="K101" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L101" t="s">
         <v>14</v>
@@ -7267,19 +7264,19 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>61</v>
+        <v>443</v>
       </c>
       <c r="B102" t="s">
-        <v>69</v>
+        <v>461</v>
       </c>
       <c r="C102" t="s">
-        <v>70</v>
+        <v>447</v>
       </c>
       <c r="D102" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E102" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F102" t="s">
         <v>13</v>
@@ -7288,16 +7285,16 @@
         <v>110</v>
       </c>
       <c r="H102" t="s">
-        <v>479</v>
+        <v>205</v>
       </c>
       <c r="I102" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J102" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="K102" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L102" t="s">
         <v>14</v>
@@ -7311,28 +7308,31 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>62</v>
+        <v>501</v>
       </c>
       <c r="B103" t="s">
-        <v>71</v>
+        <v>800</v>
       </c>
       <c r="C103" t="s">
-        <v>293</v>
+        <v>508</v>
       </c>
       <c r="D103" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E103" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F103" t="s">
         <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>142</v>
+        <v>221</v>
       </c>
       <c r="H103" t="s">
-        <v>525</v>
+        <v>281</v>
+      </c>
+      <c r="I103" t="s">
+        <v>55</v>
       </c>
       <c r="J103" t="s">
         <v>182</v>
@@ -7352,34 +7352,34 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>63</v>
+        <v>499</v>
       </c>
       <c r="B104" t="s">
-        <v>72</v>
+        <v>504</v>
       </c>
       <c r="C104" t="s">
-        <v>73</v>
+        <v>505</v>
       </c>
       <c r="D104" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E104" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F104" t="s">
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H104" t="s">
-        <v>485</v>
+        <v>530</v>
       </c>
       <c r="I104" t="s">
         <v>76</v>
       </c>
       <c r="J104" t="s">
-        <v>190</v>
+        <v>506</v>
       </c>
       <c r="K104" t="s">
         <v>49</v>
@@ -7396,34 +7396,31 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="B105" t="s">
-        <v>101</v>
+        <v>797</v>
       </c>
       <c r="C105" t="s">
-        <v>102</v>
+        <v>507</v>
       </c>
       <c r="D105" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E105" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F105" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G105" t="s">
-        <v>146</v>
+        <v>221</v>
       </c>
       <c r="H105" t="s">
-        <v>28</v>
-      </c>
-      <c r="I105" t="s">
-        <v>95</v>
+        <v>336</v>
       </c>
       <c r="J105" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="K105" t="s">
         <v>49</v>
@@ -7440,37 +7437,37 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>124</v>
+        <v>502</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>796</v>
       </c>
       <c r="C106" t="s">
-        <v>128</v>
+        <v>555</v>
       </c>
       <c r="D106" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E106" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F106" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="H106" t="s">
-        <v>131</v>
+        <v>336</v>
       </c>
       <c r="I106" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J106" t="s">
-        <v>148</v>
+        <v>283</v>
       </c>
       <c r="K106" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L106" t="s">
         <v>14</v>
@@ -7484,37 +7481,37 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>125</v>
+        <v>547</v>
       </c>
       <c r="B107" t="s">
-        <v>130</v>
+        <v>795</v>
       </c>
       <c r="C107" t="s">
-        <v>129</v>
+        <v>549</v>
       </c>
       <c r="D107" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E107" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F107" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G107" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="H107" t="s">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="I107" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J107" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="K107" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L107" t="s">
         <v>14</v>
@@ -7528,37 +7525,34 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>126</v>
+        <v>677</v>
       </c>
       <c r="B108" t="s">
-        <v>132</v>
+        <v>829</v>
       </c>
       <c r="C108" t="s">
-        <v>133</v>
+        <v>698</v>
       </c>
       <c r="D108" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E108" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G108" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H108" t="s">
-        <v>111</v>
-      </c>
-      <c r="I108" t="s">
-        <v>134</v>
+        <v>336</v>
       </c>
       <c r="J108" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="K108" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L108" t="s">
         <v>14</v>
@@ -7572,16 +7566,13 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>467</v>
+        <v>731</v>
       </c>
       <c r="B109" t="s">
-        <v>475</v>
-      </c>
-      <c r="C109" t="s">
-        <v>476</v>
+        <v>826</v>
       </c>
       <c r="D109" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E109" t="s">
         <v>32</v>
@@ -7590,16 +7581,19 @@
         <v>31</v>
       </c>
       <c r="G109" t="s">
-        <v>560</v>
+        <v>144</v>
       </c>
       <c r="H109" t="s">
         <v>336</v>
       </c>
+      <c r="I109" t="s">
+        <v>55</v>
+      </c>
       <c r="J109" t="s">
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="K109" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L109" t="s">
         <v>14</v>
@@ -7613,19 +7607,16 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="B110" t="s">
-        <v>521</v>
-      </c>
-      <c r="C110" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="D110" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E110" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F110" t="s">
         <v>13</v>
@@ -7634,13 +7625,16 @@
         <v>142</v>
       </c>
       <c r="H110" t="s">
-        <v>336</v>
+        <v>268</v>
+      </c>
+      <c r="I110" t="s">
+        <v>76</v>
       </c>
       <c r="J110" t="s">
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="K110" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L110" t="s">
         <v>14</v>
@@ -7654,31 +7648,28 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>151</v>
+        <v>676</v>
       </c>
       <c r="B111" t="s">
-        <v>160</v>
-      </c>
-      <c r="C111" t="s">
-        <v>161</v>
+        <v>697</v>
       </c>
       <c r="D111" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E111" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F111" t="s">
         <v>13</v>
       </c>
       <c r="G111" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H111" t="s">
         <v>336</v>
       </c>
       <c r="J111" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K111" t="s">
         <v>50</v>
@@ -7695,37 +7686,37 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>152</v>
+        <v>503</v>
       </c>
       <c r="B112" t="s">
-        <v>162</v>
+        <v>509</v>
       </c>
       <c r="C112" t="s">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="D112" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E112" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F112" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G112" t="s">
-        <v>272</v>
+        <v>144</v>
       </c>
       <c r="H112" t="s">
-        <v>336</v>
+        <v>281</v>
       </c>
       <c r="I112" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J112" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K112" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L112" t="s">
         <v>14</v>
@@ -7739,13 +7730,13 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>153</v>
+        <v>58</v>
       </c>
       <c r="B113" t="s">
-        <v>164</v>
+        <v>65</v>
       </c>
       <c r="C113" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="D113" t="s">
         <v>79</v>
@@ -7757,13 +7748,16 @@
         <v>13</v>
       </c>
       <c r="G113" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H113" t="s">
-        <v>336</v>
+        <v>532</v>
+      </c>
+      <c r="I113" t="s">
+        <v>76</v>
       </c>
       <c r="J113" t="s">
-        <v>190</v>
+        <v>96</v>
       </c>
       <c r="K113" t="s">
         <v>49</v>
@@ -7780,13 +7774,13 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>154</v>
+        <v>57</v>
       </c>
       <c r="B114" t="s">
-        <v>166</v>
+        <v>290</v>
       </c>
       <c r="C114" t="s">
-        <v>167</v>
+        <v>64</v>
       </c>
       <c r="D114" t="s">
         <v>79</v>
@@ -7798,19 +7792,19 @@
         <v>13</v>
       </c>
       <c r="G114" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H114" t="s">
-        <v>336</v>
+        <v>531</v>
       </c>
       <c r="I114" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="J114" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K114" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L114" t="s">
         <v>14</v>
@@ -7824,13 +7818,13 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="B115" t="s">
-        <v>168</v>
+        <v>291</v>
       </c>
       <c r="C115" t="s">
-        <v>243</v>
+        <v>67</v>
       </c>
       <c r="D115" t="s">
         <v>79</v>
@@ -7842,19 +7836,19 @@
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>276</v>
+        <v>142</v>
       </c>
       <c r="H115" t="s">
-        <v>336</v>
+        <v>533</v>
       </c>
       <c r="I115" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="J115" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="K115" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L115" t="s">
         <v>14</v>
@@ -7868,34 +7862,37 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>512</v>
+        <v>61</v>
       </c>
       <c r="B116" t="s">
-        <v>517</v>
+        <v>69</v>
       </c>
       <c r="C116" t="s">
-        <v>518</v>
+        <v>70</v>
       </c>
       <c r="D116" t="s">
         <v>79</v>
       </c>
       <c r="E116" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F116" t="s">
         <v>13</v>
       </c>
       <c r="G116" t="s">
-        <v>272</v>
+        <v>110</v>
       </c>
       <c r="H116" t="s">
-        <v>336</v>
+        <v>479</v>
+      </c>
+      <c r="I116" t="s">
+        <v>76</v>
       </c>
       <c r="J116" t="s">
-        <v>190</v>
+        <v>93</v>
       </c>
       <c r="K116" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L116" t="s">
         <v>14</v>
@@ -7909,13 +7906,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>339</v>
+        <v>62</v>
       </c>
       <c r="B117" t="s">
-        <v>348</v>
+        <v>71</v>
       </c>
       <c r="C117" t="s">
-        <v>349</v>
+        <v>293</v>
       </c>
       <c r="D117" t="s">
         <v>79</v>
@@ -7924,22 +7921,19 @@
         <v>52</v>
       </c>
       <c r="F117" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G117" t="s">
-        <v>350</v>
+        <v>142</v>
       </c>
       <c r="H117" t="s">
-        <v>336</v>
-      </c>
-      <c r="I117" t="s">
-        <v>76</v>
+        <v>525</v>
       </c>
       <c r="J117" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K117" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L117" t="s">
         <v>14</v>
@@ -7953,28 +7947,31 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>157</v>
+        <v>63</v>
       </c>
       <c r="B118" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="C118" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="D118" t="s">
         <v>79</v>
       </c>
       <c r="E118" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F118" t="s">
         <v>13</v>
       </c>
       <c r="G118" t="s">
-        <v>272</v>
+        <v>222</v>
       </c>
       <c r="H118" t="s">
-        <v>336</v>
+        <v>485</v>
+      </c>
+      <c r="I118" t="s">
+        <v>76</v>
       </c>
       <c r="J118" t="s">
         <v>190</v>
@@ -7994,34 +7991,37 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>340</v>
+        <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>351</v>
+        <v>132</v>
       </c>
       <c r="C119" t="s">
-        <v>546</v>
+        <v>133</v>
       </c>
       <c r="D119" t="s">
         <v>79</v>
       </c>
       <c r="E119" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F119" t="s">
         <v>13</v>
       </c>
       <c r="G119" t="s">
-        <v>352</v>
+        <v>142</v>
       </c>
       <c r="H119" t="s">
-        <v>353</v>
+        <v>111</v>
+      </c>
+      <c r="I119" t="s">
+        <v>134</v>
       </c>
       <c r="J119" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K119" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L119" t="s">
         <v>14</v>
@@ -8035,13 +8035,13 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>156</v>
+        <v>467</v>
       </c>
       <c r="B120" t="s">
-        <v>523</v>
+        <v>475</v>
       </c>
       <c r="C120" t="s">
-        <v>169</v>
+        <v>476</v>
       </c>
       <c r="D120" t="s">
         <v>79</v>
@@ -8050,19 +8050,19 @@
         <v>32</v>
       </c>
       <c r="F120" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G120" t="s">
-        <v>272</v>
+        <v>559</v>
       </c>
       <c r="H120" t="s">
-        <v>486</v>
+        <v>336</v>
       </c>
       <c r="J120" t="s">
         <v>190</v>
       </c>
       <c r="K120" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L120" t="s">
         <v>14</v>
@@ -8076,13 +8076,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B121" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C121" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D121" t="s">
         <v>79</v>
@@ -8094,19 +8094,16 @@
         <v>13</v>
       </c>
       <c r="G121" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H121" t="s">
         <v>336</v>
       </c>
-      <c r="I121" t="s">
-        <v>76</v>
-      </c>
       <c r="J121" t="s">
         <v>190</v>
       </c>
       <c r="K121" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L121" t="s">
         <v>14</v>
@@ -8120,13 +8117,13 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="B122" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="C122" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="D122" t="s">
         <v>79</v>
@@ -8138,16 +8135,16 @@
         <v>13</v>
       </c>
       <c r="G122" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H122" t="s">
-        <v>336</v>
+        <v>268</v>
       </c>
       <c r="J122" t="s">
         <v>190</v>
       </c>
       <c r="K122" t="s">
-        <v>839</v>
+        <v>50</v>
       </c>
       <c r="L122" t="s">
         <v>14</v>
@@ -8161,13 +8158,13 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>226</v>
+        <v>151</v>
       </c>
       <c r="B123" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="C123" t="s">
-        <v>238</v>
+        <v>161</v>
       </c>
       <c r="D123" t="s">
         <v>79</v>
@@ -8182,10 +8179,7 @@
         <v>272</v>
       </c>
       <c r="H123" t="s">
-        <v>268</v>
-      </c>
-      <c r="I123" t="s">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="J123" t="s">
         <v>190</v>
@@ -8205,13 +8199,13 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>223</v>
+        <v>152</v>
       </c>
       <c r="B124" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="C124" t="s">
-        <v>555</v>
+        <v>163</v>
       </c>
       <c r="D124" t="s">
         <v>79</v>
@@ -8226,16 +8220,16 @@
         <v>272</v>
       </c>
       <c r="H124" t="s">
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="I124" t="s">
-        <v>233</v>
+        <v>76</v>
       </c>
       <c r="J124" t="s">
         <v>190</v>
       </c>
       <c r="K124" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="L124" t="s">
         <v>14</v>
@@ -8249,19 +8243,19 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="B125" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="C125" t="s">
-        <v>833</v>
+        <v>165</v>
       </c>
       <c r="D125" t="s">
         <v>79</v>
       </c>
       <c r="E125" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F125" t="s">
         <v>13</v>
@@ -8276,7 +8270,7 @@
         <v>190</v>
       </c>
       <c r="K125" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L125" t="s">
         <v>14</v>
@@ -8290,13 +8284,13 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
       <c r="B126" t="s">
-        <v>234</v>
+        <v>166</v>
       </c>
       <c r="C126" t="s">
-        <v>554</v>
+        <v>167</v>
       </c>
       <c r="D126" t="s">
         <v>79</v>
@@ -8308,7 +8302,7 @@
         <v>13</v>
       </c>
       <c r="G126" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H126" t="s">
         <v>336</v>
@@ -8320,7 +8314,7 @@
         <v>190</v>
       </c>
       <c r="K126" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="L126" t="s">
         <v>14</v>
@@ -8334,25 +8328,25 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B127" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C127" t="s">
-        <v>832</v>
+        <v>243</v>
       </c>
       <c r="D127" t="s">
         <v>79</v>
       </c>
       <c r="E127" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F127" t="s">
         <v>13</v>
       </c>
       <c r="G127" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H127" t="s">
         <v>336</v>
@@ -8364,7 +8358,7 @@
         <v>190</v>
       </c>
       <c r="K127" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="L127" t="s">
         <v>14</v>
@@ -8378,13 +8372,13 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>535</v>
+        <v>512</v>
       </c>
       <c r="B128" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="C128" t="s">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="D128" t="s">
         <v>79</v>
@@ -8399,16 +8393,13 @@
         <v>272</v>
       </c>
       <c r="H128" t="s">
-        <v>486</v>
-      </c>
-      <c r="I128" t="s">
-        <v>55</v>
+        <v>336</v>
       </c>
       <c r="J128" t="s">
         <v>190</v>
       </c>
       <c r="K128" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="L128" t="s">
         <v>14</v>
@@ -8422,13 +8413,13 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B129" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C129" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D129" t="s">
         <v>79</v>
@@ -8437,19 +8428,22 @@
         <v>52</v>
       </c>
       <c r="F129" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G129" t="s">
-        <v>272</v>
+        <v>350</v>
       </c>
       <c r="H129" t="s">
-        <v>268</v>
+        <v>336</v>
+      </c>
+      <c r="I129" t="s">
+        <v>76</v>
       </c>
       <c r="J129" t="s">
         <v>190</v>
       </c>
       <c r="K129" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="L129" t="s">
         <v>14</v>
@@ -8463,19 +8457,19 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B130" t="s">
-        <v>545</v>
+        <v>170</v>
       </c>
       <c r="C130" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D130" t="s">
         <v>79</v>
       </c>
       <c r="E130" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F130" t="s">
         <v>13</v>
@@ -8486,14 +8480,11 @@
       <c r="H130" t="s">
         <v>336</v>
       </c>
-      <c r="I130" t="s">
-        <v>76</v>
-      </c>
       <c r="J130" t="s">
         <v>190</v>
       </c>
       <c r="K130" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L130" t="s">
         <v>14</v>
@@ -8507,13 +8498,13 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>227</v>
+        <v>340</v>
       </c>
       <c r="B131" t="s">
-        <v>235</v>
+        <v>351</v>
       </c>
       <c r="C131" t="s">
-        <v>236</v>
+        <v>546</v>
       </c>
       <c r="D131" t="s">
         <v>79</v>
@@ -8525,16 +8516,16 @@
         <v>13</v>
       </c>
       <c r="G131" t="s">
-        <v>272</v>
+        <v>352</v>
       </c>
       <c r="H131" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="J131" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="K131" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L131" t="s">
         <v>14</v>
@@ -8548,34 +8539,34 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>241</v>
+        <v>156</v>
       </c>
       <c r="B132" t="s">
-        <v>172</v>
+        <v>523</v>
       </c>
       <c r="C132" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="D132" t="s">
         <v>79</v>
       </c>
       <c r="E132" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
       </c>
       <c r="G132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H132" t="s">
-        <v>336</v>
+        <v>486</v>
       </c>
       <c r="J132" t="s">
         <v>190</v>
       </c>
       <c r="K132" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L132" t="s">
         <v>14</v>
@@ -8589,13 +8580,13 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>175</v>
+        <v>511</v>
       </c>
       <c r="B133" t="s">
-        <v>179</v>
+        <v>515</v>
       </c>
       <c r="C133" t="s">
-        <v>642</v>
+        <v>516</v>
       </c>
       <c r="D133" t="s">
         <v>79</v>
@@ -8607,19 +8598,19 @@
         <v>13</v>
       </c>
       <c r="G133" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H133" t="s">
-        <v>180</v>
+        <v>336</v>
       </c>
       <c r="I133" t="s">
         <v>76</v>
       </c>
       <c r="J133" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="K133" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="L133" t="s">
         <v>14</v>
@@ -8633,19 +8624,19 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="B134" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="C134" t="s">
-        <v>800</v>
+        <v>230</v>
       </c>
       <c r="D134" t="s">
         <v>79</v>
       </c>
       <c r="E134" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F134" t="s">
         <v>13</v>
@@ -8654,16 +8645,13 @@
         <v>272</v>
       </c>
       <c r="H134" t="s">
-        <v>487</v>
-      </c>
-      <c r="I134" t="s">
-        <v>134</v>
+        <v>336</v>
       </c>
       <c r="J134" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="K134" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L134" t="s">
         <v>14</v>
@@ -8677,19 +8665,19 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B135" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="C135" t="s">
-        <v>799</v>
+        <v>238</v>
       </c>
       <c r="D135" t="s">
         <v>79</v>
       </c>
       <c r="E135" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F135" t="s">
         <v>13</v>
@@ -8698,16 +8686,16 @@
         <v>272</v>
       </c>
       <c r="H135" t="s">
-        <v>487</v>
+        <v>268</v>
       </c>
       <c r="I135" t="s">
         <v>76</v>
       </c>
       <c r="J135" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
       <c r="K135" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L135" t="s">
         <v>14</v>
@@ -8721,37 +8709,37 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="B136" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C136" t="s">
-        <v>643</v>
+        <v>554</v>
       </c>
       <c r="D136" t="s">
         <v>79</v>
       </c>
       <c r="E136" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F136" t="s">
         <v>13</v>
       </c>
       <c r="G136" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H136" t="s">
-        <v>336</v>
+        <v>268</v>
       </c>
       <c r="I136" t="s">
-        <v>134</v>
+        <v>233</v>
       </c>
       <c r="J136" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K136" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L136" t="s">
         <v>14</v>
@@ -8765,13 +8753,13 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="B137" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C137" t="s">
-        <v>245</v>
+        <v>831</v>
       </c>
       <c r="D137" t="s">
         <v>79</v>
@@ -8783,16 +8771,16 @@
         <v>13</v>
       </c>
       <c r="G137" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H137" t="s">
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="J137" t="s">
         <v>190</v>
       </c>
       <c r="K137" t="s">
-        <v>50</v>
+        <v>838</v>
       </c>
       <c r="L137" t="s">
         <v>14</v>
@@ -8806,31 +8794,31 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>294</v>
+        <v>833</v>
       </c>
       <c r="B138" t="s">
-        <v>309</v>
+        <v>237</v>
       </c>
       <c r="C138" t="s">
-        <v>640</v>
+        <v>832</v>
       </c>
       <c r="D138" t="s">
         <v>79</v>
       </c>
       <c r="E138" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F138" t="s">
         <v>13</v>
       </c>
       <c r="G138" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H138" t="s">
-        <v>204</v>
+        <v>336</v>
       </c>
       <c r="J138" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="K138" t="s">
         <v>49</v>
@@ -8847,31 +8835,34 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>295</v>
+        <v>361</v>
       </c>
       <c r="B139" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="C139" t="s">
-        <v>641</v>
+        <v>784</v>
       </c>
       <c r="D139" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E139" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F139" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G139" t="s">
-        <v>144</v>
+        <v>274</v>
       </c>
       <c r="H139" t="s">
-        <v>281</v>
+        <v>336</v>
+      </c>
+      <c r="I139" t="s">
+        <v>141</v>
       </c>
       <c r="J139" t="s">
-        <v>98</v>
+        <v>283</v>
       </c>
       <c r="K139" t="s">
         <v>49</v>
@@ -8888,13 +8879,13 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>296</v>
+        <v>225</v>
       </c>
       <c r="B140" t="s">
-        <v>311</v>
+        <v>234</v>
       </c>
       <c r="C140" t="s">
-        <v>639</v>
+        <v>553</v>
       </c>
       <c r="D140" t="s">
         <v>79</v>
@@ -8906,16 +8897,19 @@
         <v>13</v>
       </c>
       <c r="G140" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H140" t="s">
-        <v>204</v>
+        <v>336</v>
+      </c>
+      <c r="I140" t="s">
+        <v>76</v>
       </c>
       <c r="J140" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="K140" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L140" t="s">
         <v>14</v>
@@ -8929,19 +8923,19 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>297</v>
+        <v>159</v>
       </c>
       <c r="B141" t="s">
-        <v>312</v>
+        <v>174</v>
       </c>
       <c r="C141" t="s">
-        <v>313</v>
+        <v>830</v>
       </c>
       <c r="D141" t="s">
         <v>79</v>
       </c>
       <c r="E141" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F141" t="s">
         <v>13</v>
@@ -8950,16 +8944,16 @@
         <v>272</v>
       </c>
       <c r="H141" t="s">
-        <v>525</v>
+        <v>336</v>
       </c>
       <c r="I141" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="J141" t="s">
         <v>190</v>
       </c>
       <c r="K141" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L141" t="s">
         <v>14</v>
@@ -8973,13 +8967,13 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>298</v>
+        <v>535</v>
       </c>
       <c r="B142" t="s">
-        <v>314</v>
+        <v>538</v>
       </c>
       <c r="C142" t="s">
-        <v>315</v>
+        <v>539</v>
       </c>
       <c r="D142" t="s">
         <v>79</v>
@@ -8991,16 +8985,19 @@
         <v>13</v>
       </c>
       <c r="G142" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H142" t="s">
-        <v>281</v>
+        <v>486</v>
+      </c>
+      <c r="I142" t="s">
+        <v>55</v>
       </c>
       <c r="J142" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="K142" t="s">
-        <v>50</v>
+        <v>838</v>
       </c>
       <c r="L142" t="s">
         <v>14</v>
@@ -9014,13 +9011,13 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="B143" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="C143" t="s">
-        <v>802</v>
+        <v>347</v>
       </c>
       <c r="D143" t="s">
         <v>79</v>
@@ -9035,16 +9032,13 @@
         <v>272</v>
       </c>
       <c r="H143" t="s">
-        <v>317</v>
-      </c>
-      <c r="I143" t="s">
-        <v>76</v>
+        <v>268</v>
       </c>
       <c r="J143" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K143" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L143" t="s">
         <v>14</v>
@@ -9058,13 +9052,13 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>300</v>
+        <v>537</v>
       </c>
       <c r="B144" t="s">
-        <v>318</v>
+        <v>542</v>
       </c>
       <c r="C144" t="s">
-        <v>319</v>
+        <v>544</v>
       </c>
       <c r="D144" t="s">
         <v>79</v>
@@ -9076,19 +9070,16 @@
         <v>13</v>
       </c>
       <c r="G144" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
       <c r="H144" t="s">
-        <v>489</v>
-      </c>
-      <c r="I144" t="s">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="J144" t="s">
         <v>190</v>
       </c>
       <c r="K144" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="L144" t="s">
         <v>14</v>
@@ -9102,31 +9093,31 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>301</v>
+        <v>834</v>
       </c>
       <c r="B145" t="s">
-        <v>322</v>
+        <v>835</v>
       </c>
       <c r="C145" t="s">
-        <v>803</v>
+        <v>836</v>
       </c>
       <c r="D145" t="s">
         <v>79</v>
       </c>
       <c r="E145" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F145" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G145" t="s">
-        <v>144</v>
+        <v>272</v>
       </c>
       <c r="H145" t="s">
-        <v>490</v>
+        <v>336</v>
       </c>
       <c r="J145" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="K145" t="s">
         <v>49</v>
@@ -9143,13 +9134,13 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>302</v>
+        <v>158</v>
       </c>
       <c r="B146" t="s">
-        <v>323</v>
+        <v>545</v>
       </c>
       <c r="C146" t="s">
-        <v>611</v>
+        <v>173</v>
       </c>
       <c r="D146" t="s">
         <v>79</v>
@@ -9164,13 +9155,16 @@
         <v>272</v>
       </c>
       <c r="H146" t="s">
-        <v>111</v>
+        <v>336</v>
+      </c>
+      <c r="I146" t="s">
+        <v>76</v>
       </c>
       <c r="J146" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="K146" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L146" t="s">
         <v>14</v>
@@ -9184,19 +9178,19 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="B147" t="s">
-        <v>324</v>
+        <v>235</v>
       </c>
       <c r="C147" t="s">
-        <v>804</v>
+        <v>236</v>
       </c>
       <c r="D147" t="s">
         <v>79</v>
       </c>
       <c r="E147" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F147" t="s">
         <v>13</v>
@@ -9205,16 +9199,13 @@
         <v>272</v>
       </c>
       <c r="H147" t="s">
-        <v>317</v>
-      </c>
-      <c r="I147" t="s">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="J147" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="K147" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L147" t="s">
         <v>14</v>
@@ -9228,13 +9219,13 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>304</v>
+        <v>241</v>
       </c>
       <c r="B148" t="s">
-        <v>325</v>
+        <v>172</v>
       </c>
       <c r="C148" t="s">
-        <v>326</v>
+        <v>242</v>
       </c>
       <c r="D148" t="s">
         <v>79</v>
@@ -9243,22 +9234,19 @@
         <v>52</v>
       </c>
       <c r="F148" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G148" t="s">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="H148" t="s">
-        <v>328</v>
-      </c>
-      <c r="I148" t="s">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="J148" t="s">
         <v>190</v>
       </c>
       <c r="K148" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="L148" t="s">
         <v>14</v>
@@ -9272,13 +9260,13 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>305</v>
+        <v>175</v>
       </c>
       <c r="B149" t="s">
-        <v>329</v>
+        <v>179</v>
       </c>
       <c r="C149" t="s">
-        <v>805</v>
+        <v>641</v>
       </c>
       <c r="D149" t="s">
         <v>79</v>
@@ -9290,19 +9278,19 @@
         <v>13</v>
       </c>
       <c r="G149" t="s">
-        <v>330</v>
+        <v>142</v>
       </c>
       <c r="H149" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="I149" t="s">
         <v>76</v>
       </c>
       <c r="J149" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="K149" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L149" t="s">
         <v>14</v>
@@ -9316,13 +9304,13 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>306</v>
+        <v>176</v>
       </c>
       <c r="B150" t="s">
-        <v>331</v>
+        <v>184</v>
       </c>
       <c r="C150" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D150" t="s">
         <v>79</v>
@@ -9337,13 +9325,13 @@
         <v>272</v>
       </c>
       <c r="H150" t="s">
-        <v>209</v>
+        <v>487</v>
       </c>
       <c r="I150" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="J150" t="s">
-        <v>98</v>
+        <v>199</v>
       </c>
       <c r="K150" t="s">
         <v>49</v>
@@ -9360,19 +9348,19 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>307</v>
+        <v>177</v>
       </c>
       <c r="B151" t="s">
-        <v>332</v>
+        <v>186</v>
       </c>
       <c r="C151" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="D151" t="s">
         <v>79</v>
       </c>
       <c r="E151" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F151" t="s">
         <v>13</v>
@@ -9381,13 +9369,13 @@
         <v>272</v>
       </c>
       <c r="H151" t="s">
-        <v>209</v>
+        <v>487</v>
       </c>
       <c r="I151" t="s">
         <v>76</v>
       </c>
       <c r="J151" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K151" t="s">
         <v>49</v>
@@ -9404,13 +9392,13 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>308</v>
+        <v>239</v>
       </c>
       <c r="B152" t="s">
-        <v>333</v>
+        <v>240</v>
       </c>
       <c r="C152" t="s">
-        <v>334</v>
+        <v>642</v>
       </c>
       <c r="D152" t="s">
         <v>79</v>
@@ -9425,13 +9413,13 @@
         <v>142</v>
       </c>
       <c r="H152" t="s">
-        <v>489</v>
+        <v>336</v>
       </c>
       <c r="I152" t="s">
         <v>134</v>
       </c>
       <c r="J152" t="s">
-        <v>335</v>
+        <v>182</v>
       </c>
       <c r="K152" t="s">
         <v>49</v>
@@ -9492,13 +9480,16 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>341</v>
+        <v>570</v>
       </c>
       <c r="B154" t="s">
-        <v>354</v>
+        <v>578</v>
+      </c>
+      <c r="C154" t="s">
+        <v>814</v>
       </c>
       <c r="D154" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E154" t="s">
         <v>52</v>
@@ -9510,10 +9501,13 @@
         <v>142</v>
       </c>
       <c r="H154" t="s">
-        <v>433</v>
+        <v>268</v>
+      </c>
+      <c r="I154" t="s">
+        <v>76</v>
       </c>
       <c r="J154" t="s">
-        <v>96</v>
+        <v>569</v>
       </c>
       <c r="K154" t="s">
         <v>49</v>
@@ -9530,13 +9524,13 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>342</v>
+        <v>708</v>
       </c>
       <c r="B155" t="s">
-        <v>807</v>
+        <v>716</v>
       </c>
       <c r="C155" t="s">
-        <v>355</v>
+        <v>717</v>
       </c>
       <c r="D155" t="s">
         <v>79</v>
@@ -9548,16 +9542,16 @@
         <v>13</v>
       </c>
       <c r="G155" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="H155" t="s">
-        <v>525</v>
+        <v>336</v>
       </c>
       <c r="I155" t="s">
         <v>76</v>
       </c>
       <c r="J155" t="s">
-        <v>190</v>
+        <v>335</v>
       </c>
       <c r="K155" t="s">
         <v>49</v>
@@ -9574,13 +9568,13 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>410</v>
+        <v>297</v>
       </c>
       <c r="B156" t="s">
-        <v>806</v>
+        <v>312</v>
       </c>
       <c r="C156" t="s">
-        <v>416</v>
+        <v>313</v>
       </c>
       <c r="D156" t="s">
         <v>79</v>
@@ -9592,16 +9586,16 @@
         <v>13</v>
       </c>
       <c r="G156" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H156" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="I156" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="J156" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="K156" t="s">
         <v>49</v>
@@ -9618,31 +9612,31 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>411</v>
+        <v>624</v>
       </c>
       <c r="B157" t="s">
-        <v>808</v>
+        <v>634</v>
       </c>
       <c r="C157" t="s">
-        <v>809</v>
+        <v>635</v>
       </c>
       <c r="D157" t="s">
         <v>79</v>
       </c>
       <c r="E157" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F157" t="s">
         <v>13</v>
       </c>
       <c r="G157" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H157" t="s">
-        <v>494</v>
+        <v>204</v>
       </c>
       <c r="J157" t="s">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="K157" t="s">
         <v>49</v>
@@ -9659,13 +9653,13 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>462</v>
+        <v>625</v>
       </c>
       <c r="B158" t="s">
-        <v>552</v>
+        <v>636</v>
       </c>
       <c r="C158" t="s">
-        <v>553</v>
+        <v>637</v>
       </c>
       <c r="D158" t="s">
         <v>79</v>
@@ -9677,16 +9671,13 @@
         <v>13</v>
       </c>
       <c r="G158" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H158" t="s">
-        <v>111</v>
-      </c>
-      <c r="I158" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="J158" t="s">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="K158" t="s">
         <v>49</v>
@@ -9703,13 +9694,13 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>463</v>
+        <v>296</v>
       </c>
       <c r="B159" t="s">
-        <v>469</v>
+        <v>311</v>
       </c>
       <c r="C159" t="s">
-        <v>470</v>
+        <v>638</v>
       </c>
       <c r="D159" t="s">
         <v>79</v>
@@ -9721,16 +9712,13 @@
         <v>13</v>
       </c>
       <c r="G159" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H159" t="s">
-        <v>265</v>
-      </c>
-      <c r="I159" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="J159" t="s">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="K159" t="s">
         <v>49</v>
@@ -9747,13 +9735,13 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>464</v>
+        <v>294</v>
       </c>
       <c r="B160" t="s">
-        <v>471</v>
+        <v>309</v>
       </c>
       <c r="C160" t="s">
-        <v>472</v>
+        <v>639</v>
       </c>
       <c r="D160" t="s">
         <v>79</v>
@@ -9768,13 +9756,10 @@
         <v>272</v>
       </c>
       <c r="H160" t="s">
-        <v>310</v>
-      </c>
-      <c r="I160" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="J160" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K160" t="s">
         <v>49</v>
@@ -9791,13 +9776,13 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>465</v>
+        <v>622</v>
       </c>
       <c r="B161" t="s">
-        <v>473</v>
+        <v>415</v>
       </c>
       <c r="C161" t="s">
-        <v>470</v>
+        <v>631</v>
       </c>
       <c r="D161" t="s">
         <v>79</v>
@@ -9809,16 +9794,13 @@
         <v>13</v>
       </c>
       <c r="G161" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H161" t="s">
-        <v>265</v>
-      </c>
-      <c r="I161" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="J161" t="s">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="K161" t="s">
         <v>49</v>
@@ -9835,13 +9817,13 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>466</v>
+        <v>629</v>
       </c>
       <c r="B162" t="s">
-        <v>810</v>
+        <v>648</v>
       </c>
       <c r="C162" t="s">
-        <v>474</v>
+        <v>649</v>
       </c>
       <c r="D162" t="s">
         <v>79</v>
@@ -9856,10 +9838,13 @@
         <v>142</v>
       </c>
       <c r="H162" t="s">
-        <v>281</v>
+        <v>204</v>
+      </c>
+      <c r="I162" t="s">
+        <v>134</v>
       </c>
       <c r="J162" t="s">
-        <v>498</v>
+        <v>345</v>
       </c>
       <c r="K162" t="s">
         <v>49</v>
@@ -9876,31 +9861,31 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>468</v>
+        <v>295</v>
       </c>
       <c r="B163" t="s">
-        <v>477</v>
+        <v>800</v>
       </c>
       <c r="C163" t="s">
-        <v>478</v>
+        <v>640</v>
       </c>
       <c r="D163" t="s">
         <v>79</v>
       </c>
       <c r="E163" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F163" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G163" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H163" t="s">
-        <v>111</v>
+        <v>281</v>
       </c>
       <c r="J163" t="s">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="K163" t="s">
         <v>49</v>
@@ -9917,13 +9902,13 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>513</v>
+        <v>298</v>
       </c>
       <c r="B164" t="s">
-        <v>811</v>
+        <v>314</v>
       </c>
       <c r="C164" t="s">
-        <v>519</v>
+        <v>315</v>
       </c>
       <c r="D164" t="s">
         <v>79</v>
@@ -9932,22 +9917,19 @@
         <v>32</v>
       </c>
       <c r="F164" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G164" t="s">
-        <v>520</v>
+        <v>142</v>
       </c>
       <c r="H164" t="s">
-        <v>487</v>
-      </c>
-      <c r="I164" t="s">
-        <v>76</v>
+        <v>281</v>
       </c>
       <c r="J164" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="K164" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L164" t="s">
         <v>14</v>
@@ -9961,13 +9943,13 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>536</v>
+        <v>300</v>
       </c>
       <c r="B165" t="s">
-        <v>543</v>
+        <v>318</v>
       </c>
       <c r="C165" t="s">
-        <v>540</v>
+        <v>319</v>
       </c>
       <c r="D165" t="s">
         <v>79</v>
@@ -9979,19 +9961,19 @@
         <v>13</v>
       </c>
       <c r="G165" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="H165" t="s">
-        <v>541</v>
+        <v>489</v>
       </c>
       <c r="I165" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="J165" t="s">
         <v>190</v>
       </c>
       <c r="K165" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L165" t="s">
         <v>14</v>
@@ -10005,34 +9987,34 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>537</v>
+        <v>301</v>
       </c>
       <c r="B166" t="s">
-        <v>542</v>
+        <v>322</v>
       </c>
       <c r="C166" t="s">
-        <v>544</v>
+        <v>802</v>
       </c>
       <c r="D166" t="s">
         <v>79</v>
       </c>
       <c r="E166" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F166" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G166" t="s">
-        <v>272</v>
+        <v>144</v>
       </c>
       <c r="H166" t="s">
-        <v>336</v>
+        <v>490</v>
       </c>
       <c r="J166" t="s">
-        <v>190</v>
+        <v>96</v>
       </c>
       <c r="K166" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L166" t="s">
         <v>14</v>
@@ -10046,13 +10028,13 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>561</v>
+        <v>302</v>
       </c>
       <c r="B167" t="s">
-        <v>565</v>
+        <v>323</v>
       </c>
       <c r="C167" t="s">
-        <v>566</v>
+        <v>610</v>
       </c>
       <c r="D167" t="s">
         <v>79</v>
@@ -10064,19 +10046,16 @@
         <v>13</v>
       </c>
       <c r="G167" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H167" t="s">
-        <v>491</v>
-      </c>
-      <c r="I167" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="J167" t="s">
-        <v>190</v>
+        <v>96</v>
       </c>
       <c r="K167" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L167" t="s">
         <v>14</v>
@@ -10090,13 +10069,13 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>562</v>
+        <v>304</v>
       </c>
       <c r="B168" t="s">
-        <v>567</v>
+        <v>325</v>
       </c>
       <c r="C168" t="s">
-        <v>601</v>
+        <v>326</v>
       </c>
       <c r="D168" t="s">
         <v>79</v>
@@ -10105,19 +10084,22 @@
         <v>52</v>
       </c>
       <c r="F168" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G168" t="s">
-        <v>110</v>
+        <v>327</v>
+      </c>
+      <c r="H168" t="s">
+        <v>328</v>
       </c>
       <c r="I168" t="s">
         <v>76</v>
       </c>
       <c r="J168" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="K168" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L168" t="s">
         <v>14</v>
@@ -10131,13 +10113,13 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>563</v>
+        <v>299</v>
       </c>
       <c r="B169" t="s">
-        <v>812</v>
+        <v>316</v>
       </c>
       <c r="C169" t="s">
-        <v>568</v>
+        <v>801</v>
       </c>
       <c r="D169" t="s">
         <v>79</v>
@@ -10149,19 +10131,19 @@
         <v>13</v>
       </c>
       <c r="G169" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H169" t="s">
-        <v>489</v>
+        <v>317</v>
       </c>
       <c r="I169" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="J169" t="s">
-        <v>581</v>
+        <v>185</v>
       </c>
       <c r="K169" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L169" t="s">
         <v>14</v>
@@ -10175,13 +10157,13 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>564</v>
+        <v>303</v>
       </c>
       <c r="B170" t="s">
-        <v>813</v>
+        <v>324</v>
       </c>
       <c r="C170" t="s">
-        <v>569</v>
+        <v>803</v>
       </c>
       <c r="D170" t="s">
         <v>79</v>
@@ -10193,16 +10175,16 @@
         <v>13</v>
       </c>
       <c r="G170" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H170" t="s">
-        <v>492</v>
+        <v>317</v>
       </c>
       <c r="I170" t="s">
         <v>76</v>
       </c>
       <c r="J170" t="s">
-        <v>570</v>
+        <v>98</v>
       </c>
       <c r="K170" t="s">
         <v>49</v>
@@ -10219,34 +10201,37 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>572</v>
+        <v>305</v>
       </c>
       <c r="B171" t="s">
-        <v>112</v>
+        <v>329</v>
       </c>
       <c r="C171" t="s">
-        <v>576</v>
+        <v>804</v>
       </c>
       <c r="D171" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E171" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F171" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G171" t="s">
-        <v>146</v>
+        <v>330</v>
       </c>
       <c r="H171" t="s">
-        <v>28</v>
+        <v>209</v>
+      </c>
+      <c r="I171" t="s">
+        <v>76</v>
       </c>
       <c r="J171" t="s">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="K171" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L171" t="s">
         <v>14</v>
@@ -10260,19 +10245,19 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="B172" t="s">
-        <v>577</v>
+        <v>604</v>
       </c>
       <c r="C172" t="s">
-        <v>387</v>
+        <v>801</v>
       </c>
       <c r="D172" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E172" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F172" t="s">
         <v>13</v>
@@ -10281,13 +10266,16 @@
         <v>272</v>
       </c>
       <c r="H172" t="s">
-        <v>205</v>
+        <v>494</v>
+      </c>
+      <c r="I172" t="s">
+        <v>76</v>
       </c>
       <c r="J172" t="s">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="K172" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L172" t="s">
         <v>14</v>
@@ -10301,19 +10289,19 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>574</v>
+        <v>306</v>
       </c>
       <c r="B173" t="s">
-        <v>578</v>
+        <v>331</v>
       </c>
       <c r="C173" t="s">
-        <v>387</v>
+        <v>801</v>
       </c>
       <c r="D173" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E173" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F173" t="s">
         <v>13</v>
@@ -10322,10 +10310,13 @@
         <v>272</v>
       </c>
       <c r="H173" t="s">
-        <v>525</v>
+        <v>209</v>
+      </c>
+      <c r="I173" t="s">
+        <v>76</v>
       </c>
       <c r="J173" t="s">
-        <v>580</v>
+        <v>98</v>
       </c>
       <c r="K173" t="s">
         <v>49</v>
@@ -10342,16 +10333,16 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>571</v>
+        <v>307</v>
       </c>
       <c r="B174" t="s">
-        <v>579</v>
+        <v>332</v>
       </c>
       <c r="C174" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="D174" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E174" t="s">
         <v>52</v>
@@ -10360,16 +10351,16 @@
         <v>13</v>
       </c>
       <c r="G174" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H174" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="I174" t="s">
         <v>76</v>
       </c>
       <c r="J174" t="s">
-        <v>570</v>
+        <v>98</v>
       </c>
       <c r="K174" t="s">
         <v>49</v>
@@ -10386,31 +10377,34 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>575</v>
+        <v>308</v>
       </c>
       <c r="B175" t="s">
-        <v>582</v>
+        <v>333</v>
       </c>
       <c r="C175" t="s">
-        <v>583</v>
+        <v>334</v>
       </c>
       <c r="D175" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E175" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F175" t="s">
         <v>13</v>
       </c>
       <c r="G175" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="H175" t="s">
-        <v>131</v>
+        <v>489</v>
+      </c>
+      <c r="I175" t="s">
+        <v>134</v>
       </c>
       <c r="J175" t="s">
-        <v>390</v>
+        <v>335</v>
       </c>
       <c r="K175" t="s">
         <v>49</v>
@@ -10427,19 +10421,16 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>584</v>
+        <v>341</v>
       </c>
       <c r="B176" t="s">
-        <v>588</v>
-      </c>
-      <c r="C176" t="s">
-        <v>589</v>
+        <v>354</v>
       </c>
       <c r="D176" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E176" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F176" t="s">
         <v>13</v>
@@ -10448,13 +10439,10 @@
         <v>142</v>
       </c>
       <c r="H176" t="s">
-        <v>492</v>
-      </c>
-      <c r="I176" t="s">
-        <v>141</v>
+        <v>433</v>
       </c>
       <c r="J176" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K176" t="s">
         <v>49</v>
@@ -10471,16 +10459,16 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>585</v>
+        <v>342</v>
       </c>
       <c r="B177" t="s">
-        <v>590</v>
+        <v>806</v>
       </c>
       <c r="C177" t="s">
-        <v>553</v>
+        <v>355</v>
       </c>
       <c r="D177" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E177" t="s">
         <v>52</v>
@@ -10489,16 +10477,16 @@
         <v>13</v>
       </c>
       <c r="G177" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="H177" t="s">
-        <v>591</v>
+        <v>525</v>
       </c>
       <c r="I177" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="J177" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K177" t="s">
         <v>49</v>
@@ -10515,34 +10503,34 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>586</v>
+        <v>410</v>
       </c>
       <c r="B178" t="s">
-        <v>592</v>
+        <v>805</v>
       </c>
       <c r="C178" t="s">
-        <v>600</v>
+        <v>416</v>
       </c>
       <c r="D178" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E178" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F178" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G178" t="s">
-        <v>593</v>
+        <v>142</v>
       </c>
       <c r="H178" t="s">
-        <v>281</v>
+        <v>534</v>
       </c>
       <c r="I178" t="s">
         <v>76</v>
       </c>
       <c r="J178" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K178" t="s">
         <v>49</v>
@@ -10559,19 +10547,19 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>587</v>
+        <v>463</v>
       </c>
       <c r="B179" t="s">
-        <v>594</v>
+        <v>469</v>
       </c>
       <c r="C179" t="s">
-        <v>595</v>
+        <v>470</v>
       </c>
       <c r="D179" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E179" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F179" t="s">
         <v>13</v>
@@ -10580,16 +10568,16 @@
         <v>142</v>
       </c>
       <c r="H179" t="s">
-        <v>488</v>
+        <v>265</v>
       </c>
       <c r="I179" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="J179" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="K179" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L179" t="s">
         <v>14</v>
@@ -10603,34 +10591,34 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>596</v>
+        <v>465</v>
       </c>
       <c r="B180" t="s">
-        <v>602</v>
+        <v>473</v>
       </c>
       <c r="C180" t="s">
-        <v>603</v>
+        <v>470</v>
       </c>
       <c r="D180" t="s">
         <v>79</v>
       </c>
       <c r="E180" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F180" t="s">
         <v>13</v>
       </c>
       <c r="G180" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H180" t="s">
-        <v>604</v>
+        <v>265</v>
       </c>
       <c r="I180" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="J180" t="s">
-        <v>498</v>
+        <v>199</v>
       </c>
       <c r="K180" t="s">
         <v>49</v>
@@ -10647,34 +10635,31 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>598</v>
+        <v>673</v>
       </c>
       <c r="B181" t="s">
-        <v>605</v>
-      </c>
-      <c r="C181" t="s">
-        <v>802</v>
+        <v>693</v>
       </c>
       <c r="D181" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E181" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F181" t="s">
         <v>13</v>
       </c>
       <c r="G181" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H181" t="s">
-        <v>494</v>
+        <v>189</v>
       </c>
       <c r="I181" t="s">
         <v>76</v>
       </c>
       <c r="J181" t="s">
-        <v>98</v>
+        <v>694</v>
       </c>
       <c r="K181" t="s">
         <v>49</v>
@@ -10691,19 +10676,19 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>597</v>
+        <v>411</v>
       </c>
       <c r="B182" t="s">
-        <v>606</v>
+        <v>807</v>
       </c>
       <c r="C182" t="s">
-        <v>607</v>
+        <v>808</v>
       </c>
       <c r="D182" t="s">
         <v>79</v>
       </c>
       <c r="E182" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F182" t="s">
         <v>13</v>
@@ -10712,16 +10697,13 @@
         <v>142</v>
       </c>
       <c r="H182" t="s">
-        <v>492</v>
-      </c>
-      <c r="I182" t="s">
-        <v>76</v>
+        <v>494</v>
       </c>
       <c r="J182" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K182" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L182" t="s">
         <v>14</v>
@@ -10735,13 +10717,13 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>599</v>
+        <v>462</v>
       </c>
       <c r="B183" t="s">
-        <v>608</v>
+        <v>551</v>
       </c>
       <c r="C183" t="s">
-        <v>609</v>
+        <v>552</v>
       </c>
       <c r="D183" t="s">
         <v>79</v>
@@ -10756,16 +10738,16 @@
         <v>142</v>
       </c>
       <c r="H183" t="s">
-        <v>281</v>
+        <v>111</v>
       </c>
       <c r="I183" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="J183" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K183" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L183" t="s">
         <v>14</v>
@@ -10779,13 +10761,13 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>623</v>
+        <v>464</v>
       </c>
       <c r="B184" t="s">
-        <v>415</v>
+        <v>471</v>
       </c>
       <c r="C184" t="s">
-        <v>632</v>
+        <v>472</v>
       </c>
       <c r="D184" t="s">
         <v>79</v>
@@ -10800,10 +10782,13 @@
         <v>272</v>
       </c>
       <c r="H184" t="s">
-        <v>204</v>
+        <v>310</v>
+      </c>
+      <c r="I184" t="s">
+        <v>76</v>
       </c>
       <c r="J184" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K184" t="s">
         <v>49</v>
@@ -10820,19 +10805,19 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>624</v>
+        <v>466</v>
       </c>
       <c r="B185" t="s">
-        <v>633</v>
+        <v>809</v>
       </c>
       <c r="C185" t="s">
-        <v>634</v>
+        <v>474</v>
       </c>
       <c r="D185" t="s">
         <v>79</v>
       </c>
       <c r="E185" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F185" t="s">
         <v>13</v>
@@ -10841,13 +10826,13 @@
         <v>142</v>
       </c>
       <c r="H185" t="s">
-        <v>525</v>
+        <v>281</v>
       </c>
       <c r="J185" t="s">
-        <v>190</v>
+        <v>498</v>
       </c>
       <c r="K185" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L185" t="s">
         <v>14</v>
@@ -10861,13 +10846,13 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>625</v>
+        <v>468</v>
       </c>
       <c r="B186" t="s">
-        <v>635</v>
+        <v>477</v>
       </c>
       <c r="C186" t="s">
-        <v>636</v>
+        <v>478</v>
       </c>
       <c r="D186" t="s">
         <v>79</v>
@@ -10879,13 +10864,13 @@
         <v>13</v>
       </c>
       <c r="G186" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H186" t="s">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="J186" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="K186" t="s">
         <v>49</v>
@@ -10902,31 +10887,34 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>626</v>
+        <v>513</v>
       </c>
       <c r="B187" t="s">
-        <v>637</v>
+        <v>810</v>
       </c>
       <c r="C187" t="s">
-        <v>638</v>
+        <v>519</v>
       </c>
       <c r="D187" t="s">
         <v>79</v>
       </c>
       <c r="E187" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F187" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G187" t="s">
-        <v>272</v>
+        <v>520</v>
       </c>
       <c r="H187" t="s">
-        <v>204</v>
+        <v>487</v>
+      </c>
+      <c r="I187" t="s">
+        <v>76</v>
       </c>
       <c r="J187" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="K187" t="s">
         <v>49</v>
@@ -10943,34 +10931,34 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>627</v>
+        <v>536</v>
       </c>
       <c r="B188" t="s">
-        <v>816</v>
+        <v>543</v>
       </c>
       <c r="C188" t="s">
-        <v>644</v>
+        <v>540</v>
       </c>
       <c r="D188" t="s">
         <v>79</v>
       </c>
       <c r="E188" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F188" t="s">
         <v>13</v>
       </c>
       <c r="G188" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H188" t="s">
-        <v>204</v>
+        <v>541</v>
       </c>
       <c r="I188" t="s">
         <v>134</v>
       </c>
       <c r="J188" t="s">
-        <v>335</v>
+        <v>190</v>
       </c>
       <c r="K188" t="s">
         <v>49</v>
@@ -10987,13 +10975,13 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>628</v>
+        <v>560</v>
       </c>
       <c r="B189" t="s">
-        <v>645</v>
+        <v>564</v>
       </c>
       <c r="C189" t="s">
-        <v>646</v>
+        <v>565</v>
       </c>
       <c r="D189" t="s">
         <v>79</v>
@@ -11002,19 +10990,22 @@
         <v>52</v>
       </c>
       <c r="F189" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G189" t="s">
-        <v>222</v>
+        <v>142</v>
       </c>
       <c r="H189" t="s">
-        <v>205</v>
+        <v>491</v>
+      </c>
+      <c r="I189" t="s">
+        <v>76</v>
       </c>
       <c r="J189" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="K189" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L189" t="s">
         <v>14</v>
@@ -11028,13 +11019,13 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>629</v>
+        <v>561</v>
       </c>
       <c r="B190" t="s">
-        <v>647</v>
+        <v>566</v>
       </c>
       <c r="C190" t="s">
-        <v>648</v>
+        <v>600</v>
       </c>
       <c r="D190" t="s">
         <v>79</v>
@@ -11043,16 +11034,16 @@
         <v>52</v>
       </c>
       <c r="F190" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G190" t="s">
-        <v>450</v>
-      </c>
-      <c r="H190" t="s">
-        <v>205</v>
+        <v>110</v>
+      </c>
+      <c r="I190" t="s">
+        <v>76</v>
       </c>
       <c r="J190" t="s">
-        <v>96</v>
+        <v>199</v>
       </c>
       <c r="K190" t="s">
         <v>49</v>
@@ -11069,19 +11060,19 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>630</v>
+        <v>562</v>
       </c>
       <c r="B191" t="s">
-        <v>649</v>
+        <v>811</v>
       </c>
       <c r="C191" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="D191" t="s">
         <v>79</v>
       </c>
       <c r="E191" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F191" t="s">
         <v>13</v>
@@ -11090,16 +11081,16 @@
         <v>142</v>
       </c>
       <c r="H191" t="s">
-        <v>204</v>
+        <v>489</v>
       </c>
       <c r="I191" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="J191" t="s">
-        <v>345</v>
+        <v>580</v>
       </c>
       <c r="K191" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L191" t="s">
         <v>14</v>
@@ -11113,34 +11104,37 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>631</v>
+        <v>563</v>
       </c>
       <c r="B192" t="s">
-        <v>651</v>
+        <v>812</v>
       </c>
       <c r="C192" t="s">
-        <v>817</v>
+        <v>568</v>
       </c>
       <c r="D192" t="s">
         <v>79</v>
       </c>
       <c r="E192" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F192" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G192" t="s">
-        <v>450</v>
+        <v>142</v>
       </c>
       <c r="H192" t="s">
-        <v>281</v>
+        <v>492</v>
+      </c>
+      <c r="I192" t="s">
+        <v>76</v>
       </c>
       <c r="J192" t="s">
-        <v>190</v>
+        <v>569</v>
       </c>
       <c r="K192" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L192" t="s">
         <v>14</v>
@@ -11154,13 +11148,13 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>612</v>
+        <v>572</v>
       </c>
       <c r="B193" t="s">
-        <v>652</v>
+        <v>576</v>
       </c>
       <c r="C193" t="s">
-        <v>653</v>
+        <v>387</v>
       </c>
       <c r="D193" t="s">
         <v>48</v>
@@ -11172,13 +11166,16 @@
         <v>13</v>
       </c>
       <c r="G193" t="s">
-        <v>142</v>
+        <v>272</v>
+      </c>
+      <c r="H193" t="s">
+        <v>205</v>
       </c>
       <c r="J193" t="s">
         <v>182</v>
       </c>
       <c r="K193" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L193" t="s">
         <v>14</v>
@@ -11192,13 +11189,13 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>613</v>
+        <v>573</v>
       </c>
       <c r="B194" t="s">
-        <v>654</v>
+        <v>577</v>
       </c>
       <c r="C194" t="s">
-        <v>818</v>
+        <v>387</v>
       </c>
       <c r="D194" t="s">
         <v>48</v>
@@ -11210,16 +11207,16 @@
         <v>13</v>
       </c>
       <c r="G194" t="s">
-        <v>142</v>
-      </c>
-      <c r="I194" t="s">
-        <v>55</v>
+        <v>272</v>
+      </c>
+      <c r="H194" t="s">
+        <v>525</v>
       </c>
       <c r="J194" t="s">
-        <v>182</v>
+        <v>579</v>
       </c>
       <c r="K194" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L194" t="s">
         <v>14</v>
@@ -11233,13 +11230,13 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>614</v>
+        <v>583</v>
       </c>
       <c r="B195" t="s">
-        <v>655</v>
+        <v>587</v>
       </c>
       <c r="C195" t="s">
-        <v>447</v>
+        <v>588</v>
       </c>
       <c r="D195" t="s">
         <v>48</v>
@@ -11251,13 +11248,16 @@
         <v>13</v>
       </c>
       <c r="G195" t="s">
-        <v>110</v>
+        <v>142</v>
+      </c>
+      <c r="H195" t="s">
+        <v>492</v>
       </c>
       <c r="I195" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="J195" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K195" t="s">
         <v>49</v>
@@ -11274,31 +11274,34 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>615</v>
+        <v>584</v>
       </c>
       <c r="B196" t="s">
-        <v>819</v>
+        <v>589</v>
       </c>
       <c r="C196" t="s">
-        <v>657</v>
+        <v>552</v>
       </c>
       <c r="D196" t="s">
         <v>48</v>
       </c>
       <c r="E196" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F196" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G196" t="s">
-        <v>656</v>
+        <v>142</v>
       </c>
       <c r="H196" t="s">
-        <v>111</v>
+        <v>590</v>
+      </c>
+      <c r="I196" t="s">
+        <v>134</v>
       </c>
       <c r="J196" t="s">
-        <v>390</v>
+        <v>182</v>
       </c>
       <c r="K196" t="s">
         <v>49</v>
@@ -11315,10 +11318,13 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>616</v>
+        <v>585</v>
       </c>
       <c r="B197" t="s">
-        <v>662</v>
+        <v>591</v>
+      </c>
+      <c r="C197" t="s">
+        <v>599</v>
       </c>
       <c r="D197" t="s">
         <v>48</v>
@@ -11327,22 +11333,22 @@
         <v>32</v>
       </c>
       <c r="F197" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G197" t="s">
-        <v>142</v>
+        <v>592</v>
       </c>
       <c r="H197" t="s">
-        <v>204</v>
+        <v>281</v>
       </c>
       <c r="I197" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="J197" t="s">
         <v>182</v>
       </c>
       <c r="K197" t="s">
-        <v>839</v>
+        <v>49</v>
       </c>
       <c r="L197" t="s">
         <v>14</v>
@@ -11356,13 +11362,13 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>617</v>
+        <v>586</v>
       </c>
       <c r="B198" t="s">
-        <v>820</v>
+        <v>593</v>
       </c>
       <c r="C198" t="s">
-        <v>658</v>
+        <v>594</v>
       </c>
       <c r="D198" t="s">
         <v>48</v>
@@ -11371,19 +11377,22 @@
         <v>32</v>
       </c>
       <c r="F198" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G198" t="s">
-        <v>656</v>
+        <v>142</v>
       </c>
       <c r="H198" t="s">
-        <v>111</v>
+        <v>488</v>
+      </c>
+      <c r="I198" t="s">
+        <v>55</v>
       </c>
       <c r="J198" t="s">
-        <v>390</v>
+        <v>183</v>
       </c>
       <c r="K198" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L198" t="s">
         <v>14</v>
@@ -11397,31 +11406,34 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="B199" t="s">
-        <v>821</v>
+        <v>601</v>
       </c>
       <c r="C199" t="s">
-        <v>659</v>
+        <v>602</v>
       </c>
       <c r="D199" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E199" t="s">
         <v>32</v>
       </c>
       <c r="F199" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G199" t="s">
-        <v>656</v>
+        <v>272</v>
       </c>
       <c r="H199" t="s">
-        <v>328</v>
+        <v>603</v>
+      </c>
+      <c r="I199" t="s">
+        <v>54</v>
       </c>
       <c r="J199" t="s">
-        <v>390</v>
+        <v>498</v>
       </c>
       <c r="K199" t="s">
         <v>49</v>
@@ -11438,37 +11450,37 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>619</v>
+        <v>596</v>
       </c>
       <c r="B200" t="s">
-        <v>822</v>
+        <v>605</v>
       </c>
       <c r="C200" t="s">
-        <v>663</v>
+        <v>606</v>
       </c>
       <c r="D200" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E200" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F200" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G200" t="s">
         <v>142</v>
       </c>
       <c r="H200" t="s">
-        <v>131</v>
+        <v>492</v>
       </c>
       <c r="I200" t="s">
-        <v>419</v>
+        <v>76</v>
       </c>
       <c r="J200" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="K200" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L200" t="s">
         <v>14</v>
@@ -11482,34 +11494,37 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="B201" t="s">
-        <v>823</v>
+        <v>607</v>
       </c>
       <c r="C201" t="s">
-        <v>660</v>
+        <v>608</v>
       </c>
       <c r="D201" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E201" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F201" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G201" t="s">
-        <v>656</v>
+        <v>142</v>
       </c>
       <c r="H201" t="s">
-        <v>111</v>
+        <v>281</v>
+      </c>
+      <c r="I201" t="s">
+        <v>76</v>
       </c>
       <c r="J201" t="s">
-        <v>390</v>
+        <v>96</v>
       </c>
       <c r="K201" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L201" t="s">
         <v>14</v>
@@ -11523,34 +11538,34 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B202" t="s">
-        <v>664</v>
+        <v>632</v>
       </c>
       <c r="C202" t="s">
-        <v>824</v>
+        <v>633</v>
       </c>
       <c r="D202" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E202" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F202" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G202" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H202" t="s">
-        <v>281</v>
+        <v>525</v>
       </c>
       <c r="J202" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K202" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L202" t="s">
         <v>14</v>
@@ -11564,31 +11579,34 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B203" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="C203" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="D203" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E203" t="s">
         <v>32</v>
       </c>
       <c r="F203" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G203" t="s">
-        <v>656</v>
+        <v>142</v>
       </c>
       <c r="H203" t="s">
-        <v>111</v>
+        <v>204</v>
+      </c>
+      <c r="I203" t="s">
+        <v>134</v>
       </c>
       <c r="J203" t="s">
-        <v>182</v>
+        <v>335</v>
       </c>
       <c r="K203" t="s">
         <v>49</v>
@@ -11605,31 +11623,31 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>665</v>
+        <v>627</v>
       </c>
       <c r="B204" t="s">
-        <v>375</v>
+        <v>644</v>
       </c>
       <c r="C204" t="s">
-        <v>681</v>
+        <v>645</v>
       </c>
       <c r="D204" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E204" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F204" t="s">
         <v>31</v>
       </c>
       <c r="G204" t="s">
-        <v>144</v>
+        <v>222</v>
       </c>
       <c r="H204" t="s">
-        <v>485</v>
+        <v>205</v>
       </c>
       <c r="J204" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K204" t="s">
         <v>49</v>
@@ -11646,34 +11664,31 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>666</v>
+        <v>628</v>
       </c>
       <c r="B205" t="s">
-        <v>682</v>
+        <v>646</v>
       </c>
       <c r="C205" t="s">
-        <v>683</v>
+        <v>647</v>
       </c>
       <c r="D205" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E205" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F205" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G205" t="s">
-        <v>142</v>
+        <v>450</v>
       </c>
       <c r="H205" t="s">
-        <v>481</v>
-      </c>
-      <c r="I205" t="s">
-        <v>419</v>
+        <v>205</v>
       </c>
       <c r="J205" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K205" t="s">
         <v>49</v>
@@ -11690,37 +11705,34 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>667</v>
+        <v>630</v>
       </c>
       <c r="B206" t="s">
-        <v>112</v>
+        <v>650</v>
       </c>
       <c r="C206" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="D206" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E206" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F206" t="s">
         <v>31</v>
       </c>
       <c r="G206" t="s">
-        <v>146</v>
+        <v>450</v>
       </c>
       <c r="H206" t="s">
-        <v>481</v>
-      </c>
-      <c r="I206" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="J206" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K206" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L206" t="s">
         <v>14</v>
@@ -11734,19 +11746,19 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>668</v>
+        <v>611</v>
       </c>
       <c r="B207" t="s">
-        <v>684</v>
+        <v>651</v>
       </c>
       <c r="C207" t="s">
-        <v>685</v>
+        <v>652</v>
       </c>
       <c r="D207" t="s">
         <v>48</v>
       </c>
       <c r="E207" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F207" t="s">
         <v>13</v>
@@ -11754,12 +11766,6 @@
       <c r="G207" t="s">
         <v>142</v>
       </c>
-      <c r="H207" t="s">
-        <v>205</v>
-      </c>
-      <c r="I207" t="s">
-        <v>134</v>
-      </c>
       <c r="J207" t="s">
         <v>182</v>
       </c>
@@ -11778,37 +11784,34 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>669</v>
+        <v>612</v>
       </c>
       <c r="B208" t="s">
-        <v>686</v>
+        <v>653</v>
       </c>
       <c r="C208" t="s">
-        <v>687</v>
+        <v>817</v>
       </c>
       <c r="D208" t="s">
         <v>48</v>
       </c>
       <c r="E208" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F208" t="s">
         <v>13</v>
       </c>
       <c r="G208" t="s">
-        <v>110</v>
-      </c>
-      <c r="H208" t="s">
-        <v>281</v>
+        <v>142</v>
       </c>
       <c r="I208" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J208" t="s">
         <v>182</v>
       </c>
       <c r="K208" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L208" t="s">
         <v>14</v>
@@ -11822,13 +11825,13 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>670</v>
+        <v>613</v>
       </c>
       <c r="B209" t="s">
-        <v>688</v>
+        <v>654</v>
       </c>
       <c r="C209" t="s">
-        <v>689</v>
+        <v>447</v>
       </c>
       <c r="D209" t="s">
         <v>48</v>
@@ -11840,13 +11843,13 @@
         <v>13</v>
       </c>
       <c r="G209" t="s">
-        <v>142</v>
-      </c>
-      <c r="H209" t="s">
-        <v>281</v>
+        <v>110</v>
+      </c>
+      <c r="I209" t="s">
+        <v>55</v>
       </c>
       <c r="J209" t="s">
-        <v>345</v>
+        <v>183</v>
       </c>
       <c r="K209" t="s">
         <v>49</v>
@@ -11863,13 +11866,13 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>671</v>
+        <v>614</v>
       </c>
       <c r="B210" t="s">
-        <v>690</v>
+        <v>818</v>
       </c>
       <c r="C210" t="s">
-        <v>691</v>
+        <v>656</v>
       </c>
       <c r="D210" t="s">
         <v>48</v>
@@ -11878,16 +11881,13 @@
         <v>32</v>
       </c>
       <c r="F210" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G210" t="s">
-        <v>450</v>
+        <v>655</v>
       </c>
       <c r="H210" t="s">
-        <v>205</v>
-      </c>
-      <c r="I210" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="J210" t="s">
         <v>390</v>
@@ -11907,34 +11907,31 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>672</v>
+        <v>616</v>
       </c>
       <c r="B211" t="s">
-        <v>692</v>
+        <v>819</v>
       </c>
       <c r="C211" t="s">
-        <v>693</v>
+        <v>657</v>
       </c>
       <c r="D211" t="s">
         <v>48</v>
       </c>
       <c r="E211" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F211" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G211" t="s">
-        <v>110</v>
+        <v>655</v>
       </c>
       <c r="H211" t="s">
-        <v>281</v>
-      </c>
-      <c r="I211" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="J211" t="s">
-        <v>182</v>
+        <v>390</v>
       </c>
       <c r="K211" t="s">
         <v>49</v>
@@ -11951,13 +11948,13 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>673</v>
+        <v>617</v>
       </c>
       <c r="B212" t="s">
-        <v>715</v>
+        <v>820</v>
       </c>
       <c r="C212" t="s">
-        <v>716</v>
+        <v>658</v>
       </c>
       <c r="D212" t="s">
         <v>48</v>
@@ -11966,16 +11963,16 @@
         <v>32</v>
       </c>
       <c r="F212" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G212" t="s">
-        <v>142</v>
+        <v>655</v>
       </c>
       <c r="H212" t="s">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="J212" t="s">
-        <v>182</v>
+        <v>390</v>
       </c>
       <c r="K212" t="s">
         <v>49</v>
@@ -11992,10 +11989,13 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>674</v>
+        <v>619</v>
       </c>
       <c r="B213" t="s">
-        <v>694</v>
+        <v>821</v>
+      </c>
+      <c r="C213" t="s">
+        <v>659</v>
       </c>
       <c r="D213" t="s">
         <v>48</v>
@@ -12004,19 +12004,16 @@
         <v>32</v>
       </c>
       <c r="F213" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G213" t="s">
-        <v>142</v>
+        <v>655</v>
       </c>
       <c r="H213" t="s">
-        <v>189</v>
-      </c>
-      <c r="I213" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="J213" t="s">
-        <v>695</v>
+        <v>390</v>
       </c>
       <c r="K213" t="s">
         <v>49</v>
@@ -12033,13 +12030,13 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>675</v>
+        <v>621</v>
       </c>
       <c r="B214" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C214" t="s">
-        <v>691</v>
+        <v>660</v>
       </c>
       <c r="D214" t="s">
         <v>48</v>
@@ -12048,19 +12045,16 @@
         <v>32</v>
       </c>
       <c r="F214" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G214" t="s">
-        <v>450</v>
+        <v>655</v>
       </c>
       <c r="H214" t="s">
-        <v>205</v>
-      </c>
-      <c r="I214" t="s">
-        <v>208</v>
+        <v>111</v>
       </c>
       <c r="J214" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K214" t="s">
         <v>49</v>
@@ -12077,13 +12071,10 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>676</v>
+        <v>615</v>
       </c>
       <c r="B215" t="s">
-        <v>696</v>
-      </c>
-      <c r="C215" t="s">
-        <v>697</v>
+        <v>661</v>
       </c>
       <c r="D215" t="s">
         <v>48</v>
@@ -12092,22 +12083,22 @@
         <v>32</v>
       </c>
       <c r="F215" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G215" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="H215" t="s">
-        <v>281</v>
+        <v>204</v>
       </c>
       <c r="I215" t="s">
-        <v>419</v>
+        <v>55</v>
       </c>
       <c r="J215" t="s">
         <v>182</v>
       </c>
       <c r="K215" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="L215" t="s">
         <v>14</v>
@@ -12121,34 +12112,34 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>677</v>
+        <v>620</v>
       </c>
       <c r="B216" t="s">
-        <v>698</v>
+        <v>663</v>
       </c>
       <c r="C216" t="s">
-        <v>336</v>
+        <v>822</v>
       </c>
       <c r="D216" t="s">
         <v>48</v>
       </c>
       <c r="E216" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="F216" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G216" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H216" t="s">
-        <v>336</v>
+        <v>281</v>
       </c>
       <c r="J216" t="s">
         <v>182</v>
       </c>
       <c r="K216" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L216" t="s">
         <v>14</v>
@@ -12162,31 +12153,34 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="B217" t="s">
-        <v>831</v>
+        <v>683</v>
       </c>
       <c r="C217" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="D217" t="s">
         <v>48</v>
       </c>
       <c r="E217" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F217" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G217" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H217" t="s">
-        <v>336</v>
+        <v>205</v>
+      </c>
+      <c r="I217" t="s">
+        <v>134</v>
       </c>
       <c r="J217" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="K217" t="s">
         <v>49</v>
@@ -12203,16 +12197,16 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="B218" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="C218" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="D218" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E218" t="s">
         <v>52</v>
@@ -12221,16 +12215,19 @@
         <v>13</v>
       </c>
       <c r="G218" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="H218" t="s">
-        <v>701</v>
+        <v>281</v>
+      </c>
+      <c r="I218" t="s">
+        <v>76</v>
       </c>
       <c r="J218" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K218" t="s">
-        <v>840</v>
+        <v>49</v>
       </c>
       <c r="L218" t="s">
         <v>14</v>
@@ -12244,34 +12241,31 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="B219" t="s">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="C219" t="s">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="D219" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E219" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F219" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G219" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H219" t="s">
-        <v>205</v>
-      </c>
-      <c r="I219" t="s">
-        <v>76</v>
+        <v>281</v>
       </c>
       <c r="J219" t="s">
-        <v>96</v>
+        <v>345</v>
       </c>
       <c r="K219" t="s">
         <v>49</v>
@@ -12288,16 +12282,16 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>706</v>
+        <v>670</v>
       </c>
       <c r="B220" t="s">
-        <v>710</v>
+        <v>689</v>
       </c>
       <c r="C220" t="s">
-        <v>712</v>
+        <v>690</v>
       </c>
       <c r="D220" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E220" t="s">
         <v>32</v>
@@ -12306,16 +12300,19 @@
         <v>13</v>
       </c>
       <c r="G220" t="s">
-        <v>142</v>
+        <v>450</v>
       </c>
       <c r="H220" t="s">
-        <v>525</v>
+        <v>205</v>
+      </c>
+      <c r="I220" t="s">
+        <v>134</v>
       </c>
       <c r="J220" t="s">
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="K220" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L220" t="s">
         <v>14</v>
@@ -12329,34 +12326,37 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>707</v>
+        <v>671</v>
       </c>
       <c r="B221" t="s">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="C221" t="s">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="D221" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E221" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F221" t="s">
         <v>13</v>
       </c>
       <c r="G221" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="H221" t="s">
-        <v>591</v>
+        <v>281</v>
+      </c>
+      <c r="I221" t="s">
+        <v>76</v>
       </c>
       <c r="J221" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K221" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L221" t="s">
         <v>14</v>
@@ -12370,31 +12370,31 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>708</v>
+        <v>672</v>
       </c>
       <c r="B222" t="s">
         <v>714</v>
       </c>
+      <c r="C222" t="s">
+        <v>715</v>
+      </c>
       <c r="D222" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E222" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F222" t="s">
         <v>13</v>
       </c>
       <c r="G222" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="H222" t="s">
-        <v>328</v>
-      </c>
-      <c r="I222" t="s">
-        <v>76</v>
+        <v>281</v>
       </c>
       <c r="J222" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="K222" t="s">
         <v>49</v>
@@ -12411,34 +12411,34 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>709</v>
+        <v>674</v>
       </c>
       <c r="B223" t="s">
-        <v>717</v>
+        <v>825</v>
       </c>
       <c r="C223" t="s">
-        <v>718</v>
+        <v>690</v>
       </c>
       <c r="D223" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E223" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F223" t="s">
         <v>13</v>
       </c>
       <c r="G223" t="s">
-        <v>142</v>
+        <v>450</v>
       </c>
       <c r="H223" t="s">
-        <v>336</v>
+        <v>205</v>
       </c>
       <c r="I223" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="J223" t="s">
-        <v>335</v>
+        <v>183</v>
       </c>
       <c r="K223" t="s">
         <v>49</v>
@@ -12455,10 +12455,13 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>719</v>
+        <v>675</v>
       </c>
       <c r="B224" t="s">
-        <v>747</v>
+        <v>695</v>
+      </c>
+      <c r="C224" t="s">
+        <v>696</v>
       </c>
       <c r="D224" t="s">
         <v>48</v>
@@ -12467,10 +12470,16 @@
         <v>32</v>
       </c>
       <c r="F224" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G224" t="s">
-        <v>142</v>
+        <v>109</v>
+      </c>
+      <c r="H224" t="s">
+        <v>281</v>
+      </c>
+      <c r="I224" t="s">
+        <v>419</v>
       </c>
       <c r="J224" t="s">
         <v>182</v>
@@ -12490,16 +12499,19 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>720</v>
+        <v>678</v>
       </c>
       <c r="B225" t="s">
-        <v>748</v>
+        <v>699</v>
+      </c>
+      <c r="C225" t="s">
+        <v>703</v>
       </c>
       <c r="D225" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E225" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F225" t="s">
         <v>13</v>
@@ -12507,11 +12519,14 @@
       <c r="G225" t="s">
         <v>142</v>
       </c>
+      <c r="H225" t="s">
+        <v>700</v>
+      </c>
       <c r="J225" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K225" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L225" t="s">
         <v>14</v>
@@ -12525,28 +12540,34 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>721</v>
+        <v>679</v>
       </c>
       <c r="B226" t="s">
-        <v>746</v>
+        <v>701</v>
       </c>
       <c r="C226" t="s">
-        <v>749</v>
+        <v>704</v>
       </c>
       <c r="D226" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E226" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F226" t="s">
         <v>31</v>
       </c>
       <c r="G226" t="s">
-        <v>221</v>
+        <v>144</v>
+      </c>
+      <c r="H226" t="s">
+        <v>205</v>
+      </c>
+      <c r="I226" t="s">
+        <v>76</v>
       </c>
       <c r="J226" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="K226" t="s">
         <v>49</v>
@@ -12563,37 +12584,34 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="B227" t="s">
-        <v>745</v>
+        <v>709</v>
       </c>
       <c r="C227" t="s">
-        <v>750</v>
+        <v>711</v>
       </c>
       <c r="D227" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E227" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F227" t="s">
         <v>13</v>
       </c>
       <c r="G227" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H227" t="s">
-        <v>209</v>
-      </c>
-      <c r="I227" t="s">
-        <v>208</v>
+        <v>525</v>
       </c>
       <c r="J227" t="s">
-        <v>182</v>
+        <v>345</v>
       </c>
       <c r="K227" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L227" t="s">
         <v>14</v>
@@ -12607,16 +12625,16 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>723</v>
+        <v>706</v>
       </c>
       <c r="B228" t="s">
-        <v>744</v>
+        <v>710</v>
       </c>
       <c r="C228" t="s">
-        <v>751</v>
+        <v>712</v>
       </c>
       <c r="D228" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E228" t="s">
         <v>32</v>
@@ -12625,19 +12643,16 @@
         <v>13</v>
       </c>
       <c r="G228" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H228" t="s">
-        <v>281</v>
-      </c>
-      <c r="I228" t="s">
-        <v>55</v>
+        <v>590</v>
       </c>
       <c r="J228" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K228" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L228" t="s">
         <v>14</v>
@@ -12651,13 +12666,13 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B229" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C229" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D229" t="s">
         <v>48</v>
@@ -12666,16 +12681,10 @@
         <v>32</v>
       </c>
       <c r="F229" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G229" t="s">
-        <v>272</v>
-      </c>
-      <c r="H229" t="s">
-        <v>281</v>
-      </c>
-      <c r="I229" t="s">
-        <v>55</v>
+        <v>221</v>
       </c>
       <c r="J229" t="s">
         <v>182</v>
@@ -12695,19 +12704,19 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B230" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C230" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D230" t="s">
         <v>48</v>
       </c>
       <c r="E230" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F230" t="s">
         <v>13</v>
@@ -12716,10 +12725,10 @@
         <v>272</v>
       </c>
       <c r="H230" t="s">
-        <v>281</v>
+        <v>209</v>
       </c>
       <c r="I230" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
       <c r="J230" t="s">
         <v>182</v>
@@ -12739,13 +12748,13 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B231" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C231" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D231" t="s">
         <v>48</v>
@@ -12763,7 +12772,7 @@
         <v>281</v>
       </c>
       <c r="I231" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="J231" t="s">
         <v>182</v>
@@ -12783,34 +12792,34 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B232" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C232" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D232" t="s">
         <v>48</v>
       </c>
       <c r="E232" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F232" t="s">
         <v>13</v>
       </c>
       <c r="G232" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H232" t="s">
-        <v>492</v>
+        <v>281</v>
       </c>
       <c r="I232" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="J232" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="K232" t="s">
         <v>49</v>
@@ -12827,25 +12836,31 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B233" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C233" t="s">
-        <v>553</v>
+        <v>750</v>
       </c>
       <c r="D233" t="s">
         <v>48</v>
       </c>
       <c r="E233" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F233" t="s">
         <v>13</v>
       </c>
       <c r="G233" t="s">
-        <v>142</v>
+        <v>272</v>
+      </c>
+      <c r="H233" t="s">
+        <v>281</v>
+      </c>
+      <c r="I233" t="s">
+        <v>55</v>
       </c>
       <c r="J233" t="s">
         <v>182</v>
@@ -12865,13 +12880,13 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B234" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C234" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="D234" t="s">
         <v>48</v>
@@ -12883,10 +12898,13 @@
         <v>13</v>
       </c>
       <c r="G234" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="H234" t="s">
-        <v>111</v>
+        <v>281</v>
+      </c>
+      <c r="I234" t="s">
+        <v>141</v>
       </c>
       <c r="J234" t="s">
         <v>182</v>
@@ -12906,28 +12924,34 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B235" t="s">
-        <v>829</v>
+        <v>734</v>
+      </c>
+      <c r="C235" t="s">
+        <v>750</v>
       </c>
       <c r="D235" t="s">
         <v>48</v>
       </c>
       <c r="E235" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F235" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G235" t="s">
-        <v>144</v>
+        <v>272</v>
       </c>
       <c r="H235" t="s">
-        <v>754</v>
+        <v>281</v>
+      </c>
+      <c r="I235" t="s">
+        <v>55</v>
       </c>
       <c r="J235" t="s">
-        <v>390</v>
+        <v>182</v>
       </c>
       <c r="K235" t="s">
         <v>49</v>
@@ -12944,34 +12968,34 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B236" t="s">
-        <v>830</v>
+        <v>739</v>
       </c>
       <c r="C236" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="D236" t="s">
         <v>48</v>
       </c>
       <c r="E236" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F236" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G236" t="s">
-        <v>450</v>
+        <v>142</v>
       </c>
       <c r="H236" t="s">
-        <v>131</v>
+        <v>492</v>
       </c>
       <c r="I236" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="J236" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="K236" t="s">
         <v>49</v>
@@ -12988,31 +13012,28 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B237" t="s">
-        <v>828</v>
+        <v>738</v>
+      </c>
+      <c r="C237" t="s">
+        <v>552</v>
       </c>
       <c r="D237" t="s">
         <v>48</v>
       </c>
       <c r="E237" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F237" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G237" t="s">
-        <v>144</v>
-      </c>
-      <c r="H237" t="s">
-        <v>336</v>
-      </c>
-      <c r="I237" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="J237" t="s">
-        <v>390</v>
+        <v>182</v>
       </c>
       <c r="K237" t="s">
         <v>49</v>
@@ -13029,19 +13050,19 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="B238" t="s">
         <v>736</v>
       </c>
       <c r="C238" t="s">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="D238" t="s">
         <v>48</v>
       </c>
       <c r="E238" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F238" t="s">
         <v>13</v>
@@ -13050,10 +13071,7 @@
         <v>142</v>
       </c>
       <c r="H238" t="s">
-        <v>525</v>
-      </c>
-      <c r="I238" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="J238" t="s">
         <v>182</v>
@@ -13073,31 +13091,31 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B239" t="s">
         <v>735</v>
       </c>
       <c r="C239" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D239" t="s">
         <v>48</v>
       </c>
       <c r="E239" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F239" t="s">
         <v>13</v>
       </c>
       <c r="G239" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="H239" t="s">
-        <v>281</v>
+        <v>525</v>
       </c>
       <c r="I239" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="J239" t="s">
         <v>182</v>
@@ -13117,16 +13135,16 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B240" t="s">
-        <v>237</v>
+        <v>841</v>
       </c>
       <c r="C240" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="D240" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E240" t="s">
         <v>32</v>
@@ -13135,16 +13153,19 @@
         <v>13</v>
       </c>
       <c r="G240" t="s">
-        <v>274</v>
+        <v>110</v>
       </c>
       <c r="H240" t="s">
-        <v>336</v>
+        <v>281</v>
+      </c>
+      <c r="I240" t="s">
+        <v>208</v>
       </c>
       <c r="J240" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K240" t="s">
-        <v>49</v>
+        <v>838</v>
       </c>
       <c r="L240" t="s">
         <v>14</v>
@@ -13158,31 +13179,25 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>836</v>
+        <v>718</v>
       </c>
       <c r="B241" t="s">
-        <v>837</v>
-      </c>
-      <c r="C241" t="s">
-        <v>838</v>
+        <v>746</v>
       </c>
       <c r="D241" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E241" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F241" t="s">
         <v>13</v>
       </c>
       <c r="G241" t="s">
-        <v>272</v>
-      </c>
-      <c r="H241" t="s">
-        <v>336</v>
+        <v>142</v>
       </c>
       <c r="J241" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K241" t="s">
         <v>49</v>
@@ -13194,6 +13209,82 @@
         <v>15</v>
       </c>
       <c r="N241" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A242" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B242" t="s">
+        <v>747</v>
+      </c>
+      <c r="D242" t="s">
+        <v>48</v>
+      </c>
+      <c r="E242" t="s">
+        <v>32</v>
+      </c>
+      <c r="F242" t="s">
+        <v>13</v>
+      </c>
+      <c r="G242" t="s">
+        <v>142</v>
+      </c>
+      <c r="J242" t="s">
+        <v>182</v>
+      </c>
+      <c r="K242" t="s">
+        <v>49</v>
+      </c>
+      <c r="L242" t="s">
+        <v>14</v>
+      </c>
+      <c r="M242" t="s">
+        <v>15</v>
+      </c>
+      <c r="N242" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A243" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B243" t="s">
+        <v>843</v>
+      </c>
+      <c r="D243" t="s">
+        <v>48</v>
+      </c>
+      <c r="E243" t="s">
+        <v>32</v>
+      </c>
+      <c r="F243" t="s">
+        <v>13</v>
+      </c>
+      <c r="G243" t="s">
+        <v>142</v>
+      </c>
+      <c r="H243" t="s">
+        <v>281</v>
+      </c>
+      <c r="I243" t="s">
+        <v>55</v>
+      </c>
+      <c r="J243" t="s">
+        <v>182</v>
+      </c>
+      <c r="K243" t="s">
+        <v>49</v>
+      </c>
+      <c r="L243" t="s">
+        <v>14</v>
+      </c>
+      <c r="M243" t="s">
+        <v>15</v>
+      </c>
+      <c r="N243" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93160D6-B925-9648-994B-CC6BA727DAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8AAB10-EE95-6348-B6E0-B98CD02F16AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3762" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3919" uniqueCount="1281">
   <si>
     <t>id</t>
   </si>
@@ -3752,6 +3752,117 @@
   </si>
   <si>
     <t>Signed: Champagnat</t>
+  </si>
+  <si>
+    <t>ILU-0149</t>
+  </si>
+  <si>
+    <t>ILU-0150</t>
+  </si>
+  <si>
+    <t>ILU-0151</t>
+  </si>
+  <si>
+    <t>ILU-0152</t>
+  </si>
+  <si>
+    <t>ILU-0153</t>
+  </si>
+  <si>
+    <t>ILU-0154</t>
+  </si>
+  <si>
+    <t>ILU-0155</t>
+  </si>
+  <si>
+    <t>ILU-0156</t>
+  </si>
+  <si>
+    <t>Marist-Art II</t>
+  </si>
+  <si>
+    <t>Lavatorio</t>
+  </si>
+  <si>
+    <t>Para cartel Cuaresma</t>
+  </si>
+  <si>
+    <t>Foot-washing</t>
+  </si>
+  <si>
+    <t>For Lent poster</t>
+  </si>
+  <si>
+    <t>Tu mano</t>
+  </si>
+  <si>
+    <t>Your hand</t>
+  </si>
+  <si>
+    <t>San Marcelino - XIV</t>
+  </si>
+  <si>
+    <t>Saint Marcellin - XIV</t>
+  </si>
+  <si>
+    <t>Maristas 1817</t>
+  </si>
+  <si>
+    <t>Marists 1817</t>
+  </si>
+  <si>
+    <t>3 Violetas</t>
+  </si>
+  <si>
+    <t>3 violets</t>
+  </si>
+  <si>
+    <t>Arturo_MP_A_Gil</t>
+  </si>
+  <si>
+    <t>Paloma de la paz</t>
+  </si>
+  <si>
+    <t>Peace Dove</t>
+  </si>
+  <si>
+    <t>paz</t>
+  </si>
+  <si>
+    <t>El taburete GVX</t>
+  </si>
+  <si>
+    <t>The stool GVX</t>
+  </si>
+  <si>
+    <t>DIS-0095</t>
+  </si>
+  <si>
+    <t>DIS-0096</t>
+  </si>
+  <si>
+    <t>DIS-0097</t>
+  </si>
+  <si>
+    <t>Vive!</t>
+  </si>
+  <si>
+    <t>Fondo cartel</t>
+  </si>
+  <si>
+    <t>Dios en la ciiudad</t>
+  </si>
+  <si>
+    <t>Live!!</t>
+  </si>
+  <si>
+    <t>For general poster</t>
+  </si>
+  <si>
+    <t>God in the city</t>
+  </si>
+  <si>
+    <t>C_Towers_Arturo_MP</t>
   </si>
 </sst>
 </file>
@@ -4108,17 +4219,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P243"/>
+  <dimension ref="A1:P254"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="31.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
+    <col min="2" max="2" width="27.5" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="4" width="33.1640625" customWidth="1"/>
     <col min="5" max="5" width="32.83203125" customWidth="1"/>
     <col min="6" max="6" width="8.5" customWidth="1"/>
     <col min="7" max="7" width="6.5" customWidth="1"/>
     <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="9" width="12.5" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.5" customWidth="1"/>
     <col min="11" max="11" width="10.1640625" customWidth="1"/>
     <col min="12" max="12" width="11.1640625" customWidth="1"/>
@@ -7543,43 +7654,43 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>254</v>
+        <v>838</v>
       </c>
       <c r="B71" t="s">
-        <v>414</v>
+        <v>840</v>
       </c>
       <c r="C71" t="s">
-        <v>414</v>
+        <v>1233</v>
       </c>
       <c r="D71" t="s">
-        <v>608</v>
+        <v>841</v>
       </c>
       <c r="E71" t="s">
-        <v>901</v>
+        <v>1027</v>
       </c>
       <c r="F71" t="s">
         <v>48</v>
       </c>
       <c r="G71" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H71" t="s">
         <v>13</v>
       </c>
       <c r="I71" t="s">
-        <v>270</v>
+        <v>110</v>
       </c>
       <c r="J71" t="s">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="K71" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="L71" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M71" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N71" t="s">
         <v>14</v>
@@ -9483,16 +9594,22 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>675</v>
+        <v>238</v>
       </c>
       <c r="B111" t="s">
-        <v>696</v>
+        <v>239</v>
       </c>
       <c r="C111" t="s">
-        <v>1129</v>
+        <v>239</v>
+      </c>
+      <c r="D111" t="s">
+        <v>641</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1043</v>
       </c>
       <c r="F111" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G111" t="s">
         <v>32</v>
@@ -9506,11 +9623,14 @@
       <c r="J111" t="s">
         <v>335</v>
       </c>
+      <c r="K111" t="s">
+        <v>134</v>
+      </c>
       <c r="L111" t="s">
         <v>181</v>
       </c>
       <c r="M111" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N111" t="s">
         <v>14</v>
@@ -9524,19 +9644,13 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>502</v>
+        <v>675</v>
       </c>
       <c r="B112" t="s">
-        <v>508</v>
+        <v>696</v>
       </c>
       <c r="C112" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D112" t="s">
-        <v>509</v>
-      </c>
-      <c r="E112" t="s">
-        <v>931</v>
+        <v>1129</v>
       </c>
       <c r="F112" t="s">
         <v>48</v>
@@ -9545,22 +9659,19 @@
         <v>32</v>
       </c>
       <c r="H112" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I112" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J112" t="s">
-        <v>280</v>
-      </c>
-      <c r="K112" t="s">
-        <v>55</v>
+        <v>335</v>
       </c>
       <c r="L112" t="s">
         <v>181</v>
       </c>
       <c r="M112" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N112" t="s">
         <v>14</v>
@@ -9574,40 +9685,40 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>58</v>
+        <v>502</v>
       </c>
       <c r="B113" t="s">
-        <v>65</v>
+        <v>508</v>
       </c>
       <c r="C113" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D113" t="s">
-        <v>66</v>
+        <v>509</v>
       </c>
       <c r="E113" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F113" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G113" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H113" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I113" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J113" t="s">
-        <v>531</v>
+        <v>280</v>
       </c>
       <c r="K113" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L113" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M113" t="s">
         <v>49</v>
@@ -9624,19 +9735,19 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B114" t="s">
-        <v>289</v>
+        <v>65</v>
       </c>
       <c r="C114" t="s">
-        <v>289</v>
+        <v>1131</v>
       </c>
       <c r="D114" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E114" t="s">
-        <v>64</v>
+        <v>932</v>
       </c>
       <c r="F114" t="s">
         <v>79</v>
@@ -9651,13 +9762,13 @@
         <v>142</v>
       </c>
       <c r="J114" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K114" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="L114" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M114" t="s">
         <v>49</v>
@@ -9674,19 +9785,19 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B115" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C115" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D115" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E115" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F115" t="s">
         <v>79</v>
@@ -9701,13 +9812,13 @@
         <v>142</v>
       </c>
       <c r="J115" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K115" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L115" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M115" t="s">
         <v>49</v>
@@ -9724,19 +9835,19 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B116" t="s">
-        <v>69</v>
+        <v>290</v>
       </c>
       <c r="C116" t="s">
-        <v>1132</v>
+        <v>290</v>
       </c>
       <c r="D116" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E116" t="s">
-        <v>933</v>
+        <v>67</v>
       </c>
       <c r="F116" t="s">
         <v>79</v>
@@ -9748,16 +9859,16 @@
         <v>13</v>
       </c>
       <c r="I116" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J116" t="s">
-        <v>478</v>
+        <v>532</v>
       </c>
       <c r="K116" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="L116" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="M116" t="s">
         <v>49</v>
@@ -9774,19 +9885,19 @@
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B117" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C117" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D117" t="s">
-        <v>292</v>
+        <v>70</v>
       </c>
       <c r="E117" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F117" t="s">
         <v>79</v>
@@ -9798,13 +9909,16 @@
         <v>13</v>
       </c>
       <c r="I117" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="J117" t="s">
-        <v>524</v>
+        <v>478</v>
+      </c>
+      <c r="K117" t="s">
+        <v>76</v>
       </c>
       <c r="L117" t="s">
-        <v>181</v>
+        <v>93</v>
       </c>
       <c r="M117" t="s">
         <v>49</v>
@@ -9821,19 +9935,19 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B118" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C118" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D118" t="s">
-        <v>73</v>
+        <v>292</v>
       </c>
       <c r="E118" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F118" t="s">
         <v>79</v>
@@ -9845,16 +9959,13 @@
         <v>13</v>
       </c>
       <c r="I118" t="s">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="J118" t="s">
-        <v>484</v>
-      </c>
-      <c r="K118" t="s">
-        <v>76</v>
+        <v>524</v>
       </c>
       <c r="L118" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M118" t="s">
         <v>49</v>
@@ -9871,19 +9982,19 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="B119" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="C119" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D119" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="E119" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F119" t="s">
         <v>79</v>
@@ -9895,19 +10006,19 @@
         <v>13</v>
       </c>
       <c r="I119" t="s">
-        <v>142</v>
+        <v>221</v>
       </c>
       <c r="J119" t="s">
-        <v>111</v>
+        <v>484</v>
       </c>
       <c r="K119" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L119" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M119" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N119" t="s">
         <v>14</v>
@@ -9921,40 +10032,43 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>466</v>
+        <v>126</v>
       </c>
       <c r="B120" t="s">
-        <v>474</v>
+        <v>132</v>
       </c>
       <c r="C120" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D120" t="s">
-        <v>475</v>
+        <v>133</v>
       </c>
       <c r="E120" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F120" t="s">
         <v>79</v>
       </c>
       <c r="G120" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H120" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I120" t="s">
-        <v>558</v>
+        <v>142</v>
       </c>
       <c r="J120" t="s">
-        <v>335</v>
+        <v>111</v>
+      </c>
+      <c r="K120" t="s">
+        <v>134</v>
       </c>
       <c r="L120" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M120" t="s">
-        <v>50</v>
+        <v>836</v>
       </c>
       <c r="N120" t="s">
         <v>14</v>
@@ -9968,31 +10082,31 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>513</v>
+        <v>466</v>
       </c>
       <c r="B121" t="s">
-        <v>520</v>
+        <v>474</v>
       </c>
       <c r="C121" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D121" t="s">
-        <v>521</v>
+        <v>475</v>
       </c>
       <c r="E121" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F121" t="s">
         <v>79</v>
       </c>
       <c r="G121" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H121" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I121" t="s">
-        <v>142</v>
+        <v>558</v>
       </c>
       <c r="J121" t="s">
         <v>335</v>
@@ -10001,7 +10115,7 @@
         <v>189</v>
       </c>
       <c r="M121" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N121" t="s">
         <v>14</v>
@@ -10015,25 +10129,25 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>243</v>
+        <v>513</v>
       </c>
       <c r="B122" t="s">
-        <v>245</v>
+        <v>520</v>
       </c>
       <c r="C122" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D122" t="s">
-        <v>244</v>
+        <v>521</v>
       </c>
       <c r="E122" t="s">
-        <v>1037</v>
+        <v>938</v>
       </c>
       <c r="F122" t="s">
         <v>79</v>
       </c>
       <c r="G122" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H122" t="s">
         <v>13</v>
@@ -10042,13 +10156,13 @@
         <v>142</v>
       </c>
       <c r="J122" t="s">
-        <v>267</v>
+        <v>335</v>
       </c>
       <c r="L122" t="s">
         <v>189</v>
       </c>
       <c r="M122" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N122" t="s">
         <v>14</v>
@@ -10062,34 +10176,34 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>151</v>
+        <v>243</v>
       </c>
       <c r="B123" t="s">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="C123" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D123" t="s">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="E123" t="s">
-        <v>939</v>
+        <v>1037</v>
       </c>
       <c r="F123" t="s">
         <v>79</v>
       </c>
       <c r="G123" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H123" t="s">
         <v>13</v>
       </c>
       <c r="I123" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J123" t="s">
-        <v>335</v>
+        <v>267</v>
       </c>
       <c r="L123" t="s">
         <v>189</v>
@@ -10109,19 +10223,19 @@
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B124" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C124" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D124" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E124" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="F124" t="s">
         <v>79</v>
@@ -10138,14 +10252,11 @@
       <c r="J124" t="s">
         <v>335</v>
       </c>
-      <c r="K124" t="s">
-        <v>76</v>
-      </c>
       <c r="L124" t="s">
         <v>189</v>
       </c>
       <c r="M124" t="s">
-        <v>836</v>
+        <v>50</v>
       </c>
       <c r="N124" t="s">
         <v>14</v>
@@ -10159,19 +10270,19 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B125" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C125" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D125" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E125" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F125" t="s">
         <v>79</v>
@@ -10188,11 +10299,14 @@
       <c r="J125" t="s">
         <v>335</v>
       </c>
+      <c r="K125" t="s">
+        <v>76</v>
+      </c>
       <c r="L125" t="s">
         <v>189</v>
       </c>
       <c r="M125" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N125" t="s">
         <v>14</v>
@@ -10206,19 +10320,19 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B126" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C126" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D126" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E126" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F126" t="s">
         <v>79</v>
@@ -10235,14 +10349,11 @@
       <c r="J126" t="s">
         <v>335</v>
       </c>
-      <c r="K126" t="s">
-        <v>76</v>
-      </c>
       <c r="L126" t="s">
         <v>189</v>
       </c>
       <c r="M126" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N126" t="s">
         <v>14</v>
@@ -10256,19 +10367,19 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B127" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C127" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D127" t="s">
-        <v>242</v>
+        <v>167</v>
       </c>
       <c r="E127" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F127" t="s">
         <v>79</v>
@@ -10280,7 +10391,7 @@
         <v>13</v>
       </c>
       <c r="I127" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J127" t="s">
         <v>335</v>
@@ -10306,35 +10417,38 @@
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>511</v>
+        <v>155</v>
       </c>
       <c r="B128" t="s">
-        <v>516</v>
+        <v>168</v>
       </c>
       <c r="C128" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D128" t="s">
-        <v>517</v>
+        <v>242</v>
       </c>
       <c r="E128" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F128" t="s">
         <v>79</v>
       </c>
       <c r="G128" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H128" t="s">
         <v>13</v>
       </c>
       <c r="I128" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="J128" t="s">
         <v>335</v>
       </c>
+      <c r="K128" t="s">
+        <v>76</v>
+      </c>
       <c r="L128" t="s">
         <v>189</v>
       </c>
@@ -10353,43 +10467,40 @@
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>338</v>
+        <v>511</v>
       </c>
       <c r="B129" t="s">
-        <v>347</v>
+        <v>516</v>
       </c>
       <c r="C129" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D129" t="s">
-        <v>348</v>
+        <v>517</v>
       </c>
       <c r="E129" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F129" t="s">
         <v>79</v>
       </c>
       <c r="G129" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H129" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I129" t="s">
-        <v>349</v>
+        <v>271</v>
       </c>
       <c r="J129" t="s">
         <v>335</v>
       </c>
-      <c r="K129" t="s">
-        <v>76</v>
-      </c>
       <c r="L129" t="s">
         <v>189</v>
       </c>
       <c r="M129" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="N129" t="s">
         <v>14</v>
@@ -10403,40 +10514,43 @@
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>157</v>
+        <v>338</v>
       </c>
       <c r="B130" t="s">
-        <v>170</v>
+        <v>347</v>
       </c>
       <c r="C130" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D130" t="s">
-        <v>171</v>
+        <v>348</v>
       </c>
       <c r="E130" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F130" t="s">
         <v>79</v>
       </c>
       <c r="G130" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H130" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I130" t="s">
-        <v>271</v>
+        <v>349</v>
       </c>
       <c r="J130" t="s">
         <v>335</v>
       </c>
+      <c r="K130" t="s">
+        <v>76</v>
+      </c>
       <c r="L130" t="s">
         <v>189</v>
       </c>
       <c r="M130" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N130" t="s">
         <v>14</v>
@@ -10450,19 +10564,19 @@
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>339</v>
+        <v>157</v>
       </c>
       <c r="B131" t="s">
-        <v>350</v>
+        <v>170</v>
       </c>
       <c r="C131" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D131" t="s">
-        <v>545</v>
+        <v>171</v>
       </c>
       <c r="E131" t="s">
-        <v>1038</v>
+        <v>946</v>
       </c>
       <c r="F131" t="s">
         <v>79</v>
@@ -10474,10 +10588,10 @@
         <v>13</v>
       </c>
       <c r="I131" t="s">
-        <v>351</v>
+        <v>271</v>
       </c>
       <c r="J131" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="L131" t="s">
         <v>189</v>
@@ -10497,19 +10611,19 @@
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>156</v>
+        <v>339</v>
       </c>
       <c r="B132" t="s">
-        <v>522</v>
+        <v>350</v>
       </c>
       <c r="C132" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D132" t="s">
-        <v>169</v>
+        <v>545</v>
       </c>
       <c r="E132" t="s">
-        <v>947</v>
+        <v>1038</v>
       </c>
       <c r="F132" t="s">
         <v>79</v>
@@ -10521,10 +10635,10 @@
         <v>13</v>
       </c>
       <c r="I132" t="s">
-        <v>271</v>
+        <v>351</v>
       </c>
       <c r="J132" t="s">
-        <v>485</v>
+        <v>352</v>
       </c>
       <c r="L132" t="s">
         <v>189</v>
@@ -10544,25 +10658,25 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>510</v>
+        <v>156</v>
       </c>
       <c r="B133" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C133" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D133" t="s">
-        <v>515</v>
+        <v>169</v>
       </c>
       <c r="E133" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F133" t="s">
         <v>79</v>
       </c>
       <c r="G133" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H133" t="s">
         <v>13</v>
@@ -10571,16 +10685,13 @@
         <v>271</v>
       </c>
       <c r="J133" t="s">
-        <v>335</v>
-      </c>
-      <c r="K133" t="s">
-        <v>76</v>
+        <v>485</v>
       </c>
       <c r="L133" t="s">
         <v>189</v>
       </c>
       <c r="M133" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N133" t="s">
         <v>14</v>
@@ -10594,25 +10705,25 @@
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>223</v>
+        <v>510</v>
       </c>
       <c r="B134" t="s">
-        <v>228</v>
+        <v>514</v>
       </c>
       <c r="C134" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D134" t="s">
-        <v>229</v>
+        <v>515</v>
       </c>
       <c r="E134" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F134" t="s">
         <v>79</v>
       </c>
       <c r="G134" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H134" t="s">
         <v>13</v>
@@ -10623,6 +10734,9 @@
       <c r="J134" t="s">
         <v>335</v>
       </c>
+      <c r="K134" t="s">
+        <v>76</v>
+      </c>
       <c r="L134" t="s">
         <v>189</v>
       </c>
@@ -10641,25 +10755,25 @@
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B135" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C135" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D135" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E135" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F135" t="s">
         <v>79</v>
       </c>
       <c r="G135" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H135" t="s">
         <v>13</v>
@@ -10668,16 +10782,13 @@
         <v>271</v>
       </c>
       <c r="J135" t="s">
-        <v>267</v>
-      </c>
-      <c r="K135" t="s">
-        <v>76</v>
+        <v>335</v>
       </c>
       <c r="L135" t="s">
         <v>189</v>
       </c>
       <c r="M135" t="s">
-        <v>50</v>
+        <v>836</v>
       </c>
       <c r="N135" t="s">
         <v>14</v>
@@ -10691,19 +10802,19 @@
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B136" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C136" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D136" t="s">
-        <v>553</v>
+        <v>237</v>
       </c>
       <c r="E136" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="F136" t="s">
         <v>79</v>
@@ -10721,13 +10832,13 @@
         <v>267</v>
       </c>
       <c r="K136" t="s">
-        <v>232</v>
+        <v>76</v>
       </c>
       <c r="L136" t="s">
         <v>189</v>
       </c>
       <c r="M136" t="s">
-        <v>837</v>
+        <v>50</v>
       </c>
       <c r="N136" t="s">
         <v>14</v>
@@ -10741,25 +10852,25 @@
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B137" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C137" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D137" t="s">
-        <v>830</v>
+        <v>553</v>
       </c>
       <c r="E137" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F137" t="s">
         <v>79</v>
       </c>
       <c r="G137" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H137" t="s">
         <v>13</v>
@@ -10768,7 +10879,10 @@
         <v>271</v>
       </c>
       <c r="J137" t="s">
-        <v>335</v>
+        <v>267</v>
+      </c>
+      <c r="K137" t="s">
+        <v>232</v>
       </c>
       <c r="L137" t="s">
         <v>189</v>
@@ -10788,7 +10902,7 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>832</v>
+        <v>227</v>
       </c>
       <c r="B138" t="s">
         <v>236</v>
@@ -10797,10 +10911,10 @@
         <v>1153</v>
       </c>
       <c r="D138" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E138" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F138" t="s">
         <v>79</v>
@@ -10812,7 +10926,7 @@
         <v>13</v>
       </c>
       <c r="I138" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J138" t="s">
         <v>335</v>
@@ -10821,7 +10935,7 @@
         <v>189</v>
       </c>
       <c r="M138" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N138" t="s">
         <v>14</v>
@@ -10835,25 +10949,25 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>360</v>
+        <v>832</v>
       </c>
       <c r="B139" t="s">
-        <v>784</v>
+        <v>236</v>
       </c>
       <c r="C139" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="D139" t="s">
-        <v>783</v>
+        <v>831</v>
       </c>
       <c r="E139" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F139" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G139" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H139" t="s">
         <v>13</v>
@@ -10864,11 +10978,8 @@
       <c r="J139" t="s">
         <v>335</v>
       </c>
-      <c r="K139" t="s">
-        <v>141</v>
-      </c>
       <c r="L139" t="s">
-        <v>282</v>
+        <v>189</v>
       </c>
       <c r="M139" t="s">
         <v>49</v>
@@ -10885,22 +10996,22 @@
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>224</v>
+        <v>360</v>
       </c>
       <c r="B140" t="s">
-        <v>233</v>
+        <v>784</v>
       </c>
       <c r="C140" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D140" t="s">
-        <v>552</v>
+        <v>783</v>
       </c>
       <c r="E140" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F140" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G140" t="s">
         <v>52</v>
@@ -10909,19 +11020,19 @@
         <v>13</v>
       </c>
       <c r="I140" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J140" t="s">
         <v>335</v>
       </c>
       <c r="K140" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="L140" t="s">
-        <v>189</v>
+        <v>282</v>
       </c>
       <c r="M140" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N140" t="s">
         <v>14</v>
@@ -10935,31 +11046,31 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="B141" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="C141" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D141" t="s">
-        <v>829</v>
+        <v>552</v>
       </c>
       <c r="E141" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F141" t="s">
         <v>79</v>
       </c>
       <c r="G141" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H141" t="s">
         <v>13</v>
       </c>
       <c r="I141" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="J141" t="s">
         <v>335</v>
@@ -10985,19 +11096,19 @@
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>534</v>
+        <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>537</v>
+        <v>173</v>
       </c>
       <c r="C142" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D142" t="s">
-        <v>538</v>
+        <v>829</v>
       </c>
       <c r="E142" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F142" t="s">
         <v>79</v>
@@ -11012,16 +11123,16 @@
         <v>271</v>
       </c>
       <c r="J142" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="K142" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L142" t="s">
         <v>189</v>
       </c>
       <c r="M142" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="N142" t="s">
         <v>14</v>
@@ -11035,25 +11146,25 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>337</v>
+        <v>534</v>
       </c>
       <c r="B143" t="s">
-        <v>345</v>
+        <v>537</v>
       </c>
       <c r="C143" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D143" t="s">
-        <v>346</v>
+        <v>538</v>
       </c>
       <c r="E143" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F143" t="s">
         <v>79</v>
       </c>
       <c r="G143" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H143" t="s">
         <v>13</v>
@@ -11062,7 +11173,10 @@
         <v>271</v>
       </c>
       <c r="J143" t="s">
-        <v>267</v>
+        <v>485</v>
+      </c>
+      <c r="K143" t="s">
+        <v>55</v>
       </c>
       <c r="L143" t="s">
         <v>189</v>
@@ -11082,19 +11196,19 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>536</v>
+        <v>337</v>
       </c>
       <c r="B144" t="s">
-        <v>541</v>
+        <v>345</v>
       </c>
       <c r="C144" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D144" t="s">
-        <v>543</v>
+        <v>346</v>
       </c>
       <c r="E144" t="s">
-        <v>543</v>
+        <v>958</v>
       </c>
       <c r="F144" t="s">
         <v>79</v>
@@ -11109,7 +11223,7 @@
         <v>271</v>
       </c>
       <c r="J144" t="s">
-        <v>335</v>
+        <v>267</v>
       </c>
       <c r="L144" t="s">
         <v>189</v>
@@ -11129,19 +11243,19 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>833</v>
+        <v>536</v>
       </c>
       <c r="B145" t="s">
-        <v>834</v>
+        <v>541</v>
       </c>
       <c r="C145" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D145" t="s">
-        <v>835</v>
+        <v>543</v>
       </c>
       <c r="E145" t="s">
-        <v>959</v>
+        <v>543</v>
       </c>
       <c r="F145" t="s">
         <v>79</v>
@@ -11162,7 +11276,7 @@
         <v>189</v>
       </c>
       <c r="M145" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N145" t="s">
         <v>14</v>
@@ -11176,19 +11290,19 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>158</v>
+        <v>833</v>
       </c>
       <c r="B146" t="s">
-        <v>544</v>
+        <v>834</v>
       </c>
       <c r="C146" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D146" t="s">
-        <v>1039</v>
+        <v>835</v>
       </c>
       <c r="E146" t="s">
-        <v>1040</v>
+        <v>959</v>
       </c>
       <c r="F146" t="s">
         <v>79</v>
@@ -11205,14 +11319,11 @@
       <c r="J146" t="s">
         <v>335</v>
       </c>
-      <c r="K146" t="s">
-        <v>76</v>
-      </c>
       <c r="L146" t="s">
         <v>189</v>
       </c>
       <c r="M146" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N146" t="s">
         <v>14</v>
@@ -11226,25 +11337,25 @@
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>226</v>
+        <v>158</v>
       </c>
       <c r="B147" t="s">
-        <v>234</v>
+        <v>544</v>
       </c>
       <c r="C147" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D147" t="s">
-        <v>235</v>
+        <v>1039</v>
       </c>
       <c r="E147" t="s">
-        <v>960</v>
+        <v>1040</v>
       </c>
       <c r="F147" t="s">
         <v>79</v>
       </c>
       <c r="G147" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H147" t="s">
         <v>13</v>
@@ -11255,8 +11366,11 @@
       <c r="J147" t="s">
         <v>335</v>
       </c>
+      <c r="K147" t="s">
+        <v>76</v>
+      </c>
       <c r="L147" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="M147" t="s">
         <v>837</v>
@@ -11273,40 +11387,40 @@
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B148" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="C148" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D148" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E148" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F148" t="s">
         <v>79</v>
       </c>
       <c r="G148" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H148" t="s">
         <v>13</v>
       </c>
       <c r="I148" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J148" t="s">
         <v>335</v>
       </c>
       <c r="L148" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="M148" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N148" t="s">
         <v>14</v>
@@ -11320,19 +11434,19 @@
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>174</v>
+        <v>240</v>
       </c>
       <c r="B149" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>178</v>
+        <v>1163</v>
       </c>
       <c r="D149" t="s">
-        <v>640</v>
+        <v>241</v>
       </c>
       <c r="E149" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F149" t="s">
         <v>79</v>
@@ -11344,16 +11458,13 @@
         <v>13</v>
       </c>
       <c r="I149" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="J149" t="s">
-        <v>179</v>
-      </c>
-      <c r="K149" t="s">
-        <v>76</v>
+        <v>335</v>
       </c>
       <c r="L149" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="M149" t="s">
         <v>836</v>
@@ -11370,19 +11481,19 @@
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B150" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C150" t="s">
-        <v>1164</v>
+        <v>178</v>
       </c>
       <c r="D150" t="s">
-        <v>798</v>
+        <v>640</v>
       </c>
       <c r="E150" t="s">
-        <v>1041</v>
+        <v>962</v>
       </c>
       <c r="F150" t="s">
         <v>79</v>
@@ -11394,19 +11505,19 @@
         <v>13</v>
       </c>
       <c r="I150" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J150" t="s">
-        <v>486</v>
+        <v>179</v>
       </c>
       <c r="K150" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L150" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="M150" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N150" t="s">
         <v>14</v>
@@ -11420,25 +11531,25 @@
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B151" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C151" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D151" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E151" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F151" t="s">
         <v>79</v>
       </c>
       <c r="G151" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H151" t="s">
         <v>13</v>
@@ -11450,10 +11561,10 @@
         <v>486</v>
       </c>
       <c r="K151" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="L151" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="M151" t="s">
         <v>49</v>
@@ -11470,19 +11581,19 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>238</v>
+        <v>176</v>
       </c>
       <c r="B152" t="s">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="C152" t="s">
-        <v>239</v>
+        <v>1165</v>
       </c>
       <c r="D152" t="s">
-        <v>641</v>
+        <v>797</v>
       </c>
       <c r="E152" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F152" t="s">
         <v>79</v>
@@ -11494,16 +11605,16 @@
         <v>13</v>
       </c>
       <c r="I152" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J152" t="s">
-        <v>335</v>
+        <v>486</v>
       </c>
       <c r="K152" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L152" t="s">
-        <v>181</v>
+        <v>93</v>
       </c>
       <c r="M152" t="s">
         <v>49</v>
@@ -11720,22 +11831,22 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>623</v>
+        <v>254</v>
       </c>
       <c r="B157" t="s">
-        <v>633</v>
+        <v>414</v>
       </c>
       <c r="C157" t="s">
-        <v>1169</v>
+        <v>414</v>
       </c>
       <c r="D157" t="s">
-        <v>634</v>
+        <v>608</v>
       </c>
       <c r="E157" t="s">
-        <v>966</v>
+        <v>901</v>
       </c>
       <c r="F157" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G157" t="s">
         <v>52</v>
@@ -11744,16 +11855,19 @@
         <v>13</v>
       </c>
       <c r="I157" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J157" t="s">
-        <v>203</v>
+        <v>111</v>
+      </c>
+      <c r="K157" t="s">
+        <v>141</v>
       </c>
       <c r="L157" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="M157" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N157" t="s">
         <v>14</v>
@@ -11767,19 +11881,19 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B158" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C158" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D158" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E158" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F158" t="s">
         <v>79</v>
@@ -11814,19 +11928,19 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>295</v>
+        <v>624</v>
       </c>
       <c r="B159" t="s">
-        <v>310</v>
+        <v>635</v>
       </c>
       <c r="C159" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="D159" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E159" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F159" t="s">
         <v>79</v>
@@ -11861,19 +11975,19 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B160" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C160" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D160" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E160" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F160" t="s">
         <v>79</v>
@@ -11908,19 +12022,19 @@
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>621</v>
+        <v>293</v>
       </c>
       <c r="B161" t="s">
-        <v>414</v>
+        <v>308</v>
       </c>
       <c r="C161" t="s">
-        <v>414</v>
+        <v>1172</v>
       </c>
       <c r="D161" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="E161" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F161" t="s">
         <v>79</v>
@@ -11955,40 +12069,37 @@
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B162" t="s">
-        <v>647</v>
+        <v>414</v>
       </c>
       <c r="C162" t="s">
-        <v>1173</v>
+        <v>414</v>
       </c>
       <c r="D162" t="s">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="E162" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F162" t="s">
         <v>79</v>
       </c>
       <c r="G162" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H162" t="s">
         <v>13</v>
       </c>
       <c r="I162" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J162" t="s">
         <v>203</v>
       </c>
-      <c r="K162" t="s">
-        <v>134</v>
-      </c>
       <c r="L162" t="s">
-        <v>344</v>
+        <v>98</v>
       </c>
       <c r="M162" t="s">
         <v>49</v>
@@ -12005,19 +12116,19 @@
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>294</v>
+        <v>628</v>
       </c>
       <c r="B163" t="s">
-        <v>799</v>
+        <v>647</v>
       </c>
       <c r="C163" t="s">
-        <v>1122</v>
+        <v>1173</v>
       </c>
       <c r="D163" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="E163" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F163" t="s">
         <v>79</v>
@@ -12026,16 +12137,19 @@
         <v>32</v>
       </c>
       <c r="H163" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I163" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J163" t="s">
-        <v>280</v>
+        <v>203</v>
+      </c>
+      <c r="K163" t="s">
+        <v>134</v>
       </c>
       <c r="L163" t="s">
-        <v>98</v>
+        <v>344</v>
       </c>
       <c r="M163" t="s">
         <v>49</v>
@@ -12052,19 +12166,19 @@
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B164" t="s">
-        <v>313</v>
+        <v>799</v>
       </c>
       <c r="C164" t="s">
-        <v>1174</v>
+        <v>1122</v>
       </c>
       <c r="D164" t="s">
-        <v>314</v>
+        <v>639</v>
       </c>
       <c r="E164" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F164" t="s">
         <v>79</v>
@@ -12073,19 +12187,19 @@
         <v>32</v>
       </c>
       <c r="H164" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I164" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J164" t="s">
         <v>280</v>
       </c>
       <c r="L164" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M164" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N164" t="s">
         <v>14</v>
@@ -12099,43 +12213,40 @@
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B165" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C165" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D165" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E165" t="s">
-        <v>1045</v>
+        <v>973</v>
       </c>
       <c r="F165" t="s">
         <v>79</v>
       </c>
       <c r="G165" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H165" t="s">
         <v>13</v>
       </c>
       <c r="I165" t="s">
-        <v>319</v>
+        <v>142</v>
       </c>
       <c r="J165" t="s">
-        <v>488</v>
-      </c>
-      <c r="K165" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="L165" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="M165" t="s">
-        <v>837</v>
+        <v>50</v>
       </c>
       <c r="N165" t="s">
         <v>14</v>
@@ -12149,40 +12260,43 @@
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B166" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C166" t="s">
-        <v>321</v>
+        <v>1175</v>
       </c>
       <c r="D166" t="s">
-        <v>801</v>
+        <v>318</v>
       </c>
       <c r="E166" t="s">
-        <v>974</v>
+        <v>1045</v>
       </c>
       <c r="F166" t="s">
         <v>79</v>
       </c>
       <c r="G166" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H166" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I166" t="s">
-        <v>144</v>
+        <v>319</v>
       </c>
       <c r="J166" t="s">
-        <v>489</v>
+        <v>488</v>
+      </c>
+      <c r="K166" t="s">
+        <v>76</v>
       </c>
       <c r="L166" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="M166" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N166" t="s">
         <v>14</v>
@@ -12196,34 +12310,34 @@
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B167" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C167" t="s">
-        <v>1176</v>
+        <v>321</v>
       </c>
       <c r="D167" t="s">
-        <v>609</v>
+        <v>801</v>
       </c>
       <c r="E167" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F167" t="s">
         <v>79</v>
       </c>
       <c r="G167" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H167" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I167" t="s">
-        <v>271</v>
+        <v>144</v>
       </c>
       <c r="J167" t="s">
-        <v>111</v>
+        <v>489</v>
       </c>
       <c r="L167" t="s">
         <v>96</v>
@@ -12243,19 +12357,19 @@
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B168" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C168" t="s">
-        <v>324</v>
+        <v>1176</v>
       </c>
       <c r="D168" t="s">
-        <v>325</v>
+        <v>609</v>
       </c>
       <c r="E168" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F168" t="s">
         <v>79</v>
@@ -12264,22 +12378,19 @@
         <v>52</v>
       </c>
       <c r="H168" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I168" t="s">
-        <v>326</v>
+        <v>271</v>
       </c>
       <c r="J168" t="s">
-        <v>327</v>
-      </c>
-      <c r="K168" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="L168" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="M168" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N168" t="s">
         <v>14</v>
@@ -12293,19 +12404,19 @@
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B169" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C169" t="s">
-        <v>1177</v>
+        <v>324</v>
       </c>
       <c r="D169" t="s">
-        <v>800</v>
+        <v>325</v>
       </c>
       <c r="E169" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F169" t="s">
         <v>79</v>
@@ -12314,22 +12425,22 @@
         <v>52</v>
       </c>
       <c r="H169" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I169" t="s">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="J169" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="K169" t="s">
         <v>76</v>
       </c>
       <c r="L169" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="M169" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N169" t="s">
         <v>14</v>
@@ -12343,19 +12454,19 @@
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B170" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C170" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D170" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E170" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F170" t="s">
         <v>79</v>
@@ -12376,7 +12487,7 @@
         <v>76</v>
       </c>
       <c r="L170" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="M170" t="s">
         <v>49</v>
@@ -12393,19 +12504,19 @@
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B171" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C171" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D171" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E171" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F171" t="s">
         <v>79</v>
@@ -12417,10 +12528,10 @@
         <v>13</v>
       </c>
       <c r="I171" t="s">
-        <v>329</v>
+        <v>271</v>
       </c>
       <c r="J171" t="s">
-        <v>208</v>
+        <v>316</v>
       </c>
       <c r="K171" t="s">
         <v>76</v>
@@ -12443,19 +12554,19 @@
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>596</v>
+        <v>304</v>
       </c>
       <c r="B172" t="s">
-        <v>603</v>
+        <v>328</v>
       </c>
       <c r="C172" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="D172" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="E172" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="F172" t="s">
         <v>79</v>
@@ -12467,10 +12578,10 @@
         <v>13</v>
       </c>
       <c r="I172" t="s">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="J172" t="s">
-        <v>493</v>
+        <v>208</v>
       </c>
       <c r="K172" t="s">
         <v>76</v>
@@ -12493,13 +12604,13 @@
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>305</v>
+        <v>596</v>
       </c>
       <c r="B173" t="s">
-        <v>330</v>
+        <v>603</v>
       </c>
       <c r="C173" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D173" t="s">
         <v>800</v>
@@ -12520,7 +12631,7 @@
         <v>271</v>
       </c>
       <c r="J173" t="s">
-        <v>208</v>
+        <v>493</v>
       </c>
       <c r="K173" t="s">
         <v>76</v>
@@ -12543,19 +12654,19 @@
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B174" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C174" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D174" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E174" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F174" t="s">
         <v>79</v>
@@ -12593,40 +12704,40 @@
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B175" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C175" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D175" t="s">
-        <v>333</v>
+        <v>802</v>
       </c>
       <c r="E175" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F175" t="s">
         <v>79</v>
       </c>
       <c r="G175" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H175" t="s">
         <v>13</v>
       </c>
       <c r="I175" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J175" t="s">
-        <v>488</v>
+        <v>208</v>
       </c>
       <c r="K175" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L175" t="s">
-        <v>334</v>
+        <v>98</v>
       </c>
       <c r="M175" t="s">
         <v>49</v>
@@ -12643,16 +12754,22 @@
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>340</v>
+        <v>720</v>
       </c>
       <c r="B176" t="s">
-        <v>353</v>
+        <v>743</v>
       </c>
       <c r="C176" t="s">
-        <v>1184</v>
+        <v>1224</v>
+      </c>
+      <c r="D176" t="s">
+        <v>748</v>
+      </c>
+      <c r="E176" t="s">
+        <v>1023</v>
       </c>
       <c r="F176" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G176" t="s">
         <v>52</v>
@@ -12661,13 +12778,16 @@
         <v>13</v>
       </c>
       <c r="I176" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J176" t="s">
-        <v>432</v>
+        <v>208</v>
+      </c>
+      <c r="K176" t="s">
+        <v>207</v>
       </c>
       <c r="L176" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M176" t="s">
         <v>49</v>
@@ -12684,40 +12804,40 @@
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>341</v>
+        <v>721</v>
       </c>
       <c r="B177" t="s">
-        <v>805</v>
+        <v>742</v>
       </c>
       <c r="C177" t="s">
-        <v>1185</v>
+        <v>1225</v>
       </c>
       <c r="D177" t="s">
-        <v>354</v>
+        <v>749</v>
       </c>
       <c r="E177" t="s">
-        <v>981</v>
+        <v>1024</v>
       </c>
       <c r="F177" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G177" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H177" t="s">
         <v>13</v>
       </c>
       <c r="I177" t="s">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="J177" t="s">
-        <v>524</v>
+        <v>280</v>
       </c>
       <c r="K177" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L177" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M177" t="s">
         <v>49</v>
@@ -12734,40 +12854,40 @@
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>409</v>
+        <v>722</v>
       </c>
       <c r="B178" t="s">
-        <v>804</v>
+        <v>741</v>
       </c>
       <c r="C178" t="s">
-        <v>1186</v>
+        <v>1226</v>
       </c>
       <c r="D178" t="s">
-        <v>415</v>
+        <v>749</v>
       </c>
       <c r="E178" t="s">
-        <v>982</v>
+        <v>1024</v>
       </c>
       <c r="F178" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G178" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H178" t="s">
         <v>13</v>
       </c>
       <c r="I178" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J178" t="s">
-        <v>533</v>
+        <v>280</v>
       </c>
       <c r="K178" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L178" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M178" t="s">
         <v>49</v>
@@ -12784,40 +12904,40 @@
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>462</v>
+        <v>723</v>
       </c>
       <c r="B179" t="s">
-        <v>468</v>
+        <v>740</v>
       </c>
       <c r="C179" t="s">
-        <v>468</v>
+        <v>1227</v>
       </c>
       <c r="D179" t="s">
-        <v>469</v>
+        <v>749</v>
       </c>
       <c r="E179" t="s">
-        <v>983</v>
+        <v>1024</v>
       </c>
       <c r="F179" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G179" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H179" t="s">
         <v>13</v>
       </c>
       <c r="I179" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J179" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="K179" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L179" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M179" t="s">
         <v>49</v>
@@ -12834,40 +12954,40 @@
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>464</v>
+        <v>724</v>
       </c>
       <c r="B180" t="s">
-        <v>472</v>
+        <v>739</v>
       </c>
       <c r="C180" t="s">
-        <v>472</v>
+        <v>1228</v>
       </c>
       <c r="D180" t="s">
-        <v>469</v>
+        <v>749</v>
       </c>
       <c r="E180" t="s">
-        <v>983</v>
+        <v>1024</v>
       </c>
       <c r="F180" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G180" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H180" t="s">
         <v>13</v>
       </c>
       <c r="I180" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J180" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="K180" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="L180" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M180" t="s">
         <v>49</v>
@@ -12884,13 +13004,19 @@
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>672</v>
+        <v>732</v>
       </c>
       <c r="B181" t="s">
-        <v>692</v>
+        <v>733</v>
       </c>
       <c r="C181" t="s">
-        <v>1187</v>
+        <v>1229</v>
+      </c>
+      <c r="D181" t="s">
+        <v>749</v>
+      </c>
+      <c r="E181" t="s">
+        <v>1024</v>
       </c>
       <c r="F181" t="s">
         <v>48</v>
@@ -12902,16 +13028,16 @@
         <v>13</v>
       </c>
       <c r="I181" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J181" t="s">
-        <v>188</v>
+        <v>280</v>
       </c>
       <c r="K181" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L181" t="s">
-        <v>693</v>
+        <v>181</v>
       </c>
       <c r="M181" t="s">
         <v>49</v>
@@ -12928,19 +13054,19 @@
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="B182" t="s">
-        <v>806</v>
+        <v>332</v>
       </c>
       <c r="C182" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="D182" t="s">
-        <v>807</v>
+        <v>333</v>
       </c>
       <c r="E182" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="F182" t="s">
         <v>79</v>
@@ -12955,10 +13081,13 @@
         <v>142</v>
       </c>
       <c r="J182" t="s">
-        <v>493</v>
+        <v>488</v>
+      </c>
+      <c r="K182" t="s">
+        <v>134</v>
       </c>
       <c r="L182" t="s">
-        <v>184</v>
+        <v>334</v>
       </c>
       <c r="M182" t="s">
         <v>49</v>
@@ -12975,19 +13104,13 @@
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>461</v>
+        <v>340</v>
       </c>
       <c r="B183" t="s">
-        <v>550</v>
+        <v>353</v>
       </c>
       <c r="C183" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D183" t="s">
-        <v>551</v>
-      </c>
-      <c r="E183" t="s">
-        <v>985</v>
+        <v>1184</v>
       </c>
       <c r="F183" t="s">
         <v>79</v>
@@ -13002,13 +13125,10 @@
         <v>142</v>
       </c>
       <c r="J183" t="s">
-        <v>111</v>
-      </c>
-      <c r="K183" t="s">
-        <v>134</v>
+        <v>432</v>
       </c>
       <c r="L183" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M183" t="s">
         <v>49</v>
@@ -13025,19 +13145,19 @@
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>463</v>
+        <v>341</v>
       </c>
       <c r="B184" t="s">
-        <v>470</v>
+        <v>805</v>
       </c>
       <c r="C184" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="D184" t="s">
-        <v>471</v>
+        <v>354</v>
       </c>
       <c r="E184" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="F184" t="s">
         <v>79</v>
@@ -13049,16 +13169,16 @@
         <v>13</v>
       </c>
       <c r="I184" t="s">
-        <v>271</v>
+        <v>110</v>
       </c>
       <c r="J184" t="s">
-        <v>309</v>
+        <v>524</v>
       </c>
       <c r="K184" t="s">
         <v>76</v>
       </c>
       <c r="L184" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="M184" t="s">
         <v>49</v>
@@ -13075,25 +13195,25 @@
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>465</v>
+        <v>409</v>
       </c>
       <c r="B185" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C185" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="D185" t="s">
-        <v>473</v>
+        <v>415</v>
       </c>
       <c r="E185" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="F185" t="s">
         <v>79</v>
       </c>
       <c r="G185" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H185" t="s">
         <v>13</v>
@@ -13102,10 +13222,13 @@
         <v>142</v>
       </c>
       <c r="J185" t="s">
-        <v>280</v>
+        <v>533</v>
+      </c>
+      <c r="K185" t="s">
+        <v>76</v>
       </c>
       <c r="L185" t="s">
-        <v>497</v>
+        <v>96</v>
       </c>
       <c r="M185" t="s">
         <v>49</v>
@@ -13122,19 +13245,19 @@
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B186" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C186" t="s">
-        <v>1191</v>
+        <v>468</v>
       </c>
       <c r="D186" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="E186" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="F186" t="s">
         <v>79</v>
@@ -13149,10 +13272,13 @@
         <v>142</v>
       </c>
       <c r="J186" t="s">
-        <v>111</v>
+        <v>264</v>
+      </c>
+      <c r="K186" t="s">
+        <v>76</v>
       </c>
       <c r="L186" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="M186" t="s">
         <v>49</v>
@@ -13169,40 +13295,40 @@
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>512</v>
+        <v>464</v>
       </c>
       <c r="B187" t="s">
-        <v>809</v>
+        <v>472</v>
       </c>
       <c r="C187" t="s">
-        <v>1192</v>
+        <v>472</v>
       </c>
       <c r="D187" t="s">
-        <v>518</v>
+        <v>469</v>
       </c>
       <c r="E187" t="s">
-        <v>1046</v>
+        <v>983</v>
       </c>
       <c r="F187" t="s">
         <v>79</v>
       </c>
       <c r="G187" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H187" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I187" t="s">
-        <v>519</v>
+        <v>142</v>
       </c>
       <c r="J187" t="s">
-        <v>486</v>
+        <v>264</v>
       </c>
       <c r="K187" t="s">
         <v>76</v>
       </c>
       <c r="L187" t="s">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="M187" t="s">
         <v>49</v>
@@ -13219,40 +13345,34 @@
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>535</v>
+        <v>672</v>
       </c>
       <c r="B188" t="s">
-        <v>542</v>
+        <v>692</v>
       </c>
       <c r="C188" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D188" t="s">
-        <v>539</v>
-      </c>
-      <c r="E188" t="s">
-        <v>989</v>
+        <v>1187</v>
       </c>
       <c r="F188" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G188" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H188" t="s">
         <v>13</v>
       </c>
       <c r="I188" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J188" t="s">
-        <v>540</v>
+        <v>188</v>
       </c>
       <c r="K188" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L188" t="s">
-        <v>189</v>
+        <v>693</v>
       </c>
       <c r="M188" t="s">
         <v>49</v>
@@ -13269,25 +13389,25 @@
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>559</v>
+        <v>410</v>
       </c>
       <c r="B189" t="s">
-        <v>563</v>
+        <v>806</v>
       </c>
       <c r="C189" t="s">
-        <v>563</v>
+        <v>1188</v>
       </c>
       <c r="D189" t="s">
-        <v>564</v>
+        <v>807</v>
       </c>
       <c r="E189" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="F189" t="s">
         <v>79</v>
       </c>
       <c r="G189" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H189" t="s">
         <v>13</v>
@@ -13296,16 +13416,13 @@
         <v>142</v>
       </c>
       <c r="J189" t="s">
-        <v>490</v>
-      </c>
-      <c r="K189" t="s">
-        <v>76</v>
+        <v>493</v>
       </c>
       <c r="L189" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="M189" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N189" t="s">
         <v>14</v>
@@ -13319,19 +13436,19 @@
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>560</v>
+        <v>461</v>
       </c>
       <c r="B190" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="C190" t="s">
-        <v>1194</v>
+        <v>1240</v>
       </c>
       <c r="D190" t="s">
-        <v>599</v>
+        <v>551</v>
       </c>
       <c r="E190" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="F190" t="s">
         <v>79</v>
@@ -13343,13 +13460,16 @@
         <v>13</v>
       </c>
       <c r="I190" t="s">
-        <v>110</v>
+        <v>142</v>
+      </c>
+      <c r="J190" t="s">
+        <v>111</v>
       </c>
       <c r="K190" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="L190" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M190" t="s">
         <v>49</v>
@@ -13366,19 +13486,19 @@
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>561</v>
+        <v>463</v>
       </c>
       <c r="B191" t="s">
-        <v>810</v>
+        <v>470</v>
       </c>
       <c r="C191" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="D191" t="s">
-        <v>566</v>
+        <v>471</v>
       </c>
       <c r="E191" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="F191" t="s">
         <v>79</v>
@@ -13390,19 +13510,19 @@
         <v>13</v>
       </c>
       <c r="I191" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J191" t="s">
-        <v>488</v>
+        <v>309</v>
       </c>
       <c r="K191" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L191" t="s">
-        <v>579</v>
+        <v>96</v>
       </c>
       <c r="M191" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N191" t="s">
         <v>14</v>
@@ -13416,25 +13536,25 @@
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>562</v>
+        <v>465</v>
       </c>
       <c r="B192" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C192" t="s">
-        <v>1239</v>
+        <v>1190</v>
       </c>
       <c r="D192" t="s">
-        <v>567</v>
+        <v>473</v>
       </c>
       <c r="E192" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="F192" t="s">
         <v>79</v>
       </c>
       <c r="G192" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H192" t="s">
         <v>13</v>
@@ -13443,13 +13563,10 @@
         <v>142</v>
       </c>
       <c r="J192" t="s">
-        <v>491</v>
-      </c>
-      <c r="K192" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="L192" t="s">
-        <v>568</v>
+        <v>497</v>
       </c>
       <c r="M192" t="s">
         <v>49</v>
@@ -13466,40 +13583,40 @@
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>571</v>
+        <v>467</v>
       </c>
       <c r="B193" t="s">
-        <v>575</v>
+        <v>476</v>
       </c>
       <c r="C193" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="D193" t="s">
-        <v>386</v>
+        <v>477</v>
       </c>
       <c r="E193" t="s">
-        <v>909</v>
+        <v>988</v>
       </c>
       <c r="F193" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G193" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H193" t="s">
         <v>13</v>
       </c>
       <c r="I193" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J193" t="s">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="L193" t="s">
         <v>181</v>
       </c>
       <c r="M193" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N193" t="s">
         <v>14</v>
@@ -13513,37 +13630,40 @@
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>572</v>
+        <v>512</v>
       </c>
       <c r="B194" t="s">
-        <v>576</v>
+        <v>809</v>
       </c>
       <c r="C194" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="D194" t="s">
-        <v>386</v>
+        <v>518</v>
       </c>
       <c r="E194" t="s">
-        <v>909</v>
+        <v>1046</v>
       </c>
       <c r="F194" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G194" t="s">
         <v>32</v>
       </c>
       <c r="H194" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I194" t="s">
-        <v>271</v>
+        <v>519</v>
       </c>
       <c r="J194" t="s">
-        <v>524</v>
+        <v>486</v>
+      </c>
+      <c r="K194" t="s">
+        <v>76</v>
       </c>
       <c r="L194" t="s">
-        <v>578</v>
+        <v>78</v>
       </c>
       <c r="M194" t="s">
         <v>49</v>
@@ -13560,40 +13680,40 @@
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>582</v>
+        <v>535</v>
       </c>
       <c r="B195" t="s">
-        <v>586</v>
+        <v>542</v>
       </c>
       <c r="C195" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="D195" t="s">
-        <v>587</v>
+        <v>539</v>
       </c>
       <c r="E195" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="F195" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G195" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H195" t="s">
         <v>13</v>
       </c>
       <c r="I195" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J195" t="s">
-        <v>491</v>
+        <v>540</v>
       </c>
       <c r="K195" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="L195" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M195" t="s">
         <v>49</v>
@@ -13610,22 +13730,22 @@
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="B196" t="s">
-        <v>588</v>
+        <v>563</v>
       </c>
       <c r="C196" t="s">
-        <v>1199</v>
+        <v>563</v>
       </c>
       <c r="D196" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="E196" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="F196" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G196" t="s">
         <v>52</v>
@@ -13637,16 +13757,16 @@
         <v>142</v>
       </c>
       <c r="J196" t="s">
-        <v>589</v>
+        <v>490</v>
       </c>
       <c r="K196" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L196" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M196" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N196" t="s">
         <v>14</v>
@@ -13660,40 +13780,37 @@
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="B197" t="s">
-        <v>590</v>
+        <v>565</v>
       </c>
       <c r="C197" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="D197" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E197" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="F197" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G197" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H197" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I197" t="s">
-        <v>591</v>
-      </c>
-      <c r="J197" t="s">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="K197" t="s">
         <v>76</v>
       </c>
       <c r="L197" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="M197" t="s">
         <v>49</v>
@@ -13710,25 +13827,25 @@
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="B198" t="s">
-        <v>592</v>
+        <v>810</v>
       </c>
       <c r="C198" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="D198" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="E198" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="F198" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G198" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H198" t="s">
         <v>13</v>
@@ -13737,13 +13854,13 @@
         <v>142</v>
       </c>
       <c r="J198" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K198" t="s">
         <v>55</v>
       </c>
       <c r="L198" t="s">
-        <v>182</v>
+        <v>579</v>
       </c>
       <c r="M198" t="s">
         <v>837</v>
@@ -13760,40 +13877,40 @@
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>594</v>
+        <v>562</v>
       </c>
       <c r="B199" t="s">
-        <v>600</v>
+        <v>811</v>
       </c>
       <c r="C199" t="s">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="D199" t="s">
-        <v>601</v>
+        <v>567</v>
       </c>
       <c r="E199" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="F199" t="s">
         <v>79</v>
       </c>
       <c r="G199" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H199" t="s">
         <v>13</v>
       </c>
       <c r="I199" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J199" t="s">
-        <v>602</v>
+        <v>491</v>
       </c>
       <c r="K199" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L199" t="s">
-        <v>497</v>
+        <v>568</v>
       </c>
       <c r="M199" t="s">
         <v>49</v>
@@ -13810,40 +13927,37 @@
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="B200" t="s">
-        <v>604</v>
+        <v>575</v>
       </c>
       <c r="C200" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
       <c r="D200" t="s">
-        <v>605</v>
+        <v>386</v>
       </c>
       <c r="E200" t="s">
-        <v>998</v>
+        <v>909</v>
       </c>
       <c r="F200" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G200" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H200" t="s">
         <v>13</v>
       </c>
       <c r="I200" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J200" t="s">
-        <v>491</v>
-      </c>
-      <c r="K200" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="L200" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M200" t="s">
         <v>836</v>
@@ -13860,43 +13974,40 @@
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="B201" t="s">
-        <v>606</v>
+        <v>576</v>
       </c>
       <c r="C201" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="D201" t="s">
-        <v>607</v>
+        <v>386</v>
       </c>
       <c r="E201" t="s">
-        <v>999</v>
+        <v>909</v>
       </c>
       <c r="F201" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G201" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H201" t="s">
         <v>13</v>
       </c>
       <c r="I201" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J201" t="s">
-        <v>280</v>
-      </c>
-      <c r="K201" t="s">
-        <v>76</v>
+        <v>524</v>
       </c>
       <c r="L201" t="s">
-        <v>96</v>
+        <v>578</v>
       </c>
       <c r="M201" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N201" t="s">
         <v>14</v>
@@ -13910,25 +14021,25 @@
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>622</v>
+        <v>582</v>
       </c>
       <c r="B202" t="s">
-        <v>631</v>
+        <v>586</v>
       </c>
       <c r="C202" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
       <c r="D202" t="s">
-        <v>632</v>
+        <v>587</v>
       </c>
       <c r="E202" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="F202" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G202" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H202" t="s">
         <v>13</v>
@@ -13937,13 +14048,16 @@
         <v>142</v>
       </c>
       <c r="J202" t="s">
-        <v>524</v>
+        <v>491</v>
+      </c>
+      <c r="K202" t="s">
+        <v>141</v>
       </c>
       <c r="L202" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M202" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N202" t="s">
         <v>14</v>
@@ -13957,25 +14071,25 @@
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>625</v>
+        <v>583</v>
       </c>
       <c r="B203" t="s">
-        <v>814</v>
+        <v>588</v>
       </c>
       <c r="C203" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
       <c r="D203" t="s">
-        <v>642</v>
+        <v>551</v>
       </c>
       <c r="E203" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="F203" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G203" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H203" t="s">
         <v>13</v>
@@ -13984,13 +14098,13 @@
         <v>142</v>
       </c>
       <c r="J203" t="s">
-        <v>203</v>
+        <v>589</v>
       </c>
       <c r="K203" t="s">
         <v>134</v>
       </c>
       <c r="L203" t="s">
-        <v>334</v>
+        <v>181</v>
       </c>
       <c r="M203" t="s">
         <v>49</v>
@@ -14007,37 +14121,40 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>626</v>
+        <v>584</v>
       </c>
       <c r="B204" t="s">
-        <v>643</v>
+        <v>590</v>
       </c>
       <c r="C204" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="D204" t="s">
-        <v>644</v>
+        <v>598</v>
       </c>
       <c r="E204" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="F204" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G204" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H204" t="s">
         <v>31</v>
       </c>
       <c r="I204" t="s">
-        <v>221</v>
+        <v>591</v>
       </c>
       <c r="J204" t="s">
-        <v>204</v>
+        <v>280</v>
+      </c>
+      <c r="K204" t="s">
+        <v>76</v>
       </c>
       <c r="L204" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M204" t="s">
         <v>49</v>
@@ -14054,40 +14171,43 @@
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>627</v>
+        <v>585</v>
       </c>
       <c r="B205" t="s">
-        <v>645</v>
+        <v>592</v>
       </c>
       <c r="C205" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="D205" t="s">
-        <v>646</v>
+        <v>593</v>
       </c>
       <c r="E205" t="s">
-        <v>1047</v>
+        <v>996</v>
       </c>
       <c r="F205" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G205" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H205" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I205" t="s">
-        <v>449</v>
+        <v>142</v>
       </c>
       <c r="J205" t="s">
-        <v>204</v>
+        <v>487</v>
+      </c>
+      <c r="K205" t="s">
+        <v>55</v>
       </c>
       <c r="L205" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="M205" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N205" t="s">
         <v>14</v>
@@ -14101,19 +14221,19 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>629</v>
+        <v>594</v>
       </c>
       <c r="B206" t="s">
-        <v>649</v>
+        <v>600</v>
       </c>
       <c r="C206" t="s">
-        <v>1238</v>
+        <v>1202</v>
       </c>
       <c r="D206" t="s">
-        <v>815</v>
+        <v>601</v>
       </c>
       <c r="E206" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="F206" t="s">
         <v>79</v>
@@ -14122,19 +14242,22 @@
         <v>32</v>
       </c>
       <c r="H206" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I206" t="s">
-        <v>449</v>
+        <v>271</v>
       </c>
       <c r="J206" t="s">
-        <v>280</v>
+        <v>602</v>
+      </c>
+      <c r="K206" t="s">
+        <v>54</v>
       </c>
       <c r="L206" t="s">
-        <v>189</v>
+        <v>497</v>
       </c>
       <c r="M206" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N206" t="s">
         <v>14</v>
@@ -14148,25 +14271,25 @@
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>610</v>
+        <v>595</v>
       </c>
       <c r="B207" t="s">
-        <v>650</v>
+        <v>604</v>
       </c>
       <c r="C207" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="D207" t="s">
-        <v>651</v>
+        <v>605</v>
       </c>
       <c r="E207" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="F207" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G207" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H207" t="s">
         <v>13</v>
@@ -14174,11 +14297,17 @@
       <c r="I207" t="s">
         <v>142</v>
       </c>
+      <c r="J207" t="s">
+        <v>491</v>
+      </c>
+      <c r="K207" t="s">
+        <v>76</v>
+      </c>
       <c r="L207" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M207" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N207" t="s">
         <v>14</v>
@@ -14192,25 +14321,25 @@
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="B208" t="s">
-        <v>652</v>
+        <v>606</v>
       </c>
       <c r="C208" t="s">
-        <v>652</v>
+        <v>1204</v>
       </c>
       <c r="D208" t="s">
-        <v>816</v>
+        <v>607</v>
       </c>
       <c r="E208" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="F208" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G208" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H208" t="s">
         <v>13</v>
@@ -14218,14 +14347,17 @@
       <c r="I208" t="s">
         <v>142</v>
       </c>
+      <c r="J208" t="s">
+        <v>280</v>
+      </c>
       <c r="K208" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L208" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M208" t="s">
-        <v>837</v>
+        <v>50</v>
       </c>
       <c r="N208" t="s">
         <v>14</v>
@@ -14239,40 +14371,40 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="B209" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
       <c r="C209" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="D209" t="s">
-        <v>446</v>
+        <v>632</v>
       </c>
       <c r="E209" t="s">
-        <v>920</v>
+        <v>1000</v>
       </c>
       <c r="F209" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G209" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H209" t="s">
         <v>13</v>
       </c>
       <c r="I209" t="s">
-        <v>110</v>
-      </c>
-      <c r="K209" t="s">
-        <v>55</v>
+        <v>142</v>
+      </c>
+      <c r="J209" t="s">
+        <v>524</v>
       </c>
       <c r="L209" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="M209" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N209" t="s">
         <v>14</v>
@@ -14286,37 +14418,40 @@
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="B210" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C210" t="s">
-        <v>817</v>
+        <v>1206</v>
       </c>
       <c r="D210" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="E210" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="F210" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G210" t="s">
         <v>32</v>
       </c>
       <c r="H210" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I210" t="s">
-        <v>654</v>
+        <v>142</v>
       </c>
       <c r="J210" t="s">
-        <v>111</v>
+        <v>203</v>
+      </c>
+      <c r="K210" t="s">
+        <v>134</v>
       </c>
       <c r="L210" t="s">
-        <v>389</v>
+        <v>334</v>
       </c>
       <c r="M210" t="s">
         <v>49</v>
@@ -14333,37 +14468,37 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="B211" t="s">
-        <v>818</v>
+        <v>643</v>
       </c>
       <c r="C211" t="s">
-        <v>818</v>
+        <v>1207</v>
       </c>
       <c r="D211" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="E211" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="F211" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G211" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H211" t="s">
         <v>31</v>
       </c>
       <c r="I211" t="s">
-        <v>654</v>
+        <v>221</v>
       </c>
       <c r="J211" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="L211" t="s">
-        <v>389</v>
+        <v>96</v>
       </c>
       <c r="M211" t="s">
         <v>49</v>
@@ -14380,37 +14515,37 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="B212" t="s">
-        <v>819</v>
+        <v>645</v>
       </c>
       <c r="C212" t="s">
-        <v>819</v>
+        <v>1208</v>
       </c>
       <c r="D212" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="E212" t="s">
-        <v>1008</v>
+        <v>1047</v>
       </c>
       <c r="F212" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G212" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H212" t="s">
         <v>31</v>
       </c>
       <c r="I212" t="s">
-        <v>654</v>
+        <v>449</v>
       </c>
       <c r="J212" t="s">
-        <v>327</v>
+        <v>204</v>
       </c>
       <c r="L212" t="s">
-        <v>389</v>
+        <v>96</v>
       </c>
       <c r="M212" t="s">
         <v>49</v>
@@ -14427,22 +14562,22 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="B213" t="s">
-        <v>820</v>
+        <v>649</v>
       </c>
       <c r="C213" t="s">
-        <v>820</v>
+        <v>1238</v>
       </c>
       <c r="D213" t="s">
-        <v>658</v>
+        <v>815</v>
       </c>
       <c r="E213" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="F213" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G213" t="s">
         <v>32</v>
@@ -14451,16 +14586,16 @@
         <v>31</v>
       </c>
       <c r="I213" t="s">
-        <v>654</v>
+        <v>449</v>
       </c>
       <c r="J213" t="s">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="L213" t="s">
-        <v>389</v>
+        <v>189</v>
       </c>
       <c r="M213" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N213" t="s">
         <v>14</v>
@@ -14474,19 +14609,19 @@
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="B214" t="s">
-        <v>822</v>
+        <v>650</v>
       </c>
       <c r="C214" t="s">
-        <v>822</v>
+        <v>1209</v>
       </c>
       <c r="D214" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="E214" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="F214" t="s">
         <v>48</v>
@@ -14495,13 +14630,10 @@
         <v>32</v>
       </c>
       <c r="H214" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I214" t="s">
-        <v>654</v>
-      </c>
-      <c r="J214" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="L214" t="s">
         <v>181</v>
@@ -14521,13 +14653,19 @@
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B215" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C215" t="s">
-        <v>1211</v>
+        <v>652</v>
+      </c>
+      <c r="D215" t="s">
+        <v>816</v>
+      </c>
+      <c r="E215" t="s">
+        <v>1005</v>
       </c>
       <c r="F215" t="s">
         <v>48</v>
@@ -14541,9 +14679,6 @@
       <c r="I215" t="s">
         <v>142</v>
       </c>
-      <c r="J215" t="s">
-        <v>203</v>
-      </c>
       <c r="K215" t="s">
         <v>55</v>
       </c>
@@ -14551,7 +14686,7 @@
         <v>181</v>
       </c>
       <c r="M215" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N215" t="s">
         <v>14</v>
@@ -14565,37 +14700,37 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="B216" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="C216" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="D216" t="s">
-        <v>821</v>
+        <v>446</v>
       </c>
       <c r="E216" t="s">
-        <v>1011</v>
+        <v>920</v>
       </c>
       <c r="F216" t="s">
         <v>48</v>
       </c>
       <c r="G216" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="H216" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I216" t="s">
-        <v>144</v>
-      </c>
-      <c r="J216" t="s">
-        <v>280</v>
+        <v>110</v>
+      </c>
+      <c r="K216" t="s">
+        <v>55</v>
       </c>
       <c r="L216" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M216" t="s">
         <v>49</v>
@@ -14612,40 +14747,37 @@
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>666</v>
+        <v>613</v>
       </c>
       <c r="B217" t="s">
-        <v>682</v>
+        <v>817</v>
       </c>
       <c r="C217" t="s">
-        <v>1213</v>
+        <v>817</v>
       </c>
       <c r="D217" t="s">
-        <v>683</v>
+        <v>655</v>
       </c>
       <c r="E217" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="F217" t="s">
         <v>48</v>
       </c>
       <c r="G217" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H217" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I217" t="s">
-        <v>142</v>
+        <v>654</v>
       </c>
       <c r="J217" t="s">
-        <v>204</v>
-      </c>
-      <c r="K217" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="L217" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M217" t="s">
         <v>49</v>
@@ -14662,40 +14794,37 @@
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>667</v>
+        <v>615</v>
       </c>
       <c r="B218" t="s">
-        <v>684</v>
+        <v>818</v>
       </c>
       <c r="C218" t="s">
-        <v>1214</v>
+        <v>818</v>
       </c>
       <c r="D218" t="s">
-        <v>685</v>
+        <v>656</v>
       </c>
       <c r="E218" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="F218" t="s">
         <v>48</v>
       </c>
       <c r="G218" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H218" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I218" t="s">
-        <v>110</v>
+        <v>654</v>
       </c>
       <c r="J218" t="s">
-        <v>280</v>
-      </c>
-      <c r="K218" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="L218" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M218" t="s">
         <v>49</v>
@@ -14712,19 +14841,19 @@
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>668</v>
+        <v>616</v>
       </c>
       <c r="B219" t="s">
-        <v>686</v>
+        <v>819</v>
       </c>
       <c r="C219" t="s">
-        <v>1215</v>
+        <v>819</v>
       </c>
       <c r="D219" t="s">
-        <v>687</v>
+        <v>657</v>
       </c>
       <c r="E219" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="F219" t="s">
         <v>48</v>
@@ -14733,16 +14862,16 @@
         <v>32</v>
       </c>
       <c r="H219" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I219" t="s">
-        <v>142</v>
+        <v>654</v>
       </c>
       <c r="J219" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="L219" t="s">
-        <v>344</v>
+        <v>389</v>
       </c>
       <c r="M219" t="s">
         <v>49</v>
@@ -14759,19 +14888,19 @@
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>669</v>
+        <v>618</v>
       </c>
       <c r="B220" t="s">
-        <v>688</v>
+        <v>820</v>
       </c>
       <c r="C220" t="s">
-        <v>688</v>
+        <v>820</v>
       </c>
       <c r="D220" t="s">
-        <v>689</v>
+        <v>658</v>
       </c>
       <c r="E220" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="F220" t="s">
         <v>48</v>
@@ -14780,16 +14909,13 @@
         <v>32</v>
       </c>
       <c r="H220" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I220" t="s">
-        <v>449</v>
+        <v>654</v>
       </c>
       <c r="J220" t="s">
-        <v>204</v>
-      </c>
-      <c r="K220" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="L220" t="s">
         <v>389</v>
@@ -14809,37 +14935,34 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>670</v>
+        <v>620</v>
       </c>
       <c r="B221" t="s">
-        <v>690</v>
+        <v>822</v>
       </c>
       <c r="C221" t="s">
-        <v>1216</v>
+        <v>822</v>
       </c>
       <c r="D221" t="s">
-        <v>691</v>
+        <v>659</v>
       </c>
       <c r="E221" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="F221" t="s">
         <v>48</v>
       </c>
       <c r="G221" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H221" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I221" t="s">
-        <v>110</v>
+        <v>654</v>
       </c>
       <c r="J221" t="s">
-        <v>280</v>
-      </c>
-      <c r="K221" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="L221" t="s">
         <v>181</v>
@@ -14859,19 +14982,13 @@
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>671</v>
+        <v>614</v>
       </c>
       <c r="B222" t="s">
-        <v>713</v>
+        <v>660</v>
       </c>
       <c r="C222" t="s">
-        <v>713</v>
-      </c>
-      <c r="D222" t="s">
-        <v>714</v>
-      </c>
-      <c r="E222" t="s">
-        <v>1017</v>
+        <v>1211</v>
       </c>
       <c r="F222" t="s">
         <v>48</v>
@@ -14886,13 +15003,16 @@
         <v>142</v>
       </c>
       <c r="J222" t="s">
-        <v>280</v>
+        <v>203</v>
+      </c>
+      <c r="K222" t="s">
+        <v>55</v>
       </c>
       <c r="L222" t="s">
         <v>181</v>
       </c>
       <c r="M222" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N222" t="s">
         <v>14</v>
@@ -14906,40 +15026,37 @@
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>673</v>
+        <v>619</v>
       </c>
       <c r="B223" t="s">
-        <v>824</v>
+        <v>662</v>
       </c>
       <c r="C223" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="D223" t="s">
-        <v>689</v>
+        <v>821</v>
       </c>
       <c r="E223" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="F223" t="s">
         <v>48</v>
       </c>
       <c r="G223" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H223" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I223" t="s">
-        <v>449</v>
+        <v>144</v>
       </c>
       <c r="J223" t="s">
-        <v>204</v>
-      </c>
-      <c r="K223" t="s">
-        <v>207</v>
+        <v>280</v>
       </c>
       <c r="L223" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M223" t="s">
         <v>49</v>
@@ -14956,37 +15073,37 @@
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="B224" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="C224" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="D224" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="E224" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="F224" t="s">
         <v>48</v>
       </c>
       <c r="G224" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H224" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I224" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="J224" t="s">
-        <v>280</v>
+        <v>204</v>
       </c>
       <c r="K224" t="s">
-        <v>418</v>
+        <v>134</v>
       </c>
       <c r="L224" t="s">
         <v>181</v>
@@ -15006,22 +15123,22 @@
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="B225" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="C225" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="D225" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="E225" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="F225" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G225" t="s">
         <v>52</v>
@@ -15030,16 +15147,19 @@
         <v>13</v>
       </c>
       <c r="I225" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="J225" t="s">
-        <v>699</v>
+        <v>280</v>
+      </c>
+      <c r="K225" t="s">
+        <v>76</v>
       </c>
       <c r="L225" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M225" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N225" t="s">
         <v>14</v>
@@ -15053,40 +15173,37 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="B226" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="C226" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="D226" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="E226" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="F226" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G226" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H226" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I226" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J226" t="s">
-        <v>204</v>
-      </c>
-      <c r="K226" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="L226" t="s">
-        <v>96</v>
+        <v>344</v>
       </c>
       <c r="M226" t="s">
         <v>49</v>
@@ -15103,22 +15220,22 @@
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>704</v>
+        <v>669</v>
       </c>
       <c r="B227" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="C227" t="s">
-        <v>1221</v>
+        <v>688</v>
       </c>
       <c r="D227" t="s">
-        <v>710</v>
+        <v>689</v>
       </c>
       <c r="E227" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="F227" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G227" t="s">
         <v>32</v>
@@ -15127,16 +15244,19 @@
         <v>13</v>
       </c>
       <c r="I227" t="s">
-        <v>142</v>
+        <v>449</v>
       </c>
       <c r="J227" t="s">
-        <v>524</v>
+        <v>204</v>
+      </c>
+      <c r="K227" t="s">
+        <v>134</v>
       </c>
       <c r="L227" t="s">
-        <v>344</v>
+        <v>389</v>
       </c>
       <c r="M227" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N227" t="s">
         <v>14</v>
@@ -15150,40 +15270,43 @@
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>705</v>
+        <v>670</v>
       </c>
       <c r="B228" t="s">
-        <v>709</v>
+        <v>690</v>
       </c>
       <c r="C228" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="D228" t="s">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="E228" t="s">
-        <v>1048</v>
+        <v>1016</v>
       </c>
       <c r="F228" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G228" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H228" t="s">
         <v>13</v>
       </c>
       <c r="I228" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="J228" t="s">
-        <v>589</v>
+        <v>280</v>
+      </c>
+      <c r="K228" t="s">
+        <v>76</v>
       </c>
       <c r="L228" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M228" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N228" t="s">
         <v>14</v>
@@ -15197,19 +15320,19 @@
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>719</v>
+        <v>671</v>
       </c>
       <c r="B229" t="s">
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="C229" t="s">
-        <v>1223</v>
+        <v>713</v>
       </c>
       <c r="D229" t="s">
-        <v>747</v>
+        <v>714</v>
       </c>
       <c r="E229" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="F229" t="s">
         <v>48</v>
@@ -15218,10 +15341,13 @@
         <v>32</v>
       </c>
       <c r="H229" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I229" t="s">
-        <v>220</v>
+        <v>142</v>
+      </c>
+      <c r="J229" t="s">
+        <v>280</v>
       </c>
       <c r="L229" t="s">
         <v>181</v>
@@ -15241,40 +15367,40 @@
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>720</v>
+        <v>673</v>
       </c>
       <c r="B230" t="s">
-        <v>743</v>
+        <v>824</v>
       </c>
       <c r="C230" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
       <c r="D230" t="s">
-        <v>748</v>
+        <v>689</v>
       </c>
       <c r="E230" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="F230" t="s">
         <v>48</v>
       </c>
       <c r="G230" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H230" t="s">
         <v>13</v>
       </c>
       <c r="I230" t="s">
-        <v>271</v>
+        <v>449</v>
       </c>
       <c r="J230" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K230" t="s">
         <v>207</v>
       </c>
       <c r="L230" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M230" t="s">
         <v>49</v>
@@ -15291,19 +15417,19 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>721</v>
+        <v>674</v>
       </c>
       <c r="B231" t="s">
-        <v>742</v>
+        <v>694</v>
       </c>
       <c r="C231" t="s">
-        <v>1225</v>
+        <v>1218</v>
       </c>
       <c r="D231" t="s">
-        <v>749</v>
+        <v>695</v>
       </c>
       <c r="E231" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="F231" t="s">
         <v>48</v>
@@ -15312,16 +15438,16 @@
         <v>32</v>
       </c>
       <c r="H231" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I231" t="s">
-        <v>271</v>
+        <v>109</v>
       </c>
       <c r="J231" t="s">
         <v>280</v>
       </c>
       <c r="K231" t="s">
-        <v>55</v>
+        <v>418</v>
       </c>
       <c r="L231" t="s">
         <v>181</v>
@@ -15341,43 +15467,40 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>722</v>
+        <v>677</v>
       </c>
       <c r="B232" t="s">
-        <v>741</v>
+        <v>698</v>
       </c>
       <c r="C232" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
       <c r="D232" t="s">
-        <v>749</v>
+        <v>702</v>
       </c>
       <c r="E232" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="F232" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G232" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H232" t="s">
         <v>13</v>
       </c>
       <c r="I232" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J232" t="s">
-        <v>280</v>
-      </c>
-      <c r="K232" t="s">
-        <v>55</v>
+        <v>699</v>
       </c>
       <c r="L232" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M232" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N232" t="s">
         <v>14</v>
@@ -15391,40 +15514,40 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>723</v>
+        <v>678</v>
       </c>
       <c r="B233" t="s">
-        <v>740</v>
+        <v>700</v>
       </c>
       <c r="C233" t="s">
-        <v>1227</v>
+        <v>1220</v>
       </c>
       <c r="D233" t="s">
-        <v>749</v>
+        <v>703</v>
       </c>
       <c r="E233" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="F233" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G233" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H233" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I233" t="s">
-        <v>271</v>
+        <v>144</v>
       </c>
       <c r="J233" t="s">
-        <v>280</v>
+        <v>204</v>
       </c>
       <c r="K233" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L233" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M233" t="s">
         <v>49</v>
@@ -15441,22 +15564,22 @@
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>724</v>
+        <v>704</v>
       </c>
       <c r="B234" t="s">
-        <v>739</v>
+        <v>708</v>
       </c>
       <c r="C234" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
       <c r="D234" t="s">
-        <v>749</v>
+        <v>710</v>
       </c>
       <c r="E234" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="F234" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G234" t="s">
         <v>32</v>
@@ -15465,19 +15588,16 @@
         <v>13</v>
       </c>
       <c r="I234" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J234" t="s">
-        <v>280</v>
-      </c>
-      <c r="K234" t="s">
-        <v>141</v>
+        <v>524</v>
       </c>
       <c r="L234" t="s">
-        <v>181</v>
+        <v>344</v>
       </c>
       <c r="M234" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N234" t="s">
         <v>14</v>
@@ -15491,22 +15611,22 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>732</v>
+        <v>705</v>
       </c>
       <c r="B235" t="s">
-        <v>733</v>
+        <v>709</v>
       </c>
       <c r="C235" t="s">
-        <v>1229</v>
+        <v>1222</v>
       </c>
       <c r="D235" t="s">
-        <v>749</v>
+        <v>711</v>
       </c>
       <c r="E235" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
       <c r="F235" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G235" t="s">
         <v>32</v>
@@ -15515,19 +15635,16 @@
         <v>13</v>
       </c>
       <c r="I235" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J235" t="s">
-        <v>280</v>
-      </c>
-      <c r="K235" t="s">
-        <v>55</v>
+        <v>589</v>
       </c>
       <c r="L235" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M235" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N235" t="s">
         <v>14</v>
@@ -15541,40 +15658,34 @@
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="B236" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="C236" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
       <c r="D236" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E236" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="F236" t="s">
         <v>48</v>
       </c>
       <c r="G236" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H236" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I236" t="s">
-        <v>142</v>
-      </c>
-      <c r="J236" t="s">
-        <v>491</v>
-      </c>
-      <c r="K236" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="L236" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M236" t="s">
         <v>49</v>
@@ -15591,19 +15702,19 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B237" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C237" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="D237" t="s">
-        <v>551</v>
+        <v>750</v>
       </c>
       <c r="E237" t="s">
-        <v>985</v>
+        <v>1025</v>
       </c>
       <c r="F237" t="s">
         <v>48</v>
@@ -15617,8 +15728,14 @@
       <c r="I237" t="s">
         <v>142</v>
       </c>
+      <c r="J237" t="s">
+        <v>491</v>
+      </c>
+      <c r="K237" t="s">
+        <v>76</v>
+      </c>
       <c r="L237" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="M237" t="s">
         <v>49</v>
@@ -15635,25 +15752,25 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B238" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C238" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D238" t="s">
-        <v>736</v>
+        <v>551</v>
       </c>
       <c r="E238" t="s">
-        <v>736</v>
+        <v>985</v>
       </c>
       <c r="F238" t="s">
         <v>48</v>
       </c>
       <c r="G238" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H238" t="s">
         <v>13</v>
@@ -15661,9 +15778,6 @@
       <c r="I238" t="s">
         <v>142</v>
       </c>
-      <c r="J238" t="s">
-        <v>111</v>
-      </c>
       <c r="L238" t="s">
         <v>181</v>
       </c>
@@ -15682,25 +15796,25 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B239" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C239" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D239" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="E239" t="s">
-        <v>1026</v>
+        <v>736</v>
       </c>
       <c r="F239" t="s">
         <v>48</v>
       </c>
       <c r="G239" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H239" t="s">
         <v>13</v>
@@ -15709,10 +15823,7 @@
         <v>142</v>
       </c>
       <c r="J239" t="s">
-        <v>524</v>
-      </c>
-      <c r="K239" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="L239" t="s">
         <v>181</v>
@@ -15732,43 +15843,43 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>838</v>
+        <v>731</v>
       </c>
       <c r="B240" t="s">
-        <v>840</v>
+        <v>734</v>
       </c>
       <c r="C240" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="D240" t="s">
-        <v>841</v>
+        <v>751</v>
       </c>
       <c r="E240" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="F240" t="s">
         <v>48</v>
       </c>
       <c r="G240" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H240" t="s">
         <v>13</v>
       </c>
       <c r="I240" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J240" t="s">
-        <v>280</v>
+        <v>524</v>
       </c>
       <c r="K240" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="L240" t="s">
         <v>181</v>
       </c>
       <c r="M240" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N240" t="s">
         <v>14</v>
@@ -15897,6 +16008,499 @@
         <v>15</v>
       </c>
       <c r="P243" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A244" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C244" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F244" t="s">
+        <v>48</v>
+      </c>
+      <c r="G244" t="s">
+        <v>32</v>
+      </c>
+      <c r="H244" t="s">
+        <v>31</v>
+      </c>
+      <c r="I244" t="s">
+        <v>449</v>
+      </c>
+      <c r="J244" t="s">
+        <v>204</v>
+      </c>
+      <c r="K244" t="s">
+        <v>55</v>
+      </c>
+      <c r="L244" t="s">
+        <v>181</v>
+      </c>
+      <c r="M244" t="s">
+        <v>49</v>
+      </c>
+      <c r="N244" t="s">
+        <v>14</v>
+      </c>
+      <c r="O244" t="s">
+        <v>15</v>
+      </c>
+      <c r="P244" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A245" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E245" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F245" t="s">
+        <v>48</v>
+      </c>
+      <c r="G245" t="s">
+        <v>32</v>
+      </c>
+      <c r="H245" t="s">
+        <v>13</v>
+      </c>
+      <c r="I245" t="s">
+        <v>142</v>
+      </c>
+      <c r="J245" t="s">
+        <v>280</v>
+      </c>
+      <c r="K245" t="s">
+        <v>55</v>
+      </c>
+      <c r="L245" t="s">
+        <v>181</v>
+      </c>
+      <c r="M245" t="s">
+        <v>836</v>
+      </c>
+      <c r="N245" t="s">
+        <v>14</v>
+      </c>
+      <c r="O245" t="s">
+        <v>15</v>
+      </c>
+      <c r="P245" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A246" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C246" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D246" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E246" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F246" t="s">
+        <v>48</v>
+      </c>
+      <c r="G246" t="s">
+        <v>32</v>
+      </c>
+      <c r="H246" t="s">
+        <v>13</v>
+      </c>
+      <c r="I246" t="s">
+        <v>142</v>
+      </c>
+      <c r="J246" t="s">
+        <v>589</v>
+      </c>
+      <c r="K246" t="s">
+        <v>55</v>
+      </c>
+      <c r="L246" t="s">
+        <v>181</v>
+      </c>
+      <c r="M246" t="s">
+        <v>49</v>
+      </c>
+      <c r="N246" t="s">
+        <v>14</v>
+      </c>
+      <c r="O246" t="s">
+        <v>15</v>
+      </c>
+      <c r="P246" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A247" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B247" t="s">
+        <v>112</v>
+      </c>
+      <c r="C247" t="s">
+        <v>112</v>
+      </c>
+      <c r="D247" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E247" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F247" t="s">
+        <v>48</v>
+      </c>
+      <c r="G247" t="s">
+        <v>30</v>
+      </c>
+      <c r="H247" t="s">
+        <v>31</v>
+      </c>
+      <c r="I247" t="s">
+        <v>326</v>
+      </c>
+      <c r="J247" t="s">
+        <v>480</v>
+      </c>
+      <c r="L247" t="s">
+        <v>96</v>
+      </c>
+      <c r="M247" t="s">
+        <v>50</v>
+      </c>
+      <c r="N247" t="s">
+        <v>14</v>
+      </c>
+      <c r="O247" t="s">
+        <v>15</v>
+      </c>
+      <c r="P247" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A248" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C248" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F248" t="s">
+        <v>48</v>
+      </c>
+      <c r="G248" t="s">
+        <v>52</v>
+      </c>
+      <c r="H248" t="s">
+        <v>13</v>
+      </c>
+      <c r="I248" t="s">
+        <v>142</v>
+      </c>
+      <c r="J248" t="s">
+        <v>188</v>
+      </c>
+      <c r="L248" t="s">
+        <v>96</v>
+      </c>
+      <c r="M248" t="s">
+        <v>836</v>
+      </c>
+      <c r="N248" t="s">
+        <v>14</v>
+      </c>
+      <c r="O248" t="s">
+        <v>15</v>
+      </c>
+      <c r="P248" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A249" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C249" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F249" t="s">
+        <v>48</v>
+      </c>
+      <c r="G249" t="s">
+        <v>32</v>
+      </c>
+      <c r="H249" t="s">
+        <v>31</v>
+      </c>
+      <c r="I249" t="s">
+        <v>1265</v>
+      </c>
+      <c r="J249" t="s">
+        <v>487</v>
+      </c>
+      <c r="K249" t="s">
+        <v>55</v>
+      </c>
+      <c r="L249" t="s">
+        <v>181</v>
+      </c>
+      <c r="M249" t="s">
+        <v>837</v>
+      </c>
+      <c r="N249" t="s">
+        <v>14</v>
+      </c>
+      <c r="O249" t="s">
+        <v>15</v>
+      </c>
+      <c r="P249" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A250" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C250" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D250" t="s">
+        <v>459</v>
+      </c>
+      <c r="E250" t="s">
+        <v>924</v>
+      </c>
+      <c r="F250" t="s">
+        <v>48</v>
+      </c>
+      <c r="G250" t="s">
+        <v>32</v>
+      </c>
+      <c r="H250" t="s">
+        <v>31</v>
+      </c>
+      <c r="I250" t="s">
+        <v>144</v>
+      </c>
+      <c r="J250" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L250" t="s">
+        <v>96</v>
+      </c>
+      <c r="M250" t="s">
+        <v>49</v>
+      </c>
+      <c r="N250" t="s">
+        <v>14</v>
+      </c>
+      <c r="O250" t="s">
+        <v>15</v>
+      </c>
+      <c r="P250" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A251" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C251" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F251" t="s">
+        <v>48</v>
+      </c>
+      <c r="G251" t="s">
+        <v>32</v>
+      </c>
+      <c r="H251" t="s">
+        <v>31</v>
+      </c>
+      <c r="I251" t="s">
+        <v>144</v>
+      </c>
+      <c r="J251" t="s">
+        <v>267</v>
+      </c>
+      <c r="L251" t="s">
+        <v>96</v>
+      </c>
+      <c r="M251" t="s">
+        <v>49</v>
+      </c>
+      <c r="N251" t="s">
+        <v>14</v>
+      </c>
+      <c r="O251" t="s">
+        <v>15</v>
+      </c>
+      <c r="P251" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A252" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D252" t="s">
+        <v>687</v>
+      </c>
+      <c r="E252" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F252" t="s">
+        <v>79</v>
+      </c>
+      <c r="G252" t="s">
+        <v>32</v>
+      </c>
+      <c r="H252" t="s">
+        <v>31</v>
+      </c>
+      <c r="I252" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J252" t="s">
+        <v>280</v>
+      </c>
+      <c r="L252" t="s">
+        <v>98</v>
+      </c>
+      <c r="M252" t="s">
+        <v>49</v>
+      </c>
+      <c r="N252" t="s">
+        <v>14</v>
+      </c>
+      <c r="O252" t="s">
+        <v>15</v>
+      </c>
+      <c r="P252" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A253" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F253" t="s">
+        <v>79</v>
+      </c>
+      <c r="G253" t="s">
+        <v>32</v>
+      </c>
+      <c r="H253" t="s">
+        <v>13</v>
+      </c>
+      <c r="I253" t="s">
+        <v>142</v>
+      </c>
+      <c r="J253" t="s">
+        <v>432</v>
+      </c>
+      <c r="L253" t="s">
+        <v>98</v>
+      </c>
+      <c r="M253" t="s">
+        <v>49</v>
+      </c>
+      <c r="N253" t="s">
+        <v>14</v>
+      </c>
+      <c r="O253" t="s">
+        <v>15</v>
+      </c>
+      <c r="P253" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A254" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C254" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F254" t="s">
+        <v>79</v>
+      </c>
+      <c r="G254" t="s">
+        <v>32</v>
+      </c>
+      <c r="H254" t="s">
+        <v>31</v>
+      </c>
+      <c r="I254" t="s">
+        <v>144</v>
+      </c>
+      <c r="J254" t="s">
+        <v>280</v>
+      </c>
+      <c r="L254" t="s">
+        <v>96</v>
+      </c>
+      <c r="M254" t="s">
+        <v>49</v>
+      </c>
+      <c r="N254" t="s">
+        <v>14</v>
+      </c>
+      <c r="O254" t="s">
+        <v>15</v>
+      </c>
+      <c r="P254" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DCE0AA-F06C-3D41-920B-91BDF6B63FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415731C3-A80E-5541-A530-CABB2012365A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6652,40 +6652,43 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>113</v>
+        <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>764</v>
+        <v>428</v>
       </c>
       <c r="C44" t="s">
-        <v>1059</v>
+        <v>428</v>
       </c>
       <c r="D44" t="s">
-        <v>765</v>
+        <v>429</v>
       </c>
       <c r="E44" t="s">
-        <v>876</v>
+        <v>918</v>
       </c>
       <c r="F44" t="s">
         <v>48</v>
       </c>
       <c r="G44" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H44" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I44" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J44" t="s">
-        <v>416</v>
+        <v>525</v>
+      </c>
+      <c r="K44" t="s">
+        <v>55</v>
       </c>
       <c r="L44" t="s">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="M44" t="s">
-        <v>50</v>
+        <v>836</v>
       </c>
       <c r="N44" t="s">
         <v>14</v>
@@ -6699,13 +6702,19 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>728</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s">
-        <v>826</v>
+        <v>764</v>
       </c>
       <c r="C45" t="s">
-        <v>1060</v>
+        <v>1059</v>
+      </c>
+      <c r="D45" t="s">
+        <v>765</v>
+      </c>
+      <c r="E45" t="s">
+        <v>876</v>
       </c>
       <c r="F45" t="s">
         <v>48</v>
@@ -6720,13 +6729,13 @@
         <v>144</v>
       </c>
       <c r="J45" t="s">
-        <v>752</v>
+        <v>416</v>
       </c>
       <c r="L45" t="s">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="M45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N45" t="s">
         <v>14</v>
@@ -6740,19 +6749,13 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>114</v>
+        <v>728</v>
       </c>
       <c r="B46" t="s">
-        <v>766</v>
+        <v>826</v>
       </c>
       <c r="C46" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D46" t="s">
-        <v>767</v>
-      </c>
-      <c r="E46" t="s">
-        <v>767</v>
+        <v>1060</v>
       </c>
       <c r="F46" t="s">
         <v>48</v>
@@ -6767,10 +6770,10 @@
         <v>144</v>
       </c>
       <c r="J46" t="s">
-        <v>417</v>
+        <v>752</v>
       </c>
       <c r="L46" t="s">
-        <v>96</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s">
         <v>49</v>
@@ -6787,13 +6790,19 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B47" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C47" t="s">
-        <v>1062</v>
+        <v>1061</v>
+      </c>
+      <c r="D47" t="s">
+        <v>767</v>
+      </c>
+      <c r="E47" t="s">
+        <v>767</v>
       </c>
       <c r="F47" t="s">
         <v>48</v>
@@ -6808,13 +6817,13 @@
         <v>144</v>
       </c>
       <c r="J47" t="s">
-        <v>131</v>
+        <v>417</v>
       </c>
       <c r="L47" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="M47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N47" t="s">
         <v>14</v>
@@ -6828,13 +6837,13 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B48" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C48" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F48" t="s">
         <v>48</v>
@@ -6843,19 +6852,16 @@
         <v>120</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I48" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J48" t="s">
         <v>131</v>
       </c>
-      <c r="K48" t="s">
-        <v>55</v>
-      </c>
       <c r="L48" t="s">
-        <v>555</v>
+        <v>77</v>
       </c>
       <c r="M48" t="s">
         <v>50</v>
@@ -6872,40 +6878,34 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B49" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C49" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D49" t="s">
-        <v>121</v>
-      </c>
-      <c r="E49" t="s">
-        <v>877</v>
+        <v>1063</v>
       </c>
       <c r="F49" t="s">
         <v>48</v>
       </c>
       <c r="G49" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H49" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I49" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="J49" t="s">
-        <v>327</v>
+        <v>131</v>
       </c>
       <c r="K49" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L49" t="s">
-        <v>77</v>
+        <v>555</v>
       </c>
       <c r="M49" t="s">
         <v>50</v>
@@ -6922,40 +6922,43 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B50" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C50" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E50" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F50" t="s">
         <v>48</v>
       </c>
       <c r="G50" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I50" t="s">
-        <v>220</v>
+        <v>91</v>
       </c>
       <c r="J50" t="s">
-        <v>131</v>
+        <v>327</v>
+      </c>
+      <c r="K50" t="s">
+        <v>76</v>
       </c>
       <c r="L50" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="M50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N50" t="s">
         <v>14</v>
@@ -6969,19 +6972,19 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B51" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C51" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E51" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F51" t="s">
         <v>48</v>
@@ -6990,10 +6993,10 @@
         <v>120</v>
       </c>
       <c r="H51" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I51" t="s">
-        <v>144</v>
+        <v>220</v>
       </c>
       <c r="J51" t="s">
         <v>131</v>
@@ -7016,34 +7019,34 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>137</v>
+        <v>772</v>
       </c>
       <c r="C52" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="D52" t="s">
-        <v>774</v>
+        <v>123</v>
       </c>
       <c r="E52" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F52" t="s">
         <v>48</v>
       </c>
       <c r="G52" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H52" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I52" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J52" t="s">
-        <v>455</v>
+        <v>131</v>
       </c>
       <c r="L52" t="s">
         <v>96</v>
@@ -7063,25 +7066,25 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B53" t="s">
-        <v>773</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D53" t="s">
-        <v>138</v>
+        <v>774</v>
       </c>
       <c r="E53" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F53" t="s">
         <v>48</v>
       </c>
       <c r="G53" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
@@ -7090,7 +7093,7 @@
         <v>142</v>
       </c>
       <c r="J53" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="L53" t="s">
         <v>96</v>
@@ -7110,19 +7113,19 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>397</v>
+        <v>136</v>
       </c>
       <c r="B54" t="s">
-        <v>791</v>
+        <v>773</v>
       </c>
       <c r="C54" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D54" t="s">
-        <v>402</v>
+        <v>138</v>
       </c>
       <c r="E54" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F54" t="s">
         <v>48</v>
@@ -7131,22 +7134,19 @@
         <v>120</v>
       </c>
       <c r="H54" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I54" t="s">
         <v>142</v>
       </c>
       <c r="J54" t="s">
-        <v>131</v>
-      </c>
-      <c r="K54" t="s">
-        <v>418</v>
+        <v>481</v>
       </c>
       <c r="L54" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M54" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N54" t="s">
         <v>14</v>
@@ -7160,19 +7160,19 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>617</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s">
-        <v>843</v>
+        <v>791</v>
       </c>
       <c r="C55" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="D55" t="s">
-        <v>661</v>
+        <v>402</v>
       </c>
       <c r="E55" t="s">
-        <v>1029</v>
+        <v>882</v>
       </c>
       <c r="F55" t="s">
         <v>48</v>
@@ -7193,10 +7193,10 @@
         <v>418</v>
       </c>
       <c r="L55" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="M55" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N55" t="s">
         <v>14</v>
@@ -7210,19 +7210,19 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>573</v>
+        <v>617</v>
       </c>
       <c r="B56" t="s">
-        <v>580</v>
+        <v>843</v>
       </c>
       <c r="C56" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D56" t="s">
-        <v>581</v>
+        <v>661</v>
       </c>
       <c r="E56" t="s">
-        <v>883</v>
+        <v>1029</v>
       </c>
       <c r="F56" t="s">
         <v>48</v>
@@ -7231,16 +7231,19 @@
         <v>120</v>
       </c>
       <c r="H56" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I56" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J56" t="s">
         <v>131</v>
       </c>
+      <c r="K56" t="s">
+        <v>418</v>
+      </c>
       <c r="L56" t="s">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="M56" t="s">
         <v>49</v>
@@ -7257,19 +7260,19 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>729</v>
+        <v>573</v>
       </c>
       <c r="B57" t="s">
-        <v>827</v>
+        <v>580</v>
       </c>
       <c r="C57" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D57" t="s">
-        <v>753</v>
+        <v>581</v>
       </c>
       <c r="E57" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F57" t="s">
         <v>48</v>
@@ -7278,19 +7281,16 @@
         <v>120</v>
       </c>
       <c r="H57" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I57" t="s">
-        <v>449</v>
+        <v>110</v>
       </c>
       <c r="J57" t="s">
         <v>131</v>
       </c>
-      <c r="K57" t="s">
-        <v>55</v>
-      </c>
       <c r="L57" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M57" t="s">
         <v>49</v>
@@ -7307,40 +7307,40 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>124</v>
+        <v>729</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>827</v>
       </c>
       <c r="C58" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D58" t="s">
-        <v>128</v>
+        <v>753</v>
       </c>
       <c r="E58" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F58" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G58" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="H58" t="s">
         <v>31</v>
       </c>
       <c r="I58" t="s">
-        <v>219</v>
+        <v>449</v>
       </c>
       <c r="J58" t="s">
         <v>131</v>
       </c>
       <c r="K58" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L58" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="M58" t="s">
         <v>49</v>
@@ -7357,19 +7357,19 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E59" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F59" t="s">
         <v>79</v>
@@ -7390,10 +7390,10 @@
         <v>76</v>
       </c>
       <c r="L59" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="M59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N59" t="s">
         <v>14</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>398</v>
+        <v>125</v>
       </c>
       <c r="B60" t="s">
-        <v>403</v>
+        <v>130</v>
       </c>
       <c r="C60" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D60" t="s">
-        <v>404</v>
+        <v>129</v>
       </c>
       <c r="E60" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F60" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s">
         <v>52</v>
@@ -7431,19 +7431,19 @@
         <v>31</v>
       </c>
       <c r="I60" t="s">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="J60" t="s">
         <v>131</v>
       </c>
       <c r="K60" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="L60" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="M60" t="s">
-        <v>836</v>
+        <v>50</v>
       </c>
       <c r="N60" t="s">
         <v>14</v>
@@ -7457,43 +7457,43 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>439</v>
+        <v>398</v>
       </c>
       <c r="B61" t="s">
-        <v>453</v>
+        <v>403</v>
       </c>
       <c r="C61" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D61" t="s">
-        <v>454</v>
+        <v>404</v>
       </c>
       <c r="E61" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F61" t="s">
         <v>48</v>
       </c>
       <c r="G61" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H61" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I61" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="J61" t="s">
-        <v>527</v>
+        <v>131</v>
       </c>
       <c r="K61" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="L61" t="s">
         <v>181</v>
       </c>
       <c r="M61" t="s">
-        <v>51</v>
+        <v>836</v>
       </c>
       <c r="N61" t="s">
         <v>14</v>
@@ -7507,37 +7507,43 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>706</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s">
-        <v>712</v>
+        <v>453</v>
       </c>
       <c r="C62" t="s">
-        <v>1077</v>
+        <v>1076</v>
+      </c>
+      <c r="D62" t="s">
+        <v>454</v>
+      </c>
+      <c r="E62" t="s">
+        <v>888</v>
       </c>
       <c r="F62" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G62" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
       </c>
       <c r="I62" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J62" t="s">
-        <v>327</v>
+        <v>527</v>
       </c>
       <c r="K62" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L62" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M62" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N62" t="s">
         <v>14</v>
@@ -7551,40 +7557,34 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>1334</v>
+        <v>706</v>
       </c>
       <c r="B63" t="s">
-        <v>1349</v>
+        <v>712</v>
       </c>
       <c r="C63" t="s">
-        <v>1358</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E63" t="s">
-        <v>1316</v>
+        <v>1077</v>
       </c>
       <c r="F63" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H63" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I63" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="J63" t="s">
-        <v>131</v>
+        <v>327</v>
       </c>
       <c r="K63" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L63" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M63" t="s">
         <v>49</v>
@@ -7601,13 +7601,19 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="B64" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="C64" t="s">
-        <v>879</v>
+        <v>1358</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E64" t="s">
+        <v>1316</v>
       </c>
       <c r="F64" t="s">
         <v>48</v>
@@ -7616,10 +7622,10 @@
         <v>120</v>
       </c>
       <c r="H64" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I64" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J64" t="s">
         <v>131</v>
@@ -7631,7 +7637,7 @@
         <v>181</v>
       </c>
       <c r="M64" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N64" t="s">
         <v>14</v>
@@ -7645,13 +7651,13 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>1336</v>
+        <v>1329</v>
       </c>
       <c r="B65" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
       <c r="C65" t="s">
-        <v>1357</v>
+        <v>879</v>
       </c>
       <c r="F65" t="s">
         <v>48</v>
@@ -7675,7 +7681,7 @@
         <v>181</v>
       </c>
       <c r="M65" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N65" t="s">
         <v>14</v>
@@ -7689,13 +7695,13 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="B66" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="C66" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="F66" t="s">
         <v>48</v>
@@ -7704,13 +7710,13 @@
         <v>120</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I66" t="s">
-        <v>449</v>
+        <v>142</v>
       </c>
       <c r="J66" t="s">
-        <v>280</v>
+        <v>131</v>
       </c>
       <c r="K66" t="s">
         <v>55</v>
@@ -7733,28 +7739,28 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B67" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C67" t="s">
-        <v>1350</v>
+        <v>1359</v>
       </c>
       <c r="F67" t="s">
         <v>48</v>
       </c>
       <c r="G67" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H67" t="s">
         <v>31</v>
       </c>
       <c r="I67" t="s">
-        <v>143</v>
+        <v>449</v>
       </c>
       <c r="J67" t="s">
-        <v>487</v>
+        <v>280</v>
       </c>
       <c r="K67" t="s">
         <v>55</v>
@@ -7763,7 +7769,7 @@
         <v>181</v>
       </c>
       <c r="M67" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N67" t="s">
         <v>14</v>
@@ -7777,19 +7783,13 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>139</v>
+        <v>1333</v>
       </c>
       <c r="B68" t="s">
-        <v>775</v>
+        <v>1348</v>
       </c>
       <c r="C68" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D68" t="s">
-        <v>140</v>
-      </c>
-      <c r="E68" t="s">
-        <v>894</v>
+        <v>1350</v>
       </c>
       <c r="F68" t="s">
         <v>48</v>
@@ -7801,19 +7801,19 @@
         <v>31</v>
       </c>
       <c r="I68" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="J68" t="s">
-        <v>188</v>
+        <v>487</v>
       </c>
       <c r="K68" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="L68" t="s">
         <v>181</v>
       </c>
       <c r="M68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N68" t="s">
         <v>14</v>
@@ -7827,13 +7827,13 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="B69" t="s">
-        <v>786</v>
+        <v>775</v>
       </c>
       <c r="C69" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D69" t="s">
         <v>140</v>
@@ -7848,16 +7848,16 @@
         <v>32</v>
       </c>
       <c r="H69" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I69" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="J69" t="s">
-        <v>487</v>
+        <v>188</v>
       </c>
       <c r="K69" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s">
         <v>181</v>
@@ -7877,19 +7877,19 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B70" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C70" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D70" t="s">
-        <v>413</v>
+        <v>140</v>
       </c>
       <c r="E70" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F70" t="s">
         <v>48</v>
@@ -7913,7 +7913,7 @@
         <v>181</v>
       </c>
       <c r="M70" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N70" t="s">
         <v>14</v>
@@ -7927,16 +7927,16 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B71" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C71" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D71" t="s">
-        <v>215</v>
+        <v>413</v>
       </c>
       <c r="E71" t="s">
         <v>895</v>
@@ -7963,7 +7963,7 @@
         <v>181</v>
       </c>
       <c r="M71" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N71" t="s">
         <v>14</v>
@@ -7977,19 +7977,19 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B72" t="s">
-        <v>216</v>
+        <v>788</v>
       </c>
       <c r="C72" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D72" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E72" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F72" t="s">
         <v>48</v>
@@ -8007,10 +8007,10 @@
         <v>487</v>
       </c>
       <c r="K72" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="L72" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M72" t="s">
         <v>49</v>
@@ -8027,19 +8027,19 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>363</v>
+        <v>214</v>
       </c>
       <c r="B73" t="s">
-        <v>785</v>
+        <v>216</v>
       </c>
       <c r="C73" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D73" t="s">
-        <v>384</v>
+        <v>217</v>
       </c>
       <c r="E73" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F73" t="s">
         <v>48</v>
@@ -8051,16 +8051,16 @@
         <v>13</v>
       </c>
       <c r="I73" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="J73" t="s">
         <v>487</v>
       </c>
       <c r="K73" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="L73" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M73" t="s">
         <v>49</v>
@@ -8077,13 +8077,19 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>1249</v>
+        <v>363</v>
       </c>
       <c r="B74" t="s">
-        <v>1263</v>
+        <v>785</v>
       </c>
       <c r="C74" t="s">
-        <v>1264</v>
+        <v>1089</v>
+      </c>
+      <c r="D74" t="s">
+        <v>384</v>
+      </c>
+      <c r="E74" t="s">
+        <v>897</v>
       </c>
       <c r="F74" t="s">
         <v>48</v>
@@ -8092,10 +8098,10 @@
         <v>32</v>
       </c>
       <c r="H74" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I74" t="s">
-        <v>1265</v>
+        <v>220</v>
       </c>
       <c r="J74" t="s">
         <v>487</v>
@@ -8107,7 +8113,7 @@
         <v>181</v>
       </c>
       <c r="M74" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N74" t="s">
         <v>14</v>
@@ -8121,19 +8127,13 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>727</v>
+        <v>1249</v>
       </c>
       <c r="B75" t="s">
-        <v>735</v>
+        <v>1263</v>
       </c>
       <c r="C75" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D75" t="s">
-        <v>736</v>
-      </c>
-      <c r="E75" t="s">
-        <v>736</v>
+        <v>1264</v>
       </c>
       <c r="F75" t="s">
         <v>48</v>
@@ -8142,19 +8142,22 @@
         <v>32</v>
       </c>
       <c r="H75" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I75" t="s">
-        <v>142</v>
+        <v>1265</v>
       </c>
       <c r="J75" t="s">
-        <v>111</v>
+        <v>487</v>
+      </c>
+      <c r="K75" t="s">
+        <v>55</v>
       </c>
       <c r="L75" t="s">
         <v>181</v>
       </c>
       <c r="M75" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N75" t="s">
         <v>14</v>
@@ -8168,13 +8171,19 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>1290</v>
+        <v>727</v>
       </c>
       <c r="B76" t="s">
-        <v>1321</v>
+        <v>735</v>
       </c>
       <c r="C76" t="s">
-        <v>1322</v>
+        <v>1231</v>
+      </c>
+      <c r="D76" t="s">
+        <v>736</v>
+      </c>
+      <c r="E76" t="s">
+        <v>736</v>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -8183,16 +8192,13 @@
         <v>32</v>
       </c>
       <c r="H76" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I76" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J76" t="s">
-        <v>487</v>
-      </c>
-      <c r="K76" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="L76" t="s">
         <v>181</v>
@@ -8212,19 +8218,13 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>585</v>
+        <v>1290</v>
       </c>
       <c r="B77" t="s">
-        <v>592</v>
+        <v>1321</v>
       </c>
       <c r="C77" t="s">
-        <v>1201</v>
-      </c>
-      <c r="D77" t="s">
-        <v>593</v>
-      </c>
-      <c r="E77" t="s">
-        <v>996</v>
+        <v>1322</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -8233,10 +8233,10 @@
         <v>32</v>
       </c>
       <c r="H77" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I77" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J77" t="s">
         <v>487</v>
@@ -8245,10 +8245,10 @@
         <v>55</v>
       </c>
       <c r="L77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M77" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N77" t="s">
         <v>14</v>
@@ -8262,13 +8262,19 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>1292</v>
+        <v>585</v>
       </c>
       <c r="B78" t="s">
-        <v>1325</v>
+        <v>592</v>
       </c>
       <c r="C78" t="s">
-        <v>1326</v>
+        <v>1201</v>
+      </c>
+      <c r="D78" t="s">
+        <v>593</v>
+      </c>
+      <c r="E78" t="s">
+        <v>996</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -8277,10 +8283,10 @@
         <v>32</v>
       </c>
       <c r="H78" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I78" t="s">
-        <v>1279</v>
+        <v>142</v>
       </c>
       <c r="J78" t="s">
         <v>487</v>
@@ -8289,10 +8295,10 @@
         <v>55</v>
       </c>
       <c r="L78" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M78" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N78" t="s">
         <v>14</v>
@@ -8306,40 +8312,34 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>177</v>
+        <v>1292</v>
       </c>
       <c r="B79" t="s">
-        <v>186</v>
+        <v>1325</v>
       </c>
       <c r="C79" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D79" t="s">
-        <v>187</v>
-      </c>
-      <c r="E79" t="s">
-        <v>889</v>
+        <v>1326</v>
       </c>
       <c r="F79" t="s">
         <v>48</v>
       </c>
       <c r="G79" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H79" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I79" t="s">
-        <v>142</v>
+        <v>1279</v>
       </c>
       <c r="J79" t="s">
-        <v>188</v>
+        <v>487</v>
       </c>
       <c r="K79" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="L79" t="s">
-        <v>344</v>
+        <v>181</v>
       </c>
       <c r="M79" t="s">
         <v>49</v>
@@ -8356,13 +8356,19 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>1248</v>
+        <v>177</v>
       </c>
       <c r="B80" t="s">
-        <v>1261</v>
+        <v>186</v>
       </c>
       <c r="C80" t="s">
-        <v>1262</v>
+        <v>1078</v>
+      </c>
+      <c r="D80" t="s">
+        <v>187</v>
+      </c>
+      <c r="E80" t="s">
+        <v>889</v>
       </c>
       <c r="F80" t="s">
         <v>48</v>
@@ -8379,11 +8385,14 @@
       <c r="J80" t="s">
         <v>188</v>
       </c>
+      <c r="K80" t="s">
+        <v>141</v>
+      </c>
       <c r="L80" t="s">
-        <v>96</v>
+        <v>344</v>
       </c>
       <c r="M80" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N80" t="s">
         <v>14</v>
@@ -8397,19 +8406,13 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>362</v>
+        <v>1248</v>
       </c>
       <c r="B81" t="s">
-        <v>382</v>
+        <v>1261</v>
       </c>
       <c r="C81" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D81" t="s">
-        <v>383</v>
-      </c>
-      <c r="E81" t="s">
-        <v>908</v>
+        <v>1262</v>
       </c>
       <c r="F81" t="s">
         <v>48</v>
@@ -8424,13 +8427,13 @@
         <v>142</v>
       </c>
       <c r="J81" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="L81" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M81" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N81" t="s">
         <v>14</v>
@@ -8444,19 +8447,19 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B82" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C82" t="s">
-        <v>1103</v>
+        <v>1241</v>
       </c>
       <c r="D82" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E82" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F82" t="s">
         <v>48</v>
@@ -8468,13 +8471,13 @@
         <v>13</v>
       </c>
       <c r="I82" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J82" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s">
-        <v>389</v>
+        <v>181</v>
       </c>
       <c r="M82" t="s">
         <v>49</v>
@@ -8491,19 +8494,19 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>613</v>
+        <v>436</v>
       </c>
       <c r="B83" t="s">
-        <v>817</v>
+        <v>447</v>
       </c>
       <c r="C83" t="s">
-        <v>817</v>
+        <v>1116</v>
       </c>
       <c r="D83" t="s">
-        <v>655</v>
+        <v>793</v>
       </c>
       <c r="E83" t="s">
-        <v>1006</v>
+        <v>1036</v>
       </c>
       <c r="F83" t="s">
         <v>48</v>
@@ -8512,19 +8515,22 @@
         <v>32</v>
       </c>
       <c r="H83" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I83" t="s">
-        <v>654</v>
+        <v>142</v>
       </c>
       <c r="J83" t="s">
-        <v>111</v>
+        <v>494</v>
+      </c>
+      <c r="K83" t="s">
+        <v>55</v>
       </c>
       <c r="L83" t="s">
-        <v>389</v>
+        <v>181</v>
       </c>
       <c r="M83" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N83" t="s">
         <v>14</v>
@@ -8538,19 +8544,19 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B84" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C84" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D84" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E84" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F84" t="s">
         <v>48</v>
@@ -8585,19 +8591,19 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B85" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C85" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D85" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E85" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F85" t="s">
         <v>48</v>
@@ -8612,7 +8618,7 @@
         <v>654</v>
       </c>
       <c r="J85" t="s">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="L85" t="s">
         <v>389</v>
@@ -8632,19 +8638,19 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B86" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C86" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D86" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E86" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F86" t="s">
         <v>48</v>
@@ -8659,7 +8665,7 @@
         <v>654</v>
       </c>
       <c r="J86" t="s">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="L86" t="s">
         <v>389</v>
@@ -8679,19 +8685,19 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B87" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C87" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D87" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E87" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F87" t="s">
         <v>48</v>
@@ -8709,7 +8715,7 @@
         <v>111</v>
       </c>
       <c r="L87" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M87" t="s">
         <v>49</v>
@@ -8726,43 +8732,40 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>303</v>
+        <v>620</v>
       </c>
       <c r="B88" t="s">
-        <v>324</v>
+        <v>822</v>
       </c>
       <c r="C88" t="s">
-        <v>324</v>
+        <v>822</v>
       </c>
       <c r="D88" t="s">
-        <v>325</v>
+        <v>659</v>
       </c>
       <c r="E88" t="s">
-        <v>976</v>
+        <v>1010</v>
       </c>
       <c r="F88" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G88" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H88" t="s">
         <v>31</v>
       </c>
       <c r="I88" t="s">
-        <v>326</v>
+        <v>654</v>
       </c>
       <c r="J88" t="s">
-        <v>327</v>
-      </c>
-      <c r="K88" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M88" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N88" t="s">
         <v>14</v>
@@ -8776,37 +8779,43 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>1335</v>
+        <v>303</v>
       </c>
       <c r="B89" t="s">
-        <v>1355</v>
+        <v>324</v>
       </c>
       <c r="C89" t="s">
-        <v>1355</v>
+        <v>324</v>
+      </c>
+      <c r="D89" t="s">
+        <v>325</v>
+      </c>
+      <c r="E89" t="s">
+        <v>976</v>
       </c>
       <c r="F89" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s">
         <v>52</v>
       </c>
       <c r="H89" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>142</v>
+        <v>326</v>
       </c>
       <c r="J89" t="s">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="K89" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L89" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M89" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N89" t="s">
         <v>14</v>
@@ -8820,25 +8829,19 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>671</v>
+        <v>1335</v>
       </c>
       <c r="B90" t="s">
-        <v>713</v>
+        <v>1355</v>
       </c>
       <c r="C90" t="s">
-        <v>713</v>
-      </c>
-      <c r="D90" t="s">
-        <v>714</v>
-      </c>
-      <c r="E90" t="s">
-        <v>1017</v>
+        <v>1355</v>
       </c>
       <c r="F90" t="s">
         <v>48</v>
       </c>
       <c r="G90" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H90" t="s">
         <v>13</v>
@@ -8847,7 +8850,10 @@
         <v>142</v>
       </c>
       <c r="J90" t="s">
-        <v>280</v>
+        <v>111</v>
+      </c>
+      <c r="K90" t="s">
+        <v>55</v>
       </c>
       <c r="L90" t="s">
         <v>181</v>
@@ -8867,40 +8873,37 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="B91" t="s">
-        <v>195</v>
+        <v>321</v>
       </c>
       <c r="C91" t="s">
-        <v>1079</v>
+        <v>321</v>
       </c>
       <c r="D91" t="s">
-        <v>196</v>
+        <v>801</v>
       </c>
       <c r="E91" t="s">
-        <v>1030</v>
+        <v>974</v>
       </c>
       <c r="F91" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G91" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H91" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I91" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J91" t="s">
-        <v>197</v>
-      </c>
-      <c r="K91" t="s">
-        <v>76</v>
+        <v>489</v>
       </c>
       <c r="L91" t="s">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="M91" t="s">
         <v>49</v>
@@ -8917,25 +8920,25 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B92" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C92" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D92" t="s">
-        <v>411</v>
+        <v>263</v>
       </c>
       <c r="E92" t="s">
-        <v>1031</v>
+        <v>898</v>
       </c>
       <c r="F92" t="s">
         <v>48</v>
       </c>
       <c r="G92" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H92" t="s">
         <v>13</v>
@@ -8944,10 +8947,10 @@
         <v>142</v>
       </c>
       <c r="J92" t="s">
-        <v>335</v>
+        <v>264</v>
       </c>
       <c r="K92" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="L92" t="s">
         <v>181</v>
@@ -8967,25 +8970,25 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>248</v>
+        <v>174</v>
       </c>
       <c r="B93" t="s">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="C93" t="s">
-        <v>1091</v>
+        <v>178</v>
       </c>
       <c r="D93" t="s">
-        <v>412</v>
+        <v>640</v>
       </c>
       <c r="E93" t="s">
-        <v>1032</v>
+        <v>962</v>
       </c>
       <c r="F93" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G93" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H93" t="s">
         <v>13</v>
@@ -8994,16 +8997,16 @@
         <v>142</v>
       </c>
       <c r="J93" t="s">
-        <v>335</v>
+        <v>179</v>
       </c>
       <c r="K93" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="L93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M93" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N93" t="s">
         <v>14</v>
@@ -9017,43 +9020,43 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>252</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>776</v>
+        <v>183</v>
       </c>
       <c r="C94" t="s">
-        <v>1094</v>
+        <v>1164</v>
       </c>
       <c r="D94" t="s">
-        <v>265</v>
+        <v>798</v>
       </c>
       <c r="E94" t="s">
-        <v>899</v>
+        <v>1041</v>
       </c>
       <c r="F94" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G94" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H94" t="s">
         <v>13</v>
       </c>
       <c r="I94" t="s">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="J94" t="s">
-        <v>280</v>
+        <v>486</v>
       </c>
       <c r="K94" t="s">
         <v>134</v>
       </c>
       <c r="L94" t="s">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="M94" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N94" t="s">
         <v>14</v>
@@ -9067,22 +9070,22 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
       <c r="B95" t="s">
-        <v>777</v>
+        <v>185</v>
       </c>
       <c r="C95" t="s">
-        <v>1095</v>
+        <v>1165</v>
       </c>
       <c r="D95" t="s">
-        <v>266</v>
+        <v>797</v>
       </c>
       <c r="E95" t="s">
-        <v>900</v>
+        <v>1042</v>
       </c>
       <c r="F95" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G95" t="s">
         <v>32</v>
@@ -9091,19 +9094,19 @@
         <v>13</v>
       </c>
       <c r="I95" t="s">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="J95" t="s">
-        <v>280</v>
+        <v>486</v>
       </c>
       <c r="K95" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L95" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M95" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N95" t="s">
         <v>14</v>
@@ -9117,43 +9120,43 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>838</v>
+        <v>355</v>
       </c>
       <c r="B96" t="s">
-        <v>840</v>
+        <v>370</v>
       </c>
       <c r="C96" t="s">
-        <v>1233</v>
+        <v>370</v>
       </c>
       <c r="D96" t="s">
-        <v>841</v>
+        <v>380</v>
       </c>
       <c r="E96" t="s">
-        <v>1027</v>
+        <v>905</v>
       </c>
       <c r="F96" t="s">
         <v>48</v>
       </c>
       <c r="G96" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H96" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I96" t="s">
-        <v>110</v>
+        <v>371</v>
       </c>
       <c r="J96" t="s">
-        <v>280</v>
+        <v>432</v>
       </c>
       <c r="K96" t="s">
         <v>207</v>
       </c>
       <c r="L96" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="M96" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N96" t="s">
         <v>14</v>
@@ -9167,19 +9170,19 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="B97" t="s">
-        <v>279</v>
+        <v>353</v>
       </c>
       <c r="C97" t="s">
-        <v>1097</v>
+        <v>1184</v>
       </c>
       <c r="F97" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G97" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H97" t="s">
         <v>13</v>
@@ -9188,7 +9191,7 @@
         <v>142</v>
       </c>
       <c r="J97" t="s">
-        <v>280</v>
+        <v>432</v>
       </c>
       <c r="L97" t="s">
         <v>96</v>
@@ -9208,40 +9211,40 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>257</v>
+        <v>409</v>
       </c>
       <c r="B98" t="s">
-        <v>778</v>
+        <v>804</v>
       </c>
       <c r="C98" t="s">
-        <v>1098</v>
+        <v>1186</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>415</v>
       </c>
       <c r="E98" t="s">
-        <v>902</v>
+        <v>982</v>
       </c>
       <c r="F98" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G98" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H98" t="s">
         <v>13</v>
       </c>
       <c r="I98" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J98" t="s">
-        <v>281</v>
+        <v>533</v>
       </c>
       <c r="K98" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L98" t="s">
-        <v>389</v>
+        <v>96</v>
       </c>
       <c r="M98" t="s">
         <v>49</v>
@@ -9258,34 +9261,34 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>359</v>
+        <v>462</v>
       </c>
       <c r="B99" t="s">
-        <v>378</v>
+        <v>468</v>
       </c>
       <c r="C99" t="s">
-        <v>1101</v>
+        <v>468</v>
       </c>
       <c r="D99" t="s">
-        <v>782</v>
+        <v>469</v>
       </c>
       <c r="E99" t="s">
-        <v>907</v>
+        <v>983</v>
       </c>
       <c r="F99" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G99" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H99" t="s">
         <v>13</v>
       </c>
       <c r="I99" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J99" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K99" t="s">
         <v>76</v>
@@ -9308,37 +9311,40 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>361</v>
+        <v>464</v>
       </c>
       <c r="B100" t="s">
-        <v>379</v>
+        <v>472</v>
       </c>
       <c r="C100" t="s">
-        <v>1102</v>
+        <v>472</v>
       </c>
       <c r="D100" t="s">
-        <v>380</v>
+        <v>469</v>
       </c>
       <c r="E100" t="s">
-        <v>905</v>
+        <v>983</v>
       </c>
       <c r="F100" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G100" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H100" t="s">
         <v>13</v>
       </c>
       <c r="I100" t="s">
-        <v>381</v>
+        <v>142</v>
       </c>
       <c r="J100" t="s">
-        <v>490</v>
+        <v>264</v>
+      </c>
+      <c r="K100" t="s">
+        <v>76</v>
       </c>
       <c r="L100" t="s">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="M100" t="s">
         <v>49</v>
@@ -9355,25 +9361,19 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>365</v>
+        <v>672</v>
       </c>
       <c r="B101" t="s">
-        <v>387</v>
+        <v>692</v>
       </c>
       <c r="C101" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D101" t="s">
-        <v>388</v>
-      </c>
-      <c r="E101" t="s">
-        <v>910</v>
+        <v>1187</v>
       </c>
       <c r="F101" t="s">
         <v>48</v>
       </c>
       <c r="G101" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H101" t="s">
         <v>13</v>
@@ -9382,13 +9382,16 @@
         <v>142</v>
       </c>
       <c r="J101" t="s">
-        <v>523</v>
+        <v>188</v>
+      </c>
+      <c r="K101" t="s">
+        <v>76</v>
       </c>
       <c r="L101" t="s">
-        <v>389</v>
+        <v>693</v>
       </c>
       <c r="M101" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N101" t="s">
         <v>14</v>
@@ -9402,25 +9405,25 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>366</v>
+        <v>559</v>
       </c>
       <c r="B102" t="s">
-        <v>390</v>
+        <v>563</v>
       </c>
       <c r="C102" t="s">
-        <v>1105</v>
+        <v>563</v>
       </c>
       <c r="D102" t="s">
-        <v>391</v>
+        <v>564</v>
       </c>
       <c r="E102" t="s">
-        <v>911</v>
+        <v>990</v>
       </c>
       <c r="F102" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G102" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H102" t="s">
         <v>13</v>
@@ -9429,16 +9432,16 @@
         <v>142</v>
       </c>
       <c r="J102" t="s">
-        <v>203</v>
+        <v>490</v>
       </c>
       <c r="K102" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L102" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M102" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N102" t="s">
         <v>14</v>
@@ -9452,22 +9455,22 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>367</v>
+        <v>467</v>
       </c>
       <c r="B103" t="s">
-        <v>392</v>
+        <v>476</v>
       </c>
       <c r="C103" t="s">
-        <v>1106</v>
+        <v>1191</v>
       </c>
       <c r="D103" t="s">
-        <v>393</v>
+        <v>477</v>
       </c>
       <c r="E103" t="s">
-        <v>912</v>
+        <v>988</v>
       </c>
       <c r="F103" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G103" t="s">
         <v>52</v>
@@ -9476,13 +9479,13 @@
         <v>13</v>
       </c>
       <c r="I103" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J103" t="s">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="L103" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M103" t="s">
         <v>49</v>
@@ -9499,34 +9502,40 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>368</v>
+        <v>512</v>
       </c>
       <c r="B104" t="s">
-        <v>789</v>
+        <v>809</v>
       </c>
       <c r="C104" t="s">
-        <v>1107</v>
+        <v>1192</v>
+      </c>
+      <c r="D104" t="s">
+        <v>518</v>
+      </c>
+      <c r="E104" t="s">
+        <v>1046</v>
       </c>
       <c r="F104" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G104" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="H104" t="s">
         <v>31</v>
       </c>
       <c r="I104" t="s">
-        <v>144</v>
+        <v>519</v>
       </c>
       <c r="J104" t="s">
-        <v>280</v>
+        <v>486</v>
       </c>
       <c r="K104" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L104" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="M104" t="s">
         <v>49</v>
@@ -9543,19 +9552,19 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>369</v>
+        <v>422</v>
       </c>
       <c r="B105" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="C105" t="s">
-        <v>1108</v>
+        <v>430</v>
       </c>
       <c r="D105" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="E105" t="s">
-        <v>1035</v>
+        <v>919</v>
       </c>
       <c r="F105" t="s">
         <v>48</v>
@@ -9570,7 +9579,10 @@
         <v>142</v>
       </c>
       <c r="J105" t="s">
-        <v>280</v>
+        <v>432</v>
+      </c>
+      <c r="K105" t="s">
+        <v>55</v>
       </c>
       <c r="L105" t="s">
         <v>198</v>
@@ -9590,19 +9602,19 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>396</v>
+        <v>361</v>
       </c>
       <c r="B106" t="s">
-        <v>790</v>
+        <v>379</v>
       </c>
       <c r="C106" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="D106" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="E106" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="F106" t="s">
         <v>48</v>
@@ -9614,13 +9626,13 @@
         <v>13</v>
       </c>
       <c r="I106" t="s">
-        <v>142</v>
+        <v>381</v>
       </c>
       <c r="J106" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="L106" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="M106" t="s">
         <v>49</v>
@@ -9637,25 +9649,25 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>399</v>
+        <v>671</v>
       </c>
       <c r="B107" t="s">
-        <v>405</v>
+        <v>713</v>
       </c>
       <c r="C107" t="s">
-        <v>1110</v>
+        <v>713</v>
       </c>
       <c r="D107" t="s">
-        <v>406</v>
+        <v>714</v>
       </c>
       <c r="E107" t="s">
-        <v>914</v>
+        <v>1017</v>
       </c>
       <c r="F107" t="s">
         <v>48</v>
       </c>
       <c r="G107" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H107" t="s">
         <v>13</v>
@@ -9664,13 +9676,10 @@
         <v>142</v>
       </c>
       <c r="J107" t="s">
-        <v>492</v>
-      </c>
-      <c r="K107" t="s">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="L107" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M107" t="s">
         <v>49</v>
@@ -9687,43 +9696,40 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="B108" t="s">
-        <v>792</v>
+        <v>392</v>
       </c>
       <c r="C108" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="D108" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="E108" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="F108" t="s">
         <v>48</v>
       </c>
       <c r="G108" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H108" t="s">
         <v>13</v>
       </c>
       <c r="I108" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="J108" t="s">
-        <v>408</v>
-      </c>
-      <c r="K108" t="s">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="L108" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M108" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N108" t="s">
         <v>14</v>
@@ -9737,34 +9743,28 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>419</v>
+        <v>368</v>
       </c>
       <c r="B109" t="s">
-        <v>423</v>
+        <v>789</v>
       </c>
       <c r="C109" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D109" t="s">
-        <v>424</v>
-      </c>
-      <c r="E109" t="s">
-        <v>916</v>
+        <v>1107</v>
       </c>
       <c r="F109" t="s">
         <v>48</v>
       </c>
       <c r="G109" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H109" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I109" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J109" t="s">
-        <v>408</v>
+        <v>280</v>
       </c>
       <c r="K109" t="s">
         <v>55</v>
@@ -9787,40 +9787,40 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="B110" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C110" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="D110" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="E110" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="F110" t="s">
         <v>48</v>
       </c>
       <c r="G110" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H110" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I110" t="s">
-        <v>433</v>
+        <v>142</v>
       </c>
       <c r="J110" t="s">
-        <v>426</v>
+        <v>492</v>
       </c>
       <c r="K110" t="s">
         <v>55</v>
       </c>
       <c r="L110" t="s">
-        <v>389</v>
+        <v>198</v>
       </c>
       <c r="M110" t="s">
         <v>49</v>
@@ -9837,34 +9837,34 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="B111" t="s">
-        <v>1282</v>
+        <v>792</v>
       </c>
       <c r="C111" t="s">
-        <v>1283</v>
+        <v>1111</v>
       </c>
       <c r="D111" t="s">
-        <v>507</v>
+        <v>407</v>
       </c>
       <c r="E111" t="s">
-        <v>925</v>
+        <v>915</v>
       </c>
       <c r="F111" t="s">
         <v>48</v>
       </c>
       <c r="G111" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H111" t="s">
         <v>13</v>
       </c>
       <c r="I111" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="J111" t="s">
-        <v>280</v>
+        <v>408</v>
       </c>
       <c r="K111" t="s">
         <v>55</v>
@@ -9873,7 +9873,7 @@
         <v>181</v>
       </c>
       <c r="M111" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N111" t="s">
         <v>14</v>
@@ -9887,37 +9887,40 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>294</v>
+        <v>419</v>
       </c>
       <c r="B112" t="s">
-        <v>799</v>
+        <v>423</v>
       </c>
       <c r="C112" t="s">
-        <v>1122</v>
+        <v>1112</v>
       </c>
       <c r="D112" t="s">
-        <v>639</v>
+        <v>424</v>
       </c>
       <c r="E112" t="s">
-        <v>972</v>
+        <v>916</v>
       </c>
       <c r="F112" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G112" t="s">
         <v>32</v>
       </c>
       <c r="H112" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I112" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J112" t="s">
-        <v>280</v>
+        <v>408</v>
+      </c>
+      <c r="K112" t="s">
+        <v>55</v>
       </c>
       <c r="L112" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="M112" t="s">
         <v>49</v>
@@ -9934,43 +9937,43 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B113" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C113" t="s">
-        <v>428</v>
+        <v>1113</v>
       </c>
       <c r="D113" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E113" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F113" t="s">
         <v>48</v>
       </c>
       <c r="G113" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H113" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I113" t="s">
-        <v>142</v>
+        <v>433</v>
       </c>
       <c r="J113" t="s">
-        <v>525</v>
+        <v>426</v>
       </c>
       <c r="K113" t="s">
         <v>55</v>
       </c>
       <c r="L113" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M113" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N113" t="s">
         <v>14</v>
@@ -9984,19 +9987,19 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>422</v>
+        <v>500</v>
       </c>
       <c r="B114" t="s">
-        <v>430</v>
+        <v>1282</v>
       </c>
       <c r="C114" t="s">
-        <v>430</v>
+        <v>1283</v>
       </c>
       <c r="D114" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="E114" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="F114" t="s">
         <v>48</v>
@@ -10008,16 +10011,16 @@
         <v>13</v>
       </c>
       <c r="I114" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="J114" t="s">
-        <v>432</v>
+        <v>280</v>
       </c>
       <c r="K114" t="s">
         <v>55</v>
       </c>
       <c r="L114" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M114" t="s">
         <v>49</v>
@@ -10034,40 +10037,37 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>434</v>
+        <v>294</v>
       </c>
       <c r="B115" t="s">
-        <v>443</v>
+        <v>799</v>
       </c>
       <c r="C115" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="D115" t="s">
-        <v>446</v>
+        <v>639</v>
       </c>
       <c r="E115" t="s">
-        <v>920</v>
+        <v>972</v>
       </c>
       <c r="F115" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G115" t="s">
         <v>32</v>
       </c>
       <c r="H115" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I115" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="J115" t="s">
-        <v>444</v>
-      </c>
-      <c r="K115" t="s">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="L115" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="M115" t="s">
         <v>49</v>
@@ -10084,19 +10084,19 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>435</v>
+        <v>252</v>
       </c>
       <c r="B116" t="s">
-        <v>445</v>
+        <v>776</v>
       </c>
       <c r="C116" t="s">
-        <v>1115</v>
+        <v>1094</v>
       </c>
       <c r="D116" t="s">
-        <v>446</v>
+        <v>265</v>
       </c>
       <c r="E116" t="s">
-        <v>920</v>
+        <v>899</v>
       </c>
       <c r="F116" t="s">
         <v>48</v>
@@ -10111,16 +10111,16 @@
         <v>110</v>
       </c>
       <c r="J116" t="s">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="K116" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="L116" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M116" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N116" t="s">
         <v>14</v>
@@ -10134,19 +10134,19 @@
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>436</v>
+        <v>253</v>
       </c>
       <c r="B117" t="s">
-        <v>447</v>
+        <v>777</v>
       </c>
       <c r="C117" t="s">
-        <v>1116</v>
+        <v>1095</v>
       </c>
       <c r="D117" t="s">
-        <v>793</v>
+        <v>266</v>
       </c>
       <c r="E117" t="s">
-        <v>1036</v>
+        <v>900</v>
       </c>
       <c r="F117" t="s">
         <v>48</v>
@@ -10158,19 +10158,19 @@
         <v>13</v>
       </c>
       <c r="I117" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="J117" t="s">
-        <v>494</v>
+        <v>280</v>
       </c>
       <c r="K117" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="L117" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M117" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N117" t="s">
         <v>14</v>
@@ -10184,19 +10184,19 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>442</v>
+        <v>838</v>
       </c>
       <c r="B118" t="s">
-        <v>460</v>
+        <v>840</v>
       </c>
       <c r="C118" t="s">
-        <v>1121</v>
+        <v>1233</v>
       </c>
       <c r="D118" t="s">
-        <v>446</v>
+        <v>841</v>
       </c>
       <c r="E118" t="s">
-        <v>920</v>
+        <v>1027</v>
       </c>
       <c r="F118" t="s">
         <v>48</v>
@@ -10211,16 +10211,16 @@
         <v>110</v>
       </c>
       <c r="J118" t="s">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="K118" t="s">
-        <v>55</v>
+        <v>207</v>
       </c>
       <c r="L118" t="s">
         <v>181</v>
       </c>
       <c r="M118" t="s">
-        <v>51</v>
+        <v>837</v>
       </c>
       <c r="N118" t="s">
         <v>14</v>
@@ -10234,19 +10234,13 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>498</v>
+        <v>256</v>
       </c>
       <c r="B119" t="s">
-        <v>503</v>
+        <v>279</v>
       </c>
       <c r="C119" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D119" t="s">
-        <v>504</v>
-      </c>
-      <c r="E119" t="s">
-        <v>926</v>
+        <v>1097</v>
       </c>
       <c r="F119" t="s">
         <v>48</v>
@@ -10258,16 +10252,13 @@
         <v>13</v>
       </c>
       <c r="I119" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="J119" t="s">
-        <v>529</v>
-      </c>
-      <c r="K119" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="L119" t="s">
-        <v>505</v>
+        <v>96</v>
       </c>
       <c r="M119" t="s">
         <v>49</v>
@@ -10284,19 +10275,19 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>499</v>
+        <v>257</v>
       </c>
       <c r="B120" t="s">
-        <v>796</v>
+        <v>778</v>
       </c>
       <c r="C120" t="s">
-        <v>1124</v>
+        <v>1098</v>
       </c>
       <c r="D120" t="s">
-        <v>506</v>
+        <v>269</v>
       </c>
       <c r="E120" t="s">
-        <v>927</v>
+        <v>902</v>
       </c>
       <c r="F120" t="s">
         <v>48</v>
@@ -10308,13 +10299,16 @@
         <v>13</v>
       </c>
       <c r="I120" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="J120" t="s">
-        <v>335</v>
+        <v>281</v>
+      </c>
+      <c r="K120" t="s">
+        <v>134</v>
       </c>
       <c r="L120" t="s">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="M120" t="s">
         <v>49</v>
@@ -10331,19 +10325,19 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B121" t="s">
-        <v>795</v>
+        <v>503</v>
       </c>
       <c r="C121" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="D121" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="E121" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="F121" t="s">
         <v>48</v>
@@ -10355,19 +10349,19 @@
         <v>13</v>
       </c>
       <c r="I121" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="J121" t="s">
-        <v>335</v>
+        <v>529</v>
       </c>
       <c r="K121" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L121" t="s">
-        <v>282</v>
+        <v>505</v>
       </c>
       <c r="M121" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N121" t="s">
         <v>14</v>
@@ -10381,19 +10375,19 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>546</v>
+        <v>499</v>
       </c>
       <c r="B122" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C122" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="D122" t="s">
-        <v>548</v>
+        <v>506</v>
       </c>
       <c r="E122" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="F122" t="s">
         <v>48</v>
@@ -10405,16 +10399,13 @@
         <v>13</v>
       </c>
       <c r="I122" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="J122" t="s">
-        <v>267</v>
-      </c>
-      <c r="K122" t="s">
-        <v>55</v>
+        <v>335</v>
       </c>
       <c r="L122" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="M122" t="s">
         <v>49</v>
@@ -10431,19 +10422,19 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>676</v>
+        <v>501</v>
       </c>
       <c r="B123" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C123" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="D123" t="s">
-        <v>697</v>
+        <v>554</v>
       </c>
       <c r="E123" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="F123" t="s">
         <v>48</v>
@@ -10452,19 +10443,22 @@
         <v>32</v>
       </c>
       <c r="H123" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I123" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J123" t="s">
         <v>335</v>
       </c>
+      <c r="K123" t="s">
+        <v>55</v>
+      </c>
       <c r="L123" t="s">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="M123" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N123" t="s">
         <v>14</v>
@@ -10478,13 +10472,19 @@
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>730</v>
+        <v>546</v>
       </c>
       <c r="B124" t="s">
-        <v>825</v>
+        <v>794</v>
       </c>
       <c r="C124" t="s">
-        <v>1128</v>
+        <v>1126</v>
+      </c>
+      <c r="D124" t="s">
+        <v>548</v>
+      </c>
+      <c r="E124" t="s">
+        <v>929</v>
       </c>
       <c r="F124" t="s">
         <v>48</v>
@@ -10493,19 +10493,19 @@
         <v>32</v>
       </c>
       <c r="H124" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I124" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J124" t="s">
-        <v>335</v>
+        <v>267</v>
       </c>
       <c r="K124" t="s">
         <v>55</v>
       </c>
       <c r="L124" t="s">
-        <v>389</v>
+        <v>181</v>
       </c>
       <c r="M124" t="s">
         <v>49</v>
@@ -10522,13 +10522,19 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>547</v>
+        <v>676</v>
       </c>
       <c r="B125" t="s">
-        <v>549</v>
+        <v>828</v>
       </c>
       <c r="C125" t="s">
-        <v>549</v>
+        <v>1127</v>
+      </c>
+      <c r="D125" t="s">
+        <v>697</v>
+      </c>
+      <c r="E125" t="s">
+        <v>930</v>
       </c>
       <c r="F125" t="s">
         <v>48</v>
@@ -10537,22 +10543,19 @@
         <v>32</v>
       </c>
       <c r="H125" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I125" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J125" t="s">
-        <v>267</v>
-      </c>
-      <c r="K125" t="s">
-        <v>76</v>
+        <v>335</v>
       </c>
       <c r="L125" t="s">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="M125" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N125" t="s">
         <v>14</v>
@@ -10566,40 +10569,34 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>238</v>
+        <v>730</v>
       </c>
       <c r="B126" t="s">
-        <v>239</v>
+        <v>825</v>
       </c>
       <c r="C126" t="s">
-        <v>239</v>
-      </c>
-      <c r="D126" t="s">
-        <v>641</v>
-      </c>
-      <c r="E126" t="s">
-        <v>1043</v>
+        <v>1128</v>
       </c>
       <c r="F126" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G126" t="s">
         <v>32</v>
       </c>
       <c r="H126" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I126" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J126" t="s">
         <v>335</v>
       </c>
       <c r="K126" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="L126" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M126" t="s">
         <v>49</v>
@@ -10616,43 +10613,37 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>667</v>
+        <v>547</v>
       </c>
       <c r="B127" t="s">
-        <v>684</v>
+        <v>549</v>
       </c>
       <c r="C127" t="s">
-        <v>1214</v>
-      </c>
-      <c r="D127" t="s">
-        <v>685</v>
-      </c>
-      <c r="E127" t="s">
-        <v>1013</v>
+        <v>549</v>
       </c>
       <c r="F127" t="s">
         <v>48</v>
       </c>
       <c r="G127" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H127" t="s">
         <v>13</v>
       </c>
       <c r="I127" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J127" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="K127" t="s">
         <v>76</v>
       </c>
       <c r="L127" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M127" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N127" t="s">
         <v>14</v>
@@ -10666,16 +10657,22 @@
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>675</v>
+        <v>238</v>
       </c>
       <c r="B128" t="s">
-        <v>696</v>
+        <v>239</v>
       </c>
       <c r="C128" t="s">
-        <v>1129</v>
+        <v>239</v>
+      </c>
+      <c r="D128" t="s">
+        <v>641</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1043</v>
       </c>
       <c r="F128" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G128" t="s">
         <v>32</v>
@@ -10689,11 +10686,14 @@
       <c r="J128" t="s">
         <v>335</v>
       </c>
+      <c r="K128" t="s">
+        <v>134</v>
+      </c>
       <c r="L128" t="s">
         <v>181</v>
       </c>
       <c r="M128" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N128" t="s">
         <v>14</v>
@@ -10707,37 +10707,40 @@
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>358</v>
+        <v>667</v>
       </c>
       <c r="B129" t="s">
-        <v>377</v>
+        <v>684</v>
       </c>
       <c r="C129" t="s">
-        <v>1100</v>
+        <v>1214</v>
       </c>
       <c r="D129" t="s">
-        <v>781</v>
+        <v>685</v>
       </c>
       <c r="E129" t="s">
-        <v>906</v>
+        <v>1013</v>
       </c>
       <c r="F129" t="s">
         <v>48</v>
       </c>
       <c r="G129" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H129" t="s">
         <v>13</v>
       </c>
       <c r="I129" t="s">
-        <v>271</v>
+        <v>110</v>
       </c>
       <c r="J129" t="s">
-        <v>267</v>
+        <v>280</v>
+      </c>
+      <c r="K129" t="s">
+        <v>76</v>
       </c>
       <c r="L129" t="s">
-        <v>701</v>
+        <v>181</v>
       </c>
       <c r="M129" t="s">
         <v>49</v>
@@ -10754,13 +10757,13 @@
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>1251</v>
+        <v>675</v>
       </c>
       <c r="B130" t="s">
-        <v>1269</v>
+        <v>696</v>
       </c>
       <c r="C130" t="s">
-        <v>1270</v>
+        <v>1129</v>
       </c>
       <c r="F130" t="s">
         <v>48</v>
@@ -10769,19 +10772,19 @@
         <v>32</v>
       </c>
       <c r="H130" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I130" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J130" t="s">
-        <v>267</v>
+        <v>335</v>
       </c>
       <c r="L130" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M130" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N130" t="s">
         <v>14</v>
@@ -10795,37 +10798,37 @@
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>62</v>
+        <v>358</v>
       </c>
       <c r="B131" t="s">
-        <v>71</v>
+        <v>377</v>
       </c>
       <c r="C131" t="s">
-        <v>1133</v>
+        <v>1100</v>
       </c>
       <c r="D131" t="s">
-        <v>292</v>
+        <v>781</v>
       </c>
       <c r="E131" t="s">
-        <v>934</v>
+        <v>906</v>
       </c>
       <c r="F131" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G131" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="H131" t="s">
         <v>13</v>
       </c>
       <c r="I131" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J131" t="s">
-        <v>524</v>
+        <v>267</v>
       </c>
       <c r="L131" t="s">
-        <v>181</v>
+        <v>701</v>
       </c>
       <c r="M131" t="s">
         <v>49</v>
@@ -10842,43 +10845,34 @@
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>126</v>
+        <v>1251</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>1269</v>
       </c>
       <c r="C132" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D132" t="s">
-        <v>133</v>
-      </c>
-      <c r="E132" t="s">
-        <v>936</v>
+        <v>1270</v>
       </c>
       <c r="F132" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G132" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H132" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I132" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J132" t="s">
-        <v>111</v>
-      </c>
-      <c r="K132" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="L132" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M132" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N132" t="s">
         <v>14</v>
@@ -12535,31 +12529,31 @@
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>569</v>
+        <v>359</v>
       </c>
       <c r="B167" t="s">
-        <v>577</v>
+        <v>378</v>
       </c>
       <c r="C167" t="s">
-        <v>577</v>
+        <v>1101</v>
       </c>
       <c r="D167" t="s">
-        <v>813</v>
+        <v>782</v>
       </c>
       <c r="E167" t="s">
-        <v>963</v>
+        <v>907</v>
       </c>
       <c r="F167" t="s">
         <v>48</v>
       </c>
       <c r="G167" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H167" t="s">
         <v>13</v>
       </c>
       <c r="I167" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J167" t="s">
         <v>267</v>
@@ -12568,7 +12562,7 @@
         <v>76</v>
       </c>
       <c r="L167" t="s">
-        <v>568</v>
+        <v>198</v>
       </c>
       <c r="M167" t="s">
         <v>49</v>
@@ -12585,19 +12579,19 @@
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>251</v>
+        <v>569</v>
       </c>
       <c r="B168" t="s">
-        <v>262</v>
+        <v>577</v>
       </c>
       <c r="C168" t="s">
-        <v>1093</v>
+        <v>577</v>
       </c>
       <c r="D168" t="s">
-        <v>263</v>
+        <v>813</v>
       </c>
       <c r="E168" t="s">
-        <v>898</v>
+        <v>963</v>
       </c>
       <c r="F168" t="s">
         <v>48</v>
@@ -12612,13 +12606,13 @@
         <v>142</v>
       </c>
       <c r="J168" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K168" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L168" t="s">
-        <v>181</v>
+        <v>568</v>
       </c>
       <c r="M168" t="s">
         <v>49</v>
@@ -12635,19 +12629,19 @@
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>174</v>
+        <v>1373</v>
       </c>
       <c r="B169" t="s">
-        <v>178</v>
+        <v>1380</v>
       </c>
       <c r="C169" t="s">
-        <v>178</v>
+        <v>1380</v>
       </c>
       <c r="D169" t="s">
-        <v>640</v>
+        <v>1381</v>
       </c>
       <c r="E169" t="s">
-        <v>962</v>
+        <v>1382</v>
       </c>
       <c r="F169" t="s">
         <v>79</v>
@@ -12659,19 +12653,19 @@
         <v>13</v>
       </c>
       <c r="I169" t="s">
-        <v>142</v>
+        <v>1383</v>
       </c>
       <c r="J169" t="s">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="K169" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L169" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M169" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N169" t="s">
         <v>14</v>
@@ -12685,40 +12679,40 @@
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="B170" t="s">
-        <v>183</v>
+        <v>247</v>
       </c>
       <c r="C170" t="s">
-        <v>1164</v>
+        <v>1090</v>
       </c>
       <c r="D170" t="s">
-        <v>798</v>
+        <v>411</v>
       </c>
       <c r="E170" t="s">
-        <v>1041</v>
+        <v>1031</v>
       </c>
       <c r="F170" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G170" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H170" t="s">
         <v>13</v>
       </c>
       <c r="I170" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J170" t="s">
-        <v>486</v>
+        <v>335</v>
       </c>
       <c r="K170" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="L170" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M170" t="s">
         <v>49</v>
@@ -12735,22 +12729,22 @@
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="B171" t="s">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="C171" t="s">
-        <v>1165</v>
+        <v>1091</v>
       </c>
       <c r="D171" t="s">
-        <v>797</v>
+        <v>412</v>
       </c>
       <c r="E171" t="s">
-        <v>1042</v>
+        <v>1032</v>
       </c>
       <c r="F171" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G171" t="s">
         <v>32</v>
@@ -12759,16 +12753,16 @@
         <v>13</v>
       </c>
       <c r="I171" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J171" t="s">
-        <v>486</v>
+        <v>335</v>
       </c>
       <c r="K171" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="L171" t="s">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="M171" t="s">
         <v>49</v>
@@ -12785,19 +12779,19 @@
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>467</v>
+        <v>296</v>
       </c>
       <c r="B172" t="s">
-        <v>476</v>
+        <v>311</v>
       </c>
       <c r="C172" t="s">
-        <v>1191</v>
+        <v>1168</v>
       </c>
       <c r="D172" t="s">
-        <v>477</v>
+        <v>312</v>
       </c>
       <c r="E172" t="s">
-        <v>988</v>
+        <v>965</v>
       </c>
       <c r="F172" t="s">
         <v>79</v>
@@ -12809,13 +12803,16 @@
         <v>13</v>
       </c>
       <c r="I172" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J172" t="s">
-        <v>111</v>
+        <v>524</v>
+      </c>
+      <c r="K172" t="s">
+        <v>134</v>
       </c>
       <c r="L172" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M172" t="s">
         <v>49</v>
@@ -12832,40 +12829,37 @@
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>512</v>
+        <v>623</v>
       </c>
       <c r="B173" t="s">
-        <v>809</v>
+        <v>633</v>
       </c>
       <c r="C173" t="s">
-        <v>1192</v>
+        <v>1169</v>
       </c>
       <c r="D173" t="s">
-        <v>518</v>
+        <v>634</v>
       </c>
       <c r="E173" t="s">
-        <v>1046</v>
+        <v>966</v>
       </c>
       <c r="F173" t="s">
         <v>79</v>
       </c>
       <c r="G173" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H173" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I173" t="s">
-        <v>519</v>
+        <v>271</v>
       </c>
       <c r="J173" t="s">
-        <v>486</v>
-      </c>
-      <c r="K173" t="s">
-        <v>76</v>
+        <v>203</v>
       </c>
       <c r="L173" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="M173" t="s">
         <v>49</v>
@@ -12882,19 +12876,19 @@
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>296</v>
+        <v>624</v>
       </c>
       <c r="B174" t="s">
-        <v>311</v>
+        <v>635</v>
       </c>
       <c r="C174" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D174" t="s">
-        <v>312</v>
+        <v>636</v>
       </c>
       <c r="E174" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="F174" t="s">
         <v>79</v>
@@ -12909,13 +12903,10 @@
         <v>271</v>
       </c>
       <c r="J174" t="s">
-        <v>524</v>
-      </c>
-      <c r="K174" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="L174" t="s">
-        <v>189</v>
+        <v>98</v>
       </c>
       <c r="M174" t="s">
         <v>49</v>
@@ -12932,22 +12923,22 @@
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
       <c r="B175" t="s">
-        <v>414</v>
+        <v>310</v>
       </c>
       <c r="C175" t="s">
-        <v>414</v>
+        <v>1171</v>
       </c>
       <c r="D175" t="s">
-        <v>608</v>
+        <v>637</v>
       </c>
       <c r="E175" t="s">
-        <v>901</v>
+        <v>968</v>
       </c>
       <c r="F175" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G175" t="s">
         <v>52</v>
@@ -12956,19 +12947,16 @@
         <v>13</v>
       </c>
       <c r="I175" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J175" t="s">
-        <v>111</v>
-      </c>
-      <c r="K175" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="L175" t="s">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="M175" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N175" t="s">
         <v>14</v>
@@ -12982,19 +12970,19 @@
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>623</v>
+        <v>293</v>
       </c>
       <c r="B176" t="s">
-        <v>633</v>
+        <v>308</v>
       </c>
       <c r="C176" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="D176" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E176" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="F176" t="s">
         <v>79</v>
@@ -13029,22 +13017,22 @@
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>624</v>
+        <v>254</v>
       </c>
       <c r="B177" t="s">
-        <v>635</v>
+        <v>414</v>
       </c>
       <c r="C177" t="s">
-        <v>1170</v>
+        <v>414</v>
       </c>
       <c r="D177" t="s">
-        <v>636</v>
+        <v>608</v>
       </c>
       <c r="E177" t="s">
-        <v>967</v>
+        <v>901</v>
       </c>
       <c r="F177" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G177" t="s">
         <v>52</v>
@@ -13053,16 +13041,19 @@
         <v>13</v>
       </c>
       <c r="I177" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J177" t="s">
-        <v>203</v>
+        <v>111</v>
+      </c>
+      <c r="K177" t="s">
+        <v>141</v>
       </c>
       <c r="L177" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="M177" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N177" t="s">
         <v>14</v>
@@ -13076,19 +13067,19 @@
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>295</v>
+        <v>621</v>
       </c>
       <c r="B178" t="s">
-        <v>310</v>
+        <v>414</v>
       </c>
       <c r="C178" t="s">
-        <v>1171</v>
+        <v>414</v>
       </c>
       <c r="D178" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="E178" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="F178" t="s">
         <v>79</v>
@@ -13123,37 +13114,40 @@
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>293</v>
+        <v>628</v>
       </c>
       <c r="B179" t="s">
-        <v>308</v>
+        <v>647</v>
       </c>
       <c r="C179" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D179" t="s">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="E179" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="F179" t="s">
         <v>79</v>
       </c>
       <c r="G179" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H179" t="s">
         <v>13</v>
       </c>
       <c r="I179" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J179" t="s">
         <v>203</v>
       </c>
+      <c r="K179" t="s">
+        <v>134</v>
+      </c>
       <c r="L179" t="s">
-        <v>98</v>
+        <v>344</v>
       </c>
       <c r="M179" t="s">
         <v>49</v>
@@ -13170,22 +13164,22 @@
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>621</v>
+        <v>1327</v>
       </c>
       <c r="B180" t="s">
-        <v>414</v>
+        <v>1342</v>
       </c>
       <c r="C180" t="s">
-        <v>414</v>
+        <v>1352</v>
       </c>
       <c r="D180" t="s">
-        <v>630</v>
+        <v>386</v>
       </c>
       <c r="E180" t="s">
-        <v>970</v>
+        <v>909</v>
       </c>
       <c r="F180" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G180" t="s">
         <v>52</v>
@@ -13194,13 +13188,13 @@
         <v>13</v>
       </c>
       <c r="I180" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J180" t="s">
-        <v>203</v>
+        <v>491</v>
       </c>
       <c r="L180" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M180" t="s">
         <v>49</v>
@@ -13217,40 +13211,37 @@
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>628</v>
+        <v>301</v>
       </c>
       <c r="B181" t="s">
-        <v>647</v>
+        <v>322</v>
       </c>
       <c r="C181" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="D181" t="s">
-        <v>648</v>
+        <v>609</v>
       </c>
       <c r="E181" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="F181" t="s">
         <v>79</v>
       </c>
       <c r="G181" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H181" t="s">
         <v>13</v>
       </c>
       <c r="I181" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J181" t="s">
-        <v>203</v>
-      </c>
-      <c r="K181" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="L181" t="s">
-        <v>344</v>
+        <v>96</v>
       </c>
       <c r="M181" t="s">
         <v>49</v>
@@ -13267,25 +13258,25 @@
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>1327</v>
+        <v>610</v>
       </c>
       <c r="B182" t="s">
-        <v>1342</v>
+        <v>650</v>
       </c>
       <c r="C182" t="s">
-        <v>1352</v>
+        <v>1209</v>
       </c>
       <c r="D182" t="s">
-        <v>386</v>
+        <v>651</v>
       </c>
       <c r="E182" t="s">
-        <v>909</v>
+        <v>1004</v>
       </c>
       <c r="F182" t="s">
         <v>48</v>
       </c>
       <c r="G182" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H182" t="s">
         <v>13</v>
@@ -13293,11 +13284,8 @@
       <c r="I182" t="s">
         <v>142</v>
       </c>
-      <c r="J182" t="s">
-        <v>491</v>
-      </c>
       <c r="L182" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M182" t="s">
         <v>49</v>
@@ -13314,19 +13302,19 @@
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B183" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C183" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D183" t="s">
-        <v>609</v>
+        <v>318</v>
       </c>
       <c r="E183" t="s">
-        <v>975</v>
+        <v>1045</v>
       </c>
       <c r="F183" t="s">
         <v>79</v>
@@ -13338,16 +13326,19 @@
         <v>13</v>
       </c>
       <c r="I183" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="J183" t="s">
-        <v>111</v>
+        <v>488</v>
+      </c>
+      <c r="K183" t="s">
+        <v>76</v>
       </c>
       <c r="L183" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="M183" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N183" t="s">
         <v>14</v>
@@ -13361,25 +13352,25 @@
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="B184" t="s">
-        <v>313</v>
+        <v>779</v>
       </c>
       <c r="C184" t="s">
-        <v>1174</v>
+        <v>779</v>
       </c>
       <c r="D184" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="E184" t="s">
-        <v>973</v>
+        <v>903</v>
       </c>
       <c r="F184" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G184" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H184" t="s">
         <v>13</v>
@@ -13388,13 +13379,16 @@
         <v>142</v>
       </c>
       <c r="J184" t="s">
-        <v>280</v>
+        <v>320</v>
+      </c>
+      <c r="K184" t="s">
+        <v>141</v>
       </c>
       <c r="L184" t="s">
-        <v>96</v>
+        <v>282</v>
       </c>
       <c r="M184" t="s">
-        <v>50</v>
+        <v>836</v>
       </c>
       <c r="N184" t="s">
         <v>14</v>
@@ -13408,43 +13402,43 @@
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B185" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="C185" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="D185" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="E185" t="s">
-        <v>1045</v>
+        <v>980</v>
       </c>
       <c r="F185" t="s">
         <v>79</v>
       </c>
       <c r="G185" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H185" t="s">
         <v>13</v>
       </c>
       <c r="I185" t="s">
-        <v>319</v>
+        <v>142</v>
       </c>
       <c r="J185" t="s">
         <v>488</v>
       </c>
       <c r="K185" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="L185" t="s">
-        <v>189</v>
+        <v>334</v>
       </c>
       <c r="M185" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N185" t="s">
         <v>14</v>
@@ -13458,22 +13452,22 @@
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>258</v>
+        <v>561</v>
       </c>
       <c r="B186" t="s">
-        <v>779</v>
+        <v>810</v>
       </c>
       <c r="C186" t="s">
-        <v>779</v>
+        <v>1195</v>
       </c>
       <c r="D186" t="s">
-        <v>283</v>
+        <v>566</v>
       </c>
       <c r="E186" t="s">
-        <v>903</v>
+        <v>992</v>
       </c>
       <c r="F186" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G186" t="s">
         <v>52</v>
@@ -13485,16 +13479,16 @@
         <v>142</v>
       </c>
       <c r="J186" t="s">
-        <v>320</v>
+        <v>488</v>
       </c>
       <c r="K186" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="L186" t="s">
-        <v>282</v>
+        <v>579</v>
       </c>
       <c r="M186" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N186" t="s">
         <v>14</v>
@@ -13508,40 +13502,40 @@
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B187" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="C187" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="D187" t="s">
-        <v>333</v>
+        <v>800</v>
       </c>
       <c r="E187" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="F187" t="s">
         <v>79</v>
       </c>
       <c r="G187" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H187" t="s">
         <v>13</v>
       </c>
       <c r="I187" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J187" t="s">
-        <v>488</v>
+        <v>316</v>
       </c>
       <c r="K187" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L187" t="s">
-        <v>334</v>
+        <v>184</v>
       </c>
       <c r="M187" t="s">
         <v>49</v>
@@ -13558,19 +13552,19 @@
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>561</v>
+        <v>302</v>
       </c>
       <c r="B188" t="s">
-        <v>810</v>
+        <v>323</v>
       </c>
       <c r="C188" t="s">
-        <v>1195</v>
+        <v>1178</v>
       </c>
       <c r="D188" t="s">
-        <v>566</v>
+        <v>802</v>
       </c>
       <c r="E188" t="s">
-        <v>992</v>
+        <v>978</v>
       </c>
       <c r="F188" t="s">
         <v>79</v>
@@ -13582,19 +13576,19 @@
         <v>13</v>
       </c>
       <c r="I188" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J188" t="s">
-        <v>488</v>
+        <v>316</v>
       </c>
       <c r="K188" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L188" t="s">
-        <v>579</v>
+        <v>98</v>
       </c>
       <c r="M188" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N188" t="s">
         <v>14</v>
@@ -13608,37 +13602,40 @@
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B189" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C189" t="s">
-        <v>321</v>
+        <v>1179</v>
       </c>
       <c r="D189" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E189" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="F189" t="s">
         <v>79</v>
       </c>
       <c r="G189" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H189" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I189" t="s">
-        <v>144</v>
+        <v>329</v>
       </c>
       <c r="J189" t="s">
-        <v>489</v>
+        <v>208</v>
+      </c>
+      <c r="K189" t="s">
+        <v>76</v>
       </c>
       <c r="L189" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M189" t="s">
         <v>49</v>
@@ -13655,13 +13652,13 @@
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>298</v>
+        <v>596</v>
       </c>
       <c r="B190" t="s">
-        <v>315</v>
+        <v>603</v>
       </c>
       <c r="C190" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="D190" t="s">
         <v>800</v>
@@ -13682,13 +13679,13 @@
         <v>271</v>
       </c>
       <c r="J190" t="s">
-        <v>316</v>
+        <v>493</v>
       </c>
       <c r="K190" t="s">
         <v>76</v>
       </c>
       <c r="L190" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="M190" t="s">
         <v>49</v>
@@ -13705,19 +13702,19 @@
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B191" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C191" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="D191" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E191" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F191" t="s">
         <v>79</v>
@@ -13732,7 +13729,7 @@
         <v>271</v>
       </c>
       <c r="J191" t="s">
-        <v>316</v>
+        <v>208</v>
       </c>
       <c r="K191" t="s">
         <v>76</v>
@@ -13755,19 +13752,19 @@
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B192" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C192" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="D192" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E192" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F192" t="s">
         <v>79</v>
@@ -13779,7 +13776,7 @@
         <v>13</v>
       </c>
       <c r="I192" t="s">
-        <v>329</v>
+        <v>271</v>
       </c>
       <c r="J192" t="s">
         <v>208</v>
@@ -13805,22 +13802,22 @@
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>596</v>
+        <v>720</v>
       </c>
       <c r="B193" t="s">
-        <v>603</v>
+        <v>743</v>
       </c>
       <c r="C193" t="s">
-        <v>1180</v>
+        <v>1224</v>
       </c>
       <c r="D193" t="s">
-        <v>800</v>
+        <v>748</v>
       </c>
       <c r="E193" t="s">
-        <v>977</v>
+        <v>1023</v>
       </c>
       <c r="F193" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G193" t="s">
         <v>52</v>
@@ -13832,13 +13829,13 @@
         <v>271</v>
       </c>
       <c r="J193" t="s">
-        <v>493</v>
+        <v>208</v>
       </c>
       <c r="K193" t="s">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="L193" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="M193" t="s">
         <v>49</v>
@@ -13855,25 +13852,25 @@
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>305</v>
+        <v>721</v>
       </c>
       <c r="B194" t="s">
-        <v>330</v>
+        <v>742</v>
       </c>
       <c r="C194" t="s">
-        <v>1181</v>
+        <v>1225</v>
       </c>
       <c r="D194" t="s">
-        <v>800</v>
+        <v>749</v>
       </c>
       <c r="E194" t="s">
-        <v>977</v>
+        <v>1024</v>
       </c>
       <c r="F194" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G194" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H194" t="s">
         <v>13</v>
@@ -13882,13 +13879,13 @@
         <v>271</v>
       </c>
       <c r="J194" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="K194" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L194" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="M194" t="s">
         <v>49</v>
@@ -13905,25 +13902,25 @@
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>306</v>
+        <v>722</v>
       </c>
       <c r="B195" t="s">
-        <v>331</v>
+        <v>741</v>
       </c>
       <c r="C195" t="s">
-        <v>1182</v>
+        <v>1226</v>
       </c>
       <c r="D195" t="s">
-        <v>802</v>
+        <v>749</v>
       </c>
       <c r="E195" t="s">
-        <v>978</v>
+        <v>1024</v>
       </c>
       <c r="F195" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G195" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H195" t="s">
         <v>13</v>
@@ -13932,13 +13929,13 @@
         <v>271</v>
       </c>
       <c r="J195" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="K195" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L195" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="M195" t="s">
         <v>49</v>
@@ -13955,25 +13952,25 @@
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B196" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C196" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="D196" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E196" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F196" t="s">
         <v>48</v>
       </c>
       <c r="G196" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H196" t="s">
         <v>13</v>
@@ -13982,10 +13979,10 @@
         <v>271</v>
       </c>
       <c r="J196" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="K196" t="s">
-        <v>207</v>
+        <v>55</v>
       </c>
       <c r="L196" t="s">
         <v>181</v>
@@ -14005,13 +14002,13 @@
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B197" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C197" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="D197" t="s">
         <v>749</v>
@@ -14035,7 +14032,7 @@
         <v>280</v>
       </c>
       <c r="K197" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="L197" t="s">
         <v>181</v>
@@ -14055,13 +14052,13 @@
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B198" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="C198" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="D198" t="s">
         <v>749</v>
@@ -14105,19 +14102,19 @@
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>723</v>
+        <v>1285</v>
       </c>
       <c r="B199" t="s">
-        <v>740</v>
+        <v>1309</v>
       </c>
       <c r="C199" t="s">
-        <v>1227</v>
+        <v>1310</v>
       </c>
       <c r="D199" t="s">
-        <v>749</v>
+        <v>1254</v>
       </c>
       <c r="E199" t="s">
-        <v>1024</v>
+        <v>1256</v>
       </c>
       <c r="F199" t="s">
         <v>48</v>
@@ -14126,22 +14123,22 @@
         <v>32</v>
       </c>
       <c r="H199" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I199" t="s">
-        <v>271</v>
+        <v>449</v>
       </c>
       <c r="J199" t="s">
         <v>280</v>
       </c>
       <c r="K199" t="s">
-        <v>55</v>
+        <v>418</v>
       </c>
       <c r="L199" t="s">
         <v>181</v>
       </c>
       <c r="M199" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N199" t="s">
         <v>14</v>
@@ -14155,19 +14152,19 @@
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>724</v>
+        <v>1286</v>
       </c>
       <c r="B200" t="s">
-        <v>739</v>
+        <v>1311</v>
       </c>
       <c r="C200" t="s">
-        <v>1228</v>
+        <v>1312</v>
       </c>
       <c r="D200" t="s">
-        <v>749</v>
+        <v>1313</v>
       </c>
       <c r="E200" t="s">
-        <v>1024</v>
+        <v>1313</v>
       </c>
       <c r="F200" t="s">
         <v>48</v>
@@ -14179,7 +14176,7 @@
         <v>13</v>
       </c>
       <c r="I200" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J200" t="s">
         <v>280</v>
@@ -14205,38 +14202,35 @@
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>732</v>
+        <v>619</v>
       </c>
       <c r="B201" t="s">
-        <v>733</v>
+        <v>662</v>
       </c>
       <c r="C201" t="s">
-        <v>1229</v>
+        <v>1212</v>
       </c>
       <c r="D201" t="s">
-        <v>749</v>
+        <v>821</v>
       </c>
       <c r="E201" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="F201" t="s">
         <v>48</v>
       </c>
       <c r="G201" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H201" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I201" t="s">
-        <v>271</v>
+        <v>144</v>
       </c>
       <c r="J201" t="s">
         <v>280</v>
       </c>
-      <c r="K201" t="s">
-        <v>55</v>
-      </c>
       <c r="L201" t="s">
         <v>181</v>
       </c>
@@ -14255,19 +14249,19 @@
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>1285</v>
+        <v>584</v>
       </c>
       <c r="B202" t="s">
-        <v>1309</v>
+        <v>590</v>
       </c>
       <c r="C202" t="s">
-        <v>1310</v>
+        <v>1200</v>
       </c>
       <c r="D202" t="s">
-        <v>1254</v>
+        <v>598</v>
       </c>
       <c r="E202" t="s">
-        <v>1256</v>
+        <v>995</v>
       </c>
       <c r="F202" t="s">
         <v>48</v>
@@ -14279,19 +14273,19 @@
         <v>31</v>
       </c>
       <c r="I202" t="s">
-        <v>449</v>
+        <v>591</v>
       </c>
       <c r="J202" t="s">
         <v>280</v>
       </c>
       <c r="K202" t="s">
-        <v>418</v>
+        <v>76</v>
       </c>
       <c r="L202" t="s">
         <v>181</v>
       </c>
       <c r="M202" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N202" t="s">
         <v>14</v>
@@ -14305,19 +14299,19 @@
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>1286</v>
+        <v>668</v>
       </c>
       <c r="B203" t="s">
-        <v>1311</v>
+        <v>686</v>
       </c>
       <c r="C203" t="s">
-        <v>1312</v>
+        <v>1215</v>
       </c>
       <c r="D203" t="s">
-        <v>1313</v>
+        <v>687</v>
       </c>
       <c r="E203" t="s">
-        <v>1313</v>
+        <v>1014</v>
       </c>
       <c r="F203" t="s">
         <v>48</v>
@@ -14334,11 +14328,8 @@
       <c r="J203" t="s">
         <v>280</v>
       </c>
-      <c r="K203" t="s">
-        <v>141</v>
-      </c>
       <c r="L203" t="s">
-        <v>181</v>
+        <v>344</v>
       </c>
       <c r="M203" t="s">
         <v>49</v>
@@ -14355,40 +14346,43 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>619</v>
+        <v>1245</v>
       </c>
       <c r="B204" t="s">
-        <v>662</v>
+        <v>1253</v>
       </c>
       <c r="C204" t="s">
-        <v>1212</v>
+        <v>1255</v>
       </c>
       <c r="D204" t="s">
-        <v>821</v>
+        <v>1254</v>
       </c>
       <c r="E204" t="s">
-        <v>1011</v>
+        <v>1256</v>
       </c>
       <c r="F204" t="s">
         <v>48</v>
       </c>
       <c r="G204" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="H204" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I204" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J204" t="s">
         <v>280</v>
       </c>
+      <c r="K204" t="s">
+        <v>55</v>
+      </c>
       <c r="L204" t="s">
         <v>181</v>
       </c>
       <c r="M204" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N204" t="s">
         <v>14</v>
@@ -14402,19 +14396,19 @@
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>584</v>
+        <v>1246</v>
       </c>
       <c r="B205" t="s">
-        <v>590</v>
+        <v>1257</v>
       </c>
       <c r="C205" t="s">
-        <v>1200</v>
+        <v>1258</v>
       </c>
       <c r="D205" t="s">
-        <v>598</v>
+        <v>1254</v>
       </c>
       <c r="E205" t="s">
-        <v>995</v>
+        <v>1256</v>
       </c>
       <c r="F205" t="s">
         <v>48</v>
@@ -14423,16 +14417,16 @@
         <v>32</v>
       </c>
       <c r="H205" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I205" t="s">
-        <v>591</v>
+        <v>142</v>
       </c>
       <c r="J205" t="s">
-        <v>280</v>
+        <v>589</v>
       </c>
       <c r="K205" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L205" t="s">
         <v>181</v>
@@ -14452,13 +14446,13 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>668</v>
+        <v>1271</v>
       </c>
       <c r="B206" t="s">
-        <v>686</v>
+        <v>1274</v>
       </c>
       <c r="C206" t="s">
-        <v>1215</v>
+        <v>1276</v>
       </c>
       <c r="D206" t="s">
         <v>687</v>
@@ -14467,22 +14461,22 @@
         <v>1014</v>
       </c>
       <c r="F206" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G206" t="s">
         <v>32</v>
       </c>
       <c r="H206" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I206" t="s">
-        <v>142</v>
+        <v>1279</v>
       </c>
       <c r="J206" t="s">
         <v>280</v>
       </c>
       <c r="L206" t="s">
-        <v>344</v>
+        <v>98</v>
       </c>
       <c r="M206" t="s">
         <v>49</v>
@@ -14499,31 +14493,31 @@
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>1245</v>
+        <v>1339</v>
       </c>
       <c r="B207" t="s">
-        <v>1253</v>
+        <v>1364</v>
       </c>
       <c r="C207" t="s">
-        <v>1255</v>
+        <v>1365</v>
       </c>
       <c r="D207" t="s">
-        <v>1254</v>
+        <v>1368</v>
       </c>
       <c r="E207" t="s">
-        <v>1256</v>
+        <v>1369</v>
       </c>
       <c r="F207" t="s">
         <v>48</v>
       </c>
       <c r="G207" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H207" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I207" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="J207" t="s">
         <v>280</v>
@@ -14535,7 +14529,7 @@
         <v>181</v>
       </c>
       <c r="M207" t="s">
-        <v>836</v>
+        <v>50</v>
       </c>
       <c r="N207" t="s">
         <v>14</v>
@@ -14549,19 +14543,19 @@
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>1246</v>
+        <v>259</v>
       </c>
       <c r="B208" t="s">
-        <v>1257</v>
+        <v>284</v>
       </c>
       <c r="C208" t="s">
-        <v>1258</v>
+        <v>1099</v>
       </c>
       <c r="D208" t="s">
-        <v>1254</v>
+        <v>285</v>
       </c>
       <c r="E208" t="s">
-        <v>1256</v>
+        <v>904</v>
       </c>
       <c r="F208" t="s">
         <v>48</v>
@@ -14576,16 +14570,13 @@
         <v>142</v>
       </c>
       <c r="J208" t="s">
-        <v>589</v>
-      </c>
-      <c r="K208" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="L208" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M208" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N208" t="s">
         <v>14</v>
@@ -14599,37 +14590,31 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>1271</v>
+        <v>1291</v>
       </c>
       <c r="B209" t="s">
-        <v>1274</v>
+        <v>1323</v>
       </c>
       <c r="C209" t="s">
-        <v>1276</v>
-      </c>
-      <c r="D209" t="s">
-        <v>687</v>
-      </c>
-      <c r="E209" t="s">
-        <v>1014</v>
+        <v>1324</v>
       </c>
       <c r="F209" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G209" t="s">
         <v>32</v>
       </c>
       <c r="H209" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I209" t="s">
-        <v>1279</v>
+        <v>142</v>
       </c>
       <c r="J209" t="s">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="L209" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M209" t="s">
         <v>49</v>
@@ -14646,13 +14631,19 @@
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B210" t="s">
-        <v>353</v>
+        <v>805</v>
       </c>
       <c r="C210" t="s">
-        <v>1184</v>
+        <v>1185</v>
+      </c>
+      <c r="D210" t="s">
+        <v>354</v>
+      </c>
+      <c r="E210" t="s">
+        <v>981</v>
       </c>
       <c r="F210" t="s">
         <v>79</v>
@@ -14664,13 +14655,16 @@
         <v>13</v>
       </c>
       <c r="I210" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="J210" t="s">
-        <v>432</v>
+        <v>524</v>
+      </c>
+      <c r="K210" t="s">
+        <v>76</v>
       </c>
       <c r="L210" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="M210" t="s">
         <v>49</v>
@@ -14687,22 +14681,22 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>409</v>
+        <v>670</v>
       </c>
       <c r="B211" t="s">
-        <v>804</v>
+        <v>690</v>
       </c>
       <c r="C211" t="s">
-        <v>1186</v>
+        <v>1216</v>
       </c>
       <c r="D211" t="s">
-        <v>415</v>
+        <v>691</v>
       </c>
       <c r="E211" t="s">
-        <v>982</v>
+        <v>1016</v>
       </c>
       <c r="F211" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G211" t="s">
         <v>52</v>
@@ -14711,16 +14705,16 @@
         <v>13</v>
       </c>
       <c r="I211" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="J211" t="s">
-        <v>533</v>
+        <v>280</v>
       </c>
       <c r="K211" t="s">
         <v>76</v>
       </c>
       <c r="L211" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M211" t="s">
         <v>49</v>
@@ -14737,25 +14731,25 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>462</v>
+        <v>250</v>
       </c>
       <c r="B212" t="s">
-        <v>468</v>
+        <v>260</v>
       </c>
       <c r="C212" t="s">
-        <v>468</v>
+        <v>1092</v>
       </c>
       <c r="D212" t="s">
-        <v>469</v>
+        <v>261</v>
       </c>
       <c r="E212" t="s">
-        <v>983</v>
+        <v>1033</v>
       </c>
       <c r="F212" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G212" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H212" t="s">
         <v>13</v>
@@ -14764,16 +14758,16 @@
         <v>142</v>
       </c>
       <c r="J212" t="s">
-        <v>264</v>
+        <v>208</v>
       </c>
       <c r="K212" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="L212" t="s">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="M212" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N212" t="s">
         <v>14</v>
@@ -14787,25 +14781,25 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B213" t="s">
-        <v>472</v>
+        <v>808</v>
       </c>
       <c r="C213" t="s">
-        <v>472</v>
+        <v>1190</v>
       </c>
       <c r="D213" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E213" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="F213" t="s">
         <v>79</v>
       </c>
       <c r="G213" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H213" t="s">
         <v>13</v>
@@ -14814,13 +14808,10 @@
         <v>142</v>
       </c>
       <c r="J213" t="s">
-        <v>264</v>
-      </c>
-      <c r="K213" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="L213" t="s">
-        <v>198</v>
+        <v>497</v>
       </c>
       <c r="M213" t="s">
         <v>49</v>
@@ -14837,13 +14828,19 @@
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>672</v>
+        <v>255</v>
       </c>
       <c r="B214" t="s">
-        <v>692</v>
+        <v>276</v>
       </c>
       <c r="C214" t="s">
-        <v>1187</v>
+        <v>1096</v>
+      </c>
+      <c r="D214" t="s">
+        <v>277</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1034</v>
       </c>
       <c r="F214" t="s">
         <v>48</v>
@@ -14858,13 +14855,13 @@
         <v>142</v>
       </c>
       <c r="J214" t="s">
-        <v>188</v>
+        <v>278</v>
       </c>
       <c r="K214" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L214" t="s">
-        <v>693</v>
+        <v>96</v>
       </c>
       <c r="M214" t="s">
         <v>49</v>
@@ -14881,25 +14878,25 @@
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>559</v>
+        <v>410</v>
       </c>
       <c r="B215" t="s">
-        <v>563</v>
+        <v>806</v>
       </c>
       <c r="C215" t="s">
-        <v>563</v>
+        <v>1188</v>
       </c>
       <c r="D215" t="s">
-        <v>564</v>
+        <v>807</v>
       </c>
       <c r="E215" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="F215" t="s">
         <v>79</v>
       </c>
       <c r="G215" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H215" t="s">
         <v>13</v>
@@ -14908,16 +14905,13 @@
         <v>142</v>
       </c>
       <c r="J215" t="s">
-        <v>490</v>
-      </c>
-      <c r="K215" t="s">
-        <v>76</v>
+        <v>493</v>
       </c>
       <c r="L215" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="M215" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N215" t="s">
         <v>14</v>
@@ -14931,22 +14925,22 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>259</v>
+        <v>594</v>
       </c>
       <c r="B216" t="s">
-        <v>284</v>
+        <v>600</v>
       </c>
       <c r="C216" t="s">
-        <v>1099</v>
+        <v>1202</v>
       </c>
       <c r="D216" t="s">
-        <v>285</v>
+        <v>601</v>
       </c>
       <c r="E216" t="s">
-        <v>904</v>
+        <v>997</v>
       </c>
       <c r="F216" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G216" t="s">
         <v>32</v>
@@ -14955,16 +14949,19 @@
         <v>13</v>
       </c>
       <c r="I216" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
       <c r="J216" t="s">
-        <v>111</v>
+        <v>602</v>
+      </c>
+      <c r="K216" t="s">
+        <v>54</v>
       </c>
       <c r="L216" t="s">
-        <v>96</v>
+        <v>497</v>
       </c>
       <c r="M216" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N216" t="s">
         <v>14</v>
@@ -14978,40 +14975,40 @@
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>355</v>
+        <v>674</v>
       </c>
       <c r="B217" t="s">
-        <v>370</v>
+        <v>694</v>
       </c>
       <c r="C217" t="s">
-        <v>370</v>
+        <v>1218</v>
       </c>
       <c r="D217" t="s">
-        <v>380</v>
+        <v>695</v>
       </c>
       <c r="E217" t="s">
-        <v>905</v>
+        <v>1018</v>
       </c>
       <c r="F217" t="s">
         <v>48</v>
       </c>
       <c r="G217" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H217" t="s">
         <v>31</v>
       </c>
       <c r="I217" t="s">
-        <v>371</v>
+        <v>109</v>
       </c>
       <c r="J217" t="s">
-        <v>432</v>
+        <v>280</v>
       </c>
       <c r="K217" t="s">
-        <v>207</v>
+        <v>418</v>
       </c>
       <c r="L217" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M217" t="s">
         <v>49</v>
@@ -15028,40 +15025,40 @@
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>341</v>
+        <v>502</v>
       </c>
       <c r="B218" t="s">
-        <v>805</v>
+        <v>508</v>
       </c>
       <c r="C218" t="s">
-        <v>1185</v>
+        <v>1130</v>
       </c>
       <c r="D218" t="s">
-        <v>354</v>
+        <v>509</v>
       </c>
       <c r="E218" t="s">
-        <v>981</v>
+        <v>931</v>
       </c>
       <c r="F218" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G218" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H218" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I218" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="J218" t="s">
-        <v>524</v>
+        <v>280</v>
       </c>
       <c r="K218" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L218" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M218" t="s">
         <v>49</v>
@@ -15078,22 +15075,22 @@
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>670</v>
+        <v>463</v>
       </c>
       <c r="B219" t="s">
-        <v>690</v>
+        <v>470</v>
       </c>
       <c r="C219" t="s">
-        <v>1216</v>
+        <v>1189</v>
       </c>
       <c r="D219" t="s">
-        <v>691</v>
+        <v>471</v>
       </c>
       <c r="E219" t="s">
-        <v>1016</v>
+        <v>986</v>
       </c>
       <c r="F219" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G219" t="s">
         <v>52</v>
@@ -15102,16 +15099,16 @@
         <v>13</v>
       </c>
       <c r="I219" t="s">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="J219" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="K219" t="s">
         <v>76</v>
       </c>
       <c r="L219" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M219" t="s">
         <v>49</v>
@@ -15128,43 +15125,40 @@
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>250</v>
+        <v>560</v>
       </c>
       <c r="B220" t="s">
-        <v>260</v>
+        <v>565</v>
       </c>
       <c r="C220" t="s">
-        <v>1092</v>
+        <v>1194</v>
       </c>
       <c r="D220" t="s">
-        <v>261</v>
+        <v>599</v>
       </c>
       <c r="E220" t="s">
-        <v>1033</v>
+        <v>991</v>
       </c>
       <c r="F220" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G220" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H220" t="s">
         <v>13</v>
       </c>
       <c r="I220" t="s">
-        <v>142</v>
-      </c>
-      <c r="J220" t="s">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="K220" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L220" t="s">
-        <v>268</v>
+        <v>198</v>
       </c>
       <c r="M220" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N220" t="s">
         <v>14</v>
@@ -15178,40 +15172,43 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="B221" t="s">
-        <v>808</v>
+        <v>450</v>
       </c>
       <c r="C221" t="s">
-        <v>1190</v>
+        <v>1117</v>
       </c>
       <c r="D221" t="s">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="E221" t="s">
-        <v>987</v>
+        <v>921</v>
       </c>
       <c r="F221" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G221" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H221" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I221" t="s">
-        <v>142</v>
+        <v>449</v>
       </c>
       <c r="J221" t="s">
-        <v>280</v>
+        <v>432</v>
+      </c>
+      <c r="K221" t="s">
+        <v>55</v>
       </c>
       <c r="L221" t="s">
-        <v>497</v>
+        <v>198</v>
       </c>
       <c r="M221" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N221" t="s">
         <v>14</v>
@@ -15225,43 +15222,43 @@
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>255</v>
+        <v>438</v>
       </c>
       <c r="B222" t="s">
-        <v>276</v>
+        <v>451</v>
       </c>
       <c r="C222" t="s">
-        <v>1096</v>
+        <v>1118</v>
       </c>
       <c r="D222" t="s">
-        <v>277</v>
+        <v>452</v>
       </c>
       <c r="E222" t="s">
-        <v>1034</v>
+        <v>922</v>
       </c>
       <c r="F222" t="s">
         <v>48</v>
       </c>
       <c r="G222" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H222" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I222" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="J222" t="s">
-        <v>278</v>
+        <v>526</v>
       </c>
       <c r="K222" t="s">
         <v>55</v>
       </c>
       <c r="L222" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M222" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N222" t="s">
         <v>14</v>
@@ -15275,37 +15272,40 @@
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
       <c r="B223" t="s">
-        <v>806</v>
+        <v>458</v>
       </c>
       <c r="C223" t="s">
-        <v>1188</v>
+        <v>1120</v>
       </c>
       <c r="D223" t="s">
-        <v>807</v>
+        <v>459</v>
       </c>
       <c r="E223" t="s">
-        <v>984</v>
+        <v>924</v>
       </c>
       <c r="F223" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G223" t="s">
         <v>32</v>
       </c>
       <c r="H223" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I223" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J223" t="s">
-        <v>493</v>
+        <v>528</v>
+      </c>
+      <c r="K223" t="s">
+        <v>55</v>
       </c>
       <c r="L223" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M223" t="s">
         <v>49</v>
@@ -15322,43 +15322,43 @@
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B224" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C224" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D224" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E224" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F224" t="s">
         <v>79</v>
       </c>
       <c r="G224" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H224" t="s">
         <v>13</v>
       </c>
       <c r="I224" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J224" t="s">
-        <v>602</v>
+        <v>491</v>
       </c>
       <c r="K224" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L224" t="s">
-        <v>497</v>
+        <v>189</v>
       </c>
       <c r="M224" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N224" t="s">
         <v>14</v>
@@ -15372,19 +15372,19 @@
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>674</v>
+        <v>1250</v>
       </c>
       <c r="B225" t="s">
-        <v>694</v>
+        <v>1266</v>
       </c>
       <c r="C225" t="s">
-        <v>1218</v>
+        <v>1267</v>
       </c>
       <c r="D225" t="s">
-        <v>695</v>
+        <v>459</v>
       </c>
       <c r="E225" t="s">
-        <v>1018</v>
+        <v>924</v>
       </c>
       <c r="F225" t="s">
         <v>48</v>
@@ -15396,16 +15396,13 @@
         <v>31</v>
       </c>
       <c r="I225" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="J225" t="s">
-        <v>280</v>
-      </c>
-      <c r="K225" t="s">
-        <v>418</v>
+        <v>1268</v>
       </c>
       <c r="L225" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M225" t="s">
         <v>49</v>
@@ -15422,19 +15419,13 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>502</v>
+        <v>1337</v>
       </c>
       <c r="B226" t="s">
-        <v>508</v>
+        <v>1360</v>
       </c>
       <c r="C226" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D226" t="s">
-        <v>509</v>
-      </c>
-      <c r="E226" t="s">
-        <v>931</v>
+        <v>1361</v>
       </c>
       <c r="F226" t="s">
         <v>48</v>
@@ -15446,10 +15437,10 @@
         <v>31</v>
       </c>
       <c r="I226" t="s">
-        <v>144</v>
+        <v>1279</v>
       </c>
       <c r="J226" t="s">
-        <v>280</v>
+        <v>1268</v>
       </c>
       <c r="K226" t="s">
         <v>55</v>
@@ -15472,19 +15463,19 @@
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>463</v>
+        <v>622</v>
       </c>
       <c r="B227" t="s">
-        <v>470</v>
+        <v>631</v>
       </c>
       <c r="C227" t="s">
-        <v>1189</v>
+        <v>1205</v>
       </c>
       <c r="D227" t="s">
-        <v>471</v>
+        <v>632</v>
       </c>
       <c r="E227" t="s">
-        <v>986</v>
+        <v>1000</v>
       </c>
       <c r="F227" t="s">
         <v>79</v>
@@ -15496,19 +15487,16 @@
         <v>13</v>
       </c>
       <c r="I227" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="J227" t="s">
-        <v>309</v>
-      </c>
-      <c r="K227" t="s">
-        <v>76</v>
+        <v>524</v>
       </c>
       <c r="L227" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="M227" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N227" t="s">
         <v>14</v>
@@ -15522,40 +15510,37 @@
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>560</v>
+        <v>614</v>
       </c>
       <c r="B228" t="s">
-        <v>565</v>
+        <v>660</v>
       </c>
       <c r="C228" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D228" t="s">
-        <v>599</v>
-      </c>
-      <c r="E228" t="s">
-        <v>991</v>
+        <v>1211</v>
       </c>
       <c r="F228" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G228" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H228" t="s">
         <v>13</v>
       </c>
       <c r="I228" t="s">
-        <v>110</v>
+        <v>142</v>
+      </c>
+      <c r="J228" t="s">
+        <v>203</v>
       </c>
       <c r="K228" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L228" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M228" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N228" t="s">
         <v>14</v>
@@ -15569,43 +15554,43 @@
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>437</v>
+        <v>666</v>
       </c>
       <c r="B229" t="s">
-        <v>450</v>
+        <v>682</v>
       </c>
       <c r="C229" t="s">
-        <v>1117</v>
+        <v>1213</v>
       </c>
       <c r="D229" t="s">
-        <v>448</v>
+        <v>683</v>
       </c>
       <c r="E229" t="s">
-        <v>921</v>
+        <v>1012</v>
       </c>
       <c r="F229" t="s">
         <v>48</v>
       </c>
       <c r="G229" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H229" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I229" t="s">
-        <v>449</v>
+        <v>142</v>
       </c>
       <c r="J229" t="s">
-        <v>432</v>
+        <v>204</v>
       </c>
       <c r="K229" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="L229" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="M229" t="s">
-        <v>837</v>
+        <v>49</v>
       </c>
       <c r="N229" t="s">
         <v>14</v>
@@ -15619,43 +15604,40 @@
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>438</v>
+        <v>571</v>
       </c>
       <c r="B230" t="s">
-        <v>451</v>
+        <v>575</v>
       </c>
       <c r="C230" t="s">
-        <v>1118</v>
+        <v>1196</v>
       </c>
       <c r="D230" t="s">
-        <v>452</v>
+        <v>386</v>
       </c>
       <c r="E230" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="F230" t="s">
         <v>48</v>
       </c>
       <c r="G230" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H230" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I230" t="s">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="J230" t="s">
-        <v>526</v>
-      </c>
-      <c r="K230" t="s">
-        <v>55</v>
+        <v>204</v>
       </c>
       <c r="L230" t="s">
         <v>181</v>
       </c>
       <c r="M230" t="s">
-        <v>50</v>
+        <v>836</v>
       </c>
       <c r="N230" t="s">
         <v>14</v>
@@ -15669,43 +15651,40 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>441</v>
+        <v>365</v>
       </c>
       <c r="B231" t="s">
-        <v>458</v>
+        <v>387</v>
       </c>
       <c r="C231" t="s">
-        <v>1120</v>
+        <v>1104</v>
       </c>
       <c r="D231" t="s">
-        <v>459</v>
+        <v>388</v>
       </c>
       <c r="E231" t="s">
-        <v>924</v>
+        <v>910</v>
       </c>
       <c r="F231" t="s">
         <v>48</v>
       </c>
       <c r="G231" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H231" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I231" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J231" t="s">
-        <v>528</v>
-      </c>
-      <c r="K231" t="s">
-        <v>55</v>
+        <v>523</v>
       </c>
       <c r="L231" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M231" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N231" t="s">
         <v>14</v>
@@ -15719,25 +15698,25 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>595</v>
+        <v>366</v>
       </c>
       <c r="B232" t="s">
-        <v>604</v>
+        <v>390</v>
       </c>
       <c r="C232" t="s">
-        <v>1203</v>
+        <v>1105</v>
       </c>
       <c r="D232" t="s">
-        <v>605</v>
+        <v>391</v>
       </c>
       <c r="E232" t="s">
-        <v>998</v>
+        <v>911</v>
       </c>
       <c r="F232" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G232" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="H232" t="s">
         <v>13</v>
@@ -15746,16 +15725,16 @@
         <v>142</v>
       </c>
       <c r="J232" t="s">
-        <v>491</v>
+        <v>203</v>
       </c>
       <c r="K232" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L232" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M232" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N232" t="s">
         <v>14</v>
@@ -15769,19 +15748,19 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>1250</v>
+        <v>572</v>
       </c>
       <c r="B233" t="s">
-        <v>1266</v>
+        <v>576</v>
       </c>
       <c r="C233" t="s">
-        <v>1267</v>
+        <v>1197</v>
       </c>
       <c r="D233" t="s">
-        <v>459</v>
+        <v>386</v>
       </c>
       <c r="E233" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="F233" t="s">
         <v>48</v>
@@ -15790,16 +15769,16 @@
         <v>32</v>
       </c>
       <c r="H233" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I233" t="s">
-        <v>144</v>
+        <v>271</v>
       </c>
       <c r="J233" t="s">
-        <v>1268</v>
+        <v>524</v>
       </c>
       <c r="L233" t="s">
-        <v>96</v>
+        <v>578</v>
       </c>
       <c r="M233" t="s">
         <v>49</v>
@@ -15816,13 +15795,19 @@
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>1337</v>
+        <v>582</v>
       </c>
       <c r="B234" t="s">
-        <v>1360</v>
+        <v>586</v>
       </c>
       <c r="C234" t="s">
-        <v>1361</v>
+        <v>1198</v>
+      </c>
+      <c r="D234" t="s">
+        <v>587</v>
+      </c>
+      <c r="E234" t="s">
+        <v>994</v>
       </c>
       <c r="F234" t="s">
         <v>48</v>
@@ -15831,16 +15816,16 @@
         <v>32</v>
       </c>
       <c r="H234" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I234" t="s">
-        <v>1279</v>
+        <v>142</v>
       </c>
       <c r="J234" t="s">
-        <v>1268</v>
+        <v>491</v>
       </c>
       <c r="K234" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="L234" t="s">
         <v>181</v>
@@ -15860,25 +15845,25 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="B235" t="s">
-        <v>606</v>
+        <v>814</v>
       </c>
       <c r="C235" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="D235" t="s">
-        <v>607</v>
+        <v>642</v>
       </c>
       <c r="E235" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="F235" t="s">
         <v>79</v>
       </c>
       <c r="G235" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H235" t="s">
         <v>13</v>
@@ -15887,16 +15872,16 @@
         <v>142</v>
       </c>
       <c r="J235" t="s">
-        <v>280</v>
+        <v>203</v>
       </c>
       <c r="K235" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="L235" t="s">
-        <v>96</v>
+        <v>334</v>
       </c>
       <c r="M235" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N235" t="s">
         <v>14</v>
@@ -15910,25 +15895,25 @@
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>622</v>
+        <v>192</v>
       </c>
       <c r="B236" t="s">
-        <v>631</v>
+        <v>201</v>
       </c>
       <c r="C236" t="s">
-        <v>1205</v>
+        <v>1081</v>
       </c>
       <c r="D236" t="s">
-        <v>632</v>
+        <v>202</v>
       </c>
       <c r="E236" t="s">
-        <v>1000</v>
+        <v>891</v>
       </c>
       <c r="F236" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G236" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H236" t="s">
         <v>13</v>
@@ -15937,13 +15922,16 @@
         <v>142</v>
       </c>
       <c r="J236" t="s">
-        <v>524</v>
+        <v>203</v>
+      </c>
+      <c r="K236" t="s">
+        <v>54</v>
       </c>
       <c r="L236" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M236" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N236" t="s">
         <v>14</v>
@@ -15957,13 +15945,19 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>614</v>
+        <v>193</v>
       </c>
       <c r="B237" t="s">
-        <v>660</v>
+        <v>205</v>
       </c>
       <c r="C237" t="s">
-        <v>1211</v>
+        <v>1082</v>
+      </c>
+      <c r="D237" t="s">
+        <v>206</v>
+      </c>
+      <c r="E237" t="s">
+        <v>892</v>
       </c>
       <c r="F237" t="s">
         <v>48</v>
@@ -15972,13 +15966,13 @@
         <v>32</v>
       </c>
       <c r="H237" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I237" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J237" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="K237" t="s">
         <v>55</v>
@@ -15987,7 +15981,7 @@
         <v>181</v>
       </c>
       <c r="M237" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N237" t="s">
         <v>14</v>
@@ -16001,25 +15995,25 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>666</v>
+        <v>194</v>
       </c>
       <c r="B238" t="s">
-        <v>682</v>
+        <v>209</v>
       </c>
       <c r="C238" t="s">
-        <v>1213</v>
+        <v>1083</v>
       </c>
       <c r="D238" t="s">
-        <v>683</v>
+        <v>210</v>
       </c>
       <c r="E238" t="s">
-        <v>1012</v>
+        <v>893</v>
       </c>
       <c r="F238" t="s">
         <v>48</v>
       </c>
       <c r="G238" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H238" t="s">
         <v>13</v>
@@ -16028,13 +16022,13 @@
         <v>142</v>
       </c>
       <c r="J238" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K238" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="L238" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M238" t="s">
         <v>49</v>
@@ -16051,19 +16045,19 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>571</v>
+        <v>191</v>
       </c>
       <c r="B239" t="s">
-        <v>575</v>
+        <v>199</v>
       </c>
       <c r="C239" t="s">
-        <v>1196</v>
+        <v>1080</v>
       </c>
       <c r="D239" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E239" t="s">
-        <v>909</v>
+        <v>890</v>
       </c>
       <c r="F239" t="s">
         <v>48</v>
@@ -16072,19 +16066,22 @@
         <v>32</v>
       </c>
       <c r="H239" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I239" t="s">
-        <v>271</v>
+        <v>109</v>
       </c>
       <c r="J239" t="s">
         <v>204</v>
       </c>
+      <c r="K239" t="s">
+        <v>54</v>
+      </c>
       <c r="L239" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M239" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N239" t="s">
         <v>14</v>
@@ -16098,37 +16095,37 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>572</v>
+        <v>626</v>
       </c>
       <c r="B240" t="s">
-        <v>576</v>
+        <v>643</v>
       </c>
       <c r="C240" t="s">
-        <v>1197</v>
+        <v>1207</v>
       </c>
       <c r="D240" t="s">
-        <v>386</v>
+        <v>644</v>
       </c>
       <c r="E240" t="s">
-        <v>909</v>
+        <v>1002</v>
       </c>
       <c r="F240" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G240" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H240" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I240" t="s">
-        <v>271</v>
+        <v>221</v>
       </c>
       <c r="J240" t="s">
-        <v>524</v>
+        <v>204</v>
       </c>
       <c r="L240" t="s">
-        <v>578</v>
+        <v>96</v>
       </c>
       <c r="M240" t="s">
         <v>49</v>
@@ -16145,40 +16142,37 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="B241" t="s">
-        <v>586</v>
+        <v>645</v>
       </c>
       <c r="C241" t="s">
-        <v>1198</v>
+        <v>1208</v>
       </c>
       <c r="D241" t="s">
-        <v>587</v>
+        <v>646</v>
       </c>
       <c r="E241" t="s">
-        <v>994</v>
+        <v>1047</v>
       </c>
       <c r="F241" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G241" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H241" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I241" t="s">
-        <v>142</v>
+        <v>449</v>
       </c>
       <c r="J241" t="s">
-        <v>491</v>
-      </c>
-      <c r="K241" t="s">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="L241" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M241" t="s">
         <v>49</v>
@@ -16195,40 +16189,40 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>625</v>
+        <v>678</v>
       </c>
       <c r="B242" t="s">
-        <v>814</v>
+        <v>700</v>
       </c>
       <c r="C242" t="s">
-        <v>1206</v>
+        <v>1220</v>
       </c>
       <c r="D242" t="s">
-        <v>642</v>
+        <v>703</v>
       </c>
       <c r="E242" t="s">
-        <v>1001</v>
+        <v>1020</v>
       </c>
       <c r="F242" t="s">
         <v>79</v>
       </c>
       <c r="G242" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H242" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I242" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J242" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K242" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L242" t="s">
-        <v>334</v>
+        <v>96</v>
       </c>
       <c r="M242" t="s">
         <v>49</v>
@@ -16245,19 +16239,19 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>192</v>
+        <v>1289</v>
       </c>
       <c r="B243" t="s">
-        <v>201</v>
+        <v>1317</v>
       </c>
       <c r="C243" t="s">
-        <v>1081</v>
+        <v>1318</v>
       </c>
       <c r="D243" t="s">
-        <v>202</v>
+        <v>1319</v>
       </c>
       <c r="E243" t="s">
-        <v>891</v>
+        <v>1313</v>
       </c>
       <c r="F243" t="s">
         <v>48</v>
@@ -16266,22 +16260,22 @@
         <v>32</v>
       </c>
       <c r="H243" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I243" t="s">
-        <v>142</v>
+        <v>1320</v>
       </c>
       <c r="J243" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K243" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="L243" t="s">
         <v>181</v>
       </c>
       <c r="M243" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N243" t="s">
         <v>14</v>
@@ -16295,43 +16289,43 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>193</v>
+        <v>1294</v>
       </c>
       <c r="B244" t="s">
-        <v>205</v>
+        <v>1298</v>
       </c>
       <c r="C244" t="s">
-        <v>1082</v>
+        <v>1299</v>
       </c>
       <c r="D244" t="s">
-        <v>206</v>
+        <v>1300</v>
       </c>
       <c r="E244" t="s">
-        <v>892</v>
+        <v>1301</v>
       </c>
       <c r="F244" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G244" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H244" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I244" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J244" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K244" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L244" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M244" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N244" t="s">
         <v>14</v>
@@ -16345,19 +16339,13 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>194</v>
+        <v>1340</v>
       </c>
       <c r="B245" t="s">
-        <v>209</v>
+        <v>1366</v>
       </c>
       <c r="C245" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D245" t="s">
-        <v>210</v>
-      </c>
-      <c r="E245" t="s">
-        <v>893</v>
+        <v>1367</v>
       </c>
       <c r="F245" t="s">
         <v>48</v>
@@ -16372,13 +16360,10 @@
         <v>142</v>
       </c>
       <c r="J245" t="s">
-        <v>203</v>
-      </c>
-      <c r="K245" t="s">
-        <v>54</v>
+        <v>524</v>
       </c>
       <c r="L245" t="s">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="M245" t="s">
         <v>49</v>
@@ -16395,19 +16380,19 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>191</v>
+        <v>612</v>
       </c>
       <c r="B246" t="s">
-        <v>199</v>
+        <v>653</v>
       </c>
       <c r="C246" t="s">
-        <v>1080</v>
+        <v>1210</v>
       </c>
       <c r="D246" t="s">
-        <v>200</v>
+        <v>446</v>
       </c>
       <c r="E246" t="s">
-        <v>890</v>
+        <v>920</v>
       </c>
       <c r="F246" t="s">
         <v>48</v>
@@ -16416,19 +16401,16 @@
         <v>32</v>
       </c>
       <c r="H246" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I246" t="s">
-        <v>109</v>
-      </c>
-      <c r="J246" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="K246" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L246" t="s">
-        <v>389</v>
+        <v>182</v>
       </c>
       <c r="M246" t="s">
         <v>49</v>
@@ -16445,37 +16427,40 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>626</v>
+        <v>434</v>
       </c>
       <c r="B247" t="s">
-        <v>643</v>
+        <v>443</v>
       </c>
       <c r="C247" t="s">
-        <v>1207</v>
+        <v>1114</v>
       </c>
       <c r="D247" t="s">
-        <v>644</v>
+        <v>446</v>
       </c>
       <c r="E247" t="s">
-        <v>1002</v>
+        <v>920</v>
       </c>
       <c r="F247" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G247" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H247" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I247" t="s">
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="J247" t="s">
-        <v>204</v>
+        <v>444</v>
+      </c>
+      <c r="K247" t="s">
+        <v>55</v>
       </c>
       <c r="L247" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M247" t="s">
         <v>49</v>
@@ -16492,37 +16477,40 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>627</v>
+        <v>435</v>
       </c>
       <c r="B248" t="s">
-        <v>645</v>
+        <v>445</v>
       </c>
       <c r="C248" t="s">
-        <v>1208</v>
+        <v>1115</v>
       </c>
       <c r="D248" t="s">
-        <v>646</v>
+        <v>446</v>
       </c>
       <c r="E248" t="s">
-        <v>1047</v>
+        <v>920</v>
       </c>
       <c r="F248" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G248" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H248" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I248" t="s">
-        <v>449</v>
+        <v>110</v>
       </c>
       <c r="J248" t="s">
         <v>204</v>
       </c>
+      <c r="K248" t="s">
+        <v>55</v>
+      </c>
       <c r="L248" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M248" t="s">
         <v>49</v>
@@ -16539,43 +16527,43 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>678</v>
+        <v>442</v>
       </c>
       <c r="B249" t="s">
-        <v>700</v>
+        <v>460</v>
       </c>
       <c r="C249" t="s">
-        <v>1220</v>
+        <v>1121</v>
       </c>
       <c r="D249" t="s">
-        <v>703</v>
+        <v>446</v>
       </c>
       <c r="E249" t="s">
-        <v>1020</v>
+        <v>920</v>
       </c>
       <c r="F249" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G249" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H249" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I249" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="J249" t="s">
         <v>204</v>
       </c>
       <c r="K249" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="L249" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M249" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N249" t="s">
         <v>14</v>
@@ -16589,19 +16577,19 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>1289</v>
+        <v>669</v>
       </c>
       <c r="B250" t="s">
-        <v>1317</v>
+        <v>688</v>
       </c>
       <c r="C250" t="s">
-        <v>1318</v>
+        <v>688</v>
       </c>
       <c r="D250" t="s">
-        <v>1319</v>
+        <v>689</v>
       </c>
       <c r="E250" t="s">
-        <v>1313</v>
+        <v>1015</v>
       </c>
       <c r="F250" t="s">
         <v>48</v>
@@ -16610,22 +16598,22 @@
         <v>32</v>
       </c>
       <c r="H250" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I250" t="s">
-        <v>1320</v>
+        <v>449</v>
       </c>
       <c r="J250" t="s">
         <v>204</v>
       </c>
       <c r="K250" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="L250" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M250" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N250" t="s">
         <v>14</v>
@@ -16639,43 +16627,43 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>1294</v>
+        <v>673</v>
       </c>
       <c r="B251" t="s">
-        <v>1298</v>
+        <v>824</v>
       </c>
       <c r="C251" t="s">
-        <v>1299</v>
+        <v>1217</v>
       </c>
       <c r="D251" t="s">
-        <v>1300</v>
+        <v>689</v>
       </c>
       <c r="E251" t="s">
-        <v>1301</v>
+        <v>1015</v>
       </c>
       <c r="F251" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G251" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H251" t="s">
         <v>13</v>
       </c>
       <c r="I251" t="s">
-        <v>142</v>
+        <v>449</v>
       </c>
       <c r="J251" t="s">
         <v>204</v>
       </c>
       <c r="K251" t="s">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="L251" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="M251" t="s">
-        <v>836</v>
+        <v>49</v>
       </c>
       <c r="N251" t="s">
         <v>14</v>
@@ -16689,31 +16677,40 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>1340</v>
+        <v>440</v>
       </c>
       <c r="B252" t="s">
-        <v>1366</v>
+        <v>456</v>
       </c>
       <c r="C252" t="s">
-        <v>1367</v>
+        <v>1119</v>
+      </c>
+      <c r="D252" t="s">
+        <v>457</v>
+      </c>
+      <c r="E252" t="s">
+        <v>923</v>
       </c>
       <c r="F252" t="s">
         <v>48</v>
       </c>
       <c r="G252" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H252" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I252" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J252" t="s">
-        <v>524</v>
+        <v>204</v>
+      </c>
+      <c r="K252" t="s">
+        <v>55</v>
       </c>
       <c r="L252" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M252" t="s">
         <v>49</v>
@@ -16730,31 +16727,25 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>440</v>
+        <v>1244</v>
       </c>
       <c r="B253" t="s">
-        <v>456</v>
+        <v>1252</v>
       </c>
       <c r="C253" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D253" t="s">
-        <v>457</v>
-      </c>
-      <c r="E253" t="s">
-        <v>923</v>
+        <v>1252</v>
       </c>
       <c r="F253" t="s">
         <v>48</v>
       </c>
       <c r="G253" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="H253" t="s">
         <v>31</v>
       </c>
       <c r="I253" t="s">
-        <v>144</v>
+        <v>449</v>
       </c>
       <c r="J253" t="s">
         <v>204</v>
@@ -16780,13 +16771,19 @@
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>1244</v>
+        <v>611</v>
       </c>
       <c r="B254" t="s">
-        <v>1252</v>
+        <v>652</v>
       </c>
       <c r="C254" t="s">
-        <v>1252</v>
+        <v>652</v>
+      </c>
+      <c r="D254" t="s">
+        <v>816</v>
+      </c>
+      <c r="E254" t="s">
+        <v>1005</v>
       </c>
       <c r="F254" t="s">
         <v>48</v>
@@ -16795,13 +16792,10 @@
         <v>32</v>
       </c>
       <c r="H254" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I254" t="s">
-        <v>449</v>
-      </c>
-      <c r="J254" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="K254" t="s">
         <v>55</v>
@@ -16810,7 +16804,7 @@
         <v>181</v>
       </c>
       <c r="M254" t="s">
-        <v>49</v>
+        <v>837</v>
       </c>
       <c r="N254" t="s">
         <v>14</v>
@@ -16824,34 +16818,37 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>610</v>
+        <v>364</v>
       </c>
       <c r="B255" t="s">
-        <v>650</v>
+        <v>385</v>
       </c>
       <c r="C255" t="s">
-        <v>1209</v>
+        <v>1103</v>
       </c>
       <c r="D255" t="s">
-        <v>651</v>
+        <v>386</v>
       </c>
       <c r="E255" t="s">
-        <v>1004</v>
+        <v>909</v>
       </c>
       <c r="F255" t="s">
         <v>48</v>
       </c>
       <c r="G255" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H255" t="s">
         <v>13</v>
       </c>
       <c r="I255" t="s">
-        <v>142</v>
+        <v>271</v>
+      </c>
+      <c r="J255" t="s">
+        <v>491</v>
       </c>
       <c r="L255" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="M255" t="s">
         <v>49</v>
@@ -16868,25 +16865,25 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>611</v>
+        <v>677</v>
       </c>
       <c r="B256" t="s">
-        <v>652</v>
+        <v>698</v>
       </c>
       <c r="C256" t="s">
-        <v>652</v>
+        <v>1219</v>
       </c>
       <c r="D256" t="s">
-        <v>816</v>
+        <v>702</v>
       </c>
       <c r="E256" t="s">
-        <v>1005</v>
+        <v>1019</v>
       </c>
       <c r="F256" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G256" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H256" t="s">
         <v>13</v>
@@ -16894,11 +16891,11 @@
       <c r="I256" t="s">
         <v>142</v>
       </c>
-      <c r="K256" t="s">
-        <v>55</v>
+      <c r="J256" t="s">
+        <v>699</v>
       </c>
       <c r="L256" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M256" t="s">
         <v>837</v>
@@ -16915,22 +16912,22 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>612</v>
+        <v>704</v>
       </c>
       <c r="B257" t="s">
-        <v>653</v>
+        <v>708</v>
       </c>
       <c r="C257" t="s">
-        <v>1210</v>
+        <v>1221</v>
       </c>
       <c r="D257" t="s">
-        <v>446</v>
+        <v>710</v>
       </c>
       <c r="E257" t="s">
-        <v>920</v>
+        <v>1021</v>
       </c>
       <c r="F257" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G257" t="s">
         <v>32</v>
@@ -16939,16 +16936,16 @@
         <v>13</v>
       </c>
       <c r="I257" t="s">
-        <v>110</v>
-      </c>
-      <c r="K257" t="s">
-        <v>55</v>
+        <v>142</v>
+      </c>
+      <c r="J257" t="s">
+        <v>524</v>
       </c>
       <c r="L257" t="s">
-        <v>182</v>
+        <v>344</v>
       </c>
       <c r="M257" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N257" t="s">
         <v>14</v>
@@ -16962,40 +16959,40 @@
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>669</v>
+        <v>583</v>
       </c>
       <c r="B258" t="s">
-        <v>688</v>
+        <v>588</v>
       </c>
       <c r="C258" t="s">
-        <v>688</v>
+        <v>1199</v>
       </c>
       <c r="D258" t="s">
-        <v>689</v>
+        <v>551</v>
       </c>
       <c r="E258" t="s">
-        <v>1015</v>
+        <v>985</v>
       </c>
       <c r="F258" t="s">
         <v>48</v>
       </c>
       <c r="G258" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H258" t="s">
         <v>13</v>
       </c>
       <c r="I258" t="s">
-        <v>449</v>
+        <v>142</v>
       </c>
       <c r="J258" t="s">
-        <v>204</v>
+        <v>589</v>
       </c>
       <c r="K258" t="s">
         <v>134</v>
       </c>
       <c r="L258" t="s">
-        <v>389</v>
+        <v>181</v>
       </c>
       <c r="M258" t="s">
         <v>49</v>
@@ -17012,40 +17009,40 @@
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>673</v>
+        <v>562</v>
       </c>
       <c r="B259" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="C259" t="s">
-        <v>1217</v>
+        <v>1239</v>
       </c>
       <c r="D259" t="s">
-        <v>689</v>
+        <v>567</v>
       </c>
       <c r="E259" t="s">
-        <v>1015</v>
+        <v>993</v>
       </c>
       <c r="F259" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G259" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H259" t="s">
         <v>13</v>
       </c>
       <c r="I259" t="s">
-        <v>449</v>
+        <v>142</v>
       </c>
       <c r="J259" t="s">
-        <v>204</v>
+        <v>491</v>
       </c>
       <c r="K259" t="s">
-        <v>207</v>
+        <v>76</v>
       </c>
       <c r="L259" t="s">
-        <v>182</v>
+        <v>568</v>
       </c>
       <c r="M259" t="s">
         <v>49</v>
@@ -17062,25 +17059,25 @@
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>677</v>
+        <v>705</v>
       </c>
       <c r="B260" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="C260" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="D260" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="E260" t="s">
-        <v>1019</v>
+        <v>1048</v>
       </c>
       <c r="F260" t="s">
         <v>79</v>
       </c>
       <c r="G260" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H260" t="s">
         <v>13</v>
@@ -17089,13 +17086,13 @@
         <v>142</v>
       </c>
       <c r="J260" t="s">
-        <v>699</v>
+        <v>491</v>
       </c>
       <c r="L260" t="s">
         <v>189</v>
       </c>
       <c r="M260" t="s">
-        <v>837</v>
+        <v>50</v>
       </c>
       <c r="N260" t="s">
         <v>14</v>
@@ -17109,25 +17106,25 @@
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>704</v>
+        <v>1296</v>
       </c>
       <c r="B261" t="s">
-        <v>708</v>
+        <v>1304</v>
       </c>
       <c r="C261" t="s">
-        <v>1221</v>
+        <v>1305</v>
       </c>
       <c r="D261" t="s">
-        <v>710</v>
+        <v>1306</v>
       </c>
       <c r="E261" t="s">
-        <v>1021</v>
+        <v>1307</v>
       </c>
       <c r="F261" t="s">
         <v>79</v>
       </c>
       <c r="G261" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H261" t="s">
         <v>13</v>
@@ -17136,13 +17133,16 @@
         <v>142</v>
       </c>
       <c r="J261" t="s">
-        <v>524</v>
+        <v>491</v>
+      </c>
+      <c r="K261" t="s">
+        <v>76</v>
       </c>
       <c r="L261" t="s">
-        <v>344</v>
+        <v>189</v>
       </c>
       <c r="M261" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N261" t="s">
         <v>14</v>
@@ -17156,37 +17156,31 @@
     </row>
     <row r="262" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>583</v>
+        <v>719</v>
       </c>
       <c r="B262" t="s">
-        <v>588</v>
+        <v>744</v>
       </c>
       <c r="C262" t="s">
-        <v>1199</v>
+        <v>1223</v>
       </c>
       <c r="D262" t="s">
-        <v>551</v>
+        <v>747</v>
       </c>
       <c r="E262" t="s">
-        <v>985</v>
+        <v>1022</v>
       </c>
       <c r="F262" t="s">
         <v>48</v>
       </c>
       <c r="G262" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H262" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I262" t="s">
-        <v>142</v>
-      </c>
-      <c r="J262" t="s">
-        <v>589</v>
-      </c>
-      <c r="K262" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="L262" t="s">
         <v>181</v>
@@ -17206,22 +17200,22 @@
     </row>
     <row r="263" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>562</v>
+        <v>725</v>
       </c>
       <c r="B263" t="s">
-        <v>811</v>
+        <v>738</v>
       </c>
       <c r="C263" t="s">
-        <v>1239</v>
+        <v>1230</v>
       </c>
       <c r="D263" t="s">
-        <v>567</v>
+        <v>750</v>
       </c>
       <c r="E263" t="s">
-        <v>993</v>
+        <v>1025</v>
       </c>
       <c r="F263" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G263" t="s">
         <v>52</v>
@@ -17239,7 +17233,7 @@
         <v>76</v>
       </c>
       <c r="L263" t="s">
-        <v>568</v>
+        <v>198</v>
       </c>
       <c r="M263" t="s">
         <v>49</v>
@@ -17256,25 +17250,25 @@
     </row>
     <row r="264" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>705</v>
+        <v>731</v>
       </c>
       <c r="B264" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="C264" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="D264" t="s">
-        <v>711</v>
+        <v>751</v>
       </c>
       <c r="E264" t="s">
-        <v>1048</v>
+        <v>1026</v>
       </c>
       <c r="F264" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G264" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H264" t="s">
         <v>13</v>
@@ -17283,13 +17277,16 @@
         <v>142</v>
       </c>
       <c r="J264" t="s">
-        <v>491</v>
+        <v>524</v>
+      </c>
+      <c r="K264" t="s">
+        <v>141</v>
       </c>
       <c r="L264" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M264" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N264" t="s">
         <v>14</v>
@@ -17303,40 +17300,37 @@
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>1296</v>
+        <v>1273</v>
       </c>
       <c r="B265" t="s">
-        <v>1304</v>
+        <v>1280</v>
       </c>
       <c r="C265" t="s">
-        <v>1305</v>
+        <v>1278</v>
       </c>
       <c r="D265" t="s">
-        <v>1306</v>
+        <v>1281</v>
       </c>
       <c r="E265" t="s">
-        <v>1307</v>
+        <v>1281</v>
       </c>
       <c r="F265" t="s">
         <v>79</v>
       </c>
       <c r="G265" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H265" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I265" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J265" t="s">
-        <v>491</v>
-      </c>
-      <c r="K265" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="L265" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="M265" t="s">
         <v>49</v>
@@ -17353,34 +17347,34 @@
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>719</v>
+        <v>1293</v>
       </c>
       <c r="B266" t="s">
-        <v>744</v>
+        <v>1297</v>
       </c>
       <c r="C266" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D266" t="s">
-        <v>747</v>
-      </c>
-      <c r="E266" t="s">
-        <v>1022</v>
+        <v>1308</v>
       </c>
       <c r="F266" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G266" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H266" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I266" t="s">
-        <v>220</v>
+        <v>110</v>
+      </c>
+      <c r="J266" t="s">
+        <v>111</v>
+      </c>
+      <c r="K266" t="s">
+        <v>76</v>
       </c>
       <c r="L266" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M266" t="s">
         <v>49</v>
@@ -17397,19 +17391,19 @@
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>725</v>
+        <v>1328</v>
       </c>
       <c r="B267" t="s">
-        <v>738</v>
+        <v>1343</v>
       </c>
       <c r="C267" t="s">
-        <v>1230</v>
+        <v>1351</v>
       </c>
       <c r="D267" t="s">
-        <v>750</v>
+        <v>386</v>
       </c>
       <c r="E267" t="s">
-        <v>1025</v>
+        <v>909</v>
       </c>
       <c r="F267" t="s">
         <v>48</v>
@@ -17426,11 +17420,8 @@
       <c r="J267" t="s">
         <v>491</v>
       </c>
-      <c r="K267" t="s">
-        <v>76</v>
-      </c>
       <c r="L267" t="s">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="M267" t="s">
         <v>49</v>
@@ -17447,25 +17438,25 @@
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>731</v>
+        <v>396</v>
       </c>
       <c r="B268" t="s">
-        <v>734</v>
+        <v>790</v>
       </c>
       <c r="C268" t="s">
-        <v>1232</v>
+        <v>1109</v>
       </c>
       <c r="D268" t="s">
-        <v>751</v>
+        <v>401</v>
       </c>
       <c r="E268" t="s">
-        <v>1026</v>
+        <v>913</v>
       </c>
       <c r="F268" t="s">
         <v>48</v>
       </c>
       <c r="G268" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H268" t="s">
         <v>13</v>
@@ -17476,9 +17467,6 @@
       <c r="J268" t="s">
         <v>524</v>
       </c>
-      <c r="K268" t="s">
-        <v>141</v>
-      </c>
       <c r="L268" t="s">
         <v>181</v>
       </c>
@@ -17497,37 +17485,40 @@
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>1273</v>
+        <v>190</v>
       </c>
       <c r="B269" t="s">
-        <v>1280</v>
+        <v>195</v>
       </c>
       <c r="C269" t="s">
-        <v>1278</v>
+        <v>1079</v>
       </c>
       <c r="D269" t="s">
-        <v>1281</v>
+        <v>196</v>
       </c>
       <c r="E269" t="s">
-        <v>1281</v>
+        <v>1030</v>
       </c>
       <c r="F269" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G269" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H269" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I269" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J269" t="s">
-        <v>280</v>
+        <v>197</v>
+      </c>
+      <c r="K269" t="s">
+        <v>76</v>
       </c>
       <c r="L269" t="s">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="M269" t="s">
         <v>49</v>
@@ -17544,34 +17535,37 @@
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>1293</v>
+        <v>369</v>
       </c>
       <c r="B270" t="s">
-        <v>1297</v>
+        <v>395</v>
       </c>
       <c r="C270" t="s">
-        <v>1308</v>
+        <v>1108</v>
+      </c>
+      <c r="D270" t="s">
+        <v>394</v>
+      </c>
+      <c r="E270" t="s">
+        <v>1035</v>
       </c>
       <c r="F270" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G270" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H270" t="s">
         <v>13</v>
       </c>
       <c r="I270" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="J270" t="s">
-        <v>111</v>
-      </c>
-      <c r="K270" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="L270" t="s">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="M270" t="s">
         <v>49</v>
@@ -17588,19 +17582,19 @@
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="B271" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="C271" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="D271" t="s">
-        <v>386</v>
+        <v>1354</v>
       </c>
       <c r="E271" t="s">
-        <v>909</v>
+        <v>1353</v>
       </c>
       <c r="F271" t="s">
         <v>48</v>
@@ -17615,7 +17609,7 @@
         <v>142</v>
       </c>
       <c r="J271" t="s">
-        <v>491</v>
+        <v>280</v>
       </c>
       <c r="L271" t="s">
         <v>96</v>
@@ -17635,19 +17629,19 @@
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>461</v>
+        <v>62</v>
       </c>
       <c r="B272" t="s">
-        <v>550</v>
+        <v>71</v>
       </c>
       <c r="C272" t="s">
-        <v>1240</v>
+        <v>1133</v>
       </c>
       <c r="D272" t="s">
-        <v>551</v>
+        <v>292</v>
       </c>
       <c r="E272" t="s">
-        <v>985</v>
+        <v>934</v>
       </c>
       <c r="F272" t="s">
         <v>79</v>
@@ -17662,10 +17656,7 @@
         <v>142</v>
       </c>
       <c r="J272" t="s">
-        <v>111</v>
-      </c>
-      <c r="K272" t="s">
-        <v>134</v>
+        <v>524</v>
       </c>
       <c r="L272" t="s">
         <v>181</v>
@@ -17685,22 +17676,22 @@
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>726</v>
+        <v>126</v>
       </c>
       <c r="B273" t="s">
-        <v>737</v>
+        <v>132</v>
       </c>
       <c r="C273" t="s">
-        <v>1237</v>
+        <v>1135</v>
       </c>
       <c r="D273" t="s">
-        <v>551</v>
+        <v>133</v>
       </c>
       <c r="E273" t="s">
-        <v>985</v>
+        <v>936</v>
       </c>
       <c r="F273" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G273" t="s">
         <v>52</v>
@@ -17711,11 +17702,17 @@
       <c r="I273" t="s">
         <v>142</v>
       </c>
+      <c r="J273" t="s">
+        <v>111</v>
+      </c>
+      <c r="K273" t="s">
+        <v>134</v>
+      </c>
       <c r="L273" t="s">
         <v>181</v>
       </c>
       <c r="M273" t="s">
-        <v>49</v>
+        <v>836</v>
       </c>
       <c r="N273" t="s">
         <v>14</v>
@@ -17849,13 +17846,10 @@
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
-        <v>1291</v>
+        <v>1331</v>
       </c>
       <c r="B277" t="s">
-        <v>1323</v>
-      </c>
-      <c r="C277" t="s">
-        <v>1324</v>
+        <v>1346</v>
       </c>
       <c r="F277" t="s">
         <v>48</v>
@@ -17864,16 +17858,16 @@
         <v>32</v>
       </c>
       <c r="H277" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I277" t="s">
-        <v>142</v>
-      </c>
-      <c r="J277" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="K277" t="s">
+        <v>55</v>
       </c>
       <c r="L277" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M277" t="s">
         <v>49</v>
@@ -17890,19 +17884,19 @@
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="B278" t="s">
-        <v>1345</v>
+        <v>1362</v>
       </c>
       <c r="C278" t="s">
-        <v>1345</v>
+        <v>1363</v>
       </c>
       <c r="D278" t="s">
-        <v>1354</v>
+        <v>1319</v>
       </c>
       <c r="E278" t="s">
-        <v>1353</v>
+        <v>985</v>
       </c>
       <c r="F278" t="s">
         <v>48</v>
@@ -17917,7 +17911,7 @@
         <v>142</v>
       </c>
       <c r="J278" t="s">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="L278" t="s">
         <v>96</v>
@@ -17937,28 +17931,37 @@
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
-        <v>1331</v>
+        <v>1372</v>
       </c>
       <c r="B279" t="s">
-        <v>1346</v>
+        <v>1375</v>
+      </c>
+      <c r="C279" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E279" t="s">
+        <v>1377</v>
       </c>
       <c r="F279" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G279" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H279" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I279" t="s">
-        <v>109</v>
-      </c>
-      <c r="K279" t="s">
-        <v>55</v>
+        <v>1378</v>
+      </c>
+      <c r="J279" t="s">
+        <v>1379</v>
       </c>
       <c r="L279" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M279" t="s">
         <v>49</v>
@@ -17975,22 +17978,22 @@
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>1338</v>
+        <v>461</v>
       </c>
       <c r="B280" t="s">
-        <v>1362</v>
+        <v>550</v>
       </c>
       <c r="C280" t="s">
-        <v>1363</v>
+        <v>1240</v>
       </c>
       <c r="D280" t="s">
-        <v>1319</v>
+        <v>551</v>
       </c>
       <c r="E280" t="s">
         <v>985</v>
       </c>
       <c r="F280" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G280" t="s">
         <v>52</v>
@@ -18004,8 +18007,11 @@
       <c r="J280" t="s">
         <v>111</v>
       </c>
+      <c r="K280" t="s">
+        <v>134</v>
+      </c>
       <c r="L280" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="M280" t="s">
         <v>49</v>
@@ -18022,43 +18028,37 @@
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>1339</v>
+        <v>726</v>
       </c>
       <c r="B281" t="s">
-        <v>1364</v>
+        <v>737</v>
       </c>
       <c r="C281" t="s">
-        <v>1365</v>
+        <v>1237</v>
       </c>
       <c r="D281" t="s">
-        <v>1368</v>
+        <v>551</v>
       </c>
       <c r="E281" t="s">
-        <v>1369</v>
+        <v>985</v>
       </c>
       <c r="F281" t="s">
         <v>48</v>
       </c>
       <c r="G281" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H281" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I281" t="s">
-        <v>109</v>
-      </c>
-      <c r="J281" t="s">
-        <v>280</v>
-      </c>
-      <c r="K281" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="L281" t="s">
         <v>181</v>
       </c>
       <c r="M281" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N281" t="s">
         <v>14</v>
@@ -18072,19 +18072,19 @@
     </row>
     <row r="282" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
-        <v>1372</v>
+        <v>597</v>
       </c>
       <c r="B282" t="s">
-        <v>1375</v>
+        <v>606</v>
       </c>
       <c r="C282" t="s">
-        <v>1374</v>
+        <v>1204</v>
       </c>
       <c r="D282" t="s">
-        <v>1376</v>
+        <v>607</v>
       </c>
       <c r="E282" t="s">
-        <v>1377</v>
+        <v>999</v>
       </c>
       <c r="F282" t="s">
         <v>79</v>
@@ -18096,16 +18096,19 @@
         <v>13</v>
       </c>
       <c r="I282" t="s">
-        <v>1378</v>
+        <v>142</v>
       </c>
       <c r="J282" t="s">
-        <v>1379</v>
+        <v>280</v>
+      </c>
+      <c r="K282" t="s">
+        <v>76</v>
       </c>
       <c r="L282" t="s">
         <v>96</v>
       </c>
       <c r="M282" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N282" t="s">
         <v>14</v>
@@ -18119,43 +18122,40 @@
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>1373</v>
+        <v>297</v>
       </c>
       <c r="B283" t="s">
-        <v>1380</v>
+        <v>313</v>
       </c>
       <c r="C283" t="s">
-        <v>1380</v>
+        <v>1174</v>
       </c>
       <c r="D283" t="s">
-        <v>1381</v>
+        <v>314</v>
       </c>
       <c r="E283" t="s">
-        <v>1382</v>
+        <v>973</v>
       </c>
       <c r="F283" t="s">
         <v>79</v>
       </c>
       <c r="G283" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H283" t="s">
         <v>13</v>
       </c>
       <c r="I283" t="s">
-        <v>1383</v>
+        <v>142</v>
       </c>
       <c r="J283" t="s">
-        <v>267</v>
-      </c>
-      <c r="K283" t="s">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="L283" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="M283" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N283" t="s">
         <v>14</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2E1469-B9A3-ED48-AB74-017AB8AD0AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3952E9-61D1-0D4C-BA4E-B91C2F9665A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
         <v>111</v>
@@ -4778,10 +4778,10 @@
         <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="F4" t="s">
         <v>47</v>
@@ -4796,10 +4796,7 @@
         <v>141</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="L4" t="s">
         <v>95</v>
@@ -4818,38 +4815,41 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>19</v>
+      <c r="A5" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>1238</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>846</v>
+        <v>867</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="J5" t="s">
         <v>28</v>
       </c>
+      <c r="K5" t="s">
+        <v>94</v>
+      </c>
       <c r="L5" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="M5" t="s">
         <v>48</v>
@@ -4865,41 +4865,41 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>20</v>
+      <c r="A6" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="B6" t="s">
-        <v>751</v>
+        <v>372</v>
       </c>
       <c r="C6" t="s">
-        <v>1045</v>
+        <v>1054</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>676</v>
       </c>
       <c r="E6" t="s">
-        <v>847</v>
+        <v>869</v>
       </c>
       <c r="F6" t="s">
         <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J6" t="s">
-        <v>28</v>
+        <v>482</v>
       </c>
       <c r="L6" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="M6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N6" t="s">
         <v>14</v>
@@ -4913,40 +4913,43 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>753</v>
       </c>
       <c r="C7" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D7" t="s">
-        <v>752</v>
+        <v>286</v>
       </c>
       <c r="E7" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F7" t="s">
         <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
         <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="M7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N7" t="s">
         <v>14</v>
@@ -4960,19 +4963,19 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>753</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>1047</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="F8" t="s">
         <v>47</v>
@@ -4981,19 +4984,19 @@
         <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L8" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s">
         <v>48</v>
@@ -5010,19 +5013,19 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>754</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>1048</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="F9" t="s">
         <v>47</v>
@@ -5034,19 +5037,16 @@
         <v>13</v>
       </c>
       <c r="I9" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="J9" t="s">
         <v>28</v>
       </c>
-      <c r="K9" t="s">
-        <v>53</v>
-      </c>
       <c r="L9" t="s">
         <v>95</v>
       </c>
       <c r="M9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N9" t="s">
         <v>14</v>
@@ -5059,20 +5059,20 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
+      <c r="A10" t="s">
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>751</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>1045</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="F10" t="s">
         <v>47</v>
@@ -5089,14 +5089,11 @@
       <c r="J10" t="s">
         <v>28</v>
       </c>
-      <c r="K10" t="s">
-        <v>53</v>
-      </c>
       <c r="L10" t="s">
         <v>95</v>
       </c>
       <c r="M10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N10" t="s">
         <v>14</v>
@@ -5109,44 +5106,41 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
+      <c r="A11" t="s">
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>1046</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>752</v>
       </c>
       <c r="E11" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="L11" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="M11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N11" t="s">
         <v>14</v>
@@ -5159,20 +5153,20 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>26</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>754</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>1048</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="F12" t="s">
         <v>47</v>
@@ -5196,7 +5190,7 @@
         <v>95</v>
       </c>
       <c r="M12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N12" t="s">
         <v>14</v>
@@ -5210,7 +5204,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
         <v>111</v>
@@ -5219,10 +5213,10 @@
         <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="F13" t="s">
         <v>47</v>
@@ -5243,10 +5237,10 @@
         <v>53</v>
       </c>
       <c r="L13" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="M13" t="s">
-        <v>834</v>
+        <v>48</v>
       </c>
       <c r="N13" t="s">
         <v>14</v>
@@ -5260,7 +5254,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
         <v>111</v>
@@ -5269,10 +5263,10 @@
         <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="F14" t="s">
         <v>47</v>
@@ -5293,10 +5287,10 @@
         <v>94</v>
       </c>
       <c r="L14" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="M14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N14" t="s">
         <v>14</v>
@@ -5310,40 +5304,40 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>1049</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>1405</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>1406</v>
+        <v>853</v>
       </c>
       <c r="F15" t="s">
         <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I15" t="s">
-        <v>1404</v>
+        <v>141</v>
       </c>
       <c r="J15" t="s">
-        <v>476</v>
+        <v>28</v>
       </c>
       <c r="K15" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="L15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M15" t="s">
         <v>48</v>
@@ -5360,7 +5354,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
         <v>111</v>
@@ -5369,10 +5363,10 @@
         <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="F16" t="s">
         <v>47</v>
@@ -5384,19 +5378,19 @@
         <v>13</v>
       </c>
       <c r="I16" t="s">
-        <v>447</v>
+        <v>141</v>
       </c>
       <c r="J16" t="s">
         <v>28</v>
       </c>
       <c r="K16" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="L16" t="s">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s">
-        <v>48</v>
+        <v>834</v>
       </c>
       <c r="N16" t="s">
         <v>14</v>
@@ -5410,43 +5404,43 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>1050</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F17" t="s">
         <v>47</v>
       </c>
       <c r="G17" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I17" t="s">
-        <v>553</v>
+        <v>141</v>
       </c>
       <c r="J17" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="K17" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="L17" t="s">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="M17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N17" t="s">
         <v>14</v>
@@ -5460,37 +5454,40 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>755</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D18" t="s">
-        <v>756</v>
+        <v>1405</v>
       </c>
       <c r="E18" t="s">
-        <v>858</v>
+        <v>1406</v>
       </c>
       <c r="F18" t="s">
         <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="H18" t="s">
         <v>31</v>
       </c>
       <c r="I18" t="s">
-        <v>553</v>
+        <v>1404</v>
       </c>
       <c r="J18" t="s">
-        <v>477</v>
+        <v>476</v>
+      </c>
+      <c r="K18" t="s">
+        <v>94</v>
       </c>
       <c r="L18" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="M18" t="s">
         <v>48</v>
@@ -5507,31 +5504,31 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>1052</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="F19" t="s">
         <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I19" t="s">
-        <v>554</v>
+        <v>447</v>
       </c>
       <c r="J19" t="s">
         <v>28</v>
@@ -5540,7 +5537,7 @@
         <v>94</v>
       </c>
       <c r="L19" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="M19" t="s">
         <v>48</v>
@@ -5557,37 +5554,40 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>757</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>757</v>
+        <v>1050</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="F20" t="s">
         <v>47</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H20" t="s">
         <v>31</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>553</v>
       </c>
       <c r="J20" t="s">
-        <v>74</v>
+        <v>52</v>
+      </c>
+      <c r="K20" t="s">
+        <v>54</v>
       </c>
       <c r="L20" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="M20" t="s">
         <v>48</v>
@@ -5604,40 +5604,40 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C21" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>756</v>
       </c>
       <c r="E21" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="F21" t="s">
         <v>47</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
         <v>31</v>
       </c>
       <c r="I21" t="s">
-        <v>91</v>
+        <v>553</v>
       </c>
       <c r="J21" t="s">
-        <v>74</v>
+        <v>477</v>
       </c>
       <c r="L21" t="s">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="M21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N21" t="s">
         <v>14</v>
@@ -5651,19 +5651,19 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>1052</v>
       </c>
       <c r="D22" t="s">
-        <v>759</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="F22" t="s">
         <v>47</v>
@@ -5672,19 +5672,19 @@
         <v>119</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I22" t="s">
-        <v>141</v>
+        <v>554</v>
       </c>
       <c r="J22" t="s">
-        <v>478</v>
+        <v>28</v>
       </c>
       <c r="K22" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="L22" t="s">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="M22" t="s">
         <v>48</v>
@@ -5701,40 +5701,37 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C23" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D23" t="s">
-        <v>809</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="F23" t="s">
         <v>47</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H23" t="s">
         <v>31</v>
       </c>
       <c r="I23" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="J23" t="s">
-        <v>52</v>
-      </c>
-      <c r="K23" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="L23" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="M23" t="s">
         <v>48</v>
@@ -5751,40 +5748,40 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>758</v>
       </c>
       <c r="C24" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="F24" t="s">
         <v>47</v>
       </c>
       <c r="G24" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="H24" t="s">
         <v>31</v>
       </c>
       <c r="I24" t="s">
-        <v>554</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="L24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N24" t="s">
         <v>14</v>
@@ -5797,26 +5794,26 @@
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>148</v>
+      <c r="A25" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>759</v>
       </c>
       <c r="E25" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="F25" t="s">
         <v>47</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
@@ -5825,10 +5822,13 @@
         <v>141</v>
       </c>
       <c r="J25" t="s">
-        <v>73</v>
+        <v>478</v>
+      </c>
+      <c r="K25" t="s">
+        <v>54</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="M25" t="s">
         <v>48</v>
@@ -5845,40 +5845,43 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>354</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>370</v>
+        <v>760</v>
       </c>
       <c r="C26" t="s">
-        <v>370</v>
+        <v>760</v>
       </c>
       <c r="D26" t="s">
-        <v>371</v>
+        <v>809</v>
       </c>
       <c r="E26" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="F26" t="s">
         <v>47</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
         <v>31</v>
       </c>
       <c r="I26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J26" t="s">
-        <v>480</v>
+        <v>52</v>
+      </c>
+      <c r="K26" t="s">
+        <v>54</v>
       </c>
       <c r="L26" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="M26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N26" t="s">
         <v>14</v>
@@ -5892,40 +5895,37 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>355</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>1052</v>
       </c>
       <c r="D27" t="s">
-        <v>777</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>1024</v>
+        <v>863</v>
       </c>
       <c r="F27" t="s">
         <v>47</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H27" t="s">
         <v>31</v>
       </c>
       <c r="I27" t="s">
-        <v>373</v>
+        <v>554</v>
       </c>
       <c r="J27" t="s">
-        <v>374</v>
-      </c>
-      <c r="K27" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="L27" t="s">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="M27" t="s">
         <v>48</v>
@@ -5942,37 +5942,37 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>59</v>
+        <v>354</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>370</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>370</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>371</v>
       </c>
       <c r="E28" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F28" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G28" t="s">
         <v>32</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I28" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J28" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M28" t="s">
         <v>50</v>
@@ -5989,37 +5989,37 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>99</v>
+        <v>355</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>1238</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>777</v>
       </c>
       <c r="E29" t="s">
-        <v>867</v>
+        <v>1024</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H29" t="s">
         <v>31</v>
       </c>
       <c r="I29" t="s">
-        <v>145</v>
+        <v>373</v>
       </c>
       <c r="J29" t="s">
-        <v>28</v>
+        <v>374</v>
       </c>
       <c r="K29" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="L29" t="s">
         <v>146</v>
@@ -6039,40 +6039,40 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>567</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
-        <v>571</v>
+        <v>289</v>
       </c>
       <c r="E30" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F30" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I30" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J30" t="s">
-        <v>28</v>
+        <v>481</v>
       </c>
       <c r="L30" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="M30" t="s">
-        <v>834</v>
+        <v>50</v>
       </c>
       <c r="N30" t="s">
         <v>14</v>
@@ -6086,19 +6086,19 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>660</v>
+        <v>567</v>
       </c>
       <c r="B31" t="s">
-        <v>372</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>1054</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>676</v>
+        <v>571</v>
       </c>
       <c r="E31" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F31" t="s">
         <v>47</v>
@@ -6110,16 +6110,16 @@
         <v>31</v>
       </c>
       <c r="I31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J31" t="s">
-        <v>482</v>
+        <v>28</v>
       </c>
       <c r="L31" t="s">
         <v>180</v>
       </c>
       <c r="M31" t="s">
-        <v>48</v>
+        <v>834</v>
       </c>
       <c r="N31" t="s">
         <v>14</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1F5BCC-203A-654A-82D1-127CD2D1C105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A072300-84FC-D644-9355-4EC1B6069662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4652" uniqueCount="1461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4754" uniqueCount="1484">
   <si>
     <t>id</t>
   </si>
@@ -4403,6 +4403,75 @@
   </si>
   <si>
     <t>Double G - Heart GVX</t>
+  </si>
+  <si>
+    <t>ILU-0198</t>
+  </si>
+  <si>
+    <t>ILU-0199</t>
+  </si>
+  <si>
+    <t>ILU-0200</t>
+  </si>
+  <si>
+    <t>ILU-0201</t>
+  </si>
+  <si>
+    <t>ILU-0202</t>
+  </si>
+  <si>
+    <t>Tu mano II</t>
+  </si>
+  <si>
+    <t>Tu mano III</t>
+  </si>
+  <si>
+    <t>Tu mano IV</t>
+  </si>
+  <si>
+    <t>Your hand II</t>
+  </si>
+  <si>
+    <t>Your hand III</t>
+  </si>
+  <si>
+    <t>Your hand IV</t>
+  </si>
+  <si>
+    <t>3 cruces</t>
+  </si>
+  <si>
+    <t>3 cross</t>
+  </si>
+  <si>
+    <t>Sal + luz</t>
+  </si>
+  <si>
+    <t>Salt + Light</t>
+  </si>
+  <si>
+    <t>Estrella de Belén</t>
+  </si>
+  <si>
+    <t>Bethleem Star</t>
+  </si>
+  <si>
+    <t>DIS-0106</t>
+  </si>
+  <si>
+    <t>DIS-0107</t>
+  </si>
+  <si>
+    <t>¿Estás en casa?</t>
+  </si>
+  <si>
+    <t>Are you at home?</t>
+  </si>
+  <si>
+    <t>En voz alta</t>
+  </si>
+  <si>
+    <t>Aloud</t>
   </si>
 </sst>
 </file>
@@ -4759,7 +4828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P303"/>
+  <dimension ref="A1:P310"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.5" customWidth="1"/>
@@ -14697,19 +14766,19 @@
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>301</v>
+        <v>1478</v>
       </c>
       <c r="B207" t="s">
-        <v>325</v>
+        <v>1482</v>
       </c>
       <c r="C207" t="s">
-        <v>1174</v>
+        <v>1483</v>
       </c>
       <c r="D207" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E207" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F207" t="s">
         <v>78</v>
@@ -14797,22 +14866,22 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>302</v>
+        <v>716</v>
       </c>
       <c r="B209" t="s">
-        <v>327</v>
+        <v>739</v>
       </c>
       <c r="C209" t="s">
-        <v>1176</v>
+        <v>1219</v>
       </c>
       <c r="D209" t="s">
-        <v>796</v>
+        <v>744</v>
       </c>
       <c r="E209" t="s">
-        <v>972</v>
+        <v>1018</v>
       </c>
       <c r="F209" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G209" t="s">
         <v>51</v>
@@ -14827,10 +14896,10 @@
         <v>206</v>
       </c>
       <c r="K209" t="s">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="L209" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="M209" t="s">
         <v>48</v>
@@ -14847,19 +14916,19 @@
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B210" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C210" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D210" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E210" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F210" t="s">
         <v>78</v>
@@ -14897,22 +14966,22 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>716</v>
+        <v>303</v>
       </c>
       <c r="B211" t="s">
-        <v>739</v>
+        <v>328</v>
       </c>
       <c r="C211" t="s">
-        <v>1219</v>
+        <v>1177</v>
       </c>
       <c r="D211" t="s">
-        <v>744</v>
+        <v>798</v>
       </c>
       <c r="E211" t="s">
-        <v>1018</v>
+        <v>973</v>
       </c>
       <c r="F211" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G211" t="s">
         <v>51</v>
@@ -14927,10 +14996,10 @@
         <v>206</v>
       </c>
       <c r="K211" t="s">
-        <v>205</v>
+        <v>75</v>
       </c>
       <c r="L211" t="s">
-        <v>179</v>
+        <v>97</v>
       </c>
       <c r="M211" t="s">
         <v>48</v>
@@ -15197,19 +15266,19 @@
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>1280</v>
+        <v>580</v>
       </c>
       <c r="B217" t="s">
-        <v>1304</v>
+        <v>586</v>
       </c>
       <c r="C217" t="s">
-        <v>1305</v>
+        <v>1195</v>
       </c>
       <c r="D217" t="s">
-        <v>1249</v>
+        <v>594</v>
       </c>
       <c r="E217" t="s">
-        <v>1251</v>
+        <v>990</v>
       </c>
       <c r="F217" t="s">
         <v>47</v>
@@ -15221,19 +15290,19 @@
         <v>31</v>
       </c>
       <c r="I217" t="s">
-        <v>446</v>
+        <v>587</v>
       </c>
       <c r="J217" t="s">
         <v>277</v>
       </c>
       <c r="K217" t="s">
-        <v>415</v>
+        <v>75</v>
       </c>
       <c r="L217" t="s">
         <v>179</v>
       </c>
       <c r="M217" t="s">
-        <v>833</v>
+        <v>48</v>
       </c>
       <c r="N217" t="s">
         <v>14</v>
@@ -15247,19 +15316,19 @@
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B218" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C218" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="D218" t="s">
-        <v>1308</v>
+        <v>1249</v>
       </c>
       <c r="E218" t="s">
-        <v>1308</v>
+        <v>1251</v>
       </c>
       <c r="F218" t="s">
         <v>47</v>
@@ -15268,22 +15337,22 @@
         <v>32</v>
       </c>
       <c r="H218" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I218" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="J218" t="s">
         <v>277</v>
       </c>
       <c r="K218" t="s">
-        <v>140</v>
+        <v>415</v>
       </c>
       <c r="L218" t="s">
         <v>179</v>
       </c>
       <c r="M218" t="s">
-        <v>48</v>
+        <v>833</v>
       </c>
       <c r="N218" t="s">
         <v>14</v>
@@ -15297,35 +15366,38 @@
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>615</v>
+        <v>1281</v>
       </c>
       <c r="B219" t="s">
-        <v>658</v>
+        <v>1306</v>
       </c>
       <c r="C219" t="s">
-        <v>1207</v>
+        <v>1307</v>
       </c>
       <c r="D219" t="s">
-        <v>817</v>
+        <v>1308</v>
       </c>
       <c r="E219" t="s">
-        <v>1006</v>
+        <v>1308</v>
       </c>
       <c r="F219" t="s">
         <v>47</v>
       </c>
       <c r="G219" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="H219" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I219" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J219" t="s">
         <v>277</v>
       </c>
+      <c r="K219" t="s">
+        <v>140</v>
+      </c>
       <c r="L219" t="s">
         <v>179</v>
       </c>
@@ -15344,37 +15416,34 @@
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>580</v>
+        <v>615</v>
       </c>
       <c r="B220" t="s">
-        <v>586</v>
+        <v>658</v>
       </c>
       <c r="C220" t="s">
-        <v>1195</v>
+        <v>1207</v>
       </c>
       <c r="D220" t="s">
-        <v>594</v>
+        <v>817</v>
       </c>
       <c r="E220" t="s">
-        <v>990</v>
+        <v>1006</v>
       </c>
       <c r="F220" t="s">
         <v>47</v>
       </c>
       <c r="G220" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H220" t="s">
         <v>31</v>
       </c>
       <c r="I220" t="s">
-        <v>587</v>
+        <v>143</v>
       </c>
       <c r="J220" t="s">
         <v>277</v>
-      </c>
-      <c r="K220" t="s">
-        <v>75</v>
       </c>
       <c r="L220" t="s">
         <v>179</v>
@@ -15541,22 +15610,16 @@
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>1266</v>
+        <v>1461</v>
       </c>
       <c r="B224" t="s">
-        <v>1269</v>
+        <v>1466</v>
       </c>
       <c r="C224" t="s">
-        <v>1271</v>
-      </c>
-      <c r="D224" t="s">
-        <v>683</v>
-      </c>
-      <c r="E224" t="s">
-        <v>1009</v>
+        <v>1469</v>
       </c>
       <c r="F224" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G224" t="s">
         <v>32</v>
@@ -15565,13 +15628,13 @@
         <v>31</v>
       </c>
       <c r="I224" t="s">
-        <v>1274</v>
-      </c>
-      <c r="J224" t="s">
-        <v>277</v>
+        <v>446</v>
+      </c>
+      <c r="K224" t="s">
+        <v>54</v>
       </c>
       <c r="L224" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="M224" t="s">
         <v>48</v>
@@ -15588,34 +15651,25 @@
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>1334</v>
+        <v>1462</v>
       </c>
       <c r="B225" t="s">
-        <v>1359</v>
+        <v>1467</v>
       </c>
       <c r="C225" t="s">
-        <v>1360</v>
-      </c>
-      <c r="D225" t="s">
-        <v>1363</v>
-      </c>
-      <c r="E225" t="s">
-        <v>1364</v>
+        <v>1470</v>
       </c>
       <c r="F225" t="s">
         <v>47</v>
       </c>
       <c r="G225" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="H225" t="s">
         <v>31</v>
       </c>
       <c r="I225" t="s">
-        <v>108</v>
-      </c>
-      <c r="J225" t="s">
-        <v>277</v>
+        <v>446</v>
       </c>
       <c r="K225" t="s">
         <v>54</v>
@@ -15624,7 +15678,7 @@
         <v>179</v>
       </c>
       <c r="M225" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N225" t="s">
         <v>14</v>
@@ -15638,19 +15692,13 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>256</v>
+        <v>1463</v>
       </c>
       <c r="B226" t="s">
-        <v>281</v>
+        <v>1468</v>
       </c>
       <c r="C226" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D226" t="s">
-        <v>282</v>
-      </c>
-      <c r="E226" t="s">
-        <v>899</v>
+        <v>1471</v>
       </c>
       <c r="F226" t="s">
         <v>47</v>
@@ -15659,19 +15707,19 @@
         <v>32</v>
       </c>
       <c r="H226" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I226" t="s">
-        <v>141</v>
-      </c>
-      <c r="J226" t="s">
-        <v>110</v>
+        <v>446</v>
+      </c>
+      <c r="K226" t="s">
+        <v>54</v>
       </c>
       <c r="L226" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="M226" t="s">
-        <v>833</v>
+        <v>48</v>
       </c>
       <c r="N226" t="s">
         <v>14</v>
@@ -15685,31 +15733,37 @@
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>1286</v>
+        <v>1266</v>
       </c>
       <c r="B227" t="s">
-        <v>1318</v>
+        <v>1269</v>
       </c>
       <c r="C227" t="s">
-        <v>1319</v>
+        <v>1271</v>
+      </c>
+      <c r="D227" t="s">
+        <v>683</v>
+      </c>
+      <c r="E227" t="s">
+        <v>1009</v>
       </c>
       <c r="F227" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G227" t="s">
         <v>32</v>
       </c>
       <c r="H227" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I227" t="s">
-        <v>141</v>
+        <v>1274</v>
       </c>
       <c r="J227" t="s">
-        <v>110</v>
+        <v>277</v>
       </c>
       <c r="L227" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M227" t="s">
         <v>48</v>
@@ -15726,43 +15780,43 @@
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>338</v>
+        <v>1334</v>
       </c>
       <c r="B228" t="s">
-        <v>801</v>
+        <v>1359</v>
       </c>
       <c r="C228" t="s">
-        <v>1180</v>
+        <v>1360</v>
       </c>
       <c r="D228" t="s">
-        <v>351</v>
+        <v>1363</v>
       </c>
       <c r="E228" t="s">
-        <v>976</v>
+        <v>1364</v>
       </c>
       <c r="F228" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G228" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="H228" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I228" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J228" t="s">
-        <v>520</v>
+        <v>277</v>
       </c>
       <c r="K228" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L228" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="M228" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N228" t="s">
         <v>14</v>
@@ -15776,43 +15830,40 @@
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>666</v>
+        <v>256</v>
       </c>
       <c r="B229" t="s">
-        <v>686</v>
+        <v>281</v>
       </c>
       <c r="C229" t="s">
-        <v>1211</v>
+        <v>1094</v>
       </c>
       <c r="D229" t="s">
-        <v>687</v>
+        <v>282</v>
       </c>
       <c r="E229" t="s">
-        <v>1011</v>
+        <v>899</v>
       </c>
       <c r="F229" t="s">
         <v>47</v>
       </c>
       <c r="G229" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H229" t="s">
         <v>13</v>
       </c>
       <c r="I229" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="J229" t="s">
-        <v>277</v>
-      </c>
-      <c r="K229" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="L229" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="M229" t="s">
-        <v>48</v>
+        <v>833</v>
       </c>
       <c r="N229" t="s">
         <v>14</v>
@@ -15826,19 +15877,13 @@
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>247</v>
+        <v>1286</v>
       </c>
       <c r="B230" t="s">
-        <v>257</v>
+        <v>1318</v>
       </c>
       <c r="C230" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D230" t="s">
-        <v>258</v>
-      </c>
-      <c r="E230" t="s">
-        <v>1028</v>
+        <v>1319</v>
       </c>
       <c r="F230" t="s">
         <v>47</v>
@@ -15853,16 +15898,13 @@
         <v>141</v>
       </c>
       <c r="J230" t="s">
-        <v>206</v>
-      </c>
-      <c r="K230" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="L230" t="s">
-        <v>265</v>
+        <v>95</v>
       </c>
       <c r="M230" t="s">
-        <v>833</v>
+        <v>48</v>
       </c>
       <c r="N230" t="s">
         <v>14</v>
@@ -15876,37 +15918,40 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>462</v>
+        <v>338</v>
       </c>
       <c r="B231" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C231" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>351</v>
       </c>
       <c r="E231" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="F231" t="s">
         <v>78</v>
       </c>
       <c r="G231" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H231" t="s">
         <v>13</v>
       </c>
       <c r="I231" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="J231" t="s">
-        <v>277</v>
+        <v>520</v>
+      </c>
+      <c r="K231" t="s">
+        <v>75</v>
       </c>
       <c r="L231" t="s">
-        <v>493</v>
+        <v>187</v>
       </c>
       <c r="M231" t="s">
         <v>48</v>
@@ -15923,40 +15968,40 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>252</v>
+        <v>301</v>
       </c>
       <c r="B232" t="s">
-        <v>273</v>
+        <v>325</v>
       </c>
       <c r="C232" t="s">
-        <v>1091</v>
+        <v>1174</v>
       </c>
       <c r="D232" t="s">
-        <v>274</v>
+        <v>799</v>
       </c>
       <c r="E232" t="s">
-        <v>1029</v>
+        <v>974</v>
       </c>
       <c r="F232" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G232" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H232" t="s">
         <v>13</v>
       </c>
       <c r="I232" t="s">
-        <v>141</v>
+        <v>326</v>
       </c>
       <c r="J232" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="K232" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L232" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M232" t="s">
         <v>48</v>
@@ -15973,37 +16018,40 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>407</v>
+        <v>1479</v>
       </c>
       <c r="B233" t="s">
-        <v>802</v>
+        <v>1480</v>
       </c>
       <c r="C233" t="s">
-        <v>1183</v>
+        <v>1481</v>
       </c>
       <c r="D233" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="E233" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="F233" t="s">
         <v>78</v>
       </c>
       <c r="G233" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H233" t="s">
         <v>13</v>
       </c>
       <c r="I233" t="s">
-        <v>141</v>
+        <v>268</v>
       </c>
       <c r="J233" t="s">
-        <v>490</v>
+        <v>206</v>
+      </c>
+      <c r="K233" t="s">
+        <v>75</v>
       </c>
       <c r="L233" t="s">
-        <v>182</v>
+        <v>97</v>
       </c>
       <c r="M233" t="s">
         <v>48</v>
@@ -16020,40 +16068,40 @@
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>590</v>
+        <v>666</v>
       </c>
       <c r="B234" t="s">
-        <v>596</v>
+        <v>686</v>
       </c>
       <c r="C234" t="s">
-        <v>1197</v>
+        <v>1211</v>
       </c>
       <c r="D234" t="s">
-        <v>597</v>
+        <v>687</v>
       </c>
       <c r="E234" t="s">
-        <v>992</v>
+        <v>1011</v>
       </c>
       <c r="F234" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G234" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H234" t="s">
         <v>13</v>
       </c>
       <c r="I234" t="s">
-        <v>268</v>
+        <v>109</v>
       </c>
       <c r="J234" t="s">
-        <v>598</v>
+        <v>277</v>
       </c>
       <c r="K234" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="L234" t="s">
-        <v>493</v>
+        <v>179</v>
       </c>
       <c r="M234" t="s">
         <v>48</v>
@@ -16070,19 +16118,19 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>670</v>
+        <v>247</v>
       </c>
       <c r="B235" t="s">
-        <v>690</v>
+        <v>257</v>
       </c>
       <c r="C235" t="s">
-        <v>1213</v>
+        <v>1087</v>
       </c>
       <c r="D235" t="s">
-        <v>691</v>
+        <v>258</v>
       </c>
       <c r="E235" t="s">
-        <v>1013</v>
+        <v>1028</v>
       </c>
       <c r="F235" t="s">
         <v>47</v>
@@ -16091,22 +16139,22 @@
         <v>32</v>
       </c>
       <c r="H235" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I235" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="J235" t="s">
-        <v>277</v>
+        <v>206</v>
       </c>
       <c r="K235" t="s">
-        <v>415</v>
+        <v>53</v>
       </c>
       <c r="L235" t="s">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="M235" t="s">
-        <v>48</v>
+        <v>833</v>
       </c>
       <c r="N235" t="s">
         <v>14</v>
@@ -16120,40 +16168,37 @@
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>498</v>
+        <v>462</v>
       </c>
       <c r="B236" t="s">
-        <v>504</v>
+        <v>804</v>
       </c>
       <c r="C236" t="s">
-        <v>1125</v>
+        <v>1185</v>
       </c>
       <c r="D236" t="s">
-        <v>505</v>
+        <v>470</v>
       </c>
       <c r="E236" t="s">
-        <v>926</v>
+        <v>982</v>
       </c>
       <c r="F236" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G236" t="s">
         <v>32</v>
       </c>
       <c r="H236" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I236" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J236" t="s">
         <v>277</v>
       </c>
-      <c r="K236" t="s">
-        <v>54</v>
-      </c>
       <c r="L236" t="s">
-        <v>179</v>
+        <v>493</v>
       </c>
       <c r="M236" t="s">
         <v>48</v>
@@ -16170,37 +16215,37 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>460</v>
+        <v>252</v>
       </c>
       <c r="B237" t="s">
-        <v>467</v>
+        <v>273</v>
       </c>
       <c r="C237" t="s">
-        <v>1184</v>
+        <v>1091</v>
       </c>
       <c r="D237" t="s">
-        <v>468</v>
+        <v>274</v>
       </c>
       <c r="E237" t="s">
-        <v>981</v>
+        <v>1029</v>
       </c>
       <c r="F237" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G237" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H237" t="s">
         <v>13</v>
       </c>
       <c r="I237" t="s">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="J237" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="K237" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L237" t="s">
         <v>95</v>
@@ -16220,37 +16265,37 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>556</v>
+        <v>407</v>
       </c>
       <c r="B238" t="s">
-        <v>561</v>
+        <v>802</v>
       </c>
       <c r="C238" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="D238" t="s">
-        <v>595</v>
+        <v>803</v>
       </c>
       <c r="E238" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="F238" t="s">
         <v>78</v>
       </c>
       <c r="G238" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H238" t="s">
         <v>13</v>
       </c>
       <c r="I238" t="s">
-        <v>109</v>
-      </c>
-      <c r="K238" t="s">
-        <v>75</v>
+        <v>141</v>
+      </c>
+      <c r="J238" t="s">
+        <v>490</v>
       </c>
       <c r="L238" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="M238" t="s">
         <v>48</v>
@@ -16267,43 +16312,43 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>435</v>
+        <v>590</v>
       </c>
       <c r="B239" t="s">
-        <v>448</v>
+        <v>596</v>
       </c>
       <c r="C239" t="s">
-        <v>1113</v>
+        <v>1197</v>
       </c>
       <c r="D239" t="s">
-        <v>449</v>
+        <v>597</v>
       </c>
       <c r="E239" t="s">
-        <v>917</v>
+        <v>992</v>
       </c>
       <c r="F239" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G239" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H239" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I239" t="s">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="J239" t="s">
-        <v>522</v>
+        <v>598</v>
       </c>
       <c r="K239" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L239" t="s">
-        <v>179</v>
+        <v>493</v>
       </c>
       <c r="M239" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N239" t="s">
         <v>14</v>
@@ -16317,19 +16362,19 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>438</v>
+        <v>670</v>
       </c>
       <c r="B240" t="s">
-        <v>455</v>
+        <v>690</v>
       </c>
       <c r="C240" t="s">
-        <v>1115</v>
+        <v>1213</v>
       </c>
       <c r="D240" t="s">
-        <v>456</v>
+        <v>691</v>
       </c>
       <c r="E240" t="s">
-        <v>919</v>
+        <v>1013</v>
       </c>
       <c r="F240" t="s">
         <v>47</v>
@@ -16341,13 +16386,13 @@
         <v>31</v>
       </c>
       <c r="I240" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="J240" t="s">
-        <v>524</v>
+        <v>277</v>
       </c>
       <c r="K240" t="s">
-        <v>54</v>
+        <v>415</v>
       </c>
       <c r="L240" t="s">
         <v>179</v>
@@ -16367,43 +16412,43 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>591</v>
+        <v>498</v>
       </c>
       <c r="B241" t="s">
-        <v>600</v>
+        <v>504</v>
       </c>
       <c r="C241" t="s">
-        <v>1198</v>
+        <v>1125</v>
       </c>
       <c r="D241" t="s">
-        <v>601</v>
+        <v>505</v>
       </c>
       <c r="E241" t="s">
-        <v>993</v>
+        <v>926</v>
       </c>
       <c r="F241" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G241" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H241" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I241" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J241" t="s">
-        <v>488</v>
+        <v>277</v>
       </c>
       <c r="K241" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L241" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="M241" t="s">
-        <v>832</v>
+        <v>48</v>
       </c>
       <c r="N241" t="s">
         <v>14</v>
@@ -16417,19 +16462,13 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>1245</v>
+        <v>1465</v>
       </c>
       <c r="B242" t="s">
-        <v>1261</v>
+        <v>1476</v>
       </c>
       <c r="C242" t="s">
-        <v>1262</v>
-      </c>
-      <c r="D242" t="s">
-        <v>456</v>
-      </c>
-      <c r="E242" t="s">
-        <v>919</v>
+        <v>1477</v>
       </c>
       <c r="F242" t="s">
         <v>47</v>
@@ -16441,13 +16480,16 @@
         <v>31</v>
       </c>
       <c r="I242" t="s">
-        <v>143</v>
+        <v>446</v>
       </c>
       <c r="J242" t="s">
-        <v>1263</v>
+        <v>277</v>
+      </c>
+      <c r="K242" t="s">
+        <v>54</v>
       </c>
       <c r="L242" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="M242" t="s">
         <v>48</v>
@@ -16464,34 +16506,40 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>1332</v>
+        <v>460</v>
       </c>
       <c r="B243" t="s">
-        <v>1355</v>
+        <v>467</v>
       </c>
       <c r="C243" t="s">
-        <v>1356</v>
+        <v>1184</v>
+      </c>
+      <c r="D243" t="s">
+        <v>468</v>
+      </c>
+      <c r="E243" t="s">
+        <v>981</v>
       </c>
       <c r="F243" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G243" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H243" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I243" t="s">
-        <v>1274</v>
+        <v>268</v>
       </c>
       <c r="J243" t="s">
-        <v>1263</v>
+        <v>306</v>
       </c>
       <c r="K243" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L243" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="M243" t="s">
         <v>48</v>
@@ -16508,37 +16556,40 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>610</v>
+        <v>556</v>
       </c>
       <c r="B244" t="s">
-        <v>656</v>
+        <v>561</v>
       </c>
       <c r="C244" t="s">
-        <v>1206</v>
+        <v>1189</v>
+      </c>
+      <c r="D244" t="s">
+        <v>595</v>
+      </c>
+      <c r="E244" t="s">
+        <v>986</v>
       </c>
       <c r="F244" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G244" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H244" t="s">
         <v>13</v>
       </c>
       <c r="I244" t="s">
-        <v>141</v>
-      </c>
-      <c r="J244" t="s">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="K244" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L244" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="M244" t="s">
-        <v>832</v>
+        <v>48</v>
       </c>
       <c r="N244" t="s">
         <v>14</v>
@@ -16552,19 +16603,19 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>662</v>
+        <v>435</v>
       </c>
       <c r="B245" t="s">
-        <v>678</v>
+        <v>448</v>
       </c>
       <c r="C245" t="s">
-        <v>1208</v>
+        <v>1113</v>
       </c>
       <c r="D245" t="s">
-        <v>679</v>
+        <v>449</v>
       </c>
       <c r="E245" t="s">
-        <v>1007</v>
+        <v>917</v>
       </c>
       <c r="F245" t="s">
         <v>47</v>
@@ -16573,22 +16624,22 @@
         <v>51</v>
       </c>
       <c r="H245" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I245" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="J245" t="s">
-        <v>202</v>
+        <v>522</v>
       </c>
       <c r="K245" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="L245" t="s">
         <v>179</v>
       </c>
       <c r="M245" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N245" t="s">
         <v>14</v>
@@ -16602,19 +16653,19 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>567</v>
+        <v>438</v>
       </c>
       <c r="B246" t="s">
-        <v>571</v>
+        <v>455</v>
       </c>
       <c r="C246" t="s">
-        <v>1191</v>
+        <v>1115</v>
       </c>
       <c r="D246" t="s">
-        <v>383</v>
+        <v>456</v>
       </c>
       <c r="E246" t="s">
-        <v>904</v>
+        <v>919</v>
       </c>
       <c r="F246" t="s">
         <v>47</v>
@@ -16623,19 +16674,22 @@
         <v>32</v>
       </c>
       <c r="H246" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I246" t="s">
-        <v>268</v>
+        <v>143</v>
       </c>
       <c r="J246" t="s">
-        <v>202</v>
+        <v>524</v>
+      </c>
+      <c r="K246" t="s">
+        <v>54</v>
       </c>
       <c r="L246" t="s">
         <v>179</v>
       </c>
       <c r="M246" t="s">
-        <v>832</v>
+        <v>48</v>
       </c>
       <c r="N246" t="s">
         <v>14</v>
@@ -16649,22 +16703,22 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>362</v>
+        <v>591</v>
       </c>
       <c r="B247" t="s">
-        <v>384</v>
+        <v>600</v>
       </c>
       <c r="C247" t="s">
-        <v>1099</v>
+        <v>1198</v>
       </c>
       <c r="D247" t="s">
-        <v>385</v>
+        <v>601</v>
       </c>
       <c r="E247" t="s">
-        <v>905</v>
+        <v>993</v>
       </c>
       <c r="F247" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G247" t="s">
         <v>51</v>
@@ -16676,13 +16730,16 @@
         <v>141</v>
       </c>
       <c r="J247" t="s">
-        <v>519</v>
+        <v>488</v>
+      </c>
+      <c r="K247" t="s">
+        <v>75</v>
       </c>
       <c r="L247" t="s">
-        <v>386</v>
+        <v>187</v>
       </c>
       <c r="M247" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="N247" t="s">
         <v>14</v>
@@ -16696,40 +16753,37 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>363</v>
+        <v>1245</v>
       </c>
       <c r="B248" t="s">
-        <v>387</v>
+        <v>1261</v>
       </c>
       <c r="C248" t="s">
-        <v>1100</v>
+        <v>1262</v>
       </c>
       <c r="D248" t="s">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="E248" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="F248" t="s">
         <v>47</v>
       </c>
       <c r="G248" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="H248" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I248" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J248" t="s">
-        <v>201</v>
-      </c>
-      <c r="K248" t="s">
-        <v>54</v>
+        <v>1263</v>
       </c>
       <c r="L248" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="M248" t="s">
         <v>48</v>
@@ -16746,19 +16800,13 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>568</v>
+        <v>1332</v>
       </c>
       <c r="B249" t="s">
-        <v>572</v>
+        <v>1355</v>
       </c>
       <c r="C249" t="s">
-        <v>1192</v>
-      </c>
-      <c r="D249" t="s">
-        <v>383</v>
-      </c>
-      <c r="E249" t="s">
-        <v>904</v>
+        <v>1356</v>
       </c>
       <c r="F249" t="s">
         <v>47</v>
@@ -16767,16 +16815,19 @@
         <v>32</v>
       </c>
       <c r="H249" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I249" t="s">
-        <v>268</v>
+        <v>1274</v>
       </c>
       <c r="J249" t="s">
-        <v>520</v>
+        <v>1263</v>
+      </c>
+      <c r="K249" t="s">
+        <v>54</v>
       </c>
       <c r="L249" t="s">
-        <v>574</v>
+        <v>179</v>
       </c>
       <c r="M249" t="s">
         <v>48</v>
@@ -16793,19 +16844,13 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>578</v>
+        <v>610</v>
       </c>
       <c r="B250" t="s">
-        <v>582</v>
+        <v>656</v>
       </c>
       <c r="C250" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D250" t="s">
-        <v>583</v>
-      </c>
-      <c r="E250" t="s">
-        <v>989</v>
+        <v>1206</v>
       </c>
       <c r="F250" t="s">
         <v>47</v>
@@ -16820,16 +16865,16 @@
         <v>141</v>
       </c>
       <c r="J250" t="s">
-        <v>488</v>
+        <v>201</v>
       </c>
       <c r="K250" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="L250" t="s">
         <v>179</v>
       </c>
       <c r="M250" t="s">
-        <v>48</v>
+        <v>832</v>
       </c>
       <c r="N250" t="s">
         <v>14</v>
@@ -16843,25 +16888,25 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>621</v>
+        <v>662</v>
       </c>
       <c r="B251" t="s">
-        <v>810</v>
+        <v>678</v>
       </c>
       <c r="C251" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="D251" t="s">
-        <v>638</v>
+        <v>679</v>
       </c>
       <c r="E251" t="s">
-        <v>996</v>
+        <v>1007</v>
       </c>
       <c r="F251" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G251" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H251" t="s">
         <v>13</v>
@@ -16870,13 +16915,13 @@
         <v>141</v>
       </c>
       <c r="J251" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K251" t="s">
         <v>133</v>
       </c>
       <c r="L251" t="s">
-        <v>331</v>
+        <v>179</v>
       </c>
       <c r="M251" t="s">
         <v>48</v>
@@ -16893,19 +16938,19 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>190</v>
+        <v>567</v>
       </c>
       <c r="B252" t="s">
-        <v>199</v>
+        <v>571</v>
       </c>
       <c r="C252" t="s">
-        <v>1076</v>
+        <v>1191</v>
       </c>
       <c r="D252" t="s">
-        <v>200</v>
+        <v>383</v>
       </c>
       <c r="E252" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="F252" t="s">
         <v>47</v>
@@ -16917,19 +16962,16 @@
         <v>13</v>
       </c>
       <c r="I252" t="s">
-        <v>141</v>
+        <v>268</v>
       </c>
       <c r="J252" t="s">
-        <v>201</v>
-      </c>
-      <c r="K252" t="s">
-        <v>53</v>
+        <v>202</v>
       </c>
       <c r="L252" t="s">
         <v>179</v>
       </c>
       <c r="M252" t="s">
-        <v>48</v>
+        <v>832</v>
       </c>
       <c r="N252" t="s">
         <v>14</v>
@@ -16943,43 +16985,40 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>191</v>
+        <v>362</v>
       </c>
       <c r="B253" t="s">
-        <v>203</v>
+        <v>384</v>
       </c>
       <c r="C253" t="s">
-        <v>1077</v>
+        <v>1099</v>
       </c>
       <c r="D253" t="s">
-        <v>204</v>
+        <v>385</v>
       </c>
       <c r="E253" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="F253" t="s">
         <v>47</v>
       </c>
       <c r="G253" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H253" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I253" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J253" t="s">
-        <v>206</v>
-      </c>
-      <c r="K253" t="s">
-        <v>54</v>
+        <v>519</v>
       </c>
       <c r="L253" t="s">
-        <v>179</v>
+        <v>386</v>
       </c>
       <c r="M253" t="s">
-        <v>48</v>
+        <v>833</v>
       </c>
       <c r="N253" t="s">
         <v>14</v>
@@ -16993,25 +17032,25 @@
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>192</v>
+        <v>363</v>
       </c>
       <c r="B254" t="s">
-        <v>207</v>
+        <v>387</v>
       </c>
       <c r="C254" t="s">
-        <v>1078</v>
+        <v>1100</v>
       </c>
       <c r="D254" t="s">
-        <v>208</v>
+        <v>388</v>
       </c>
       <c r="E254" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="F254" t="s">
         <v>47</v>
       </c>
       <c r="G254" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H254" t="s">
         <v>13</v>
@@ -17023,10 +17062,10 @@
         <v>201</v>
       </c>
       <c r="K254" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L254" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M254" t="s">
         <v>48</v>
@@ -17043,19 +17082,19 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>189</v>
+        <v>568</v>
       </c>
       <c r="B255" t="s">
-        <v>197</v>
+        <v>572</v>
       </c>
       <c r="C255" t="s">
-        <v>1075</v>
+        <v>1192</v>
       </c>
       <c r="D255" t="s">
-        <v>198</v>
+        <v>383</v>
       </c>
       <c r="E255" t="s">
-        <v>885</v>
+        <v>904</v>
       </c>
       <c r="F255" t="s">
         <v>47</v>
@@ -17064,19 +17103,16 @@
         <v>32</v>
       </c>
       <c r="H255" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I255" t="s">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="J255" t="s">
-        <v>202</v>
-      </c>
-      <c r="K255" t="s">
-        <v>53</v>
+        <v>520</v>
       </c>
       <c r="L255" t="s">
-        <v>386</v>
+        <v>574</v>
       </c>
       <c r="M255" t="s">
         <v>48</v>
@@ -17093,37 +17129,40 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>622</v>
+        <v>578</v>
       </c>
       <c r="B256" t="s">
-        <v>639</v>
+        <v>582</v>
       </c>
       <c r="C256" t="s">
-        <v>1202</v>
+        <v>1193</v>
       </c>
       <c r="D256" t="s">
-        <v>640</v>
+        <v>583</v>
       </c>
       <c r="E256" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="F256" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G256" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H256" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I256" t="s">
-        <v>218</v>
+        <v>141</v>
       </c>
       <c r="J256" t="s">
-        <v>202</v>
+        <v>488</v>
+      </c>
+      <c r="K256" t="s">
+        <v>140</v>
       </c>
       <c r="L256" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="M256" t="s">
         <v>48</v>
@@ -17140,37 +17179,40 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B257" t="s">
-        <v>641</v>
+        <v>810</v>
       </c>
       <c r="C257" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="D257" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E257" t="s">
-        <v>1042</v>
+        <v>996</v>
       </c>
       <c r="F257" t="s">
         <v>78</v>
       </c>
       <c r="G257" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H257" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I257" t="s">
-        <v>446</v>
+        <v>141</v>
       </c>
       <c r="J257" t="s">
-        <v>202</v>
+        <v>201</v>
+      </c>
+      <c r="K257" t="s">
+        <v>133</v>
       </c>
       <c r="L257" t="s">
-        <v>95</v>
+        <v>331</v>
       </c>
       <c r="M257" t="s">
         <v>48</v>
@@ -17187,40 +17229,40 @@
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>674</v>
+        <v>190</v>
       </c>
       <c r="B258" t="s">
-        <v>696</v>
+        <v>199</v>
       </c>
       <c r="C258" t="s">
-        <v>1215</v>
+        <v>1076</v>
       </c>
       <c r="D258" t="s">
-        <v>699</v>
+        <v>200</v>
       </c>
       <c r="E258" t="s">
-        <v>1015</v>
+        <v>886</v>
       </c>
       <c r="F258" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G258" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H258" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I258" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J258" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K258" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="L258" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="M258" t="s">
         <v>48</v>
@@ -17237,19 +17279,19 @@
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>1284</v>
+        <v>191</v>
       </c>
       <c r="B259" t="s">
-        <v>1312</v>
+        <v>203</v>
       </c>
       <c r="C259" t="s">
-        <v>1313</v>
+        <v>1077</v>
       </c>
       <c r="D259" t="s">
-        <v>1314</v>
+        <v>204</v>
       </c>
       <c r="E259" t="s">
-        <v>1308</v>
+        <v>887</v>
       </c>
       <c r="F259" t="s">
         <v>47</v>
@@ -17261,19 +17303,19 @@
         <v>31</v>
       </c>
       <c r="I259" t="s">
-        <v>1315</v>
+        <v>143</v>
       </c>
       <c r="J259" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="K259" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="L259" t="s">
         <v>179</v>
       </c>
       <c r="M259" t="s">
-        <v>832</v>
+        <v>48</v>
       </c>
       <c r="N259" t="s">
         <v>14</v>
@@ -17287,25 +17329,25 @@
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>1289</v>
+        <v>192</v>
       </c>
       <c r="B260" t="s">
-        <v>1293</v>
+        <v>207</v>
       </c>
       <c r="C260" t="s">
-        <v>1294</v>
+        <v>1078</v>
       </c>
       <c r="D260" t="s">
-        <v>1295</v>
+        <v>208</v>
       </c>
       <c r="E260" t="s">
-        <v>1296</v>
+        <v>888</v>
       </c>
       <c r="F260" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G260" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H260" t="s">
         <v>13</v>
@@ -17314,16 +17356,16 @@
         <v>141</v>
       </c>
       <c r="J260" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K260" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="L260" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="M260" t="s">
-        <v>832</v>
+        <v>48</v>
       </c>
       <c r="N260" t="s">
         <v>14</v>
@@ -17337,13 +17379,19 @@
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>1335</v>
+        <v>189</v>
       </c>
       <c r="B261" t="s">
-        <v>1361</v>
+        <v>197</v>
       </c>
       <c r="C261" t="s">
-        <v>1362</v>
+        <v>1075</v>
+      </c>
+      <c r="D261" t="s">
+        <v>198</v>
+      </c>
+      <c r="E261" t="s">
+        <v>885</v>
       </c>
       <c r="F261" t="s">
         <v>47</v>
@@ -17352,16 +17400,19 @@
         <v>32</v>
       </c>
       <c r="H261" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I261" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="J261" t="s">
-        <v>520</v>
+        <v>202</v>
+      </c>
+      <c r="K261" t="s">
+        <v>53</v>
       </c>
       <c r="L261" t="s">
-        <v>95</v>
+        <v>386</v>
       </c>
       <c r="M261" t="s">
         <v>48</v>
@@ -17378,37 +17429,37 @@
     </row>
     <row r="262" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="B262" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="C262" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="D262" t="s">
-        <v>443</v>
+        <v>640</v>
       </c>
       <c r="E262" t="s">
-        <v>915</v>
+        <v>997</v>
       </c>
       <c r="F262" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G262" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H262" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I262" t="s">
-        <v>109</v>
-      </c>
-      <c r="K262" t="s">
-        <v>54</v>
+        <v>218</v>
+      </c>
+      <c r="J262" t="s">
+        <v>202</v>
       </c>
       <c r="L262" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="M262" t="s">
         <v>48</v>
@@ -17425,31 +17476,37 @@
     </row>
     <row r="263" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>1381</v>
+        <v>623</v>
       </c>
       <c r="B263" t="s">
-        <v>1390</v>
+        <v>641</v>
       </c>
       <c r="C263" t="s">
-        <v>1391</v>
+        <v>1203</v>
+      </c>
+      <c r="D263" t="s">
+        <v>642</v>
+      </c>
+      <c r="E263" t="s">
+        <v>1042</v>
       </c>
       <c r="F263" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G263" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H263" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I263" t="s">
-        <v>141</v>
-      </c>
-      <c r="K263" t="s">
-        <v>54</v>
+        <v>446</v>
+      </c>
+      <c r="J263" t="s">
+        <v>202</v>
       </c>
       <c r="L263" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="M263" t="s">
         <v>48</v>
@@ -17466,40 +17523,40 @@
     </row>
     <row r="264" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>431</v>
+        <v>674</v>
       </c>
       <c r="B264" t="s">
-        <v>440</v>
+        <v>696</v>
       </c>
       <c r="C264" t="s">
-        <v>1109</v>
+        <v>1215</v>
       </c>
       <c r="D264" t="s">
-        <v>443</v>
+        <v>699</v>
       </c>
       <c r="E264" t="s">
-        <v>915</v>
+        <v>1015</v>
       </c>
       <c r="F264" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G264" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H264" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I264" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="J264" t="s">
-        <v>441</v>
+        <v>202</v>
       </c>
       <c r="K264" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L264" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="M264" t="s">
         <v>48</v>
@@ -17516,19 +17573,19 @@
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>432</v>
+        <v>1284</v>
       </c>
       <c r="B265" t="s">
-        <v>442</v>
+        <v>1312</v>
       </c>
       <c r="C265" t="s">
-        <v>1110</v>
+        <v>1313</v>
       </c>
       <c r="D265" t="s">
-        <v>443</v>
+        <v>1314</v>
       </c>
       <c r="E265" t="s">
-        <v>915</v>
+        <v>1308</v>
       </c>
       <c r="F265" t="s">
         <v>47</v>
@@ -17537,22 +17594,22 @@
         <v>32</v>
       </c>
       <c r="H265" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I265" t="s">
-        <v>109</v>
+        <v>1315</v>
       </c>
       <c r="J265" t="s">
         <v>202</v>
       </c>
       <c r="K265" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="L265" t="s">
         <v>179</v>
       </c>
       <c r="M265" t="s">
-        <v>48</v>
+        <v>832</v>
       </c>
       <c r="N265" t="s">
         <v>14</v>
@@ -17566,43 +17623,43 @@
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>439</v>
+        <v>1289</v>
       </c>
       <c r="B266" t="s">
-        <v>457</v>
+        <v>1293</v>
       </c>
       <c r="C266" t="s">
-        <v>1116</v>
+        <v>1294</v>
       </c>
       <c r="D266" t="s">
-        <v>443</v>
+        <v>1295</v>
       </c>
       <c r="E266" t="s">
-        <v>915</v>
+        <v>1296</v>
       </c>
       <c r="F266" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G266" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H266" t="s">
         <v>13</v>
       </c>
       <c r="I266" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="J266" t="s">
         <v>202</v>
       </c>
       <c r="K266" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L266" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="M266" t="s">
-        <v>50</v>
+        <v>832</v>
       </c>
       <c r="N266" t="s">
         <v>14</v>
@@ -17616,19 +17673,13 @@
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>665</v>
+        <v>1335</v>
       </c>
       <c r="B267" t="s">
-        <v>684</v>
+        <v>1361</v>
       </c>
       <c r="C267" t="s">
-        <v>684</v>
-      </c>
-      <c r="D267" t="s">
-        <v>685</v>
-      </c>
-      <c r="E267" t="s">
-        <v>1010</v>
+        <v>1362</v>
       </c>
       <c r="F267" t="s">
         <v>47</v>
@@ -17640,16 +17691,13 @@
         <v>13</v>
       </c>
       <c r="I267" t="s">
-        <v>446</v>
+        <v>141</v>
       </c>
       <c r="J267" t="s">
-        <v>202</v>
-      </c>
-      <c r="K267" t="s">
-        <v>133</v>
+        <v>520</v>
       </c>
       <c r="L267" t="s">
-        <v>386</v>
+        <v>95</v>
       </c>
       <c r="M267" t="s">
         <v>48</v>
@@ -17666,19 +17714,19 @@
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>669</v>
+        <v>608</v>
       </c>
       <c r="B268" t="s">
-        <v>820</v>
+        <v>649</v>
       </c>
       <c r="C268" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="D268" t="s">
-        <v>685</v>
+        <v>443</v>
       </c>
       <c r="E268" t="s">
-        <v>1010</v>
+        <v>915</v>
       </c>
       <c r="F268" t="s">
         <v>47</v>
@@ -17690,13 +17738,10 @@
         <v>13</v>
       </c>
       <c r="I268" t="s">
-        <v>446</v>
-      </c>
-      <c r="J268" t="s">
-        <v>202</v>
+        <v>109</v>
       </c>
       <c r="K268" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="L268" t="s">
         <v>180</v>
@@ -17716,34 +17761,25 @@
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>437</v>
+        <v>1381</v>
       </c>
       <c r="B269" t="s">
-        <v>453</v>
+        <v>1390</v>
       </c>
       <c r="C269" t="s">
-        <v>1114</v>
-      </c>
-      <c r="D269" t="s">
-        <v>454</v>
-      </c>
-      <c r="E269" t="s">
-        <v>918</v>
+        <v>1391</v>
       </c>
       <c r="F269" t="s">
         <v>47</v>
       </c>
       <c r="G269" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="H269" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I269" t="s">
-        <v>143</v>
-      </c>
-      <c r="J269" t="s">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="K269" t="s">
         <v>54</v>
@@ -17766,13 +17802,19 @@
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>1239</v>
+        <v>431</v>
       </c>
       <c r="B270" t="s">
-        <v>1247</v>
+        <v>440</v>
       </c>
       <c r="C270" t="s">
-        <v>1247</v>
+        <v>1109</v>
+      </c>
+      <c r="D270" t="s">
+        <v>443</v>
+      </c>
+      <c r="E270" t="s">
+        <v>915</v>
       </c>
       <c r="F270" t="s">
         <v>47</v>
@@ -17781,13 +17823,13 @@
         <v>32</v>
       </c>
       <c r="H270" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I270" t="s">
-        <v>446</v>
+        <v>109</v>
       </c>
       <c r="J270" t="s">
-        <v>202</v>
+        <v>441</v>
       </c>
       <c r="K270" t="s">
         <v>54</v>
@@ -17810,19 +17852,19 @@
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>607</v>
+        <v>432</v>
       </c>
       <c r="B271" t="s">
-        <v>648</v>
+        <v>442</v>
       </c>
       <c r="C271" t="s">
-        <v>648</v>
+        <v>1110</v>
       </c>
       <c r="D271" t="s">
-        <v>812</v>
+        <v>443</v>
       </c>
       <c r="E271" t="s">
-        <v>1000</v>
+        <v>915</v>
       </c>
       <c r="F271" t="s">
         <v>47</v>
@@ -17834,7 +17876,10 @@
         <v>13</v>
       </c>
       <c r="I271" t="s">
-        <v>141</v>
+        <v>109</v>
+      </c>
+      <c r="J271" t="s">
+        <v>202</v>
       </c>
       <c r="K271" t="s">
         <v>54</v>
@@ -17843,7 +17888,7 @@
         <v>179</v>
       </c>
       <c r="M271" t="s">
-        <v>833</v>
+        <v>48</v>
       </c>
       <c r="N271" t="s">
         <v>14</v>
@@ -17857,40 +17902,43 @@
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>361</v>
+        <v>439</v>
       </c>
       <c r="B272" t="s">
-        <v>382</v>
+        <v>457</v>
       </c>
       <c r="C272" t="s">
-        <v>1098</v>
+        <v>1116</v>
       </c>
       <c r="D272" t="s">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="E272" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="F272" t="s">
         <v>47</v>
       </c>
       <c r="G272" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H272" t="s">
         <v>13</v>
       </c>
       <c r="I272" t="s">
-        <v>268</v>
+        <v>109</v>
       </c>
       <c r="J272" t="s">
-        <v>488</v>
+        <v>202</v>
+      </c>
+      <c r="K272" t="s">
+        <v>54</v>
       </c>
       <c r="L272" t="s">
-        <v>386</v>
+        <v>179</v>
       </c>
       <c r="M272" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N272" t="s">
         <v>14</v>
@@ -17904,40 +17952,43 @@
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="B273" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="C273" t="s">
-        <v>1214</v>
+        <v>684</v>
       </c>
       <c r="D273" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="E273" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="F273" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G273" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H273" t="s">
         <v>13</v>
       </c>
       <c r="I273" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="J273" t="s">
-        <v>695</v>
+        <v>202</v>
+      </c>
+      <c r="K273" t="s">
+        <v>133</v>
       </c>
       <c r="L273" t="s">
-        <v>187</v>
+        <v>386</v>
       </c>
       <c r="M273" t="s">
-        <v>833</v>
+        <v>48</v>
       </c>
       <c r="N273" t="s">
         <v>14</v>
@@ -17951,22 +18002,22 @@
     </row>
     <row r="274" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>700</v>
+        <v>669</v>
       </c>
       <c r="B274" t="s">
-        <v>704</v>
+        <v>820</v>
       </c>
       <c r="C274" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="D274" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="E274" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="F274" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G274" t="s">
         <v>32</v>
@@ -17975,16 +18026,19 @@
         <v>13</v>
       </c>
       <c r="I274" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="J274" t="s">
-        <v>520</v>
+        <v>202</v>
+      </c>
+      <c r="K274" t="s">
+        <v>205</v>
       </c>
       <c r="L274" t="s">
-        <v>341</v>
+        <v>180</v>
       </c>
       <c r="M274" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N274" t="s">
         <v>14</v>
@@ -17998,40 +18052,43 @@
     </row>
     <row r="275" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
-        <v>618</v>
+        <v>437</v>
       </c>
       <c r="B275" t="s">
-        <v>627</v>
+        <v>453</v>
       </c>
       <c r="C275" t="s">
-        <v>1200</v>
+        <v>1114</v>
       </c>
       <c r="D275" t="s">
-        <v>628</v>
+        <v>454</v>
       </c>
       <c r="E275" t="s">
-        <v>995</v>
+        <v>918</v>
       </c>
       <c r="F275" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G275" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="H275" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I275" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J275" t="s">
-        <v>520</v>
+        <v>202</v>
+      </c>
+      <c r="K275" t="s">
+        <v>54</v>
       </c>
       <c r="L275" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="M275" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N275" t="s">
         <v>14</v>
@@ -18045,37 +18102,31 @@
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
-        <v>579</v>
+        <v>1239</v>
       </c>
       <c r="B276" t="s">
-        <v>584</v>
+        <v>1247</v>
       </c>
       <c r="C276" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D276" t="s">
-        <v>547</v>
-      </c>
-      <c r="E276" t="s">
-        <v>980</v>
+        <v>1247</v>
       </c>
       <c r="F276" t="s">
         <v>47</v>
       </c>
       <c r="G276" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H276" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I276" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="J276" t="s">
-        <v>585</v>
+        <v>202</v>
       </c>
       <c r="K276" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="L276" t="s">
         <v>179</v>
@@ -18095,25 +18146,25 @@
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
-        <v>558</v>
+        <v>607</v>
       </c>
       <c r="B277" t="s">
-        <v>807</v>
+        <v>648</v>
       </c>
       <c r="C277" t="s">
-        <v>1234</v>
+        <v>648</v>
       </c>
       <c r="D277" t="s">
-        <v>563</v>
+        <v>812</v>
       </c>
       <c r="E277" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="F277" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G277" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H277" t="s">
         <v>13</v>
@@ -18121,17 +18172,14 @@
       <c r="I277" t="s">
         <v>141</v>
       </c>
-      <c r="J277" t="s">
-        <v>488</v>
-      </c>
       <c r="K277" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L277" t="s">
-        <v>564</v>
+        <v>179</v>
       </c>
       <c r="M277" t="s">
-        <v>48</v>
+        <v>833</v>
       </c>
       <c r="N277" t="s">
         <v>14</v>
@@ -18145,40 +18193,40 @@
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>701</v>
+        <v>361</v>
       </c>
       <c r="B278" t="s">
-        <v>705</v>
+        <v>382</v>
       </c>
       <c r="C278" t="s">
-        <v>1217</v>
+        <v>1098</v>
       </c>
       <c r="D278" t="s">
-        <v>707</v>
+        <v>383</v>
       </c>
       <c r="E278" t="s">
-        <v>1043</v>
+        <v>904</v>
       </c>
       <c r="F278" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G278" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H278" t="s">
         <v>13</v>
       </c>
       <c r="I278" t="s">
-        <v>141</v>
+        <v>268</v>
       </c>
       <c r="J278" t="s">
         <v>488</v>
       </c>
       <c r="L278" t="s">
-        <v>187</v>
+        <v>386</v>
       </c>
       <c r="M278" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N278" t="s">
         <v>14</v>
@@ -18192,19 +18240,19 @@
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
-        <v>1291</v>
+        <v>673</v>
       </c>
       <c r="B279" t="s">
-        <v>1299</v>
+        <v>694</v>
       </c>
       <c r="C279" t="s">
-        <v>1300</v>
+        <v>1214</v>
       </c>
       <c r="D279" t="s">
-        <v>1301</v>
+        <v>698</v>
       </c>
       <c r="E279" t="s">
-        <v>1302</v>
+        <v>1014</v>
       </c>
       <c r="F279" t="s">
         <v>78</v>
@@ -18219,16 +18267,13 @@
         <v>141</v>
       </c>
       <c r="J279" t="s">
-        <v>488</v>
-      </c>
-      <c r="K279" t="s">
-        <v>75</v>
+        <v>695</v>
       </c>
       <c r="L279" t="s">
         <v>187</v>
       </c>
       <c r="M279" t="s">
-        <v>48</v>
+        <v>833</v>
       </c>
       <c r="N279" t="s">
         <v>14</v>
@@ -18242,37 +18287,40 @@
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="B280" t="s">
-        <v>740</v>
+        <v>704</v>
       </c>
       <c r="C280" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D280" t="s">
-        <v>743</v>
+        <v>706</v>
       </c>
       <c r="E280" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F280" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G280" t="s">
         <v>32</v>
       </c>
       <c r="H280" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I280" t="s">
-        <v>217</v>
+        <v>141</v>
+      </c>
+      <c r="J280" t="s">
+        <v>520</v>
       </c>
       <c r="L280" t="s">
-        <v>179</v>
+        <v>341</v>
       </c>
       <c r="M280" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N280" t="s">
         <v>14</v>
@@ -18286,22 +18334,22 @@
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>721</v>
+        <v>618</v>
       </c>
       <c r="B281" t="s">
-        <v>734</v>
+        <v>627</v>
       </c>
       <c r="C281" t="s">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="D281" t="s">
-        <v>746</v>
+        <v>628</v>
       </c>
       <c r="E281" t="s">
-        <v>1020</v>
+        <v>995</v>
       </c>
       <c r="F281" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G281" t="s">
         <v>51</v>
@@ -18313,16 +18361,13 @@
         <v>141</v>
       </c>
       <c r="J281" t="s">
-        <v>488</v>
-      </c>
-      <c r="K281" t="s">
-        <v>75</v>
+        <v>520</v>
       </c>
       <c r="L281" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="M281" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N281" t="s">
         <v>14</v>
@@ -18336,19 +18381,19 @@
     </row>
     <row r="282" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
-        <v>727</v>
+        <v>579</v>
       </c>
       <c r="B282" t="s">
-        <v>730</v>
+        <v>584</v>
       </c>
       <c r="C282" t="s">
-        <v>1227</v>
+        <v>1194</v>
       </c>
       <c r="D282" t="s">
-        <v>747</v>
+        <v>547</v>
       </c>
       <c r="E282" t="s">
-        <v>1021</v>
+        <v>980</v>
       </c>
       <c r="F282" t="s">
         <v>47</v>
@@ -18363,10 +18408,10 @@
         <v>141</v>
       </c>
       <c r="J282" t="s">
-        <v>520</v>
+        <v>585</v>
       </c>
       <c r="K282" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="L282" t="s">
         <v>179</v>
@@ -18386,37 +18431,40 @@
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>1268</v>
+        <v>558</v>
       </c>
       <c r="B283" t="s">
-        <v>1275</v>
+        <v>807</v>
       </c>
       <c r="C283" t="s">
-        <v>1273</v>
+        <v>1234</v>
       </c>
       <c r="D283" t="s">
-        <v>1276</v>
+        <v>563</v>
       </c>
       <c r="E283" t="s">
-        <v>1276</v>
+        <v>988</v>
       </c>
       <c r="F283" t="s">
         <v>78</v>
       </c>
       <c r="G283" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H283" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I283" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J283" t="s">
-        <v>277</v>
+        <v>488</v>
+      </c>
+      <c r="K283" t="s">
+        <v>75</v>
       </c>
       <c r="L283" t="s">
-        <v>95</v>
+        <v>564</v>
       </c>
       <c r="M283" t="s">
         <v>48</v>
@@ -18433,37 +18481,40 @@
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
-        <v>1288</v>
+        <v>701</v>
       </c>
       <c r="B284" t="s">
-        <v>1292</v>
+        <v>705</v>
       </c>
       <c r="C284" t="s">
-        <v>1303</v>
+        <v>1217</v>
+      </c>
+      <c r="D284" t="s">
+        <v>707</v>
+      </c>
+      <c r="E284" t="s">
+        <v>1043</v>
       </c>
       <c r="F284" t="s">
         <v>78</v>
       </c>
       <c r="G284" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H284" t="s">
         <v>13</v>
       </c>
       <c r="I284" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="J284" t="s">
-        <v>110</v>
-      </c>
-      <c r="K284" t="s">
-        <v>75</v>
+        <v>488</v>
       </c>
       <c r="L284" t="s">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="M284" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N284" t="s">
         <v>14</v>
@@ -18477,22 +18528,22 @@
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
-        <v>1323</v>
+        <v>1291</v>
       </c>
       <c r="B285" t="s">
-        <v>1338</v>
+        <v>1299</v>
       </c>
       <c r="C285" t="s">
-        <v>1346</v>
+        <v>1300</v>
       </c>
       <c r="D285" t="s">
-        <v>383</v>
+        <v>1301</v>
       </c>
       <c r="E285" t="s">
-        <v>904</v>
+        <v>1302</v>
       </c>
       <c r="F285" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G285" t="s">
         <v>51</v>
@@ -18506,8 +18557,11 @@
       <c r="J285" t="s">
         <v>488</v>
       </c>
+      <c r="K285" t="s">
+        <v>75</v>
+      </c>
       <c r="L285" t="s">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="M285" t="s">
         <v>48</v>
@@ -18524,19 +18578,19 @@
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
-        <v>393</v>
+        <v>715</v>
       </c>
       <c r="B286" t="s">
-        <v>786</v>
+        <v>740</v>
       </c>
       <c r="C286" t="s">
-        <v>1104</v>
+        <v>1218</v>
       </c>
       <c r="D286" t="s">
-        <v>398</v>
+        <v>743</v>
       </c>
       <c r="E286" t="s">
-        <v>908</v>
+        <v>1017</v>
       </c>
       <c r="F286" t="s">
         <v>47</v>
@@ -18545,13 +18599,10 @@
         <v>32</v>
       </c>
       <c r="H286" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I286" t="s">
-        <v>141</v>
-      </c>
-      <c r="J286" t="s">
-        <v>520</v>
+        <v>217</v>
       </c>
       <c r="L286" t="s">
         <v>179</v>
@@ -18571,19 +18622,19 @@
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
-        <v>188</v>
+        <v>721</v>
       </c>
       <c r="B287" t="s">
-        <v>193</v>
+        <v>734</v>
       </c>
       <c r="C287" t="s">
-        <v>1074</v>
+        <v>1225</v>
       </c>
       <c r="D287" t="s">
-        <v>194</v>
+        <v>746</v>
       </c>
       <c r="E287" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="F287" t="s">
         <v>47</v>
@@ -18598,7 +18649,7 @@
         <v>141</v>
       </c>
       <c r="J287" t="s">
-        <v>195</v>
+        <v>488</v>
       </c>
       <c r="K287" t="s">
         <v>75</v>
@@ -18621,25 +18672,25 @@
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
-        <v>366</v>
+        <v>727</v>
       </c>
       <c r="B288" t="s">
-        <v>392</v>
+        <v>730</v>
       </c>
       <c r="C288" t="s">
-        <v>1103</v>
+        <v>1227</v>
       </c>
       <c r="D288" t="s">
-        <v>391</v>
+        <v>747</v>
       </c>
       <c r="E288" t="s">
-        <v>1030</v>
+        <v>1021</v>
       </c>
       <c r="F288" t="s">
         <v>47</v>
       </c>
       <c r="G288" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H288" t="s">
         <v>13</v>
@@ -18648,10 +18699,13 @@
         <v>141</v>
       </c>
       <c r="J288" t="s">
-        <v>277</v>
+        <v>520</v>
+      </c>
+      <c r="K288" t="s">
+        <v>140</v>
       </c>
       <c r="L288" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="M288" t="s">
         <v>48</v>
@@ -18668,31 +18722,31 @@
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
-        <v>1325</v>
+        <v>1268</v>
       </c>
       <c r="B289" t="s">
-        <v>1340</v>
+        <v>1275</v>
       </c>
       <c r="C289" t="s">
-        <v>1340</v>
+        <v>1273</v>
       </c>
       <c r="D289" t="s">
-        <v>1349</v>
+        <v>1276</v>
       </c>
       <c r="E289" t="s">
-        <v>1348</v>
+        <v>1276</v>
       </c>
       <c r="F289" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G289" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H289" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I289" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J289" t="s">
         <v>277</v>
@@ -18715,19 +18769,13 @@
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
-        <v>61</v>
+        <v>1288</v>
       </c>
       <c r="B290" t="s">
-        <v>70</v>
+        <v>1292</v>
       </c>
       <c r="C290" t="s">
-        <v>1128</v>
-      </c>
-      <c r="D290" t="s">
-        <v>289</v>
-      </c>
-      <c r="E290" t="s">
-        <v>929</v>
+        <v>1303</v>
       </c>
       <c r="F290" t="s">
         <v>78</v>
@@ -18739,13 +18787,16 @@
         <v>13</v>
       </c>
       <c r="I290" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="J290" t="s">
-        <v>520</v>
+        <v>110</v>
+      </c>
+      <c r="K290" t="s">
+        <v>75</v>
       </c>
       <c r="L290" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="M290" t="s">
         <v>48</v>
@@ -18762,22 +18813,22 @@
     </row>
     <row r="291" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
-        <v>125</v>
+        <v>1323</v>
       </c>
       <c r="B291" t="s">
-        <v>131</v>
+        <v>1338</v>
       </c>
       <c r="C291" t="s">
-        <v>1130</v>
+        <v>1346</v>
       </c>
       <c r="D291" t="s">
-        <v>132</v>
+        <v>383</v>
       </c>
       <c r="E291" t="s">
-        <v>931</v>
+        <v>904</v>
       </c>
       <c r="F291" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G291" t="s">
         <v>51</v>
@@ -18789,16 +18840,13 @@
         <v>141</v>
       </c>
       <c r="J291" t="s">
-        <v>110</v>
-      </c>
-      <c r="K291" t="s">
-        <v>133</v>
+        <v>488</v>
       </c>
       <c r="L291" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="M291" t="s">
-        <v>832</v>
+        <v>48</v>
       </c>
       <c r="N291" t="s">
         <v>14</v>
@@ -18812,13 +18860,19 @@
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
-        <v>713</v>
+        <v>393</v>
       </c>
       <c r="B292" t="s">
-        <v>741</v>
+        <v>786</v>
       </c>
       <c r="C292" t="s">
-        <v>1229</v>
+        <v>1104</v>
+      </c>
+      <c r="D292" t="s">
+        <v>398</v>
+      </c>
+      <c r="E292" t="s">
+        <v>908</v>
       </c>
       <c r="F292" t="s">
         <v>47</v>
@@ -18832,6 +18886,9 @@
       <c r="I292" t="s">
         <v>141</v>
       </c>
+      <c r="J292" t="s">
+        <v>520</v>
+      </c>
       <c r="L292" t="s">
         <v>179</v>
       </c>
@@ -18850,19 +18907,25 @@
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
-        <v>714</v>
+        <v>188</v>
       </c>
       <c r="B293" t="s">
-        <v>742</v>
+        <v>193</v>
       </c>
       <c r="C293" t="s">
-        <v>1230</v>
+        <v>1074</v>
+      </c>
+      <c r="D293" t="s">
+        <v>194</v>
+      </c>
+      <c r="E293" t="s">
+        <v>1025</v>
       </c>
       <c r="F293" t="s">
         <v>47</v>
       </c>
       <c r="G293" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H293" t="s">
         <v>13</v>
@@ -18870,8 +18933,14 @@
       <c r="I293" t="s">
         <v>141</v>
       </c>
+      <c r="J293" t="s">
+        <v>195</v>
+      </c>
+      <c r="K293" t="s">
+        <v>75</v>
+      </c>
       <c r="L293" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="M293" t="s">
         <v>48</v>
@@ -18888,13 +18957,19 @@
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
-        <v>835</v>
+        <v>366</v>
       </c>
       <c r="B294" t="s">
-        <v>838</v>
+        <v>392</v>
       </c>
       <c r="C294" t="s">
-        <v>1231</v>
+        <v>1103</v>
+      </c>
+      <c r="D294" t="s">
+        <v>391</v>
+      </c>
+      <c r="E294" t="s">
+        <v>1030</v>
       </c>
       <c r="F294" t="s">
         <v>47</v>
@@ -18911,11 +18986,8 @@
       <c r="J294" t="s">
         <v>277</v>
       </c>
-      <c r="K294" t="s">
-        <v>54</v>
-      </c>
       <c r="L294" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="M294" t="s">
         <v>48</v>
@@ -18932,28 +19004,37 @@
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B295" t="s">
-        <v>1341</v>
+        <v>1340</v>
+      </c>
+      <c r="C295" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E295" t="s">
+        <v>1348</v>
       </c>
       <c r="F295" t="s">
         <v>47</v>
       </c>
       <c r="G295" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H295" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I295" t="s">
-        <v>108</v>
-      </c>
-      <c r="K295" t="s">
-        <v>54</v>
+        <v>141</v>
+      </c>
+      <c r="J295" t="s">
+        <v>277</v>
       </c>
       <c r="L295" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="M295" t="s">
         <v>48</v>
@@ -18970,22 +19051,22 @@
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
-        <v>1333</v>
+        <v>61</v>
       </c>
       <c r="B296" t="s">
-        <v>1357</v>
+        <v>70</v>
       </c>
       <c r="C296" t="s">
-        <v>1358</v>
+        <v>1128</v>
       </c>
       <c r="D296" t="s">
-        <v>1314</v>
+        <v>289</v>
       </c>
       <c r="E296" t="s">
-        <v>980</v>
+        <v>929</v>
       </c>
       <c r="F296" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G296" t="s">
         <v>51</v>
@@ -18997,10 +19078,10 @@
         <v>141</v>
       </c>
       <c r="J296" t="s">
-        <v>110</v>
+        <v>520</v>
       </c>
       <c r="L296" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="M296" t="s">
         <v>48</v>
@@ -19017,19 +19098,19 @@
     </row>
     <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>458</v>
+        <v>125</v>
       </c>
       <c r="B297" t="s">
-        <v>546</v>
+        <v>131</v>
       </c>
       <c r="C297" t="s">
-        <v>1235</v>
+        <v>1130</v>
       </c>
       <c r="D297" t="s">
-        <v>547</v>
+        <v>132</v>
       </c>
       <c r="E297" t="s">
-        <v>980</v>
+        <v>931</v>
       </c>
       <c r="F297" t="s">
         <v>78</v>
@@ -19053,7 +19134,7 @@
         <v>179</v>
       </c>
       <c r="M297" t="s">
-        <v>48</v>
+        <v>832</v>
       </c>
       <c r="N297" t="s">
         <v>14</v>
@@ -19067,25 +19148,19 @@
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="B298" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="C298" t="s">
-        <v>1232</v>
-      </c>
-      <c r="D298" t="s">
-        <v>547</v>
-      </c>
-      <c r="E298" t="s">
-        <v>980</v>
+        <v>1229</v>
       </c>
       <c r="F298" t="s">
         <v>47</v>
       </c>
       <c r="G298" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H298" t="s">
         <v>13</v>
@@ -19111,25 +19186,19 @@
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>593</v>
+        <v>714</v>
       </c>
       <c r="B299" t="s">
-        <v>602</v>
+        <v>742</v>
       </c>
       <c r="C299" t="s">
-        <v>1199</v>
-      </c>
-      <c r="D299" t="s">
-        <v>603</v>
-      </c>
-      <c r="E299" t="s">
-        <v>994</v>
+        <v>1230</v>
       </c>
       <c r="F299" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G299" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H299" t="s">
         <v>13</v>
@@ -19137,17 +19206,11 @@
       <c r="I299" t="s">
         <v>141</v>
       </c>
-      <c r="J299" t="s">
-        <v>277</v>
-      </c>
-      <c r="K299" t="s">
-        <v>75</v>
-      </c>
       <c r="L299" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="M299" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N299" t="s">
         <v>14</v>
@@ -19161,22 +19224,16 @@
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
-        <v>294</v>
+        <v>835</v>
       </c>
       <c r="B300" t="s">
-        <v>310</v>
+        <v>838</v>
       </c>
       <c r="C300" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D300" t="s">
-        <v>311</v>
-      </c>
-      <c r="E300" t="s">
-        <v>968</v>
+        <v>1231</v>
       </c>
       <c r="F300" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G300" t="s">
         <v>32</v>
@@ -19190,11 +19247,14 @@
       <c r="J300" t="s">
         <v>277</v>
       </c>
+      <c r="K300" t="s">
+        <v>54</v>
+      </c>
       <c r="L300" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="M300" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N300" t="s">
         <v>14</v>
@@ -19208,19 +19268,13 @@
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>1379</v>
+        <v>1416</v>
       </c>
       <c r="B301" t="s">
-        <v>1384</v>
+        <v>1437</v>
       </c>
       <c r="C301" t="s">
-        <v>1384</v>
-      </c>
-      <c r="D301" t="s">
-        <v>1388</v>
-      </c>
-      <c r="E301" t="s">
-        <v>1389</v>
+        <v>1437</v>
       </c>
       <c r="F301" t="s">
         <v>47</v>
@@ -19255,40 +19309,31 @@
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>1380</v>
+        <v>1326</v>
       </c>
       <c r="B302" t="s">
-        <v>1385</v>
-      </c>
-      <c r="C302" t="s">
-        <v>1386</v>
-      </c>
-      <c r="D302" t="s">
-        <v>1387</v>
-      </c>
-      <c r="E302" t="s">
-        <v>1113</v>
+        <v>1341</v>
       </c>
       <c r="F302" t="s">
         <v>47</v>
       </c>
       <c r="G302" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="H302" t="s">
         <v>31</v>
       </c>
       <c r="I302" t="s">
-        <v>446</v>
-      </c>
-      <c r="J302" t="s">
-        <v>206</v>
+        <v>108</v>
+      </c>
+      <c r="K302" t="s">
+        <v>54</v>
       </c>
       <c r="L302" t="s">
         <v>179</v>
       </c>
       <c r="M302" t="s">
-        <v>833</v>
+        <v>48</v>
       </c>
       <c r="N302" t="s">
         <v>14</v>
@@ -19302,19 +19347,25 @@
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>1416</v>
+        <v>1333</v>
       </c>
       <c r="B303" t="s">
-        <v>1437</v>
+        <v>1357</v>
       </c>
       <c r="C303" t="s">
-        <v>1437</v>
+        <v>1358</v>
+      </c>
+      <c r="D303" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E303" t="s">
+        <v>980</v>
       </c>
       <c r="F303" t="s">
         <v>47</v>
       </c>
       <c r="G303" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H303" t="s">
         <v>13</v>
@@ -19322,22 +19373,360 @@
       <c r="I303" t="s">
         <v>141</v>
       </c>
-      <c r="K303" t="s">
+      <c r="J303" t="s">
+        <v>110</v>
+      </c>
+      <c r="L303" t="s">
+        <v>95</v>
+      </c>
+      <c r="M303" t="s">
+        <v>48</v>
+      </c>
+      <c r="N303" t="s">
+        <v>14</v>
+      </c>
+      <c r="O303" t="s">
+        <v>15</v>
+      </c>
+      <c r="P303" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A304" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B304" t="s">
+        <v>546</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D304" t="s">
+        <v>547</v>
+      </c>
+      <c r="E304" t="s">
+        <v>980</v>
+      </c>
+      <c r="F304" t="s">
+        <v>78</v>
+      </c>
+      <c r="G304" t="s">
+        <v>51</v>
+      </c>
+      <c r="H304" t="s">
+        <v>13</v>
+      </c>
+      <c r="I304" t="s">
+        <v>141</v>
+      </c>
+      <c r="J304" t="s">
+        <v>110</v>
+      </c>
+      <c r="K304" t="s">
+        <v>133</v>
+      </c>
+      <c r="L304" t="s">
+        <v>179</v>
+      </c>
+      <c r="M304" t="s">
+        <v>48</v>
+      </c>
+      <c r="N304" t="s">
+        <v>14</v>
+      </c>
+      <c r="O304" t="s">
+        <v>15</v>
+      </c>
+      <c r="P304" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A305" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B305" t="s">
+        <v>733</v>
+      </c>
+      <c r="C305" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D305" t="s">
+        <v>547</v>
+      </c>
+      <c r="E305" t="s">
+        <v>980</v>
+      </c>
+      <c r="F305" t="s">
+        <v>47</v>
+      </c>
+      <c r="G305" t="s">
+        <v>51</v>
+      </c>
+      <c r="H305" t="s">
+        <v>13</v>
+      </c>
+      <c r="I305" t="s">
+        <v>141</v>
+      </c>
+      <c r="L305" t="s">
+        <v>179</v>
+      </c>
+      <c r="M305" t="s">
+        <v>48</v>
+      </c>
+      <c r="N305" t="s">
+        <v>14</v>
+      </c>
+      <c r="O305" t="s">
+        <v>15</v>
+      </c>
+      <c r="P305" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A306" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B306" t="s">
+        <v>602</v>
+      </c>
+      <c r="C306" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D306" t="s">
+        <v>603</v>
+      </c>
+      <c r="E306" t="s">
+        <v>994</v>
+      </c>
+      <c r="F306" t="s">
+        <v>78</v>
+      </c>
+      <c r="G306" t="s">
+        <v>51</v>
+      </c>
+      <c r="H306" t="s">
+        <v>13</v>
+      </c>
+      <c r="I306" t="s">
+        <v>141</v>
+      </c>
+      <c r="J306" t="s">
+        <v>277</v>
+      </c>
+      <c r="K306" t="s">
+        <v>75</v>
+      </c>
+      <c r="L306" t="s">
+        <v>95</v>
+      </c>
+      <c r="M306" t="s">
+        <v>49</v>
+      </c>
+      <c r="N306" t="s">
+        <v>14</v>
+      </c>
+      <c r="O306" t="s">
+        <v>15</v>
+      </c>
+      <c r="P306" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="307" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A307" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B307" t="s">
+        <v>310</v>
+      </c>
+      <c r="C307" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D307" t="s">
+        <v>311</v>
+      </c>
+      <c r="E307" t="s">
+        <v>968</v>
+      </c>
+      <c r="F307" t="s">
+        <v>78</v>
+      </c>
+      <c r="G307" t="s">
+        <v>32</v>
+      </c>
+      <c r="H307" t="s">
+        <v>13</v>
+      </c>
+      <c r="I307" t="s">
+        <v>141</v>
+      </c>
+      <c r="J307" t="s">
+        <v>277</v>
+      </c>
+      <c r="L307" t="s">
+        <v>95</v>
+      </c>
+      <c r="M307" t="s">
+        <v>49</v>
+      </c>
+      <c r="N307" t="s">
+        <v>14</v>
+      </c>
+      <c r="O307" t="s">
+        <v>15</v>
+      </c>
+      <c r="P307" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="308" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A308" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C308" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D308" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E308" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F308" t="s">
+        <v>47</v>
+      </c>
+      <c r="G308" t="s">
+        <v>32</v>
+      </c>
+      <c r="H308" t="s">
+        <v>13</v>
+      </c>
+      <c r="I308" t="s">
+        <v>141</v>
+      </c>
+      <c r="K308" t="s">
         <v>54</v>
       </c>
-      <c r="L303" t="s">
+      <c r="L308" t="s">
         <v>179</v>
       </c>
-      <c r="M303" t="s">
-        <v>48</v>
-      </c>
-      <c r="N303" t="s">
-        <v>14</v>
-      </c>
-      <c r="O303" t="s">
-        <v>15</v>
-      </c>
-      <c r="P303" t="s">
+      <c r="M308" t="s">
+        <v>48</v>
+      </c>
+      <c r="N308" t="s">
+        <v>14</v>
+      </c>
+      <c r="O308" t="s">
+        <v>15</v>
+      </c>
+      <c r="P308" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="309" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A309" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C309" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D309" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E309" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F309" t="s">
+        <v>47</v>
+      </c>
+      <c r="G309" t="s">
+        <v>119</v>
+      </c>
+      <c r="H309" t="s">
+        <v>31</v>
+      </c>
+      <c r="I309" t="s">
+        <v>446</v>
+      </c>
+      <c r="J309" t="s">
+        <v>206</v>
+      </c>
+      <c r="K309" t="s">
+        <v>54</v>
+      </c>
+      <c r="L309" t="s">
+        <v>179</v>
+      </c>
+      <c r="M309" t="s">
+        <v>833</v>
+      </c>
+      <c r="N309" t="s">
+        <v>14</v>
+      </c>
+      <c r="O309" t="s">
+        <v>15</v>
+      </c>
+      <c r="P309" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="310" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A310" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C310" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E310" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F310" t="s">
+        <v>47</v>
+      </c>
+      <c r="G310" t="s">
+        <v>32</v>
+      </c>
+      <c r="H310" t="s">
+        <v>31</v>
+      </c>
+      <c r="I310" t="s">
+        <v>446</v>
+      </c>
+      <c r="J310" t="s">
+        <v>277</v>
+      </c>
+      <c r="K310" t="s">
+        <v>54</v>
+      </c>
+      <c r="L310" t="s">
+        <v>179</v>
+      </c>
+      <c r="M310" t="s">
+        <v>48</v>
+      </c>
+      <c r="N310" t="s">
+        <v>14</v>
+      </c>
+      <c r="O310" t="s">
+        <v>15</v>
+      </c>
+      <c r="P310" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1424E2C5-E80C-EA42-A62E-710C89715602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6D7424-D2A2-4F45-804C-C10D6D9A27CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -1699,9 +1699,6 @@
     <t>Choose Marist Brothers</t>
   </si>
   <si>
-    <t>Para sudadera Prov_Mediterranea</t>
-  </si>
-  <si>
     <t>Hoy puede ser…</t>
   </si>
   <si>
@@ -3274,9 +3271,6 @@
     <t>I look for a star</t>
   </si>
   <si>
-    <t>Vocation</t>
-  </si>
-  <si>
     <t>Spirit Cross - I</t>
   </si>
   <si>
@@ -4541,6 +4535,12 @@
   </si>
   <si>
     <t>For GVX Summer 2018</t>
+  </si>
+  <si>
+    <t>Para sudadera Prov Mediterránea</t>
+  </si>
+  <si>
+    <t>Vocaction</t>
   </si>
 </sst>
 </file>
@@ -4925,13 +4925,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -4981,7 +4981,7 @@
         <v>282</v>
       </c>
       <c r="E2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F2" t="s">
         <v>47</v>
@@ -5005,7 +5005,7 @@
         <v>178</v>
       </c>
       <c r="M2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N2" t="s">
         <v>14</v>
@@ -5025,13 +5025,13 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="D3" t="s">
         <v>283</v>
       </c>
       <c r="E3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F3" t="s">
         <v>47</v>
@@ -5081,7 +5081,7 @@
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F4" t="s">
         <v>47</v>
@@ -5122,13 +5122,13 @@
         <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="D5" t="s">
         <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F5" t="s">
         <v>78</v>
@@ -5166,19 +5166,19 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B6" t="s">
         <v>370</v>
       </c>
       <c r="C6" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F6" t="s">
         <v>47</v>
@@ -5219,13 +5219,13 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E7" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F7" t="s">
         <v>47</v>
@@ -5263,16 +5263,16 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C8" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D8" t="s">
         <v>284</v>
       </c>
       <c r="E8" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="F8" t="s">
         <v>47</v>
@@ -5316,13 +5316,13 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D9" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="E9" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="F9" t="s">
         <v>47</v>
@@ -5334,7 +5334,7 @@
         <v>31</v>
       </c>
       <c r="I9" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="J9" t="s">
         <v>474</v>
@@ -5372,7 +5372,7 @@
         <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F10" t="s">
         <v>47</v>
@@ -5422,7 +5422,7 @@
         <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -5460,16 +5460,16 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C12" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D12" t="s">
         <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F12" t="s">
         <v>47</v>
@@ -5507,16 +5507,16 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C13" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D13" t="s">
         <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F13" t="s">
         <v>47</v>
@@ -5566,7 +5566,7 @@
         <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F14" t="s">
         <v>47</v>
@@ -5616,7 +5616,7 @@
         <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F15" t="s">
         <v>47</v>
@@ -5666,7 +5666,7 @@
         <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F16" t="s">
         <v>47</v>
@@ -5716,7 +5716,7 @@
         <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F17" t="s">
         <v>47</v>
@@ -5740,7 +5740,7 @@
         <v>186</v>
       </c>
       <c r="M17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N17" t="s">
         <v>14</v>
@@ -5766,7 +5766,7 @@
         <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F18" t="s">
         <v>47</v>
@@ -5816,7 +5816,7 @@
         <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F19" t="s">
         <v>47</v>
@@ -5860,13 +5860,13 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="D20" t="s">
         <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F20" t="s">
         <v>47</v>
@@ -5907,16 +5907,16 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>752</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D21" t="s">
         <v>753</v>
       </c>
-      <c r="C21" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D21" t="s">
-        <v>754</v>
-      </c>
       <c r="E21" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F21" t="s">
         <v>47</v>
@@ -5957,13 +5957,13 @@
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D22" t="s">
         <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F22" t="s">
         <v>47</v>
@@ -6004,16 +6004,16 @@
         <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="C23" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="D23" t="s">
         <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F23" t="s">
         <v>47</v>
@@ -6051,16 +6051,16 @@
         <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C24" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D24" t="s">
         <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F24" t="s">
         <v>47</v>
@@ -6098,16 +6098,16 @@
         <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C25" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D25" t="s">
         <v>55</v>
       </c>
       <c r="E25" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F25" t="s">
         <v>47</v>
@@ -6151,10 +6151,10 @@
         <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E26" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F26" t="s">
         <v>47</v>
@@ -6195,16 +6195,16 @@
         <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C27" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D27" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E27" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F27" t="s">
         <v>47</v>
@@ -6254,7 +6254,7 @@
         <v>369</v>
       </c>
       <c r="E28" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F28" t="s">
         <v>47</v>
@@ -6298,10 +6298,10 @@
         <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E29" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F29" t="s">
         <v>47</v>
@@ -6351,7 +6351,7 @@
         <v>287</v>
       </c>
       <c r="E30" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F30" t="s">
         <v>78</v>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B31" t="s">
         <v>110</v>
@@ -6395,10 +6395,10 @@
         <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E31" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F31" t="s">
         <v>47</v>
@@ -6419,7 +6419,7 @@
         <v>178</v>
       </c>
       <c r="M31" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N31" t="s">
         <v>14</v>
@@ -6433,19 +6433,19 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B32" t="s">
+        <v>674</v>
+      </c>
+      <c r="C32" t="s">
+        <v>674</v>
+      </c>
+      <c r="D32" t="s">
         <v>675</v>
       </c>
-      <c r="C32" t="s">
-        <v>675</v>
-      </c>
-      <c r="D32" t="s">
-        <v>676</v>
-      </c>
       <c r="E32" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F32" t="s">
         <v>47</v>
@@ -6483,7 +6483,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B33" t="s">
         <v>110</v>
@@ -6492,10 +6492,10 @@
         <v>110</v>
       </c>
       <c r="D33" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E33" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F33" t="s">
         <v>47</v>
@@ -6533,7 +6533,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B34" t="s">
         <v>110</v>
@@ -6542,10 +6542,10 @@
         <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="E34" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="F34" t="s">
         <v>47</v>
@@ -6580,19 +6580,19 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="B35" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E35" t="s">
         <v>1305</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1307</v>
       </c>
       <c r="F35" t="s">
         <v>47</v>
@@ -6616,7 +6616,7 @@
         <v>178</v>
       </c>
       <c r="M35" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N35" t="s">
         <v>14</v>
@@ -6630,7 +6630,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B36" t="s">
         <v>110</v>
@@ -6642,7 +6642,7 @@
         <v>89</v>
       </c>
       <c r="E36" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F36" t="s">
         <v>47</v>
@@ -6666,7 +6666,7 @@
         <v>178</v>
       </c>
       <c r="M36" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N36" t="s">
         <v>14</v>
@@ -6680,13 +6680,13 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B37" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="C37" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="F37" t="s">
         <v>47</v>
@@ -6698,7 +6698,7 @@
         <v>31</v>
       </c>
       <c r="I37" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="J37" t="s">
         <v>476</v>
@@ -6730,13 +6730,13 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="D38" t="s">
         <v>72</v>
       </c>
       <c r="E38" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F38" t="s">
         <v>78</v>
@@ -6774,19 +6774,19 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B39" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C39" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D39" t="s">
         <v>72</v>
       </c>
       <c r="E39" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F39" t="s">
         <v>78</v>
@@ -6830,13 +6830,13 @@
         <v>443</v>
       </c>
       <c r="C40" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="D40" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E40" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F40" t="s">
         <v>47</v>
@@ -6860,7 +6860,7 @@
         <v>178</v>
       </c>
       <c r="M40" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N40" t="s">
         <v>14</v>
@@ -6883,10 +6883,10 @@
         <v>317</v>
       </c>
       <c r="D41" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E41" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F41" t="s">
         <v>78</v>
@@ -6927,13 +6927,13 @@
         <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="D42" t="s">
         <v>65</v>
       </c>
       <c r="E42" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F42" t="s">
         <v>78</v>
@@ -6971,13 +6971,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="B43" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C43" t="s">
         <v>1266</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1268</v>
       </c>
       <c r="F43" t="s">
         <v>78</v>
@@ -7118,13 +7118,13 @@
         <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="D46" t="s">
         <v>69</v>
       </c>
       <c r="E46" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F46" t="s">
         <v>78</v>
@@ -7174,7 +7174,7 @@
         <v>425</v>
       </c>
       <c r="E47" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F47" t="s">
         <v>47</v>
@@ -7198,7 +7198,7 @@
         <v>178</v>
       </c>
       <c r="M47" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N47" t="s">
         <v>14</v>
@@ -7215,16 +7215,16 @@
         <v>111</v>
       </c>
       <c r="B48" t="s">
+        <v>758</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D48" t="s">
         <v>759</v>
       </c>
-      <c r="C48" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D48" t="s">
-        <v>760</v>
-      </c>
       <c r="E48" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F48" t="s">
         <v>47</v>
@@ -7259,13 +7259,13 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B49" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C49" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F49" t="s">
         <v>47</v>
@@ -7280,7 +7280,7 @@
         <v>142</v>
       </c>
       <c r="J49" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="L49" t="s">
         <v>385</v>
@@ -7303,16 +7303,16 @@
         <v>112</v>
       </c>
       <c r="B50" t="s">
+        <v>760</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D50" t="s">
         <v>761</v>
       </c>
-      <c r="C50" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D50" t="s">
-        <v>762</v>
-      </c>
       <c r="E50" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F50" t="s">
         <v>47</v>
@@ -7347,19 +7347,19 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B51" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C51" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D51" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E51" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F51" t="s">
         <v>47</v>
@@ -7400,10 +7400,10 @@
         <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C52" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F52" t="s">
         <v>47</v>
@@ -7441,16 +7441,16 @@
         <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C53" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="D53" t="s">
         <v>121</v>
       </c>
       <c r="E53" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F53" t="s">
         <v>47</v>
@@ -7488,10 +7488,10 @@
         <v>114</v>
       </c>
       <c r="B54" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C54" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F54" t="s">
         <v>47</v>
@@ -7529,19 +7529,19 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B55" t="s">
+        <v>574</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D55" t="s">
         <v>575</v>
       </c>
-      <c r="C55" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D55" t="s">
-        <v>576</v>
-      </c>
       <c r="E55" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F55" t="s">
         <v>47</v>
@@ -7579,16 +7579,16 @@
         <v>115</v>
       </c>
       <c r="B56" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C56" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D56" t="s">
         <v>119</v>
       </c>
       <c r="E56" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F56" t="s">
         <v>47</v>
@@ -7629,16 +7629,16 @@
         <v>116</v>
       </c>
       <c r="B57" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C57" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="D57" t="s">
         <v>120</v>
       </c>
       <c r="E57" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F57" t="s">
         <v>47</v>
@@ -7679,13 +7679,13 @@
         <v>135</v>
       </c>
       <c r="C58" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D58" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E58" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F58" t="s">
         <v>47</v>
@@ -7723,16 +7723,16 @@
         <v>134</v>
       </c>
       <c r="B59" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C59" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D59" t="s">
         <v>136</v>
       </c>
       <c r="E59" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F59" t="s">
         <v>47</v>
@@ -7770,16 +7770,16 @@
         <v>393</v>
       </c>
       <c r="B60" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C60" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D60" t="s">
         <v>398</v>
       </c>
       <c r="E60" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F60" t="s">
         <v>47</v>
@@ -7803,7 +7803,7 @@
         <v>178</v>
       </c>
       <c r="M60" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N60" t="s">
         <v>14</v>
@@ -7817,19 +7817,19 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B61" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="C61" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="D61" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="E61" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="F61" t="s">
         <v>47</v>
@@ -7867,19 +7867,19 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B62" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C62" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D62" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E62" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F62" t="s">
         <v>47</v>
@@ -7917,13 +7917,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B63" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="C63" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F63" t="s">
         <v>47</v>
@@ -7947,7 +7947,7 @@
         <v>178</v>
       </c>
       <c r="M63" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N63" t="s">
         <v>14</v>
@@ -7967,13 +7967,13 @@
         <v>125</v>
       </c>
       <c r="C64" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="D64" t="s">
         <v>126</v>
       </c>
       <c r="E64" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F64" t="s">
         <v>78</v>
@@ -8017,13 +8017,13 @@
         <v>128</v>
       </c>
       <c r="C65" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D65" t="s">
         <v>127</v>
       </c>
       <c r="E65" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F65" t="s">
         <v>78</v>
@@ -8067,13 +8067,13 @@
         <v>399</v>
       </c>
       <c r="C66" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="D66" t="s">
         <v>400</v>
       </c>
       <c r="E66" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F66" t="s">
         <v>47</v>
@@ -8097,7 +8097,7 @@
         <v>178</v>
       </c>
       <c r="M66" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N66" t="s">
         <v>14</v>
@@ -8117,13 +8117,13 @@
         <v>449</v>
       </c>
       <c r="C67" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="D67" t="s">
         <v>450</v>
       </c>
       <c r="E67" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F67" t="s">
         <v>47</v>
@@ -8161,13 +8161,13 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B68" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C68" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F68" t="s">
         <v>78</v>
@@ -8205,13 +8205,13 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B69" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C69" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="F69" t="s">
         <v>47</v>
@@ -8249,13 +8249,13 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B70" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C70" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="F70" t="s">
         <v>47</v>
@@ -8293,13 +8293,13 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B71" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C71" t="s">
         <v>1338</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1340</v>
       </c>
       <c r="F71" t="s">
         <v>47</v>
@@ -8340,16 +8340,16 @@
         <v>137</v>
       </c>
       <c r="B72" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C72" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D72" t="s">
         <v>138</v>
       </c>
       <c r="E72" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F72" t="s">
         <v>47</v>
@@ -8390,16 +8390,16 @@
         <v>208</v>
       </c>
       <c r="B73" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C73" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D73" t="s">
         <v>138</v>
       </c>
       <c r="E73" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F73" t="s">
         <v>47</v>
@@ -8440,16 +8440,16 @@
         <v>209</v>
       </c>
       <c r="B74" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C74" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="D74" t="s">
         <v>409</v>
       </c>
       <c r="E74" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F74" t="s">
         <v>47</v>
@@ -8473,7 +8473,7 @@
         <v>178</v>
       </c>
       <c r="M74" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N74" t="s">
         <v>14</v>
@@ -8490,16 +8490,16 @@
         <v>210</v>
       </c>
       <c r="B75" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C75" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D75" t="s">
         <v>212</v>
       </c>
       <c r="E75" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F75" t="s">
         <v>47</v>
@@ -8543,13 +8543,13 @@
         <v>213</v>
       </c>
       <c r="C76" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D76" t="s">
         <v>214</v>
       </c>
       <c r="E76" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F76" t="s">
         <v>47</v>
@@ -8587,13 +8587,13 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B77" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C77" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="F77" t="s">
         <v>47</v>
@@ -8605,7 +8605,7 @@
         <v>31</v>
       </c>
       <c r="I77" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="J77" t="s">
         <v>483</v>
@@ -8617,7 +8617,7 @@
         <v>178</v>
       </c>
       <c r="M77" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N77" t="s">
         <v>14</v>
@@ -8634,16 +8634,16 @@
         <v>359</v>
       </c>
       <c r="B78" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C78" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="D78" t="s">
         <v>380</v>
       </c>
       <c r="E78" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F78" t="s">
         <v>47</v>
@@ -8681,13 +8681,13 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B79" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C79" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="F79" t="s">
         <v>47</v>
@@ -8725,19 +8725,19 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B80" t="s">
+        <v>586</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D80" t="s">
         <v>587</v>
       </c>
-      <c r="C80" t="s">
-        <v>1192</v>
-      </c>
-      <c r="D80" t="s">
-        <v>588</v>
-      </c>
       <c r="E80" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F80" t="s">
         <v>47</v>
@@ -8761,7 +8761,7 @@
         <v>179</v>
       </c>
       <c r="M80" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N80" t="s">
         <v>14</v>
@@ -8775,13 +8775,13 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="B81" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="C81" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="F81" t="s">
         <v>47</v>
@@ -8793,7 +8793,7 @@
         <v>31</v>
       </c>
       <c r="I81" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="J81" t="s">
         <v>483</v>
@@ -8805,7 +8805,7 @@
         <v>178</v>
       </c>
       <c r="M81" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N81" t="s">
         <v>14</v>
@@ -8819,19 +8819,19 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B82" t="s">
+        <v>729</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D82" t="s">
         <v>730</v>
       </c>
-      <c r="C82" t="s">
-        <v>1222</v>
-      </c>
-      <c r="D82" t="s">
-        <v>731</v>
-      </c>
       <c r="E82" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F82" t="s">
         <v>47</v>
@@ -8866,19 +8866,19 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B83" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="C83" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E83" t="s">
         <v>1496</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1497</v>
-      </c>
-      <c r="E83" t="s">
-        <v>1498</v>
       </c>
       <c r="F83" t="s">
         <v>47</v>
@@ -8913,13 +8913,13 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B84" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C84" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="F84" t="s">
         <v>47</v>
@@ -8931,7 +8931,7 @@
         <v>31</v>
       </c>
       <c r="I84" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="J84" t="s">
         <v>483</v>
@@ -8963,13 +8963,13 @@
         <v>183</v>
       </c>
       <c r="C85" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D85" t="s">
         <v>184</v>
       </c>
       <c r="E85" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F85" t="s">
         <v>47</v>
@@ -9007,13 +9007,13 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B86" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C86" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="F86" t="s">
         <v>47</v>
@@ -9034,7 +9034,7 @@
         <v>95</v>
       </c>
       <c r="M86" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N86" t="s">
         <v>14</v>
@@ -9054,13 +9054,13 @@
         <v>378</v>
       </c>
       <c r="C87" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="D87" t="s">
         <v>379</v>
       </c>
       <c r="E87" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F87" t="s">
         <v>47</v>
@@ -9095,19 +9095,19 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B88" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C88" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D88" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E88" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F88" t="s">
         <v>47</v>
@@ -9119,7 +9119,7 @@
         <v>31</v>
       </c>
       <c r="I88" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J88" t="s">
         <v>109</v>
@@ -9142,19 +9142,19 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B89" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C89" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D89" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E89" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F89" t="s">
         <v>47</v>
@@ -9166,7 +9166,7 @@
         <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J89" t="s">
         <v>109</v>
@@ -9189,19 +9189,19 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B90" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C90" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D90" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E90" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F90" t="s">
         <v>47</v>
@@ -9213,7 +9213,7 @@
         <v>31</v>
       </c>
       <c r="I90" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J90" t="s">
         <v>323</v>
@@ -9236,19 +9236,19 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B91" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C91" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D91" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E91" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F91" t="s">
         <v>47</v>
@@ -9260,7 +9260,7 @@
         <v>31</v>
       </c>
       <c r="I91" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J91" t="s">
         <v>109</v>
@@ -9283,19 +9283,19 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B92" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C92" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D92" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E92" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F92" t="s">
         <v>47</v>
@@ -9307,7 +9307,7 @@
         <v>31</v>
       </c>
       <c r="I92" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J92" t="s">
         <v>109</v>
@@ -9342,7 +9342,7 @@
         <v>321</v>
       </c>
       <c r="E93" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F93" t="s">
         <v>78</v>
@@ -9366,7 +9366,7 @@
         <v>186</v>
       </c>
       <c r="M93" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N93" t="s">
         <v>14</v>
@@ -9380,13 +9380,13 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B94" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="C94" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="F94" t="s">
         <v>47</v>
@@ -9433,10 +9433,10 @@
         <v>558</v>
       </c>
       <c r="D95" t="s">
-        <v>559</v>
+        <v>1505</v>
       </c>
       <c r="E95" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F95" t="s">
         <v>78</v>
@@ -9460,7 +9460,7 @@
         <v>186</v>
       </c>
       <c r="M95" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N95" t="s">
         <v>14</v>
@@ -9480,13 +9480,13 @@
         <v>472</v>
       </c>
       <c r="C96" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="D96" t="s">
         <v>473</v>
       </c>
       <c r="E96" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F96" t="s">
         <v>78</v>
@@ -9527,13 +9527,13 @@
         <v>258</v>
       </c>
       <c r="C97" t="s">
-        <v>1084</v>
+        <v>1506</v>
       </c>
       <c r="D97" t="s">
         <v>259</v>
       </c>
       <c r="E97" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F97" t="s">
         <v>47</v>
@@ -9580,10 +9580,10 @@
         <v>175</v>
       </c>
       <c r="D98" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E98" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F98" t="s">
         <v>78</v>
@@ -9607,7 +9607,7 @@
         <v>177</v>
       </c>
       <c r="M98" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N98" t="s">
         <v>14</v>
@@ -9627,13 +9627,13 @@
         <v>180</v>
       </c>
       <c r="C99" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D99" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E99" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F99" t="s">
         <v>78</v>
@@ -9677,13 +9677,13 @@
         <v>182</v>
       </c>
       <c r="C100" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="D100" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E100" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F100" t="s">
         <v>78</v>
@@ -9733,7 +9733,7 @@
         <v>376</v>
       </c>
       <c r="E101" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F101" t="s">
         <v>47</v>
@@ -9777,7 +9777,7 @@
         <v>349</v>
       </c>
       <c r="C102" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="F102" t="s">
         <v>78</v>
@@ -9815,16 +9815,16 @@
         <v>405</v>
       </c>
       <c r="B103" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C103" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D103" t="s">
         <v>411</v>
       </c>
       <c r="E103" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F103" t="s">
         <v>78</v>
@@ -9874,7 +9874,7 @@
         <v>465</v>
       </c>
       <c r="E104" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F104" t="s">
         <v>78</v>
@@ -9924,7 +9924,7 @@
         <v>465</v>
       </c>
       <c r="E105" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F105" t="s">
         <v>78</v>
@@ -9962,13 +9962,13 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B106" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C106" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="F106" t="s">
         <v>47</v>
@@ -9989,7 +9989,7 @@
         <v>75</v>
       </c>
       <c r="L106" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="M106" t="s">
         <v>48</v>
@@ -10009,16 +10009,16 @@
         <v>507</v>
       </c>
       <c r="B107" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C107" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="D107" t="s">
         <v>513</v>
       </c>
       <c r="E107" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F107" t="s">
         <v>78</v>
@@ -10068,7 +10068,7 @@
         <v>427</v>
       </c>
       <c r="E108" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F108" t="s">
         <v>47</v>
@@ -10112,13 +10112,13 @@
         <v>375</v>
       </c>
       <c r="C109" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="D109" t="s">
         <v>376</v>
       </c>
       <c r="E109" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F109" t="s">
         <v>47</v>
@@ -10153,19 +10153,19 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B110" t="s">
+        <v>707</v>
+      </c>
+      <c r="C110" t="s">
+        <v>707</v>
+      </c>
+      <c r="D110" t="s">
         <v>708</v>
       </c>
-      <c r="C110" t="s">
-        <v>708</v>
-      </c>
-      <c r="D110" t="s">
-        <v>709</v>
-      </c>
       <c r="E110" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F110" t="s">
         <v>47</v>
@@ -10206,13 +10206,13 @@
         <v>388</v>
       </c>
       <c r="C111" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="D111" t="s">
         <v>389</v>
       </c>
       <c r="E111" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F111" t="s">
         <v>47</v>
@@ -10253,13 +10253,13 @@
         <v>401</v>
       </c>
       <c r="C112" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="D112" t="s">
         <v>402</v>
       </c>
       <c r="E112" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F112" t="s">
         <v>47</v>
@@ -10300,16 +10300,16 @@
         <v>396</v>
       </c>
       <c r="B113" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C113" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D113" t="s">
         <v>403</v>
       </c>
       <c r="E113" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F113" t="s">
         <v>47</v>
@@ -10353,13 +10353,13 @@
         <v>446</v>
       </c>
       <c r="C114" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="D114" t="s">
         <v>444</v>
       </c>
       <c r="E114" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F114" t="s">
         <v>47</v>
@@ -10383,7 +10383,7 @@
         <v>195</v>
       </c>
       <c r="M114" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N114" t="s">
         <v>14</v>
@@ -10403,13 +10403,13 @@
         <v>419</v>
       </c>
       <c r="C115" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D115" t="s">
         <v>420</v>
       </c>
       <c r="E115" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F115" t="s">
         <v>47</v>
@@ -10450,10 +10450,10 @@
         <v>364</v>
       </c>
       <c r="B116" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C116" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="F116" t="s">
         <v>47</v>
@@ -10497,13 +10497,13 @@
         <v>421</v>
       </c>
       <c r="C117" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D117" t="s">
         <v>423</v>
       </c>
       <c r="E117" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F117" t="s">
         <v>47</v>
@@ -10544,16 +10544,16 @@
         <v>495</v>
       </c>
       <c r="B118" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C118" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D118" t="s">
         <v>502</v>
       </c>
       <c r="E118" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F118" t="s">
         <v>47</v>
@@ -10594,16 +10594,16 @@
         <v>290</v>
       </c>
       <c r="B119" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C119" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="D119" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E119" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F119" t="s">
         <v>78</v>
@@ -10644,7 +10644,7 @@
         <v>275</v>
       </c>
       <c r="C120" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="F120" t="s">
         <v>47</v>
@@ -10682,16 +10682,16 @@
         <v>248</v>
       </c>
       <c r="B121" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C121" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D121" t="s">
         <v>261</v>
       </c>
       <c r="E121" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F121" t="s">
         <v>47</v>
@@ -10715,7 +10715,7 @@
         <v>95</v>
       </c>
       <c r="M121" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N121" t="s">
         <v>14</v>
@@ -10732,16 +10732,16 @@
         <v>249</v>
       </c>
       <c r="B122" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C122" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="D122" t="s">
         <v>262</v>
       </c>
       <c r="E122" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F122" t="s">
         <v>47</v>
@@ -10765,7 +10765,7 @@
         <v>95</v>
       </c>
       <c r="M122" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N122" t="s">
         <v>14</v>
@@ -10779,19 +10779,19 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B123" t="s">
+        <v>833</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D123" t="s">
         <v>834</v>
       </c>
-      <c r="C123" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D123" t="s">
-        <v>835</v>
-      </c>
       <c r="E123" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F123" t="s">
         <v>47</v>
@@ -10815,7 +10815,7 @@
         <v>178</v>
       </c>
       <c r="M123" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N123" t="s">
         <v>14</v>
@@ -10832,16 +10832,16 @@
         <v>253</v>
       </c>
       <c r="B124" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C124" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D124" t="s">
         <v>265</v>
       </c>
       <c r="E124" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F124" t="s">
         <v>47</v>
@@ -10885,13 +10885,13 @@
         <v>498</v>
       </c>
       <c r="C125" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="D125" t="s">
         <v>499</v>
       </c>
       <c r="E125" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F125" t="s">
         <v>47</v>
@@ -10932,16 +10932,16 @@
         <v>494</v>
       </c>
       <c r="B126" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C126" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="D126" t="s">
         <v>501</v>
       </c>
       <c r="E126" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F126" t="s">
         <v>47</v>
@@ -10979,16 +10979,16 @@
         <v>496</v>
       </c>
       <c r="B127" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C127" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="D127" t="s">
         <v>549</v>
       </c>
       <c r="E127" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F127" t="s">
         <v>47</v>
@@ -11012,7 +11012,7 @@
         <v>278</v>
       </c>
       <c r="M127" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N127" t="s">
         <v>14</v>
@@ -11029,16 +11029,16 @@
         <v>541</v>
       </c>
       <c r="B128" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C128" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="D128" t="s">
         <v>543</v>
       </c>
       <c r="E128" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F128" t="s">
         <v>47</v>
@@ -11076,19 +11076,19 @@
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B129" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C129" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="D129" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E129" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F129" t="s">
         <v>47</v>
@@ -11123,13 +11123,13 @@
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B130" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C130" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="F130" t="s">
         <v>47</v>
@@ -11197,7 +11197,7 @@
         <v>385</v>
       </c>
       <c r="M131" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N131" t="s">
         <v>14</v>
@@ -11220,10 +11220,10 @@
         <v>235</v>
       </c>
       <c r="D132" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E132" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="F132" t="s">
         <v>78</v>
@@ -11261,19 +11261,19 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B133" t="s">
+        <v>678</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D133" t="s">
         <v>679</v>
       </c>
-      <c r="C133" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D133" t="s">
-        <v>680</v>
-      </c>
       <c r="E133" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F133" t="s">
         <v>47</v>
@@ -11311,13 +11311,13 @@
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B134" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C134" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="F134" t="s">
         <v>47</v>
@@ -11352,13 +11352,13 @@
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B135" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C135" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="F135" t="s">
         <v>47</v>
@@ -11399,13 +11399,13 @@
         <v>373</v>
       </c>
       <c r="C136" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="D136" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E136" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F136" t="s">
         <v>47</v>
@@ -11423,7 +11423,7 @@
         <v>263</v>
       </c>
       <c r="L136" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="M136" t="s">
         <v>48</v>
@@ -11446,13 +11446,13 @@
         <v>470</v>
       </c>
       <c r="C137" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="D137" t="s">
         <v>471</v>
       </c>
       <c r="E137" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F137" t="s">
         <v>78</v>
@@ -11487,13 +11487,13 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="B138" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="C138" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="F138" t="s">
         <v>47</v>
@@ -11537,13 +11537,13 @@
         <v>515</v>
       </c>
       <c r="C139" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="D139" t="s">
         <v>516</v>
       </c>
       <c r="E139" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F139" t="s">
         <v>78</v>
@@ -11584,13 +11584,13 @@
         <v>241</v>
       </c>
       <c r="C140" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="D140" t="s">
         <v>240</v>
       </c>
       <c r="E140" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="F140" t="s">
         <v>78</v>
@@ -11625,13 +11625,13 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="B141" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="C141" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="F141" t="s">
         <v>47</v>
@@ -11675,13 +11675,13 @@
         <v>338</v>
       </c>
       <c r="C142" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="D142" t="s">
         <v>339</v>
       </c>
       <c r="E142" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F142" t="s">
         <v>78</v>
@@ -11719,19 +11719,19 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B143" t="s">
+        <v>709</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D143" t="s">
         <v>710</v>
       </c>
-      <c r="C143" t="s">
-        <v>1158</v>
-      </c>
-      <c r="D143" t="s">
-        <v>711</v>
-      </c>
       <c r="E143" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F143" t="s">
         <v>78</v>
@@ -11775,13 +11775,13 @@
         <v>158</v>
       </c>
       <c r="C144" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D144" t="s">
         <v>159</v>
       </c>
       <c r="E144" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F144" t="s">
         <v>78</v>
@@ -11816,19 +11816,19 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="B145" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D145" t="s">
         <v>1433</v>
       </c>
-      <c r="C145" t="s">
+      <c r="E145" t="s">
         <v>1434</v>
-      </c>
-      <c r="D145" t="s">
-        <v>1435</v>
-      </c>
-      <c r="E145" t="s">
-        <v>1436</v>
       </c>
       <c r="F145" t="s">
         <v>47</v>
@@ -11852,7 +11852,7 @@
         <v>178</v>
       </c>
       <c r="M145" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N145" t="s">
         <v>14</v>
@@ -11872,13 +11872,13 @@
         <v>160</v>
       </c>
       <c r="C146" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="D146" t="s">
         <v>161</v>
       </c>
       <c r="E146" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F146" t="s">
         <v>78</v>
@@ -11902,7 +11902,7 @@
         <v>186</v>
       </c>
       <c r="M146" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N146" t="s">
         <v>14</v>
@@ -11916,19 +11916,19 @@
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B147" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C147" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="D147" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E147" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="F147" t="s">
         <v>47</v>
@@ -11952,7 +11952,7 @@
         <v>178</v>
       </c>
       <c r="M147" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N147" t="s">
         <v>14</v>
@@ -11972,13 +11972,13 @@
         <v>162</v>
       </c>
       <c r="C148" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="D148" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="E148" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="F148" t="s">
         <v>78</v>
@@ -12013,19 +12013,19 @@
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B149" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="C149" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="D149" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="E149" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="F149" t="s">
         <v>47</v>
@@ -12066,13 +12066,13 @@
         <v>163</v>
       </c>
       <c r="C150" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D150" t="s">
         <v>164</v>
       </c>
       <c r="E150" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F150" t="s">
         <v>78</v>
@@ -12096,7 +12096,7 @@
         <v>186</v>
       </c>
       <c r="M150" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N150" t="s">
         <v>14</v>
@@ -12116,13 +12116,13 @@
         <v>165</v>
       </c>
       <c r="C151" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="D151" t="s">
         <v>238</v>
       </c>
       <c r="E151" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F151" t="s">
         <v>78</v>
@@ -12146,7 +12146,7 @@
         <v>186</v>
       </c>
       <c r="M151" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N151" t="s">
         <v>14</v>
@@ -12166,13 +12166,13 @@
         <v>511</v>
       </c>
       <c r="C152" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="D152" t="s">
         <v>512</v>
       </c>
       <c r="E152" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F152" t="s">
         <v>78</v>
@@ -12193,7 +12193,7 @@
         <v>186</v>
       </c>
       <c r="M152" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N152" t="s">
         <v>14</v>
@@ -12207,22 +12207,22 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>1332</v>
+        <v>334</v>
       </c>
       <c r="B153" t="s">
-        <v>1360</v>
+        <v>343</v>
       </c>
       <c r="C153" t="s">
-        <v>1361</v>
+        <v>1134</v>
       </c>
       <c r="D153" t="s">
         <v>344</v>
       </c>
       <c r="E153" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F153" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G153" t="s">
         <v>51</v>
@@ -12231,16 +12231,19 @@
         <v>31</v>
       </c>
       <c r="I153" t="s">
-        <v>142</v>
+        <v>345</v>
       </c>
       <c r="J153" t="s">
         <v>331</v>
       </c>
+      <c r="K153" t="s">
+        <v>75</v>
+      </c>
       <c r="L153" t="s">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="M153" t="s">
-        <v>48</v>
+        <v>830</v>
       </c>
       <c r="N153" t="s">
         <v>14</v>
@@ -12254,22 +12257,22 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>334</v>
+        <v>1330</v>
       </c>
       <c r="B154" t="s">
-        <v>343</v>
+        <v>1358</v>
       </c>
       <c r="C154" t="s">
-        <v>1136</v>
+        <v>1359</v>
       </c>
       <c r="D154" t="s">
         <v>344</v>
       </c>
       <c r="E154" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F154" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G154" t="s">
         <v>51</v>
@@ -12278,19 +12281,16 @@
         <v>31</v>
       </c>
       <c r="I154" t="s">
-        <v>345</v>
+        <v>142</v>
       </c>
       <c r="J154" t="s">
         <v>331</v>
       </c>
-      <c r="K154" t="s">
-        <v>75</v>
-      </c>
       <c r="L154" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="M154" t="s">
-        <v>831</v>
+        <v>48</v>
       </c>
       <c r="N154" t="s">
         <v>14</v>
@@ -12310,13 +12310,13 @@
         <v>167</v>
       </c>
       <c r="C155" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="D155" t="s">
         <v>168</v>
       </c>
       <c r="E155" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F155" t="s">
         <v>78</v>
@@ -12357,13 +12357,13 @@
         <v>346</v>
       </c>
       <c r="C156" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="D156" t="s">
         <v>540</v>
       </c>
       <c r="E156" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="F156" t="s">
         <v>78</v>
@@ -12398,19 +12398,19 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="B157" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="C157" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="D157" t="s">
         <v>540</v>
       </c>
       <c r="E157" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="F157" t="s">
         <v>78</v>
@@ -12454,13 +12454,13 @@
         <v>517</v>
       </c>
       <c r="C158" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="D158" t="s">
         <v>166</v>
       </c>
       <c r="E158" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F158" t="s">
         <v>78</v>
@@ -12495,43 +12495,40 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>1484</v>
+        <v>623</v>
       </c>
       <c r="B159" t="s">
-        <v>1501</v>
+        <v>643</v>
       </c>
       <c r="C159" t="s">
-        <v>1502</v>
+        <v>1227</v>
       </c>
       <c r="D159" t="s">
-        <v>1503</v>
+        <v>808</v>
       </c>
       <c r="E159" t="s">
-        <v>1504</v>
+        <v>994</v>
       </c>
       <c r="F159" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G159" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H159" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I159" t="s">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="J159" t="s">
         <v>276</v>
       </c>
-      <c r="K159" t="s">
-        <v>54</v>
-      </c>
       <c r="L159" t="s">
-        <v>278</v>
+        <v>186</v>
       </c>
       <c r="M159" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N159" t="s">
         <v>14</v>
@@ -12545,40 +12542,43 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>624</v>
+        <v>1482</v>
       </c>
       <c r="B160" t="s">
-        <v>644</v>
+        <v>1499</v>
       </c>
       <c r="C160" t="s">
-        <v>1229</v>
+        <v>1500</v>
       </c>
       <c r="D160" t="s">
-        <v>809</v>
+        <v>1501</v>
       </c>
       <c r="E160" t="s">
-        <v>995</v>
+        <v>1502</v>
       </c>
       <c r="F160" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G160" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H160" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I160" t="s">
-        <v>445</v>
+        <v>140</v>
       </c>
       <c r="J160" t="s">
         <v>276</v>
       </c>
+      <c r="K160" t="s">
+        <v>54</v>
+      </c>
       <c r="L160" t="s">
-        <v>186</v>
+        <v>278</v>
       </c>
       <c r="M160" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N160" t="s">
         <v>14</v>
@@ -12598,13 +12598,13 @@
         <v>509</v>
       </c>
       <c r="C161" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="D161" t="s">
         <v>510</v>
       </c>
       <c r="E161" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="F161" t="s">
         <v>78</v>
@@ -12628,7 +12628,7 @@
         <v>186</v>
       </c>
       <c r="M161" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N161" t="s">
         <v>14</v>
@@ -12648,13 +12648,13 @@
         <v>224</v>
       </c>
       <c r="C162" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="D162" t="s">
         <v>225</v>
       </c>
       <c r="E162" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F162" t="s">
         <v>78</v>
@@ -12675,7 +12675,7 @@
         <v>186</v>
       </c>
       <c r="M162" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N162" t="s">
         <v>14</v>
@@ -12695,13 +12695,13 @@
         <v>226</v>
       </c>
       <c r="C163" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="D163" t="s">
         <v>233</v>
       </c>
       <c r="E163" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F163" t="s">
         <v>78</v>
@@ -12745,13 +12745,13 @@
         <v>227</v>
       </c>
       <c r="C164" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="D164" t="s">
         <v>548</v>
       </c>
       <c r="E164" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F164" t="s">
         <v>78</v>
@@ -12775,7 +12775,7 @@
         <v>186</v>
       </c>
       <c r="M164" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N164" t="s">
         <v>14</v>
@@ -12789,19 +12789,19 @@
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B165" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="C165" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="D165" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="E165" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="F165" t="s">
         <v>47</v>
@@ -12825,7 +12825,7 @@
         <v>178</v>
       </c>
       <c r="M165" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N165" t="s">
         <v>14</v>
@@ -12845,13 +12845,13 @@
         <v>232</v>
       </c>
       <c r="C166" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D166" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E166" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F166" t="s">
         <v>78</v>
@@ -12872,7 +12872,7 @@
         <v>186</v>
       </c>
       <c r="M166" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N166" t="s">
         <v>14</v>
@@ -12886,19 +12886,19 @@
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B167" t="s">
         <v>232</v>
       </c>
       <c r="C167" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D167" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E167" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F167" t="s">
         <v>78</v>
@@ -12936,16 +12936,16 @@
         <v>356</v>
       </c>
       <c r="B168" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C168" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="D168" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E168" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F168" t="s">
         <v>47</v>
@@ -12989,13 +12989,13 @@
         <v>229</v>
       </c>
       <c r="C169" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D169" t="s">
         <v>547</v>
       </c>
       <c r="E169" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F169" t="s">
         <v>78</v>
@@ -13019,7 +13019,7 @@
         <v>186</v>
       </c>
       <c r="M169" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N169" t="s">
         <v>14</v>
@@ -13033,19 +13033,19 @@
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="B170" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C170" t="s">
         <v>1442</v>
       </c>
-      <c r="C170" t="s">
-        <v>1444</v>
-      </c>
       <c r="D170" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="E170" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="F170" t="s">
         <v>47</v>
@@ -13089,13 +13089,13 @@
         <v>170</v>
       </c>
       <c r="C171" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="D171" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E171" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F171" t="s">
         <v>78</v>
@@ -13119,7 +13119,7 @@
         <v>186</v>
       </c>
       <c r="M171" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N171" t="s">
         <v>14</v>
@@ -13139,13 +13139,13 @@
         <v>537</v>
       </c>
       <c r="C172" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D172" t="s">
         <v>534</v>
       </c>
       <c r="E172" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F172" t="s">
         <v>78</v>
@@ -13189,13 +13189,13 @@
         <v>532</v>
       </c>
       <c r="C173" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="D173" t="s">
         <v>533</v>
       </c>
       <c r="E173" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F173" t="s">
         <v>78</v>
@@ -13219,7 +13219,7 @@
         <v>186</v>
       </c>
       <c r="M173" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N173" t="s">
         <v>14</v>
@@ -13239,13 +13239,13 @@
         <v>341</v>
       </c>
       <c r="C174" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="D174" t="s">
         <v>342</v>
       </c>
       <c r="E174" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F174" t="s">
         <v>78</v>
@@ -13257,7 +13257,7 @@
         <v>13</v>
       </c>
       <c r="I174" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="J174" t="s">
         <v>263</v>
@@ -13266,7 +13266,7 @@
         <v>186</v>
       </c>
       <c r="M174" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N174" t="s">
         <v>14</v>
@@ -13286,7 +13286,7 @@
         <v>536</v>
       </c>
       <c r="C175" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="D175" t="s">
         <v>538</v>
@@ -13304,7 +13304,7 @@
         <v>13</v>
       </c>
       <c r="I175" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="J175" t="s">
         <v>331</v>
@@ -13313,7 +13313,7 @@
         <v>186</v>
       </c>
       <c r="M175" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N175" t="s">
         <v>14</v>
@@ -13327,19 +13327,19 @@
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B176" t="s">
         <v>827</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D176" t="s">
         <v>828</v>
       </c>
-      <c r="C176" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D176" t="s">
-        <v>829</v>
-      </c>
       <c r="E176" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="F176" t="s">
         <v>78</v>
@@ -13380,13 +13380,13 @@
         <v>539</v>
       </c>
       <c r="C177" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="D177" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E177" t="s">
         <v>1031</v>
-      </c>
-      <c r="E177" t="s">
-        <v>1032</v>
       </c>
       <c r="F177" t="s">
         <v>78</v>
@@ -13410,7 +13410,7 @@
         <v>186</v>
       </c>
       <c r="M177" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N177" t="s">
         <v>14</v>
@@ -13424,19 +13424,19 @@
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B178" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="C178" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="D178" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="E178" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="F178" t="s">
         <v>47</v>
@@ -13460,7 +13460,7 @@
         <v>178</v>
       </c>
       <c r="M178" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N178" t="s">
         <v>14</v>
@@ -13480,13 +13480,13 @@
         <v>230</v>
       </c>
       <c r="C179" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="D179" t="s">
         <v>231</v>
       </c>
       <c r="E179" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F179" t="s">
         <v>78</v>
@@ -13507,7 +13507,7 @@
         <v>179</v>
       </c>
       <c r="M179" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N179" t="s">
         <v>14</v>
@@ -13521,13 +13521,13 @@
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B180" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="C180" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="F180" t="s">
         <v>47</v>
@@ -13551,7 +13551,7 @@
         <v>178</v>
       </c>
       <c r="M180" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N180" t="s">
         <v>14</v>
@@ -13571,13 +13571,13 @@
         <v>169</v>
       </c>
       <c r="C181" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="D181" t="s">
         <v>237</v>
       </c>
       <c r="E181" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F181" t="s">
         <v>78</v>
@@ -13598,7 +13598,7 @@
         <v>186</v>
       </c>
       <c r="M181" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N181" t="s">
         <v>14</v>
@@ -13612,13 +13612,13 @@
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B182" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="C182" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="F182" t="s">
         <v>47</v>
@@ -13656,19 +13656,19 @@
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="B183" t="s">
         <v>169</v>
       </c>
       <c r="C183" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="D183" t="s">
         <v>237</v>
       </c>
       <c r="E183" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F183" t="s">
         <v>47</v>
@@ -13680,7 +13680,7 @@
         <v>13</v>
       </c>
       <c r="I183" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="J183" t="s">
         <v>331</v>
@@ -13706,19 +13706,19 @@
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B184" t="s">
         <v>1390</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>1392</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
         <v>1394</v>
       </c>
-      <c r="D184" t="s">
-        <v>1396</v>
-      </c>
       <c r="E184" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F184" t="s">
         <v>78</v>
@@ -13742,7 +13742,7 @@
         <v>186</v>
       </c>
       <c r="M184" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N184" t="s">
         <v>14</v>
@@ -13756,19 +13756,19 @@
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B185" t="s">
         <v>1391</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>1393</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D185" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E185" t="s">
         <v>1395</v>
-      </c>
-      <c r="D185" t="s">
-        <v>1396</v>
-      </c>
-      <c r="E185" t="s">
-        <v>1397</v>
       </c>
       <c r="F185" t="s">
         <v>78</v>
@@ -13792,7 +13792,7 @@
         <v>186</v>
       </c>
       <c r="M185" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N185" t="s">
         <v>14</v>
@@ -13806,19 +13806,19 @@
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D186" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E186" t="s">
         <v>1413</v>
-      </c>
-      <c r="B186" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D186" t="s">
-        <v>1416</v>
-      </c>
-      <c r="E186" t="s">
-        <v>1415</v>
       </c>
       <c r="F186" t="s">
         <v>47</v>
@@ -13842,7 +13842,7 @@
         <v>178</v>
       </c>
       <c r="M186" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N186" t="s">
         <v>14</v>
@@ -13856,19 +13856,19 @@
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B187" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="C187" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D187" t="s">
         <v>1438</v>
       </c>
-      <c r="D187" t="s">
-        <v>1440</v>
-      </c>
       <c r="E187" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="F187" t="s">
         <v>47</v>
@@ -13892,7 +13892,7 @@
         <v>178</v>
       </c>
       <c r="M187" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N187" t="s">
         <v>14</v>
@@ -13912,13 +13912,13 @@
         <v>374</v>
       </c>
       <c r="C188" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D188" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E188" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F188" t="s">
         <v>47</v>
@@ -13956,19 +13956,19 @@
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B189" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C189" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D189" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E189" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F189" t="s">
         <v>47</v>
@@ -13989,7 +13989,7 @@
         <v>75</v>
       </c>
       <c r="L189" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M189" t="s">
         <v>48</v>
@@ -14006,19 +14006,19 @@
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B190" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D190" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E190" t="s">
         <v>1370</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D190" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E190" t="s">
-        <v>1372</v>
       </c>
       <c r="F190" t="s">
         <v>78</v>
@@ -14030,7 +14030,7 @@
         <v>13</v>
       </c>
       <c r="I190" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="J190" t="s">
         <v>263</v>
@@ -14056,19 +14056,19 @@
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="B191" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="C191" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="D191" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E191" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F191" t="s">
         <v>47</v>
@@ -14092,7 +14092,7 @@
         <v>178</v>
       </c>
       <c r="M191" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N191" t="s">
         <v>14</v>
@@ -14112,13 +14112,13 @@
         <v>243</v>
       </c>
       <c r="C192" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="D192" t="s">
         <v>407</v>
       </c>
       <c r="E192" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F192" t="s">
         <v>47</v>
@@ -14162,13 +14162,13 @@
         <v>245</v>
       </c>
       <c r="C193" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D193" t="s">
         <v>408</v>
       </c>
       <c r="E193" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F193" t="s">
         <v>47</v>
@@ -14206,19 +14206,19 @@
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C194" t="s">
         <v>1362</v>
       </c>
-      <c r="B194" t="s">
+      <c r="D194" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E194" t="s">
         <v>1365</v>
-      </c>
-      <c r="C194" t="s">
-        <v>1364</v>
-      </c>
-      <c r="D194" t="s">
-        <v>1366</v>
-      </c>
-      <c r="E194" t="s">
-        <v>1367</v>
       </c>
       <c r="F194" t="s">
         <v>78</v>
@@ -14230,10 +14230,10 @@
         <v>13</v>
       </c>
       <c r="I194" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="J194" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="L194" t="s">
         <v>95</v>
@@ -14259,13 +14259,13 @@
         <v>307</v>
       </c>
       <c r="C195" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="D195" t="s">
         <v>308</v>
       </c>
       <c r="E195" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F195" t="s">
         <v>78</v>
@@ -14303,19 +14303,19 @@
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B196" t="s">
+        <v>627</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D196" t="s">
         <v>628</v>
       </c>
-      <c r="C196" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D196" t="s">
-        <v>629</v>
-      </c>
       <c r="E196" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F196" t="s">
         <v>78</v>
@@ -14350,19 +14350,19 @@
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B197" t="s">
+        <v>629</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D197" t="s">
         <v>630</v>
       </c>
-      <c r="C197" t="s">
-        <v>1161</v>
-      </c>
-      <c r="D197" t="s">
-        <v>631</v>
-      </c>
       <c r="E197" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F197" t="s">
         <v>78</v>
@@ -14403,13 +14403,13 @@
         <v>306</v>
       </c>
       <c r="C198" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="D198" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E198" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F198" t="s">
         <v>78</v>
@@ -14450,13 +14450,13 @@
         <v>304</v>
       </c>
       <c r="C199" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="D199" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E199" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F199" t="s">
         <v>78</v>
@@ -14500,10 +14500,10 @@
         <v>410</v>
       </c>
       <c r="D200" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E200" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F200" t="s">
         <v>47</v>
@@ -14527,7 +14527,7 @@
         <v>179</v>
       </c>
       <c r="M200" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N200" t="s">
         <v>14</v>
@@ -14541,7 +14541,7 @@
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B201" t="s">
         <v>410</v>
@@ -14550,10 +14550,10 @@
         <v>410</v>
       </c>
       <c r="D201" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E201" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F201" t="s">
         <v>78</v>
@@ -14588,19 +14588,19 @@
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B202" t="s">
+        <v>641</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D202" t="s">
         <v>642</v>
       </c>
-      <c r="C202" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D202" t="s">
-        <v>643</v>
-      </c>
       <c r="E202" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F202" t="s">
         <v>78</v>
@@ -14644,13 +14644,13 @@
         <v>318</v>
       </c>
       <c r="C203" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="D203" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E203" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F203" t="s">
         <v>78</v>
@@ -14685,19 +14685,19 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B204" t="s">
+        <v>644</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D204" t="s">
         <v>645</v>
       </c>
-      <c r="C204" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D204" t="s">
-        <v>646</v>
-      </c>
       <c r="E204" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F204" t="s">
         <v>47</v>
@@ -14735,13 +14735,13 @@
         <v>313</v>
       </c>
       <c r="C205" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="D205" t="s">
         <v>314</v>
       </c>
       <c r="E205" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F205" t="s">
         <v>78</v>
@@ -14765,7 +14765,7 @@
         <v>186</v>
       </c>
       <c r="M205" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N205" t="s">
         <v>14</v>
@@ -14782,16 +14782,16 @@
         <v>254</v>
       </c>
       <c r="B206" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C206" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D206" t="s">
         <v>279</v>
       </c>
       <c r="E206" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F206" t="s">
         <v>47</v>
@@ -14815,7 +14815,7 @@
         <v>278</v>
       </c>
       <c r="M206" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N206" t="s">
         <v>14</v>
@@ -14835,13 +14835,13 @@
         <v>328</v>
       </c>
       <c r="C207" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="D207" t="s">
         <v>329</v>
       </c>
       <c r="E207" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F207" t="s">
         <v>78</v>
@@ -14882,16 +14882,16 @@
         <v>556</v>
       </c>
       <c r="B208" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C208" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="D208" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E208" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F208" t="s">
         <v>78</v>
@@ -14912,10 +14912,10 @@
         <v>54</v>
       </c>
       <c r="L208" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="M208" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N208" t="s">
         <v>14</v>
@@ -14935,13 +14935,13 @@
         <v>311</v>
       </c>
       <c r="C209" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="D209" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E209" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F209" t="s">
         <v>78</v>
@@ -14985,13 +14985,13 @@
         <v>319</v>
       </c>
       <c r="C210" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="D210" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E210" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F210" t="s">
         <v>78</v>
@@ -15029,19 +15029,19 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B211" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="C211" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="D211" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E211" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F211" t="s">
         <v>78</v>
@@ -15079,19 +15079,19 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B212" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C212" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="D212" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E212" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F212" t="s">
         <v>78</v>
@@ -15129,19 +15129,19 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B213" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C213" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="D213" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E213" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F213" t="s">
         <v>47</v>
@@ -15185,13 +15185,13 @@
         <v>326</v>
       </c>
       <c r="C214" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="D214" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E214" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F214" t="s">
         <v>78</v>
@@ -15235,13 +15235,13 @@
         <v>327</v>
       </c>
       <c r="C215" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="D215" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E215" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F215" t="s">
         <v>78</v>
@@ -15279,19 +15279,19 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B216" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C216" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="D216" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E216" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F216" t="s">
         <v>47</v>
@@ -15329,19 +15329,19 @@
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B217" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C217" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="D217" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E217" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F217" t="s">
         <v>47</v>
@@ -15379,19 +15379,19 @@
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B218" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C218" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D218" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E218" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F218" t="s">
         <v>47</v>
@@ -15429,19 +15429,19 @@
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B219" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C219" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D219" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E219" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F219" t="s">
         <v>47</v>
@@ -15479,19 +15479,19 @@
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B220" t="s">
         <v>727</v>
       </c>
-      <c r="B220" t="s">
-        <v>728</v>
-      </c>
       <c r="C220" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="D220" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E220" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F220" t="s">
         <v>47</v>
@@ -15529,19 +15529,19 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B221" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C221" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="D221" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E221" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F221" t="s">
         <v>47</v>
@@ -15553,7 +15553,7 @@
         <v>31</v>
       </c>
       <c r="I221" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J221" t="s">
         <v>276</v>
@@ -15579,19 +15579,19 @@
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B222" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C222" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D222" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E222" t="s">
         <v>1245</v>
-      </c>
-      <c r="E222" t="s">
-        <v>1247</v>
       </c>
       <c r="F222" t="s">
         <v>47</v>
@@ -15615,7 +15615,7 @@
         <v>178</v>
       </c>
       <c r="M222" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N222" t="s">
         <v>14</v>
@@ -15629,19 +15629,19 @@
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B223" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D223" t="s">
         <v>1302</v>
       </c>
-      <c r="C223" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D223" t="s">
-        <v>1304</v>
-      </c>
       <c r="E223" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="F223" t="s">
         <v>47</v>
@@ -15679,19 +15679,19 @@
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B224" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C224" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="D224" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E224" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F224" t="s">
         <v>47</v>
@@ -15726,19 +15726,19 @@
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B225" t="s">
+        <v>680</v>
+      </c>
+      <c r="C225" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D225" t="s">
         <v>681</v>
       </c>
-      <c r="C225" t="s">
-        <v>1206</v>
-      </c>
-      <c r="D225" t="s">
-        <v>682</v>
-      </c>
       <c r="E225" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F225" t="s">
         <v>47</v>
@@ -15773,19 +15773,19 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B226" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C226" t="s">
         <v>1244</v>
       </c>
-      <c r="C226" t="s">
-        <v>1246</v>
-      </c>
       <c r="D226" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E226" t="s">
         <v>1245</v>
-      </c>
-      <c r="E226" t="s">
-        <v>1247</v>
       </c>
       <c r="F226" t="s">
         <v>47</v>
@@ -15809,7 +15809,7 @@
         <v>178</v>
       </c>
       <c r="M226" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N226" t="s">
         <v>14</v>
@@ -15823,19 +15823,19 @@
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>1459</v>
+        <v>1235</v>
       </c>
       <c r="B227" t="s">
-        <v>1467</v>
+        <v>1246</v>
       </c>
       <c r="C227" t="s">
-        <v>1468</v>
+        <v>1247</v>
       </c>
       <c r="D227" t="s">
-        <v>1469</v>
+        <v>1243</v>
       </c>
       <c r="E227" t="s">
-        <v>1470</v>
+        <v>1245</v>
       </c>
       <c r="F227" t="s">
         <v>47</v>
@@ -15844,13 +15844,13 @@
         <v>32</v>
       </c>
       <c r="H227" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I227" t="s">
-        <v>445</v>
+        <v>140</v>
       </c>
       <c r="J227" t="s">
-        <v>276</v>
+        <v>583</v>
       </c>
       <c r="K227" t="s">
         <v>54</v>
@@ -15873,22 +15873,16 @@
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>1262</v>
+        <v>1454</v>
       </c>
       <c r="B228" t="s">
-        <v>1265</v>
+        <v>1459</v>
       </c>
       <c r="C228" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D228" t="s">
-        <v>682</v>
-      </c>
-      <c r="E228" t="s">
-        <v>1006</v>
+        <v>1462</v>
       </c>
       <c r="F228" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G228" t="s">
         <v>32</v>
@@ -15897,13 +15891,13 @@
         <v>31</v>
       </c>
       <c r="I228" t="s">
-        <v>1270</v>
-      </c>
-      <c r="J228" t="s">
-        <v>276</v>
+        <v>445</v>
+      </c>
+      <c r="K228" t="s">
+        <v>54</v>
       </c>
       <c r="L228" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="M228" t="s">
         <v>48</v>
@@ -15920,34 +15914,25 @@
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>1330</v>
+        <v>1455</v>
       </c>
       <c r="B229" t="s">
-        <v>1354</v>
+        <v>1460</v>
       </c>
       <c r="C229" t="s">
-        <v>1355</v>
-      </c>
-      <c r="D229" t="s">
-        <v>1358</v>
-      </c>
-      <c r="E229" t="s">
-        <v>1359</v>
+        <v>1463</v>
       </c>
       <c r="F229" t="s">
         <v>47</v>
       </c>
       <c r="G229" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="H229" t="s">
         <v>31</v>
       </c>
       <c r="I229" t="s">
-        <v>107</v>
-      </c>
-      <c r="J229" t="s">
-        <v>276</v>
+        <v>445</v>
       </c>
       <c r="K229" t="s">
         <v>54</v>
@@ -15956,7 +15941,7 @@
         <v>178</v>
       </c>
       <c r="M229" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N229" t="s">
         <v>14</v>
@@ -15970,19 +15955,13 @@
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>1237</v>
+        <v>1456</v>
       </c>
       <c r="B230" t="s">
-        <v>1248</v>
+        <v>1461</v>
       </c>
       <c r="C230" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D230" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E230" t="s">
-        <v>1247</v>
+        <v>1464</v>
       </c>
       <c r="F230" t="s">
         <v>47</v>
@@ -15991,13 +15970,10 @@
         <v>32</v>
       </c>
       <c r="H230" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I230" t="s">
-        <v>140</v>
-      </c>
-      <c r="J230" t="s">
-        <v>584</v>
+        <v>445</v>
       </c>
       <c r="K230" t="s">
         <v>54</v>
@@ -16020,13 +15996,19 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B231" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="C231" t="s">
-        <v>1464</v>
+        <v>1466</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E231" t="s">
+        <v>1468</v>
       </c>
       <c r="F231" t="s">
         <v>47</v>
@@ -16040,6 +16022,9 @@
       <c r="I231" t="s">
         <v>445</v>
       </c>
+      <c r="J231" t="s">
+        <v>276</v>
+      </c>
       <c r="K231" t="s">
         <v>54</v>
       </c>
@@ -16061,16 +16046,22 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>1457</v>
+        <v>1260</v>
       </c>
       <c r="B232" t="s">
-        <v>1462</v>
+        <v>1263</v>
       </c>
       <c r="C232" t="s">
-        <v>1465</v>
+        <v>1265</v>
+      </c>
+      <c r="D232" t="s">
+        <v>681</v>
+      </c>
+      <c r="E232" t="s">
+        <v>1005</v>
       </c>
       <c r="F232" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G232" t="s">
         <v>32</v>
@@ -16079,13 +16070,13 @@
         <v>31</v>
       </c>
       <c r="I232" t="s">
-        <v>445</v>
-      </c>
-      <c r="K232" t="s">
-        <v>54</v>
+        <v>1268</v>
+      </c>
+      <c r="J232" t="s">
+        <v>276</v>
       </c>
       <c r="L232" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="M232" t="s">
         <v>48</v>
@@ -16102,25 +16093,34 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>1458</v>
+        <v>1328</v>
       </c>
       <c r="B233" t="s">
-        <v>1463</v>
+        <v>1352</v>
       </c>
       <c r="C233" t="s">
-        <v>1466</v>
+        <v>1353</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E233" t="s">
+        <v>1357</v>
       </c>
       <c r="F233" t="s">
         <v>47</v>
       </c>
       <c r="G233" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="H233" t="s">
         <v>31</v>
       </c>
       <c r="I233" t="s">
-        <v>445</v>
+        <v>107</v>
+      </c>
+      <c r="J233" t="s">
+        <v>276</v>
       </c>
       <c r="K233" t="s">
         <v>54</v>
@@ -16129,7 +16129,7 @@
         <v>178</v>
       </c>
       <c r="M233" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N233" t="s">
         <v>14</v>
@@ -16149,13 +16149,13 @@
         <v>280</v>
       </c>
       <c r="C234" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="D234" t="s">
         <v>281</v>
       </c>
       <c r="E234" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F234" t="s">
         <v>47</v>
@@ -16176,7 +16176,7 @@
         <v>95</v>
       </c>
       <c r="M234" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N234" t="s">
         <v>14</v>
@@ -16190,13 +16190,13 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B235" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C235" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="F235" t="s">
         <v>47</v>
@@ -16231,19 +16231,19 @@
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="B236" t="s">
-        <v>799</v>
+        <v>324</v>
       </c>
       <c r="C236" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
       <c r="D236" t="s">
-        <v>350</v>
+        <v>796</v>
       </c>
       <c r="E236" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="F236" t="s">
         <v>78</v>
@@ -16255,16 +16255,16 @@
         <v>13</v>
       </c>
       <c r="I236" t="s">
-        <v>108</v>
+        <v>325</v>
       </c>
       <c r="J236" t="s">
-        <v>519</v>
+        <v>205</v>
       </c>
       <c r="K236" t="s">
         <v>75</v>
       </c>
       <c r="L236" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="M236" t="s">
         <v>48</v>
@@ -16281,19 +16281,19 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>300</v>
+        <v>1472</v>
       </c>
       <c r="B237" t="s">
-        <v>324</v>
+        <v>1473</v>
       </c>
       <c r="C237" t="s">
-        <v>1170</v>
+        <v>1474</v>
       </c>
       <c r="D237" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E237" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F237" t="s">
         <v>78</v>
@@ -16305,7 +16305,7 @@
         <v>13</v>
       </c>
       <c r="I237" t="s">
-        <v>325</v>
+        <v>267</v>
       </c>
       <c r="J237" t="s">
         <v>205</v>
@@ -16331,22 +16331,22 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>1474</v>
+        <v>664</v>
       </c>
       <c r="B238" t="s">
-        <v>1475</v>
+        <v>684</v>
       </c>
       <c r="C238" t="s">
-        <v>1476</v>
+        <v>1205</v>
       </c>
       <c r="D238" t="s">
-        <v>797</v>
+        <v>685</v>
       </c>
       <c r="E238" t="s">
-        <v>971</v>
+        <v>1007</v>
       </c>
       <c r="F238" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G238" t="s">
         <v>51</v>
@@ -16355,16 +16355,16 @@
         <v>13</v>
       </c>
       <c r="I238" t="s">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="J238" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="K238" t="s">
         <v>75</v>
       </c>
       <c r="L238" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="M238" t="s">
         <v>48</v>
@@ -16381,43 +16381,43 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>665</v>
+        <v>246</v>
       </c>
       <c r="B239" t="s">
-        <v>685</v>
+        <v>256</v>
       </c>
       <c r="C239" t="s">
-        <v>1207</v>
+        <v>1082</v>
       </c>
       <c r="D239" t="s">
-        <v>686</v>
+        <v>257</v>
       </c>
       <c r="E239" t="s">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="F239" t="s">
         <v>47</v>
       </c>
       <c r="G239" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H239" t="s">
         <v>13</v>
       </c>
       <c r="I239" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="J239" t="s">
-        <v>276</v>
+        <v>205</v>
       </c>
       <c r="K239" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="L239" t="s">
-        <v>178</v>
+        <v>264</v>
       </c>
       <c r="M239" t="s">
-        <v>48</v>
+        <v>830</v>
       </c>
       <c r="N239" t="s">
         <v>14</v>
@@ -16431,22 +16431,22 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>246</v>
+        <v>461</v>
       </c>
       <c r="B240" t="s">
-        <v>256</v>
+        <v>801</v>
       </c>
       <c r="C240" t="s">
-        <v>1083</v>
+        <v>1179</v>
       </c>
       <c r="D240" t="s">
-        <v>257</v>
+        <v>469</v>
       </c>
       <c r="E240" t="s">
-        <v>1025</v>
+        <v>978</v>
       </c>
       <c r="F240" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G240" t="s">
         <v>32</v>
@@ -16458,16 +16458,13 @@
         <v>140</v>
       </c>
       <c r="J240" t="s">
-        <v>205</v>
-      </c>
-      <c r="K240" t="s">
-        <v>53</v>
+        <v>276</v>
       </c>
       <c r="L240" t="s">
-        <v>264</v>
+        <v>492</v>
       </c>
       <c r="M240" t="s">
-        <v>831</v>
+        <v>48</v>
       </c>
       <c r="N240" t="s">
         <v>14</v>
@@ -16481,22 +16478,22 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>461</v>
+        <v>251</v>
       </c>
       <c r="B241" t="s">
-        <v>802</v>
+        <v>272</v>
       </c>
       <c r="C241" t="s">
-        <v>1181</v>
+        <v>1085</v>
       </c>
       <c r="D241" t="s">
-        <v>469</v>
+        <v>273</v>
       </c>
       <c r="E241" t="s">
-        <v>979</v>
+        <v>1025</v>
       </c>
       <c r="F241" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G241" t="s">
         <v>32</v>
@@ -16508,10 +16505,13 @@
         <v>140</v>
       </c>
       <c r="J241" t="s">
-        <v>276</v>
+        <v>274</v>
+      </c>
+      <c r="K241" t="s">
+        <v>54</v>
       </c>
       <c r="L241" t="s">
-        <v>492</v>
+        <v>95</v>
       </c>
       <c r="M241" t="s">
         <v>48</v>
@@ -16528,22 +16528,22 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>251</v>
+        <v>406</v>
       </c>
       <c r="B242" t="s">
-        <v>272</v>
+        <v>799</v>
       </c>
       <c r="C242" t="s">
-        <v>1087</v>
+        <v>1177</v>
       </c>
       <c r="D242" t="s">
-        <v>273</v>
+        <v>800</v>
       </c>
       <c r="E242" t="s">
-        <v>1026</v>
+        <v>975</v>
       </c>
       <c r="F242" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G242" t="s">
         <v>32</v>
@@ -16555,13 +16555,10 @@
         <v>140</v>
       </c>
       <c r="J242" t="s">
-        <v>274</v>
-      </c>
-      <c r="K242" t="s">
-        <v>54</v>
+        <v>489</v>
       </c>
       <c r="L242" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="M242" t="s">
         <v>48</v>
@@ -16578,19 +16575,19 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>406</v>
+        <v>588</v>
       </c>
       <c r="B243" t="s">
-        <v>800</v>
+        <v>594</v>
       </c>
       <c r="C243" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="D243" t="s">
-        <v>801</v>
+        <v>595</v>
       </c>
       <c r="E243" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="F243" t="s">
         <v>78</v>
@@ -16602,13 +16599,16 @@
         <v>13</v>
       </c>
       <c r="I243" t="s">
-        <v>140</v>
+        <v>267</v>
       </c>
       <c r="J243" t="s">
-        <v>489</v>
+        <v>596</v>
+      </c>
+      <c r="K243" t="s">
+        <v>53</v>
       </c>
       <c r="L243" t="s">
-        <v>181</v>
+        <v>492</v>
       </c>
       <c r="M243" t="s">
         <v>48</v>
@@ -16625,40 +16625,40 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>589</v>
+        <v>668</v>
       </c>
       <c r="B244" t="s">
-        <v>595</v>
+        <v>688</v>
       </c>
       <c r="C244" t="s">
-        <v>1193</v>
+        <v>1207</v>
       </c>
       <c r="D244" t="s">
-        <v>596</v>
+        <v>689</v>
       </c>
       <c r="E244" t="s">
-        <v>989</v>
+        <v>1009</v>
       </c>
       <c r="F244" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G244" t="s">
         <v>32</v>
       </c>
       <c r="H244" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I244" t="s">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="J244" t="s">
-        <v>597</v>
+        <v>276</v>
       </c>
       <c r="K244" t="s">
-        <v>53</v>
+        <v>414</v>
       </c>
       <c r="L244" t="s">
-        <v>492</v>
+        <v>178</v>
       </c>
       <c r="M244" t="s">
         <v>48</v>
@@ -16675,19 +16675,19 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>669</v>
+        <v>497</v>
       </c>
       <c r="B245" t="s">
-        <v>689</v>
+        <v>503</v>
       </c>
       <c r="C245" t="s">
-        <v>1209</v>
+        <v>1119</v>
       </c>
       <c r="D245" t="s">
-        <v>690</v>
+        <v>504</v>
       </c>
       <c r="E245" t="s">
-        <v>1010</v>
+        <v>922</v>
       </c>
       <c r="F245" t="s">
         <v>47</v>
@@ -16699,13 +16699,13 @@
         <v>31</v>
       </c>
       <c r="I245" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="J245" t="s">
         <v>276</v>
       </c>
       <c r="K245" t="s">
-        <v>414</v>
+        <v>54</v>
       </c>
       <c r="L245" t="s">
         <v>178</v>
@@ -16725,19 +16725,13 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>497</v>
+        <v>1458</v>
       </c>
       <c r="B246" t="s">
-        <v>503</v>
+        <v>1469</v>
       </c>
       <c r="C246" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D246" t="s">
-        <v>504</v>
-      </c>
-      <c r="E246" t="s">
-        <v>923</v>
+        <v>1470</v>
       </c>
       <c r="F246" t="s">
         <v>47</v>
@@ -16749,7 +16743,7 @@
         <v>31</v>
       </c>
       <c r="I246" t="s">
-        <v>142</v>
+        <v>445</v>
       </c>
       <c r="J246" t="s">
         <v>276</v>
@@ -16775,34 +16769,40 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>1460</v>
+        <v>459</v>
       </c>
       <c r="B247" t="s">
-        <v>1471</v>
+        <v>466</v>
       </c>
       <c r="C247" t="s">
-        <v>1472</v>
+        <v>1178</v>
+      </c>
+      <c r="D247" t="s">
+        <v>467</v>
+      </c>
+      <c r="E247" t="s">
+        <v>977</v>
       </c>
       <c r="F247" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G247" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H247" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I247" t="s">
-        <v>445</v>
+        <v>267</v>
       </c>
       <c r="J247" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="K247" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L247" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M247" t="s">
         <v>48</v>
@@ -16819,19 +16819,19 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>459</v>
+        <v>337</v>
       </c>
       <c r="B248" t="s">
-        <v>466</v>
+        <v>798</v>
       </c>
       <c r="C248" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="D248" t="s">
-        <v>467</v>
+        <v>350</v>
       </c>
       <c r="E248" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="F248" t="s">
         <v>78</v>
@@ -16843,16 +16843,16 @@
         <v>13</v>
       </c>
       <c r="I248" t="s">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="J248" t="s">
-        <v>305</v>
+        <v>519</v>
       </c>
       <c r="K248" t="s">
         <v>75</v>
       </c>
       <c r="L248" t="s">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="M248" t="s">
         <v>48</v>
@@ -16872,16 +16872,16 @@
         <v>555</v>
       </c>
       <c r="B249" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C249" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="D249" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E249" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F249" t="s">
         <v>78</v>
@@ -16922,13 +16922,13 @@
         <v>447</v>
       </c>
       <c r="C250" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="D250" t="s">
         <v>448</v>
       </c>
       <c r="E250" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F250" t="s">
         <v>47</v>
@@ -16972,13 +16972,13 @@
         <v>454</v>
       </c>
       <c r="C251" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="D251" t="s">
         <v>455</v>
       </c>
       <c r="E251" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F251" t="s">
         <v>47</v>
@@ -17016,19 +17016,19 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B252" t="s">
+        <v>598</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D252" t="s">
         <v>599</v>
       </c>
-      <c r="C252" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D252" t="s">
-        <v>600</v>
-      </c>
       <c r="E252" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F252" t="s">
         <v>78</v>
@@ -17052,7 +17052,7 @@
         <v>186</v>
       </c>
       <c r="M252" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N252" t="s">
         <v>14</v>
@@ -17066,19 +17066,19 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B253" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C253" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="D253" t="s">
         <v>455</v>
       </c>
       <c r="E253" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F253" t="s">
         <v>47</v>
@@ -17093,7 +17093,7 @@
         <v>142</v>
       </c>
       <c r="J253" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="L253" t="s">
         <v>95</v>
@@ -17113,13 +17113,13 @@
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B254" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C254" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="F254" t="s">
         <v>47</v>
@@ -17131,10 +17131,10 @@
         <v>31</v>
       </c>
       <c r="I254" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="J254" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="K254" t="s">
         <v>54</v>
@@ -17157,13 +17157,13 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B255" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C255" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="F255" t="s">
         <v>47</v>
@@ -17187,7 +17187,7 @@
         <v>178</v>
       </c>
       <c r="M255" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N255" t="s">
         <v>14</v>
@@ -17201,19 +17201,19 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="B256" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="C256" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="D256" t="s">
         <v>382</v>
       </c>
       <c r="E256" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F256" t="s">
         <v>47</v>
@@ -17248,19 +17248,19 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B257" t="s">
+        <v>676</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D257" t="s">
         <v>677</v>
       </c>
-      <c r="C257" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D257" t="s">
-        <v>678</v>
-      </c>
       <c r="E257" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F257" t="s">
         <v>47</v>
@@ -17298,19 +17298,19 @@
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B258" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C258" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="D258" t="s">
         <v>382</v>
       </c>
       <c r="E258" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F258" t="s">
         <v>47</v>
@@ -17331,7 +17331,7 @@
         <v>178</v>
       </c>
       <c r="M258" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N258" t="s">
         <v>14</v>
@@ -17351,13 +17351,13 @@
         <v>383</v>
       </c>
       <c r="C259" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="D259" t="s">
         <v>384</v>
       </c>
       <c r="E259" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F259" t="s">
         <v>47</v>
@@ -17378,7 +17378,7 @@
         <v>385</v>
       </c>
       <c r="M259" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N259" t="s">
         <v>14</v>
@@ -17398,13 +17398,13 @@
         <v>386</v>
       </c>
       <c r="C260" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="D260" t="s">
         <v>387</v>
       </c>
       <c r="E260" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F260" t="s">
         <v>47</v>
@@ -17442,19 +17442,19 @@
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B261" t="s">
+        <v>580</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D261" t="s">
         <v>581</v>
       </c>
-      <c r="C261" t="s">
-        <v>1189</v>
-      </c>
-      <c r="D261" t="s">
-        <v>582</v>
-      </c>
       <c r="E261" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F261" t="s">
         <v>47</v>
@@ -17492,19 +17492,19 @@
     </row>
     <row r="262" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B262" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C262" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D262" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E262" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F262" t="s">
         <v>78</v>
@@ -17548,13 +17548,13 @@
         <v>198</v>
       </c>
       <c r="C263" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D263" t="s">
         <v>199</v>
       </c>
       <c r="E263" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F263" t="s">
         <v>47</v>
@@ -17598,13 +17598,13 @@
         <v>202</v>
       </c>
       <c r="C264" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D264" t="s">
         <v>203</v>
       </c>
       <c r="E264" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F264" t="s">
         <v>47</v>
@@ -17648,13 +17648,13 @@
         <v>206</v>
       </c>
       <c r="C265" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D265" t="s">
         <v>207</v>
       </c>
       <c r="E265" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F265" t="s">
         <v>47</v>
@@ -17698,13 +17698,13 @@
         <v>196</v>
       </c>
       <c r="C266" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D266" t="s">
         <v>197</v>
       </c>
       <c r="E266" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F266" t="s">
         <v>47</v>
@@ -17742,19 +17742,19 @@
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B267" t="s">
+        <v>637</v>
+      </c>
+      <c r="C267" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D267" t="s">
         <v>638</v>
       </c>
-      <c r="C267" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D267" t="s">
-        <v>639</v>
-      </c>
       <c r="E267" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F267" t="s">
         <v>78</v>
@@ -17789,19 +17789,19 @@
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B268" t="s">
+        <v>639</v>
+      </c>
+      <c r="C268" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D268" t="s">
         <v>640</v>
       </c>
-      <c r="C268" t="s">
-        <v>1199</v>
-      </c>
-      <c r="D268" t="s">
-        <v>641</v>
-      </c>
       <c r="E268" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F268" t="s">
         <v>78</v>
@@ -17836,19 +17836,19 @@
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B269" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C269" t="s">
         <v>1489</v>
       </c>
-      <c r="B269" t="s">
-        <v>1490</v>
-      </c>
-      <c r="C269" t="s">
-        <v>1491</v>
-      </c>
       <c r="D269" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E269" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F269" t="s">
         <v>78</v>
@@ -17886,19 +17886,19 @@
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B270" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C270" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="D270" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E270" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F270" t="s">
         <v>78</v>
@@ -17936,19 +17936,19 @@
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B271" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C271" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D271" t="s">
         <v>1308</v>
       </c>
-      <c r="C271" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D271" t="s">
-        <v>1310</v>
-      </c>
       <c r="E271" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="F271" t="s">
         <v>47</v>
@@ -17960,7 +17960,7 @@
         <v>31</v>
       </c>
       <c r="I271" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="J271" t="s">
         <v>201</v>
@@ -17972,7 +17972,7 @@
         <v>178</v>
       </c>
       <c r="M271" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N271" t="s">
         <v>14</v>
@@ -17986,19 +17986,19 @@
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B272" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C272" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D272" t="s">
         <v>1289</v>
       </c>
-      <c r="C272" t="s">
+      <c r="E272" t="s">
         <v>1290</v>
-      </c>
-      <c r="D272" t="s">
-        <v>1291</v>
-      </c>
-      <c r="E272" t="s">
-        <v>1292</v>
       </c>
       <c r="F272" t="s">
         <v>78</v>
@@ -18022,7 +18022,7 @@
         <v>186</v>
       </c>
       <c r="M272" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N272" t="s">
         <v>14</v>
@@ -18036,13 +18036,13 @@
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B273" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C273" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="F273" t="s">
         <v>47</v>
@@ -18077,19 +18077,19 @@
     </row>
     <row r="274" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B274" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C274" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D274" t="s">
         <v>1380</v>
       </c>
-      <c r="C274" t="s">
-        <v>1381</v>
-      </c>
-      <c r="D274" t="s">
-        <v>1382</v>
-      </c>
       <c r="E274" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F274" t="s">
         <v>47</v>
@@ -18113,7 +18113,7 @@
         <v>178</v>
       </c>
       <c r="M274" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N274" t="s">
         <v>14</v>
@@ -18127,19 +18127,19 @@
     </row>
     <row r="275" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B275" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C275" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="D275" t="s">
         <v>442</v>
       </c>
       <c r="E275" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F275" t="s">
         <v>47</v>
@@ -18174,13 +18174,13 @@
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="B276" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="C276" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F276" t="s">
         <v>47</v>
@@ -18221,13 +18221,13 @@
         <v>439</v>
       </c>
       <c r="C277" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="D277" t="s">
         <v>442</v>
       </c>
       <c r="E277" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F277" t="s">
         <v>47</v>
@@ -18271,13 +18271,13 @@
         <v>441</v>
       </c>
       <c r="C278" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="D278" t="s">
         <v>442</v>
       </c>
       <c r="E278" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F278" t="s">
         <v>47</v>
@@ -18321,13 +18321,13 @@
         <v>456</v>
       </c>
       <c r="C279" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="D279" t="s">
         <v>442</v>
       </c>
       <c r="E279" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F279" t="s">
         <v>47</v>
@@ -18365,19 +18365,19 @@
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B280" t="s">
+        <v>682</v>
+      </c>
+      <c r="C280" t="s">
+        <v>682</v>
+      </c>
+      <c r="D280" t="s">
         <v>683</v>
       </c>
-      <c r="C280" t="s">
-        <v>683</v>
-      </c>
-      <c r="D280" t="s">
-        <v>684</v>
-      </c>
       <c r="E280" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F280" t="s">
         <v>47</v>
@@ -18415,19 +18415,19 @@
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B281" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C281" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="D281" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E281" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F281" t="s">
         <v>47</v>
@@ -18471,13 +18471,13 @@
         <v>452</v>
       </c>
       <c r="C282" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="D282" t="s">
         <v>453</v>
       </c>
       <c r="E282" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F282" t="s">
         <v>47</v>
@@ -18515,13 +18515,13 @@
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B283" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C283" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="F283" t="s">
         <v>47</v>
@@ -18559,19 +18559,19 @@
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B284" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C284" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D284" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E284" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F284" t="s">
         <v>47</v>
@@ -18592,7 +18592,7 @@
         <v>178</v>
       </c>
       <c r="M284" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N284" t="s">
         <v>14</v>
@@ -18606,19 +18606,19 @@
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B285" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C285" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="D285" t="s">
         <v>382</v>
       </c>
       <c r="E285" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F285" t="s">
         <v>47</v>
@@ -18636,7 +18636,7 @@
         <v>519</v>
       </c>
       <c r="L285" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="M285" t="s">
         <v>48</v>
@@ -18659,13 +18659,13 @@
         <v>381</v>
       </c>
       <c r="C286" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="D286" t="s">
         <v>382</v>
       </c>
       <c r="E286" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F286" t="s">
         <v>47</v>
@@ -18700,19 +18700,19 @@
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B287" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C287" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D287" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E287" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F287" t="s">
         <v>78</v>
@@ -18727,13 +18727,13 @@
         <v>140</v>
       </c>
       <c r="J287" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="L287" t="s">
         <v>186</v>
       </c>
       <c r="M287" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N287" t="s">
         <v>14</v>
@@ -18747,19 +18747,19 @@
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B288" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C288" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="D288" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E288" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F288" t="s">
         <v>78</v>
@@ -18794,19 +18794,19 @@
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B289" t="s">
+        <v>625</v>
+      </c>
+      <c r="C289" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D289" t="s">
         <v>626</v>
       </c>
-      <c r="C289" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D289" t="s">
-        <v>627</v>
-      </c>
       <c r="E289" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F289" t="s">
         <v>78</v>
@@ -18841,19 +18841,19 @@
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B290" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C290" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="D290" t="s">
         <v>546</v>
       </c>
       <c r="E290" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F290" t="s">
         <v>47</v>
@@ -18868,7 +18868,7 @@
         <v>140</v>
       </c>
       <c r="J290" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K290" t="s">
         <v>132</v>
@@ -18894,16 +18894,16 @@
         <v>557</v>
       </c>
       <c r="B291" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C291" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="D291" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E291" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F291" t="s">
         <v>78</v>
@@ -18924,7 +18924,7 @@
         <v>75</v>
       </c>
       <c r="L291" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M291" t="s">
         <v>48</v>
@@ -18941,19 +18941,19 @@
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B292" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C292" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D292" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E292" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F292" t="s">
         <v>78</v>
@@ -18988,19 +18988,19 @@
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B293" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C293" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D293" t="s">
         <v>1295</v>
       </c>
-      <c r="C293" t="s">
+      <c r="E293" t="s">
         <v>1296</v>
-      </c>
-      <c r="D293" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E293" t="s">
-        <v>1298</v>
       </c>
       <c r="F293" t="s">
         <v>78</v>
@@ -19038,19 +19038,19 @@
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B294" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C294" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="D294" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E294" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F294" t="s">
         <v>47</v>
@@ -19082,19 +19082,19 @@
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B295" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C295" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="D295" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E295" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F295" t="s">
         <v>47</v>
@@ -19132,19 +19132,19 @@
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B296" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C296" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="D296" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E296" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="F296" t="s">
         <v>47</v>
@@ -19182,19 +19182,19 @@
     </row>
     <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B297" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C297" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D297" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="E297" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="F297" t="s">
         <v>78</v>
@@ -19229,13 +19229,13 @@
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B298" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C298" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F298" t="s">
         <v>78</v>
@@ -19273,19 +19273,19 @@
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B299" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C299" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D299" t="s">
         <v>382</v>
       </c>
       <c r="E299" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F299" t="s">
         <v>47</v>
@@ -19323,16 +19323,16 @@
         <v>392</v>
       </c>
       <c r="B300" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C300" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="D300" t="s">
         <v>397</v>
       </c>
       <c r="E300" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F300" t="s">
         <v>47</v>
@@ -19373,13 +19373,13 @@
         <v>192</v>
       </c>
       <c r="C301" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="D301" t="s">
         <v>193</v>
       </c>
       <c r="E301" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F301" t="s">
         <v>47</v>
@@ -19423,13 +19423,13 @@
         <v>391</v>
       </c>
       <c r="C302" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="D302" t="s">
         <v>390</v>
       </c>
       <c r="E302" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="F302" t="s">
         <v>47</v>
@@ -19464,19 +19464,19 @@
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B303" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C303" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="D303" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="E303" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="F303" t="s">
         <v>47</v>
@@ -19517,13 +19517,13 @@
         <v>70</v>
       </c>
       <c r="C304" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="D304" t="s">
         <v>288</v>
       </c>
       <c r="E304" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="F304" t="s">
         <v>78</v>
@@ -19564,13 +19564,13 @@
         <v>130</v>
       </c>
       <c r="C305" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="D305" t="s">
         <v>131</v>
       </c>
       <c r="E305" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F305" t="s">
         <v>78</v>
@@ -19594,7 +19594,7 @@
         <v>178</v>
       </c>
       <c r="M305" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N305" t="s">
         <v>14</v>
@@ -19608,13 +19608,13 @@
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B306" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C306" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="F306" t="s">
         <v>47</v>
@@ -19646,13 +19646,13 @@
     </row>
     <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B307" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C307" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="F307" t="s">
         <v>47</v>
@@ -19684,13 +19684,13 @@
     </row>
     <row r="308" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B308" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C308" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="F308" t="s">
         <v>47</v>
@@ -19728,13 +19728,13 @@
     </row>
     <row r="309" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B309" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="C309" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="F309" t="s">
         <v>47</v>
@@ -19769,10 +19769,10 @@
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B310" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="F310" t="s">
         <v>47</v>
@@ -19807,19 +19807,19 @@
     </row>
     <row r="311" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B311" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C311" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="D311" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="E311" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F311" t="s">
         <v>47</v>
@@ -19860,13 +19860,13 @@
         <v>545</v>
       </c>
       <c r="C312" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="D312" t="s">
         <v>546</v>
       </c>
       <c r="E312" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F312" t="s">
         <v>78</v>
@@ -19904,19 +19904,19 @@
     </row>
     <row r="313" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B313" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C313" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="D313" t="s">
         <v>546</v>
       </c>
       <c r="E313" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F313" t="s">
         <v>47</v>
@@ -19948,19 +19948,19 @@
     </row>
     <row r="314" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B314" t="s">
+        <v>600</v>
+      </c>
+      <c r="C314" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D314" t="s">
         <v>601</v>
       </c>
-      <c r="C314" t="s">
-        <v>1195</v>
-      </c>
-      <c r="D314" t="s">
-        <v>602</v>
-      </c>
       <c r="E314" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F314" t="s">
         <v>78</v>
@@ -20004,13 +20004,13 @@
         <v>309</v>
       </c>
       <c r="C315" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="D315" t="s">
         <v>310</v>
       </c>
       <c r="E315" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F315" t="s">
         <v>78</v>
@@ -20045,19 +20045,19 @@
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B316" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="C316" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D316" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="E316" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="F316" t="s">
         <v>47</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C10C75E-E201-E34F-98AC-30A62CC1AE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9D9FA0-2A14-CD42-8E47-B873D430213D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4941" uniqueCount="1527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5031" uniqueCount="1548">
   <si>
     <t>id</t>
   </si>
@@ -4601,6 +4601,69 @@
   </si>
   <si>
     <t>For Iberica Province hoodie</t>
+  </si>
+  <si>
+    <t>ILU-0213</t>
+  </si>
+  <si>
+    <t>ILU-0214</t>
+  </si>
+  <si>
+    <t>ILU-0215</t>
+  </si>
+  <si>
+    <t>ILU-0216</t>
+  </si>
+  <si>
+    <t>ILU-0217</t>
+  </si>
+  <si>
+    <t>DIS-0110</t>
+  </si>
+  <si>
+    <t>Pancarta CB Maristas (anterior logo)</t>
+  </si>
+  <si>
+    <t>BC Marists Banner (previous logo)</t>
+  </si>
+  <si>
+    <t>For BC Maristas Seville</t>
+  </si>
+  <si>
+    <t>Occupiamo il futuro logo</t>
+  </si>
+  <si>
+    <t>Let’s occupy the future logo</t>
+  </si>
+  <si>
+    <t>Gente (buena)</t>
+  </si>
+  <si>
+    <t>People (good)</t>
+  </si>
+  <si>
+    <t>Vive Maristas</t>
+  </si>
+  <si>
+    <t>Variación de logo</t>
+  </si>
+  <si>
+    <t>Logo alternative</t>
+  </si>
+  <si>
+    <t>Sueña 200+</t>
+  </si>
+  <si>
+    <t>Dream 200+</t>
+  </si>
+  <si>
+    <t>Faros de Esperanza II</t>
+  </si>
+  <si>
+    <t>Para Asamblea Prov Mediterránea 2021</t>
+  </si>
+  <si>
+    <t>For Provincial Assembly Mediterranea 2021</t>
   </si>
 </sst>
 </file>
@@ -4957,7 +5020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P322"/>
+  <dimension ref="A1:P328"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.5" customWidth="1"/>
@@ -14513,40 +14576,43 @@
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>617</v>
+        <v>1529</v>
       </c>
       <c r="B199" t="s">
-        <v>627</v>
+        <v>1540</v>
       </c>
       <c r="C199" t="s">
-        <v>1156</v>
+        <v>1263</v>
       </c>
       <c r="D199" t="s">
-        <v>628</v>
+        <v>1541</v>
       </c>
       <c r="E199" t="s">
-        <v>956</v>
+        <v>1542</v>
       </c>
       <c r="F199" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G199" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H199" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I199" t="s">
-        <v>267</v>
+        <v>445</v>
       </c>
       <c r="J199" t="s">
         <v>200</v>
       </c>
+      <c r="K199" t="s">
+        <v>54</v>
+      </c>
       <c r="L199" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="M199" t="s">
-        <v>48</v>
+        <v>829</v>
       </c>
       <c r="N199" t="s">
         <v>14</v>
@@ -14560,19 +14626,19 @@
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B200" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C200" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D200" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E200" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F200" t="s">
         <v>78</v>
@@ -14607,19 +14673,19 @@
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>291</v>
+        <v>618</v>
       </c>
       <c r="B201" t="s">
-        <v>306</v>
+        <v>629</v>
       </c>
       <c r="C201" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D201" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E201" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F201" t="s">
         <v>78</v>
@@ -14654,19 +14720,19 @@
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B202" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C202" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D202" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E202" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F202" t="s">
         <v>78</v>
@@ -14701,22 +14767,22 @@
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="B203" t="s">
-        <v>410</v>
+        <v>304</v>
       </c>
       <c r="C203" t="s">
-        <v>410</v>
+        <v>1159</v>
       </c>
       <c r="D203" t="s">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="E203" t="s">
-        <v>891</v>
+        <v>959</v>
       </c>
       <c r="F203" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G203" t="s">
         <v>51</v>
@@ -14725,19 +14791,16 @@
         <v>13</v>
       </c>
       <c r="I203" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J203" t="s">
-        <v>109</v>
-      </c>
-      <c r="K203" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
       <c r="L203" t="s">
-        <v>179</v>
+        <v>97</v>
       </c>
       <c r="M203" t="s">
-        <v>828</v>
+        <v>48</v>
       </c>
       <c r="N203" t="s">
         <v>14</v>
@@ -14751,7 +14814,7 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>615</v>
+        <v>250</v>
       </c>
       <c r="B204" t="s">
         <v>410</v>
@@ -14760,13 +14823,13 @@
         <v>410</v>
       </c>
       <c r="D204" t="s">
-        <v>624</v>
+        <v>602</v>
       </c>
       <c r="E204" t="s">
-        <v>960</v>
+        <v>891</v>
       </c>
       <c r="F204" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G204" t="s">
         <v>51</v>
@@ -14775,16 +14838,19 @@
         <v>13</v>
       </c>
       <c r="I204" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J204" t="s">
-        <v>200</v>
+        <v>109</v>
+      </c>
+      <c r="K204" t="s">
+        <v>139</v>
       </c>
       <c r="L204" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="M204" t="s">
-        <v>48</v>
+        <v>828</v>
       </c>
       <c r="N204" t="s">
         <v>14</v>
@@ -14798,40 +14864,37 @@
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="B205" t="s">
-        <v>641</v>
+        <v>410</v>
       </c>
       <c r="C205" t="s">
-        <v>1160</v>
+        <v>410</v>
       </c>
       <c r="D205" t="s">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="E205" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F205" t="s">
         <v>78</v>
       </c>
       <c r="G205" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H205" t="s">
         <v>13</v>
       </c>
       <c r="I205" t="s">
-        <v>140</v>
+        <v>267</v>
       </c>
       <c r="J205" t="s">
         <v>200</v>
       </c>
-      <c r="K205" t="s">
-        <v>132</v>
-      </c>
       <c r="L205" t="s">
-        <v>340</v>
+        <v>97</v>
       </c>
       <c r="M205" t="s">
         <v>48</v>
@@ -14848,37 +14911,40 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>297</v>
+        <v>622</v>
       </c>
       <c r="B206" t="s">
-        <v>318</v>
+        <v>641</v>
       </c>
       <c r="C206" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="D206" t="s">
-        <v>603</v>
+        <v>642</v>
       </c>
       <c r="E206" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="F206" t="s">
         <v>78</v>
       </c>
       <c r="G206" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H206" t="s">
         <v>13</v>
       </c>
       <c r="I206" t="s">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="J206" t="s">
-        <v>109</v>
+        <v>200</v>
+      </c>
+      <c r="K206" t="s">
+        <v>132</v>
       </c>
       <c r="L206" t="s">
-        <v>95</v>
+        <v>340</v>
       </c>
       <c r="M206" t="s">
         <v>48</v>
@@ -14895,22 +14961,22 @@
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>604</v>
+        <v>1530</v>
       </c>
       <c r="B207" t="s">
-        <v>644</v>
+        <v>1536</v>
       </c>
       <c r="C207" t="s">
-        <v>1196</v>
+        <v>1537</v>
       </c>
       <c r="D207" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E207" t="s">
-        <v>994</v>
+        <v>961</v>
       </c>
       <c r="F207" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G207" t="s">
         <v>32</v>
@@ -14921,6 +14987,12 @@
       <c r="I207" t="s">
         <v>140</v>
       </c>
+      <c r="J207" t="s">
+        <v>200</v>
+      </c>
+      <c r="K207" t="s">
+        <v>132</v>
+      </c>
       <c r="L207" t="s">
         <v>178</v>
       </c>
@@ -14939,19 +15011,19 @@
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B208" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C208" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D208" t="s">
-        <v>314</v>
+        <v>603</v>
       </c>
       <c r="E208" t="s">
-        <v>1035</v>
+        <v>965</v>
       </c>
       <c r="F208" t="s">
         <v>78</v>
@@ -14963,19 +15035,16 @@
         <v>13</v>
       </c>
       <c r="I208" t="s">
-        <v>315</v>
+        <v>267</v>
       </c>
       <c r="J208" t="s">
-        <v>484</v>
-      </c>
-      <c r="K208" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="L208" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="M208" t="s">
-        <v>829</v>
+        <v>48</v>
       </c>
       <c r="N208" t="s">
         <v>14</v>
@@ -14989,25 +15058,25 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>254</v>
+        <v>1527</v>
       </c>
       <c r="B209" t="s">
-        <v>771</v>
+        <v>1545</v>
       </c>
       <c r="C209" t="s">
-        <v>771</v>
+        <v>1163</v>
       </c>
       <c r="D209" t="s">
-        <v>279</v>
+        <v>1546</v>
       </c>
       <c r="E209" t="s">
-        <v>893</v>
+        <v>1547</v>
       </c>
       <c r="F209" t="s">
         <v>47</v>
       </c>
       <c r="G209" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H209" t="s">
         <v>13</v>
@@ -15016,16 +15085,16 @@
         <v>140</v>
       </c>
       <c r="J209" t="s">
-        <v>316</v>
+        <v>109</v>
       </c>
       <c r="K209" t="s">
-        <v>139</v>
+        <v>54</v>
       </c>
       <c r="L209" t="s">
-        <v>278</v>
+        <v>178</v>
       </c>
       <c r="M209" t="s">
-        <v>828</v>
+        <v>48</v>
       </c>
       <c r="N209" t="s">
         <v>14</v>
@@ -15039,22 +15108,22 @@
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>303</v>
+        <v>604</v>
       </c>
       <c r="B210" t="s">
-        <v>328</v>
+        <v>644</v>
       </c>
       <c r="C210" t="s">
-        <v>1170</v>
+        <v>1196</v>
       </c>
       <c r="D210" t="s">
-        <v>329</v>
+        <v>645</v>
       </c>
       <c r="E210" t="s">
-        <v>970</v>
+        <v>994</v>
       </c>
       <c r="F210" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G210" t="s">
         <v>32</v>
@@ -15065,14 +15134,8 @@
       <c r="I210" t="s">
         <v>140</v>
       </c>
-      <c r="J210" t="s">
-        <v>484</v>
-      </c>
-      <c r="K210" t="s">
-        <v>132</v>
-      </c>
       <c r="L210" t="s">
-        <v>330</v>
+        <v>178</v>
       </c>
       <c r="M210" t="s">
         <v>48</v>
@@ -15089,19 +15152,19 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>556</v>
+        <v>295</v>
       </c>
       <c r="B211" t="s">
-        <v>802</v>
+        <v>313</v>
       </c>
       <c r="C211" t="s">
-        <v>1182</v>
+        <v>1162</v>
       </c>
       <c r="D211" t="s">
-        <v>560</v>
+        <v>314</v>
       </c>
       <c r="E211" t="s">
-        <v>982</v>
+        <v>1035</v>
       </c>
       <c r="F211" t="s">
         <v>78</v>
@@ -15113,16 +15176,16 @@
         <v>13</v>
       </c>
       <c r="I211" t="s">
-        <v>140</v>
+        <v>315</v>
       </c>
       <c r="J211" t="s">
         <v>484</v>
       </c>
       <c r="K211" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L211" t="s">
-        <v>573</v>
+        <v>186</v>
       </c>
       <c r="M211" t="s">
         <v>829</v>
@@ -15139,22 +15202,22 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="B212" t="s">
-        <v>311</v>
+        <v>771</v>
       </c>
       <c r="C212" t="s">
-        <v>1164</v>
+        <v>771</v>
       </c>
       <c r="D212" t="s">
-        <v>792</v>
+        <v>279</v>
       </c>
       <c r="E212" t="s">
-        <v>967</v>
+        <v>893</v>
       </c>
       <c r="F212" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G212" t="s">
         <v>51</v>
@@ -15163,19 +15226,19 @@
         <v>13</v>
       </c>
       <c r="I212" t="s">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="J212" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K212" t="s">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="L212" t="s">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="M212" t="s">
-        <v>48</v>
+        <v>828</v>
       </c>
       <c r="N212" t="s">
         <v>14</v>
@@ -15189,40 +15252,40 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B213" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C213" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="D213" t="s">
-        <v>794</v>
+        <v>329</v>
       </c>
       <c r="E213" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="F213" t="s">
         <v>78</v>
       </c>
       <c r="G213" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H213" t="s">
         <v>13</v>
       </c>
       <c r="I213" t="s">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="J213" t="s">
-        <v>312</v>
+        <v>484</v>
       </c>
       <c r="K213" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="L213" t="s">
-        <v>97</v>
+        <v>330</v>
       </c>
       <c r="M213" t="s">
         <v>48</v>
@@ -15239,19 +15302,19 @@
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>1469</v>
+        <v>1532</v>
       </c>
       <c r="B214" t="s">
-        <v>1473</v>
+        <v>1533</v>
       </c>
       <c r="C214" t="s">
-        <v>1474</v>
+        <v>1534</v>
       </c>
       <c r="D214" t="s">
-        <v>792</v>
+        <v>314</v>
       </c>
       <c r="E214" t="s">
-        <v>967</v>
+        <v>1535</v>
       </c>
       <c r="F214" t="s">
         <v>78</v>
@@ -15263,13 +15326,10 @@
         <v>13</v>
       </c>
       <c r="I214" t="s">
-        <v>325</v>
+        <v>140</v>
       </c>
       <c r="J214" t="s">
-        <v>205</v>
-      </c>
-      <c r="K214" t="s">
-        <v>75</v>
+        <v>484</v>
       </c>
       <c r="L214" t="s">
         <v>97</v>
@@ -15289,19 +15349,19 @@
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="B215" t="s">
-        <v>597</v>
+        <v>802</v>
       </c>
       <c r="C215" t="s">
-        <v>1167</v>
+        <v>1182</v>
       </c>
       <c r="D215" t="s">
-        <v>792</v>
+        <v>560</v>
       </c>
       <c r="E215" t="s">
-        <v>967</v>
+        <v>982</v>
       </c>
       <c r="F215" t="s">
         <v>78</v>
@@ -15313,19 +15373,19 @@
         <v>13</v>
       </c>
       <c r="I215" t="s">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="J215" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="K215" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L215" t="s">
-        <v>97</v>
+        <v>573</v>
       </c>
       <c r="M215" t="s">
-        <v>48</v>
+        <v>829</v>
       </c>
       <c r="N215" t="s">
         <v>14</v>
@@ -15339,22 +15399,22 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>713</v>
+        <v>294</v>
       </c>
       <c r="B216" t="s">
-        <v>736</v>
+        <v>311</v>
       </c>
       <c r="C216" t="s">
-        <v>1211</v>
+        <v>1164</v>
       </c>
       <c r="D216" t="s">
-        <v>741</v>
+        <v>792</v>
       </c>
       <c r="E216" t="s">
-        <v>1013</v>
+        <v>967</v>
       </c>
       <c r="F216" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G216" t="s">
         <v>51</v>
@@ -15366,13 +15426,13 @@
         <v>267</v>
       </c>
       <c r="J216" t="s">
-        <v>205</v>
+        <v>312</v>
       </c>
       <c r="K216" t="s">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="L216" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M216" t="s">
         <v>48</v>
@@ -15389,19 +15449,19 @@
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B217" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C217" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="D217" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="E217" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F217" t="s">
         <v>78</v>
@@ -15416,7 +15476,7 @@
         <v>267</v>
       </c>
       <c r="J217" t="s">
-        <v>205</v>
+        <v>312</v>
       </c>
       <c r="K217" t="s">
         <v>75</v>
@@ -15439,19 +15499,19 @@
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>302</v>
+        <v>1469</v>
       </c>
       <c r="B218" t="s">
-        <v>327</v>
+        <v>1473</v>
       </c>
       <c r="C218" t="s">
-        <v>1169</v>
+        <v>1474</v>
       </c>
       <c r="D218" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E218" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F218" t="s">
         <v>78</v>
@@ -15463,7 +15523,7 @@
         <v>13</v>
       </c>
       <c r="I218" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="J218" t="s">
         <v>205</v>
@@ -15489,25 +15549,25 @@
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>714</v>
+        <v>590</v>
       </c>
       <c r="B219" t="s">
-        <v>735</v>
+        <v>597</v>
       </c>
       <c r="C219" t="s">
-        <v>1212</v>
+        <v>1167</v>
       </c>
       <c r="D219" t="s">
-        <v>742</v>
+        <v>792</v>
       </c>
       <c r="E219" t="s">
-        <v>1014</v>
+        <v>967</v>
       </c>
       <c r="F219" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G219" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H219" t="s">
         <v>13</v>
@@ -15516,13 +15576,13 @@
         <v>267</v>
       </c>
       <c r="J219" t="s">
-        <v>276</v>
+        <v>489</v>
       </c>
       <c r="K219" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L219" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="M219" t="s">
         <v>48</v>
@@ -15539,25 +15599,25 @@
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B220" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C220" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D220" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E220" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F220" t="s">
         <v>47</v>
       </c>
       <c r="G220" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H220" t="s">
         <v>13</v>
@@ -15566,10 +15626,10 @@
         <v>267</v>
       </c>
       <c r="J220" t="s">
-        <v>276</v>
+        <v>205</v>
       </c>
       <c r="K220" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="L220" t="s">
         <v>178</v>
@@ -15589,25 +15649,25 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>716</v>
+        <v>301</v>
       </c>
       <c r="B221" t="s">
-        <v>733</v>
+        <v>326</v>
       </c>
       <c r="C221" t="s">
-        <v>1214</v>
+        <v>1168</v>
       </c>
       <c r="D221" t="s">
-        <v>742</v>
+        <v>792</v>
       </c>
       <c r="E221" t="s">
-        <v>1014</v>
+        <v>967</v>
       </c>
       <c r="F221" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G221" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H221" t="s">
         <v>13</v>
@@ -15616,13 +15676,13 @@
         <v>267</v>
       </c>
       <c r="J221" t="s">
-        <v>276</v>
+        <v>205</v>
       </c>
       <c r="K221" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L221" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="M221" t="s">
         <v>48</v>
@@ -15639,25 +15699,25 @@
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>717</v>
+        <v>302</v>
       </c>
       <c r="B222" t="s">
-        <v>732</v>
+        <v>327</v>
       </c>
       <c r="C222" t="s">
-        <v>1215</v>
+        <v>1169</v>
       </c>
       <c r="D222" t="s">
-        <v>742</v>
+        <v>794</v>
       </c>
       <c r="E222" t="s">
-        <v>1014</v>
+        <v>968</v>
       </c>
       <c r="F222" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G222" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H222" t="s">
         <v>13</v>
@@ -15666,13 +15726,13 @@
         <v>267</v>
       </c>
       <c r="J222" t="s">
-        <v>276</v>
+        <v>205</v>
       </c>
       <c r="K222" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="L222" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="M222" t="s">
         <v>48</v>
@@ -15689,13 +15749,13 @@
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="B223" t="s">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="C223" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="D223" t="s">
         <v>742</v>
@@ -15739,19 +15799,19 @@
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>578</v>
+        <v>715</v>
       </c>
       <c r="B224" t="s">
-        <v>584</v>
+        <v>734</v>
       </c>
       <c r="C224" t="s">
-        <v>1187</v>
+        <v>1213</v>
       </c>
       <c r="D224" t="s">
-        <v>592</v>
+        <v>742</v>
       </c>
       <c r="E224" t="s">
-        <v>985</v>
+        <v>1014</v>
       </c>
       <c r="F224" t="s">
         <v>47</v>
@@ -15760,16 +15820,16 @@
         <v>32</v>
       </c>
       <c r="H224" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I224" t="s">
-        <v>585</v>
+        <v>267</v>
       </c>
       <c r="J224" t="s">
         <v>276</v>
       </c>
       <c r="K224" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L224" t="s">
         <v>178</v>
@@ -15789,19 +15849,19 @@
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>1272</v>
+        <v>716</v>
       </c>
       <c r="B225" t="s">
-        <v>1296</v>
+        <v>733</v>
       </c>
       <c r="C225" t="s">
-        <v>1297</v>
+        <v>1214</v>
       </c>
       <c r="D225" t="s">
-        <v>1241</v>
+        <v>742</v>
       </c>
       <c r="E225" t="s">
-        <v>1243</v>
+        <v>1014</v>
       </c>
       <c r="F225" t="s">
         <v>47</v>
@@ -15810,22 +15870,22 @@
         <v>32</v>
       </c>
       <c r="H225" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I225" t="s">
-        <v>445</v>
+        <v>267</v>
       </c>
       <c r="J225" t="s">
         <v>276</v>
       </c>
       <c r="K225" t="s">
-        <v>414</v>
+        <v>54</v>
       </c>
       <c r="L225" t="s">
         <v>178</v>
       </c>
       <c r="M225" t="s">
-        <v>829</v>
+        <v>48</v>
       </c>
       <c r="N225" t="s">
         <v>14</v>
@@ -15839,19 +15899,19 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>1273</v>
+        <v>717</v>
       </c>
       <c r="B226" t="s">
-        <v>1298</v>
+        <v>732</v>
       </c>
       <c r="C226" t="s">
-        <v>1299</v>
+        <v>1215</v>
       </c>
       <c r="D226" t="s">
-        <v>1300</v>
+        <v>742</v>
       </c>
       <c r="E226" t="s">
-        <v>1300</v>
+        <v>1014</v>
       </c>
       <c r="F226" t="s">
         <v>47</v>
@@ -15863,7 +15923,7 @@
         <v>13</v>
       </c>
       <c r="I226" t="s">
-        <v>140</v>
+        <v>267</v>
       </c>
       <c r="J226" t="s">
         <v>276</v>
@@ -15889,35 +15949,38 @@
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>613</v>
+        <v>725</v>
       </c>
       <c r="B227" t="s">
-        <v>656</v>
+        <v>726</v>
       </c>
       <c r="C227" t="s">
-        <v>1199</v>
+        <v>1216</v>
       </c>
       <c r="D227" t="s">
-        <v>813</v>
+        <v>742</v>
       </c>
       <c r="E227" t="s">
-        <v>1001</v>
+        <v>1014</v>
       </c>
       <c r="F227" t="s">
         <v>47</v>
       </c>
       <c r="G227" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="H227" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I227" t="s">
-        <v>142</v>
+        <v>267</v>
       </c>
       <c r="J227" t="s">
         <v>276</v>
       </c>
+      <c r="K227" t="s">
+        <v>54</v>
+      </c>
       <c r="L227" t="s">
         <v>178</v>
       </c>
@@ -15936,19 +15999,19 @@
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>662</v>
+        <v>578</v>
       </c>
       <c r="B228" t="s">
-        <v>680</v>
+        <v>584</v>
       </c>
       <c r="C228" t="s">
-        <v>1202</v>
+        <v>1187</v>
       </c>
       <c r="D228" t="s">
-        <v>681</v>
+        <v>592</v>
       </c>
       <c r="E228" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="F228" t="s">
         <v>47</v>
@@ -15957,16 +16020,19 @@
         <v>32</v>
       </c>
       <c r="H228" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I228" t="s">
-        <v>140</v>
+        <v>585</v>
       </c>
       <c r="J228" t="s">
         <v>276</v>
       </c>
+      <c r="K228" t="s">
+        <v>75</v>
+      </c>
       <c r="L228" t="s">
-        <v>340</v>
+        <v>178</v>
       </c>
       <c r="M228" t="s">
         <v>48</v>
@@ -15983,13 +16049,13 @@
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>1232</v>
+        <v>1272</v>
       </c>
       <c r="B229" t="s">
-        <v>1240</v>
+        <v>1296</v>
       </c>
       <c r="C229" t="s">
-        <v>1242</v>
+        <v>1297</v>
       </c>
       <c r="D229" t="s">
         <v>1241</v>
@@ -16004,22 +16070,22 @@
         <v>32</v>
       </c>
       <c r="H229" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I229" t="s">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="J229" t="s">
         <v>276</v>
       </c>
       <c r="K229" t="s">
-        <v>54</v>
+        <v>414</v>
       </c>
       <c r="L229" t="s">
         <v>178</v>
       </c>
       <c r="M229" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N229" t="s">
         <v>14</v>
@@ -16033,19 +16099,19 @@
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>1233</v>
+        <v>1273</v>
       </c>
       <c r="B230" t="s">
-        <v>1244</v>
+        <v>1298</v>
       </c>
       <c r="C230" t="s">
-        <v>1245</v>
+        <v>1299</v>
       </c>
       <c r="D230" t="s">
-        <v>1241</v>
+        <v>1300</v>
       </c>
       <c r="E230" t="s">
-        <v>1243</v>
+        <v>1300</v>
       </c>
       <c r="F230" t="s">
         <v>47</v>
@@ -16060,10 +16126,10 @@
         <v>140</v>
       </c>
       <c r="J230" t="s">
-        <v>583</v>
+        <v>276</v>
       </c>
       <c r="K230" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="L230" t="s">
         <v>178</v>
@@ -16083,28 +16149,34 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>1452</v>
+        <v>613</v>
       </c>
       <c r="B231" t="s">
-        <v>1457</v>
+        <v>656</v>
       </c>
       <c r="C231" t="s">
-        <v>1460</v>
+        <v>1199</v>
+      </c>
+      <c r="D231" t="s">
+        <v>813</v>
+      </c>
+      <c r="E231" t="s">
+        <v>1001</v>
       </c>
       <c r="F231" t="s">
         <v>47</v>
       </c>
       <c r="G231" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="H231" t="s">
         <v>31</v>
       </c>
       <c r="I231" t="s">
-        <v>445</v>
-      </c>
-      <c r="K231" t="s">
-        <v>54</v>
+        <v>142</v>
+      </c>
+      <c r="J231" t="s">
+        <v>276</v>
       </c>
       <c r="L231" t="s">
         <v>178</v>
@@ -16124,13 +16196,19 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>1453</v>
+        <v>662</v>
       </c>
       <c r="B232" t="s">
-        <v>1458</v>
+        <v>680</v>
       </c>
       <c r="C232" t="s">
-        <v>1461</v>
+        <v>1202</v>
+      </c>
+      <c r="D232" t="s">
+        <v>681</v>
+      </c>
+      <c r="E232" t="s">
+        <v>1004</v>
       </c>
       <c r="F232" t="s">
         <v>47</v>
@@ -16139,16 +16217,16 @@
         <v>32</v>
       </c>
       <c r="H232" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I232" t="s">
-        <v>445</v>
-      </c>
-      <c r="K232" t="s">
-        <v>54</v>
+        <v>140</v>
+      </c>
+      <c r="J232" t="s">
+        <v>276</v>
       </c>
       <c r="L232" t="s">
-        <v>178</v>
+        <v>340</v>
       </c>
       <c r="M232" t="s">
         <v>48</v>
@@ -16165,13 +16243,19 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>1454</v>
+        <v>1232</v>
       </c>
       <c r="B233" t="s">
-        <v>1459</v>
+        <v>1240</v>
       </c>
       <c r="C233" t="s">
-        <v>1462</v>
+        <v>1242</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E233" t="s">
+        <v>1243</v>
       </c>
       <c r="F233" t="s">
         <v>47</v>
@@ -16180,10 +16264,13 @@
         <v>32</v>
       </c>
       <c r="H233" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I233" t="s">
-        <v>445</v>
+        <v>140</v>
+      </c>
+      <c r="J233" t="s">
+        <v>276</v>
       </c>
       <c r="K233" t="s">
         <v>54</v>
@@ -16192,7 +16279,7 @@
         <v>178</v>
       </c>
       <c r="M233" t="s">
-        <v>48</v>
+        <v>828</v>
       </c>
       <c r="N233" t="s">
         <v>14</v>
@@ -16206,19 +16293,19 @@
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>1455</v>
+        <v>1233</v>
       </c>
       <c r="B234" t="s">
-        <v>1463</v>
+        <v>1244</v>
       </c>
       <c r="C234" t="s">
-        <v>1464</v>
+        <v>1245</v>
       </c>
       <c r="D234" t="s">
-        <v>1465</v>
+        <v>1241</v>
       </c>
       <c r="E234" t="s">
-        <v>1466</v>
+        <v>1243</v>
       </c>
       <c r="F234" t="s">
         <v>47</v>
@@ -16227,13 +16314,13 @@
         <v>32</v>
       </c>
       <c r="H234" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I234" t="s">
-        <v>445</v>
+        <v>140</v>
       </c>
       <c r="J234" t="s">
-        <v>276</v>
+        <v>583</v>
       </c>
       <c r="K234" t="s">
         <v>54</v>
@@ -16256,22 +16343,16 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>1258</v>
+        <v>1452</v>
       </c>
       <c r="B235" t="s">
-        <v>1261</v>
+        <v>1457</v>
       </c>
       <c r="C235" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D235" t="s">
-        <v>681</v>
-      </c>
-      <c r="E235" t="s">
-        <v>1004</v>
+        <v>1460</v>
       </c>
       <c r="F235" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G235" t="s">
         <v>32</v>
@@ -16280,13 +16361,13 @@
         <v>31</v>
       </c>
       <c r="I235" t="s">
-        <v>1266</v>
-      </c>
-      <c r="J235" t="s">
-        <v>276</v>
+        <v>445</v>
+      </c>
+      <c r="K235" t="s">
+        <v>54</v>
       </c>
       <c r="L235" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="M235" t="s">
         <v>48</v>
@@ -16303,34 +16384,25 @@
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>1326</v>
+        <v>1453</v>
       </c>
       <c r="B236" t="s">
-        <v>1350</v>
+        <v>1458</v>
       </c>
       <c r="C236" t="s">
-        <v>1351</v>
-      </c>
-      <c r="D236" t="s">
-        <v>1354</v>
-      </c>
-      <c r="E236" t="s">
-        <v>1355</v>
+        <v>1461</v>
       </c>
       <c r="F236" t="s">
         <v>47</v>
       </c>
       <c r="G236" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="H236" t="s">
         <v>31</v>
       </c>
       <c r="I236" t="s">
-        <v>107</v>
-      </c>
-      <c r="J236" t="s">
-        <v>276</v>
+        <v>445</v>
       </c>
       <c r="K236" t="s">
         <v>54</v>
@@ -16339,7 +16411,7 @@
         <v>178</v>
       </c>
       <c r="M236" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N236" t="s">
         <v>14</v>
@@ -16353,19 +16425,13 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>255</v>
+        <v>1454</v>
       </c>
       <c r="B237" t="s">
-        <v>280</v>
+        <v>1459</v>
       </c>
       <c r="C237" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D237" t="s">
-        <v>281</v>
-      </c>
-      <c r="E237" t="s">
-        <v>894</v>
+        <v>1462</v>
       </c>
       <c r="F237" t="s">
         <v>47</v>
@@ -16374,19 +16440,19 @@
         <v>32</v>
       </c>
       <c r="H237" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I237" t="s">
-        <v>140</v>
-      </c>
-      <c r="J237" t="s">
-        <v>109</v>
+        <v>445</v>
+      </c>
+      <c r="K237" t="s">
+        <v>54</v>
       </c>
       <c r="L237" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="M237" t="s">
-        <v>829</v>
+        <v>48</v>
       </c>
       <c r="N237" t="s">
         <v>14</v>
@@ -16400,13 +16466,19 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>1278</v>
+        <v>1455</v>
       </c>
       <c r="B238" t="s">
-        <v>1310</v>
+        <v>1463</v>
       </c>
       <c r="C238" t="s">
-        <v>1311</v>
+        <v>1464</v>
+      </c>
+      <c r="D238" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E238" t="s">
+        <v>1466</v>
       </c>
       <c r="F238" t="s">
         <v>47</v>
@@ -16415,16 +16487,19 @@
         <v>32</v>
       </c>
       <c r="H238" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I238" t="s">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="J238" t="s">
-        <v>109</v>
+        <v>276</v>
+      </c>
+      <c r="K238" t="s">
+        <v>54</v>
       </c>
       <c r="L238" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="M238" t="s">
         <v>48</v>
@@ -16441,37 +16516,34 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>300</v>
+        <v>1258</v>
       </c>
       <c r="B239" t="s">
-        <v>324</v>
+        <v>1261</v>
       </c>
       <c r="C239" t="s">
-        <v>1166</v>
+        <v>1263</v>
       </c>
       <c r="D239" t="s">
-        <v>795</v>
+        <v>681</v>
       </c>
       <c r="E239" t="s">
-        <v>969</v>
+        <v>1004</v>
       </c>
       <c r="F239" t="s">
         <v>78</v>
       </c>
       <c r="G239" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H239" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I239" t="s">
-        <v>325</v>
+        <v>1266</v>
       </c>
       <c r="J239" t="s">
-        <v>205</v>
-      </c>
-      <c r="K239" t="s">
-        <v>75</v>
+        <v>276</v>
       </c>
       <c r="L239" t="s">
         <v>97</v>
@@ -16491,43 +16563,43 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>1470</v>
+        <v>1326</v>
       </c>
       <c r="B240" t="s">
-        <v>1471</v>
+        <v>1350</v>
       </c>
       <c r="C240" t="s">
-        <v>1472</v>
+        <v>1351</v>
       </c>
       <c r="D240" t="s">
-        <v>795</v>
+        <v>1354</v>
       </c>
       <c r="E240" t="s">
-        <v>969</v>
+        <v>1355</v>
       </c>
       <c r="F240" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G240" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="H240" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I240" t="s">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="J240" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="K240" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L240" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="M240" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N240" t="s">
         <v>14</v>
@@ -16541,43 +16613,40 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>664</v>
+        <v>255</v>
       </c>
       <c r="B241" t="s">
-        <v>684</v>
+        <v>280</v>
       </c>
       <c r="C241" t="s">
-        <v>1203</v>
+        <v>1086</v>
       </c>
       <c r="D241" t="s">
-        <v>685</v>
+        <v>281</v>
       </c>
       <c r="E241" t="s">
-        <v>1006</v>
+        <v>894</v>
       </c>
       <c r="F241" t="s">
         <v>47</v>
       </c>
       <c r="G241" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H241" t="s">
         <v>13</v>
       </c>
       <c r="I241" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="J241" t="s">
-        <v>276</v>
-      </c>
-      <c r="K241" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="L241" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M241" t="s">
-        <v>48</v>
+        <v>829</v>
       </c>
       <c r="N241" t="s">
         <v>14</v>
@@ -16591,19 +16660,13 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>246</v>
+        <v>1278</v>
       </c>
       <c r="B242" t="s">
-        <v>256</v>
+        <v>1310</v>
       </c>
       <c r="C242" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D242" t="s">
-        <v>257</v>
-      </c>
-      <c r="E242" t="s">
-        <v>1023</v>
+        <v>1311</v>
       </c>
       <c r="F242" t="s">
         <v>47</v>
@@ -16618,16 +16681,13 @@
         <v>140</v>
       </c>
       <c r="J242" t="s">
-        <v>205</v>
-      </c>
-      <c r="K242" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="L242" t="s">
-        <v>264</v>
+        <v>95</v>
       </c>
       <c r="M242" t="s">
-        <v>829</v>
+        <v>48</v>
       </c>
       <c r="N242" t="s">
         <v>14</v>
@@ -16641,37 +16701,40 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>461</v>
+        <v>300</v>
       </c>
       <c r="B243" t="s">
-        <v>800</v>
+        <v>324</v>
       </c>
       <c r="C243" t="s">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="D243" t="s">
-        <v>469</v>
+        <v>795</v>
       </c>
       <c r="E243" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="F243" t="s">
         <v>78</v>
       </c>
       <c r="G243" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H243" t="s">
         <v>13</v>
       </c>
       <c r="I243" t="s">
-        <v>140</v>
+        <v>325</v>
       </c>
       <c r="J243" t="s">
-        <v>276</v>
+        <v>205</v>
+      </c>
+      <c r="K243" t="s">
+        <v>75</v>
       </c>
       <c r="L243" t="s">
-        <v>492</v>
+        <v>97</v>
       </c>
       <c r="M243" t="s">
         <v>48</v>
@@ -16688,40 +16751,40 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>251</v>
+        <v>1470</v>
       </c>
       <c r="B244" t="s">
-        <v>272</v>
+        <v>1471</v>
       </c>
       <c r="C244" t="s">
-        <v>1083</v>
+        <v>1472</v>
       </c>
       <c r="D244" t="s">
-        <v>273</v>
+        <v>795</v>
       </c>
       <c r="E244" t="s">
-        <v>1024</v>
+        <v>969</v>
       </c>
       <c r="F244" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G244" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H244" t="s">
         <v>13</v>
       </c>
       <c r="I244" t="s">
-        <v>140</v>
+        <v>267</v>
       </c>
       <c r="J244" t="s">
-        <v>274</v>
+        <v>205</v>
       </c>
       <c r="K244" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L244" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M244" t="s">
         <v>48</v>
@@ -16738,37 +16801,40 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>406</v>
+        <v>664</v>
       </c>
       <c r="B245" t="s">
-        <v>798</v>
+        <v>684</v>
       </c>
       <c r="C245" t="s">
-        <v>1175</v>
+        <v>1203</v>
       </c>
       <c r="D245" t="s">
-        <v>799</v>
+        <v>685</v>
       </c>
       <c r="E245" t="s">
-        <v>974</v>
+        <v>1006</v>
       </c>
       <c r="F245" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G245" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H245" t="s">
         <v>13</v>
       </c>
       <c r="I245" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="J245" t="s">
-        <v>489</v>
+        <v>276</v>
+      </c>
+      <c r="K245" t="s">
+        <v>75</v>
       </c>
       <c r="L245" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="M245" t="s">
         <v>48</v>
@@ -16785,22 +16851,22 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>588</v>
+        <v>246</v>
       </c>
       <c r="B246" t="s">
-        <v>594</v>
+        <v>256</v>
       </c>
       <c r="C246" t="s">
-        <v>1189</v>
+        <v>1080</v>
       </c>
       <c r="D246" t="s">
-        <v>595</v>
+        <v>257</v>
       </c>
       <c r="E246" t="s">
-        <v>987</v>
+        <v>1023</v>
       </c>
       <c r="F246" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G246" t="s">
         <v>32</v>
@@ -16809,19 +16875,19 @@
         <v>13</v>
       </c>
       <c r="I246" t="s">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="J246" t="s">
-        <v>596</v>
+        <v>205</v>
       </c>
       <c r="K246" t="s">
         <v>53</v>
       </c>
       <c r="L246" t="s">
-        <v>492</v>
+        <v>264</v>
       </c>
       <c r="M246" t="s">
-        <v>48</v>
+        <v>829</v>
       </c>
       <c r="N246" t="s">
         <v>14</v>
@@ -16835,40 +16901,37 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>668</v>
+        <v>461</v>
       </c>
       <c r="B247" t="s">
-        <v>688</v>
+        <v>800</v>
       </c>
       <c r="C247" t="s">
-        <v>1205</v>
+        <v>1177</v>
       </c>
       <c r="D247" t="s">
-        <v>689</v>
+        <v>469</v>
       </c>
       <c r="E247" t="s">
-        <v>1008</v>
+        <v>977</v>
       </c>
       <c r="F247" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G247" t="s">
         <v>32</v>
       </c>
       <c r="H247" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I247" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J247" t="s">
         <v>276</v>
       </c>
-      <c r="K247" t="s">
-        <v>414</v>
-      </c>
       <c r="L247" t="s">
-        <v>178</v>
+        <v>492</v>
       </c>
       <c r="M247" t="s">
         <v>48</v>
@@ -16885,19 +16948,19 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>497</v>
+        <v>251</v>
       </c>
       <c r="B248" t="s">
-        <v>503</v>
+        <v>272</v>
       </c>
       <c r="C248" t="s">
-        <v>1117</v>
+        <v>1083</v>
       </c>
       <c r="D248" t="s">
-        <v>504</v>
+        <v>273</v>
       </c>
       <c r="E248" t="s">
-        <v>921</v>
+        <v>1024</v>
       </c>
       <c r="F248" t="s">
         <v>47</v>
@@ -16906,19 +16969,19 @@
         <v>32</v>
       </c>
       <c r="H248" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I248" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J248" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K248" t="s">
         <v>54</v>
       </c>
       <c r="L248" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M248" t="s">
         <v>48</v>
@@ -16935,34 +16998,37 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>1456</v>
+        <v>406</v>
       </c>
       <c r="B249" t="s">
-        <v>1467</v>
+        <v>798</v>
       </c>
       <c r="C249" t="s">
-        <v>1468</v>
+        <v>1175</v>
+      </c>
+      <c r="D249" t="s">
+        <v>799</v>
+      </c>
+      <c r="E249" t="s">
+        <v>974</v>
       </c>
       <c r="F249" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G249" t="s">
         <v>32</v>
       </c>
       <c r="H249" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I249" t="s">
-        <v>445</v>
+        <v>140</v>
       </c>
       <c r="J249" t="s">
-        <v>276</v>
-      </c>
-      <c r="K249" t="s">
-        <v>54</v>
+        <v>489</v>
       </c>
       <c r="L249" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M249" t="s">
         <v>48</v>
@@ -16979,25 +17045,25 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>459</v>
+        <v>588</v>
       </c>
       <c r="B250" t="s">
-        <v>466</v>
+        <v>594</v>
       </c>
       <c r="C250" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="D250" t="s">
-        <v>467</v>
+        <v>595</v>
       </c>
       <c r="E250" t="s">
-        <v>976</v>
+        <v>987</v>
       </c>
       <c r="F250" t="s">
         <v>78</v>
       </c>
       <c r="G250" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H250" t="s">
         <v>13</v>
@@ -17006,13 +17072,13 @@
         <v>267</v>
       </c>
       <c r="J250" t="s">
-        <v>305</v>
+        <v>596</v>
       </c>
       <c r="K250" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="L250" t="s">
-        <v>95</v>
+        <v>492</v>
       </c>
       <c r="M250" t="s">
         <v>48</v>
@@ -17029,40 +17095,40 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>337</v>
+        <v>668</v>
       </c>
       <c r="B251" t="s">
-        <v>797</v>
+        <v>688</v>
       </c>
       <c r="C251" t="s">
-        <v>1172</v>
+        <v>1205</v>
       </c>
       <c r="D251" t="s">
-        <v>350</v>
+        <v>689</v>
       </c>
       <c r="E251" t="s">
-        <v>971</v>
+        <v>1008</v>
       </c>
       <c r="F251" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G251" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H251" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I251" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J251" t="s">
-        <v>519</v>
+        <v>276</v>
       </c>
       <c r="K251" t="s">
-        <v>75</v>
+        <v>414</v>
       </c>
       <c r="L251" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M251" t="s">
         <v>48</v>
@@ -17079,37 +17145,40 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>555</v>
+        <v>497</v>
       </c>
       <c r="B252" t="s">
-        <v>559</v>
+        <v>503</v>
       </c>
       <c r="C252" t="s">
-        <v>1181</v>
+        <v>1117</v>
       </c>
       <c r="D252" t="s">
-        <v>593</v>
+        <v>504</v>
       </c>
       <c r="E252" t="s">
-        <v>981</v>
+        <v>921</v>
       </c>
       <c r="F252" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G252" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H252" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I252" t="s">
-        <v>108</v>
+        <v>142</v>
+      </c>
+      <c r="J252" t="s">
+        <v>276</v>
       </c>
       <c r="K252" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L252" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="M252" t="s">
         <v>48</v>
@@ -17126,34 +17195,28 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>434</v>
+        <v>1456</v>
       </c>
       <c r="B253" t="s">
-        <v>447</v>
+        <v>1467</v>
       </c>
       <c r="C253" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D253" t="s">
-        <v>448</v>
-      </c>
-      <c r="E253" t="s">
-        <v>912</v>
+        <v>1468</v>
       </c>
       <c r="F253" t="s">
         <v>47</v>
       </c>
       <c r="G253" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H253" t="s">
         <v>31</v>
       </c>
       <c r="I253" t="s">
-        <v>107</v>
+        <v>445</v>
       </c>
       <c r="J253" t="s">
-        <v>521</v>
+        <v>276</v>
       </c>
       <c r="K253" t="s">
         <v>54</v>
@@ -17162,7 +17225,7 @@
         <v>178</v>
       </c>
       <c r="M253" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N253" t="s">
         <v>14</v>
@@ -17176,40 +17239,40 @@
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="B254" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C254" t="s">
-        <v>1107</v>
+        <v>1176</v>
       </c>
       <c r="D254" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="E254" t="s">
-        <v>914</v>
+        <v>976</v>
       </c>
       <c r="F254" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G254" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H254" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I254" t="s">
-        <v>142</v>
+        <v>267</v>
       </c>
       <c r="J254" t="s">
-        <v>523</v>
+        <v>305</v>
       </c>
       <c r="K254" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L254" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M254" t="s">
         <v>48</v>
@@ -17226,19 +17289,19 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>589</v>
+        <v>337</v>
       </c>
       <c r="B255" t="s">
-        <v>598</v>
+        <v>797</v>
       </c>
       <c r="C255" t="s">
-        <v>1190</v>
+        <v>1172</v>
       </c>
       <c r="D255" t="s">
-        <v>599</v>
+        <v>350</v>
       </c>
       <c r="E255" t="s">
-        <v>988</v>
+        <v>971</v>
       </c>
       <c r="F255" t="s">
         <v>78</v>
@@ -17250,10 +17313,10 @@
         <v>13</v>
       </c>
       <c r="I255" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="J255" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="K255" t="s">
         <v>75</v>
@@ -17262,7 +17325,7 @@
         <v>186</v>
       </c>
       <c r="M255" t="s">
-        <v>828</v>
+        <v>48</v>
       </c>
       <c r="N255" t="s">
         <v>14</v>
@@ -17276,37 +17339,37 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>1237</v>
+        <v>555</v>
       </c>
       <c r="B256" t="s">
-        <v>1253</v>
+        <v>559</v>
       </c>
       <c r="C256" t="s">
-        <v>1254</v>
+        <v>1181</v>
       </c>
       <c r="D256" t="s">
-        <v>455</v>
+        <v>593</v>
       </c>
       <c r="E256" t="s">
-        <v>914</v>
+        <v>981</v>
       </c>
       <c r="F256" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G256" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H256" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I256" t="s">
-        <v>142</v>
-      </c>
-      <c r="J256" t="s">
-        <v>1255</v>
+        <v>108</v>
+      </c>
+      <c r="K256" t="s">
+        <v>75</v>
       </c>
       <c r="L256" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="M256" t="s">
         <v>48</v>
@@ -17323,28 +17386,34 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>1324</v>
+        <v>434</v>
       </c>
       <c r="B257" t="s">
-        <v>1346</v>
+        <v>447</v>
       </c>
       <c r="C257" t="s">
-        <v>1347</v>
+        <v>1105</v>
+      </c>
+      <c r="D257" t="s">
+        <v>448</v>
+      </c>
+      <c r="E257" t="s">
+        <v>912</v>
       </c>
       <c r="F257" t="s">
         <v>47</v>
       </c>
       <c r="G257" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H257" t="s">
         <v>31</v>
       </c>
       <c r="I257" t="s">
-        <v>1266</v>
+        <v>107</v>
       </c>
       <c r="J257" t="s">
-        <v>1255</v>
+        <v>521</v>
       </c>
       <c r="K257" t="s">
         <v>54</v>
@@ -17353,7 +17422,7 @@
         <v>178</v>
       </c>
       <c r="M257" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N257" t="s">
         <v>14</v>
@@ -17367,13 +17436,19 @@
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>608</v>
+        <v>437</v>
       </c>
       <c r="B258" t="s">
-        <v>654</v>
+        <v>454</v>
       </c>
       <c r="C258" t="s">
-        <v>1198</v>
+        <v>1107</v>
+      </c>
+      <c r="D258" t="s">
+        <v>455</v>
+      </c>
+      <c r="E258" t="s">
+        <v>914</v>
       </c>
       <c r="F258" t="s">
         <v>47</v>
@@ -17382,13 +17457,13 @@
         <v>32</v>
       </c>
       <c r="H258" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I258" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J258" t="s">
-        <v>200</v>
+        <v>523</v>
       </c>
       <c r="K258" t="s">
         <v>54</v>
@@ -17397,7 +17472,7 @@
         <v>178</v>
       </c>
       <c r="M258" t="s">
-        <v>828</v>
+        <v>48</v>
       </c>
       <c r="N258" t="s">
         <v>14</v>
@@ -17411,22 +17486,22 @@
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>1314</v>
+        <v>589</v>
       </c>
       <c r="B259" t="s">
-        <v>1329</v>
+        <v>598</v>
       </c>
       <c r="C259" t="s">
-        <v>1338</v>
+        <v>1190</v>
       </c>
       <c r="D259" t="s">
-        <v>382</v>
+        <v>599</v>
       </c>
       <c r="E259" t="s">
-        <v>899</v>
+        <v>988</v>
       </c>
       <c r="F259" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G259" t="s">
         <v>51</v>
@@ -17440,11 +17515,14 @@
       <c r="J259" t="s">
         <v>487</v>
       </c>
+      <c r="K259" t="s">
+        <v>75</v>
+      </c>
       <c r="L259" t="s">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="M259" t="s">
-        <v>48</v>
+        <v>828</v>
       </c>
       <c r="N259" t="s">
         <v>14</v>
@@ -17458,40 +17536,37 @@
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>660</v>
+        <v>1237</v>
       </c>
       <c r="B260" t="s">
-        <v>676</v>
+        <v>1253</v>
       </c>
       <c r="C260" t="s">
-        <v>1200</v>
+        <v>1254</v>
       </c>
       <c r="D260" t="s">
-        <v>677</v>
+        <v>455</v>
       </c>
       <c r="E260" t="s">
-        <v>1002</v>
+        <v>914</v>
       </c>
       <c r="F260" t="s">
         <v>47</v>
       </c>
       <c r="G260" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H260" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I260" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J260" t="s">
-        <v>201</v>
-      </c>
-      <c r="K260" t="s">
-        <v>132</v>
+        <v>1255</v>
       </c>
       <c r="L260" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M260" t="s">
         <v>48</v>
@@ -17508,19 +17583,13 @@
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>565</v>
+        <v>1324</v>
       </c>
       <c r="B261" t="s">
-        <v>569</v>
+        <v>1346</v>
       </c>
       <c r="C261" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D261" t="s">
-        <v>382</v>
-      </c>
-      <c r="E261" t="s">
-        <v>899</v>
+        <v>1347</v>
       </c>
       <c r="F261" t="s">
         <v>47</v>
@@ -17529,19 +17598,22 @@
         <v>32</v>
       </c>
       <c r="H261" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I261" t="s">
-        <v>267</v>
+        <v>1266</v>
       </c>
       <c r="J261" t="s">
-        <v>201</v>
+        <v>1255</v>
+      </c>
+      <c r="K261" t="s">
+        <v>54</v>
       </c>
       <c r="L261" t="s">
         <v>178</v>
       </c>
       <c r="M261" t="s">
-        <v>828</v>
+        <v>48</v>
       </c>
       <c r="N261" t="s">
         <v>14</v>
@@ -17555,25 +17627,19 @@
     </row>
     <row r="262" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>361</v>
+        <v>608</v>
       </c>
       <c r="B262" t="s">
-        <v>383</v>
+        <v>654</v>
       </c>
       <c r="C262" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D262" t="s">
-        <v>384</v>
-      </c>
-      <c r="E262" t="s">
-        <v>900</v>
+        <v>1198</v>
       </c>
       <c r="F262" t="s">
         <v>47</v>
       </c>
       <c r="G262" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H262" t="s">
         <v>13</v>
@@ -17582,13 +17648,16 @@
         <v>140</v>
       </c>
       <c r="J262" t="s">
-        <v>518</v>
+        <v>200</v>
+      </c>
+      <c r="K262" t="s">
+        <v>54</v>
       </c>
       <c r="L262" t="s">
-        <v>385</v>
+        <v>178</v>
       </c>
       <c r="M262" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="N262" t="s">
         <v>14</v>
@@ -17602,25 +17671,25 @@
     </row>
     <row r="263" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>362</v>
+        <v>1314</v>
       </c>
       <c r="B263" t="s">
-        <v>386</v>
+        <v>1329</v>
       </c>
       <c r="C263" t="s">
-        <v>1092</v>
+        <v>1338</v>
       </c>
       <c r="D263" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E263" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="F263" t="s">
         <v>47</v>
       </c>
       <c r="G263" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="H263" t="s">
         <v>13</v>
@@ -17629,13 +17698,10 @@
         <v>140</v>
       </c>
       <c r="J263" t="s">
-        <v>200</v>
-      </c>
-      <c r="K263" t="s">
-        <v>54</v>
+        <v>487</v>
       </c>
       <c r="L263" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M263" t="s">
         <v>48</v>
@@ -17652,25 +17718,25 @@
     </row>
     <row r="264" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>576</v>
+        <v>660</v>
       </c>
       <c r="B264" t="s">
-        <v>580</v>
+        <v>676</v>
       </c>
       <c r="C264" t="s">
-        <v>1185</v>
+        <v>1200</v>
       </c>
       <c r="D264" t="s">
-        <v>581</v>
+        <v>677</v>
       </c>
       <c r="E264" t="s">
-        <v>984</v>
+        <v>1002</v>
       </c>
       <c r="F264" t="s">
         <v>47</v>
       </c>
       <c r="G264" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H264" t="s">
         <v>13</v>
@@ -17679,10 +17745,10 @@
         <v>140</v>
       </c>
       <c r="J264" t="s">
-        <v>487</v>
+        <v>201</v>
       </c>
       <c r="K264" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="L264" t="s">
         <v>178</v>
@@ -17702,22 +17768,22 @@
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>619</v>
+        <v>565</v>
       </c>
       <c r="B265" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
       <c r="C265" t="s">
-        <v>1193</v>
+        <v>1183</v>
       </c>
       <c r="D265" t="s">
-        <v>636</v>
+        <v>382</v>
       </c>
       <c r="E265" t="s">
-        <v>991</v>
+        <v>899</v>
       </c>
       <c r="F265" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G265" t="s">
         <v>32</v>
@@ -17726,19 +17792,16 @@
         <v>13</v>
       </c>
       <c r="I265" t="s">
-        <v>140</v>
+        <v>267</v>
       </c>
       <c r="J265" t="s">
-        <v>200</v>
-      </c>
-      <c r="K265" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="L265" t="s">
-        <v>330</v>
+        <v>178</v>
       </c>
       <c r="M265" t="s">
-        <v>48</v>
+        <v>828</v>
       </c>
       <c r="N265" t="s">
         <v>14</v>
@@ -17752,25 +17815,25 @@
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>189</v>
+        <v>361</v>
       </c>
       <c r="B266" t="s">
-        <v>198</v>
+        <v>383</v>
       </c>
       <c r="C266" t="s">
-        <v>1069</v>
+        <v>1091</v>
       </c>
       <c r="D266" t="s">
-        <v>199</v>
+        <v>384</v>
       </c>
       <c r="E266" t="s">
-        <v>881</v>
+        <v>900</v>
       </c>
       <c r="F266" t="s">
         <v>47</v>
       </c>
       <c r="G266" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H266" t="s">
         <v>13</v>
@@ -17779,16 +17842,13 @@
         <v>140</v>
       </c>
       <c r="J266" t="s">
-        <v>200</v>
-      </c>
-      <c r="K266" t="s">
-        <v>53</v>
+        <v>518</v>
       </c>
       <c r="L266" t="s">
-        <v>178</v>
+        <v>385</v>
       </c>
       <c r="M266" t="s">
-        <v>48</v>
+        <v>829</v>
       </c>
       <c r="N266" t="s">
         <v>14</v>
@@ -17802,34 +17862,34 @@
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>190</v>
+        <v>362</v>
       </c>
       <c r="B267" t="s">
-        <v>202</v>
+        <v>386</v>
       </c>
       <c r="C267" t="s">
-        <v>1070</v>
+        <v>1092</v>
       </c>
       <c r="D267" t="s">
-        <v>203</v>
+        <v>387</v>
       </c>
       <c r="E267" t="s">
-        <v>882</v>
+        <v>901</v>
       </c>
       <c r="F267" t="s">
         <v>47</v>
       </c>
       <c r="G267" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="H267" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I267" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J267" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K267" t="s">
         <v>54</v>
@@ -17852,19 +17912,19 @@
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>191</v>
+        <v>576</v>
       </c>
       <c r="B268" t="s">
-        <v>206</v>
+        <v>580</v>
       </c>
       <c r="C268" t="s">
-        <v>1071</v>
+        <v>1185</v>
       </c>
       <c r="D268" t="s">
-        <v>207</v>
+        <v>581</v>
       </c>
       <c r="E268" t="s">
-        <v>883</v>
+        <v>984</v>
       </c>
       <c r="F268" t="s">
         <v>47</v>
@@ -17879,13 +17939,13 @@
         <v>140</v>
       </c>
       <c r="J268" t="s">
-        <v>200</v>
+        <v>487</v>
       </c>
       <c r="K268" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="L268" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M268" t="s">
         <v>48</v>
@@ -17902,40 +17962,40 @@
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>188</v>
+        <v>619</v>
       </c>
       <c r="B269" t="s">
-        <v>196</v>
+        <v>806</v>
       </c>
       <c r="C269" t="s">
-        <v>1068</v>
+        <v>1193</v>
       </c>
       <c r="D269" t="s">
-        <v>197</v>
+        <v>636</v>
       </c>
       <c r="E269" t="s">
-        <v>880</v>
+        <v>991</v>
       </c>
       <c r="F269" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G269" t="s">
         <v>32</v>
       </c>
       <c r="H269" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I269" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J269" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K269" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="L269" t="s">
-        <v>385</v>
+        <v>330</v>
       </c>
       <c r="M269" t="s">
         <v>48</v>
@@ -17952,37 +18012,40 @@
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>620</v>
+        <v>189</v>
       </c>
       <c r="B270" t="s">
-        <v>637</v>
+        <v>198</v>
       </c>
       <c r="C270" t="s">
-        <v>1194</v>
+        <v>1069</v>
       </c>
       <c r="D270" t="s">
-        <v>638</v>
+        <v>199</v>
       </c>
       <c r="E270" t="s">
-        <v>992</v>
+        <v>881</v>
       </c>
       <c r="F270" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G270" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H270" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I270" t="s">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="J270" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="K270" t="s">
+        <v>53</v>
       </c>
       <c r="L270" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="M270" t="s">
         <v>48</v>
@@ -17999,37 +18062,40 @@
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>621</v>
+        <v>190</v>
       </c>
       <c r="B271" t="s">
-        <v>639</v>
+        <v>202</v>
       </c>
       <c r="C271" t="s">
-        <v>1195</v>
+        <v>1070</v>
       </c>
       <c r="D271" t="s">
-        <v>640</v>
+        <v>203</v>
       </c>
       <c r="E271" t="s">
-        <v>1037</v>
+        <v>882</v>
       </c>
       <c r="F271" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G271" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H271" t="s">
         <v>31</v>
       </c>
       <c r="I271" t="s">
-        <v>445</v>
+        <v>142</v>
       </c>
       <c r="J271" t="s">
-        <v>201</v>
+        <v>205</v>
+      </c>
+      <c r="K271" t="s">
+        <v>54</v>
       </c>
       <c r="L271" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="M271" t="s">
         <v>48</v>
@@ -18046,43 +18112,43 @@
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>1485</v>
+        <v>191</v>
       </c>
       <c r="B272" t="s">
-        <v>1486</v>
+        <v>206</v>
       </c>
       <c r="C272" t="s">
-        <v>1487</v>
+        <v>1071</v>
       </c>
       <c r="D272" t="s">
-        <v>697</v>
+        <v>207</v>
       </c>
       <c r="E272" t="s">
-        <v>1010</v>
+        <v>883</v>
       </c>
       <c r="F272" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G272" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H272" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I272" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J272" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K272" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="L272" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="M272" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N272" t="s">
         <v>14</v>
@@ -18096,40 +18162,40 @@
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>672</v>
+        <v>188</v>
       </c>
       <c r="B273" t="s">
-        <v>694</v>
+        <v>196</v>
       </c>
       <c r="C273" t="s">
-        <v>1207</v>
+        <v>1068</v>
       </c>
       <c r="D273" t="s">
-        <v>697</v>
+        <v>197</v>
       </c>
       <c r="E273" t="s">
-        <v>1010</v>
+        <v>880</v>
       </c>
       <c r="F273" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G273" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H273" t="s">
         <v>31</v>
       </c>
       <c r="I273" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="J273" t="s">
         <v>201</v>
       </c>
       <c r="K273" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="L273" t="s">
-        <v>95</v>
+        <v>385</v>
       </c>
       <c r="M273" t="s">
         <v>48</v>
@@ -18146,43 +18212,40 @@
     </row>
     <row r="274" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>1276</v>
+        <v>620</v>
       </c>
       <c r="B274" t="s">
-        <v>1304</v>
+        <v>637</v>
       </c>
       <c r="C274" t="s">
-        <v>1305</v>
+        <v>1194</v>
       </c>
       <c r="D274" t="s">
-        <v>1306</v>
+        <v>638</v>
       </c>
       <c r="E274" t="s">
-        <v>1300</v>
+        <v>992</v>
       </c>
       <c r="F274" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G274" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H274" t="s">
         <v>31</v>
       </c>
       <c r="I274" t="s">
-        <v>1307</v>
+        <v>217</v>
       </c>
       <c r="J274" t="s">
         <v>201</v>
       </c>
-      <c r="K274" t="s">
-        <v>139</v>
-      </c>
       <c r="L274" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M274" t="s">
-        <v>828</v>
+        <v>48</v>
       </c>
       <c r="N274" t="s">
         <v>14</v>
@@ -18196,19 +18259,19 @@
     </row>
     <row r="275" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
-        <v>1281</v>
+        <v>621</v>
       </c>
       <c r="B275" t="s">
-        <v>1285</v>
+        <v>639</v>
       </c>
       <c r="C275" t="s">
-        <v>1286</v>
+        <v>1195</v>
       </c>
       <c r="D275" t="s">
-        <v>1287</v>
+        <v>640</v>
       </c>
       <c r="E275" t="s">
-        <v>1288</v>
+        <v>1037</v>
       </c>
       <c r="F275" t="s">
         <v>78</v>
@@ -18217,22 +18280,19 @@
         <v>51</v>
       </c>
       <c r="H275" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I275" t="s">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="J275" t="s">
         <v>201</v>
       </c>
-      <c r="K275" t="s">
-        <v>75</v>
-      </c>
       <c r="L275" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="M275" t="s">
-        <v>828</v>
+        <v>48</v>
       </c>
       <c r="N275" t="s">
         <v>14</v>
@@ -18246,34 +18306,43 @@
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
-        <v>1327</v>
+        <v>1485</v>
       </c>
       <c r="B276" t="s">
-        <v>1352</v>
+        <v>1486</v>
       </c>
       <c r="C276" t="s">
-        <v>1353</v>
+        <v>1487</v>
+      </c>
+      <c r="D276" t="s">
+        <v>697</v>
+      </c>
+      <c r="E276" t="s">
+        <v>1010</v>
       </c>
       <c r="F276" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G276" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H276" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I276" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J276" t="s">
-        <v>519</v>
+        <v>201</v>
+      </c>
+      <c r="K276" t="s">
+        <v>75</v>
       </c>
       <c r="L276" t="s">
         <v>95</v>
       </c>
       <c r="M276" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N276" t="s">
         <v>14</v>
@@ -18287,43 +18356,43 @@
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
-        <v>1371</v>
+        <v>672</v>
       </c>
       <c r="B277" t="s">
-        <v>1376</v>
+        <v>694</v>
       </c>
       <c r="C277" t="s">
-        <v>1377</v>
+        <v>1207</v>
       </c>
       <c r="D277" t="s">
-        <v>1378</v>
+        <v>697</v>
       </c>
       <c r="E277" t="s">
-        <v>1105</v>
+        <v>1010</v>
       </c>
       <c r="F277" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G277" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="H277" t="s">
         <v>31</v>
       </c>
       <c r="I277" t="s">
-        <v>445</v>
+        <v>142</v>
       </c>
       <c r="J277" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K277" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L277" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M277" t="s">
-        <v>829</v>
+        <v>48</v>
       </c>
       <c r="N277" t="s">
         <v>14</v>
@@ -18337,19 +18406,19 @@
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>606</v>
+        <v>1276</v>
       </c>
       <c r="B278" t="s">
-        <v>647</v>
+        <v>1304</v>
       </c>
       <c r="C278" t="s">
-        <v>1197</v>
+        <v>1305</v>
       </c>
       <c r="D278" t="s">
-        <v>442</v>
+        <v>1306</v>
       </c>
       <c r="E278" t="s">
-        <v>910</v>
+        <v>1300</v>
       </c>
       <c r="F278" t="s">
         <v>47</v>
@@ -18358,19 +18427,22 @@
         <v>32</v>
       </c>
       <c r="H278" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I278" t="s">
-        <v>108</v>
+        <v>1307</v>
+      </c>
+      <c r="J278" t="s">
+        <v>201</v>
       </c>
       <c r="K278" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="L278" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M278" t="s">
-        <v>48</v>
+        <v>828</v>
       </c>
       <c r="N278" t="s">
         <v>14</v>
@@ -18384,19 +18456,25 @@
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
-        <v>1372</v>
+        <v>1281</v>
       </c>
       <c r="B279" t="s">
-        <v>1381</v>
+        <v>1285</v>
       </c>
       <c r="C279" t="s">
-        <v>1382</v>
+        <v>1286</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E279" t="s">
+        <v>1288</v>
       </c>
       <c r="F279" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G279" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H279" t="s">
         <v>13</v>
@@ -18404,14 +18482,17 @@
       <c r="I279" t="s">
         <v>140</v>
       </c>
+      <c r="J279" t="s">
+        <v>201</v>
+      </c>
       <c r="K279" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="L279" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M279" t="s">
-        <v>48</v>
+        <v>828</v>
       </c>
       <c r="N279" t="s">
         <v>14</v>
@@ -18425,19 +18506,13 @@
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>430</v>
+        <v>1327</v>
       </c>
       <c r="B280" t="s">
-        <v>439</v>
+        <v>1352</v>
       </c>
       <c r="C280" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D280" t="s">
-        <v>442</v>
-      </c>
-      <c r="E280" t="s">
-        <v>910</v>
+        <v>1353</v>
       </c>
       <c r="F280" t="s">
         <v>47</v>
@@ -18449,16 +18524,13 @@
         <v>13</v>
       </c>
       <c r="I280" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="J280" t="s">
-        <v>440</v>
-      </c>
-      <c r="K280" t="s">
-        <v>54</v>
+        <v>519</v>
       </c>
       <c r="L280" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M280" t="s">
         <v>48</v>
@@ -18475,34 +18547,34 @@
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>431</v>
+        <v>1371</v>
       </c>
       <c r="B281" t="s">
-        <v>441</v>
+        <v>1376</v>
       </c>
       <c r="C281" t="s">
-        <v>1102</v>
+        <v>1377</v>
       </c>
       <c r="D281" t="s">
-        <v>442</v>
+        <v>1378</v>
       </c>
       <c r="E281" t="s">
-        <v>910</v>
+        <v>1105</v>
       </c>
       <c r="F281" t="s">
         <v>47</v>
       </c>
       <c r="G281" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="H281" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I281" t="s">
-        <v>108</v>
+        <v>445</v>
       </c>
       <c r="J281" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K281" t="s">
         <v>54</v>
@@ -18511,7 +18583,7 @@
         <v>178</v>
       </c>
       <c r="M281" t="s">
-        <v>48</v>
+        <v>829</v>
       </c>
       <c r="N281" t="s">
         <v>14</v>
@@ -18525,13 +18597,13 @@
     </row>
     <row r="282" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
-        <v>438</v>
+        <v>606</v>
       </c>
       <c r="B282" t="s">
-        <v>456</v>
+        <v>647</v>
       </c>
       <c r="C282" t="s">
-        <v>1108</v>
+        <v>1197</v>
       </c>
       <c r="D282" t="s">
         <v>442</v>
@@ -18551,17 +18623,14 @@
       <c r="I282" t="s">
         <v>108</v>
       </c>
-      <c r="J282" t="s">
-        <v>201</v>
-      </c>
       <c r="K282" t="s">
         <v>54</v>
       </c>
       <c r="L282" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M282" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N282" t="s">
         <v>14</v>
@@ -18575,19 +18644,13 @@
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>663</v>
+        <v>1372</v>
       </c>
       <c r="B283" t="s">
-        <v>682</v>
+        <v>1381</v>
       </c>
       <c r="C283" t="s">
-        <v>682</v>
-      </c>
-      <c r="D283" t="s">
-        <v>683</v>
-      </c>
-      <c r="E283" t="s">
-        <v>1005</v>
+        <v>1382</v>
       </c>
       <c r="F283" t="s">
         <v>47</v>
@@ -18599,16 +18662,13 @@
         <v>13</v>
       </c>
       <c r="I283" t="s">
-        <v>445</v>
-      </c>
-      <c r="J283" t="s">
-        <v>201</v>
+        <v>140</v>
       </c>
       <c r="K283" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="L283" t="s">
-        <v>385</v>
+        <v>178</v>
       </c>
       <c r="M283" t="s">
         <v>48</v>
@@ -18625,19 +18685,19 @@
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
-        <v>667</v>
+        <v>430</v>
       </c>
       <c r="B284" t="s">
-        <v>816</v>
+        <v>439</v>
       </c>
       <c r="C284" t="s">
-        <v>1204</v>
+        <v>1101</v>
       </c>
       <c r="D284" t="s">
-        <v>683</v>
+        <v>442</v>
       </c>
       <c r="E284" t="s">
-        <v>1005</v>
+        <v>910</v>
       </c>
       <c r="F284" t="s">
         <v>47</v>
@@ -18649,16 +18709,16 @@
         <v>13</v>
       </c>
       <c r="I284" t="s">
-        <v>445</v>
+        <v>108</v>
       </c>
       <c r="J284" t="s">
-        <v>201</v>
+        <v>440</v>
       </c>
       <c r="K284" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="L284" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M284" t="s">
         <v>48</v>
@@ -18675,31 +18735,31 @@
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B285" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C285" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="D285" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="E285" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="F285" t="s">
         <v>47</v>
       </c>
       <c r="G285" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="H285" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I285" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="J285" t="s">
         <v>201</v>
@@ -18725,13 +18785,19 @@
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
-        <v>1231</v>
+        <v>438</v>
       </c>
       <c r="B286" t="s">
-        <v>1239</v>
+        <v>456</v>
       </c>
       <c r="C286" t="s">
-        <v>1239</v>
+        <v>1108</v>
+      </c>
+      <c r="D286" t="s">
+        <v>442</v>
+      </c>
+      <c r="E286" t="s">
+        <v>910</v>
       </c>
       <c r="F286" t="s">
         <v>47</v>
@@ -18740,10 +18806,10 @@
         <v>32</v>
       </c>
       <c r="H286" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I286" t="s">
-        <v>445</v>
+        <v>108</v>
       </c>
       <c r="J286" t="s">
         <v>201</v>
@@ -18755,7 +18821,7 @@
         <v>178</v>
       </c>
       <c r="M286" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N286" t="s">
         <v>14</v>
@@ -18769,19 +18835,19 @@
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
-        <v>605</v>
+        <v>663</v>
       </c>
       <c r="B287" t="s">
-        <v>646</v>
+        <v>682</v>
       </c>
       <c r="C287" t="s">
-        <v>646</v>
+        <v>682</v>
       </c>
       <c r="D287" t="s">
-        <v>808</v>
+        <v>683</v>
       </c>
       <c r="E287" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="F287" t="s">
         <v>47</v>
@@ -18793,16 +18859,19 @@
         <v>13</v>
       </c>
       <c r="I287" t="s">
-        <v>140</v>
+        <v>445</v>
+      </c>
+      <c r="J287" t="s">
+        <v>201</v>
       </c>
       <c r="K287" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="L287" t="s">
-        <v>178</v>
+        <v>385</v>
       </c>
       <c r="M287" t="s">
-        <v>829</v>
+        <v>48</v>
       </c>
       <c r="N287" t="s">
         <v>14</v>
@@ -18816,19 +18885,19 @@
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
-        <v>566</v>
+        <v>667</v>
       </c>
       <c r="B288" t="s">
-        <v>570</v>
+        <v>816</v>
       </c>
       <c r="C288" t="s">
-        <v>1184</v>
+        <v>1204</v>
       </c>
       <c r="D288" t="s">
-        <v>382</v>
+        <v>683</v>
       </c>
       <c r="E288" t="s">
-        <v>899</v>
+        <v>1005</v>
       </c>
       <c r="F288" t="s">
         <v>47</v>
@@ -18840,13 +18909,16 @@
         <v>13</v>
       </c>
       <c r="I288" t="s">
-        <v>267</v>
+        <v>445</v>
       </c>
       <c r="J288" t="s">
-        <v>519</v>
+        <v>201</v>
+      </c>
+      <c r="K288" t="s">
+        <v>204</v>
       </c>
       <c r="L288" t="s">
-        <v>572</v>
+        <v>179</v>
       </c>
       <c r="M288" t="s">
         <v>48</v>
@@ -18863,37 +18935,40 @@
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
-        <v>360</v>
+        <v>436</v>
       </c>
       <c r="B289" t="s">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="C289" t="s">
-        <v>1090</v>
+        <v>1106</v>
       </c>
       <c r="D289" t="s">
-        <v>382</v>
+        <v>453</v>
       </c>
       <c r="E289" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="F289" t="s">
         <v>47</v>
       </c>
       <c r="G289" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="H289" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I289" t="s">
-        <v>267</v>
+        <v>142</v>
       </c>
       <c r="J289" t="s">
-        <v>487</v>
+        <v>201</v>
+      </c>
+      <c r="K289" t="s">
+        <v>54</v>
       </c>
       <c r="L289" t="s">
-        <v>385</v>
+        <v>178</v>
       </c>
       <c r="M289" t="s">
         <v>48</v>
@@ -18910,40 +18985,37 @@
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
-        <v>671</v>
+        <v>1231</v>
       </c>
       <c r="B290" t="s">
-        <v>692</v>
+        <v>1239</v>
       </c>
       <c r="C290" t="s">
-        <v>1206</v>
-      </c>
-      <c r="D290" t="s">
-        <v>696</v>
-      </c>
-      <c r="E290" t="s">
-        <v>1009</v>
+        <v>1239</v>
       </c>
       <c r="F290" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G290" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H290" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I290" t="s">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="J290" t="s">
-        <v>693</v>
+        <v>201</v>
+      </c>
+      <c r="K290" t="s">
+        <v>54</v>
       </c>
       <c r="L290" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M290" t="s">
-        <v>829</v>
+        <v>48</v>
       </c>
       <c r="N290" t="s">
         <v>14</v>
@@ -18957,22 +19029,22 @@
     </row>
     <row r="291" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
-        <v>698</v>
+        <v>605</v>
       </c>
       <c r="B291" t="s">
-        <v>702</v>
+        <v>646</v>
       </c>
       <c r="C291" t="s">
-        <v>1208</v>
+        <v>646</v>
       </c>
       <c r="D291" t="s">
-        <v>704</v>
+        <v>808</v>
       </c>
       <c r="E291" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="F291" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G291" t="s">
         <v>32</v>
@@ -18983,14 +19055,14 @@
       <c r="I291" t="s">
         <v>140</v>
       </c>
-      <c r="J291" t="s">
-        <v>519</v>
+      <c r="K291" t="s">
+        <v>54</v>
       </c>
       <c r="L291" t="s">
-        <v>340</v>
+        <v>178</v>
       </c>
       <c r="M291" t="s">
-        <v>49</v>
+        <v>829</v>
       </c>
       <c r="N291" t="s">
         <v>14</v>
@@ -19004,40 +19076,40 @@
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
-        <v>616</v>
+        <v>566</v>
       </c>
       <c r="B292" t="s">
-        <v>625</v>
+        <v>570</v>
       </c>
       <c r="C292" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
       <c r="D292" t="s">
-        <v>626</v>
+        <v>382</v>
       </c>
       <c r="E292" t="s">
-        <v>990</v>
+        <v>899</v>
       </c>
       <c r="F292" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G292" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H292" t="s">
         <v>13</v>
       </c>
       <c r="I292" t="s">
-        <v>140</v>
+        <v>267</v>
       </c>
       <c r="J292" t="s">
         <v>519</v>
       </c>
       <c r="L292" t="s">
-        <v>186</v>
+        <v>572</v>
       </c>
       <c r="M292" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N292" t="s">
         <v>14</v>
@@ -19051,19 +19123,19 @@
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
-        <v>577</v>
+        <v>360</v>
       </c>
       <c r="B293" t="s">
-        <v>582</v>
+        <v>381</v>
       </c>
       <c r="C293" t="s">
-        <v>1186</v>
+        <v>1090</v>
       </c>
       <c r="D293" t="s">
-        <v>546</v>
+        <v>382</v>
       </c>
       <c r="E293" t="s">
-        <v>975</v>
+        <v>899</v>
       </c>
       <c r="F293" t="s">
         <v>47</v>
@@ -19075,16 +19147,13 @@
         <v>13</v>
       </c>
       <c r="I293" t="s">
-        <v>140</v>
+        <v>267</v>
       </c>
       <c r="J293" t="s">
-        <v>583</v>
-      </c>
-      <c r="K293" t="s">
-        <v>132</v>
+        <v>487</v>
       </c>
       <c r="L293" t="s">
-        <v>178</v>
+        <v>385</v>
       </c>
       <c r="M293" t="s">
         <v>48</v>
@@ -19101,19 +19170,19 @@
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
-        <v>557</v>
+        <v>671</v>
       </c>
       <c r="B294" t="s">
-        <v>803</v>
+        <v>692</v>
       </c>
       <c r="C294" t="s">
-        <v>1226</v>
+        <v>1206</v>
       </c>
       <c r="D294" t="s">
-        <v>561</v>
+        <v>696</v>
       </c>
       <c r="E294" t="s">
-        <v>983</v>
+        <v>1009</v>
       </c>
       <c r="F294" t="s">
         <v>78</v>
@@ -19128,16 +19197,13 @@
         <v>140</v>
       </c>
       <c r="J294" t="s">
-        <v>487</v>
-      </c>
-      <c r="K294" t="s">
-        <v>75</v>
+        <v>693</v>
       </c>
       <c r="L294" t="s">
-        <v>562</v>
+        <v>186</v>
       </c>
       <c r="M294" t="s">
-        <v>48</v>
+        <v>829</v>
       </c>
       <c r="N294" t="s">
         <v>14</v>
@@ -19151,25 +19217,25 @@
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
-        <v>1509</v>
+        <v>698</v>
       </c>
       <c r="B295" t="s">
-        <v>1512</v>
+        <v>702</v>
       </c>
       <c r="C295" t="s">
-        <v>1511</v>
+        <v>1208</v>
       </c>
       <c r="D295" t="s">
-        <v>561</v>
+        <v>704</v>
       </c>
       <c r="E295" t="s">
-        <v>983</v>
+        <v>1011</v>
       </c>
       <c r="F295" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G295" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H295" t="s">
         <v>13</v>
@@ -19180,14 +19246,11 @@
       <c r="J295" t="s">
         <v>519</v>
       </c>
-      <c r="K295" t="s">
-        <v>54</v>
-      </c>
       <c r="L295" t="s">
-        <v>278</v>
+        <v>340</v>
       </c>
       <c r="M295" t="s">
-        <v>829</v>
+        <v>49</v>
       </c>
       <c r="N295" t="s">
         <v>14</v>
@@ -19201,25 +19264,25 @@
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
-        <v>699</v>
+        <v>616</v>
       </c>
       <c r="B296" t="s">
-        <v>703</v>
+        <v>625</v>
       </c>
       <c r="C296" t="s">
-        <v>1209</v>
+        <v>1192</v>
       </c>
       <c r="D296" t="s">
-        <v>1515</v>
+        <v>626</v>
       </c>
       <c r="E296" t="s">
-        <v>1516</v>
+        <v>990</v>
       </c>
       <c r="F296" t="s">
         <v>78</v>
       </c>
       <c r="G296" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H296" t="s">
         <v>13</v>
@@ -19228,7 +19291,7 @@
         <v>140</v>
       </c>
       <c r="J296" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="L296" t="s">
         <v>186</v>
@@ -19248,19 +19311,19 @@
     </row>
     <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>1508</v>
+        <v>577</v>
       </c>
       <c r="B297" t="s">
-        <v>1514</v>
+        <v>582</v>
       </c>
       <c r="C297" t="s">
-        <v>1513</v>
+        <v>1186</v>
       </c>
       <c r="D297" t="s">
-        <v>1515</v>
+        <v>546</v>
       </c>
       <c r="E297" t="s">
-        <v>1516</v>
+        <v>975</v>
       </c>
       <c r="F297" t="s">
         <v>47</v>
@@ -19275,16 +19338,16 @@
         <v>140</v>
       </c>
       <c r="J297" t="s">
-        <v>519</v>
+        <v>583</v>
       </c>
       <c r="K297" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="L297" t="s">
-        <v>278</v>
+        <v>178</v>
       </c>
       <c r="M297" t="s">
-        <v>829</v>
+        <v>48</v>
       </c>
       <c r="N297" t="s">
         <v>14</v>
@@ -19298,19 +19361,19 @@
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>1283</v>
+        <v>557</v>
       </c>
       <c r="B298" t="s">
-        <v>1291</v>
+        <v>803</v>
       </c>
       <c r="C298" t="s">
-        <v>1292</v>
+        <v>1226</v>
       </c>
       <c r="D298" t="s">
-        <v>1293</v>
+        <v>561</v>
       </c>
       <c r="E298" t="s">
-        <v>1294</v>
+        <v>983</v>
       </c>
       <c r="F298" t="s">
         <v>78</v>
@@ -19331,7 +19394,7 @@
         <v>75</v>
       </c>
       <c r="L298" t="s">
-        <v>186</v>
+        <v>562</v>
       </c>
       <c r="M298" t="s">
         <v>48</v>
@@ -19348,37 +19411,43 @@
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>712</v>
+        <v>1509</v>
       </c>
       <c r="B299" t="s">
-        <v>737</v>
+        <v>1512</v>
       </c>
       <c r="C299" t="s">
-        <v>1210</v>
+        <v>1511</v>
       </c>
       <c r="D299" t="s">
-        <v>740</v>
+        <v>561</v>
       </c>
       <c r="E299" t="s">
-        <v>1012</v>
+        <v>983</v>
       </c>
       <c r="F299" t="s">
         <v>47</v>
       </c>
       <c r="G299" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H299" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I299" t="s">
-        <v>216</v>
+        <v>140</v>
+      </c>
+      <c r="J299" t="s">
+        <v>519</v>
+      </c>
+      <c r="K299" t="s">
+        <v>54</v>
       </c>
       <c r="L299" t="s">
-        <v>178</v>
+        <v>278</v>
       </c>
       <c r="M299" t="s">
-        <v>48</v>
+        <v>829</v>
       </c>
       <c r="N299" t="s">
         <v>14</v>
@@ -19392,25 +19461,25 @@
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="B300" t="s">
-        <v>731</v>
+        <v>703</v>
       </c>
       <c r="C300" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
       <c r="D300" t="s">
-        <v>743</v>
+        <v>1515</v>
       </c>
       <c r="E300" t="s">
-        <v>1015</v>
+        <v>1516</v>
       </c>
       <c r="F300" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G300" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H300" t="s">
         <v>13</v>
@@ -19421,14 +19490,11 @@
       <c r="J300" t="s">
         <v>487</v>
       </c>
-      <c r="K300" t="s">
-        <v>75</v>
-      </c>
       <c r="L300" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="M300" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N300" t="s">
         <v>14</v>
@@ -19442,19 +19508,19 @@
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>724</v>
+        <v>1508</v>
       </c>
       <c r="B301" t="s">
-        <v>727</v>
+        <v>1514</v>
       </c>
       <c r="C301" t="s">
-        <v>1219</v>
+        <v>1513</v>
       </c>
       <c r="D301" t="s">
-        <v>744</v>
+        <v>1515</v>
       </c>
       <c r="E301" t="s">
-        <v>1016</v>
+        <v>1516</v>
       </c>
       <c r="F301" t="s">
         <v>47</v>
@@ -19472,13 +19538,13 @@
         <v>519</v>
       </c>
       <c r="K301" t="s">
-        <v>139</v>
+        <v>54</v>
       </c>
       <c r="L301" t="s">
-        <v>178</v>
+        <v>278</v>
       </c>
       <c r="M301" t="s">
-        <v>48</v>
+        <v>829</v>
       </c>
       <c r="N301" t="s">
         <v>14</v>
@@ -19492,37 +19558,40 @@
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>1260</v>
+        <v>1283</v>
       </c>
       <c r="B302" t="s">
-        <v>1267</v>
+        <v>1291</v>
       </c>
       <c r="C302" t="s">
-        <v>1265</v>
+        <v>1292</v>
       </c>
       <c r="D302" t="s">
-        <v>1268</v>
+        <v>1293</v>
       </c>
       <c r="E302" t="s">
-        <v>1268</v>
+        <v>1294</v>
       </c>
       <c r="F302" t="s">
         <v>78</v>
       </c>
       <c r="G302" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H302" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I302" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J302" t="s">
-        <v>276</v>
+        <v>487</v>
+      </c>
+      <c r="K302" t="s">
+        <v>75</v>
       </c>
       <c r="L302" t="s">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="M302" t="s">
         <v>48</v>
@@ -19539,34 +19608,34 @@
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>1280</v>
+        <v>712</v>
       </c>
       <c r="B303" t="s">
-        <v>1284</v>
+        <v>737</v>
       </c>
       <c r="C303" t="s">
-        <v>1295</v>
+        <v>1210</v>
+      </c>
+      <c r="D303" t="s">
+        <v>740</v>
+      </c>
+      <c r="E303" t="s">
+        <v>1012</v>
       </c>
       <c r="F303" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G303" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H303" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I303" t="s">
-        <v>108</v>
-      </c>
-      <c r="J303" t="s">
-        <v>109</v>
-      </c>
-      <c r="K303" t="s">
-        <v>75</v>
+        <v>216</v>
       </c>
       <c r="L303" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="M303" t="s">
         <v>48</v>
@@ -19583,19 +19652,19 @@
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
-        <v>1315</v>
+        <v>718</v>
       </c>
       <c r="B304" t="s">
-        <v>1330</v>
+        <v>731</v>
       </c>
       <c r="C304" t="s">
-        <v>1337</v>
+        <v>1217</v>
       </c>
       <c r="D304" t="s">
-        <v>382</v>
+        <v>743</v>
       </c>
       <c r="E304" t="s">
-        <v>899</v>
+        <v>1015</v>
       </c>
       <c r="F304" t="s">
         <v>47</v>
@@ -19612,8 +19681,11 @@
       <c r="J304" t="s">
         <v>487</v>
       </c>
+      <c r="K304" t="s">
+        <v>75</v>
+      </c>
       <c r="L304" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="M304" t="s">
         <v>48</v>
@@ -19630,25 +19702,25 @@
     </row>
     <row r="305" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
-        <v>392</v>
+        <v>724</v>
       </c>
       <c r="B305" t="s">
-        <v>782</v>
+        <v>727</v>
       </c>
       <c r="C305" t="s">
-        <v>1096</v>
+        <v>1219</v>
       </c>
       <c r="D305" t="s">
-        <v>397</v>
+        <v>744</v>
       </c>
       <c r="E305" t="s">
-        <v>903</v>
+        <v>1016</v>
       </c>
       <c r="F305" t="s">
         <v>47</v>
       </c>
       <c r="G305" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H305" t="s">
         <v>13</v>
@@ -19659,6 +19731,9 @@
       <c r="J305" t="s">
         <v>519</v>
       </c>
+      <c r="K305" t="s">
+        <v>139</v>
+      </c>
       <c r="L305" t="s">
         <v>178</v>
       </c>
@@ -19677,40 +19752,37 @@
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
-        <v>187</v>
+        <v>1260</v>
       </c>
       <c r="B306" t="s">
-        <v>192</v>
+        <v>1267</v>
       </c>
       <c r="C306" t="s">
-        <v>1067</v>
+        <v>1265</v>
       </c>
       <c r="D306" t="s">
-        <v>193</v>
+        <v>1268</v>
       </c>
       <c r="E306" t="s">
-        <v>1020</v>
+        <v>1268</v>
       </c>
       <c r="F306" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G306" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H306" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I306" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J306" t="s">
-        <v>194</v>
-      </c>
-      <c r="K306" t="s">
-        <v>75</v>
+        <v>276</v>
       </c>
       <c r="L306" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="M306" t="s">
         <v>48</v>
@@ -19727,37 +19799,34 @@
     </row>
     <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>365</v>
+        <v>1280</v>
       </c>
       <c r="B307" t="s">
-        <v>391</v>
+        <v>1284</v>
       </c>
       <c r="C307" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D307" t="s">
-        <v>390</v>
-      </c>
-      <c r="E307" t="s">
-        <v>1025</v>
+        <v>1295</v>
       </c>
       <c r="F307" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G307" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H307" t="s">
         <v>13</v>
       </c>
       <c r="I307" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="J307" t="s">
-        <v>276</v>
+        <v>109</v>
+      </c>
+      <c r="K307" t="s">
+        <v>75</v>
       </c>
       <c r="L307" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="M307" t="s">
         <v>48</v>
@@ -19774,19 +19843,19 @@
     </row>
     <row r="308" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B308" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C308" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="D308" t="s">
-        <v>1340</v>
+        <v>382</v>
       </c>
       <c r="E308" t="s">
-        <v>1339</v>
+        <v>899</v>
       </c>
       <c r="F308" t="s">
         <v>47</v>
@@ -19801,7 +19870,7 @@
         <v>140</v>
       </c>
       <c r="J308" t="s">
-        <v>276</v>
+        <v>487</v>
       </c>
       <c r="L308" t="s">
         <v>95</v>
@@ -19821,25 +19890,25 @@
     </row>
     <row r="309" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>61</v>
+        <v>392</v>
       </c>
       <c r="B309" t="s">
-        <v>70</v>
+        <v>782</v>
       </c>
       <c r="C309" t="s">
-        <v>1120</v>
+        <v>1096</v>
       </c>
       <c r="D309" t="s">
-        <v>288</v>
+        <v>397</v>
       </c>
       <c r="E309" t="s">
-        <v>924</v>
+        <v>903</v>
       </c>
       <c r="F309" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G309" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H309" t="s">
         <v>13</v>
@@ -19868,22 +19937,22 @@
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="B310" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="C310" t="s">
-        <v>1122</v>
+        <v>1067</v>
       </c>
       <c r="D310" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="E310" t="s">
-        <v>926</v>
+        <v>1020</v>
       </c>
       <c r="F310" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G310" t="s">
         <v>51</v>
@@ -19895,16 +19964,16 @@
         <v>140</v>
       </c>
       <c r="J310" t="s">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="K310" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="L310" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="M310" t="s">
-        <v>828</v>
+        <v>48</v>
       </c>
       <c r="N310" t="s">
         <v>14</v>
@@ -19918,13 +19987,19 @@
     </row>
     <row r="311" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
-        <v>710</v>
+        <v>365</v>
       </c>
       <c r="B311" t="s">
-        <v>738</v>
+        <v>391</v>
       </c>
       <c r="C311" t="s">
-        <v>1221</v>
+        <v>1095</v>
+      </c>
+      <c r="D311" t="s">
+        <v>390</v>
+      </c>
+      <c r="E311" t="s">
+        <v>1025</v>
       </c>
       <c r="F311" t="s">
         <v>47</v>
@@ -19938,8 +20013,11 @@
       <c r="I311" t="s">
         <v>140</v>
       </c>
+      <c r="J311" t="s">
+        <v>276</v>
+      </c>
       <c r="L311" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="M311" t="s">
         <v>48</v>
@@ -19956,19 +20034,25 @@
     </row>
     <row r="312" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
-        <v>711</v>
+        <v>1317</v>
       </c>
       <c r="B312" t="s">
-        <v>739</v>
+        <v>1331</v>
       </c>
       <c r="C312" t="s">
-        <v>1222</v>
+        <v>1331</v>
+      </c>
+      <c r="D312" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E312" t="s">
+        <v>1339</v>
       </c>
       <c r="F312" t="s">
         <v>47</v>
       </c>
       <c r="G312" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H312" t="s">
         <v>13</v>
@@ -19976,8 +20060,11 @@
       <c r="I312" t="s">
         <v>140</v>
       </c>
+      <c r="J312" t="s">
+        <v>276</v>
+      </c>
       <c r="L312" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="M312" t="s">
         <v>48</v>
@@ -19994,19 +20081,25 @@
     </row>
     <row r="313" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
-        <v>831</v>
+        <v>61</v>
       </c>
       <c r="B313" t="s">
-        <v>834</v>
+        <v>70</v>
       </c>
       <c r="C313" t="s">
-        <v>1223</v>
+        <v>1120</v>
+      </c>
+      <c r="D313" t="s">
+        <v>288</v>
+      </c>
+      <c r="E313" t="s">
+        <v>924</v>
       </c>
       <c r="F313" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G313" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H313" t="s">
         <v>13</v>
@@ -20015,10 +20108,7 @@
         <v>140</v>
       </c>
       <c r="J313" t="s">
-        <v>276</v>
-      </c>
-      <c r="K313" t="s">
-        <v>54</v>
+        <v>519</v>
       </c>
       <c r="L313" t="s">
         <v>178</v>
@@ -20038,19 +20128,25 @@
     </row>
     <row r="314" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>1407</v>
+        <v>124</v>
       </c>
       <c r="B314" t="s">
-        <v>1428</v>
+        <v>130</v>
       </c>
       <c r="C314" t="s">
-        <v>1428</v>
+        <v>1122</v>
+      </c>
+      <c r="D314" t="s">
+        <v>131</v>
+      </c>
+      <c r="E314" t="s">
+        <v>926</v>
       </c>
       <c r="F314" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G314" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H314" t="s">
         <v>13</v>
@@ -20058,14 +20154,17 @@
       <c r="I314" t="s">
         <v>140</v>
       </c>
+      <c r="J314" t="s">
+        <v>109</v>
+      </c>
       <c r="K314" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="L314" t="s">
         <v>178</v>
       </c>
       <c r="M314" t="s">
-        <v>48</v>
+        <v>828</v>
       </c>
       <c r="N314" t="s">
         <v>14</v>
@@ -20079,10 +20178,13 @@
     </row>
     <row r="315" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
-        <v>1318</v>
+        <v>710</v>
       </c>
       <c r="B315" t="s">
-        <v>1332</v>
+        <v>738</v>
+      </c>
+      <c r="C315" t="s">
+        <v>1221</v>
       </c>
       <c r="F315" t="s">
         <v>47</v>
@@ -20091,13 +20193,10 @@
         <v>32</v>
       </c>
       <c r="H315" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I315" t="s">
-        <v>107</v>
-      </c>
-      <c r="K315" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="L315" t="s">
         <v>178</v>
@@ -20117,25 +20216,19 @@
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
-        <v>1325</v>
+        <v>711</v>
       </c>
       <c r="B316" t="s">
-        <v>1348</v>
+        <v>739</v>
       </c>
       <c r="C316" t="s">
-        <v>1349</v>
-      </c>
-      <c r="D316" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E316" t="s">
-        <v>975</v>
+        <v>1222</v>
       </c>
       <c r="F316" t="s">
         <v>47</v>
       </c>
       <c r="G316" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H316" t="s">
         <v>13</v>
@@ -20143,11 +20236,8 @@
       <c r="I316" t="s">
         <v>140</v>
       </c>
-      <c r="J316" t="s">
-        <v>109</v>
-      </c>
       <c r="L316" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="M316" t="s">
         <v>48</v>
@@ -20164,25 +20254,19 @@
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
-        <v>457</v>
+        <v>831</v>
       </c>
       <c r="B317" t="s">
-        <v>545</v>
+        <v>834</v>
       </c>
       <c r="C317" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D317" t="s">
-        <v>546</v>
-      </c>
-      <c r="E317" t="s">
-        <v>975</v>
+        <v>1223</v>
       </c>
       <c r="F317" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G317" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H317" t="s">
         <v>13</v>
@@ -20191,10 +20275,10 @@
         <v>140</v>
       </c>
       <c r="J317" t="s">
-        <v>109</v>
+        <v>276</v>
       </c>
       <c r="K317" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="L317" t="s">
         <v>178</v>
@@ -20214,25 +20298,19 @@
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
-        <v>719</v>
+        <v>1407</v>
       </c>
       <c r="B318" t="s">
-        <v>730</v>
+        <v>1428</v>
       </c>
       <c r="C318" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D318" t="s">
-        <v>546</v>
-      </c>
-      <c r="E318" t="s">
-        <v>975</v>
+        <v>1428</v>
       </c>
       <c r="F318" t="s">
         <v>47</v>
       </c>
       <c r="G318" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H318" t="s">
         <v>13</v>
@@ -20240,6 +20318,9 @@
       <c r="I318" t="s">
         <v>140</v>
       </c>
+      <c r="K318" t="s">
+        <v>54</v>
+      </c>
       <c r="L318" t="s">
         <v>178</v>
       </c>
@@ -20258,43 +20339,31 @@
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
-        <v>591</v>
+        <v>1318</v>
       </c>
       <c r="B319" t="s">
-        <v>600</v>
-      </c>
-      <c r="C319" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D319" t="s">
-        <v>601</v>
-      </c>
-      <c r="E319" t="s">
-        <v>989</v>
+        <v>1332</v>
       </c>
       <c r="F319" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G319" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H319" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I319" t="s">
-        <v>140</v>
-      </c>
-      <c r="J319" t="s">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="K319" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="L319" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="M319" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N319" t="s">
         <v>14</v>
@@ -20308,25 +20377,25 @@
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>293</v>
+        <v>1325</v>
       </c>
       <c r="B320" t="s">
-        <v>309</v>
+        <v>1348</v>
       </c>
       <c r="C320" t="s">
-        <v>1161</v>
+        <v>1349</v>
       </c>
       <c r="D320" t="s">
-        <v>310</v>
+        <v>1306</v>
       </c>
       <c r="E320" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="F320" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G320" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H320" t="s">
         <v>13</v>
@@ -20335,13 +20404,13 @@
         <v>140</v>
       </c>
       <c r="J320" t="s">
-        <v>276</v>
+        <v>109</v>
       </c>
       <c r="L320" t="s">
         <v>95</v>
       </c>
       <c r="M320" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N320" t="s">
         <v>14</v>
@@ -20355,25 +20424,25 @@
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
-        <v>1370</v>
+        <v>457</v>
       </c>
       <c r="B321" t="s">
-        <v>1375</v>
+        <v>545</v>
       </c>
       <c r="C321" t="s">
-        <v>1375</v>
+        <v>1227</v>
       </c>
       <c r="D321" t="s">
-        <v>1379</v>
+        <v>546</v>
       </c>
       <c r="E321" t="s">
-        <v>1380</v>
+        <v>975</v>
       </c>
       <c r="F321" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G321" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H321" t="s">
         <v>13</v>
@@ -20381,8 +20450,11 @@
       <c r="I321" t="s">
         <v>140</v>
       </c>
+      <c r="J321" t="s">
+        <v>109</v>
+      </c>
       <c r="K321" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="L321" t="s">
         <v>178</v>
@@ -20402,19 +20474,25 @@
     </row>
     <row r="322" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>1507</v>
+        <v>719</v>
       </c>
       <c r="B322" t="s">
-        <v>1521</v>
+        <v>730</v>
       </c>
       <c r="C322" t="s">
-        <v>1522</v>
+        <v>1224</v>
+      </c>
+      <c r="D322" t="s">
+        <v>546</v>
+      </c>
+      <c r="E322" t="s">
+        <v>975</v>
       </c>
       <c r="F322" t="s">
         <v>47</v>
       </c>
       <c r="G322" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H322" t="s">
         <v>13</v>
@@ -20422,25 +20500,292 @@
       <c r="I322" t="s">
         <v>140</v>
       </c>
-      <c r="J322" t="s">
+      <c r="L322" t="s">
+        <v>178</v>
+      </c>
+      <c r="M322" t="s">
+        <v>48</v>
+      </c>
+      <c r="N322" t="s">
+        <v>14</v>
+      </c>
+      <c r="O322" t="s">
+        <v>15</v>
+      </c>
+      <c r="P322" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="323" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A323" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B323" t="s">
+        <v>600</v>
+      </c>
+      <c r="C323" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D323" t="s">
+        <v>601</v>
+      </c>
+      <c r="E323" t="s">
+        <v>989</v>
+      </c>
+      <c r="F323" t="s">
+        <v>78</v>
+      </c>
+      <c r="G323" t="s">
+        <v>51</v>
+      </c>
+      <c r="H323" t="s">
+        <v>13</v>
+      </c>
+      <c r="I323" t="s">
+        <v>140</v>
+      </c>
+      <c r="J323" t="s">
+        <v>276</v>
+      </c>
+      <c r="K323" t="s">
+        <v>75</v>
+      </c>
+      <c r="L323" t="s">
+        <v>95</v>
+      </c>
+      <c r="M323" t="s">
+        <v>49</v>
+      </c>
+      <c r="N323" t="s">
+        <v>14</v>
+      </c>
+      <c r="O323" t="s">
+        <v>15</v>
+      </c>
+      <c r="P323" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="324" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A324" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B324" t="s">
+        <v>309</v>
+      </c>
+      <c r="C324" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D324" t="s">
+        <v>310</v>
+      </c>
+      <c r="E324" t="s">
+        <v>963</v>
+      </c>
+      <c r="F324" t="s">
+        <v>78</v>
+      </c>
+      <c r="G324" t="s">
+        <v>32</v>
+      </c>
+      <c r="H324" t="s">
+        <v>13</v>
+      </c>
+      <c r="I324" t="s">
+        <v>140</v>
+      </c>
+      <c r="J324" t="s">
+        <v>276</v>
+      </c>
+      <c r="L324" t="s">
+        <v>95</v>
+      </c>
+      <c r="M324" t="s">
+        <v>49</v>
+      </c>
+      <c r="N324" t="s">
+        <v>14</v>
+      </c>
+      <c r="O324" t="s">
+        <v>15</v>
+      </c>
+      <c r="P324" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="325" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A325" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B325" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C325" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D325" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E325" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F325" t="s">
+        <v>47</v>
+      </c>
+      <c r="G325" t="s">
+        <v>32</v>
+      </c>
+      <c r="H325" t="s">
+        <v>13</v>
+      </c>
+      <c r="I325" t="s">
+        <v>140</v>
+      </c>
+      <c r="K325" t="s">
+        <v>54</v>
+      </c>
+      <c r="L325" t="s">
+        <v>178</v>
+      </c>
+      <c r="M325" t="s">
+        <v>48</v>
+      </c>
+      <c r="N325" t="s">
+        <v>14</v>
+      </c>
+      <c r="O325" t="s">
+        <v>15</v>
+      </c>
+      <c r="P325" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="326" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A326" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B326" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C326" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F326" t="s">
+        <v>47</v>
+      </c>
+      <c r="G326" t="s">
+        <v>32</v>
+      </c>
+      <c r="H326" t="s">
+        <v>13</v>
+      </c>
+      <c r="I326" t="s">
+        <v>140</v>
+      </c>
+      <c r="J326" t="s">
         <v>1510</v>
       </c>
-      <c r="K322" t="s">
+      <c r="K326" t="s">
         <v>54</v>
       </c>
-      <c r="L322" t="s">
+      <c r="L326" t="s">
         <v>278</v>
       </c>
-      <c r="M322" t="s">
+      <c r="M326" t="s">
         <v>829</v>
       </c>
-      <c r="N322" t="s">
-        <v>14</v>
-      </c>
-      <c r="O322" t="s">
-        <v>15</v>
-      </c>
-      <c r="P322" t="s">
+      <c r="N326" t="s">
+        <v>14</v>
+      </c>
+      <c r="O326" t="s">
+        <v>15</v>
+      </c>
+      <c r="P326" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="327" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A327" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B327" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C327" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F327" t="s">
+        <v>47</v>
+      </c>
+      <c r="G327" t="s">
+        <v>32</v>
+      </c>
+      <c r="H327" t="s">
+        <v>13</v>
+      </c>
+      <c r="I327" t="s">
+        <v>140</v>
+      </c>
+      <c r="J327" t="s">
+        <v>109</v>
+      </c>
+      <c r="L327" t="s">
+        <v>385</v>
+      </c>
+      <c r="M327" t="s">
+        <v>48</v>
+      </c>
+      <c r="N327" t="s">
+        <v>14</v>
+      </c>
+      <c r="O327" t="s">
+        <v>15</v>
+      </c>
+      <c r="P327" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="328" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A328" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B328" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C328" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F328" t="s">
+        <v>47</v>
+      </c>
+      <c r="G328" t="s">
+        <v>32</v>
+      </c>
+      <c r="H328" t="s">
+        <v>31</v>
+      </c>
+      <c r="I328" t="s">
+        <v>445</v>
+      </c>
+      <c r="J328" t="s">
+        <v>583</v>
+      </c>
+      <c r="K328" t="s">
+        <v>54</v>
+      </c>
+      <c r="L328" t="s">
+        <v>178</v>
+      </c>
+      <c r="M328" t="s">
+        <v>48</v>
+      </c>
+      <c r="N328" t="s">
+        <v>14</v>
+      </c>
+      <c r="O328" t="s">
+        <v>15</v>
+      </c>
+      <c r="P328" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9D9FA0-2A14-CD42-8E47-B873D430213D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7F570B-6FB1-FE49-8F78-31E2FE3C2947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -14979,7 +14979,7 @@
         <v>78</v>
       </c>
       <c r="G207" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="H207" t="s">
         <v>13</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7F570B-6FB1-FE49-8F78-31E2FE3C2947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27DA6C3-929F-A344-97B1-186B6B8E7BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -12686,7 +12686,7 @@
         <v>1028</v>
       </c>
       <c r="F160" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G160" t="s">
         <v>32</v>
@@ -14976,7 +14976,7 @@
         <v>961</v>
       </c>
       <c r="F207" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G207" t="s">
         <v>118</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27DA6C3-929F-A344-97B1-186B6B8E7BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8FFABB-0503-C14A-A059-46FDD5E6C10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
     <col min="6" max="6" width="8.5" customWidth="1"/>
     <col min="7" max="7" width="6.5" customWidth="1"/>
     <col min="8" max="8" width="11.1640625" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="29.6640625" customWidth="1"/>
     <col min="10" max="10" width="18.5" customWidth="1"/>
     <col min="11" max="11" width="19.1640625" customWidth="1"/>
     <col min="12" max="12" width="21.1640625" customWidth="1"/>
@@ -6495,7 +6495,7 @@
         <v>92</v>
       </c>
       <c r="M30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N30" t="s">
         <v>14</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F067A5D-96F1-4441-B9E9-B2CBCC0D2345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B48A061-3E45-3A42-828D-2D1A569CEC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -4714,9 +4714,6 @@
     <t>tiempos litúrgicos;educación;social;María</t>
   </si>
   <si>
-    <t>social;educación;tiempos litúrgicos;María, Jesús</t>
-  </si>
-  <si>
     <t>tiempos litúrgicos;María;Jesús</t>
   </si>
   <si>
@@ -4736,6 +4733,9 @@
   </si>
   <si>
     <t>social;educación;maristas</t>
+  </si>
+  <si>
+    <t>social;educación;tiempos litúrgicos;María;Jesús</t>
   </si>
 </sst>
 </file>
@@ -17168,7 +17168,7 @@
         <v>256</v>
       </c>
       <c r="J250" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="K250" t="s">
         <v>50</v>
@@ -17218,7 +17218,7 @@
         <v>102</v>
       </c>
       <c r="J251" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K251" t="s">
         <v>395</v>
@@ -17612,7 +17612,7 @@
         <v>134</v>
       </c>
       <c r="J259" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="K259" t="s">
         <v>70</v>
@@ -17941,7 +17941,7 @@
         <v>134</v>
       </c>
       <c r="J266" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L266" t="s">
         <v>368</v>
@@ -18338,7 +18338,7 @@
         <v>206</v>
       </c>
       <c r="J274" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="L274" t="s">
         <v>90</v>
@@ -18385,7 +18385,7 @@
         <v>424</v>
       </c>
       <c r="J275" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="L275" t="s">
         <v>90</v>
@@ -18532,7 +18532,7 @@
         <v>1256</v>
       </c>
       <c r="J278" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="K278" t="s">
         <v>133</v>
@@ -19205,7 +19205,7 @@
         <v>256</v>
       </c>
       <c r="J292" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="L292" t="s">
         <v>528</v>
@@ -19252,7 +19252,7 @@
         <v>256</v>
       </c>
       <c r="J293" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="L293" t="s">
         <v>368</v>
@@ -19834,7 +19834,7 @@
         <v>134</v>
       </c>
       <c r="J305" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="K305" t="s">
         <v>133</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B48A061-3E45-3A42-828D-2D1A569CEC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A06D280-8170-9A45-A17E-F1C5DE7D5630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -4684,39 +4684,6 @@
     <t>maristas;educación;social;violetas</t>
   </si>
   <si>
-    <t>educación;tiempos litúrgicos</t>
-  </si>
-  <si>
-    <t>maristas;educación;tiempos litúrgicos</t>
-  </si>
-  <si>
-    <t>evangelio;educación;maristas;tiempos litúrgicos</t>
-  </si>
-  <si>
-    <t>evangelio;tiempos litúrgicos</t>
-  </si>
-  <si>
-    <t>tiempos litúrgicos</t>
-  </si>
-  <si>
-    <t>evangelio;tiempos litúrgicos;Jesús</t>
-  </si>
-  <si>
-    <t>social;tiempos litúrgicos</t>
-  </si>
-  <si>
-    <t>tiempos litúrgicos;social;Jesús;violetas</t>
-  </si>
-  <si>
-    <t>tiempos litúrgicos;violetas;Jesús</t>
-  </si>
-  <si>
-    <t>tiempos litúrgicos;educación;social;María</t>
-  </si>
-  <si>
-    <t>tiempos litúrgicos;María;Jesús</t>
-  </si>
-  <si>
     <t>social;educación;paz</t>
   </si>
   <si>
@@ -4735,7 +4702,40 @@
     <t>social;educación;maristas</t>
   </si>
   <si>
-    <t>social;educación;tiempos litúrgicos;María;Jesús</t>
+    <t>maristas;educación;tiempos_liturgicos</t>
+  </si>
+  <si>
+    <t>evangelio;educación;maristas;tiempos_liturgicos</t>
+  </si>
+  <si>
+    <t>educación;tiempos_liturgicos</t>
+  </si>
+  <si>
+    <t>evangelio;tiempos_liturgicos</t>
+  </si>
+  <si>
+    <t>tiempos_liturgicos</t>
+  </si>
+  <si>
+    <t>evangelio;tiempos_liturgicos;Jesús</t>
+  </si>
+  <si>
+    <t>social;tiempos_liturgicos</t>
+  </si>
+  <si>
+    <t>tiempos_liturgicos;social;Jesús;violetas</t>
+  </si>
+  <si>
+    <t>tiempos_liturgicos;violetas;Jesús</t>
+  </si>
+  <si>
+    <t>tiempos_liturgicos;educación;social;María</t>
+  </si>
+  <si>
+    <t>social;educación;tiempos_liturgicos;María;Jesús</t>
+  </si>
+  <si>
+    <t>tiempos_liturgicos;María;Jesús</t>
   </si>
 </sst>
 </file>
@@ -15513,7 +15513,7 @@
         <v>256</v>
       </c>
       <c r="J216" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="K216" t="s">
         <v>70</v>
@@ -15563,7 +15563,7 @@
         <v>256</v>
       </c>
       <c r="J217" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="K217" t="s">
         <v>70</v>
@@ -15613,7 +15613,7 @@
         <v>310</v>
       </c>
       <c r="J218" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="K218" t="s">
         <v>70</v>
@@ -15663,7 +15663,7 @@
         <v>256</v>
       </c>
       <c r="J219" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="K219" t="s">
         <v>70</v>
@@ -15713,7 +15713,7 @@
         <v>256</v>
       </c>
       <c r="J220" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="K220" t="s">
         <v>194</v>
@@ -15763,7 +15763,7 @@
         <v>256</v>
       </c>
       <c r="J221" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="K221" t="s">
         <v>70</v>
@@ -15813,7 +15813,7 @@
         <v>256</v>
       </c>
       <c r="J222" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="K222" t="s">
         <v>70</v>
@@ -15863,7 +15863,7 @@
         <v>256</v>
       </c>
       <c r="J223" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="K223" t="s">
         <v>51</v>
@@ -15913,7 +15913,7 @@
         <v>256</v>
       </c>
       <c r="J224" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="K224" t="s">
         <v>51</v>
@@ -15963,7 +15963,7 @@
         <v>256</v>
       </c>
       <c r="J225" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="K225" t="s">
         <v>51</v>
@@ -16013,7 +16013,7 @@
         <v>256</v>
       </c>
       <c r="J226" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="K226" t="s">
         <v>133</v>
@@ -16063,7 +16063,7 @@
         <v>256</v>
       </c>
       <c r="J227" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="K227" t="s">
         <v>51</v>
@@ -16163,7 +16163,7 @@
         <v>424</v>
       </c>
       <c r="J229" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="K229" t="s">
         <v>395</v>
@@ -16213,7 +16213,7 @@
         <v>134</v>
       </c>
       <c r="J230" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
       <c r="K230" t="s">
         <v>133</v>
@@ -16263,7 +16263,7 @@
         <v>136</v>
       </c>
       <c r="J231" t="s">
-        <v>1559</v>
+        <v>1565</v>
       </c>
       <c r="L231" t="s">
         <v>172</v>
@@ -16357,7 +16357,7 @@
         <v>134</v>
       </c>
       <c r="J233" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="K233" t="s">
         <v>51</v>
@@ -16407,7 +16407,7 @@
         <v>134</v>
       </c>
       <c r="J234" t="s">
-        <v>1560</v>
+        <v>1566</v>
       </c>
       <c r="K234" t="s">
         <v>51</v>
@@ -16451,7 +16451,7 @@
         <v>424</v>
       </c>
       <c r="J235" t="s">
-        <v>1560</v>
+        <v>1566</v>
       </c>
       <c r="K235" t="s">
         <v>51</v>
@@ -16495,7 +16495,7 @@
         <v>424</v>
       </c>
       <c r="J236" t="s">
-        <v>1560</v>
+        <v>1566</v>
       </c>
       <c r="K236" t="s">
         <v>51</v>
@@ -16539,7 +16539,7 @@
         <v>424</v>
       </c>
       <c r="J237" t="s">
-        <v>1560</v>
+        <v>1566</v>
       </c>
       <c r="K237" t="s">
         <v>51</v>
@@ -16639,7 +16639,7 @@
         <v>1216</v>
       </c>
       <c r="J239" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="L239" t="s">
         <v>92</v>
@@ -16824,7 +16824,7 @@
         <v>310</v>
       </c>
       <c r="J243" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="K243" t="s">
         <v>70</v>
@@ -16874,7 +16874,7 @@
         <v>256</v>
       </c>
       <c r="J244" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="K244" t="s">
         <v>70</v>
@@ -16924,7 +16924,7 @@
         <v>103</v>
       </c>
       <c r="J245" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
       <c r="K245" t="s">
         <v>70</v>
@@ -16974,7 +16974,7 @@
         <v>134</v>
       </c>
       <c r="J246" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
       <c r="K246" t="s">
         <v>50</v>
@@ -17024,7 +17024,7 @@
         <v>134</v>
       </c>
       <c r="J247" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="L247" t="s">
         <v>457</v>
@@ -17071,7 +17071,7 @@
         <v>134</v>
       </c>
       <c r="J248" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="K248" t="s">
         <v>51</v>
@@ -17121,7 +17121,7 @@
         <v>134</v>
       </c>
       <c r="J249" t="s">
-        <v>1563</v>
+        <v>1569</v>
       </c>
       <c r="L249" t="s">
         <v>175</v>
@@ -17168,7 +17168,7 @@
         <v>256</v>
       </c>
       <c r="J250" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="K250" t="s">
         <v>50</v>
@@ -17218,7 +17218,7 @@
         <v>102</v>
       </c>
       <c r="J251" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="K251" t="s">
         <v>395</v>
@@ -17268,7 +17268,7 @@
         <v>136</v>
       </c>
       <c r="J252" t="s">
-        <v>1559</v>
+        <v>1565</v>
       </c>
       <c r="K252" t="s">
         <v>51</v>
@@ -17312,7 +17312,7 @@
         <v>424</v>
       </c>
       <c r="J253" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
       <c r="K253" t="s">
         <v>51</v>
@@ -17612,7 +17612,7 @@
         <v>134</v>
       </c>
       <c r="J259" t="s">
-        <v>1565</v>
+        <v>1554</v>
       </c>
       <c r="K259" t="s">
         <v>70</v>
@@ -17941,7 +17941,7 @@
         <v>134</v>
       </c>
       <c r="J266" t="s">
-        <v>1566</v>
+        <v>1555</v>
       </c>
       <c r="L266" t="s">
         <v>368</v>
@@ -18338,7 +18338,7 @@
         <v>206</v>
       </c>
       <c r="J274" t="s">
-        <v>1567</v>
+        <v>1556</v>
       </c>
       <c r="L274" t="s">
         <v>90</v>
@@ -18385,7 +18385,7 @@
         <v>424</v>
       </c>
       <c r="J275" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="L275" t="s">
         <v>90</v>
@@ -18532,7 +18532,7 @@
         <v>1256</v>
       </c>
       <c r="J278" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="K278" t="s">
         <v>133</v>
@@ -19205,7 +19205,7 @@
         <v>256</v>
       </c>
       <c r="J292" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="L292" t="s">
         <v>528</v>
@@ -19252,7 +19252,7 @@
         <v>256</v>
       </c>
       <c r="J293" t="s">
-        <v>1570</v>
+        <v>1559</v>
       </c>
       <c r="L293" t="s">
         <v>368</v>
@@ -19737,7 +19737,7 @@
         <v>205</v>
       </c>
       <c r="J303" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
       <c r="L303" t="s">
         <v>172</v>
@@ -19834,7 +19834,7 @@
         <v>134</v>
       </c>
       <c r="J305" t="s">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="K305" t="s">
         <v>133</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4673E36-D525-4047-A5AF-35895D77E0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446B6F8A-1EBF-F444-9749-D053D52B6B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5076" uniqueCount="1581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5076" uniqueCount="1582">
   <si>
     <t>id</t>
   </si>
@@ -4763,6 +4763,9 @@
   </si>
   <si>
     <t>Smug</t>
+  </si>
+  <si>
+    <t>ILU-0219</t>
   </si>
 </sst>
 </file>
@@ -20330,7 +20333,7 @@
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
-        <v>1475</v>
+        <v>1581</v>
       </c>
       <c r="B316" t="s">
         <v>1574</v>

--- a/data/PortfolioArTeV1.xlsx
+++ b/data/PortfolioArTeV1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturompw/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446B6F8A-1EBF-F444-9749-D053D52B6B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A143DCA-0225-1247-913F-0E3DA2DB0F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="600" windowWidth="22940" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5076" uniqueCount="1582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="1610">
   <si>
     <t>id</t>
   </si>
@@ -4766,6 +4766,90 @@
   </si>
   <si>
     <t>ILU-0219</t>
+  </si>
+  <si>
+    <t>ILU-0220</t>
+  </si>
+  <si>
+    <t>ILU-0221</t>
+  </si>
+  <si>
+    <t>ILU-0222</t>
+  </si>
+  <si>
+    <t>ILU-0223</t>
+  </si>
+  <si>
+    <t>ILU-0224</t>
+  </si>
+  <si>
+    <t>ILU-0225</t>
+  </si>
+  <si>
+    <t>En cartel lema MRE</t>
+  </si>
+  <si>
+    <t>In Anual Slogan poster MRE</t>
+  </si>
+  <si>
+    <t>Arturo_MP_MRE</t>
+  </si>
+  <si>
+    <t>Nubes</t>
+  </si>
+  <si>
+    <t>Lápices de colores</t>
+  </si>
+  <si>
+    <t>Corazón mandala</t>
+  </si>
+  <si>
+    <t>Goma (ita)</t>
+  </si>
+  <si>
+    <t>Libros y manzana (mundo)</t>
+  </si>
+  <si>
+    <t>Sacapuntas</t>
+  </si>
+  <si>
+    <t>Clouds</t>
+  </si>
+  <si>
+    <t>Color pencils</t>
+  </si>
+  <si>
+    <t>Mandala Heart</t>
+  </si>
+  <si>
+    <t>Apple and books</t>
+  </si>
+  <si>
+    <t>Eraser (it)</t>
+  </si>
+  <si>
+    <t>Pencil sharpener</t>
+  </si>
+  <si>
+    <t>maristas;educación;naturaleza</t>
+  </si>
+  <si>
+    <t>En cartel lema MRE 22-23</t>
+  </si>
+  <si>
+    <t>DIS-0111</t>
+  </si>
+  <si>
+    <t>Cartel lema MRE 22-23</t>
+  </si>
+  <si>
+    <t>Sonríe de corazón</t>
+  </si>
+  <si>
+    <t>Anual slogan poster MRE 22-23</t>
+  </si>
+  <si>
+    <t>Smile from heart</t>
   </si>
 </sst>
 </file>
@@ -5122,7 +5206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P330"/>
+  <dimension ref="A1:P337"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.5" customWidth="1"/>
@@ -5133,7 +5217,7 @@
     <col min="7" max="7" width="6.5" customWidth="1"/>
     <col min="8" max="8" width="11.1640625" customWidth="1"/>
     <col min="9" max="9" width="19.6640625" customWidth="1"/>
-    <col min="10" max="10" width="35.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="19.1640625" customWidth="1"/>
     <col min="12" max="12" width="11.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
@@ -14928,22 +15012,22 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>239</v>
+        <v>1605</v>
       </c>
       <c r="B204" t="s">
-        <v>393</v>
+        <v>1606</v>
       </c>
       <c r="C204" t="s">
-        <v>393</v>
+        <v>1608</v>
       </c>
       <c r="D204" t="s">
-        <v>557</v>
+        <v>1607</v>
       </c>
       <c r="E204" t="s">
-        <v>842</v>
+        <v>1609</v>
       </c>
       <c r="F204" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G204" t="s">
         <v>49</v>
@@ -14952,19 +15036,19 @@
         <v>13</v>
       </c>
       <c r="I204" t="s">
-        <v>255</v>
+        <v>1590</v>
       </c>
       <c r="J204" t="s">
-        <v>1551</v>
+        <v>1518</v>
       </c>
       <c r="K204" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="L204" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="M204" t="s">
-        <v>780</v>
+        <v>46</v>
       </c>
       <c r="N204" t="s">
         <v>14</v>
@@ -14978,43 +15062,43 @@
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>577</v>
+        <v>239</v>
       </c>
       <c r="B205" t="s">
-        <v>596</v>
+        <v>393</v>
       </c>
       <c r="C205" t="s">
-        <v>1110</v>
+        <v>393</v>
       </c>
       <c r="D205" t="s">
-        <v>597</v>
+        <v>557</v>
       </c>
       <c r="E205" t="s">
-        <v>912</v>
+        <v>842</v>
       </c>
       <c r="F205" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G205" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H205" t="s">
         <v>13</v>
       </c>
       <c r="I205" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="J205" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="K205" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L205" t="s">
-        <v>325</v>
+        <v>173</v>
       </c>
       <c r="M205" t="s">
-        <v>46</v>
+        <v>780</v>
       </c>
       <c r="N205" t="s">
         <v>14</v>
@@ -15028,13 +15112,13 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>1477</v>
+        <v>577</v>
       </c>
       <c r="B206" t="s">
-        <v>1483</v>
+        <v>596</v>
       </c>
       <c r="C206" t="s">
-        <v>1484</v>
+        <v>1110</v>
       </c>
       <c r="D206" t="s">
         <v>597</v>
@@ -15043,10 +15127,10 @@
         <v>912</v>
       </c>
       <c r="F206" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G206" t="s">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="H206" t="s">
         <v>13</v>
@@ -15061,7 +15145,7 @@
         <v>126</v>
       </c>
       <c r="L206" t="s">
-        <v>172</v>
+        <v>325</v>
       </c>
       <c r="M206" t="s">
         <v>46</v>
@@ -15078,37 +15162,40 @@
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>285</v>
+        <v>1477</v>
       </c>
       <c r="B207" t="s">
-        <v>305</v>
+        <v>1483</v>
       </c>
       <c r="C207" t="s">
-        <v>1113</v>
+        <v>1484</v>
       </c>
       <c r="D207" t="s">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="E207" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="F207" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G207" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="H207" t="s">
         <v>13</v>
       </c>
       <c r="I207" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="J207" t="s">
-        <v>104</v>
+        <v>1550</v>
+      </c>
+      <c r="K207" t="s">
+        <v>126</v>
       </c>
       <c r="L207" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="M207" t="s">
         <v>46</v>
@@ -15125,40 +15212,37 @@
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>1474</v>
+        <v>285</v>
       </c>
       <c r="B208" t="s">
-        <v>1492</v>
+        <v>305</v>
       </c>
       <c r="C208" t="s">
         <v>1113</v>
       </c>
       <c r="D208" t="s">
-        <v>1493</v>
+        <v>558</v>
       </c>
       <c r="E208" t="s">
-        <v>1494</v>
+        <v>916</v>
       </c>
       <c r="F208" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G208" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H208" t="s">
         <v>13</v>
       </c>
       <c r="I208" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="J208" t="s">
         <v>104</v>
       </c>
-      <c r="K208" t="s">
-        <v>51</v>
-      </c>
       <c r="L208" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M208" t="s">
         <v>46</v>
@@ -15175,19 +15259,19 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>559</v>
+        <v>1474</v>
       </c>
       <c r="B209" t="s">
-        <v>599</v>
+        <v>1492</v>
       </c>
       <c r="C209" t="s">
-        <v>1146</v>
+        <v>1113</v>
       </c>
       <c r="D209" t="s">
-        <v>600</v>
+        <v>1493</v>
       </c>
       <c r="E209" t="s">
-        <v>944</v>
+        <v>1494</v>
       </c>
       <c r="F209" t="s">
         <v>45</v>
@@ -15201,6 +15285,12 @@
       <c r="I209" t="s">
         <v>134</v>
       </c>
+      <c r="J209" t="s">
+        <v>104</v>
+      </c>
+      <c r="K209" t="s">
+        <v>51</v>
+      </c>
       <c r="L209" t="s">
         <v>172</v>
       </c>
@@ -15219,43 +15309,37 @@
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>283</v>
+        <v>559</v>
       </c>
       <c r="B210" t="s">
-        <v>300</v>
+        <v>599</v>
       </c>
       <c r="C210" t="s">
-        <v>1112</v>
+        <v>1146</v>
       </c>
       <c r="D210" t="s">
-        <v>301</v>
+        <v>600</v>
       </c>
       <c r="E210" t="s">
-        <v>985</v>
+        <v>944</v>
       </c>
       <c r="F210" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G210" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H210" t="s">
         <v>13</v>
       </c>
       <c r="I210" t="s">
-        <v>302</v>
-      </c>
-      <c r="J210" t="s">
-        <v>455</v>
-      </c>
-      <c r="K210" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="L210" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="M210" t="s">
-        <v>781</v>
+        <v>46</v>
       </c>
       <c r="N210" t="s">
         <v>14</v>
@@ -15269,22 +15353,22 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="B211" t="s">
-        <v>723</v>
+        <v>300</v>
       </c>
       <c r="C211" t="s">
-        <v>723</v>
+        <v>1112</v>
       </c>
       <c r="D211" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="E211" t="s">
-        <v>844</v>
+        <v>985</v>
       </c>
       <c r="F211" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G211" t="s">
         <v>49</v>
@@ -15293,19 +15377,19 @@
         <v>13</v>
       </c>
       <c r="I211" t="s">
-        <v>134</v>
+        <v>302</v>
       </c>
       <c r="J211" t="s">
-        <v>303</v>
+        <v>455</v>
       </c>
       <c r="K211" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="L211" t="s">
-        <v>266</v>
+        <v>178</v>
       </c>
       <c r="M211" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N211" t="s">
         <v>14</v>
@@ -15319,25 +15403,25 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="B212" t="s">
-        <v>313</v>
+        <v>723</v>
       </c>
       <c r="C212" t="s">
-        <v>1120</v>
+        <v>723</v>
       </c>
       <c r="D212" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
       <c r="E212" t="s">
-        <v>920</v>
+        <v>844</v>
       </c>
       <c r="F212" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G212" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H212" t="s">
         <v>13</v>
@@ -15346,16 +15430,16 @@
         <v>134</v>
       </c>
       <c r="J212" t="s">
-        <v>455</v>
+        <v>303</v>
       </c>
       <c r="K212" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L212" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="M212" t="s">
-        <v>46</v>
+        <v>780</v>
       </c>
       <c r="N212" t="s">
         <v>14</v>
@@ -15369,25 +15453,25 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>1479</v>
+        <v>291</v>
       </c>
       <c r="B213" t="s">
-        <v>1480</v>
+        <v>313</v>
       </c>
       <c r="C213" t="s">
-        <v>1481</v>
+        <v>1120</v>
       </c>
       <c r="D213" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E213" t="s">
-        <v>1482</v>
+        <v>920</v>
       </c>
       <c r="F213" t="s">
         <v>73</v>
       </c>
       <c r="G213" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H213" t="s">
         <v>13</v>
@@ -15398,8 +15482,11 @@
       <c r="J213" t="s">
         <v>455</v>
       </c>
+      <c r="K213" t="s">
+        <v>126</v>
+      </c>
       <c r="L213" t="s">
-        <v>92</v>
+        <v>315</v>
       </c>
       <c r="M213" t="s">
         <v>46</v>
@@ -15416,19 +15503,19 @@
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>512</v>
+        <v>1479</v>
       </c>
       <c r="B214" t="s">
-        <v>754</v>
+        <v>1480</v>
       </c>
       <c r="C214" t="s">
-        <v>1132</v>
+        <v>1481</v>
       </c>
       <c r="D214" t="s">
-        <v>516</v>
+        <v>301</v>
       </c>
       <c r="E214" t="s">
-        <v>932</v>
+        <v>1482</v>
       </c>
       <c r="F214" t="s">
         <v>73</v>
@@ -15445,14 +15532,11 @@
       <c r="J214" t="s">
         <v>455</v>
       </c>
-      <c r="K214" t="s">
-        <v>51</v>
-      </c>
       <c r="L214" t="s">
-        <v>529</v>
+        <v>92</v>
       </c>
       <c r="M214" t="s">
-        <v>781</v>
+        <v>46</v>
       </c>
       <c r="N214" t="s">
         <v>14</v>
@@ -15466,19 +15550,19 @@
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>282</v>
+        <v>512</v>
       </c>
       <c r="B215" t="s">
-        <v>299</v>
+        <v>754</v>
       </c>
       <c r="C215" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
       <c r="D215" t="s">
-        <v>744</v>
+        <v>516</v>
       </c>
       <c r="E215" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="F215" t="s">
         <v>73</v>
@@ -15490,19 +15574,19 @@
         <v>13</v>
       </c>
       <c r="I215" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="J215" t="s">
-        <v>1558</v>
+        <v>455</v>
       </c>
       <c r="K215" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L215" t="s">
-        <v>175</v>
+        <v>529</v>
       </c>
       <c r="M215" t="s">
-        <v>46</v>
+        <v>781</v>
       </c>
       <c r="N215" t="s">
         <v>14</v>
@@ -15516,19 +15600,19 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B216" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C216" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D216" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E216" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F216" t="s">
         <v>73</v>
@@ -15549,7 +15633,7 @@
         <v>70</v>
       </c>
       <c r="L216" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="M216" t="s">
         <v>46</v>
@@ -15566,19 +15650,19 @@
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>1417</v>
+        <v>286</v>
       </c>
       <c r="B217" t="s">
-        <v>1421</v>
+        <v>306</v>
       </c>
       <c r="C217" t="s">
-        <v>1422</v>
+        <v>1115</v>
       </c>
       <c r="D217" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E217" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F217" t="s">
         <v>73</v>
@@ -15590,7 +15674,7 @@
         <v>13</v>
       </c>
       <c r="I217" t="s">
-        <v>310</v>
+        <v>256</v>
       </c>
       <c r="J217" t="s">
         <v>1558</v>
@@ -15616,13 +15700,13 @@
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>546</v>
+        <v>1417</v>
       </c>
       <c r="B218" t="s">
-        <v>552</v>
+        <v>1421</v>
       </c>
       <c r="C218" t="s">
-        <v>1117</v>
+        <v>1422</v>
       </c>
       <c r="D218" t="s">
         <v>744</v>
@@ -15640,10 +15724,10 @@
         <v>13</v>
       </c>
       <c r="I218" t="s">
-        <v>256</v>
+        <v>310</v>
       </c>
       <c r="J218" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="K218" t="s">
         <v>70</v>
@@ -15666,40 +15750,40 @@
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>1221</v>
+        <v>546</v>
       </c>
       <c r="B219" t="s">
-        <v>1246</v>
+        <v>552</v>
       </c>
       <c r="C219" t="s">
-        <v>1247</v>
+        <v>1117</v>
       </c>
       <c r="D219" t="s">
-        <v>1248</v>
+        <v>744</v>
       </c>
       <c r="E219" t="s">
-        <v>1248</v>
+        <v>917</v>
       </c>
       <c r="F219" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G219" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H219" t="s">
         <v>13</v>
       </c>
       <c r="I219" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="J219" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="K219" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="L219" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="M219" t="s">
         <v>46</v>
@@ -15716,40 +15800,40 @@
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>289</v>
+        <v>1221</v>
       </c>
       <c r="B220" t="s">
-        <v>311</v>
+        <v>1246</v>
       </c>
       <c r="C220" t="s">
-        <v>1118</v>
+        <v>1247</v>
       </c>
       <c r="D220" t="s">
-        <v>744</v>
+        <v>1248</v>
       </c>
       <c r="E220" t="s">
-        <v>917</v>
+        <v>1248</v>
       </c>
       <c r="F220" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G220" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H220" t="s">
         <v>13</v>
       </c>
       <c r="I220" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="J220" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="K220" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="L220" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="M220" t="s">
         <v>46</v>
@@ -15766,19 +15850,19 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B221" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C221" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D221" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E221" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F221" t="s">
         <v>73</v>
@@ -15816,43 +15900,43 @@
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>1220</v>
+        <v>290</v>
       </c>
       <c r="B222" t="s">
-        <v>1244</v>
+        <v>312</v>
       </c>
       <c r="C222" t="s">
-        <v>1245</v>
+        <v>1119</v>
       </c>
       <c r="D222" t="s">
-        <v>1191</v>
+        <v>746</v>
       </c>
       <c r="E222" t="s">
-        <v>1193</v>
+        <v>918</v>
       </c>
       <c r="F222" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G222" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H222" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I222" t="s">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="J222" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="K222" t="s">
-        <v>395</v>
+        <v>70</v>
       </c>
       <c r="L222" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="M222" t="s">
-        <v>781</v>
+        <v>46</v>
       </c>
       <c r="N222" t="s">
         <v>14</v>
@@ -15866,13 +15950,13 @@
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>1182</v>
+        <v>1220</v>
       </c>
       <c r="B223" t="s">
-        <v>1190</v>
+        <v>1244</v>
       </c>
       <c r="C223" t="s">
-        <v>1192</v>
+        <v>1245</v>
       </c>
       <c r="D223" t="s">
         <v>1191</v>
@@ -15887,22 +15971,22 @@
         <v>31</v>
       </c>
       <c r="H223" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I223" t="s">
-        <v>134</v>
+        <v>424</v>
       </c>
       <c r="J223" t="s">
         <v>1561</v>
       </c>
       <c r="K223" t="s">
-        <v>51</v>
+        <v>395</v>
       </c>
       <c r="L223" t="s">
         <v>172</v>
       </c>
       <c r="M223" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N223" t="s">
         <v>14</v>
@@ -15916,13 +16000,13 @@
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B224" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="C224" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="D224" t="s">
         <v>1191</v>
@@ -15943,7 +16027,7 @@
         <v>134</v>
       </c>
       <c r="J224" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="K224" t="s">
         <v>51</v>
@@ -15952,7 +16036,7 @@
         <v>172</v>
       </c>
       <c r="M224" t="s">
-        <v>46</v>
+        <v>780</v>
       </c>
       <c r="N224" t="s">
         <v>14</v>
@@ -15966,13 +16050,19 @@
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>1400</v>
+        <v>1183</v>
       </c>
       <c r="B225" t="s">
-        <v>1405</v>
+        <v>1194</v>
       </c>
       <c r="C225" t="s">
-        <v>1408</v>
+        <v>1195</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E225" t="s">
+        <v>1193</v>
       </c>
       <c r="F225" t="s">
         <v>45</v>
@@ -15981,10 +16071,10 @@
         <v>31</v>
       </c>
       <c r="H225" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I225" t="s">
-        <v>424</v>
+        <v>134</v>
       </c>
       <c r="J225" t="s">
         <v>1564</v>
@@ -16010,13 +16100,13 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B226" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C226" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="F226" t="s">
         <v>45</v>
@@ -16054,13 +16144,13 @@
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B227" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C227" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="F227" t="s">
         <v>45</v>
@@ -16098,37 +16188,31 @@
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>667</v>
+        <v>1402</v>
       </c>
       <c r="B228" t="s">
-        <v>690</v>
+        <v>1407</v>
       </c>
       <c r="C228" t="s">
-        <v>1161</v>
-      </c>
-      <c r="D228" t="s">
-        <v>695</v>
-      </c>
-      <c r="E228" t="s">
-        <v>963</v>
+        <v>1410</v>
       </c>
       <c r="F228" t="s">
         <v>45</v>
       </c>
       <c r="G228" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H228" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I228" t="s">
-        <v>256</v>
+        <v>424</v>
       </c>
       <c r="J228" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="K228" t="s">
-        <v>194</v>
+        <v>51</v>
       </c>
       <c r="L228" t="s">
         <v>172</v>
@@ -16148,25 +16232,25 @@
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B229" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C229" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D229" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E229" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F229" t="s">
         <v>45</v>
       </c>
       <c r="G229" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H229" t="s">
         <v>13</v>
@@ -16175,10 +16259,10 @@
         <v>256</v>
       </c>
       <c r="J229" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="K229" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="L229" t="s">
         <v>172</v>
@@ -16198,13 +16282,13 @@
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B230" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C230" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D230" t="s">
         <v>696</v>
@@ -16248,13 +16332,13 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B231" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C231" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D231" t="s">
         <v>696</v>
@@ -16298,13 +16382,13 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B232" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C232" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D232" t="s">
         <v>696</v>
@@ -16328,7 +16412,7 @@
         <v>1561</v>
       </c>
       <c r="K232" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="L232" t="s">
         <v>172</v>
@@ -16348,13 +16432,13 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="B233" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="C233" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D233" t="s">
         <v>696</v>
@@ -16378,7 +16462,7 @@
         <v>1561</v>
       </c>
       <c r="K233" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="L233" t="s">
         <v>172</v>
@@ -16398,19 +16482,19 @@
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>534</v>
+        <v>679</v>
       </c>
       <c r="B234" t="s">
-        <v>540</v>
+        <v>680</v>
       </c>
       <c r="C234" t="s">
-        <v>1137</v>
+        <v>1166</v>
       </c>
       <c r="D234" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="E234" t="s">
-        <v>935</v>
+        <v>964</v>
       </c>
       <c r="F234" t="s">
         <v>45</v>
@@ -16419,16 +16503,16 @@
         <v>31</v>
       </c>
       <c r="H234" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I234" t="s">
-        <v>541</v>
+        <v>256</v>
       </c>
       <c r="J234" t="s">
-        <v>1532</v>
+        <v>1561</v>
       </c>
       <c r="K234" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L234" t="s">
         <v>172</v>
@@ -16448,34 +16532,37 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="B235" t="s">
-        <v>611</v>
+        <v>540</v>
       </c>
       <c r="C235" t="s">
-        <v>1149</v>
+        <v>1137</v>
       </c>
       <c r="D235" t="s">
-        <v>765</v>
+        <v>548</v>
       </c>
       <c r="E235" t="s">
-        <v>951</v>
+        <v>935</v>
       </c>
       <c r="F235" t="s">
         <v>45</v>
       </c>
       <c r="G235" t="s">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="H235" t="s">
         <v>30</v>
       </c>
       <c r="I235" t="s">
-        <v>136</v>
+        <v>541</v>
       </c>
       <c r="J235" t="s">
-        <v>1563</v>
+        <v>1532</v>
+      </c>
+      <c r="K235" t="s">
+        <v>70</v>
       </c>
       <c r="L235" t="s">
         <v>172</v>
@@ -16495,37 +16582,34 @@
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>1403</v>
+        <v>568</v>
       </c>
       <c r="B236" t="s">
-        <v>1411</v>
+        <v>611</v>
       </c>
       <c r="C236" t="s">
-        <v>1412</v>
+        <v>1149</v>
       </c>
       <c r="D236" t="s">
-        <v>1413</v>
+        <v>765</v>
       </c>
       <c r="E236" t="s">
-        <v>1414</v>
+        <v>951</v>
       </c>
       <c r="F236" t="s">
         <v>45</v>
       </c>
       <c r="G236" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="H236" t="s">
         <v>30</v>
       </c>
       <c r="I236" t="s">
-        <v>424</v>
+        <v>136</v>
       </c>
       <c r="J236" t="s">
-        <v>264</v>
-      </c>
-      <c r="K236" t="s">
-        <v>51</v>
+        <v>1563</v>
       </c>
       <c r="L236" t="s">
         <v>172</v>
@@ -16545,19 +16629,19 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>617</v>
+        <v>1403</v>
       </c>
       <c r="B237" t="s">
-        <v>635</v>
+        <v>1411</v>
       </c>
       <c r="C237" t="s">
-        <v>1152</v>
+        <v>1412</v>
       </c>
       <c r="D237" t="s">
-        <v>636</v>
+        <v>1413</v>
       </c>
       <c r="E237" t="s">
-        <v>954</v>
+        <v>1414</v>
       </c>
       <c r="F237" t="s">
         <v>45</v>
@@ -16566,16 +16650,19 @@
         <v>31</v>
       </c>
       <c r="H237" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I237" t="s">
-        <v>134</v>
+        <v>424</v>
       </c>
       <c r="J237" t="s">
-        <v>293</v>
+        <v>264</v>
+      </c>
+      <c r="K237" t="s">
+        <v>51</v>
       </c>
       <c r="L237" t="s">
-        <v>325</v>
+        <v>172</v>
       </c>
       <c r="M237" t="s">
         <v>46</v>
@@ -16592,43 +16679,40 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>1274</v>
+        <v>617</v>
       </c>
       <c r="B238" t="s">
-        <v>1298</v>
+        <v>635</v>
       </c>
       <c r="C238" t="s">
-        <v>1299</v>
+        <v>1152</v>
       </c>
       <c r="D238" t="s">
-        <v>1302</v>
+        <v>636</v>
       </c>
       <c r="E238" t="s">
-        <v>1303</v>
+        <v>954</v>
       </c>
       <c r="F238" t="s">
         <v>45</v>
       </c>
       <c r="G238" t="s">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="H238" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I238" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="J238" t="s">
-        <v>264</v>
-      </c>
-      <c r="K238" t="s">
-        <v>51</v>
+        <v>293</v>
       </c>
       <c r="L238" t="s">
-        <v>172</v>
+        <v>325</v>
       </c>
       <c r="M238" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N238" t="s">
         <v>14</v>
@@ -16642,40 +16726,43 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>1207</v>
+        <v>1274</v>
       </c>
       <c r="B239" t="s">
-        <v>1210</v>
+        <v>1298</v>
       </c>
       <c r="C239" t="s">
-        <v>1212</v>
+        <v>1299</v>
       </c>
       <c r="D239" t="s">
-        <v>636</v>
+        <v>1302</v>
       </c>
       <c r="E239" t="s">
-        <v>954</v>
+        <v>1303</v>
       </c>
       <c r="F239" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G239" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="H239" t="s">
         <v>30</v>
       </c>
       <c r="I239" t="s">
-        <v>1215</v>
+        <v>102</v>
       </c>
       <c r="J239" t="s">
-        <v>1561</v>
+        <v>264</v>
+      </c>
+      <c r="K239" t="s">
+        <v>51</v>
       </c>
       <c r="L239" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="M239" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N239" t="s">
         <v>14</v>
@@ -16689,40 +16776,40 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>244</v>
+        <v>1207</v>
       </c>
       <c r="B240" t="s">
-        <v>268</v>
+        <v>1210</v>
       </c>
       <c r="C240" t="s">
-        <v>1036</v>
+        <v>1212</v>
       </c>
       <c r="D240" t="s">
-        <v>269</v>
+        <v>636</v>
       </c>
       <c r="E240" t="s">
-        <v>845</v>
+        <v>954</v>
       </c>
       <c r="F240" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G240" t="s">
         <v>31</v>
       </c>
       <c r="H240" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I240" t="s">
-        <v>134</v>
+        <v>1215</v>
       </c>
       <c r="J240" t="s">
-        <v>104</v>
+        <v>1561</v>
       </c>
       <c r="L240" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M240" t="s">
-        <v>781</v>
+        <v>46</v>
       </c>
       <c r="N240" t="s">
         <v>14</v>
@@ -16736,13 +16823,19 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>1226</v>
+        <v>244</v>
       </c>
       <c r="B241" t="s">
-        <v>1258</v>
+        <v>268</v>
       </c>
       <c r="C241" t="s">
-        <v>1259</v>
+        <v>1036</v>
+      </c>
+      <c r="D241" t="s">
+        <v>269</v>
+      </c>
+      <c r="E241" t="s">
+        <v>845</v>
       </c>
       <c r="F241" t="s">
         <v>45</v>
@@ -16763,7 +16856,7 @@
         <v>90</v>
       </c>
       <c r="M241" t="s">
-        <v>46</v>
+        <v>781</v>
       </c>
       <c r="N241" t="s">
         <v>14</v>
@@ -16777,40 +16870,31 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>288</v>
+        <v>1226</v>
       </c>
       <c r="B242" t="s">
-        <v>309</v>
+        <v>1258</v>
       </c>
       <c r="C242" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D242" t="s">
-        <v>747</v>
-      </c>
-      <c r="E242" t="s">
-        <v>919</v>
+        <v>1259</v>
       </c>
       <c r="F242" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G242" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H242" t="s">
         <v>13</v>
       </c>
       <c r="I242" t="s">
-        <v>310</v>
+        <v>134</v>
       </c>
       <c r="J242" t="s">
-        <v>1560</v>
-      </c>
-      <c r="K242" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="L242" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M242" t="s">
         <v>46</v>
@@ -16827,13 +16911,13 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>1418</v>
+        <v>288</v>
       </c>
       <c r="B243" t="s">
-        <v>1419</v>
+        <v>309</v>
       </c>
       <c r="C243" t="s">
-        <v>1420</v>
+        <v>1116</v>
       </c>
       <c r="D243" t="s">
         <v>747</v>
@@ -16851,7 +16935,7 @@
         <v>13</v>
       </c>
       <c r="I243" t="s">
-        <v>256</v>
+        <v>310</v>
       </c>
       <c r="J243" t="s">
         <v>1560</v>
@@ -16877,22 +16961,22 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>619</v>
+        <v>1418</v>
       </c>
       <c r="B244" t="s">
-        <v>639</v>
+        <v>1419</v>
       </c>
       <c r="C244" t="s">
-        <v>1153</v>
+        <v>1420</v>
       </c>
       <c r="D244" t="s">
-        <v>640</v>
+        <v>747</v>
       </c>
       <c r="E244" t="s">
-        <v>956</v>
+        <v>919</v>
       </c>
       <c r="F244" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G244" t="s">
         <v>49</v>
@@ -16901,16 +16985,16 @@
         <v>13</v>
       </c>
       <c r="I244" t="s">
-        <v>103</v>
+        <v>256</v>
       </c>
       <c r="J244" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="K244" t="s">
         <v>70</v>
       </c>
       <c r="L244" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="M244" t="s">
         <v>46</v>
@@ -16927,43 +17011,43 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>235</v>
+        <v>619</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>639</v>
       </c>
       <c r="C245" t="s">
-        <v>1030</v>
+        <v>1153</v>
       </c>
       <c r="D245" t="s">
-        <v>246</v>
+        <v>640</v>
       </c>
       <c r="E245" t="s">
-        <v>973</v>
+        <v>956</v>
       </c>
       <c r="F245" t="s">
         <v>45</v>
       </c>
       <c r="G245" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H245" t="s">
         <v>13</v>
       </c>
       <c r="I245" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="J245" t="s">
         <v>1562</v>
       </c>
       <c r="K245" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="L245" t="s">
-        <v>253</v>
+        <v>172</v>
       </c>
       <c r="M245" t="s">
-        <v>781</v>
+        <v>46</v>
       </c>
       <c r="N245" t="s">
         <v>14</v>
@@ -16977,22 +17061,22 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>389</v>
+        <v>235</v>
       </c>
       <c r="B246" t="s">
-        <v>750</v>
+        <v>245</v>
       </c>
       <c r="C246" t="s">
-        <v>1125</v>
+        <v>1030</v>
       </c>
       <c r="D246" t="s">
-        <v>751</v>
+        <v>246</v>
       </c>
       <c r="E246" t="s">
-        <v>924</v>
+        <v>973</v>
       </c>
       <c r="F246" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G246" t="s">
         <v>31</v>
@@ -17004,13 +17088,16 @@
         <v>134</v>
       </c>
       <c r="J246" t="s">
-        <v>1567</v>
+        <v>1562</v>
+      </c>
+      <c r="K246" t="s">
+        <v>50</v>
       </c>
       <c r="L246" t="s">
-        <v>175</v>
+        <v>253</v>
       </c>
       <c r="M246" t="s">
-        <v>46</v>
+        <v>781</v>
       </c>
       <c r="N246" t="s">
         <v>14</v>
@@ -17024,34 +17111,37 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>1404</v>
+        <v>389</v>
       </c>
       <c r="B247" t="s">
-        <v>1415</v>
+        <v>750</v>
       </c>
       <c r="C247" t="s">
-        <v>1416</v>
+        <v>1125</v>
+      </c>
+      <c r="D247" t="s">
+        <v>751</v>
+      </c>
+      <c r="E247" t="s">
+        <v>924</v>
       </c>
       <c r="F247" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G247" t="s">
         <v>31</v>
       </c>
       <c r="H247" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I247" t="s">
-        <v>424</v>
+        <v>134</v>
       </c>
       <c r="J247" t="s">
-        <v>1562</v>
-      </c>
-      <c r="K247" t="s">
-        <v>51</v>
+        <v>1567</v>
       </c>
       <c r="L247" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="M247" t="s">
         <v>46</v>
@@ -17068,37 +17158,34 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>439</v>
+        <v>1404</v>
       </c>
       <c r="B248" t="s">
-        <v>752</v>
+        <v>1415</v>
       </c>
       <c r="C248" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D248" t="s">
-        <v>447</v>
-      </c>
-      <c r="E248" t="s">
-        <v>927</v>
+        <v>1416</v>
       </c>
       <c r="F248" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G248" t="s">
         <v>31</v>
       </c>
       <c r="H248" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I248" t="s">
-        <v>134</v>
+        <v>424</v>
       </c>
       <c r="J248" t="s">
-        <v>1565</v>
+        <v>1562</v>
+      </c>
+      <c r="K248" t="s">
+        <v>51</v>
       </c>
       <c r="L248" t="s">
-        <v>457</v>
+        <v>172</v>
       </c>
       <c r="M248" t="s">
         <v>46</v>
@@ -17115,22 +17202,22 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>240</v>
+        <v>439</v>
       </c>
       <c r="B249" t="s">
-        <v>261</v>
+        <v>752</v>
       </c>
       <c r="C249" t="s">
-        <v>1033</v>
+        <v>1127</v>
       </c>
       <c r="D249" t="s">
-        <v>262</v>
+        <v>447</v>
       </c>
       <c r="E249" t="s">
-        <v>974</v>
+        <v>927</v>
       </c>
       <c r="F249" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G249" t="s">
         <v>31</v>
@@ -17142,13 +17229,10 @@
         <v>134</v>
       </c>
       <c r="J249" t="s">
-        <v>1566</v>
-      </c>
-      <c r="K249" t="s">
-        <v>51</v>
+        <v>1565</v>
       </c>
       <c r="L249" t="s">
-        <v>90</v>
+        <v>457</v>
       </c>
       <c r="M249" t="s">
         <v>46</v>
@@ -17165,19 +17249,19 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>462</v>
+        <v>240</v>
       </c>
       <c r="B250" t="s">
-        <v>468</v>
+        <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>1067</v>
+        <v>1033</v>
       </c>
       <c r="D250" t="s">
-        <v>469</v>
+        <v>262</v>
       </c>
       <c r="E250" t="s">
-        <v>872</v>
+        <v>974</v>
       </c>
       <c r="F250" t="s">
         <v>45</v>
@@ -17186,19 +17270,19 @@
         <v>31</v>
       </c>
       <c r="H250" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I250" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J250" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K250" t="s">
         <v>51</v>
       </c>
       <c r="L250" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M250" t="s">
         <v>46</v>
@@ -17215,40 +17299,40 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>544</v>
+        <v>462</v>
       </c>
       <c r="B251" t="s">
-        <v>550</v>
+        <v>468</v>
       </c>
       <c r="C251" t="s">
-        <v>1139</v>
+        <v>1067</v>
       </c>
       <c r="D251" t="s">
-        <v>551</v>
+        <v>469</v>
       </c>
       <c r="E251" t="s">
-        <v>937</v>
+        <v>872</v>
       </c>
       <c r="F251" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G251" t="s">
         <v>31</v>
       </c>
       <c r="H251" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I251" t="s">
-        <v>256</v>
+        <v>136</v>
       </c>
       <c r="J251" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="K251" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L251" t="s">
-        <v>457</v>
+        <v>172</v>
       </c>
       <c r="M251" t="s">
         <v>46</v>
@@ -17265,40 +17349,40 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>623</v>
+        <v>544</v>
       </c>
       <c r="B252" t="s">
-        <v>643</v>
+        <v>550</v>
       </c>
       <c r="C252" t="s">
-        <v>1155</v>
+        <v>1139</v>
       </c>
       <c r="D252" t="s">
-        <v>644</v>
+        <v>551</v>
       </c>
       <c r="E252" t="s">
-        <v>958</v>
+        <v>937</v>
       </c>
       <c r="F252" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G252" t="s">
         <v>31</v>
       </c>
       <c r="H252" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I252" t="s">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="J252" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="K252" t="s">
-        <v>395</v>
+        <v>50</v>
       </c>
       <c r="L252" t="s">
-        <v>172</v>
+        <v>457</v>
       </c>
       <c r="M252" t="s">
         <v>46</v>
@@ -17315,40 +17399,40 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>437</v>
+        <v>623</v>
       </c>
       <c r="B253" t="s">
-        <v>444</v>
+        <v>643</v>
       </c>
       <c r="C253" t="s">
-        <v>1126</v>
+        <v>1155</v>
       </c>
       <c r="D253" t="s">
-        <v>445</v>
+        <v>644</v>
       </c>
       <c r="E253" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
       <c r="F253" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G253" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H253" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I253" t="s">
-        <v>256</v>
+        <v>102</v>
       </c>
       <c r="J253" t="s">
-        <v>293</v>
+        <v>1569</v>
       </c>
       <c r="K253" t="s">
-        <v>70</v>
+        <v>395</v>
       </c>
       <c r="L253" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="M253" t="s">
         <v>46</v>
@@ -17365,43 +17449,43 @@
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="B254" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="C254" t="s">
-        <v>1055</v>
+        <v>1126</v>
       </c>
       <c r="D254" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E254" t="s">
-        <v>863</v>
+        <v>926</v>
       </c>
       <c r="F254" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G254" t="s">
         <v>49</v>
       </c>
       <c r="H254" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I254" t="s">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="J254" t="s">
-        <v>1524</v>
+        <v>293</v>
       </c>
       <c r="K254" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="L254" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M254" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N254" t="s">
         <v>14</v>
@@ -17415,34 +17499,34 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B255" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C255" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D255" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="E255" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="F255" t="s">
         <v>45</v>
       </c>
       <c r="G255" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H255" t="s">
         <v>30</v>
       </c>
       <c r="I255" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="J255" t="s">
-        <v>1577</v>
+        <v>1524</v>
       </c>
       <c r="K255" t="s">
         <v>51</v>
@@ -17451,7 +17535,7 @@
         <v>172</v>
       </c>
       <c r="M255" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N255" t="s">
         <v>14</v>
@@ -17465,43 +17549,43 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>545</v>
+        <v>417</v>
       </c>
       <c r="B256" t="s">
-        <v>553</v>
+        <v>432</v>
       </c>
       <c r="C256" t="s">
-        <v>1140</v>
+        <v>1057</v>
       </c>
       <c r="D256" t="s">
-        <v>554</v>
+        <v>433</v>
       </c>
       <c r="E256" t="s">
-        <v>938</v>
+        <v>865</v>
       </c>
       <c r="F256" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G256" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H256" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I256" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J256" t="s">
-        <v>1552</v>
+        <v>1577</v>
       </c>
       <c r="K256" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L256" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="M256" t="s">
-        <v>780</v>
+        <v>46</v>
       </c>
       <c r="N256" t="s">
         <v>14</v>
@@ -17515,40 +17599,43 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>1187</v>
+        <v>545</v>
       </c>
       <c r="B257" t="s">
-        <v>1203</v>
+        <v>553</v>
       </c>
       <c r="C257" t="s">
-        <v>1204</v>
+        <v>1140</v>
       </c>
       <c r="D257" t="s">
-        <v>433</v>
+        <v>554</v>
       </c>
       <c r="E257" t="s">
-        <v>865</v>
+        <v>938</v>
       </c>
       <c r="F257" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G257" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H257" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I257" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J257" t="s">
-        <v>1578</v>
+        <v>1552</v>
+      </c>
+      <c r="K257" t="s">
+        <v>70</v>
       </c>
       <c r="L257" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="M257" t="s">
-        <v>46</v>
+        <v>780</v>
       </c>
       <c r="N257" t="s">
         <v>14</v>
@@ -17562,13 +17649,19 @@
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>1272</v>
+        <v>1187</v>
       </c>
       <c r="B258" t="s">
-        <v>1294</v>
+        <v>1203</v>
       </c>
       <c r="C258" t="s">
-        <v>1295</v>
+        <v>1204</v>
+      </c>
+      <c r="D258" t="s">
+        <v>433</v>
+      </c>
+      <c r="E258" t="s">
+        <v>865</v>
       </c>
       <c r="F258" t="s">
         <v>45</v>
@@ -17580,16 +17673,13 @@
         <v>30</v>
       </c>
       <c r="I258" t="s">
-        <v>1215</v>
+        <v>136</v>
       </c>
       <c r="J258" t="s">
         <v>1578</v>
       </c>
-      <c r="K258" t="s">
-        <v>51</v>
-      </c>
       <c r="L258" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M258" t="s">
         <v>46</v>
@@ -17606,40 +17696,34 @@
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>322</v>
+        <v>1272</v>
       </c>
       <c r="B259" t="s">
-        <v>749</v>
+        <v>1294</v>
       </c>
       <c r="C259" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D259" t="s">
-        <v>334</v>
-      </c>
-      <c r="E259" t="s">
-        <v>921</v>
+        <v>1295</v>
       </c>
       <c r="F259" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G259" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H259" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I259" t="s">
-        <v>103</v>
+        <v>1215</v>
       </c>
       <c r="J259" t="s">
-        <v>1522</v>
+        <v>1578</v>
       </c>
       <c r="K259" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L259" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="M259" t="s">
         <v>46</v>
@@ -17656,37 +17740,43 @@
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>563</v>
+        <v>322</v>
       </c>
       <c r="B260" t="s">
-        <v>609</v>
+        <v>749</v>
       </c>
       <c r="C260" t="s">
-        <v>1148</v>
+        <v>1122</v>
+      </c>
+      <c r="D260" t="s">
+        <v>334</v>
+      </c>
+      <c r="E260" t="s">
+        <v>921</v>
       </c>
       <c r="F260" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G260" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H260" t="s">
         <v>13</v>
       </c>
       <c r="I260" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="J260" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="K260" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="L260" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="M260" t="s">
-        <v>780</v>
+        <v>46</v>
       </c>
       <c r="N260" t="s">
         <v>14</v>
@@ -17700,25 +17790,19 @@
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>1262</v>
+        <v>563</v>
       </c>
       <c r="B261" t="s">
-        <v>1277</v>
+        <v>609</v>
       </c>
       <c r="C261" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D261" t="s">
-        <v>365</v>
-      </c>
-      <c r="E261" t="s">
-        <v>850</v>
+        <v>1148</v>
       </c>
       <c r="F261" t="s">
         <v>45</v>
       </c>
       <c r="G261" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H261" t="s">
         <v>13</v>
@@ -17727,13 +17811,16 @@
         <v>134</v>
       </c>
       <c r="J261" t="s">
-        <v>1525</v>
+        <v>1518</v>
+      </c>
+      <c r="K261" t="s">
+        <v>51</v>
       </c>
       <c r="L261" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="M261" t="s">
-        <v>46</v>
+        <v>780</v>
       </c>
       <c r="N261" t="s">
         <v>14</v>
@@ -17747,19 +17834,19 @@
     </row>
     <row r="262" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>615</v>
+        <v>1262</v>
       </c>
       <c r="B262" t="s">
-        <v>631</v>
+        <v>1277</v>
       </c>
       <c r="C262" t="s">
-        <v>1150</v>
+        <v>1286</v>
       </c>
       <c r="D262" t="s">
-        <v>632</v>
+        <v>365</v>
       </c>
       <c r="E262" t="s">
-        <v>952</v>
+        <v>850</v>
       </c>
       <c r="F262" t="s">
         <v>45</v>
@@ -17774,13 +17861,10 @@
         <v>134</v>
       </c>
       <c r="J262" t="s">
-        <v>1526</v>
-      </c>
-      <c r="K262" t="s">
-        <v>126</v>
+        <v>1525</v>
       </c>
       <c r="L262" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M262" t="s">
         <v>46</v>
@@ -17797,40 +17881,43 @@
     </row>
     <row r="263" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>521</v>
+        <v>615</v>
       </c>
       <c r="B263" t="s">
-        <v>525</v>
+        <v>631</v>
       </c>
       <c r="C263" t="s">
-        <v>1133</v>
+        <v>1150</v>
       </c>
       <c r="D263" t="s">
-        <v>365</v>
+        <v>632</v>
       </c>
       <c r="E263" t="s">
-        <v>850</v>
+        <v>952</v>
       </c>
       <c r="F263" t="s">
         <v>45</v>
       </c>
       <c r="G263" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H263" t="s">
         <v>13</v>
       </c>
       <c r="I263" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="J263" t="s">
         <v>1526</v>
       </c>
+      <c r="K263" t="s">
+        <v>126</v>
+      </c>
       <c r="L263" t="s">
         <v>172</v>
       </c>
       <c r="M263" t="s">
-        <v>780</v>
+        <v>46</v>
       </c>
       <c r="N263" t="s">
         <v>14</v>
@@ -17844,40 +17931,40 @@
     </row>
     <row r="264" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>345</v>
+        <v>521</v>
       </c>
       <c r="B264" t="s">
-        <v>366</v>
+        <v>525</v>
       </c>
       <c r="C264" t="s">
-        <v>1041</v>
+        <v>1133</v>
       </c>
       <c r="D264" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E264" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F264" t="s">
         <v>45</v>
       </c>
       <c r="G264" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H264" t="s">
         <v>13</v>
       </c>
       <c r="I264" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="J264" t="s">
-        <v>1553</v>
+        <v>1526</v>
       </c>
       <c r="L264" t="s">
-        <v>368</v>
+        <v>172</v>
       </c>
       <c r="M264" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="N264" t="s">
         <v>14</v>
@@ -17891,25 +17978,25 @@
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B265" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C265" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D265" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E265" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F265" t="s">
         <v>45</v>
       </c>
       <c r="G265" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="H265" t="s">
         <v>13</v>
@@ -17918,16 +18005,13 @@
         <v>134</v>
       </c>
       <c r="J265" t="s">
-        <v>1518</v>
-      </c>
-      <c r="K265" t="s">
-        <v>51</v>
+        <v>1553</v>
       </c>
       <c r="L265" t="s">
-        <v>172</v>
+        <v>368</v>
       </c>
       <c r="M265" t="s">
-        <v>46</v>
+        <v>781</v>
       </c>
       <c r="N265" t="s">
         <v>14</v>
@@ -17941,25 +18025,25 @@
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>532</v>
+        <v>346</v>
       </c>
       <c r="B266" t="s">
-        <v>536</v>
+        <v>369</v>
       </c>
       <c r="C266" t="s">
-        <v>1135</v>
+        <v>1042</v>
       </c>
       <c r="D266" t="s">
-        <v>537</v>
+        <v>370</v>
       </c>
       <c r="E266" t="s">
-        <v>934</v>
+        <v>852</v>
       </c>
       <c r="F266" t="s">
         <v>45</v>
       </c>
       <c r="G266" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="H266" t="s">
         <v>13</v>
@@ -17968,10 +18052,10 @@
         <v>134</v>
       </c>
       <c r="J266" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="K266" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="L266" t="s">
         <v>172</v>
@@ -17991,22 +18075,22 @@
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>574</v>
+        <v>532</v>
       </c>
       <c r="B267" t="s">
-        <v>758</v>
+        <v>536</v>
       </c>
       <c r="C267" t="s">
-        <v>1143</v>
+        <v>1135</v>
       </c>
       <c r="D267" t="s">
-        <v>591</v>
+        <v>537</v>
       </c>
       <c r="E267" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="F267" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G267" t="s">
         <v>31</v>
@@ -18018,13 +18102,13 @@
         <v>134</v>
       </c>
       <c r="J267" t="s">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="K267" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L267" t="s">
-        <v>315</v>
+        <v>172</v>
       </c>
       <c r="M267" t="s">
         <v>46</v>
@@ -18041,22 +18125,22 @@
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>181</v>
+        <v>574</v>
       </c>
       <c r="B268" t="s">
-        <v>190</v>
+        <v>758</v>
       </c>
       <c r="C268" t="s">
-        <v>1019</v>
+        <v>1143</v>
       </c>
       <c r="D268" t="s">
-        <v>191</v>
+        <v>591</v>
       </c>
       <c r="E268" t="s">
-        <v>832</v>
+        <v>941</v>
       </c>
       <c r="F268" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G268" t="s">
         <v>31</v>
@@ -18071,10 +18155,10 @@
         <v>1518</v>
       </c>
       <c r="K268" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="L268" t="s">
-        <v>172</v>
+        <v>315</v>
       </c>
       <c r="M268" t="s">
         <v>46</v>
@@ -18091,19 +18175,19 @@
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B269" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C269" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D269" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E269" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F269" t="s">
         <v>45</v>
@@ -18112,16 +18196,16 @@
         <v>31</v>
       </c>
       <c r="H269" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I269" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J269" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="K269" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L269" t="s">
         <v>172</v>
@@ -18141,19 +18225,19 @@
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B270" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C270" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D270" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E270" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F270" t="s">
         <v>45</v>
@@ -18162,19 +18246,19 @@
         <v>31</v>
       </c>
       <c r="H270" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I270" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J270" t="s">
-        <v>1518</v>
+        <v>1523</v>
       </c>
       <c r="K270" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L270" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M270" t="s">
         <v>46</v>
@@ -18191,19 +18275,19 @@
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B271" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C271" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="D271" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E271" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="F271" t="s">
         <v>45</v>
@@ -18212,19 +18296,19 @@
         <v>31</v>
       </c>
       <c r="H271" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I271" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="J271" t="s">
-        <v>1526</v>
+        <v>1518</v>
       </c>
       <c r="K271" t="s">
         <v>50</v>
       </c>
       <c r="L271" t="s">
-        <v>368</v>
+        <v>171</v>
       </c>
       <c r="M271" t="s">
         <v>46</v>
@@ -18241,13 +18325,19 @@
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>1478</v>
+        <v>180</v>
       </c>
       <c r="B272" t="s">
-        <v>1485</v>
+        <v>188</v>
       </c>
       <c r="C272" t="s">
-        <v>1486</v>
+        <v>1018</v>
+      </c>
+      <c r="D272" t="s">
+        <v>189</v>
+      </c>
+      <c r="E272" t="s">
+        <v>831</v>
       </c>
       <c r="F272" t="s">
         <v>45</v>
@@ -18259,16 +18349,16 @@
         <v>30</v>
       </c>
       <c r="I272" t="s">
-        <v>424</v>
+        <v>102</v>
       </c>
       <c r="J272" t="s">
         <v>1526</v>
       </c>
       <c r="K272" t="s">
-        <v>395</v>
+        <v>50</v>
       </c>
       <c r="L272" t="s">
-        <v>172</v>
+        <v>368</v>
       </c>
       <c r="M272" t="s">
         <v>46</v>
@@ -18285,37 +18375,34 @@
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>575</v>
+        <v>1478</v>
       </c>
       <c r="B273" t="s">
-        <v>592</v>
+        <v>1485</v>
       </c>
       <c r="C273" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D273" t="s">
-        <v>593</v>
-      </c>
-      <c r="E273" t="s">
-        <v>942</v>
+        <v>1486</v>
       </c>
       <c r="F273" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G273" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H273" t="s">
         <v>30</v>
       </c>
       <c r="I273" t="s">
-        <v>206</v>
+        <v>424</v>
       </c>
       <c r="J273" t="s">
-        <v>1554</v>
+        <v>1526</v>
+      </c>
+      <c r="K273" t="s">
+        <v>395</v>
       </c>
       <c r="L273" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="M273" t="s">
         <v>46</v>
@@ -18332,19 +18419,19 @@
     </row>
     <row r="274" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B274" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C274" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D274" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E274" t="s">
-        <v>987</v>
+        <v>942</v>
       </c>
       <c r="F274" t="s">
         <v>73</v>
@@ -18356,10 +18443,10 @@
         <v>30</v>
       </c>
       <c r="I274" t="s">
-        <v>424</v>
+        <v>206</v>
       </c>
       <c r="J274" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="L274" t="s">
         <v>90</v>
@@ -18379,19 +18466,19 @@
     </row>
     <row r="275" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
-        <v>1433</v>
+        <v>576</v>
       </c>
       <c r="B275" t="s">
-        <v>1434</v>
+        <v>594</v>
       </c>
       <c r="C275" t="s">
-        <v>1435</v>
+        <v>1145</v>
       </c>
       <c r="D275" t="s">
-        <v>1515</v>
+        <v>595</v>
       </c>
       <c r="E275" t="s">
-        <v>960</v>
+        <v>987</v>
       </c>
       <c r="F275" t="s">
         <v>73</v>
@@ -18403,19 +18490,16 @@
         <v>30</v>
       </c>
       <c r="I275" t="s">
-        <v>136</v>
+        <v>424</v>
       </c>
       <c r="J275" t="s">
-        <v>1526</v>
-      </c>
-      <c r="K275" t="s">
-        <v>70</v>
+        <v>1555</v>
       </c>
       <c r="L275" t="s">
         <v>90</v>
       </c>
       <c r="M275" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N275" t="s">
         <v>14</v>
@@ -18429,13 +18513,13 @@
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
-        <v>627</v>
+        <v>1433</v>
       </c>
       <c r="B276" t="s">
-        <v>649</v>
+        <v>1434</v>
       </c>
       <c r="C276" t="s">
-        <v>1157</v>
+        <v>1435</v>
       </c>
       <c r="D276" t="s">
         <v>1515</v>
@@ -18465,7 +18549,7 @@
         <v>90</v>
       </c>
       <c r="M276" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N276" t="s">
         <v>14</v>
@@ -18479,43 +18563,43 @@
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
-        <v>1224</v>
+        <v>627</v>
       </c>
       <c r="B277" t="s">
-        <v>1252</v>
+        <v>649</v>
       </c>
       <c r="C277" t="s">
-        <v>1253</v>
+        <v>1157</v>
       </c>
       <c r="D277" t="s">
-        <v>1254</v>
+        <v>1515</v>
       </c>
       <c r="E277" t="s">
-        <v>1248</v>
+        <v>960</v>
       </c>
       <c r="F277" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G277" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H277" t="s">
         <v>30</v>
       </c>
       <c r="I277" t="s">
-        <v>1255</v>
+        <v>136</v>
       </c>
       <c r="J277" t="s">
-        <v>1555</v>
+        <v>1526</v>
       </c>
       <c r="K277" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="L277" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M277" t="s">
-        <v>780</v>
+        <v>46</v>
       </c>
       <c r="N277" t="s">
         <v>14</v>
@@ -18529,40 +18613,40 @@
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="B278" t="s">
-        <v>1233</v>
+        <v>1252</v>
       </c>
       <c r="C278" t="s">
-        <v>1234</v>
+        <v>1253</v>
       </c>
       <c r="D278" t="s">
-        <v>1235</v>
+        <v>1254</v>
       </c>
       <c r="E278" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
       <c r="F278" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G278" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H278" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I278" t="s">
-        <v>134</v>
+        <v>1255</v>
       </c>
       <c r="J278" t="s">
-        <v>1526</v>
+        <v>1555</v>
       </c>
       <c r="K278" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="L278" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="M278" t="s">
         <v>780</v>
@@ -18579,19 +18663,25 @@
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
-        <v>1275</v>
+        <v>1229</v>
       </c>
       <c r="B279" t="s">
-        <v>1300</v>
+        <v>1233</v>
       </c>
       <c r="C279" t="s">
-        <v>1301</v>
+        <v>1234</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E279" t="s">
+        <v>1236</v>
       </c>
       <c r="F279" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G279" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H279" t="s">
         <v>13</v>
@@ -18600,13 +18690,16 @@
         <v>134</v>
       </c>
       <c r="J279" t="s">
-        <v>1522</v>
+        <v>1526</v>
+      </c>
+      <c r="K279" t="s">
+        <v>70</v>
       </c>
       <c r="L279" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="M279" t="s">
-        <v>46</v>
+        <v>780</v>
       </c>
       <c r="N279" t="s">
         <v>14</v>
@@ -18620,43 +18713,34 @@
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>1319</v>
+        <v>1275</v>
       </c>
       <c r="B280" t="s">
-        <v>1324</v>
+        <v>1300</v>
       </c>
       <c r="C280" t="s">
-        <v>1325</v>
-      </c>
-      <c r="D280" t="s">
-        <v>1326</v>
-      </c>
-      <c r="E280" t="s">
-        <v>1055</v>
+        <v>1301</v>
       </c>
       <c r="F280" t="s">
         <v>45</v>
       </c>
       <c r="G280" t="s">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="H280" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I280" t="s">
-        <v>424</v>
+        <v>134</v>
       </c>
       <c r="J280" t="s">
         <v>1522</v>
       </c>
-      <c r="K280" t="s">
-        <v>51</v>
-      </c>
       <c r="L280" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M280" t="s">
-        <v>781</v>
+        <v>46</v>
       </c>
       <c r="N280" t="s">
         <v>14</v>
@@ -18670,43 +18754,43 @@
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>561</v>
+        <v>1319</v>
       </c>
       <c r="B281" t="s">
-        <v>602</v>
+        <v>1324</v>
       </c>
       <c r="C281" t="s">
-        <v>1147</v>
+        <v>1325</v>
       </c>
       <c r="D281" t="s">
-        <v>421</v>
+        <v>1326</v>
       </c>
       <c r="E281" t="s">
-        <v>861</v>
+        <v>1055</v>
       </c>
       <c r="F281" t="s">
         <v>45</v>
       </c>
       <c r="G281" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="H281" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I281" t="s">
-        <v>103</v>
+        <v>424</v>
       </c>
       <c r="J281" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="K281" t="s">
         <v>51</v>
       </c>
       <c r="L281" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M281" t="s">
-        <v>46</v>
+        <v>781</v>
       </c>
       <c r="N281" t="s">
         <v>14</v>
@@ -18720,13 +18804,19 @@
     </row>
     <row r="282" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
-        <v>1320</v>
+        <v>561</v>
       </c>
       <c r="B282" t="s">
-        <v>1329</v>
+        <v>602</v>
       </c>
       <c r="C282" t="s">
-        <v>1330</v>
+        <v>1147</v>
+      </c>
+      <c r="D282" t="s">
+        <v>421</v>
+      </c>
+      <c r="E282" t="s">
+        <v>861</v>
       </c>
       <c r="F282" t="s">
         <v>45</v>
@@ -18738,7 +18828,7 @@
         <v>13</v>
       </c>
       <c r="I282" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="J282" t="s">
         <v>1526</v>
@@ -18747,7 +18837,7 @@
         <v>51</v>
       </c>
       <c r="L282" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M282" t="s">
         <v>46</v>
@@ -18764,19 +18854,13 @@
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>410</v>
+        <v>1320</v>
       </c>
       <c r="B283" t="s">
-        <v>419</v>
+        <v>1329</v>
       </c>
       <c r="C283" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D283" t="s">
-        <v>421</v>
-      </c>
-      <c r="E283" t="s">
-        <v>861</v>
+        <v>1330</v>
       </c>
       <c r="F283" t="s">
         <v>45</v>
@@ -18788,10 +18872,10 @@
         <v>13</v>
       </c>
       <c r="I283" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="J283" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="K283" t="s">
         <v>51</v>
@@ -18814,13 +18898,13 @@
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B284" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C284" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D284" t="s">
         <v>421</v>
@@ -18841,7 +18925,7 @@
         <v>103</v>
       </c>
       <c r="J284" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="K284" t="s">
         <v>51</v>
@@ -18864,13 +18948,13 @@
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B285" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="C285" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="D285" t="s">
         <v>421</v>
@@ -18900,7 +18984,7 @@
         <v>172</v>
       </c>
       <c r="M285" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N285" t="s">
         <v>14</v>
@@ -18914,19 +18998,19 @@
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
-        <v>618</v>
+        <v>418</v>
       </c>
       <c r="B286" t="s">
-        <v>637</v>
+        <v>434</v>
       </c>
       <c r="C286" t="s">
-        <v>637</v>
+        <v>1058</v>
       </c>
       <c r="D286" t="s">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="E286" t="s">
-        <v>955</v>
+        <v>861</v>
       </c>
       <c r="F286" t="s">
         <v>45</v>
@@ -18938,16 +19022,19 @@
         <v>13</v>
       </c>
       <c r="I286" t="s">
-        <v>424</v>
+        <v>103</v>
+      </c>
+      <c r="J286" t="s">
+        <v>1526</v>
       </c>
       <c r="K286" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="L286" t="s">
-        <v>368</v>
+        <v>172</v>
       </c>
       <c r="M286" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N286" t="s">
         <v>14</v>
@@ -18961,13 +19048,13 @@
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B287" t="s">
-        <v>768</v>
+        <v>637</v>
       </c>
       <c r="C287" t="s">
-        <v>1154</v>
+        <v>637</v>
       </c>
       <c r="D287" t="s">
         <v>638</v>
@@ -18988,10 +19075,10 @@
         <v>424</v>
       </c>
       <c r="K287" t="s">
-        <v>194</v>
+        <v>126</v>
       </c>
       <c r="L287" t="s">
-        <v>173</v>
+        <v>368</v>
       </c>
       <c r="M287" t="s">
         <v>46</v>
@@ -19008,19 +19095,19 @@
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
-        <v>560</v>
+        <v>622</v>
       </c>
       <c r="B288" t="s">
-        <v>601</v>
+        <v>768</v>
       </c>
       <c r="C288" t="s">
-        <v>601</v>
+        <v>1154</v>
       </c>
       <c r="D288" t="s">
-        <v>760</v>
+        <v>638</v>
       </c>
       <c r="E288" t="s">
-        <v>945</v>
+        <v>955</v>
       </c>
       <c r="F288" t="s">
         <v>45</v>
@@ -19032,19 +19119,16 @@
         <v>13</v>
       </c>
       <c r="I288" t="s">
-        <v>134</v>
-      </c>
-      <c r="J288" t="s">
-        <v>1526</v>
+        <v>424</v>
       </c>
       <c r="K288" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="L288" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M288" t="s">
-        <v>781</v>
+        <v>46</v>
       </c>
       <c r="N288" t="s">
         <v>14</v>
@@ -19058,19 +19142,19 @@
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="B289" t="s">
-        <v>526</v>
+        <v>601</v>
       </c>
       <c r="C289" t="s">
-        <v>1134</v>
+        <v>601</v>
       </c>
       <c r="D289" t="s">
-        <v>365</v>
+        <v>760</v>
       </c>
       <c r="E289" t="s">
-        <v>850</v>
+        <v>945</v>
       </c>
       <c r="F289" t="s">
         <v>45</v>
@@ -19082,16 +19166,19 @@
         <v>13</v>
       </c>
       <c r="I289" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="J289" t="s">
-        <v>1556</v>
+        <v>1526</v>
+      </c>
+      <c r="K289" t="s">
+        <v>51</v>
       </c>
       <c r="L289" t="s">
-        <v>528</v>
+        <v>172</v>
       </c>
       <c r="M289" t="s">
-        <v>46</v>
+        <v>781</v>
       </c>
       <c r="N289" t="s">
         <v>14</v>
@@ -19105,13 +19192,13 @@
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
-        <v>344</v>
+        <v>522</v>
       </c>
       <c r="B290" t="s">
-        <v>364</v>
+        <v>526</v>
       </c>
       <c r="C290" t="s">
-        <v>1040</v>
+        <v>1134</v>
       </c>
       <c r="D290" t="s">
         <v>365</v>
@@ -19123,7 +19210,7 @@
         <v>45</v>
       </c>
       <c r="G290" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H290" t="s">
         <v>13</v>
@@ -19132,10 +19219,10 @@
         <v>256</v>
       </c>
       <c r="J290" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="L290" t="s">
-        <v>368</v>
+        <v>528</v>
       </c>
       <c r="M290" t="s">
         <v>46</v>
@@ -19152,22 +19239,22 @@
     </row>
     <row r="291" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
-        <v>626</v>
+        <v>344</v>
       </c>
       <c r="B291" t="s">
-        <v>647</v>
+        <v>364</v>
       </c>
       <c r="C291" t="s">
-        <v>1156</v>
+        <v>1040</v>
       </c>
       <c r="D291" t="s">
-        <v>651</v>
+        <v>365</v>
       </c>
       <c r="E291" t="s">
-        <v>959</v>
+        <v>850</v>
       </c>
       <c r="F291" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G291" t="s">
         <v>49</v>
@@ -19176,16 +19263,16 @@
         <v>13</v>
       </c>
       <c r="I291" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="J291" t="s">
-        <v>648</v>
+        <v>1557</v>
       </c>
       <c r="L291" t="s">
-        <v>178</v>
+        <v>368</v>
       </c>
       <c r="M291" t="s">
-        <v>781</v>
+        <v>46</v>
       </c>
       <c r="N291" t="s">
         <v>14</v>
@@ -19199,25 +19286,25 @@
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
-        <v>652</v>
+        <v>626</v>
       </c>
       <c r="B292" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C292" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="D292" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="E292" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="F292" t="s">
         <v>73</v>
       </c>
       <c r="G292" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H292" t="s">
         <v>13</v>
@@ -19226,13 +19313,13 @@
         <v>134</v>
       </c>
       <c r="J292" t="s">
-        <v>1522</v>
+        <v>648</v>
       </c>
       <c r="L292" t="s">
-        <v>325</v>
+        <v>178</v>
       </c>
       <c r="M292" t="s">
-        <v>47</v>
+        <v>781</v>
       </c>
       <c r="N292" t="s">
         <v>14</v>
@@ -19246,25 +19333,25 @@
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
-        <v>571</v>
+        <v>652</v>
       </c>
       <c r="B293" t="s">
-        <v>580</v>
+        <v>656</v>
       </c>
       <c r="C293" t="s">
-        <v>1142</v>
+        <v>1158</v>
       </c>
       <c r="D293" t="s">
-        <v>581</v>
+        <v>658</v>
       </c>
       <c r="E293" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="F293" t="s">
         <v>73</v>
       </c>
       <c r="G293" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H293" t="s">
         <v>13</v>
@@ -19276,7 +19363,7 @@
         <v>1522</v>
       </c>
       <c r="L293" t="s">
-        <v>178</v>
+        <v>325</v>
       </c>
       <c r="M293" t="s">
         <v>47</v>
@@ -19293,22 +19380,22 @@
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="B294" t="s">
-        <v>538</v>
+        <v>580</v>
       </c>
       <c r="C294" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="D294" t="s">
-        <v>503</v>
+        <v>581</v>
       </c>
       <c r="E294" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
       <c r="F294" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G294" t="s">
         <v>49</v>
@@ -19320,16 +19407,13 @@
         <v>134</v>
       </c>
       <c r="J294" t="s">
-        <v>539</v>
-      </c>
-      <c r="K294" t="s">
-        <v>126</v>
+        <v>1522</v>
       </c>
       <c r="L294" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="M294" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N294" t="s">
         <v>14</v>
@@ -19343,22 +19427,22 @@
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="B295" t="s">
-        <v>755</v>
+        <v>538</v>
       </c>
       <c r="C295" t="s">
-        <v>1176</v>
+        <v>1136</v>
       </c>
       <c r="D295" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="E295" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="F295" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G295" t="s">
         <v>49</v>
@@ -19370,13 +19454,13 @@
         <v>134</v>
       </c>
       <c r="J295" t="s">
-        <v>1525</v>
+        <v>539</v>
       </c>
       <c r="K295" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="L295" t="s">
-        <v>518</v>
+        <v>172</v>
       </c>
       <c r="M295" t="s">
         <v>46</v>
@@ -19393,13 +19477,13 @@
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
-        <v>1457</v>
+        <v>513</v>
       </c>
       <c r="B296" t="s">
-        <v>1460</v>
+        <v>755</v>
       </c>
       <c r="C296" t="s">
-        <v>1459</v>
+        <v>1176</v>
       </c>
       <c r="D296" t="s">
         <v>517</v>
@@ -19408,7 +19492,7 @@
         <v>933</v>
       </c>
       <c r="F296" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G296" t="s">
         <v>49</v>
@@ -19420,16 +19504,16 @@
         <v>134</v>
       </c>
       <c r="J296" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="K296" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="L296" t="s">
-        <v>266</v>
+        <v>518</v>
       </c>
       <c r="M296" t="s">
-        <v>781</v>
+        <v>46</v>
       </c>
       <c r="N296" t="s">
         <v>14</v>
@@ -19443,25 +19527,25 @@
     </row>
     <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>653</v>
+        <v>1457</v>
       </c>
       <c r="B297" t="s">
-        <v>657</v>
+        <v>1460</v>
       </c>
       <c r="C297" t="s">
-        <v>1159</v>
+        <v>1459</v>
       </c>
       <c r="D297" t="s">
-        <v>1463</v>
+        <v>517</v>
       </c>
       <c r="E297" t="s">
-        <v>1464</v>
+        <v>933</v>
       </c>
       <c r="F297" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G297" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H297" t="s">
         <v>13</v>
@@ -19470,13 +19554,16 @@
         <v>134</v>
       </c>
       <c r="J297" t="s">
-        <v>1525</v>
+        <v>1522</v>
+      </c>
+      <c r="K297" t="s">
+        <v>51</v>
       </c>
       <c r="L297" t="s">
-        <v>178</v>
+        <v>266</v>
       </c>
       <c r="M297" t="s">
-        <v>47</v>
+        <v>781</v>
       </c>
       <c r="N297" t="s">
         <v>14</v>
@@ -19490,13 +19577,13 @@
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>1456</v>
+        <v>653</v>
       </c>
       <c r="B298" t="s">
-        <v>1462</v>
+        <v>657</v>
       </c>
       <c r="C298" t="s">
-        <v>1461</v>
+        <v>1159</v>
       </c>
       <c r="D298" t="s">
         <v>1463</v>
@@ -19505,10 +19592,10 @@
         <v>1464</v>
       </c>
       <c r="F298" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G298" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H298" t="s">
         <v>13</v>
@@ -19517,16 +19604,13 @@
         <v>134</v>
       </c>
       <c r="J298" t="s">
-        <v>1522</v>
-      </c>
-      <c r="K298" t="s">
-        <v>51</v>
+        <v>1525</v>
       </c>
       <c r="L298" t="s">
-        <v>266</v>
+        <v>178</v>
       </c>
       <c r="M298" t="s">
-        <v>781</v>
+        <v>47</v>
       </c>
       <c r="N298" t="s">
         <v>14</v>
@@ -19540,22 +19624,22 @@
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>1231</v>
+        <v>1456</v>
       </c>
       <c r="B299" t="s">
-        <v>1239</v>
+        <v>1462</v>
       </c>
       <c r="C299" t="s">
-        <v>1240</v>
+        <v>1461</v>
       </c>
       <c r="D299" t="s">
-        <v>1241</v>
+        <v>1463</v>
       </c>
       <c r="E299" t="s">
-        <v>1242</v>
+        <v>1464</v>
       </c>
       <c r="F299" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G299" t="s">
         <v>49</v>
@@ -19567,16 +19651,16 @@
         <v>134</v>
       </c>
       <c r="J299" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="K299" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L299" t="s">
-        <v>178</v>
+        <v>266</v>
       </c>
       <c r="M299" t="s">
-        <v>46</v>
+        <v>781</v>
       </c>
       <c r="N299" t="s">
         <v>14</v>
@@ -19590,37 +19674,40 @@
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
-        <v>666</v>
+        <v>1231</v>
       </c>
       <c r="B300" t="s">
-        <v>691</v>
+        <v>1239</v>
       </c>
       <c r="C300" t="s">
-        <v>1160</v>
+        <v>1240</v>
       </c>
       <c r="D300" t="s">
-        <v>694</v>
+        <v>1241</v>
       </c>
       <c r="E300" t="s">
-        <v>962</v>
+        <v>1242</v>
       </c>
       <c r="F300" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G300" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H300" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I300" t="s">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="J300" t="s">
-        <v>1562</v>
+        <v>1525</v>
+      </c>
+      <c r="K300" t="s">
+        <v>70</v>
       </c>
       <c r="L300" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="M300" t="s">
         <v>46</v>
@@ -19637,40 +19724,37 @@
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="B301" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="C301" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="D301" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E301" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="F301" t="s">
         <v>45</v>
       </c>
       <c r="G301" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H301" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I301" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="J301" t="s">
-        <v>1525</v>
-      </c>
-      <c r="K301" t="s">
-        <v>70</v>
+        <v>1562</v>
       </c>
       <c r="L301" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="M301" t="s">
         <v>46</v>
@@ -19687,19 +19771,19 @@
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="B302" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C302" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="D302" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E302" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F302" t="s">
         <v>45</v>
@@ -19714,13 +19798,13 @@
         <v>134</v>
       </c>
       <c r="J302" t="s">
-        <v>1556</v>
+        <v>1525</v>
       </c>
       <c r="K302" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="L302" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="M302" t="s">
         <v>46</v>
@@ -19737,37 +19821,40 @@
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>1209</v>
+        <v>678</v>
       </c>
       <c r="B303" t="s">
-        <v>1216</v>
+        <v>681</v>
       </c>
       <c r="C303" t="s">
-        <v>1214</v>
+        <v>1169</v>
       </c>
       <c r="D303" t="s">
-        <v>1217</v>
+        <v>698</v>
       </c>
       <c r="E303" t="s">
-        <v>1217</v>
+        <v>966</v>
       </c>
       <c r="F303" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G303" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H303" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I303" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J303" t="s">
-        <v>264</v>
+        <v>1556</v>
+      </c>
+      <c r="K303" t="s">
+        <v>133</v>
       </c>
       <c r="L303" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="M303" t="s">
         <v>46</v>
@@ -19784,31 +19871,34 @@
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
-        <v>1228</v>
+        <v>1209</v>
       </c>
       <c r="B304" t="s">
-        <v>1232</v>
+        <v>1216</v>
       </c>
       <c r="C304" t="s">
-        <v>1243</v>
+        <v>1214</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E304" t="s">
+        <v>1217</v>
       </c>
       <c r="F304" t="s">
         <v>73</v>
       </c>
       <c r="G304" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H304" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I304" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="J304" t="s">
-        <v>483</v>
-      </c>
-      <c r="K304" t="s">
-        <v>70</v>
+        <v>264</v>
       </c>
       <c r="L304" t="s">
         <v>90</v>
@@ -19828,22 +19918,16 @@
     </row>
     <row r="305" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
-        <v>1263</v>
+        <v>1228</v>
       </c>
       <c r="B305" t="s">
-        <v>1278</v>
+        <v>1232</v>
       </c>
       <c r="C305" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D305" t="s">
-        <v>365</v>
-      </c>
-      <c r="E305" t="s">
-        <v>850</v>
+        <v>1243</v>
       </c>
       <c r="F305" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G305" t="s">
         <v>49</v>
@@ -19852,10 +19936,13 @@
         <v>13</v>
       </c>
       <c r="I305" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="J305" t="s">
-        <v>1525</v>
+        <v>483</v>
+      </c>
+      <c r="K305" t="s">
+        <v>70</v>
       </c>
       <c r="L305" t="s">
         <v>90</v>
@@ -19875,25 +19962,25 @@
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
-        <v>375</v>
+        <v>1263</v>
       </c>
       <c r="B306" t="s">
-        <v>734</v>
+        <v>1278</v>
       </c>
       <c r="C306" t="s">
-        <v>1046</v>
+        <v>1285</v>
       </c>
       <c r="D306" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="E306" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="F306" t="s">
         <v>45</v>
       </c>
       <c r="G306" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H306" t="s">
         <v>13</v>
@@ -19902,10 +19989,10 @@
         <v>134</v>
       </c>
       <c r="J306" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="L306" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M306" t="s">
         <v>46</v>
@@ -19922,25 +20009,25 @@
     </row>
     <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>179</v>
+        <v>375</v>
       </c>
       <c r="B307" t="s">
-        <v>184</v>
+        <v>734</v>
       </c>
       <c r="C307" t="s">
-        <v>1017</v>
+        <v>1046</v>
       </c>
       <c r="D307" t="s">
-        <v>185</v>
+        <v>380</v>
       </c>
       <c r="E307" t="s">
-        <v>970</v>
+        <v>854</v>
       </c>
       <c r="F307" t="s">
         <v>45</v>
       </c>
       <c r="G307" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H307" t="s">
         <v>13</v>
@@ -19949,13 +20036,10 @@
         <v>134</v>
       </c>
       <c r="J307" t="s">
-        <v>186</v>
-      </c>
-      <c r="K307" t="s">
-        <v>70</v>
+        <v>1522</v>
       </c>
       <c r="L307" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="M307" t="s">
         <v>46</v>
@@ -19972,25 +20056,25 @@
     </row>
     <row r="308" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>349</v>
+        <v>179</v>
       </c>
       <c r="B308" t="s">
-        <v>374</v>
+        <v>184</v>
       </c>
       <c r="C308" t="s">
-        <v>1045</v>
+        <v>1017</v>
       </c>
       <c r="D308" t="s">
-        <v>373</v>
+        <v>185</v>
       </c>
       <c r="E308" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="F308" t="s">
         <v>45</v>
       </c>
       <c r="G308" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H308" t="s">
         <v>13</v>
@@ -19999,7 +20083,10 @@
         <v>134</v>
       </c>
       <c r="J308" t="s">
-        <v>264</v>
+        <v>186</v>
+      </c>
+      <c r="K308" t="s">
+        <v>70</v>
       </c>
       <c r="L308" t="s">
         <v>187</v>
@@ -20019,25 +20106,25 @@
     </row>
     <row r="309" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>1265</v>
+        <v>349</v>
       </c>
       <c r="B309" t="s">
-        <v>1279</v>
+        <v>374</v>
       </c>
       <c r="C309" t="s">
-        <v>1279</v>
+        <v>1045</v>
       </c>
       <c r="D309" t="s">
-        <v>1288</v>
+        <v>373</v>
       </c>
       <c r="E309" t="s">
-        <v>1287</v>
+        <v>975</v>
       </c>
       <c r="F309" t="s">
         <v>45</v>
       </c>
       <c r="G309" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H309" t="s">
         <v>13</v>
@@ -20049,7 +20136,7 @@
         <v>264</v>
       </c>
       <c r="L309" t="s">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="M309" t="s">
         <v>46</v>
@@ -20066,22 +20153,22 @@
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>58</v>
+        <v>1265</v>
       </c>
       <c r="B310" t="s">
-        <v>67</v>
+        <v>1279</v>
       </c>
       <c r="C310" t="s">
-        <v>1070</v>
+        <v>1279</v>
       </c>
       <c r="D310" t="s">
-        <v>276</v>
+        <v>1288</v>
       </c>
       <c r="E310" t="s">
-        <v>875</v>
+        <v>1287</v>
       </c>
       <c r="F310" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G310" t="s">
         <v>49</v>
@@ -20093,10 +20180,10 @@
         <v>134</v>
       </c>
       <c r="J310" t="s">
-        <v>1522</v>
+        <v>264</v>
       </c>
       <c r="L310" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M310" t="s">
         <v>46</v>
@@ -20113,19 +20200,19 @@
     </row>
     <row r="311" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="B311" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="C311" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D311" t="s">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="E311" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F311" t="s">
         <v>73</v>
@@ -20140,16 +20227,13 @@
         <v>134</v>
       </c>
       <c r="J311" t="s">
-        <v>104</v>
-      </c>
-      <c r="K311" t="s">
-        <v>126</v>
+        <v>1522</v>
       </c>
       <c r="L311" t="s">
         <v>172</v>
       </c>
       <c r="M311" t="s">
-        <v>780</v>
+        <v>46</v>
       </c>
       <c r="N311" t="s">
         <v>14</v>
@@ -20163,19 +20247,25 @@
     </row>
     <row r="312" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
-        <v>664</v>
+        <v>119</v>
       </c>
       <c r="B312" t="s">
-        <v>692</v>
+        <v>124</v>
       </c>
       <c r="C312" t="s">
-        <v>1171</v>
+        <v>1072</v>
+      </c>
+      <c r="D312" t="s">
+        <v>125</v>
+      </c>
+      <c r="E312" t="s">
+        <v>877</v>
       </c>
       <c r="F312" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G312" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H312" t="s">
         <v>13</v>
@@ -20184,13 +20274,16 @@
         <v>134</v>
       </c>
       <c r="J312" t="s">
-        <v>1575</v>
+        <v>104</v>
+      </c>
+      <c r="K312" t="s">
+        <v>126</v>
       </c>
       <c r="L312" t="s">
         <v>172</v>
       </c>
       <c r="M312" t="s">
-        <v>46</v>
+        <v>780</v>
       </c>
       <c r="N312" t="s">
         <v>14</v>
@@ -20204,13 +20297,13 @@
     </row>
     <row r="313" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B313" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C313" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="F313" t="s">
         <v>45</v>
@@ -20245,13 +20338,13 @@
     </row>
     <row r="314" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>783</v>
+        <v>665</v>
       </c>
       <c r="B314" t="s">
-        <v>786</v>
+        <v>693</v>
       </c>
       <c r="C314" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F314" t="s">
         <v>45</v>
@@ -20268,9 +20361,6 @@
       <c r="J314" t="s">
         <v>1575</v>
       </c>
-      <c r="K314" t="s">
-        <v>51</v>
-      </c>
       <c r="L314" t="s">
         <v>172</v>
       </c>
@@ -20289,13 +20379,13 @@
     </row>
     <row r="315" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
-        <v>1355</v>
+        <v>783</v>
       </c>
       <c r="B315" t="s">
-        <v>1376</v>
+        <v>786</v>
       </c>
       <c r="C315" t="s">
-        <v>1376</v>
+        <v>1173</v>
       </c>
       <c r="F315" t="s">
         <v>45</v>
@@ -20333,13 +20423,13 @@
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
-        <v>1581</v>
+        <v>1355</v>
       </c>
       <c r="B316" t="s">
-        <v>1574</v>
+        <v>1376</v>
       </c>
       <c r="C316" t="s">
-        <v>1579</v>
+        <v>1376</v>
       </c>
       <c r="F316" t="s">
         <v>45</v>
@@ -20348,10 +20438,10 @@
         <v>31</v>
       </c>
       <c r="H316" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I316" t="s">
-        <v>424</v>
+        <v>134</v>
       </c>
       <c r="J316" t="s">
         <v>1575</v>
@@ -20377,13 +20467,13 @@
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
-        <v>1266</v>
+        <v>1581</v>
       </c>
       <c r="B317" t="s">
-        <v>1280</v>
+        <v>1574</v>
       </c>
       <c r="C317" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F317" t="s">
         <v>45</v>
@@ -20395,7 +20485,10 @@
         <v>30</v>
       </c>
       <c r="I317" t="s">
-        <v>102</v>
+        <v>424</v>
+      </c>
+      <c r="J317" t="s">
+        <v>1575</v>
       </c>
       <c r="K317" t="s">
         <v>51</v>
@@ -20418,37 +20511,43 @@
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
-        <v>1273</v>
+        <v>1582</v>
       </c>
       <c r="B318" t="s">
-        <v>1296</v>
+        <v>1591</v>
       </c>
       <c r="C318" t="s">
-        <v>1297</v>
+        <v>1597</v>
       </c>
       <c r="D318" t="s">
-        <v>1254</v>
+        <v>1588</v>
       </c>
       <c r="E318" t="s">
-        <v>925</v>
+        <v>1589</v>
       </c>
       <c r="F318" t="s">
         <v>45</v>
       </c>
       <c r="G318" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H318" t="s">
         <v>13</v>
       </c>
       <c r="I318" t="s">
-        <v>134</v>
+        <v>1590</v>
+      </c>
+      <c r="J318" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K318" t="s">
+        <v>51</v>
       </c>
       <c r="L318" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="M318" t="s">
-        <v>46</v>
+        <v>780</v>
       </c>
       <c r="N318" t="s">
         <v>14</v>
@@ -20462,34 +20561,28 @@
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
-        <v>435</v>
+        <v>1266</v>
       </c>
       <c r="B319" t="s">
-        <v>502</v>
+        <v>1280</v>
       </c>
       <c r="C319" t="s">
-        <v>1177</v>
-      </c>
-      <c r="D319" t="s">
-        <v>503</v>
-      </c>
-      <c r="E319" t="s">
-        <v>925</v>
+        <v>1580</v>
       </c>
       <c r="F319" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G319" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H319" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I319" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="K319" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="L319" t="s">
         <v>172</v>
@@ -20509,16 +20602,16 @@
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>673</v>
+        <v>1273</v>
       </c>
       <c r="B320" t="s">
-        <v>684</v>
+        <v>1296</v>
       </c>
       <c r="C320" t="s">
-        <v>1174</v>
+        <v>1297</v>
       </c>
       <c r="D320" t="s">
-        <v>503</v>
+        <v>1254</v>
       </c>
       <c r="E320" t="s">
         <v>925</v>
@@ -20535,11 +20628,8 @@
       <c r="I320" t="s">
         <v>134</v>
       </c>
-      <c r="K320" t="s">
-        <v>126</v>
-      </c>
       <c r="L320" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M320" t="s">
         <v>46</v>
@@ -20556,19 +20646,19 @@
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
-        <v>547</v>
+        <v>435</v>
       </c>
       <c r="B321" t="s">
-        <v>555</v>
+        <v>502</v>
       </c>
       <c r="C321" t="s">
-        <v>1141</v>
+        <v>1177</v>
       </c>
       <c r="D321" t="s">
-        <v>556</v>
+        <v>503</v>
       </c>
       <c r="E321" t="s">
-        <v>939</v>
+        <v>925</v>
       </c>
       <c r="F321" t="s">
         <v>73</v>
@@ -20582,17 +20672,14 @@
       <c r="I321" t="s">
         <v>134</v>
       </c>
-      <c r="J321" t="s">
-        <v>264</v>
-      </c>
       <c r="K321" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="L321" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="M321" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N321" t="s">
         <v>14</v>
@@ -20606,25 +20693,25 @@
     </row>
     <row r="322" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>281</v>
+        <v>673</v>
       </c>
       <c r="B322" t="s">
-        <v>297</v>
+        <v>684</v>
       </c>
       <c r="C322" t="s">
-        <v>1111</v>
+        <v>1174</v>
       </c>
       <c r="D322" t="s">
-        <v>298</v>
+        <v>503</v>
       </c>
       <c r="E322" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="F322" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G322" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H322" t="s">
         <v>13</v>
@@ -20632,14 +20719,14 @@
       <c r="I322" t="s">
         <v>134</v>
       </c>
-      <c r="J322" t="s">
-        <v>264</v>
+      <c r="K322" t="s">
+        <v>126</v>
       </c>
       <c r="L322" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="M322" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N322" t="s">
         <v>14</v>
@@ -20653,25 +20740,25 @@
     </row>
     <row r="323" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
-        <v>1318</v>
+        <v>547</v>
       </c>
       <c r="B323" t="s">
-        <v>1323</v>
+        <v>555</v>
       </c>
       <c r="C323" t="s">
-        <v>1323</v>
+        <v>1141</v>
       </c>
       <c r="D323" t="s">
-        <v>1327</v>
+        <v>556</v>
       </c>
       <c r="E323" t="s">
-        <v>1328</v>
+        <v>939</v>
       </c>
       <c r="F323" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G323" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H323" t="s">
         <v>13</v>
@@ -20680,16 +20767,16 @@
         <v>134</v>
       </c>
       <c r="J323" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="K323" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="L323" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="M323" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N323" t="s">
         <v>14</v>
@@ -20703,16 +20790,22 @@
     </row>
     <row r="324" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
-        <v>1455</v>
+        <v>281</v>
       </c>
       <c r="B324" t="s">
-        <v>1468</v>
+        <v>297</v>
       </c>
       <c r="C324" t="s">
-        <v>1469</v>
+        <v>1111</v>
+      </c>
+      <c r="D324" t="s">
+        <v>298</v>
+      </c>
+      <c r="E324" t="s">
+        <v>914</v>
       </c>
       <c r="F324" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G324" t="s">
         <v>31</v>
@@ -20724,16 +20817,13 @@
         <v>134</v>
       </c>
       <c r="J324" t="s">
-        <v>1458</v>
-      </c>
-      <c r="K324" t="s">
-        <v>51</v>
+        <v>264</v>
       </c>
       <c r="L324" t="s">
-        <v>266</v>
+        <v>90</v>
       </c>
       <c r="M324" t="s">
-        <v>781</v>
+        <v>47</v>
       </c>
       <c r="N324" t="s">
         <v>14</v>
@@ -20747,34 +20837,34 @@
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
-        <v>416</v>
+        <v>1318</v>
       </c>
       <c r="B325" t="s">
-        <v>430</v>
+        <v>1323</v>
       </c>
       <c r="C325" t="s">
-        <v>1056</v>
+        <v>1323</v>
       </c>
       <c r="D325" t="s">
-        <v>431</v>
+        <v>1327</v>
       </c>
       <c r="E325" t="s">
-        <v>864</v>
+        <v>1328</v>
       </c>
       <c r="F325" t="s">
         <v>45</v>
       </c>
       <c r="G325" t="s">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="H325" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I325" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J325" t="s">
-        <v>1526</v>
+        <v>249</v>
       </c>
       <c r="K325" t="s">
         <v>51</v>
@@ -20796,26 +20886,20 @@
       </c>
     </row>
     <row r="326" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A326" t="s">
-        <v>12</v>
+      <c r="A326" s="1" t="s">
+        <v>1455</v>
       </c>
       <c r="B326" t="s">
-        <v>142</v>
+        <v>1468</v>
       </c>
       <c r="C326" t="s">
-        <v>142</v>
-      </c>
-      <c r="D326" t="s">
-        <v>270</v>
-      </c>
-      <c r="E326" t="s">
-        <v>790</v>
+        <v>1469</v>
       </c>
       <c r="F326" t="s">
         <v>45</v>
       </c>
       <c r="G326" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H326" t="s">
         <v>13</v>
@@ -20824,16 +20908,16 @@
         <v>134</v>
       </c>
       <c r="J326" t="s">
-        <v>177</v>
+        <v>1458</v>
       </c>
       <c r="K326" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="L326" t="s">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="M326" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N326" t="s">
         <v>14</v>
@@ -20847,25 +20931,31 @@
     </row>
     <row r="327" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
-        <v>1181</v>
+        <v>416</v>
       </c>
       <c r="B327" t="s">
-        <v>1189</v>
+        <v>430</v>
       </c>
       <c r="C327" t="s">
-        <v>1189</v>
+        <v>1056</v>
+      </c>
+      <c r="D327" t="s">
+        <v>431</v>
+      </c>
+      <c r="E327" t="s">
+        <v>864</v>
       </c>
       <c r="F327" t="s">
         <v>45</v>
       </c>
       <c r="G327" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="H327" t="s">
         <v>30</v>
       </c>
       <c r="I327" t="s">
-        <v>424</v>
+        <v>136</v>
       </c>
       <c r="J327" t="s">
         <v>1526</v>
@@ -20890,23 +20980,23 @@
       </c>
     </row>
     <row r="328" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A328" s="1" t="s">
-        <v>511</v>
+      <c r="A328" t="s">
+        <v>12</v>
       </c>
       <c r="B328" t="s">
-        <v>515</v>
+        <v>142</v>
       </c>
       <c r="C328" t="s">
-        <v>1131</v>
+        <v>142</v>
       </c>
       <c r="D328" t="s">
-        <v>549</v>
+        <v>270</v>
       </c>
       <c r="E328" t="s">
-        <v>931</v>
+        <v>790</v>
       </c>
       <c r="F328" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G328" t="s">
         <v>49</v>
@@ -20915,19 +21005,19 @@
         <v>13</v>
       </c>
       <c r="I328" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="J328" t="s">
-        <v>1526</v>
+        <v>177</v>
       </c>
       <c r="K328" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="L328" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="M328" t="s">
-        <v>46</v>
+        <v>780</v>
       </c>
       <c r="N328" t="s">
         <v>14</v>
@@ -20941,13 +21031,13 @@
     </row>
     <row r="329" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
-        <v>1475</v>
+        <v>1181</v>
       </c>
       <c r="B329" t="s">
-        <v>1490</v>
+        <v>1189</v>
       </c>
       <c r="C329" t="s">
-        <v>1491</v>
+        <v>1189</v>
       </c>
       <c r="F329" t="s">
         <v>45</v>
@@ -20956,16 +21046,19 @@
         <v>31</v>
       </c>
       <c r="H329" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I329" t="s">
-        <v>134</v>
+        <v>424</v>
       </c>
       <c r="J329" t="s">
-        <v>104</v>
+        <v>1526</v>
+      </c>
+      <c r="K329" t="s">
+        <v>51</v>
       </c>
       <c r="L329" t="s">
-        <v>368</v>
+        <v>172</v>
       </c>
       <c r="M329" t="s">
         <v>46</v>
@@ -20982,22 +21075,22 @@
     </row>
     <row r="330" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
-        <v>1570</v>
+        <v>511</v>
       </c>
       <c r="B330" t="s">
-        <v>1571</v>
+        <v>515</v>
       </c>
       <c r="C330" t="s">
-        <v>1571</v>
+        <v>1131</v>
       </c>
       <c r="D330" t="s">
-        <v>1572</v>
+        <v>549</v>
       </c>
       <c r="E330" t="s">
-        <v>1573</v>
+        <v>931</v>
       </c>
       <c r="F330" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G330" t="s">
         <v>49</v>
@@ -21006,27 +21099,365 @@
         <v>13</v>
       </c>
       <c r="I330" t="s">
+        <v>103</v>
+      </c>
+      <c r="J330" t="s">
+        <v>1526</v>
+      </c>
+      <c r="K330" t="s">
+        <v>70</v>
+      </c>
+      <c r="L330" t="s">
+        <v>187</v>
+      </c>
+      <c r="M330" t="s">
+        <v>46</v>
+      </c>
+      <c r="N330" t="s">
+        <v>14</v>
+      </c>
+      <c r="O330" t="s">
+        <v>15</v>
+      </c>
+      <c r="P330" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="331" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A331" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B331" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C331" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F331" t="s">
+        <v>45</v>
+      </c>
+      <c r="G331" t="s">
+        <v>31</v>
+      </c>
+      <c r="H331" t="s">
+        <v>13</v>
+      </c>
+      <c r="I331" t="s">
         <v>134</v>
       </c>
-      <c r="J330" t="s">
+      <c r="J331" t="s">
+        <v>104</v>
+      </c>
+      <c r="L331" t="s">
+        <v>368</v>
+      </c>
+      <c r="M331" t="s">
+        <v>46</v>
+      </c>
+      <c r="N331" t="s">
+        <v>14</v>
+      </c>
+      <c r="O331" t="s">
+        <v>15</v>
+      </c>
+      <c r="P331" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="332" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A332" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D332" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E332" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F332" t="s">
+        <v>45</v>
+      </c>
+      <c r="G332" t="s">
+        <v>49</v>
+      </c>
+      <c r="H332" t="s">
+        <v>13</v>
+      </c>
+      <c r="I332" t="s">
+        <v>134</v>
+      </c>
+      <c r="J332" t="s">
         <v>1552</v>
       </c>
-      <c r="K330" t="s">
+      <c r="K332" t="s">
         <v>51</v>
       </c>
-      <c r="L330" t="s">
+      <c r="L332" t="s">
         <v>172</v>
       </c>
-      <c r="M330" t="s">
-        <v>46</v>
-      </c>
-      <c r="N330" t="s">
-        <v>14</v>
-      </c>
-      <c r="O330" t="s">
-        <v>15</v>
-      </c>
-      <c r="P330" t="s">
+      <c r="M332" t="s">
+        <v>46</v>
+      </c>
+      <c r="N332" t="s">
+        <v>14</v>
+      </c>
+      <c r="O332" t="s">
+        <v>15</v>
+      </c>
+      <c r="P332" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="333" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A333" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B333" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C333" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E333" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F333" t="s">
+        <v>45</v>
+      </c>
+      <c r="G333" t="s">
+        <v>31</v>
+      </c>
+      <c r="H333" t="s">
+        <v>13</v>
+      </c>
+      <c r="I333" t="s">
+        <v>1590</v>
+      </c>
+      <c r="J333" t="s">
+        <v>1526</v>
+      </c>
+      <c r="K333" t="s">
+        <v>51</v>
+      </c>
+      <c r="L333" t="s">
+        <v>172</v>
+      </c>
+      <c r="M333" t="s">
+        <v>46</v>
+      </c>
+      <c r="N333" t="s">
+        <v>14</v>
+      </c>
+      <c r="O333" t="s">
+        <v>15</v>
+      </c>
+      <c r="P333" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="334" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A334" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B334" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C334" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D334" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E334" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F334" t="s">
+        <v>45</v>
+      </c>
+      <c r="G334" t="s">
+        <v>31</v>
+      </c>
+      <c r="H334" t="s">
+        <v>13</v>
+      </c>
+      <c r="I334" t="s">
+        <v>1590</v>
+      </c>
+      <c r="K334" t="s">
+        <v>51</v>
+      </c>
+      <c r="L334" t="s">
+        <v>172</v>
+      </c>
+      <c r="M334" t="s">
+        <v>781</v>
+      </c>
+      <c r="N334" t="s">
+        <v>14</v>
+      </c>
+      <c r="O334" t="s">
+        <v>15</v>
+      </c>
+      <c r="P334" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="335" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A335" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B335" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C335" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D335" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E335" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F335" t="s">
+        <v>45</v>
+      </c>
+      <c r="G335" t="s">
+        <v>31</v>
+      </c>
+      <c r="H335" t="s">
+        <v>13</v>
+      </c>
+      <c r="I335" t="s">
+        <v>1590</v>
+      </c>
+      <c r="J335" t="s">
+        <v>1518</v>
+      </c>
+      <c r="K335" t="s">
+        <v>51</v>
+      </c>
+      <c r="L335" t="s">
+        <v>172</v>
+      </c>
+      <c r="M335" t="s">
+        <v>46</v>
+      </c>
+      <c r="N335" t="s">
+        <v>14</v>
+      </c>
+      <c r="O335" t="s">
+        <v>15</v>
+      </c>
+      <c r="P335" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="336" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A336" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B336" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C336" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D336" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E336" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F336" t="s">
+        <v>45</v>
+      </c>
+      <c r="G336" t="s">
+        <v>31</v>
+      </c>
+      <c r="H336" t="s">
+        <v>13</v>
+      </c>
+      <c r="I336" t="s">
+        <v>1590</v>
+      </c>
+      <c r="J336" t="s">
+        <v>1603</v>
+      </c>
+      <c r="K336" t="s">
+        <v>133</v>
+      </c>
+      <c r="L336" t="s">
+        <v>172</v>
+      </c>
+      <c r="M336" t="s">
+        <v>46</v>
+      </c>
+      <c r="N336" t="s">
+        <v>14</v>
+      </c>
+      <c r="O336" t="s">
+        <v>15</v>
+      </c>
+      <c r="P336" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="337" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A337" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B337" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C337" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D337" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F337" t="s">
+        <v>45</v>
+      </c>
+      <c r="G337" t="s">
+        <v>31</v>
+      </c>
+      <c r="H337" t="s">
+        <v>13</v>
+      </c>
+      <c r="I337" t="s">
+        <v>1590</v>
+      </c>
+      <c r="J337" t="s">
+        <v>1526</v>
+      </c>
+      <c r="K337" t="s">
+        <v>51</v>
+      </c>
+      <c r="L337" t="s">
+        <v>172</v>
+      </c>
+      <c r="M337" t="s">
+        <v>48</v>
+      </c>
+      <c r="N337" t="s">
+        <v>14</v>
+      </c>
+      <c r="O337" t="s">
+        <v>15</v>
+      </c>
+      <c r="P337" t="s">
         <v>16</v>
       </c>
     </row>
